--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NQ_Trades" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MNQ_Trades" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="US_Stocks" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fee_Breakdown" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="NQ_Trades" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="MNQ_Trades" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="US_Stocks" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Fee_Breakdown" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Summary" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -63,7 +63,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -95,8 +95,13 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -110,11 +115,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -144,6 +177,11 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -509,8 +547,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:Z4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -775,6 +813,102 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>15:28 ET</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>29628.5</v>
+      </c>
+      <c r="I4" s="9" t="n">
+        <v>29625</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>29650</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="9" t="n">
+        <v>153.77</v>
+      </c>
+      <c r="M4" s="9" t="n">
+        <v>238.13</v>
+      </c>
+      <c r="N4" s="9" t="n">
+        <v>153.77</v>
+      </c>
+      <c r="O4" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="P4" s="9" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q4" s="9" t="n">
+        <v>46.13</v>
+      </c>
+      <c r="R4" s="9" t="n">
+        <v>84.36</v>
+      </c>
+      <c r="S4" s="9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T4" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" s="9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="V4" s="9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W4" s="9" t="n">
+        <v>76.95999999999999</v>
+      </c>
+      <c r="X4" s="9" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Y4" s="9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" s="9" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:Z1"/>
@@ -789,8 +923,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:Z4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -1055,6 +1189,102 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>14:14 ET</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="n">
+        <v>29628.25</v>
+      </c>
+      <c r="I4" s="11" t="n">
+        <v>29625</v>
+      </c>
+      <c r="J4" s="11" t="n">
+        <v>29650</v>
+      </c>
+      <c r="K4" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" s="11" t="n">
+        <v>22.38</v>
+      </c>
+      <c r="M4" s="11" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="N4" s="11" t="n">
+        <v>67.14</v>
+      </c>
+      <c r="O4" s="11" t="n">
+        <v>150</v>
+      </c>
+      <c r="P4" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q4" s="11" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="R4" s="11" t="n">
+        <v>-38.97</v>
+      </c>
+      <c r="S4" s="11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T4" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" s="11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="V4" s="11" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="W4" s="11" t="n">
+        <v>-43.89</v>
+      </c>
+      <c r="X4" s="11" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="Y4" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" s="11" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:Z1"/>
@@ -1070,7 +1300,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -1169,8 +1399,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
@@ -1304,6 +1534,76 @@
       <c r="I4" s="10" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — STOP LOSS</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1622,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -1525,9 +1825,9 @@
           <t>MNQ — Bull Call Spread</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="13" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1710,9 +2010,9 @@
           <t>Combined Totals</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="13" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -547,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:Z5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -909,6 +909,102 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>12:30 ET</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>29689.5</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>29675</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>29700</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L5" s="9" t="n">
+        <v>187.07</v>
+      </c>
+      <c r="M5" s="9" t="n">
+        <v>305.97</v>
+      </c>
+      <c r="N5" s="9" t="n">
+        <v>972.35</v>
+      </c>
+      <c r="O5" s="9" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P5" s="9" t="n">
+        <v>750</v>
+      </c>
+      <c r="Q5" s="9" t="n">
+        <v>280.6</v>
+      </c>
+      <c r="R5" s="9" t="n">
+        <v>594.5</v>
+      </c>
+      <c r="S5" s="9" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="T5" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="U5" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V5" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="W5" s="9" t="n">
+        <v>557.5</v>
+      </c>
+      <c r="X5" s="9" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Y5" s="9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" s="9" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:Z1"/>
@@ -923,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:Z5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1280,6 +1376,102 @@
         <v>1000</v>
       </c>
       <c r="Z4" s="11" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>13:32 ET</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>29689.75</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>29675</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>29700</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="L5" s="9" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="M5" s="9" t="n">
+        <v>28.82</v>
+      </c>
+      <c r="N5" s="9" t="n">
+        <v>987.3</v>
+      </c>
+      <c r="O5" s="9" t="n">
+        <v>2250</v>
+      </c>
+      <c r="P5" s="9" t="n">
+        <v>675</v>
+      </c>
+      <c r="Q5" s="9" t="n">
+        <v>274.05</v>
+      </c>
+      <c r="R5" s="9" t="n">
+        <v>383.4</v>
+      </c>
+      <c r="S5" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="T5" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="U5" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V5" s="9" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="W5" s="9" t="n">
+        <v>309.6</v>
+      </c>
+      <c r="X5" s="9" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Y5" s="9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" s="9" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -1399,7 +1591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1604,6 +1796,76 @@
       <c r="I6" s="10" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — STOP LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — PROFIT</t>
         </is>
       </c>
     </row>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -12,6 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="US_Stocks" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fee_Breakdown" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NIFTY_Trades" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BANKNIFTY_Trades" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skipped_Days" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -63,7 +66,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -90,8 +93,18 @@
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -105,11 +118,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -132,6 +173,14 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -499,7 +548,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Z2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -683,7 +732,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Z2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -867,7 +916,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -967,7 +1016,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
@@ -1049,7 +1098,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -1252,9 +1301,9 @@
           <t>MNQ — Bull Call Spread</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1437,9 +1486,9 @@
           <t>Combined Totals</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -1489,4 +1538,1328 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AK5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>NIFTY — Bull Call Spread &amp; Bear Put Spread | Paper Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="35" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Instrument</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Expiry</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Expiry Type</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>DTE</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Entry Time</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Exit Time</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Spot at Entry</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Prev Close</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Buy Strike</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Sell Strike</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Lots</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Lot Size</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Entry Premium</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Exit Premium</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost (₹)</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>Capital Used (₹)</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>Max Profit (₹)</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Target (₹)</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>Stop Loss (₹)</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>Gross P&amp;L (₹)</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>Brokerage (₹)</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>STT (₹)</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>SEBI Fee (₹)</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>Stamp Duty (₹)</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>GST (₹)</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>Total Fees (₹)</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>Net P&amp;L (₹)</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>Budget (₹)</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>Mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>10:50 IST</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="n">
+        <v>23350</v>
+      </c>
+      <c r="K3" s="11" t="n">
+        <v>23200</v>
+      </c>
+      <c r="L3" s="11" t="inlineStr">
+        <is>
+          <t>23300 CE</t>
+        </is>
+      </c>
+      <c r="M3" s="11" t="inlineStr">
+        <is>
+          <t>23400 CE</t>
+        </is>
+      </c>
+      <c r="N3" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="O3" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="P3" s="11" t="n">
+        <v>1350</v>
+      </c>
+      <c r="Q3" s="11" t="n">
+        <v>34.59</v>
+      </c>
+      <c r="R3" s="11" t="n">
+        <v>54.21</v>
+      </c>
+      <c r="S3" s="11" t="n">
+        <v>46696.5</v>
+      </c>
+      <c r="T3" s="11" t="n">
+        <v>46751.05</v>
+      </c>
+      <c r="U3" s="11" t="n">
+        <v>88303.5</v>
+      </c>
+      <c r="V3" s="11" t="n">
+        <v>26491.05</v>
+      </c>
+      <c r="W3" s="11" t="n">
+        <v>14008.95</v>
+      </c>
+      <c r="X3" s="11" t="n">
+        <v>26487</v>
+      </c>
+      <c r="Y3" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z3" s="11" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="AA3" s="11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AB3" s="11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC3" s="11" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AD3" s="11" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="AE3" s="11" t="n">
+        <v>26432.45</v>
+      </c>
+      <c r="AF3" s="11" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AG3" s="11" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AH3" s="11" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>10:06 IST</t>
+        </is>
+      </c>
+      <c r="J4" s="11" t="n">
+        <v>23350</v>
+      </c>
+      <c r="K4" s="11" t="n">
+        <v>23200</v>
+      </c>
+      <c r="L4" s="11" t="inlineStr">
+        <is>
+          <t>23400 PE</t>
+        </is>
+      </c>
+      <c r="M4" s="11" t="inlineStr">
+        <is>
+          <t>23300 PE</t>
+        </is>
+      </c>
+      <c r="N4" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="O4" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="P4" s="11" t="n">
+        <v>1650</v>
+      </c>
+      <c r="Q4" s="11" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="R4" s="11" t="n">
+        <v>50.07</v>
+      </c>
+      <c r="S4" s="11" t="n">
+        <v>47305.5</v>
+      </c>
+      <c r="T4" s="11" t="n">
+        <v>47360.14</v>
+      </c>
+      <c r="U4" s="11" t="n">
+        <v>117694.5</v>
+      </c>
+      <c r="V4" s="11" t="n">
+        <v>35308.35</v>
+      </c>
+      <c r="W4" s="11" t="n">
+        <v>14191.65</v>
+      </c>
+      <c r="X4" s="11" t="n">
+        <v>35310</v>
+      </c>
+      <c r="Y4" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z4" s="11" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AA4" s="11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AB4" s="11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC4" s="11" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AD4" s="11" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="AE4" s="11" t="n">
+        <v>35255.36</v>
+      </c>
+      <c r="AF4" s="11" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AG4" s="11" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AH4" s="11" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Price↑ (23400&gt;23200) &amp; EMA9↑ (23400.0&gt;23280.0)</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>23400</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>23280</v>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>10:50 IST</t>
+        </is>
+      </c>
+      <c r="M5" s="11" t="n">
+        <v>23400</v>
+      </c>
+      <c r="N5" s="11" t="n">
+        <v>23200</v>
+      </c>
+      <c r="O5" s="11" t="inlineStr">
+        <is>
+          <t>23400 CE</t>
+        </is>
+      </c>
+      <c r="P5" s="11" t="inlineStr">
+        <is>
+          <t>23500 CE</t>
+        </is>
+      </c>
+      <c r="Q5" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="R5" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="S5" s="11" t="n">
+        <v>1350</v>
+      </c>
+      <c r="T5" s="11" t="n">
+        <v>34.59</v>
+      </c>
+      <c r="U5" s="11" t="n">
+        <v>54.21</v>
+      </c>
+      <c r="V5" s="11" t="n">
+        <v>46696.5</v>
+      </c>
+      <c r="W5" s="11" t="n">
+        <v>46751.05</v>
+      </c>
+      <c r="X5" s="11" t="n">
+        <v>88303.5</v>
+      </c>
+      <c r="Y5" s="11" t="n">
+        <v>26491.05</v>
+      </c>
+      <c r="Z5" s="11" t="n">
+        <v>14008.95</v>
+      </c>
+      <c r="AA5" s="11" t="n">
+        <v>26487</v>
+      </c>
+      <c r="AB5" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC5" s="11" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="AD5" s="11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AE5" s="11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF5" s="11" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AG5" s="11" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="AH5" s="11" t="n">
+        <v>26432.45</v>
+      </c>
+      <c r="AI5" s="11" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AJ5" s="11" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AK5" s="11" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AH1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AK5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BANKNIFTY — Bull Call Spread &amp; Bear Put Spread | Paper Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="35" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Instrument</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Expiry</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Expiry Type</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>DTE</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Entry Time</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Exit Time</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Spot at Entry</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Prev Close</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Buy Strike</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Sell Strike</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Lots</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Lot Size</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Entry Premium</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Exit Premium</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost (₹)</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>Capital Used (₹)</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>Max Profit (₹)</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Target (₹)</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>Stop Loss (₹)</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>Gross P&amp;L (₹)</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>Brokerage (₹)</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>STT (₹)</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>SEBI Fee (₹)</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>Stamp Duty (₹)</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>GST (₹)</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>Total Fees (₹)</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>Net P&amp;L (₹)</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>Budget (₹)</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>Mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>14:14 IST</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="n">
+        <v>50200</v>
+      </c>
+      <c r="K3" s="12" t="n">
+        <v>49800</v>
+      </c>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>50200 CE</t>
+        </is>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>50400 CE</t>
+        </is>
+      </c>
+      <c r="N3" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="O3" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="P3" s="12" t="n">
+        <v>540</v>
+      </c>
+      <c r="Q3" s="12" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="R3" s="12" t="n">
+        <v>86.56999999999999</v>
+      </c>
+      <c r="S3" s="12" t="n">
+        <v>48762</v>
+      </c>
+      <c r="T3" s="12" t="n">
+        <v>48816.87</v>
+      </c>
+      <c r="U3" s="12" t="n">
+        <v>59238</v>
+      </c>
+      <c r="V3" s="12" t="n">
+        <v>17771.4</v>
+      </c>
+      <c r="W3" s="12" t="n">
+        <v>14628.6</v>
+      </c>
+      <c r="X3" s="12" t="n">
+        <v>-2014.2</v>
+      </c>
+      <c r="Y3" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z3" s="12" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA3" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB3" s="12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC3" s="12" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AD3" s="12" t="n">
+        <v>54.87</v>
+      </c>
+      <c r="AE3" s="12" t="n">
+        <v>-2069.07</v>
+      </c>
+      <c r="AF3" s="12" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AG3" s="12" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AH3" s="12" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>10:39 IST</t>
+        </is>
+      </c>
+      <c r="J4" s="11" t="n">
+        <v>50200</v>
+      </c>
+      <c r="K4" s="11" t="n">
+        <v>49800</v>
+      </c>
+      <c r="L4" s="11" t="inlineStr">
+        <is>
+          <t>50400 PE</t>
+        </is>
+      </c>
+      <c r="M4" s="11" t="inlineStr">
+        <is>
+          <t>50200 PE</t>
+        </is>
+      </c>
+      <c r="N4" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="O4" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="P4" s="11" t="n">
+        <v>690</v>
+      </c>
+      <c r="Q4" s="11" t="n">
+        <v>70.95</v>
+      </c>
+      <c r="R4" s="11" t="n">
+        <v>109.67</v>
+      </c>
+      <c r="S4" s="11" t="n">
+        <v>48955.5</v>
+      </c>
+      <c r="T4" s="11" t="n">
+        <v>49010.4</v>
+      </c>
+      <c r="U4" s="11" t="n">
+        <v>89044.5</v>
+      </c>
+      <c r="V4" s="11" t="n">
+        <v>26713.35</v>
+      </c>
+      <c r="W4" s="11" t="n">
+        <v>14686.65</v>
+      </c>
+      <c r="X4" s="11" t="n">
+        <v>26716.8</v>
+      </c>
+      <c r="Y4" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z4" s="11" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="AA4" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB4" s="11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC4" s="11" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AD4" s="11" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="AE4" s="11" t="n">
+        <v>26661.9</v>
+      </c>
+      <c r="AF4" s="11" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AG4" s="11" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AH4" s="11" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Price↓ (49800&lt;50200) &amp; EMA9↓ (49900.0&lt;50080.0)</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>49900</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>50080</v>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>10:06 IST</t>
+        </is>
+      </c>
+      <c r="M5" s="11" t="n">
+        <v>49800</v>
+      </c>
+      <c r="N5" s="11" t="n">
+        <v>50200</v>
+      </c>
+      <c r="O5" s="11" t="inlineStr">
+        <is>
+          <t>50000 PE</t>
+        </is>
+      </c>
+      <c r="P5" s="11" t="inlineStr">
+        <is>
+          <t>49800 PE</t>
+        </is>
+      </c>
+      <c r="Q5" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="R5" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="S5" s="11" t="n">
+        <v>630</v>
+      </c>
+      <c r="T5" s="11" t="n">
+        <v>77.34999999999999</v>
+      </c>
+      <c r="U5" s="11" t="n">
+        <v>114.14</v>
+      </c>
+      <c r="V5" s="11" t="n">
+        <v>48730.5</v>
+      </c>
+      <c r="W5" s="11" t="n">
+        <v>48785.37</v>
+      </c>
+      <c r="X5" s="11" t="n">
+        <v>77269.5</v>
+      </c>
+      <c r="Y5" s="11" t="n">
+        <v>23180.85</v>
+      </c>
+      <c r="Z5" s="11" t="n">
+        <v>14619.15</v>
+      </c>
+      <c r="AA5" s="11" t="n">
+        <v>23177.7</v>
+      </c>
+      <c r="AB5" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC5" s="11" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="AD5" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AE5" s="11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF5" s="11" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AG5" s="11" t="n">
+        <v>54.87</v>
+      </c>
+      <c r="AH5" s="11" t="n">
+        <v>23122.83</v>
+      </c>
+      <c r="AI5" s="11" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AJ5" s="11" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AK5" s="11" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AH1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Skipped Trading Days — Conflicting Trend Signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Instrument</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Trend Reason</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>EMA 9</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>EMA 21</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NQ_Trades" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MNQ_Trades" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="US_Stocks" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fee_Breakdown" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NIFTY_BullCall" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NIFTY_BearPut" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NIFTY_Both" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NIFTY_Smart" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BANKNIFTY_BullCall" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BANKNIFTY_BearPut" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BANKNIFTY_Both" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BANKNIFTY_Smart" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skipped_Days" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="NQ_Trades" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="MNQ_Trades" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="US_Stocks" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Fee_Breakdown" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="NIFTY_BullCall" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="NIFTY_BearPut" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="NIFTY_Both" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="NIFTY_Smart" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="BANKNIFTY_BullCall" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="BANKNIFTY_BearPut" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="BANKNIFTY_Both" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="BANKNIFTY_Smart" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Skipped_Days" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -72,7 +72,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -119,8 +119,28 @@
         <fgColor rgb="006C3483"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -134,11 +154,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -173,6 +221,23 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -539,8 +604,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:Z3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -709,6 +774,102 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="inlineStr">
+        <is>
+          <t>12:54 ET</t>
+        </is>
+      </c>
+      <c r="H3" s="15" t="n">
+        <v>30878.5</v>
+      </c>
+      <c r="I3" s="15" t="n">
+        <v>30875</v>
+      </c>
+      <c r="J3" s="15" t="n">
+        <v>30900</v>
+      </c>
+      <c r="K3" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="L3" s="15" t="n">
+        <v>124.58</v>
+      </c>
+      <c r="M3" s="15" t="n">
+        <v>237.21</v>
+      </c>
+      <c r="N3" s="15" t="n">
+        <v>923.86</v>
+      </c>
+      <c r="O3" s="15" t="n">
+        <v>3500</v>
+      </c>
+      <c r="P3" s="15" t="n">
+        <v>788.38</v>
+      </c>
+      <c r="Q3" s="15" t="n">
+        <v>261.62</v>
+      </c>
+      <c r="R3" s="15" t="n">
+        <v>788.41</v>
+      </c>
+      <c r="S3" s="15" t="n">
+        <v>16.52</v>
+      </c>
+      <c r="T3" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="U3" s="15" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="V3" s="15" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="W3" s="15" t="n">
+        <v>736.61</v>
+      </c>
+      <c r="X3" s="15" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Y3" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:Z1"/>
@@ -723,7 +884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL2"/>
+  <dimension ref="A1:AL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -965,6 +1126,150 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(56814.8&gt;55176.75) &amp; EMA9↑(55104.01&gt;54716.74)</t>
+        </is>
+      </c>
+      <c r="G3" s="17" t="n">
+        <v>55104.01</v>
+      </c>
+      <c r="H3" s="17" t="n">
+        <v>54716.74</v>
+      </c>
+      <c r="I3" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J3" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="K3" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M3" s="17" t="inlineStr">
+        <is>
+          <t>13:25 IST</t>
+        </is>
+      </c>
+      <c r="N3" s="17" t="n">
+        <v>56814.8</v>
+      </c>
+      <c r="O3" s="17" t="n">
+        <v>55176.75</v>
+      </c>
+      <c r="P3" s="17" t="inlineStr">
+        <is>
+          <t>56800 CE</t>
+        </is>
+      </c>
+      <c r="Q3" s="17" t="inlineStr">
+        <is>
+          <t>57000 CE</t>
+        </is>
+      </c>
+      <c r="R3" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="S3" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T3" s="17" t="n">
+        <v>540</v>
+      </c>
+      <c r="U3" s="17" t="n">
+        <v>88.59</v>
+      </c>
+      <c r="V3" s="17" t="n">
+        <v>92.89</v>
+      </c>
+      <c r="W3" s="17" t="n">
+        <v>47838.6</v>
+      </c>
+      <c r="X3" s="17" t="n">
+        <v>47893.33</v>
+      </c>
+      <c r="Y3" s="17" t="n">
+        <v>60161.4</v>
+      </c>
+      <c r="Z3" s="17" t="n">
+        <v>18048.42</v>
+      </c>
+      <c r="AA3" s="17" t="n">
+        <v>14351.58</v>
+      </c>
+      <c r="AB3" s="17" t="n">
+        <v>2322</v>
+      </c>
+      <c r="AC3" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD3" s="17" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AE3" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AF3" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG3" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AH3" s="17" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="AI3" s="17" t="n">
+        <v>2267.27</v>
+      </c>
+      <c r="AJ3" s="17" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AK3" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AL3" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AL1"/>
@@ -979,7 +1284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL2"/>
+  <dimension ref="A1:AL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1221,6 +1526,150 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(56814.8&gt;55176.75) &amp; EMA9↑(55104.01&gt;54716.74)</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>55104.01</v>
+      </c>
+      <c r="H3" s="15" t="n">
+        <v>54716.74</v>
+      </c>
+      <c r="I3" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J3" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="K3" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M3" s="15" t="inlineStr">
+        <is>
+          <t>09:52 IST</t>
+        </is>
+      </c>
+      <c r="N3" s="15" t="n">
+        <v>56814.8</v>
+      </c>
+      <c r="O3" s="15" t="n">
+        <v>55176.75</v>
+      </c>
+      <c r="P3" s="15" t="inlineStr">
+        <is>
+          <t>57000 PE</t>
+        </is>
+      </c>
+      <c r="Q3" s="15" t="inlineStr">
+        <is>
+          <t>56800 PE</t>
+        </is>
+      </c>
+      <c r="R3" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="S3" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="T3" s="15" t="n">
+        <v>570</v>
+      </c>
+      <c r="U3" s="15" t="n">
+        <v>83.97</v>
+      </c>
+      <c r="V3" s="15" t="n">
+        <v>118.78</v>
+      </c>
+      <c r="W3" s="15" t="n">
+        <v>47862.9</v>
+      </c>
+      <c r="X3" s="15" t="n">
+        <v>47917.63</v>
+      </c>
+      <c r="Y3" s="15" t="n">
+        <v>66137.10000000001</v>
+      </c>
+      <c r="Z3" s="15" t="n">
+        <v>19841.13</v>
+      </c>
+      <c r="AA3" s="15" t="n">
+        <v>14358.87</v>
+      </c>
+      <c r="AB3" s="15" t="n">
+        <v>19841.7</v>
+      </c>
+      <c r="AC3" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD3" s="15" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AE3" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AF3" s="15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG3" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AH3" s="15" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="AI3" s="15" t="n">
+        <v>19786.97</v>
+      </c>
+      <c r="AJ3" s="15" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AK3" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AL3" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AL1"/>
@@ -1235,7 +1684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL2"/>
+  <dimension ref="A1:AL4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1477,6 +1926,294 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(56814.8&gt;55176.75) &amp; EMA9↑(55104.01&gt;54716.74)</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>55104.01</v>
+      </c>
+      <c r="H3" s="15" t="n">
+        <v>54716.74</v>
+      </c>
+      <c r="I3" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J3" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="K3" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M3" s="15" t="inlineStr">
+        <is>
+          <t>10:18 IST</t>
+        </is>
+      </c>
+      <c r="N3" s="15" t="n">
+        <v>56814.8</v>
+      </c>
+      <c r="O3" s="15" t="n">
+        <v>55176.75</v>
+      </c>
+      <c r="P3" s="15" t="inlineStr">
+        <is>
+          <t>56800 CE</t>
+        </is>
+      </c>
+      <c r="Q3" s="15" t="inlineStr">
+        <is>
+          <t>57000 CE</t>
+        </is>
+      </c>
+      <c r="R3" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="S3" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="T3" s="15" t="n">
+        <v>510</v>
+      </c>
+      <c r="U3" s="15" t="n">
+        <v>93.39</v>
+      </c>
+      <c r="V3" s="15" t="n">
+        <v>125.37</v>
+      </c>
+      <c r="W3" s="15" t="n">
+        <v>47628.9</v>
+      </c>
+      <c r="X3" s="15" t="n">
+        <v>47683.59</v>
+      </c>
+      <c r="Y3" s="15" t="n">
+        <v>54371.1</v>
+      </c>
+      <c r="Z3" s="15" t="n">
+        <v>16311.33</v>
+      </c>
+      <c r="AA3" s="15" t="n">
+        <v>14288.67</v>
+      </c>
+      <c r="AB3" s="15" t="n">
+        <v>16309.8</v>
+      </c>
+      <c r="AC3" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD3" s="15" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AE3" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AF3" s="15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AG3" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AH3" s="15" t="n">
+        <v>54.69</v>
+      </c>
+      <c r="AI3" s="15" t="n">
+        <v>16255.11</v>
+      </c>
+      <c r="AJ3" s="15" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AK3" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AL3" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(56814.8&gt;55176.75) &amp; EMA9↑(55104.01&gt;54716.74)</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>55104.01</v>
+      </c>
+      <c r="H4" s="15" t="n">
+        <v>54716.74</v>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="K4" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M4" s="15" t="inlineStr">
+        <is>
+          <t>11:41 IST</t>
+        </is>
+      </c>
+      <c r="N4" s="15" t="n">
+        <v>56814.8</v>
+      </c>
+      <c r="O4" s="15" t="n">
+        <v>55176.75</v>
+      </c>
+      <c r="P4" s="15" t="inlineStr">
+        <is>
+          <t>57000 PE</t>
+        </is>
+      </c>
+      <c r="Q4" s="15" t="inlineStr">
+        <is>
+          <t>56800 PE</t>
+        </is>
+      </c>
+      <c r="R4" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="S4" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="T4" s="15" t="n">
+        <v>510</v>
+      </c>
+      <c r="U4" s="15" t="n">
+        <v>95.42</v>
+      </c>
+      <c r="V4" s="15" t="n">
+        <v>126.79</v>
+      </c>
+      <c r="W4" s="15" t="n">
+        <v>48664.2</v>
+      </c>
+      <c r="X4" s="15" t="n">
+        <v>48719.06</v>
+      </c>
+      <c r="Y4" s="15" t="n">
+        <v>53335.8</v>
+      </c>
+      <c r="Z4" s="15" t="n">
+        <v>16000.74</v>
+      </c>
+      <c r="AA4" s="15" t="n">
+        <v>14599.26</v>
+      </c>
+      <c r="AB4" s="15" t="n">
+        <v>15998.7</v>
+      </c>
+      <c r="AC4" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD4" s="15" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="AE4" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AF4" s="15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AG4" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AH4" s="15" t="n">
+        <v>54.86</v>
+      </c>
+      <c r="AI4" s="15" t="n">
+        <v>15943.84</v>
+      </c>
+      <c r="AJ4" s="15" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AK4" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AL4" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AL1"/>
@@ -1491,7 +2228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL2"/>
+  <dimension ref="A1:AL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1733,6 +2470,150 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(56814.8&gt;55176.75) &amp; EMA9↑(55104.01&gt;54716.74)</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>55104.01</v>
+      </c>
+      <c r="H3" s="15" t="n">
+        <v>54716.74</v>
+      </c>
+      <c r="I3" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J3" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="K3" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M3" s="15" t="inlineStr">
+        <is>
+          <t>10:53 IST</t>
+        </is>
+      </c>
+      <c r="N3" s="15" t="n">
+        <v>56814.8</v>
+      </c>
+      <c r="O3" s="15" t="n">
+        <v>55176.75</v>
+      </c>
+      <c r="P3" s="15" t="inlineStr">
+        <is>
+          <t>56800 CE</t>
+        </is>
+      </c>
+      <c r="Q3" s="15" t="inlineStr">
+        <is>
+          <t>57000 CE</t>
+        </is>
+      </c>
+      <c r="R3" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="S3" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="T3" s="15" t="n">
+        <v>630</v>
+      </c>
+      <c r="U3" s="15" t="n">
+        <v>76.12</v>
+      </c>
+      <c r="V3" s="15" t="n">
+        <v>113.28</v>
+      </c>
+      <c r="W3" s="15" t="n">
+        <v>47955.6</v>
+      </c>
+      <c r="X3" s="15" t="n">
+        <v>48010.35</v>
+      </c>
+      <c r="Y3" s="15" t="n">
+        <v>78044.39999999999</v>
+      </c>
+      <c r="Z3" s="15" t="n">
+        <v>23413.32</v>
+      </c>
+      <c r="AA3" s="15" t="n">
+        <v>14386.68</v>
+      </c>
+      <c r="AB3" s="15" t="n">
+        <v>23410.8</v>
+      </c>
+      <c r="AC3" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD3" s="15" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="AE3" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AF3" s="15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG3" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AH3" s="15" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="AI3" s="15" t="n">
+        <v>23356.05</v>
+      </c>
+      <c r="AJ3" s="15" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AK3" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AL3" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AL1"/>
@@ -1747,7 +2628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1800,6 +2681,39 @@
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Action</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BULLISH EMA:BEARISH</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="n">
+        <v>23385.72</v>
+      </c>
+      <c r="F3" s="18" t="n">
+        <v>23538</v>
+      </c>
+      <c r="G3" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
         </is>
       </c>
     </row>
@@ -1817,8 +2731,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:Z3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -1987,6 +2901,102 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="inlineStr">
+        <is>
+          <t>10:49 ET</t>
+        </is>
+      </c>
+      <c r="H3" s="15" t="n">
+        <v>30876</v>
+      </c>
+      <c r="I3" s="15" t="n">
+        <v>30875</v>
+      </c>
+      <c r="J3" s="15" t="n">
+        <v>30900</v>
+      </c>
+      <c r="K3" s="15" t="n">
+        <v>71</v>
+      </c>
+      <c r="L3" s="15" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="M3" s="15" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="N3" s="15" t="n">
+        <v>991.87</v>
+      </c>
+      <c r="O3" s="15" t="n">
+        <v>3550</v>
+      </c>
+      <c r="P3" s="15" t="n">
+        <v>802.37</v>
+      </c>
+      <c r="Q3" s="15" t="n">
+        <v>262.63</v>
+      </c>
+      <c r="R3" s="15" t="n">
+        <v>802.3</v>
+      </c>
+      <c r="S3" s="15" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="T3" s="15" t="n">
+        <v>71</v>
+      </c>
+      <c r="U3" s="15" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="V3" s="15" t="n">
+        <v>116.44</v>
+      </c>
+      <c r="W3" s="15" t="n">
+        <v>685.86</v>
+      </c>
+      <c r="X3" s="15" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Y3" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:Z1"/>
@@ -2002,7 +3012,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -2101,8 +3111,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
@@ -2166,6 +3176,76 @@
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" s="19" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="E3" s="19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F3" s="19" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G3" s="19" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="H3" s="19" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="n">
+        <v>71</v>
+      </c>
+      <c r="D4" s="19" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="E4" s="19" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="F4" s="19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G4" s="19" t="n">
+        <v>58.22</v>
+      </c>
+      <c r="H4" s="19" t="n">
+        <v>116.44</v>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — PROFIT</t>
         </is>
       </c>
     </row>
@@ -2184,7 +3264,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -2387,9 +3467,9 @@
           <t>MNQ — Bull Call Spread</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="14" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -2572,9 +3652,9 @@
           <t>Combined Totals</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="14" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2632,7 +3712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL2"/>
+  <dimension ref="A1:AL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2874,6 +3954,150 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BULLISH EMA:BEARISH</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>23385.72</v>
+      </c>
+      <c r="H3" s="15" t="n">
+        <v>23538</v>
+      </c>
+      <c r="I3" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J3" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="K3" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M3" s="15" t="inlineStr">
+        <is>
+          <t>11:36 IST</t>
+        </is>
+      </c>
+      <c r="N3" s="15" t="n">
+        <v>23622.9</v>
+      </c>
+      <c r="O3" s="15" t="n">
+        <v>23161.6</v>
+      </c>
+      <c r="P3" s="15" t="inlineStr">
+        <is>
+          <t>23600 CE</t>
+        </is>
+      </c>
+      <c r="Q3" s="15" t="inlineStr">
+        <is>
+          <t>23700 CE</t>
+        </is>
+      </c>
+      <c r="R3" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="S3" s="15" t="n">
+        <v>75</v>
+      </c>
+      <c r="T3" s="15" t="n">
+        <v>1875</v>
+      </c>
+      <c r="U3" s="15" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="V3" s="15" t="n">
+        <v>48.01</v>
+      </c>
+      <c r="W3" s="15" t="n">
+        <v>48243.75</v>
+      </c>
+      <c r="X3" s="15" t="n">
+        <v>48298.54</v>
+      </c>
+      <c r="Y3" s="15" t="n">
+        <v>139256.25</v>
+      </c>
+      <c r="Z3" s="15" t="n">
+        <v>41776.88</v>
+      </c>
+      <c r="AA3" s="15" t="n">
+        <v>14473.12</v>
+      </c>
+      <c r="AB3" s="15" t="n">
+        <v>41775</v>
+      </c>
+      <c r="AC3" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD3" s="15" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AE3" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AF3" s="15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AG3" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AH3" s="15" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="AI3" s="15" t="n">
+        <v>41720.21</v>
+      </c>
+      <c r="AJ3" s="15" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AK3" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AL3" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AL1"/>
@@ -2888,7 +4112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL2"/>
+  <dimension ref="A1:AL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3130,6 +4354,150 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BULLISH EMA:BEARISH</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>23385.72</v>
+      </c>
+      <c r="H3" s="15" t="n">
+        <v>23538</v>
+      </c>
+      <c r="I3" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J3" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="K3" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M3" s="15" t="inlineStr">
+        <is>
+          <t>12:03 IST</t>
+        </is>
+      </c>
+      <c r="N3" s="15" t="n">
+        <v>23622.9</v>
+      </c>
+      <c r="O3" s="15" t="n">
+        <v>23161.6</v>
+      </c>
+      <c r="P3" s="15" t="inlineStr">
+        <is>
+          <t>23700 PE</t>
+        </is>
+      </c>
+      <c r="Q3" s="15" t="inlineStr">
+        <is>
+          <t>23600 PE</t>
+        </is>
+      </c>
+      <c r="R3" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="S3" s="15" t="n">
+        <v>75</v>
+      </c>
+      <c r="T3" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="U3" s="15" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="V3" s="15" t="n">
+        <v>52.62</v>
+      </c>
+      <c r="W3" s="15" t="n">
+        <v>48480</v>
+      </c>
+      <c r="X3" s="15" t="n">
+        <v>48534.83</v>
+      </c>
+      <c r="Y3" s="15" t="n">
+        <v>101520</v>
+      </c>
+      <c r="Z3" s="15" t="n">
+        <v>30456</v>
+      </c>
+      <c r="AA3" s="15" t="n">
+        <v>14544</v>
+      </c>
+      <c r="AB3" s="15" t="n">
+        <v>30450</v>
+      </c>
+      <c r="AC3" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD3" s="15" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="AE3" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AF3" s="15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AG3" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AH3" s="15" t="n">
+        <v>54.83</v>
+      </c>
+      <c r="AI3" s="15" t="n">
+        <v>30395.17</v>
+      </c>
+      <c r="AJ3" s="15" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AK3" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AL3" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AL1"/>
@@ -3144,7 +4512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL2"/>
+  <dimension ref="A1:AL4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3383,6 +4751,294 @@
       <c r="AL2" s="2" t="inlineStr">
         <is>
           <t>Mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BULLISH EMA:BEARISH</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>23385.72</v>
+      </c>
+      <c r="H3" s="15" t="n">
+        <v>23538</v>
+      </c>
+      <c r="I3" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J3" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="K3" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M3" s="15" t="inlineStr">
+        <is>
+          <t>09:46 IST</t>
+        </is>
+      </c>
+      <c r="N3" s="15" t="n">
+        <v>23622.9</v>
+      </c>
+      <c r="O3" s="15" t="n">
+        <v>23161.6</v>
+      </c>
+      <c r="P3" s="15" t="inlineStr">
+        <is>
+          <t>23600 CE</t>
+        </is>
+      </c>
+      <c r="Q3" s="15" t="inlineStr">
+        <is>
+          <t>23700 CE</t>
+        </is>
+      </c>
+      <c r="R3" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="S3" s="15" t="n">
+        <v>75</v>
+      </c>
+      <c r="T3" s="15" t="n">
+        <v>1650</v>
+      </c>
+      <c r="U3" s="15" t="n">
+        <v>28.87</v>
+      </c>
+      <c r="V3" s="15" t="n">
+        <v>50.21</v>
+      </c>
+      <c r="W3" s="15" t="n">
+        <v>47635.5</v>
+      </c>
+      <c r="X3" s="15" t="n">
+        <v>47690.2</v>
+      </c>
+      <c r="Y3" s="15" t="n">
+        <v>117364.5</v>
+      </c>
+      <c r="Z3" s="15" t="n">
+        <v>35209.35</v>
+      </c>
+      <c r="AA3" s="15" t="n">
+        <v>14290.65</v>
+      </c>
+      <c r="AB3" s="15" t="n">
+        <v>35211</v>
+      </c>
+      <c r="AC3" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD3" s="15" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AE3" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AF3" s="15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AG3" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AH3" s="15" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="AI3" s="15" t="n">
+        <v>35156.3</v>
+      </c>
+      <c r="AJ3" s="15" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AK3" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AL3" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BULLISH EMA:BEARISH</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>23385.72</v>
+      </c>
+      <c r="H4" s="16" t="n">
+        <v>23538</v>
+      </c>
+      <c r="I4" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J4" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="K4" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M4" s="16" t="inlineStr">
+        <is>
+          <t>10:14 IST</t>
+        </is>
+      </c>
+      <c r="N4" s="16" t="n">
+        <v>23622.9</v>
+      </c>
+      <c r="O4" s="16" t="n">
+        <v>23161.6</v>
+      </c>
+      <c r="P4" s="16" t="inlineStr">
+        <is>
+          <t>23700 PE</t>
+        </is>
+      </c>
+      <c r="Q4" s="16" t="inlineStr">
+        <is>
+          <t>23600 PE</t>
+        </is>
+      </c>
+      <c r="R4" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="S4" s="16" t="n">
+        <v>75</v>
+      </c>
+      <c r="T4" s="16" t="n">
+        <v>1500</v>
+      </c>
+      <c r="U4" s="16" t="n">
+        <v>32.47</v>
+      </c>
+      <c r="V4" s="16" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="W4" s="16" t="n">
+        <v>48705</v>
+      </c>
+      <c r="X4" s="16" t="n">
+        <v>48759.86</v>
+      </c>
+      <c r="Y4" s="16" t="n">
+        <v>101295</v>
+      </c>
+      <c r="Z4" s="16" t="n">
+        <v>30388.5</v>
+      </c>
+      <c r="AA4" s="16" t="n">
+        <v>14611.5</v>
+      </c>
+      <c r="AB4" s="16" t="n">
+        <v>-14610</v>
+      </c>
+      <c r="AC4" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD4" s="16" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="AE4" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AF4" s="16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AG4" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AH4" s="16" t="n">
+        <v>54.86</v>
+      </c>
+      <c r="AI4" s="16" t="n">
+        <v>-14664.86</v>
+      </c>
+      <c r="AJ4" s="16" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AK4" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AL4" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
         </is>
       </c>
     </row>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NQ_Trades" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MNQ_Trades" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="US_Stocks" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fee_Breakdown" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NIFTY_BullCall" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NIFTY_BearPut" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NIFTY_Both" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NIFTY_Smart" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BANKNIFTY_BullCall" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BANKNIFTY_BearPut" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BANKNIFTY_Both" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BANKNIFTY_Smart" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skipped_Days" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="NQ_Trades" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="MNQ_Trades" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="US_Stocks" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Fee_Breakdown" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="NIFTY_BullCall" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="NIFTY_BearPut" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="NIFTY_Both" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="NIFTY_Smart" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="BANKNIFTY_BullCall" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="BANKNIFTY_BearPut" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="BANKNIFTY_Both" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="BANKNIFTY_Smart" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Skipped_Days" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -72,7 +72,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -119,8 +119,28 @@
         <fgColor rgb="006C3483"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -134,11 +154,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -173,6 +221,23 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -539,8 +604,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:AA3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -715,6 +780,105 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
+        <is>
+          <t>15:28 ET</t>
+        </is>
+      </c>
+      <c r="H3" s="16" t="n">
+        <v>30863</v>
+      </c>
+      <c r="I3" s="16" t="n">
+        <v>30850</v>
+      </c>
+      <c r="J3" s="16" t="n">
+        <v>30875</v>
+      </c>
+      <c r="K3" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="L3" s="16" t="n">
+        <v>121.65</v>
+      </c>
+      <c r="M3" s="16" t="n">
+        <v>125.64</v>
+      </c>
+      <c r="N3" s="16" t="n">
+        <v>903.35</v>
+      </c>
+      <c r="O3" s="16" t="n">
+        <v>2648.45</v>
+      </c>
+      <c r="P3" s="16" t="n">
+        <v>255.46</v>
+      </c>
+      <c r="Q3" s="16" t="n">
+        <v>255.46</v>
+      </c>
+      <c r="R3" s="16" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="S3" s="16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T3" s="16" t="n">
+        <v>16.52</v>
+      </c>
+      <c r="U3" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="V3" s="16" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="W3" s="16" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="X3" s="16" t="n">
+        <v>-23.87</v>
+      </c>
+      <c r="Y3" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="Z3" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -729,7 +893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM2"/>
+  <dimension ref="A1:AM3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -977,6 +1141,153 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(56814.8&gt;55176.75) &amp; EMA9↑(55104.01&gt;54716.74)</t>
+        </is>
+      </c>
+      <c r="G3" s="17" t="n">
+        <v>55104.01</v>
+      </c>
+      <c r="H3" s="17" t="n">
+        <v>54716.74</v>
+      </c>
+      <c r="I3" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J3" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="K3" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M3" s="17" t="inlineStr">
+        <is>
+          <t>11:45 IST</t>
+        </is>
+      </c>
+      <c r="N3" s="17" t="n">
+        <v>56814.8</v>
+      </c>
+      <c r="O3" s="17" t="n">
+        <v>55176.75</v>
+      </c>
+      <c r="P3" s="17" t="inlineStr">
+        <is>
+          <t>56800 CE</t>
+        </is>
+      </c>
+      <c r="Q3" s="17" t="inlineStr">
+        <is>
+          <t>57000 CE</t>
+        </is>
+      </c>
+      <c r="R3" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="S3" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T3" s="17" t="n">
+        <v>570</v>
+      </c>
+      <c r="U3" s="17" t="n">
+        <v>82.20999999999999</v>
+      </c>
+      <c r="V3" s="17" t="n">
+        <v>106.87</v>
+      </c>
+      <c r="W3" s="17" t="n">
+        <v>46859.7</v>
+      </c>
+      <c r="X3" s="17" t="n">
+        <v>46914.27</v>
+      </c>
+      <c r="Y3" s="17" t="n">
+        <v>67140.3</v>
+      </c>
+      <c r="Z3" s="17" t="n">
+        <v>14057.91</v>
+      </c>
+      <c r="AA3" s="17" t="n">
+        <v>14057.91</v>
+      </c>
+      <c r="AB3" s="17" t="n">
+        <v>14056.2</v>
+      </c>
+      <c r="AC3" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD3" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE3" s="17" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="AF3" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AG3" s="17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH3" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI3" s="17" t="n">
+        <v>54.57</v>
+      </c>
+      <c r="AJ3" s="17" t="n">
+        <v>14001.63</v>
+      </c>
+      <c r="AK3" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AL3" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM3" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -991,7 +1302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM2"/>
+  <dimension ref="A1:AM3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1239,6 +1550,153 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(56814.8&gt;55176.75) &amp; EMA9↑(55104.01&gt;54716.74)</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>55104.01</v>
+      </c>
+      <c r="H3" s="15" t="n">
+        <v>54716.74</v>
+      </c>
+      <c r="I3" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J3" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="K3" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M3" s="15" t="inlineStr">
+        <is>
+          <t>09:45 IST</t>
+        </is>
+      </c>
+      <c r="N3" s="15" t="n">
+        <v>56814.8</v>
+      </c>
+      <c r="O3" s="15" t="n">
+        <v>55176.75</v>
+      </c>
+      <c r="P3" s="15" t="inlineStr">
+        <is>
+          <t>57000 PE</t>
+        </is>
+      </c>
+      <c r="Q3" s="15" t="inlineStr">
+        <is>
+          <t>56800 PE</t>
+        </is>
+      </c>
+      <c r="R3" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="S3" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="T3" s="15" t="n">
+        <v>600</v>
+      </c>
+      <c r="U3" s="15" t="n">
+        <v>78.70999999999999</v>
+      </c>
+      <c r="V3" s="15" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="W3" s="15" t="n">
+        <v>47226</v>
+      </c>
+      <c r="X3" s="15" t="n">
+        <v>47280.63</v>
+      </c>
+      <c r="Y3" s="15" t="n">
+        <v>72774</v>
+      </c>
+      <c r="Z3" s="15" t="n">
+        <v>14167.8</v>
+      </c>
+      <c r="AA3" s="15" t="n">
+        <v>14167.8</v>
+      </c>
+      <c r="AB3" s="15" t="n">
+        <v>-14166</v>
+      </c>
+      <c r="AC3" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AD3" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE3" s="15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF3" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AG3" s="15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH3" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI3" s="15" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="AJ3" s="15" t="n">
+        <v>-14220.63</v>
+      </c>
+      <c r="AK3" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AL3" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM3" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -1253,7 +1711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM2"/>
+  <dimension ref="A1:AM4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1501,6 +1959,300 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Price↑(56814.8&gt;55176.75) &amp; EMA9↑(55104.01&gt;54716.74)</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="n">
+        <v>55104.01</v>
+      </c>
+      <c r="H3" s="16" t="n">
+        <v>54716.74</v>
+      </c>
+      <c r="I3" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J3" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="K3" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M3" s="16" t="inlineStr">
+        <is>
+          <t>14:24 IST</t>
+        </is>
+      </c>
+      <c r="N3" s="16" t="n">
+        <v>56814.8</v>
+      </c>
+      <c r="O3" s="16" t="n">
+        <v>55176.75</v>
+      </c>
+      <c r="P3" s="16" t="inlineStr">
+        <is>
+          <t>56800 CE</t>
+        </is>
+      </c>
+      <c r="Q3" s="16" t="inlineStr">
+        <is>
+          <t>57000 CE</t>
+        </is>
+      </c>
+      <c r="R3" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="S3" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="T3" s="16" t="n">
+        <v>540</v>
+      </c>
+      <c r="U3" s="16" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="V3" s="16" t="n">
+        <v>86.69</v>
+      </c>
+      <c r="W3" s="16" t="n">
+        <v>48961.8</v>
+      </c>
+      <c r="X3" s="16" t="n">
+        <v>49016.7</v>
+      </c>
+      <c r="Y3" s="16" t="n">
+        <v>59038.2</v>
+      </c>
+      <c r="Z3" s="16" t="n">
+        <v>14688.54</v>
+      </c>
+      <c r="AA3" s="16" t="n">
+        <v>14688.54</v>
+      </c>
+      <c r="AB3" s="16" t="n">
+        <v>-2149.2</v>
+      </c>
+      <c r="AC3" s="16" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="AD3" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE3" s="16" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="AF3" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG3" s="16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH3" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI3" s="16" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="AJ3" s="16" t="n">
+        <v>-2204.1</v>
+      </c>
+      <c r="AK3" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AL3" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM3" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(56814.8&gt;55176.75) &amp; EMA9↑(55104.01&gt;54716.74)</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="n">
+        <v>55104.01</v>
+      </c>
+      <c r="H4" s="17" t="n">
+        <v>54716.74</v>
+      </c>
+      <c r="I4" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J4" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="K4" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M4" s="17" t="inlineStr">
+        <is>
+          <t>09:56 IST</t>
+        </is>
+      </c>
+      <c r="N4" s="17" t="n">
+        <v>56814.8</v>
+      </c>
+      <c r="O4" s="17" t="n">
+        <v>55176.75</v>
+      </c>
+      <c r="P4" s="17" t="inlineStr">
+        <is>
+          <t>57000 PE</t>
+        </is>
+      </c>
+      <c r="Q4" s="17" t="inlineStr">
+        <is>
+          <t>56800 PE</t>
+        </is>
+      </c>
+      <c r="R4" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="S4" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T4" s="17" t="n">
+        <v>600</v>
+      </c>
+      <c r="U4" s="17" t="n">
+        <v>80.36</v>
+      </c>
+      <c r="V4" s="17" t="n">
+        <v>104.47</v>
+      </c>
+      <c r="W4" s="17" t="n">
+        <v>48216</v>
+      </c>
+      <c r="X4" s="17" t="n">
+        <v>48270.79</v>
+      </c>
+      <c r="Y4" s="17" t="n">
+        <v>71784</v>
+      </c>
+      <c r="Z4" s="17" t="n">
+        <v>14464.8</v>
+      </c>
+      <c r="AA4" s="17" t="n">
+        <v>14464.8</v>
+      </c>
+      <c r="AB4" s="17" t="n">
+        <v>14466</v>
+      </c>
+      <c r="AC4" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD4" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE4" s="17" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AF4" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG4" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH4" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI4" s="17" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="AJ4" s="17" t="n">
+        <v>14411.21</v>
+      </c>
+      <c r="AK4" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AL4" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM4" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -1515,7 +2267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM2"/>
+  <dimension ref="A1:AM3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1763,6 +2515,153 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(56814.8&gt;55176.75) &amp; EMA9↑(55104.01&gt;54716.74)</t>
+        </is>
+      </c>
+      <c r="G3" s="17" t="n">
+        <v>55104.01</v>
+      </c>
+      <c r="H3" s="17" t="n">
+        <v>54716.74</v>
+      </c>
+      <c r="I3" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J3" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="K3" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M3" s="17" t="inlineStr">
+        <is>
+          <t>11:40 IST</t>
+        </is>
+      </c>
+      <c r="N3" s="17" t="n">
+        <v>56814.8</v>
+      </c>
+      <c r="O3" s="17" t="n">
+        <v>55176.75</v>
+      </c>
+      <c r="P3" s="17" t="inlineStr">
+        <is>
+          <t>56800 CE</t>
+        </is>
+      </c>
+      <c r="Q3" s="17" t="inlineStr">
+        <is>
+          <t>57000 CE</t>
+        </is>
+      </c>
+      <c r="R3" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="S3" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T3" s="17" t="n">
+        <v>570</v>
+      </c>
+      <c r="U3" s="17" t="n">
+        <v>84.48999999999999</v>
+      </c>
+      <c r="V3" s="17" t="n">
+        <v>109.84</v>
+      </c>
+      <c r="W3" s="17" t="n">
+        <v>48159.3</v>
+      </c>
+      <c r="X3" s="17" t="n">
+        <v>48214.08</v>
+      </c>
+      <c r="Y3" s="17" t="n">
+        <v>65840.7</v>
+      </c>
+      <c r="Z3" s="17" t="n">
+        <v>14447.79</v>
+      </c>
+      <c r="AA3" s="17" t="n">
+        <v>14447.79</v>
+      </c>
+      <c r="AB3" s="17" t="n">
+        <v>14449.5</v>
+      </c>
+      <c r="AC3" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD3" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE3" s="17" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="AF3" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG3" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH3" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI3" s="17" t="n">
+        <v>54.78</v>
+      </c>
+      <c r="AJ3" s="17" t="n">
+        <v>14394.72</v>
+      </c>
+      <c r="AK3" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AL3" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM3" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -1777,7 +2676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1830,6 +2729,39 @@
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Action</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BULLISH EMA:BEARISH</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="n">
+        <v>23385.72</v>
+      </c>
+      <c r="F3" s="18" t="n">
+        <v>23538</v>
+      </c>
+      <c r="G3" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
         </is>
       </c>
     </row>
@@ -1847,8 +2779,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:AA3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -2023,6 +2955,105 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
+        <is>
+          <t>16:20 ET</t>
+        </is>
+      </c>
+      <c r="H3" s="16" t="n">
+        <v>30863.75</v>
+      </c>
+      <c r="I3" s="16" t="n">
+        <v>30850</v>
+      </c>
+      <c r="J3" s="16" t="n">
+        <v>30875</v>
+      </c>
+      <c r="K3" s="16" t="n">
+        <v>78</v>
+      </c>
+      <c r="L3" s="16" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="M3" s="16" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="N3" s="16" t="n">
+        <v>996.84</v>
+      </c>
+      <c r="O3" s="16" t="n">
+        <v>3031.08</v>
+      </c>
+      <c r="P3" s="16" t="n">
+        <v>260.68</v>
+      </c>
+      <c r="Q3" s="16" t="n">
+        <v>260.68</v>
+      </c>
+      <c r="R3" s="16" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="S3" s="16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T3" s="16" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="U3" s="16" t="n">
+        <v>78</v>
+      </c>
+      <c r="V3" s="16" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="W3" s="16" t="n">
+        <v>127.92</v>
+      </c>
+      <c r="X3" s="16" t="n">
+        <v>-124.8</v>
+      </c>
+      <c r="Y3" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="Z3" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -2038,7 +3069,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -2137,8 +3168,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
@@ -2202,6 +3233,76 @@
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" s="19" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="E3" s="19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F3" s="19" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G3" s="19" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="H3" s="19" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="n">
+        <v>78</v>
+      </c>
+      <c r="D4" s="19" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E4" s="19" t="n">
+        <v>39</v>
+      </c>
+      <c r="F4" s="19" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G4" s="19" t="n">
+        <v>63.96</v>
+      </c>
+      <c r="H4" s="19" t="n">
+        <v>127.92</v>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — FLAT</t>
         </is>
       </c>
     </row>
@@ -2220,7 +3321,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -2423,9 +3524,9 @@
           <t>MNQ — Bull Call Spread</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="14" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -2608,9 +3709,9 @@
           <t>Combined Totals</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="14" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2668,7 +3769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM2"/>
+  <dimension ref="A1:AM3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2916,6 +4017,153 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BULLISH EMA:BEARISH</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>23385.72</v>
+      </c>
+      <c r="H3" s="15" t="n">
+        <v>23538</v>
+      </c>
+      <c r="I3" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J3" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="K3" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M3" s="15" t="inlineStr">
+        <is>
+          <t>11:02 IST</t>
+        </is>
+      </c>
+      <c r="N3" s="15" t="n">
+        <v>23622.9</v>
+      </c>
+      <c r="O3" s="15" t="n">
+        <v>23161.6</v>
+      </c>
+      <c r="P3" s="15" t="inlineStr">
+        <is>
+          <t>23600 CE</t>
+        </is>
+      </c>
+      <c r="Q3" s="15" t="inlineStr">
+        <is>
+          <t>23700 CE</t>
+        </is>
+      </c>
+      <c r="R3" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="S3" s="15" t="n">
+        <v>75</v>
+      </c>
+      <c r="T3" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="U3" s="15" t="n">
+        <v>31.47</v>
+      </c>
+      <c r="V3" s="15" t="n">
+        <v>22.03</v>
+      </c>
+      <c r="W3" s="15" t="n">
+        <v>47205</v>
+      </c>
+      <c r="X3" s="15" t="n">
+        <v>47259.63</v>
+      </c>
+      <c r="Y3" s="15" t="n">
+        <v>102795</v>
+      </c>
+      <c r="Z3" s="15" t="n">
+        <v>14161.5</v>
+      </c>
+      <c r="AA3" s="15" t="n">
+        <v>14161.5</v>
+      </c>
+      <c r="AB3" s="15" t="n">
+        <v>-14160</v>
+      </c>
+      <c r="AC3" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AD3" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE3" s="15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF3" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AG3" s="15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH3" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI3" s="15" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="AJ3" s="15" t="n">
+        <v>-14214.63</v>
+      </c>
+      <c r="AK3" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AL3" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM3" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -2930,7 +4178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM2"/>
+  <dimension ref="A1:AM3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3178,6 +4426,153 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BULLISH EMA:BEARISH</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="n">
+        <v>23385.72</v>
+      </c>
+      <c r="H3" s="16" t="n">
+        <v>23538</v>
+      </c>
+      <c r="I3" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J3" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="K3" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M3" s="16" t="inlineStr">
+        <is>
+          <t>13:59 IST</t>
+        </is>
+      </c>
+      <c r="N3" s="16" t="n">
+        <v>23622.9</v>
+      </c>
+      <c r="O3" s="16" t="n">
+        <v>23161.6</v>
+      </c>
+      <c r="P3" s="16" t="inlineStr">
+        <is>
+          <t>23700 PE</t>
+        </is>
+      </c>
+      <c r="Q3" s="16" t="inlineStr">
+        <is>
+          <t>23600 PE</t>
+        </is>
+      </c>
+      <c r="R3" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="S3" s="16" t="n">
+        <v>75</v>
+      </c>
+      <c r="T3" s="16" t="n">
+        <v>1275</v>
+      </c>
+      <c r="U3" s="16" t="n">
+        <v>36.99</v>
+      </c>
+      <c r="V3" s="16" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="W3" s="16" t="n">
+        <v>47162.25</v>
+      </c>
+      <c r="X3" s="16" t="n">
+        <v>47216.87</v>
+      </c>
+      <c r="Y3" s="16" t="n">
+        <v>80337.75</v>
+      </c>
+      <c r="Z3" s="16" t="n">
+        <v>14148.67</v>
+      </c>
+      <c r="AA3" s="16" t="n">
+        <v>14148.67</v>
+      </c>
+      <c r="AB3" s="16" t="n">
+        <v>-1581</v>
+      </c>
+      <c r="AC3" s="16" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AD3" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE3" s="16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF3" s="16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AG3" s="16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH3" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI3" s="16" t="n">
+        <v>54.62</v>
+      </c>
+      <c r="AJ3" s="16" t="n">
+        <v>-1635.62</v>
+      </c>
+      <c r="AK3" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AL3" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM3" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -3192,7 +4587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM2"/>
+  <dimension ref="A1:AM4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3437,6 +4832,300 @@
       <c r="AM2" s="2" t="inlineStr">
         <is>
           <t>Mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BULLISH EMA:BEARISH</t>
+        </is>
+      </c>
+      <c r="G3" s="17" t="n">
+        <v>23385.72</v>
+      </c>
+      <c r="H3" s="17" t="n">
+        <v>23538</v>
+      </c>
+      <c r="I3" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J3" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="K3" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M3" s="17" t="inlineStr">
+        <is>
+          <t>11:48 IST</t>
+        </is>
+      </c>
+      <c r="N3" s="17" t="n">
+        <v>23622.9</v>
+      </c>
+      <c r="O3" s="17" t="n">
+        <v>23161.6</v>
+      </c>
+      <c r="P3" s="17" t="inlineStr">
+        <is>
+          <t>23600 CE</t>
+        </is>
+      </c>
+      <c r="Q3" s="17" t="inlineStr">
+        <is>
+          <t>23700 CE</t>
+        </is>
+      </c>
+      <c r="R3" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="S3" s="17" t="n">
+        <v>75</v>
+      </c>
+      <c r="T3" s="17" t="n">
+        <v>1200</v>
+      </c>
+      <c r="U3" s="17" t="n">
+        <v>38.73</v>
+      </c>
+      <c r="V3" s="17" t="n">
+        <v>50.35</v>
+      </c>
+      <c r="W3" s="17" t="n">
+        <v>46476</v>
+      </c>
+      <c r="X3" s="17" t="n">
+        <v>46530.51</v>
+      </c>
+      <c r="Y3" s="17" t="n">
+        <v>73524</v>
+      </c>
+      <c r="Z3" s="17" t="n">
+        <v>13942.8</v>
+      </c>
+      <c r="AA3" s="17" t="n">
+        <v>13942.8</v>
+      </c>
+      <c r="AB3" s="17" t="n">
+        <v>13944</v>
+      </c>
+      <c r="AC3" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD3" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE3" s="17" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="AF3" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AG3" s="17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AH3" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI3" s="17" t="n">
+        <v>54.51</v>
+      </c>
+      <c r="AJ3" s="17" t="n">
+        <v>13889.49</v>
+      </c>
+      <c r="AK3" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AL3" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM3" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BULLISH EMA:BEARISH</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>23385.72</v>
+      </c>
+      <c r="H4" s="15" t="n">
+        <v>23538</v>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="K4" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M4" s="15" t="inlineStr">
+        <is>
+          <t>11:13 IST</t>
+        </is>
+      </c>
+      <c r="N4" s="15" t="n">
+        <v>23622.9</v>
+      </c>
+      <c r="O4" s="15" t="n">
+        <v>23161.6</v>
+      </c>
+      <c r="P4" s="15" t="inlineStr">
+        <is>
+          <t>23700 PE</t>
+        </is>
+      </c>
+      <c r="Q4" s="15" t="inlineStr">
+        <is>
+          <t>23600 PE</t>
+        </is>
+      </c>
+      <c r="R4" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="S4" s="15" t="n">
+        <v>75</v>
+      </c>
+      <c r="T4" s="15" t="n">
+        <v>1875</v>
+      </c>
+      <c r="U4" s="15" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="V4" s="15" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="W4" s="15" t="n">
+        <v>48337.5</v>
+      </c>
+      <c r="X4" s="15" t="n">
+        <v>48392.31</v>
+      </c>
+      <c r="Y4" s="15" t="n">
+        <v>139162.5</v>
+      </c>
+      <c r="Z4" s="15" t="n">
+        <v>14501.25</v>
+      </c>
+      <c r="AA4" s="15" t="n">
+        <v>14501.25</v>
+      </c>
+      <c r="AB4" s="15" t="n">
+        <v>-14493.75</v>
+      </c>
+      <c r="AC4" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AD4" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE4" s="15" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="AF4" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG4" s="15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH4" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI4" s="15" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="AJ4" s="15" t="n">
+        <v>-14548.56</v>
+      </c>
+      <c r="AK4" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AL4" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM4" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
         </is>
       </c>
     </row>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA3"/>
+  <dimension ref="A1:AA4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -874,6 +874,105 @@
         <v>1000</v>
       </c>
       <c r="AA3" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>15:00 ET</t>
+        </is>
+      </c>
+      <c r="H4" s="16" t="n">
+        <v>30463.75</v>
+      </c>
+      <c r="I4" s="16" t="n">
+        <v>30450</v>
+      </c>
+      <c r="J4" s="16" t="n">
+        <v>30475</v>
+      </c>
+      <c r="K4" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="L4" s="16" t="n">
+        <v>139.72</v>
+      </c>
+      <c r="M4" s="16" t="n">
+        <v>144.35</v>
+      </c>
+      <c r="N4" s="16" t="n">
+        <v>882.72</v>
+      </c>
+      <c r="O4" s="16" t="n">
+        <v>2161.68</v>
+      </c>
+      <c r="P4" s="16" t="n">
+        <v>251.5</v>
+      </c>
+      <c r="Q4" s="16" t="n">
+        <v>251.5</v>
+      </c>
+      <c r="R4" s="16" t="n">
+        <v>27.78</v>
+      </c>
+      <c r="S4" s="16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T4" s="16" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="U4" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="V4" s="16" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="W4" s="16" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="X4" s="16" t="n">
+        <v>-16.62</v>
+      </c>
+      <c r="Y4" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="Z4" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" s="16" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -2779,7 +2878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA3"/>
+  <dimension ref="A1:AA4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3054,6 +3153,105 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>11:01 ET</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="n">
+        <v>30463.75</v>
+      </c>
+      <c r="I4" s="15" t="n">
+        <v>30450</v>
+      </c>
+      <c r="J4" s="15" t="n">
+        <v>30475</v>
+      </c>
+      <c r="K4" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="L4" s="15" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="M4" s="15" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="N4" s="15" t="n">
+        <v>986.4</v>
+      </c>
+      <c r="O4" s="15" t="n">
+        <v>2112</v>
+      </c>
+      <c r="P4" s="15" t="n">
+        <v>266.4</v>
+      </c>
+      <c r="Q4" s="15" t="n">
+        <v>266.4</v>
+      </c>
+      <c r="R4" s="15" t="n">
+        <v>-266.4</v>
+      </c>
+      <c r="S4" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="T4" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="U4" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="V4" s="15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W4" s="15" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="X4" s="15" t="n">
+        <v>-364.8</v>
+      </c>
+      <c r="Y4" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="Z4" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -3168,7 +3366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3303,6 +3501,76 @@
       <c r="I4" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="I5" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="I6" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — STOP LOSS</t>
         </is>
       </c>
     </row>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA4"/>
+  <dimension ref="A1:AA5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -973,6 +973,105 @@
         <v>1000</v>
       </c>
       <c r="AA4" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>12:26 ET</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>30623.75</v>
+      </c>
+      <c r="I5" s="15" t="n">
+        <v>30600</v>
+      </c>
+      <c r="J5" s="15" t="n">
+        <v>30625</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="L5" s="15" t="n">
+        <v>148</v>
+      </c>
+      <c r="M5" s="15" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="N5" s="15" t="n">
+        <v>932.4</v>
+      </c>
+      <c r="O5" s="15" t="n">
+        <v>2112</v>
+      </c>
+      <c r="P5" s="15" t="n">
+        <v>266.4</v>
+      </c>
+      <c r="Q5" s="15" t="n">
+        <v>266.4</v>
+      </c>
+      <c r="R5" s="15" t="n">
+        <v>-266.4</v>
+      </c>
+      <c r="S5" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="T5" s="15" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="U5" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="V5" s="15" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="W5" s="15" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="X5" s="15" t="n">
+        <v>-310.8</v>
+      </c>
+      <c r="Y5" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="Z5" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -2878,7 +2977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA4"/>
+  <dimension ref="A1:AA5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3252,6 +3351,105 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>10:58 ET</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>30623.5</v>
+      </c>
+      <c r="I5" s="15" t="n">
+        <v>30600</v>
+      </c>
+      <c r="J5" s="15" t="n">
+        <v>30625</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>63</v>
+      </c>
+      <c r="L5" s="15" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="M5" s="15" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="N5" s="15" t="n">
+        <v>996.66</v>
+      </c>
+      <c r="O5" s="15" t="n">
+        <v>2256.66</v>
+      </c>
+      <c r="P5" s="15" t="n">
+        <v>268</v>
+      </c>
+      <c r="Q5" s="15" t="n">
+        <v>268</v>
+      </c>
+      <c r="R5" s="15" t="n">
+        <v>-267.75</v>
+      </c>
+      <c r="S5" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="T5" s="15" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="U5" s="15" t="n">
+        <v>63</v>
+      </c>
+      <c r="V5" s="15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W5" s="15" t="n">
+        <v>103.32</v>
+      </c>
+      <c r="X5" s="15" t="n">
+        <v>-371.07</v>
+      </c>
+      <c r="Y5" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="Z5" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -3366,7 +3564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3569,6 +3767,76 @@
         <v>98.40000000000001</v>
       </c>
       <c r="I6" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — STOP LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="I7" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — STOP LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>63</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E8" s="19" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>51.66</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>103.32</v>
+      </c>
+      <c r="I8" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — STOP LOSS</t>
         </is>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA6"/>
+  <dimension ref="A1:AA7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1176,6 +1176,105 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>15:16 ET</t>
+        </is>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>30506.5</v>
+      </c>
+      <c r="I7" s="16" t="n">
+        <v>30500</v>
+      </c>
+      <c r="J7" s="16" t="n">
+        <v>30525</v>
+      </c>
+      <c r="K7" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" s="16" t="n">
+        <v>226.7</v>
+      </c>
+      <c r="M7" s="16" t="n">
+        <v>221.29</v>
+      </c>
+      <c r="N7" s="16" t="n">
+        <v>936.4</v>
+      </c>
+      <c r="O7" s="16" t="n">
+        <v>1093.2</v>
+      </c>
+      <c r="P7" s="16" t="n">
+        <v>272.04</v>
+      </c>
+      <c r="Q7" s="16" t="n">
+        <v>272.04</v>
+      </c>
+      <c r="R7" s="16" t="n">
+        <v>-21.64</v>
+      </c>
+      <c r="S7" s="16" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="T7" s="16" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="U7" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="V7" s="16" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W7" s="16" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="X7" s="16" t="n">
+        <v>-51.24</v>
+      </c>
+      <c r="Y7" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="Z7" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -1190,7 +1289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM4"/>
+  <dimension ref="A1:AM5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1732,6 +1831,153 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>56788.95</v>
+      </c>
+      <c r="H5" s="16" t="n">
+        <v>55679.28</v>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J5" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="K5" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="L5" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M5" s="16" t="inlineStr">
+        <is>
+          <t>14:40 IST</t>
+        </is>
+      </c>
+      <c r="N5" s="16" t="n">
+        <v>57685.75</v>
+      </c>
+      <c r="O5" s="16" t="n">
+        <v>57963.8</v>
+      </c>
+      <c r="P5" s="16" t="inlineStr">
+        <is>
+          <t>57600 CE</t>
+        </is>
+      </c>
+      <c r="Q5" s="16" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="R5" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="S5" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="T5" s="16" t="n">
+        <v>960</v>
+      </c>
+      <c r="U5" s="16" t="n">
+        <v>50.62</v>
+      </c>
+      <c r="V5" s="16" t="n">
+        <v>49.94</v>
+      </c>
+      <c r="W5" s="16" t="n">
+        <v>48595.2</v>
+      </c>
+      <c r="X5" s="16" t="n">
+        <v>48650.05</v>
+      </c>
+      <c r="Y5" s="16" t="n">
+        <v>143404.8</v>
+      </c>
+      <c r="Z5" s="16" t="n">
+        <v>14578.56</v>
+      </c>
+      <c r="AA5" s="16" t="n">
+        <v>14578.56</v>
+      </c>
+      <c r="AB5" s="16" t="n">
+        <v>-652.8</v>
+      </c>
+      <c r="AC5" s="16" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="AD5" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE5" s="16" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="AF5" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG5" s="16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AH5" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI5" s="16" t="n">
+        <v>54.85</v>
+      </c>
+      <c r="AJ5" s="16" t="n">
+        <v>-707.65</v>
+      </c>
+      <c r="AK5" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AL5" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM5" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -1746,7 +1992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM4"/>
+  <dimension ref="A1:AM5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2288,6 +2534,153 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>56788.95</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>55679.28</v>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J5" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="L5" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M5" s="15" t="inlineStr">
+        <is>
+          <t>10:10 IST</t>
+        </is>
+      </c>
+      <c r="N5" s="15" t="n">
+        <v>57685.75</v>
+      </c>
+      <c r="O5" s="15" t="n">
+        <v>57963.8</v>
+      </c>
+      <c r="P5" s="15" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="Q5" s="15" t="inlineStr">
+        <is>
+          <t>57600 PE</t>
+        </is>
+      </c>
+      <c r="R5" s="15" t="n">
+        <v>31</v>
+      </c>
+      <c r="S5" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="T5" s="15" t="n">
+        <v>930</v>
+      </c>
+      <c r="U5" s="15" t="n">
+        <v>51.34</v>
+      </c>
+      <c r="V5" s="15" t="n">
+        <v>35.94</v>
+      </c>
+      <c r="W5" s="15" t="n">
+        <v>47746.2</v>
+      </c>
+      <c r="X5" s="15" t="n">
+        <v>47800.91</v>
+      </c>
+      <c r="Y5" s="15" t="n">
+        <v>138253.8</v>
+      </c>
+      <c r="Z5" s="15" t="n">
+        <v>14323.86</v>
+      </c>
+      <c r="AA5" s="15" t="n">
+        <v>14323.86</v>
+      </c>
+      <c r="AB5" s="15" t="n">
+        <v>-14322</v>
+      </c>
+      <c r="AC5" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AD5" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE5" s="15" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="AF5" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG5" s="15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH5" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI5" s="15" t="n">
+        <v>54.71</v>
+      </c>
+      <c r="AJ5" s="15" t="n">
+        <v>-14376.71</v>
+      </c>
+      <c r="AK5" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AL5" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM5" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -2302,7 +2695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM6"/>
+  <dimension ref="A1:AM8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3133,6 +3526,300 @@
         <v>50000</v>
       </c>
       <c r="AM6" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>56788.95</v>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>55679.28</v>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J7" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="K7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="L7" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M7" s="17" t="inlineStr">
+        <is>
+          <t>10:32 IST</t>
+        </is>
+      </c>
+      <c r="N7" s="17" t="n">
+        <v>57685.75</v>
+      </c>
+      <c r="O7" s="17" t="n">
+        <v>57963.8</v>
+      </c>
+      <c r="P7" s="17" t="inlineStr">
+        <is>
+          <t>57600 CE</t>
+        </is>
+      </c>
+      <c r="Q7" s="17" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="R7" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="S7" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T7" s="17" t="n">
+        <v>630</v>
+      </c>
+      <c r="U7" s="17" t="n">
+        <v>76.20999999999999</v>
+      </c>
+      <c r="V7" s="17" t="n">
+        <v>99.06999999999999</v>
+      </c>
+      <c r="W7" s="17" t="n">
+        <v>48012.3</v>
+      </c>
+      <c r="X7" s="17" t="n">
+        <v>48067.06</v>
+      </c>
+      <c r="Y7" s="17" t="n">
+        <v>77987.7</v>
+      </c>
+      <c r="Z7" s="17" t="n">
+        <v>14403.69</v>
+      </c>
+      <c r="AA7" s="17" t="n">
+        <v>14403.69</v>
+      </c>
+      <c r="AB7" s="17" t="n">
+        <v>14401.8</v>
+      </c>
+      <c r="AC7" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD7" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF7" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG7" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH7" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI7" s="17" t="n">
+        <v>54.76</v>
+      </c>
+      <c r="AJ7" s="17" t="n">
+        <v>14347.04</v>
+      </c>
+      <c r="AK7" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AL7" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM7" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>56788.95</v>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>55679.28</v>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J8" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="K8" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="L8" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M8" s="17" t="inlineStr">
+        <is>
+          <t>10:02 IST</t>
+        </is>
+      </c>
+      <c r="N8" s="17" t="n">
+        <v>57685.75</v>
+      </c>
+      <c r="O8" s="17" t="n">
+        <v>57963.8</v>
+      </c>
+      <c r="P8" s="17" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="Q8" s="17" t="inlineStr">
+        <is>
+          <t>57600 PE</t>
+        </is>
+      </c>
+      <c r="R8" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="S8" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T8" s="17" t="n">
+        <v>630</v>
+      </c>
+      <c r="U8" s="17" t="n">
+        <v>74.43000000000001</v>
+      </c>
+      <c r="V8" s="17" t="n">
+        <v>96.76000000000001</v>
+      </c>
+      <c r="W8" s="17" t="n">
+        <v>46890.9</v>
+      </c>
+      <c r="X8" s="17" t="n">
+        <v>46945.48</v>
+      </c>
+      <c r="Y8" s="17" t="n">
+        <v>79109.10000000001</v>
+      </c>
+      <c r="Z8" s="17" t="n">
+        <v>14067.27</v>
+      </c>
+      <c r="AA8" s="17" t="n">
+        <v>14067.27</v>
+      </c>
+      <c r="AB8" s="17" t="n">
+        <v>14067.9</v>
+      </c>
+      <c r="AC8" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD8" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE8" s="17" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="AF8" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AG8" s="17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH8" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI8" s="17" t="n">
+        <v>54.58</v>
+      </c>
+      <c r="AJ8" s="17" t="n">
+        <v>14013.32</v>
+      </c>
+      <c r="AK8" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AL8" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM8" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -3708,7 +4395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3792,6 +4479,72 @@
         <v>23538</v>
       </c>
       <c r="G3" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="n">
+        <v>23824.67</v>
+      </c>
+      <c r="F4" s="18" t="n">
+        <v>23712.22</v>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>56788.95</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>55679.28</v>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -3811,7 +4564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA6"/>
+  <dimension ref="A1:AA7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4383,6 +5136,105 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>15:28 ET</t>
+        </is>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>30508</v>
+      </c>
+      <c r="I7" s="16" t="n">
+        <v>30500</v>
+      </c>
+      <c r="J7" s="16" t="n">
+        <v>30525</v>
+      </c>
+      <c r="K7" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="L7" s="16" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="M7" s="16" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="N7" s="16" t="n">
+        <v>993.6</v>
+      </c>
+      <c r="O7" s="16" t="n">
+        <v>1072</v>
+      </c>
+      <c r="P7" s="16" t="n">
+        <v>278.4</v>
+      </c>
+      <c r="Q7" s="16" t="n">
+        <v>278.4</v>
+      </c>
+      <c r="R7" s="16" t="n">
+        <v>-13.6</v>
+      </c>
+      <c r="S7" s="16" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="T7" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="U7" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="V7" s="16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W7" s="16" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="X7" s="16" t="n">
+        <v>-79.2</v>
+      </c>
+      <c r="Y7" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="Z7" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -4497,7 +5349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4842,6 +5694,76 @@
       <c r="I10" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — STOP LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I11" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="I12" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — FLAT</t>
         </is>
       </c>
     </row>
@@ -5308,7 +6230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM4"/>
+  <dimension ref="A1:AM5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5850,6 +6772,153 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>23824.67</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>23712.22</v>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J5" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="L5" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M5" s="15" t="inlineStr">
+        <is>
+          <t>10:43 IST</t>
+        </is>
+      </c>
+      <c r="N5" s="15" t="n">
+        <v>24013.1</v>
+      </c>
+      <c r="O5" s="15" t="n">
+        <v>24168</v>
+      </c>
+      <c r="P5" s="15" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="Q5" s="15" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="R5" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="S5" s="15" t="n">
+        <v>75</v>
+      </c>
+      <c r="T5" s="15" t="n">
+        <v>1425</v>
+      </c>
+      <c r="U5" s="15" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="V5" s="15" t="n">
+        <v>23.27</v>
+      </c>
+      <c r="W5" s="15" t="n">
+        <v>47381.25</v>
+      </c>
+      <c r="X5" s="15" t="n">
+        <v>47435.91</v>
+      </c>
+      <c r="Y5" s="15" t="n">
+        <v>95118.75</v>
+      </c>
+      <c r="Z5" s="15" t="n">
+        <v>14214.38</v>
+      </c>
+      <c r="AA5" s="15" t="n">
+        <v>14214.38</v>
+      </c>
+      <c r="AB5" s="15" t="n">
+        <v>-14221.5</v>
+      </c>
+      <c r="AC5" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AD5" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE5" s="15" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="AF5" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AG5" s="15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH5" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI5" s="15" t="n">
+        <v>54.66</v>
+      </c>
+      <c r="AJ5" s="15" t="n">
+        <v>-14276.16</v>
+      </c>
+      <c r="AK5" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AL5" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM5" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -5864,7 +6933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM4"/>
+  <dimension ref="A1:AM5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6406,6 +7475,153 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>23824.67</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>23712.22</v>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J5" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="L5" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M5" s="15" t="inlineStr">
+        <is>
+          <t>10:32 IST</t>
+        </is>
+      </c>
+      <c r="N5" s="15" t="n">
+        <v>24013.1</v>
+      </c>
+      <c r="O5" s="15" t="n">
+        <v>24168</v>
+      </c>
+      <c r="P5" s="15" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="Q5" s="15" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="R5" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="S5" s="15" t="n">
+        <v>75</v>
+      </c>
+      <c r="T5" s="15" t="n">
+        <v>1350</v>
+      </c>
+      <c r="U5" s="15" t="n">
+        <v>35.26</v>
+      </c>
+      <c r="V5" s="15" t="n">
+        <v>24.68</v>
+      </c>
+      <c r="W5" s="15" t="n">
+        <v>47601</v>
+      </c>
+      <c r="X5" s="15" t="n">
+        <v>47655.69</v>
+      </c>
+      <c r="Y5" s="15" t="n">
+        <v>87399</v>
+      </c>
+      <c r="Z5" s="15" t="n">
+        <v>14280.3</v>
+      </c>
+      <c r="AA5" s="15" t="n">
+        <v>14280.3</v>
+      </c>
+      <c r="AB5" s="15" t="n">
+        <v>-14283</v>
+      </c>
+      <c r="AC5" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AD5" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE5" s="15" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AF5" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG5" s="15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH5" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI5" s="15" t="n">
+        <v>54.69</v>
+      </c>
+      <c r="AJ5" s="15" t="n">
+        <v>-14337.69</v>
+      </c>
+      <c r="AK5" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AL5" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM5" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -6420,7 +7636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM6"/>
+  <dimension ref="A1:AM8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7251,6 +8467,300 @@
         <v>50000</v>
       </c>
       <c r="AM6" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>23824.67</v>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>23712.22</v>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J7" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="K7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="L7" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M7" s="17" t="inlineStr">
+        <is>
+          <t>12:16 IST</t>
+        </is>
+      </c>
+      <c r="N7" s="17" t="n">
+        <v>24013.1</v>
+      </c>
+      <c r="O7" s="17" t="n">
+        <v>24168</v>
+      </c>
+      <c r="P7" s="17" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="Q7" s="17" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="R7" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="S7" s="17" t="n">
+        <v>75</v>
+      </c>
+      <c r="T7" s="17" t="n">
+        <v>1875</v>
+      </c>
+      <c r="U7" s="17" t="n">
+        <v>25.32</v>
+      </c>
+      <c r="V7" s="17" t="n">
+        <v>32.92</v>
+      </c>
+      <c r="W7" s="17" t="n">
+        <v>47475</v>
+      </c>
+      <c r="X7" s="17" t="n">
+        <v>47529.67</v>
+      </c>
+      <c r="Y7" s="17" t="n">
+        <v>140025</v>
+      </c>
+      <c r="Z7" s="17" t="n">
+        <v>14242.5</v>
+      </c>
+      <c r="AA7" s="17" t="n">
+        <v>14242.5</v>
+      </c>
+      <c r="AB7" s="17" t="n">
+        <v>14250</v>
+      </c>
+      <c r="AC7" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD7" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE7" s="17" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="AF7" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AG7" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH7" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI7" s="17" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="AJ7" s="17" t="n">
+        <v>14195.33</v>
+      </c>
+      <c r="AK7" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AL7" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM7" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>23824.67</v>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>23712.22</v>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J8" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="K8" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="L8" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M8" s="17" t="inlineStr">
+        <is>
+          <t>09:54 IST</t>
+        </is>
+      </c>
+      <c r="N8" s="17" t="n">
+        <v>24013.1</v>
+      </c>
+      <c r="O8" s="17" t="n">
+        <v>24168</v>
+      </c>
+      <c r="P8" s="17" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="Q8" s="17" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="R8" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="S8" s="17" t="n">
+        <v>75</v>
+      </c>
+      <c r="T8" s="17" t="n">
+        <v>1425</v>
+      </c>
+      <c r="U8" s="17" t="n">
+        <v>33.62</v>
+      </c>
+      <c r="V8" s="17" t="n">
+        <v>43.71</v>
+      </c>
+      <c r="W8" s="17" t="n">
+        <v>47908.5</v>
+      </c>
+      <c r="X8" s="17" t="n">
+        <v>47963.24</v>
+      </c>
+      <c r="Y8" s="17" t="n">
+        <v>94591.5</v>
+      </c>
+      <c r="Z8" s="17" t="n">
+        <v>14372.55</v>
+      </c>
+      <c r="AA8" s="17" t="n">
+        <v>14372.55</v>
+      </c>
+      <c r="AB8" s="17" t="n">
+        <v>14378.25</v>
+      </c>
+      <c r="AC8" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD8" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE8" s="17" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="AF8" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG8" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH8" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI8" s="17" t="n">
+        <v>54.74</v>
+      </c>
+      <c r="AJ8" s="17" t="n">
+        <v>14323.51</v>
+      </c>
+      <c r="AK8" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AL8" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM8" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA8"/>
+  <dimension ref="A1:AA9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1374,6 +1374,105 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G9" s="17" t="inlineStr">
+        <is>
+          <t>12:16 ET</t>
+        </is>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>30627.75</v>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>30625</v>
+      </c>
+      <c r="J9" s="17" t="n">
+        <v>30650</v>
+      </c>
+      <c r="K9" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" s="17" t="n">
+        <v>267.2</v>
+      </c>
+      <c r="M9" s="17" t="n">
+        <v>347.36</v>
+      </c>
+      <c r="N9" s="17" t="n">
+        <v>823.8</v>
+      </c>
+      <c r="O9" s="17" t="n">
+        <v>698.4</v>
+      </c>
+      <c r="P9" s="17" t="n">
+        <v>240.48</v>
+      </c>
+      <c r="Q9" s="17" t="n">
+        <v>240.48</v>
+      </c>
+      <c r="R9" s="17" t="n">
+        <v>240.48</v>
+      </c>
+      <c r="S9" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T9" s="17" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="U9" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="V9" s="17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W9" s="17" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="X9" s="17" t="n">
+        <v>218.28</v>
+      </c>
+      <c r="Y9" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z9" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -1388,7 +1487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM6"/>
+  <dimension ref="A1:AM7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2224,6 +2323,153 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>56787.29</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>55649.38</v>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J7" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M7" s="15" t="inlineStr">
+        <is>
+          <t>11:05 IST</t>
+        </is>
+      </c>
+      <c r="N7" s="15" t="n">
+        <v>57685.75</v>
+      </c>
+      <c r="O7" s="15" t="n">
+        <v>57963.8</v>
+      </c>
+      <c r="P7" s="15" t="inlineStr">
+        <is>
+          <t>57600 CE</t>
+        </is>
+      </c>
+      <c r="Q7" s="15" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="R7" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="S7" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="T7" s="15" t="n">
+        <v>660</v>
+      </c>
+      <c r="U7" s="15" t="n">
+        <v>71.52</v>
+      </c>
+      <c r="V7" s="15" t="n">
+        <v>50.06</v>
+      </c>
+      <c r="W7" s="15" t="n">
+        <v>47203.2</v>
+      </c>
+      <c r="X7" s="15" t="n">
+        <v>47257.83</v>
+      </c>
+      <c r="Y7" s="15" t="n">
+        <v>84796.8</v>
+      </c>
+      <c r="Z7" s="15" t="n">
+        <v>14160.96</v>
+      </c>
+      <c r="AA7" s="15" t="n">
+        <v>14160.96</v>
+      </c>
+      <c r="AB7" s="15" t="n">
+        <v>-14163.6</v>
+      </c>
+      <c r="AC7" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AD7" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE7" s="15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF7" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AG7" s="15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH7" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI7" s="15" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="AJ7" s="15" t="n">
+        <v>-14218.23</v>
+      </c>
+      <c r="AK7" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AL7" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM7" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -2238,7 +2484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM6"/>
+  <dimension ref="A1:AM7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3074,6 +3320,153 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>56787.29</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>55649.38</v>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="K7" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M7" s="16" t="inlineStr">
+        <is>
+          <t>13:41 IST</t>
+        </is>
+      </c>
+      <c r="N7" s="16" t="n">
+        <v>57685.75</v>
+      </c>
+      <c r="O7" s="16" t="n">
+        <v>57963.8</v>
+      </c>
+      <c r="P7" s="16" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="Q7" s="16" t="inlineStr">
+        <is>
+          <t>57600 PE</t>
+        </is>
+      </c>
+      <c r="R7" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="T7" s="16" t="n">
+        <v>600</v>
+      </c>
+      <c r="U7" s="16" t="n">
+        <v>78.97</v>
+      </c>
+      <c r="V7" s="16" t="n">
+        <v>75.94</v>
+      </c>
+      <c r="W7" s="16" t="n">
+        <v>47382</v>
+      </c>
+      <c r="X7" s="16" t="n">
+        <v>47436.66</v>
+      </c>
+      <c r="Y7" s="16" t="n">
+        <v>72618</v>
+      </c>
+      <c r="Z7" s="16" t="n">
+        <v>14214.6</v>
+      </c>
+      <c r="AA7" s="16" t="n">
+        <v>14214.6</v>
+      </c>
+      <c r="AB7" s="16" t="n">
+        <v>-1818</v>
+      </c>
+      <c r="AC7" s="16" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="AD7" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE7" s="16" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="AF7" s="16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AG7" s="16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH7" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI7" s="16" t="n">
+        <v>54.66</v>
+      </c>
+      <c r="AJ7" s="16" t="n">
+        <v>-1872.66</v>
+      </c>
+      <c r="AK7" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AL7" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM7" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -3088,7 +3481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM10"/>
+  <dimension ref="A1:AM12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4507,6 +4900,300 @@
         <v>50000</v>
       </c>
       <c r="AM10" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>56787.29</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>55649.38</v>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J11" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="K11" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M11" s="17" t="inlineStr">
+        <is>
+          <t>10:59 IST</t>
+        </is>
+      </c>
+      <c r="N11" s="17" t="n">
+        <v>57685.75</v>
+      </c>
+      <c r="O11" s="17" t="n">
+        <v>57963.8</v>
+      </c>
+      <c r="P11" s="17" t="inlineStr">
+        <is>
+          <t>57600 CE</t>
+        </is>
+      </c>
+      <c r="Q11" s="17" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="R11" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="S11" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T11" s="17" t="n">
+        <v>750</v>
+      </c>
+      <c r="U11" s="17" t="n">
+        <v>63.67</v>
+      </c>
+      <c r="V11" s="17" t="n">
+        <v>82.77</v>
+      </c>
+      <c r="W11" s="17" t="n">
+        <v>47752.5</v>
+      </c>
+      <c r="X11" s="17" t="n">
+        <v>47807.21</v>
+      </c>
+      <c r="Y11" s="17" t="n">
+        <v>102247.5</v>
+      </c>
+      <c r="Z11" s="17" t="n">
+        <v>14325.75</v>
+      </c>
+      <c r="AA11" s="17" t="n">
+        <v>14325.75</v>
+      </c>
+      <c r="AB11" s="17" t="n">
+        <v>14325</v>
+      </c>
+      <c r="AC11" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD11" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE11" s="17" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="AF11" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG11" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH11" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI11" s="17" t="n">
+        <v>54.71</v>
+      </c>
+      <c r="AJ11" s="17" t="n">
+        <v>14270.29</v>
+      </c>
+      <c r="AK11" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AL11" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM11" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>56787.29</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <v>55649.38</v>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="K12" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M12" s="16" t="inlineStr">
+        <is>
+          <t>15:03 IST</t>
+        </is>
+      </c>
+      <c r="N12" s="16" t="n">
+        <v>57685.75</v>
+      </c>
+      <c r="O12" s="16" t="n">
+        <v>57963.8</v>
+      </c>
+      <c r="P12" s="16" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="Q12" s="16" t="inlineStr">
+        <is>
+          <t>57600 PE</t>
+        </is>
+      </c>
+      <c r="R12" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="S12" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="T12" s="16" t="n">
+        <v>870</v>
+      </c>
+      <c r="U12" s="16" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="V12" s="16" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="W12" s="16" t="n">
+        <v>47545.5</v>
+      </c>
+      <c r="X12" s="16" t="n">
+        <v>47600.18</v>
+      </c>
+      <c r="Y12" s="16" t="n">
+        <v>126454.5</v>
+      </c>
+      <c r="Z12" s="16" t="n">
+        <v>14263.65</v>
+      </c>
+      <c r="AA12" s="16" t="n">
+        <v>14263.65</v>
+      </c>
+      <c r="AB12" s="16" t="n">
+        <v>2166.3</v>
+      </c>
+      <c r="AC12" s="16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD12" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE12" s="16" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AF12" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG12" s="16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH12" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI12" s="16" t="n">
+        <v>54.68</v>
+      </c>
+      <c r="AJ12" s="16" t="n">
+        <v>2111.62</v>
+      </c>
+      <c r="AK12" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AL12" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM12" s="16" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -5229,7 +5916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5379,6 +6066,72 @@
         <v>55679.28</v>
       </c>
       <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>23824.22</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>23714.31</v>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>56787.29</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>55649.38</v>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -5398,7 +6151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA8"/>
+  <dimension ref="A1:AA9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6168,6 +6921,105 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t>15:44 ET</t>
+        </is>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>30629</v>
+      </c>
+      <c r="I9" s="16" t="n">
+        <v>30625</v>
+      </c>
+      <c r="J9" s="16" t="n">
+        <v>30650</v>
+      </c>
+      <c r="K9" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="L9" s="16" t="n">
+        <v>22.98</v>
+      </c>
+      <c r="M9" s="16" t="n">
+        <v>23.14</v>
+      </c>
+      <c r="N9" s="16" t="n">
+        <v>984.8</v>
+      </c>
+      <c r="O9" s="16" t="n">
+        <v>1080.8</v>
+      </c>
+      <c r="P9" s="16" t="n">
+        <v>275.76</v>
+      </c>
+      <c r="Q9" s="16" t="n">
+        <v>275.76</v>
+      </c>
+      <c r="R9" s="16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="S9" s="16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T9" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="U9" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="V9" s="16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W9" s="16" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="X9" s="16" t="n">
+        <v>-59.2</v>
+      </c>
+      <c r="Y9" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="Z9" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -6282,7 +7134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6767,6 +7619,76 @@
       <c r="I14" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — STOP LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="I15" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="D16" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="E16" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="H16" s="19" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="I16" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — FLAT</t>
         </is>
       </c>
     </row>
@@ -7233,7 +8155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM6"/>
+  <dimension ref="A1:AM7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8069,6 +8991,153 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>23824.22</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>23714.31</v>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="K7" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M7" s="16" t="inlineStr">
+        <is>
+          <t>14:04 IST</t>
+        </is>
+      </c>
+      <c r="N7" s="16" t="n">
+        <v>24013.1</v>
+      </c>
+      <c r="O7" s="16" t="n">
+        <v>24168</v>
+      </c>
+      <c r="P7" s="16" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="Q7" s="16" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="R7" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="S7" s="16" t="n">
+        <v>75</v>
+      </c>
+      <c r="T7" s="16" t="n">
+        <v>1575</v>
+      </c>
+      <c r="U7" s="16" t="n">
+        <v>30.13</v>
+      </c>
+      <c r="V7" s="16" t="n">
+        <v>29.89</v>
+      </c>
+      <c r="W7" s="16" t="n">
+        <v>47454.75</v>
+      </c>
+      <c r="X7" s="16" t="n">
+        <v>47509.42</v>
+      </c>
+      <c r="Y7" s="16" t="n">
+        <v>110045.25</v>
+      </c>
+      <c r="Z7" s="16" t="n">
+        <v>14236.42</v>
+      </c>
+      <c r="AA7" s="16" t="n">
+        <v>14236.42</v>
+      </c>
+      <c r="AB7" s="16" t="n">
+        <v>-378</v>
+      </c>
+      <c r="AC7" s="16" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AD7" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE7" s="16" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="AF7" s="16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AG7" s="16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH7" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI7" s="16" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="AJ7" s="16" t="n">
+        <v>-432.67</v>
+      </c>
+      <c r="AK7" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AL7" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM7" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -8083,7 +9152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM6"/>
+  <dimension ref="A1:AM7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8919,6 +9988,153 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>23824.22</v>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>23714.31</v>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J7" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="K7" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M7" s="17" t="inlineStr">
+        <is>
+          <t>10:13 IST</t>
+        </is>
+      </c>
+      <c r="N7" s="17" t="n">
+        <v>24013.1</v>
+      </c>
+      <c r="O7" s="17" t="n">
+        <v>24168</v>
+      </c>
+      <c r="P7" s="17" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="Q7" s="17" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="R7" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="S7" s="17" t="n">
+        <v>75</v>
+      </c>
+      <c r="T7" s="17" t="n">
+        <v>1275</v>
+      </c>
+      <c r="U7" s="17" t="n">
+        <v>38.19</v>
+      </c>
+      <c r="V7" s="17" t="n">
+        <v>49.65</v>
+      </c>
+      <c r="W7" s="17" t="n">
+        <v>48692.25</v>
+      </c>
+      <c r="X7" s="17" t="n">
+        <v>48747.11</v>
+      </c>
+      <c r="Y7" s="17" t="n">
+        <v>78807.75</v>
+      </c>
+      <c r="Z7" s="17" t="n">
+        <v>14607.67</v>
+      </c>
+      <c r="AA7" s="17" t="n">
+        <v>14607.67</v>
+      </c>
+      <c r="AB7" s="17" t="n">
+        <v>14611.5</v>
+      </c>
+      <c r="AC7" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD7" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE7" s="17" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="AF7" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG7" s="17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AH7" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI7" s="17" t="n">
+        <v>54.86</v>
+      </c>
+      <c r="AJ7" s="17" t="n">
+        <v>14556.64</v>
+      </c>
+      <c r="AK7" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AL7" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM7" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -8933,7 +10149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM10"/>
+  <dimension ref="A1:AM12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10352,6 +11568,300 @@
         <v>50000</v>
       </c>
       <c r="AM10" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>23824.22</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>23714.31</v>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J11" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="K11" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M11" s="15" t="inlineStr">
+        <is>
+          <t>09:51 IST</t>
+        </is>
+      </c>
+      <c r="N11" s="15" t="n">
+        <v>24013.1</v>
+      </c>
+      <c r="O11" s="15" t="n">
+        <v>24168</v>
+      </c>
+      <c r="P11" s="15" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="Q11" s="15" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="R11" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="S11" s="15" t="n">
+        <v>75</v>
+      </c>
+      <c r="T11" s="15" t="n">
+        <v>1350</v>
+      </c>
+      <c r="U11" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="V11" s="15" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="W11" s="15" t="n">
+        <v>47250</v>
+      </c>
+      <c r="X11" s="15" t="n">
+        <v>47304.64</v>
+      </c>
+      <c r="Y11" s="15" t="n">
+        <v>87750</v>
+      </c>
+      <c r="Z11" s="15" t="n">
+        <v>14175</v>
+      </c>
+      <c r="AA11" s="15" t="n">
+        <v>14175</v>
+      </c>
+      <c r="AB11" s="15" t="n">
+        <v>-14175</v>
+      </c>
+      <c r="AC11" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AD11" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE11" s="15" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AF11" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AG11" s="15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH11" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI11" s="15" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="AJ11" s="15" t="n">
+        <v>-14229.64</v>
+      </c>
+      <c r="AK11" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AL11" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM11" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="n">
+        <v>23824.22</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>23714.31</v>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J12" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="K12" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M12" s="17" t="inlineStr">
+        <is>
+          <t>10:07 IST</t>
+        </is>
+      </c>
+      <c r="N12" s="17" t="n">
+        <v>24013.1</v>
+      </c>
+      <c r="O12" s="17" t="n">
+        <v>24168</v>
+      </c>
+      <c r="P12" s="17" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="Q12" s="17" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="R12" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="S12" s="17" t="n">
+        <v>75</v>
+      </c>
+      <c r="T12" s="17" t="n">
+        <v>1275</v>
+      </c>
+      <c r="U12" s="17" t="n">
+        <v>37.94</v>
+      </c>
+      <c r="V12" s="17" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="W12" s="17" t="n">
+        <v>48373.5</v>
+      </c>
+      <c r="X12" s="17" t="n">
+        <v>48428.31</v>
+      </c>
+      <c r="Y12" s="17" t="n">
+        <v>79126.5</v>
+      </c>
+      <c r="Z12" s="17" t="n">
+        <v>14512.05</v>
+      </c>
+      <c r="AA12" s="17" t="n">
+        <v>14512.05</v>
+      </c>
+      <c r="AB12" s="17" t="n">
+        <v>14509.5</v>
+      </c>
+      <c r="AC12" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD12" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE12" s="17" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AF12" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG12" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH12" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI12" s="17" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="AJ12" s="17" t="n">
+        <v>14454.69</v>
+      </c>
+      <c r="AK12" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AL12" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM12" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA9"/>
+  <dimension ref="A1:AA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1473,6 +1473,105 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="inlineStr">
+        <is>
+          <t>11:12 ET</t>
+        </is>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>30662.5</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>30650</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>30675</v>
+      </c>
+      <c r="K10" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" s="17" t="n">
+        <v>237.6</v>
+      </c>
+      <c r="M10" s="17" t="n">
+        <v>308.88</v>
+      </c>
+      <c r="N10" s="17" t="n">
+        <v>980</v>
+      </c>
+      <c r="O10" s="17" t="n">
+        <v>1049.6</v>
+      </c>
+      <c r="P10" s="17" t="n">
+        <v>285.12</v>
+      </c>
+      <c r="Q10" s="17" t="n">
+        <v>285.12</v>
+      </c>
+      <c r="R10" s="17" t="n">
+        <v>285.12</v>
+      </c>
+      <c r="S10" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T10" s="17" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="U10" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="V10" s="17" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W10" s="17" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="X10" s="17" t="n">
+        <v>255.52</v>
+      </c>
+      <c r="Y10" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z10" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -1487,7 +1586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM7"/>
+  <dimension ref="A1:AM8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2470,6 +2569,153 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>56787.29</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>55649.38</v>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J8" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M8" s="15" t="inlineStr">
+        <is>
+          <t>10:34 IST</t>
+        </is>
+      </c>
+      <c r="N8" s="15" t="n">
+        <v>57685.75</v>
+      </c>
+      <c r="O8" s="15" t="n">
+        <v>57963.8</v>
+      </c>
+      <c r="P8" s="15" t="inlineStr">
+        <is>
+          <t>57600 CE</t>
+        </is>
+      </c>
+      <c r="Q8" s="15" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="R8" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="S8" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="T8" s="15" t="n">
+        <v>690</v>
+      </c>
+      <c r="U8" s="15" t="n">
+        <v>68.47</v>
+      </c>
+      <c r="V8" s="15" t="n">
+        <v>47.93</v>
+      </c>
+      <c r="W8" s="15" t="n">
+        <v>47244.3</v>
+      </c>
+      <c r="X8" s="15" t="n">
+        <v>47298.93</v>
+      </c>
+      <c r="Y8" s="15" t="n">
+        <v>90755.7</v>
+      </c>
+      <c r="Z8" s="15" t="n">
+        <v>14173.29</v>
+      </c>
+      <c r="AA8" s="15" t="n">
+        <v>14173.29</v>
+      </c>
+      <c r="AB8" s="15" t="n">
+        <v>-14172.6</v>
+      </c>
+      <c r="AC8" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AD8" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE8" s="15" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AF8" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AG8" s="15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH8" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI8" s="15" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="AJ8" s="15" t="n">
+        <v>-14227.23</v>
+      </c>
+      <c r="AK8" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AL8" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM8" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -2484,7 +2730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM7"/>
+  <dimension ref="A1:AM8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3467,6 +3713,153 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>56787.29</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>55649.38</v>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J8" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M8" s="15" t="inlineStr">
+        <is>
+          <t>10:30 IST</t>
+        </is>
+      </c>
+      <c r="N8" s="15" t="n">
+        <v>57685.75</v>
+      </c>
+      <c r="O8" s="15" t="n">
+        <v>57963.8</v>
+      </c>
+      <c r="P8" s="15" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="Q8" s="15" t="inlineStr">
+        <is>
+          <t>57600 PE</t>
+        </is>
+      </c>
+      <c r="R8" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="S8" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="T8" s="15" t="n">
+        <v>870</v>
+      </c>
+      <c r="U8" s="15" t="n">
+        <v>54.26</v>
+      </c>
+      <c r="V8" s="15" t="n">
+        <v>37.98</v>
+      </c>
+      <c r="W8" s="15" t="n">
+        <v>47206.2</v>
+      </c>
+      <c r="X8" s="15" t="n">
+        <v>47260.83</v>
+      </c>
+      <c r="Y8" s="15" t="n">
+        <v>126793.8</v>
+      </c>
+      <c r="Z8" s="15" t="n">
+        <v>14161.86</v>
+      </c>
+      <c r="AA8" s="15" t="n">
+        <v>14161.86</v>
+      </c>
+      <c r="AB8" s="15" t="n">
+        <v>-14163.6</v>
+      </c>
+      <c r="AC8" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AD8" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE8" s="15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF8" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AG8" s="15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH8" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI8" s="15" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="AJ8" s="15" t="n">
+        <v>-14218.23</v>
+      </c>
+      <c r="AK8" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AL8" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM8" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -3481,7 +3874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM12"/>
+  <dimension ref="A1:AM14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5194,6 +5587,300 @@
         <v>50000</v>
       </c>
       <c r="AM12" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>56787.29</v>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>55649.38</v>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J13" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="K13" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M13" s="15" t="inlineStr">
+        <is>
+          <t>10:09 IST</t>
+        </is>
+      </c>
+      <c r="N13" s="15" t="n">
+        <v>57685.75</v>
+      </c>
+      <c r="O13" s="15" t="n">
+        <v>57963.8</v>
+      </c>
+      <c r="P13" s="15" t="inlineStr">
+        <is>
+          <t>57600 CE</t>
+        </is>
+      </c>
+      <c r="Q13" s="15" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="R13" s="15" t="n">
+        <v>26</v>
+      </c>
+      <c r="S13" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="T13" s="15" t="n">
+        <v>780</v>
+      </c>
+      <c r="U13" s="15" t="n">
+        <v>60.44</v>
+      </c>
+      <c r="V13" s="15" t="n">
+        <v>42.31</v>
+      </c>
+      <c r="W13" s="15" t="n">
+        <v>47143.2</v>
+      </c>
+      <c r="X13" s="15" t="n">
+        <v>47197.82</v>
+      </c>
+      <c r="Y13" s="15" t="n">
+        <v>108856.8</v>
+      </c>
+      <c r="Z13" s="15" t="n">
+        <v>14142.96</v>
+      </c>
+      <c r="AA13" s="15" t="n">
+        <v>14142.96</v>
+      </c>
+      <c r="AB13" s="15" t="n">
+        <v>-14141.4</v>
+      </c>
+      <c r="AC13" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AD13" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE13" s="15" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AF13" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AG13" s="15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH13" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI13" s="15" t="n">
+        <v>54.62</v>
+      </c>
+      <c r="AJ13" s="15" t="n">
+        <v>-14196.02</v>
+      </c>
+      <c r="AK13" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AL13" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM13" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>56787.29</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>55649.38</v>
+      </c>
+      <c r="I14" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J14" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="K14" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M14" s="17" t="inlineStr">
+        <is>
+          <t>12:05 IST</t>
+        </is>
+      </c>
+      <c r="N14" s="17" t="n">
+        <v>57685.75</v>
+      </c>
+      <c r="O14" s="17" t="n">
+        <v>57963.8</v>
+      </c>
+      <c r="P14" s="17" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="Q14" s="17" t="inlineStr">
+        <is>
+          <t>57600 PE</t>
+        </is>
+      </c>
+      <c r="R14" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="S14" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T14" s="17" t="n">
+        <v>810</v>
+      </c>
+      <c r="U14" s="17" t="n">
+        <v>59.15</v>
+      </c>
+      <c r="V14" s="17" t="n">
+        <v>76.89</v>
+      </c>
+      <c r="W14" s="17" t="n">
+        <v>47911.5</v>
+      </c>
+      <c r="X14" s="17" t="n">
+        <v>47966.24</v>
+      </c>
+      <c r="Y14" s="17" t="n">
+        <v>114088.5</v>
+      </c>
+      <c r="Z14" s="17" t="n">
+        <v>14373.45</v>
+      </c>
+      <c r="AA14" s="17" t="n">
+        <v>14373.45</v>
+      </c>
+      <c r="AB14" s="17" t="n">
+        <v>14369.4</v>
+      </c>
+      <c r="AC14" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD14" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE14" s="17" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="AF14" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG14" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH14" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI14" s="17" t="n">
+        <v>54.74</v>
+      </c>
+      <c r="AJ14" s="17" t="n">
+        <v>14314.66</v>
+      </c>
+      <c r="AK14" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AL14" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM14" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -5916,7 +6603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6132,6 +6819,72 @@
         <v>55649.38</v>
       </c>
       <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>23824.22</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>23714.31</v>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>56787.29</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>55649.38</v>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -6151,7 +6904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA9"/>
+  <dimension ref="A1:AA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7020,6 +7773,105 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="inlineStr">
+        <is>
+          <t>11:26 ET</t>
+        </is>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>30662</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>30650</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>30675</v>
+      </c>
+      <c r="K10" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="L10" s="17" t="n">
+        <v>24.02</v>
+      </c>
+      <c r="M10" s="17" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="N10" s="17" t="n">
+        <v>975.08</v>
+      </c>
+      <c r="O10" s="17" t="n">
+        <v>987.24</v>
+      </c>
+      <c r="P10" s="17" t="n">
+        <v>273.83</v>
+      </c>
+      <c r="Q10" s="17" t="n">
+        <v>273.83</v>
+      </c>
+      <c r="R10" s="17" t="n">
+        <v>273.98</v>
+      </c>
+      <c r="S10" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T10" s="17" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="U10" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="V10" s="17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W10" s="17" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="X10" s="17" t="n">
+        <v>211.66</v>
+      </c>
+      <c r="Y10" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z10" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -7134,7 +7986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7689,6 +8541,76 @@
       <c r="I16" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="E17" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H17" s="19" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I17" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="n">
+        <v>38</v>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="E18" s="19" t="n">
+        <v>19</v>
+      </c>
+      <c r="F18" s="19" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="I18" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — PROFIT</t>
         </is>
       </c>
     </row>
@@ -8155,7 +9077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM7"/>
+  <dimension ref="A1:AM8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9138,6 +10060,153 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>23824.22</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>23714.31</v>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J8" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M8" s="15" t="inlineStr">
+        <is>
+          <t>10:18 IST</t>
+        </is>
+      </c>
+      <c r="N8" s="15" t="n">
+        <v>24013.1</v>
+      </c>
+      <c r="O8" s="15" t="n">
+        <v>24168</v>
+      </c>
+      <c r="P8" s="15" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="Q8" s="15" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="R8" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="S8" s="15" t="n">
+        <v>75</v>
+      </c>
+      <c r="T8" s="15" t="n">
+        <v>1350</v>
+      </c>
+      <c r="U8" s="15" t="n">
+        <v>36.35</v>
+      </c>
+      <c r="V8" s="15" t="n">
+        <v>25.45</v>
+      </c>
+      <c r="W8" s="15" t="n">
+        <v>49072.5</v>
+      </c>
+      <c r="X8" s="15" t="n">
+        <v>49127.42</v>
+      </c>
+      <c r="Y8" s="15" t="n">
+        <v>85927.5</v>
+      </c>
+      <c r="Z8" s="15" t="n">
+        <v>14721.75</v>
+      </c>
+      <c r="AA8" s="15" t="n">
+        <v>14721.75</v>
+      </c>
+      <c r="AB8" s="15" t="n">
+        <v>-14715</v>
+      </c>
+      <c r="AC8" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AD8" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE8" s="15" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="AF8" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG8" s="15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH8" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI8" s="15" t="n">
+        <v>54.92</v>
+      </c>
+      <c r="AJ8" s="15" t="n">
+        <v>-14769.92</v>
+      </c>
+      <c r="AK8" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AL8" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM8" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -9152,7 +10221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM7"/>
+  <dimension ref="A1:AM8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10135,6 +11204,153 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>23824.22</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>23714.31</v>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J8" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M8" s="15" t="inlineStr">
+        <is>
+          <t>11:13 IST</t>
+        </is>
+      </c>
+      <c r="N8" s="15" t="n">
+        <v>24013.1</v>
+      </c>
+      <c r="O8" s="15" t="n">
+        <v>24168</v>
+      </c>
+      <c r="P8" s="15" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="Q8" s="15" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="R8" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="S8" s="15" t="n">
+        <v>75</v>
+      </c>
+      <c r="T8" s="15" t="n">
+        <v>1650</v>
+      </c>
+      <c r="U8" s="15" t="n">
+        <v>29.61</v>
+      </c>
+      <c r="V8" s="15" t="n">
+        <v>20.73</v>
+      </c>
+      <c r="W8" s="15" t="n">
+        <v>48856.5</v>
+      </c>
+      <c r="X8" s="15" t="n">
+        <v>48911.39</v>
+      </c>
+      <c r="Y8" s="15" t="n">
+        <v>116143.5</v>
+      </c>
+      <c r="Z8" s="15" t="n">
+        <v>14656.95</v>
+      </c>
+      <c r="AA8" s="15" t="n">
+        <v>14656.95</v>
+      </c>
+      <c r="AB8" s="15" t="n">
+        <v>-14652</v>
+      </c>
+      <c r="AC8" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AD8" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE8" s="15" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="AF8" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG8" s="15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH8" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI8" s="15" t="n">
+        <v>54.89</v>
+      </c>
+      <c r="AJ8" s="15" t="n">
+        <v>-14706.89</v>
+      </c>
+      <c r="AK8" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AL8" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM8" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -10149,7 +11365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM12"/>
+  <dimension ref="A1:AM14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11862,6 +13078,300 @@
         <v>50000</v>
       </c>
       <c r="AM12" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>23824.22</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>23714.31</v>
+      </c>
+      <c r="I13" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J13" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="K13" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M13" s="17" t="inlineStr">
+        <is>
+          <t>11:33 IST</t>
+        </is>
+      </c>
+      <c r="N13" s="17" t="n">
+        <v>24013.1</v>
+      </c>
+      <c r="O13" s="17" t="n">
+        <v>24168</v>
+      </c>
+      <c r="P13" s="17" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="Q13" s="17" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="R13" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="S13" s="17" t="n">
+        <v>75</v>
+      </c>
+      <c r="T13" s="17" t="n">
+        <v>1500</v>
+      </c>
+      <c r="U13" s="17" t="n">
+        <v>32.72</v>
+      </c>
+      <c r="V13" s="17" t="n">
+        <v>42.54</v>
+      </c>
+      <c r="W13" s="17" t="n">
+        <v>49080</v>
+      </c>
+      <c r="X13" s="17" t="n">
+        <v>49134.92</v>
+      </c>
+      <c r="Y13" s="17" t="n">
+        <v>100920</v>
+      </c>
+      <c r="Z13" s="17" t="n">
+        <v>14724</v>
+      </c>
+      <c r="AA13" s="17" t="n">
+        <v>14724</v>
+      </c>
+      <c r="AB13" s="17" t="n">
+        <v>14730</v>
+      </c>
+      <c r="AC13" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD13" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE13" s="17" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="AF13" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG13" s="17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH13" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI13" s="17" t="n">
+        <v>54.92</v>
+      </c>
+      <c r="AJ13" s="17" t="n">
+        <v>14675.08</v>
+      </c>
+      <c r="AK13" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AL13" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM13" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>23824.22</v>
+      </c>
+      <c r="H14" s="15" t="n">
+        <v>23714.31</v>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J14" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="K14" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M14" s="15" t="inlineStr">
+        <is>
+          <t>09:34 IST</t>
+        </is>
+      </c>
+      <c r="N14" s="15" t="n">
+        <v>24013.1</v>
+      </c>
+      <c r="O14" s="15" t="n">
+        <v>24168</v>
+      </c>
+      <c r="P14" s="15" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="Q14" s="15" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="R14" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="S14" s="15" t="n">
+        <v>75</v>
+      </c>
+      <c r="T14" s="15" t="n">
+        <v>1575</v>
+      </c>
+      <c r="U14" s="15" t="n">
+        <v>30.41</v>
+      </c>
+      <c r="V14" s="15" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="W14" s="15" t="n">
+        <v>47895.75</v>
+      </c>
+      <c r="X14" s="15" t="n">
+        <v>47950.49</v>
+      </c>
+      <c r="Y14" s="15" t="n">
+        <v>109604.25</v>
+      </c>
+      <c r="Z14" s="15" t="n">
+        <v>14368.73</v>
+      </c>
+      <c r="AA14" s="15" t="n">
+        <v>14368.73</v>
+      </c>
+      <c r="AB14" s="15" t="n">
+        <v>-14364</v>
+      </c>
+      <c r="AC14" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AD14" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE14" s="15" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="AF14" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG14" s="15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH14" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI14" s="15" t="n">
+        <v>54.74</v>
+      </c>
+      <c r="AJ14" s="15" t="n">
+        <v>-14418.74</v>
+      </c>
+      <c r="AK14" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AL14" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM14" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1572,6 +1572,105 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>13:39 ET</t>
+        </is>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>29686</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>29675</v>
+      </c>
+      <c r="J11" s="17" t="n">
+        <v>29700</v>
+      </c>
+      <c r="K11" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" s="17" t="n">
+        <v>249.78</v>
+      </c>
+      <c r="M11" s="17" t="n">
+        <v>324.71</v>
+      </c>
+      <c r="N11" s="17" t="n">
+        <v>771.54</v>
+      </c>
+      <c r="O11" s="17" t="n">
+        <v>750.66</v>
+      </c>
+      <c r="P11" s="17" t="n">
+        <v>224.8</v>
+      </c>
+      <c r="Q11" s="17" t="n">
+        <v>224.8</v>
+      </c>
+      <c r="R11" s="17" t="n">
+        <v>224.79</v>
+      </c>
+      <c r="S11" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T11" s="17" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="U11" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="V11" s="17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W11" s="17" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="X11" s="17" t="n">
+        <v>202.59</v>
+      </c>
+      <c r="Y11" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z11" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -1586,7 +1685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM8"/>
+  <dimension ref="A1:AM9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2716,6 +2815,153 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>57048.75</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>55970.07</v>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J9" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="K9" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M9" s="17" t="inlineStr">
+        <is>
+          <t>09:49 IST</t>
+        </is>
+      </c>
+      <c r="N9" s="17" t="n">
+        <v>57183.75</v>
+      </c>
+      <c r="O9" s="17" t="n">
+        <v>57935.6</v>
+      </c>
+      <c r="P9" s="17" t="inlineStr">
+        <is>
+          <t>57000 CE</t>
+        </is>
+      </c>
+      <c r="Q9" s="17" t="inlineStr">
+        <is>
+          <t>57200 CE</t>
+        </is>
+      </c>
+      <c r="R9" s="17" t="n">
+        <v>49</v>
+      </c>
+      <c r="S9" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T9" s="17" t="n">
+        <v>1470</v>
+      </c>
+      <c r="U9" s="17" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="V9" s="17" t="n">
+        <v>42.31</v>
+      </c>
+      <c r="W9" s="17" t="n">
+        <v>47848.5</v>
+      </c>
+      <c r="X9" s="17" t="n">
+        <v>47903.23</v>
+      </c>
+      <c r="Y9" s="17" t="n">
+        <v>246151.5</v>
+      </c>
+      <c r="Z9" s="17" t="n">
+        <v>14354.55</v>
+      </c>
+      <c r="AA9" s="17" t="n">
+        <v>14354.55</v>
+      </c>
+      <c r="AB9" s="17" t="n">
+        <v>14347.2</v>
+      </c>
+      <c r="AC9" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD9" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE9" s="17" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AF9" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG9" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH9" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI9" s="17" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="AJ9" s="17" t="n">
+        <v>14292.47</v>
+      </c>
+      <c r="AK9" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AL9" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM9" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -2730,7 +2976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM8"/>
+  <dimension ref="A1:AM9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3860,6 +4106,153 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>57048.75</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>55970.07</v>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="K9" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M9" s="16" t="inlineStr">
+        <is>
+          <t>13:33 IST</t>
+        </is>
+      </c>
+      <c r="N9" s="16" t="n">
+        <v>57183.75</v>
+      </c>
+      <c r="O9" s="16" t="n">
+        <v>57935.6</v>
+      </c>
+      <c r="P9" s="16" t="inlineStr">
+        <is>
+          <t>57200 PE</t>
+        </is>
+      </c>
+      <c r="Q9" s="16" t="inlineStr">
+        <is>
+          <t>57000 PE</t>
+        </is>
+      </c>
+      <c r="R9" s="16" t="n">
+        <v>44</v>
+      </c>
+      <c r="S9" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="T9" s="16" t="n">
+        <v>1320</v>
+      </c>
+      <c r="U9" s="16" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="V9" s="16" t="n">
+        <v>34.91</v>
+      </c>
+      <c r="W9" s="16" t="n">
+        <v>48232.8</v>
+      </c>
+      <c r="X9" s="16" t="n">
+        <v>48287.59</v>
+      </c>
+      <c r="Y9" s="16" t="n">
+        <v>215767.2</v>
+      </c>
+      <c r="Z9" s="16" t="n">
+        <v>14469.84</v>
+      </c>
+      <c r="AA9" s="16" t="n">
+        <v>14469.84</v>
+      </c>
+      <c r="AB9" s="16" t="n">
+        <v>-2151.6</v>
+      </c>
+      <c r="AC9" s="16" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AD9" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE9" s="16" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AF9" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG9" s="16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH9" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI9" s="16" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="AJ9" s="16" t="n">
+        <v>-2206.39</v>
+      </c>
+      <c r="AK9" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AL9" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM9" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -3874,7 +4267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM14"/>
+  <dimension ref="A1:AM16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5881,6 +6274,300 @@
         <v>50000</v>
       </c>
       <c r="AM14" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>57048.75</v>
+      </c>
+      <c r="H15" s="17" t="n">
+        <v>55970.07</v>
+      </c>
+      <c r="I15" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J15" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="K15" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M15" s="17" t="inlineStr">
+        <is>
+          <t>11:24 IST</t>
+        </is>
+      </c>
+      <c r="N15" s="17" t="n">
+        <v>57183.75</v>
+      </c>
+      <c r="O15" s="17" t="n">
+        <v>57935.6</v>
+      </c>
+      <c r="P15" s="17" t="inlineStr">
+        <is>
+          <t>57000 CE</t>
+        </is>
+      </c>
+      <c r="Q15" s="17" t="inlineStr">
+        <is>
+          <t>57200 CE</t>
+        </is>
+      </c>
+      <c r="R15" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="S15" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T15" s="17" t="n">
+        <v>1560</v>
+      </c>
+      <c r="U15" s="17" t="n">
+        <v>30.53</v>
+      </c>
+      <c r="V15" s="17" t="n">
+        <v>39.69</v>
+      </c>
+      <c r="W15" s="17" t="n">
+        <v>47626.8</v>
+      </c>
+      <c r="X15" s="17" t="n">
+        <v>47681.49</v>
+      </c>
+      <c r="Y15" s="17" t="n">
+        <v>264373.2</v>
+      </c>
+      <c r="Z15" s="17" t="n">
+        <v>14288.04</v>
+      </c>
+      <c r="AA15" s="17" t="n">
+        <v>14288.04</v>
+      </c>
+      <c r="AB15" s="17" t="n">
+        <v>14289.6</v>
+      </c>
+      <c r="AC15" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD15" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE15" s="17" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AF15" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG15" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH15" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI15" s="17" t="n">
+        <v>54.69</v>
+      </c>
+      <c r="AJ15" s="17" t="n">
+        <v>14234.91</v>
+      </c>
+      <c r="AK15" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AL15" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM15" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>57048.75</v>
+      </c>
+      <c r="H16" s="17" t="n">
+        <v>55970.07</v>
+      </c>
+      <c r="I16" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J16" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="K16" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M16" s="17" t="inlineStr">
+        <is>
+          <t>10:54 IST</t>
+        </is>
+      </c>
+      <c r="N16" s="17" t="n">
+        <v>57183.75</v>
+      </c>
+      <c r="O16" s="17" t="n">
+        <v>57935.6</v>
+      </c>
+      <c r="P16" s="17" t="inlineStr">
+        <is>
+          <t>57200 PE</t>
+        </is>
+      </c>
+      <c r="Q16" s="17" t="inlineStr">
+        <is>
+          <t>57000 PE</t>
+        </is>
+      </c>
+      <c r="R16" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="S16" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T16" s="17" t="n">
+        <v>1020</v>
+      </c>
+      <c r="U16" s="17" t="n">
+        <v>46.86</v>
+      </c>
+      <c r="V16" s="17" t="n">
+        <v>60.92</v>
+      </c>
+      <c r="W16" s="17" t="n">
+        <v>47797.2</v>
+      </c>
+      <c r="X16" s="17" t="n">
+        <v>47851.92</v>
+      </c>
+      <c r="Y16" s="17" t="n">
+        <v>156202.8</v>
+      </c>
+      <c r="Z16" s="17" t="n">
+        <v>14339.16</v>
+      </c>
+      <c r="AA16" s="17" t="n">
+        <v>14339.16</v>
+      </c>
+      <c r="AB16" s="17" t="n">
+        <v>14341.2</v>
+      </c>
+      <c r="AC16" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD16" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE16" s="17" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="AF16" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG16" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH16" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI16" s="17" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="AJ16" s="17" t="n">
+        <v>14286.48</v>
+      </c>
+      <c r="AK16" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AL16" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM16" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -6603,7 +7290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6885,6 +7572,72 @@
         <v>55649.38</v>
       </c>
       <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>23868.63</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>23767.86</v>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>57048.75</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>55970.07</v>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -6904,7 +7657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7872,6 +8625,105 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>12:28 ET</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>29673.25</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>29650</v>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>29675</v>
+      </c>
+      <c r="K11" s="15" t="n">
+        <v>44</v>
+      </c>
+      <c r="L11" s="15" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="M11" s="15" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="N11" s="15" t="n">
+        <v>991.76</v>
+      </c>
+      <c r="O11" s="15" t="n">
+        <v>1280.4</v>
+      </c>
+      <c r="P11" s="15" t="n">
+        <v>275.88</v>
+      </c>
+      <c r="Q11" s="15" t="n">
+        <v>275.88</v>
+      </c>
+      <c r="R11" s="15" t="n">
+        <v>-275.88</v>
+      </c>
+      <c r="S11" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="T11" s="15" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="U11" s="15" t="n">
+        <v>44</v>
+      </c>
+      <c r="V11" s="15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="W11" s="15" t="n">
+        <v>72.16</v>
+      </c>
+      <c r="X11" s="15" t="n">
+        <v>-348.04</v>
+      </c>
+      <c r="Y11" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="Z11" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -7986,7 +8838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8611,6 +9463,76 @@
       <c r="I18" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="E19" s="19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F19" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G19" s="19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H19" s="19" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="I19" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="n">
+        <v>44</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E20" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="F20" s="19" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <v>36.08</v>
+      </c>
+      <c r="H20" s="19" t="n">
+        <v>72.16</v>
+      </c>
+      <c r="I20" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — STOP LOSS</t>
         </is>
       </c>
     </row>
@@ -9077,7 +9999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM8"/>
+  <dimension ref="A1:AM9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10207,6 +11129,153 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>23868.63</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>23767.86</v>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J9" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="K9" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M9" s="17" t="inlineStr">
+        <is>
+          <t>10:03 IST</t>
+        </is>
+      </c>
+      <c r="N9" s="17" t="n">
+        <v>23824.1</v>
+      </c>
+      <c r="O9" s="17" t="n">
+        <v>24102.9</v>
+      </c>
+      <c r="P9" s="17" t="inlineStr">
+        <is>
+          <t>23800 CE</t>
+        </is>
+      </c>
+      <c r="Q9" s="17" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="R9" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="S9" s="17" t="n">
+        <v>75</v>
+      </c>
+      <c r="T9" s="17" t="n">
+        <v>2325</v>
+      </c>
+      <c r="U9" s="17" t="n">
+        <v>20.81</v>
+      </c>
+      <c r="V9" s="17" t="n">
+        <v>27.05</v>
+      </c>
+      <c r="W9" s="17" t="n">
+        <v>48383.25</v>
+      </c>
+      <c r="X9" s="17" t="n">
+        <v>48438.06</v>
+      </c>
+      <c r="Y9" s="17" t="n">
+        <v>184116.75</v>
+      </c>
+      <c r="Z9" s="17" t="n">
+        <v>14514.98</v>
+      </c>
+      <c r="AA9" s="17" t="n">
+        <v>14514.98</v>
+      </c>
+      <c r="AB9" s="17" t="n">
+        <v>14508</v>
+      </c>
+      <c r="AC9" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD9" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE9" s="17" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AF9" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG9" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH9" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI9" s="17" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="AJ9" s="17" t="n">
+        <v>14453.19</v>
+      </c>
+      <c r="AK9" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AL9" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM9" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -10221,7 +11290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM8"/>
+  <dimension ref="A1:AM9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11351,6 +12420,153 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>23868.63</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>23767.86</v>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="K9" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M9" s="16" t="inlineStr">
+        <is>
+          <t>14:28 IST</t>
+        </is>
+      </c>
+      <c r="N9" s="16" t="n">
+        <v>23824.1</v>
+      </c>
+      <c r="O9" s="16" t="n">
+        <v>24102.9</v>
+      </c>
+      <c r="P9" s="16" t="inlineStr">
+        <is>
+          <t>23900 PE</t>
+        </is>
+      </c>
+      <c r="Q9" s="16" t="inlineStr">
+        <is>
+          <t>23800 PE</t>
+        </is>
+      </c>
+      <c r="R9" s="16" t="n">
+        <v>38</v>
+      </c>
+      <c r="S9" s="16" t="n">
+        <v>75</v>
+      </c>
+      <c r="T9" s="16" t="n">
+        <v>2850</v>
+      </c>
+      <c r="U9" s="16" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="V9" s="16" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="W9" s="16" t="n">
+        <v>47338.5</v>
+      </c>
+      <c r="X9" s="16" t="n">
+        <v>47393.15</v>
+      </c>
+      <c r="Y9" s="16" t="n">
+        <v>237661.5</v>
+      </c>
+      <c r="Z9" s="16" t="n">
+        <v>14201.55</v>
+      </c>
+      <c r="AA9" s="16" t="n">
+        <v>14201.55</v>
+      </c>
+      <c r="AB9" s="16" t="n">
+        <v>2280</v>
+      </c>
+      <c r="AC9" s="16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD9" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE9" s="16" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="AF9" s="16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AG9" s="16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH9" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI9" s="16" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="AJ9" s="16" t="n">
+        <v>2225.35</v>
+      </c>
+      <c r="AK9" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AL9" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM9" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -11365,7 +12581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM14"/>
+  <dimension ref="A1:AM16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13372,6 +14588,300 @@
         <v>50000</v>
       </c>
       <c r="AM14" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="n">
+        <v>23868.63</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>23767.86</v>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J15" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="K15" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M15" s="15" t="inlineStr">
+        <is>
+          <t>10:06 IST</t>
+        </is>
+      </c>
+      <c r="N15" s="15" t="n">
+        <v>23824.1</v>
+      </c>
+      <c r="O15" s="15" t="n">
+        <v>24102.9</v>
+      </c>
+      <c r="P15" s="15" t="inlineStr">
+        <is>
+          <t>23800 CE</t>
+        </is>
+      </c>
+      <c r="Q15" s="15" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="R15" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="S15" s="15" t="n">
+        <v>75</v>
+      </c>
+      <c r="T15" s="15" t="n">
+        <v>2850</v>
+      </c>
+      <c r="U15" s="15" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="V15" s="15" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="W15" s="15" t="n">
+        <v>47509.5</v>
+      </c>
+      <c r="X15" s="15" t="n">
+        <v>47564.18</v>
+      </c>
+      <c r="Y15" s="15" t="n">
+        <v>237490.5</v>
+      </c>
+      <c r="Z15" s="15" t="n">
+        <v>14252.85</v>
+      </c>
+      <c r="AA15" s="15" t="n">
+        <v>14252.85</v>
+      </c>
+      <c r="AB15" s="15" t="n">
+        <v>-14250</v>
+      </c>
+      <c r="AC15" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AD15" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE15" s="15" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AF15" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG15" s="15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH15" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI15" s="15" t="n">
+        <v>54.68</v>
+      </c>
+      <c r="AJ15" s="15" t="n">
+        <v>-14304.68</v>
+      </c>
+      <c r="AK15" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AL15" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM15" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>23868.63</v>
+      </c>
+      <c r="H16" s="15" t="n">
+        <v>23767.86</v>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J16" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="K16" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="M16" s="15" t="inlineStr">
+        <is>
+          <t>11:18 IST</t>
+        </is>
+      </c>
+      <c r="N16" s="15" t="n">
+        <v>23824.1</v>
+      </c>
+      <c r="O16" s="15" t="n">
+        <v>24102.9</v>
+      </c>
+      <c r="P16" s="15" t="inlineStr">
+        <is>
+          <t>23900 PE</t>
+        </is>
+      </c>
+      <c r="Q16" s="15" t="inlineStr">
+        <is>
+          <t>23800 PE</t>
+        </is>
+      </c>
+      <c r="R16" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="S16" s="15" t="n">
+        <v>75</v>
+      </c>
+      <c r="T16" s="15" t="n">
+        <v>2700</v>
+      </c>
+      <c r="U16" s="15" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="V16" s="15" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="W16" s="15" t="n">
+        <v>47277</v>
+      </c>
+      <c r="X16" s="15" t="n">
+        <v>47331.64</v>
+      </c>
+      <c r="Y16" s="15" t="n">
+        <v>222723</v>
+      </c>
+      <c r="Z16" s="15" t="n">
+        <v>14183.1</v>
+      </c>
+      <c r="AA16" s="15" t="n">
+        <v>14183.1</v>
+      </c>
+      <c r="AB16" s="15" t="n">
+        <v>-14175</v>
+      </c>
+      <c r="AC16" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AD16" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE16" s="15" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AF16" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AG16" s="15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH16" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AI16" s="15" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="AJ16" s="15" t="n">
+        <v>-14229.64</v>
+      </c>
+      <c r="AK16" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AL16" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AM16" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA12"/>
+  <dimension ref="A1:AA13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1770,6 +1770,105 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="inlineStr">
+        <is>
+          <t>12:03 ET</t>
+        </is>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>29866.25</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>29850</v>
+      </c>
+      <c r="J13" s="17" t="n">
+        <v>29875</v>
+      </c>
+      <c r="K13" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" s="17" t="n">
+        <v>246.52</v>
+      </c>
+      <c r="M13" s="17" t="n">
+        <v>320.48</v>
+      </c>
+      <c r="N13" s="17" t="n">
+        <v>761.76</v>
+      </c>
+      <c r="O13" s="17" t="n">
+        <v>760.4400000000001</v>
+      </c>
+      <c r="P13" s="17" t="n">
+        <v>221.87</v>
+      </c>
+      <c r="Q13" s="17" t="n">
+        <v>221.87</v>
+      </c>
+      <c r="R13" s="17" t="n">
+        <v>221.88</v>
+      </c>
+      <c r="S13" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T13" s="17" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="U13" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="V13" s="17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W13" s="17" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="X13" s="17" t="n">
+        <v>199.68</v>
+      </c>
+      <c r="Y13" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z13" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -1784,7 +1883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM10"/>
+  <dimension ref="A1:AN11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3208,6 +3307,158 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>Price↑(58150.35&gt;57183.75) &amp; EMA9↑(57268.28&gt;56132.92)</t>
+        </is>
+      </c>
+      <c r="H11" s="16" t="n">
+        <v>57268.28</v>
+      </c>
+      <c r="I11" s="16" t="n">
+        <v>56132.92</v>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K11" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L11" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N11" s="16" t="inlineStr">
+        <is>
+          <t>14:01 IST</t>
+        </is>
+      </c>
+      <c r="O11" s="16" t="n">
+        <v>58150.35</v>
+      </c>
+      <c r="P11" s="16" t="n">
+        <v>57183.75</v>
+      </c>
+      <c r="Q11" s="16" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="R11" s="16" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="S11" s="16" t="n">
+        <v>34</v>
+      </c>
+      <c r="T11" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U11" s="16" t="n">
+        <v>1020</v>
+      </c>
+      <c r="V11" s="16" t="n">
+        <v>46.51</v>
+      </c>
+      <c r="W11" s="16" t="n">
+        <v>45.29</v>
+      </c>
+      <c r="X11" s="16" t="n">
+        <v>47440.2</v>
+      </c>
+      <c r="Y11" s="16" t="n">
+        <v>47494.87</v>
+      </c>
+      <c r="Z11" s="16" t="n">
+        <v>156559.8</v>
+      </c>
+      <c r="AA11" s="16" t="n">
+        <v>14232.06</v>
+      </c>
+      <c r="AB11" s="16" t="n">
+        <v>14232.06</v>
+      </c>
+      <c r="AC11" s="16" t="n">
+        <v>-1244.4</v>
+      </c>
+      <c r="AD11" s="16" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="AE11" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF11" s="16" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="AG11" s="16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH11" s="16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI11" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ11" s="16" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="AK11" s="16" t="n">
+        <v>-1299.07</v>
+      </c>
+      <c r="AL11" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM11" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN11" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -3222,7 +3473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM10"/>
+  <dimension ref="A1:AN11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4646,6 +4897,158 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(58150.35&gt;57183.75) &amp; EMA9↑(57268.28&gt;56132.92)</t>
+        </is>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>57268.28</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>56132.92</v>
+      </c>
+      <c r="J11" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K11" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L11" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N11" s="17" t="inlineStr">
+        <is>
+          <t>12:12 IST</t>
+        </is>
+      </c>
+      <c r="O11" s="17" t="n">
+        <v>58150.35</v>
+      </c>
+      <c r="P11" s="17" t="n">
+        <v>57183.75</v>
+      </c>
+      <c r="Q11" s="17" t="inlineStr">
+        <is>
+          <t>58200 PE</t>
+        </is>
+      </c>
+      <c r="R11" s="17" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="S11" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="T11" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U11" s="17" t="n">
+        <v>1260</v>
+      </c>
+      <c r="V11" s="17" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="W11" s="17" t="n">
+        <v>48.88</v>
+      </c>
+      <c r="X11" s="17" t="n">
+        <v>47376</v>
+      </c>
+      <c r="Y11" s="17" t="n">
+        <v>47430.66</v>
+      </c>
+      <c r="Z11" s="17" t="n">
+        <v>204624</v>
+      </c>
+      <c r="AA11" s="17" t="n">
+        <v>14212.8</v>
+      </c>
+      <c r="AB11" s="17" t="n">
+        <v>14212.8</v>
+      </c>
+      <c r="AC11" s="17" t="n">
+        <v>14212.8</v>
+      </c>
+      <c r="AD11" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE11" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF11" s="17" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="AG11" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH11" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI11" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ11" s="17" t="n">
+        <v>54.66</v>
+      </c>
+      <c r="AK11" s="17" t="n">
+        <v>14158.14</v>
+      </c>
+      <c r="AL11" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM11" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN11" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -4660,7 +5063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM18"/>
+  <dimension ref="A1:AN20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7260,6 +7663,310 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(58150.35&gt;57183.75) &amp; EMA9↑(57268.28&gt;56132.92)</t>
+        </is>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>57268.28</v>
+      </c>
+      <c r="I19" s="17" t="n">
+        <v>56132.92</v>
+      </c>
+      <c r="J19" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K19" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L19" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N19" s="17" t="inlineStr">
+        <is>
+          <t>10:34 IST</t>
+        </is>
+      </c>
+      <c r="O19" s="17" t="n">
+        <v>58150.35</v>
+      </c>
+      <c r="P19" s="17" t="n">
+        <v>57183.75</v>
+      </c>
+      <c r="Q19" s="17" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="R19" s="17" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="S19" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="T19" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U19" s="17" t="n">
+        <v>1380</v>
+      </c>
+      <c r="V19" s="17" t="n">
+        <v>34.14</v>
+      </c>
+      <c r="W19" s="17" t="n">
+        <v>44.38</v>
+      </c>
+      <c r="X19" s="17" t="n">
+        <v>47113.2</v>
+      </c>
+      <c r="Y19" s="17" t="n">
+        <v>47167.81</v>
+      </c>
+      <c r="Z19" s="17" t="n">
+        <v>228886.8</v>
+      </c>
+      <c r="AA19" s="17" t="n">
+        <v>14133.96</v>
+      </c>
+      <c r="AB19" s="17" t="n">
+        <v>14133.96</v>
+      </c>
+      <c r="AC19" s="17" t="n">
+        <v>14131.2</v>
+      </c>
+      <c r="AD19" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE19" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF19" s="17" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AG19" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH19" s="17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI19" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ19" s="17" t="n">
+        <v>54.61</v>
+      </c>
+      <c r="AK19" s="17" t="n">
+        <v>14076.59</v>
+      </c>
+      <c r="AL19" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM19" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN19" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(58150.35&gt;57183.75) &amp; EMA9↑(57268.28&gt;56132.92)</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>57268.28</v>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>56132.92</v>
+      </c>
+      <c r="J20" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K20" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L20" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N20" s="15" t="inlineStr">
+        <is>
+          <t>09:31 IST</t>
+        </is>
+      </c>
+      <c r="O20" s="15" t="n">
+        <v>58150.35</v>
+      </c>
+      <c r="P20" s="15" t="n">
+        <v>57183.75</v>
+      </c>
+      <c r="Q20" s="15" t="inlineStr">
+        <is>
+          <t>58200 PE</t>
+        </is>
+      </c>
+      <c r="R20" s="15" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="S20" s="15" t="n">
+        <v>46</v>
+      </c>
+      <c r="T20" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U20" s="15" t="n">
+        <v>1380</v>
+      </c>
+      <c r="V20" s="15" t="n">
+        <v>34.15</v>
+      </c>
+      <c r="W20" s="15" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="X20" s="15" t="n">
+        <v>47127</v>
+      </c>
+      <c r="Y20" s="15" t="n">
+        <v>47181.62</v>
+      </c>
+      <c r="Z20" s="15" t="n">
+        <v>228873</v>
+      </c>
+      <c r="AA20" s="15" t="n">
+        <v>14138.1</v>
+      </c>
+      <c r="AB20" s="15" t="n">
+        <v>14138.1</v>
+      </c>
+      <c r="AC20" s="15" t="n">
+        <v>-14145</v>
+      </c>
+      <c r="AD20" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE20" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF20" s="15" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AG20" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH20" s="15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI20" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ20" s="15" t="n">
+        <v>54.62</v>
+      </c>
+      <c r="AK20" s="15" t="n">
+        <v>-14199.62</v>
+      </c>
+      <c r="AL20" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM20" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN20" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -7274,7 +7981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM6"/>
+  <dimension ref="A1:AN7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8110,6 +8817,158 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(58150.35&gt;57183.75) &amp; EMA9↑(57268.28&gt;56132.92)</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>57268.28</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>56132.92</v>
+      </c>
+      <c r="J7" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K7" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L7" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N7" s="15" t="inlineStr">
+        <is>
+          <t>11:08 IST</t>
+        </is>
+      </c>
+      <c r="O7" s="15" t="n">
+        <v>58150.35</v>
+      </c>
+      <c r="P7" s="15" t="n">
+        <v>57183.75</v>
+      </c>
+      <c r="Q7" s="15" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="R7" s="15" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="S7" s="15" t="n">
+        <v>44</v>
+      </c>
+      <c r="T7" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U7" s="15" t="n">
+        <v>1320</v>
+      </c>
+      <c r="V7" s="15" t="n">
+        <v>35.79</v>
+      </c>
+      <c r="W7" s="15" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="X7" s="15" t="n">
+        <v>47242.8</v>
+      </c>
+      <c r="Y7" s="15" t="n">
+        <v>47297.43</v>
+      </c>
+      <c r="Z7" s="15" t="n">
+        <v>216757.2</v>
+      </c>
+      <c r="AA7" s="15" t="n">
+        <v>14172.84</v>
+      </c>
+      <c r="AB7" s="15" t="n">
+        <v>14172.84</v>
+      </c>
+      <c r="AC7" s="15" t="n">
+        <v>-14176.8</v>
+      </c>
+      <c r="AD7" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE7" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF7" s="15" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AG7" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH7" s="15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI7" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ7" s="15" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="AK7" s="15" t="n">
+        <v>-14231.43</v>
+      </c>
+      <c r="AL7" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM7" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN7" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -8491,7 +9350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA12"/>
+  <dimension ref="A1:AA13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9652,6 +10511,105 @@
         <v>1000</v>
       </c>
       <c r="AA12" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="inlineStr">
+        <is>
+          <t>12:54 ET</t>
+        </is>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>29867.5</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>29850</v>
+      </c>
+      <c r="J13" s="17" t="n">
+        <v>29875</v>
+      </c>
+      <c r="K13" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="L13" s="17" t="n">
+        <v>24.81</v>
+      </c>
+      <c r="M13" s="17" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="N13" s="17" t="n">
+        <v>978.65</v>
+      </c>
+      <c r="O13" s="17" t="n">
+        <v>932.03</v>
+      </c>
+      <c r="P13" s="17" t="n">
+        <v>275.39</v>
+      </c>
+      <c r="Q13" s="17" t="n">
+        <v>275.39</v>
+      </c>
+      <c r="R13" s="17" t="n">
+        <v>275.28</v>
+      </c>
+      <c r="S13" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T13" s="17" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="U13" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="V13" s="17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W13" s="17" t="n">
+        <v>60.68</v>
+      </c>
+      <c r="X13" s="17" t="n">
+        <v>214.6</v>
+      </c>
+      <c r="Y13" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z13" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -9771,7 +10729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10536,6 +11494,76 @@
       <c r="I22" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" s="19" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="E23" s="19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F23" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G23" s="19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H23" s="19" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="I23" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="n">
+        <v>37</v>
+      </c>
+      <c r="D24" s="19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" s="19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F24" s="19" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G24" s="19" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="H24" s="19" t="n">
+        <v>60.68</v>
+      </c>
+      <c r="I24" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — PROFIT</t>
         </is>
       </c>
     </row>
@@ -11002,7 +12030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM10"/>
+  <dimension ref="A1:AN11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12426,6 +13454,158 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(24021.65&gt;23824.1) &amp; EMA9↑(23899.33&gt;23791.89)</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>23899.33</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>23791.89</v>
+      </c>
+      <c r="J11" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K11" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L11" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N11" s="15" t="inlineStr">
+        <is>
+          <t>10:51 IST</t>
+        </is>
+      </c>
+      <c r="O11" s="15" t="n">
+        <v>24021.65</v>
+      </c>
+      <c r="P11" s="15" t="n">
+        <v>23824.1</v>
+      </c>
+      <c r="Q11" s="15" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="R11" s="15" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="S11" s="15" t="n">
+        <v>45</v>
+      </c>
+      <c r="T11" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U11" s="15" t="n">
+        <v>2925</v>
+      </c>
+      <c r="V11" s="15" t="n">
+        <v>16.39</v>
+      </c>
+      <c r="W11" s="15" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="X11" s="15" t="n">
+        <v>47940.75</v>
+      </c>
+      <c r="Y11" s="15" t="n">
+        <v>47995.49</v>
+      </c>
+      <c r="Z11" s="15" t="n">
+        <v>244559.25</v>
+      </c>
+      <c r="AA11" s="15" t="n">
+        <v>14382.23</v>
+      </c>
+      <c r="AB11" s="15" t="n">
+        <v>14382.23</v>
+      </c>
+      <c r="AC11" s="15" t="n">
+        <v>-14391</v>
+      </c>
+      <c r="AD11" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE11" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF11" s="15" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="AG11" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH11" s="15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI11" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ11" s="15" t="n">
+        <v>54.74</v>
+      </c>
+      <c r="AK11" s="15" t="n">
+        <v>-14445.74</v>
+      </c>
+      <c r="AL11" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM11" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN11" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -12440,7 +13620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM10"/>
+  <dimension ref="A1:AN11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13864,6 +15044,158 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24021.65&gt;23824.1) &amp; EMA9↑(23899.33&gt;23791.89)</t>
+        </is>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>23899.33</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>23791.89</v>
+      </c>
+      <c r="J11" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K11" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L11" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N11" s="17" t="inlineStr">
+        <is>
+          <t>11:31 IST</t>
+        </is>
+      </c>
+      <c r="O11" s="17" t="n">
+        <v>24021.65</v>
+      </c>
+      <c r="P11" s="17" t="n">
+        <v>23824.1</v>
+      </c>
+      <c r="Q11" s="17" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="R11" s="17" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="S11" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="T11" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U11" s="17" t="n">
+        <v>2405</v>
+      </c>
+      <c r="V11" s="17" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="W11" s="17" t="n">
+        <v>25.64</v>
+      </c>
+      <c r="X11" s="17" t="n">
+        <v>47426.6</v>
+      </c>
+      <c r="Y11" s="17" t="n">
+        <v>47481.26</v>
+      </c>
+      <c r="Z11" s="17" t="n">
+        <v>193073.4</v>
+      </c>
+      <c r="AA11" s="17" t="n">
+        <v>14227.98</v>
+      </c>
+      <c r="AB11" s="17" t="n">
+        <v>14227.98</v>
+      </c>
+      <c r="AC11" s="17" t="n">
+        <v>14237.6</v>
+      </c>
+      <c r="AD11" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE11" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF11" s="17" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="AG11" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH11" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI11" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ11" s="17" t="n">
+        <v>54.66</v>
+      </c>
+      <c r="AK11" s="17" t="n">
+        <v>14182.94</v>
+      </c>
+      <c r="AL11" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM11" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN11" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -13878,7 +15210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM18"/>
+  <dimension ref="A1:AN20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16478,6 +17810,310 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24021.65&gt;23824.1) &amp; EMA9↑(23899.33&gt;23791.89)</t>
+        </is>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>23899.33</v>
+      </c>
+      <c r="I19" s="17" t="n">
+        <v>23791.89</v>
+      </c>
+      <c r="J19" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K19" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L19" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N19" s="17" t="inlineStr">
+        <is>
+          <t>10:09 IST</t>
+        </is>
+      </c>
+      <c r="O19" s="17" t="n">
+        <v>24021.65</v>
+      </c>
+      <c r="P19" s="17" t="n">
+        <v>23824.1</v>
+      </c>
+      <c r="Q19" s="17" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="R19" s="17" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="S19" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="T19" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U19" s="17" t="n">
+        <v>2860</v>
+      </c>
+      <c r="V19" s="17" t="n">
+        <v>16.56</v>
+      </c>
+      <c r="W19" s="17" t="n">
+        <v>21.53</v>
+      </c>
+      <c r="X19" s="17" t="n">
+        <v>47361.6</v>
+      </c>
+      <c r="Y19" s="17" t="n">
+        <v>47416.25</v>
+      </c>
+      <c r="Z19" s="17" t="n">
+        <v>238638.4</v>
+      </c>
+      <c r="AA19" s="17" t="n">
+        <v>14208.48</v>
+      </c>
+      <c r="AB19" s="17" t="n">
+        <v>14208.48</v>
+      </c>
+      <c r="AC19" s="17" t="n">
+        <v>14214.2</v>
+      </c>
+      <c r="AD19" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE19" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF19" s="17" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="AG19" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH19" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI19" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ19" s="17" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="AK19" s="17" t="n">
+        <v>14159.55</v>
+      </c>
+      <c r="AL19" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM19" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN19" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24021.65&gt;23824.1) &amp; EMA9↑(23899.33&gt;23791.89)</t>
+        </is>
+      </c>
+      <c r="H20" s="17" t="n">
+        <v>23899.33</v>
+      </c>
+      <c r="I20" s="17" t="n">
+        <v>23791.89</v>
+      </c>
+      <c r="J20" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L20" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N20" s="17" t="inlineStr">
+        <is>
+          <t>11:13 IST</t>
+        </is>
+      </c>
+      <c r="O20" s="17" t="n">
+        <v>24021.65</v>
+      </c>
+      <c r="P20" s="17" t="n">
+        <v>23824.1</v>
+      </c>
+      <c r="Q20" s="17" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="R20" s="17" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="S20" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="T20" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U20" s="17" t="n">
+        <v>2210</v>
+      </c>
+      <c r="V20" s="17" t="n">
+        <v>21.58</v>
+      </c>
+      <c r="W20" s="17" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="X20" s="17" t="n">
+        <v>47691.8</v>
+      </c>
+      <c r="Y20" s="17" t="n">
+        <v>47746.5</v>
+      </c>
+      <c r="Z20" s="17" t="n">
+        <v>173308.2</v>
+      </c>
+      <c r="AA20" s="17" t="n">
+        <v>14307.54</v>
+      </c>
+      <c r="AB20" s="17" t="n">
+        <v>14307.54</v>
+      </c>
+      <c r="AC20" s="17" t="n">
+        <v>14298.7</v>
+      </c>
+      <c r="AD20" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE20" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF20" s="17" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="AG20" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH20" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI20" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ20" s="17" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="AK20" s="17" t="n">
+        <v>14244</v>
+      </c>
+      <c r="AL20" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM20" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN20" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -16492,7 +18128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM5"/>
+  <dimension ref="A1:AN6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17181,6 +18817,158 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24021.65&gt;23824.1) &amp; EMA9↑(23899.33&gt;23791.89)</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="n">
+        <v>23899.33</v>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>23791.89</v>
+      </c>
+      <c r="J6" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K6" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L6" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N6" s="17" t="inlineStr">
+        <is>
+          <t>10:54 IST</t>
+        </is>
+      </c>
+      <c r="O6" s="17" t="n">
+        <v>24021.65</v>
+      </c>
+      <c r="P6" s="17" t="n">
+        <v>23824.1</v>
+      </c>
+      <c r="Q6" s="17" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="R6" s="17" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="S6" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="T6" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U6" s="17" t="n">
+        <v>2470</v>
+      </c>
+      <c r="V6" s="17" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="W6" s="17" t="n">
+        <v>25.45</v>
+      </c>
+      <c r="X6" s="17" t="n">
+        <v>48362.6</v>
+      </c>
+      <c r="Y6" s="17" t="n">
+        <v>48417.41</v>
+      </c>
+      <c r="Z6" s="17" t="n">
+        <v>198637.4</v>
+      </c>
+      <c r="AA6" s="17" t="n">
+        <v>14508.78</v>
+      </c>
+      <c r="AB6" s="17" t="n">
+        <v>14508.78</v>
+      </c>
+      <c r="AC6" s="17" t="n">
+        <v>14498.9</v>
+      </c>
+      <c r="AD6" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE6" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF6" s="17" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AG6" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH6" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI6" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ6" s="17" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="AK6" s="17" t="n">
+        <v>14444.09</v>
+      </c>
+      <c r="AL6" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM6" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN6" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA13"/>
+  <dimension ref="A1:AA14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1869,6 +1869,105 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
+        <is>
+          <t>13:10 ET</t>
+        </is>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>29838</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>29825</v>
+      </c>
+      <c r="J14" s="17" t="n">
+        <v>29850</v>
+      </c>
+      <c r="K14" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" s="17" t="n">
+        <v>268.69</v>
+      </c>
+      <c r="M14" s="17" t="n">
+        <v>349.3</v>
+      </c>
+      <c r="N14" s="17" t="n">
+        <v>828.27</v>
+      </c>
+      <c r="O14" s="17" t="n">
+        <v>693.9299999999999</v>
+      </c>
+      <c r="P14" s="17" t="n">
+        <v>241.82</v>
+      </c>
+      <c r="Q14" s="17" t="n">
+        <v>241.82</v>
+      </c>
+      <c r="R14" s="17" t="n">
+        <v>241.83</v>
+      </c>
+      <c r="S14" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T14" s="17" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="U14" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="V14" s="17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W14" s="17" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="X14" s="17" t="n">
+        <v>219.63</v>
+      </c>
+      <c r="Y14" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z14" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA14" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -1883,7 +1982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN11"/>
+  <dimension ref="A1:AN12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3459,6 +3558,158 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>57047.77</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>55931.18</v>
+      </c>
+      <c r="J12" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K12" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L12" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N12" s="17" t="inlineStr">
+        <is>
+          <t>10:50 IST</t>
+        </is>
+      </c>
+      <c r="O12" s="17" t="n">
+        <v>57183.75</v>
+      </c>
+      <c r="P12" s="17" t="n">
+        <v>57935.6</v>
+      </c>
+      <c r="Q12" s="17" t="inlineStr">
+        <is>
+          <t>57000 CE</t>
+        </is>
+      </c>
+      <c r="R12" s="17" t="inlineStr">
+        <is>
+          <t>57200 CE</t>
+        </is>
+      </c>
+      <c r="S12" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="T12" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U12" s="17" t="n">
+        <v>1320</v>
+      </c>
+      <c r="V12" s="17" t="n">
+        <v>35.77</v>
+      </c>
+      <c r="W12" s="17" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="X12" s="17" t="n">
+        <v>47216.4</v>
+      </c>
+      <c r="Y12" s="17" t="n">
+        <v>47271.03</v>
+      </c>
+      <c r="Z12" s="17" t="n">
+        <v>216783.6</v>
+      </c>
+      <c r="AA12" s="17" t="n">
+        <v>14164.92</v>
+      </c>
+      <c r="AB12" s="17" t="n">
+        <v>14164.92</v>
+      </c>
+      <c r="AC12" s="17" t="n">
+        <v>14163.6</v>
+      </c>
+      <c r="AD12" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE12" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF12" s="17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AG12" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH12" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI12" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ12" s="17" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="AK12" s="17" t="n">
+        <v>14108.97</v>
+      </c>
+      <c r="AL12" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM12" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN12" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -3473,7 +3724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN11"/>
+  <dimension ref="A1:AN12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5049,6 +5300,158 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H12" s="16" t="n">
+        <v>57047.77</v>
+      </c>
+      <c r="I12" s="16" t="n">
+        <v>55931.18</v>
+      </c>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K12" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L12" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N12" s="16" t="inlineStr">
+        <is>
+          <t>14:01 IST</t>
+        </is>
+      </c>
+      <c r="O12" s="16" t="n">
+        <v>57183.75</v>
+      </c>
+      <c r="P12" s="16" t="n">
+        <v>57935.6</v>
+      </c>
+      <c r="Q12" s="16" t="inlineStr">
+        <is>
+          <t>57200 PE</t>
+        </is>
+      </c>
+      <c r="R12" s="16" t="inlineStr">
+        <is>
+          <t>57000 PE</t>
+        </is>
+      </c>
+      <c r="S12" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="T12" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U12" s="16" t="n">
+        <v>960</v>
+      </c>
+      <c r="V12" s="16" t="n">
+        <v>49.96</v>
+      </c>
+      <c r="W12" s="16" t="n">
+        <v>50.89</v>
+      </c>
+      <c r="X12" s="16" t="n">
+        <v>47961.6</v>
+      </c>
+      <c r="Y12" s="16" t="n">
+        <v>48016.35</v>
+      </c>
+      <c r="Z12" s="16" t="n">
+        <v>144038.4</v>
+      </c>
+      <c r="AA12" s="16" t="n">
+        <v>14388.48</v>
+      </c>
+      <c r="AB12" s="16" t="n">
+        <v>14388.48</v>
+      </c>
+      <c r="AC12" s="16" t="n">
+        <v>892.8</v>
+      </c>
+      <c r="AD12" s="16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE12" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF12" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG12" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH12" s="16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI12" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ12" s="16" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="AK12" s="16" t="n">
+        <v>838.05</v>
+      </c>
+      <c r="AL12" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM12" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN12" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -5063,7 +5466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN20"/>
+  <dimension ref="A1:AN22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7962,6 +8365,310 @@
         <v>50000</v>
       </c>
       <c r="AN20" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G21" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H21" s="16" t="n">
+        <v>57047.77</v>
+      </c>
+      <c r="I21" s="16" t="n">
+        <v>55931.18</v>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K21" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L21" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N21" s="16" t="inlineStr">
+        <is>
+          <t>13:20 IST</t>
+        </is>
+      </c>
+      <c r="O21" s="16" t="n">
+        <v>57183.75</v>
+      </c>
+      <c r="P21" s="16" t="n">
+        <v>57935.6</v>
+      </c>
+      <c r="Q21" s="16" t="inlineStr">
+        <is>
+          <t>57000 CE</t>
+        </is>
+      </c>
+      <c r="R21" s="16" t="inlineStr">
+        <is>
+          <t>57200 CE</t>
+        </is>
+      </c>
+      <c r="S21" s="16" t="n">
+        <v>34</v>
+      </c>
+      <c r="T21" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U21" s="16" t="n">
+        <v>1020</v>
+      </c>
+      <c r="V21" s="16" t="n">
+        <v>46.93</v>
+      </c>
+      <c r="W21" s="16" t="n">
+        <v>46.19</v>
+      </c>
+      <c r="X21" s="16" t="n">
+        <v>47868.6</v>
+      </c>
+      <c r="Y21" s="16" t="n">
+        <v>47923.33</v>
+      </c>
+      <c r="Z21" s="16" t="n">
+        <v>156131.4</v>
+      </c>
+      <c r="AA21" s="16" t="n">
+        <v>14360.58</v>
+      </c>
+      <c r="AB21" s="16" t="n">
+        <v>14360.58</v>
+      </c>
+      <c r="AC21" s="16" t="n">
+        <v>-754.8</v>
+      </c>
+      <c r="AD21" s="16" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="AE21" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF21" s="16" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AG21" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH21" s="16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI21" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ21" s="16" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="AK21" s="16" t="n">
+        <v>-809.53</v>
+      </c>
+      <c r="AL21" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM21" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN21" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G22" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H22" s="16" t="n">
+        <v>57047.77</v>
+      </c>
+      <c r="I22" s="16" t="n">
+        <v>55931.18</v>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K22" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L22" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N22" s="16" t="inlineStr">
+        <is>
+          <t>13:48 IST</t>
+        </is>
+      </c>
+      <c r="O22" s="16" t="n">
+        <v>57183.75</v>
+      </c>
+      <c r="P22" s="16" t="n">
+        <v>57935.6</v>
+      </c>
+      <c r="Q22" s="16" t="inlineStr">
+        <is>
+          <t>57200 PE</t>
+        </is>
+      </c>
+      <c r="R22" s="16" t="inlineStr">
+        <is>
+          <t>57000 PE</t>
+        </is>
+      </c>
+      <c r="S22" s="16" t="n">
+        <v>41</v>
+      </c>
+      <c r="T22" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U22" s="16" t="n">
+        <v>1230</v>
+      </c>
+      <c r="V22" s="16" t="n">
+        <v>38.83</v>
+      </c>
+      <c r="W22" s="16" t="n">
+        <v>38.66</v>
+      </c>
+      <c r="X22" s="16" t="n">
+        <v>47760.9</v>
+      </c>
+      <c r="Y22" s="16" t="n">
+        <v>47815.62</v>
+      </c>
+      <c r="Z22" s="16" t="n">
+        <v>198239.1</v>
+      </c>
+      <c r="AA22" s="16" t="n">
+        <v>14328.27</v>
+      </c>
+      <c r="AB22" s="16" t="n">
+        <v>14328.27</v>
+      </c>
+      <c r="AC22" s="16" t="n">
+        <v>-209.1</v>
+      </c>
+      <c r="AD22" s="16" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="AE22" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF22" s="16" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="AG22" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH22" s="16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI22" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ22" s="16" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="AK22" s="16" t="n">
+        <v>-263.82</v>
+      </c>
+      <c r="AL22" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM22" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN22" s="16" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -8983,7 +9690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9331,6 +10038,72 @@
         <v>55970.07</v>
       </c>
       <c r="G11" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>23868.74</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>23768.91</v>
+      </c>
+      <c r="G12" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>57047.77</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>55931.18</v>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -9350,7 +10123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA13"/>
+  <dimension ref="A1:AA14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10610,6 +11383,105 @@
         <v>1000</v>
       </c>
       <c r="AA13" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>10:29 ET</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="n">
+        <v>29836.5</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>29825</v>
+      </c>
+      <c r="J14" s="15" t="n">
+        <v>29850</v>
+      </c>
+      <c r="K14" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="L14" s="15" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="M14" s="15" t="n">
+        <v>16.55</v>
+      </c>
+      <c r="N14" s="15" t="n">
+        <v>985.92</v>
+      </c>
+      <c r="O14" s="15" t="n">
+        <v>1028.04</v>
+      </c>
+      <c r="P14" s="15" t="n">
+        <v>276.59</v>
+      </c>
+      <c r="Q14" s="15" t="n">
+        <v>276.59</v>
+      </c>
+      <c r="R14" s="15" t="n">
+        <v>-276.51</v>
+      </c>
+      <c r="S14" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="T14" s="15" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="U14" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="V14" s="15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W14" s="15" t="n">
+        <v>63.96</v>
+      </c>
+      <c r="X14" s="15" t="n">
+        <v>-340.47</v>
+      </c>
+      <c r="Y14" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="Z14" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA14" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -10729,7 +11601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11564,6 +12436,76 @@
       <c r="I24" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="19" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="E25" s="19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F25" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G25" s="19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H25" s="19" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="I25" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="n">
+        <v>39</v>
+      </c>
+      <c r="D26" s="19" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="E26" s="19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F26" s="19" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G26" s="19" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="H26" s="19" t="n">
+        <v>63.96</v>
+      </c>
+      <c r="I26" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — STOP LOSS</t>
         </is>
       </c>
     </row>
@@ -12030,7 +12972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN11"/>
+  <dimension ref="A1:AN12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13606,6 +14548,158 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H12" s="16" t="n">
+        <v>23868.74</v>
+      </c>
+      <c r="I12" s="16" t="n">
+        <v>23768.91</v>
+      </c>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K12" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L12" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N12" s="16" t="inlineStr">
+        <is>
+          <t>15:03 IST</t>
+        </is>
+      </c>
+      <c r="O12" s="16" t="n">
+        <v>23824.1</v>
+      </c>
+      <c r="P12" s="16" t="n">
+        <v>24102.9</v>
+      </c>
+      <c r="Q12" s="16" t="inlineStr">
+        <is>
+          <t>23800 CE</t>
+        </is>
+      </c>
+      <c r="R12" s="16" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="S12" s="16" t="n">
+        <v>41</v>
+      </c>
+      <c r="T12" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U12" s="16" t="n">
+        <v>2665</v>
+      </c>
+      <c r="V12" s="16" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="W12" s="16" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="X12" s="16" t="n">
+        <v>47810.1</v>
+      </c>
+      <c r="Y12" s="16" t="n">
+        <v>47864.82</v>
+      </c>
+      <c r="Z12" s="16" t="n">
+        <v>218689.9</v>
+      </c>
+      <c r="AA12" s="16" t="n">
+        <v>14343.03</v>
+      </c>
+      <c r="AB12" s="16" t="n">
+        <v>14343.03</v>
+      </c>
+      <c r="AC12" s="16" t="n">
+        <v>239.85</v>
+      </c>
+      <c r="AD12" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE12" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF12" s="16" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AG12" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH12" s="16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI12" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ12" s="16" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="AK12" s="16" t="n">
+        <v>185.13</v>
+      </c>
+      <c r="AL12" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM12" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN12" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -13620,7 +14714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN11"/>
+  <dimension ref="A1:AN12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15196,6 +16290,158 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>23868.74</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>23768.91</v>
+      </c>
+      <c r="J12" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K12" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L12" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N12" s="17" t="inlineStr">
+        <is>
+          <t>10:16 IST</t>
+        </is>
+      </c>
+      <c r="O12" s="17" t="n">
+        <v>23824.1</v>
+      </c>
+      <c r="P12" s="17" t="n">
+        <v>24102.9</v>
+      </c>
+      <c r="Q12" s="17" t="inlineStr">
+        <is>
+          <t>23900 PE</t>
+        </is>
+      </c>
+      <c r="R12" s="17" t="inlineStr">
+        <is>
+          <t>23800 PE</t>
+        </is>
+      </c>
+      <c r="S12" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="T12" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U12" s="17" t="n">
+        <v>2080</v>
+      </c>
+      <c r="V12" s="17" t="n">
+        <v>23.06</v>
+      </c>
+      <c r="W12" s="17" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="X12" s="17" t="n">
+        <v>47964.8</v>
+      </c>
+      <c r="Y12" s="17" t="n">
+        <v>48019.55</v>
+      </c>
+      <c r="Z12" s="17" t="n">
+        <v>160035.2</v>
+      </c>
+      <c r="AA12" s="17" t="n">
+        <v>14389.44</v>
+      </c>
+      <c r="AB12" s="17" t="n">
+        <v>14389.44</v>
+      </c>
+      <c r="AC12" s="17" t="n">
+        <v>14393.6</v>
+      </c>
+      <c r="AD12" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE12" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF12" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG12" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH12" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI12" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ12" s="17" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="AK12" s="17" t="n">
+        <v>14338.85</v>
+      </c>
+      <c r="AL12" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM12" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN12" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -15210,7 +16456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN20"/>
+  <dimension ref="A1:AN22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18109,6 +19355,310 @@
         <v>50000</v>
       </c>
       <c r="AN20" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>23868.74</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>23768.91</v>
+      </c>
+      <c r="J21" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K21" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N21" s="15" t="inlineStr">
+        <is>
+          <t>10:44 IST</t>
+        </is>
+      </c>
+      <c r="O21" s="15" t="n">
+        <v>23824.1</v>
+      </c>
+      <c r="P21" s="15" t="n">
+        <v>24102.9</v>
+      </c>
+      <c r="Q21" s="15" t="inlineStr">
+        <is>
+          <t>23800 CE</t>
+        </is>
+      </c>
+      <c r="R21" s="15" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="S21" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="T21" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U21" s="15" t="n">
+        <v>2405</v>
+      </c>
+      <c r="V21" s="15" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="W21" s="15" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="X21" s="15" t="n">
+        <v>48075.95</v>
+      </c>
+      <c r="Y21" s="15" t="n">
+        <v>48130.72</v>
+      </c>
+      <c r="Z21" s="15" t="n">
+        <v>192424.05</v>
+      </c>
+      <c r="AA21" s="15" t="n">
+        <v>14422.78</v>
+      </c>
+      <c r="AB21" s="15" t="n">
+        <v>14422.78</v>
+      </c>
+      <c r="AC21" s="15" t="n">
+        <v>-14430</v>
+      </c>
+      <c r="AD21" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE21" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF21" s="15" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="AG21" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH21" s="15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI21" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ21" s="15" t="n">
+        <v>54.77</v>
+      </c>
+      <c r="AK21" s="15" t="n">
+        <v>-14484.77</v>
+      </c>
+      <c r="AL21" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM21" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN21" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G22" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H22" s="16" t="n">
+        <v>23868.74</v>
+      </c>
+      <c r="I22" s="16" t="n">
+        <v>23768.91</v>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K22" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L22" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N22" s="16" t="inlineStr">
+        <is>
+          <t>14:59 IST</t>
+        </is>
+      </c>
+      <c r="O22" s="16" t="n">
+        <v>23824.1</v>
+      </c>
+      <c r="P22" s="16" t="n">
+        <v>24102.9</v>
+      </c>
+      <c r="Q22" s="16" t="inlineStr">
+        <is>
+          <t>23900 PE</t>
+        </is>
+      </c>
+      <c r="R22" s="16" t="inlineStr">
+        <is>
+          <t>23800 PE</t>
+        </is>
+      </c>
+      <c r="S22" s="16" t="n">
+        <v>43</v>
+      </c>
+      <c r="T22" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U22" s="16" t="n">
+        <v>2795</v>
+      </c>
+      <c r="V22" s="16" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="W22" s="16" t="n">
+        <v>16.93</v>
+      </c>
+      <c r="X22" s="16" t="n">
+        <v>48074</v>
+      </c>
+      <c r="Y22" s="16" t="n">
+        <v>48128.76</v>
+      </c>
+      <c r="Z22" s="16" t="n">
+        <v>231426</v>
+      </c>
+      <c r="AA22" s="16" t="n">
+        <v>14422.2</v>
+      </c>
+      <c r="AB22" s="16" t="n">
+        <v>14422.2</v>
+      </c>
+      <c r="AC22" s="16" t="n">
+        <v>-754.65</v>
+      </c>
+      <c r="AD22" s="16" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="AE22" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF22" s="16" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="AG22" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH22" s="16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI22" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ22" s="16" t="n">
+        <v>54.76</v>
+      </c>
+      <c r="AK22" s="16" t="n">
+        <v>-809.41</v>
+      </c>
+      <c r="AL22" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM22" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN22" s="16" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA18"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2364,6 +2364,105 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>10:46 ET</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>29856.25</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>29850</v>
+      </c>
+      <c r="J19" s="15" t="n">
+        <v>29875</v>
+      </c>
+      <c r="K19" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" s="15" t="n">
+        <v>251.24</v>
+      </c>
+      <c r="M19" s="15" t="n">
+        <v>175.87</v>
+      </c>
+      <c r="N19" s="15" t="n">
+        <v>775.92</v>
+      </c>
+      <c r="O19" s="15" t="n">
+        <v>746.28</v>
+      </c>
+      <c r="P19" s="15" t="n">
+        <v>226.12</v>
+      </c>
+      <c r="Q19" s="15" t="n">
+        <v>226.12</v>
+      </c>
+      <c r="R19" s="15" t="n">
+        <v>-226.11</v>
+      </c>
+      <c r="S19" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="T19" s="15" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="U19" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="V19" s="15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W19" s="15" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="X19" s="15" t="n">
+        <v>-248.31</v>
+      </c>
+      <c r="Y19" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="Z19" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA19" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -2378,7 +2477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN16"/>
+  <dimension ref="A1:AN17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4714,6 +4813,158 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>57506.76</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>56326.72</v>
+      </c>
+      <c r="J17" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K17" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L17" s="15" t="n">
+        <v>31</v>
+      </c>
+      <c r="M17" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N17" s="15" t="inlineStr">
+        <is>
+          <t>11:18 IST</t>
+        </is>
+      </c>
+      <c r="O17" s="15" t="n">
+        <v>57727.35</v>
+      </c>
+      <c r="P17" s="15" t="n">
+        <v>58177.05</v>
+      </c>
+      <c r="Q17" s="15" t="inlineStr">
+        <is>
+          <t>57600 CE</t>
+        </is>
+      </c>
+      <c r="R17" s="15" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="S17" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="T17" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U17" s="15" t="n">
+        <v>570</v>
+      </c>
+      <c r="V17" s="15" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="W17" s="15" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="X17" s="15" t="n">
+        <v>47709</v>
+      </c>
+      <c r="Y17" s="15" t="n">
+        <v>47763.71</v>
+      </c>
+      <c r="Z17" s="15" t="n">
+        <v>66291</v>
+      </c>
+      <c r="AA17" s="15" t="n">
+        <v>14312.7</v>
+      </c>
+      <c r="AB17" s="15" t="n">
+        <v>14312.7</v>
+      </c>
+      <c r="AC17" s="15" t="n">
+        <v>-14312.7</v>
+      </c>
+      <c r="AD17" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE17" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF17" s="15" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="AG17" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH17" s="15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI17" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ17" s="15" t="n">
+        <v>54.71</v>
+      </c>
+      <c r="AK17" s="15" t="n">
+        <v>-14367.41</v>
+      </c>
+      <c r="AL17" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM17" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN17" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -4728,7 +4979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN16"/>
+  <dimension ref="A1:AN17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7064,6 +7315,158 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G17" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H17" s="17" t="n">
+        <v>57506.76</v>
+      </c>
+      <c r="I17" s="17" t="n">
+        <v>56326.72</v>
+      </c>
+      <c r="J17" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K17" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L17" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="M17" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N17" s="17" t="inlineStr">
+        <is>
+          <t>12:05 IST</t>
+        </is>
+      </c>
+      <c r="O17" s="17" t="n">
+        <v>57727.35</v>
+      </c>
+      <c r="P17" s="17" t="n">
+        <v>58177.05</v>
+      </c>
+      <c r="Q17" s="17" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="R17" s="17" t="inlineStr">
+        <is>
+          <t>57600 PE</t>
+        </is>
+      </c>
+      <c r="S17" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="T17" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U17" s="17" t="n">
+        <v>540</v>
+      </c>
+      <c r="V17" s="17" t="n">
+        <v>87.79000000000001</v>
+      </c>
+      <c r="W17" s="17" t="n">
+        <v>114.13</v>
+      </c>
+      <c r="X17" s="17" t="n">
+        <v>47406.6</v>
+      </c>
+      <c r="Y17" s="17" t="n">
+        <v>47461.26</v>
+      </c>
+      <c r="Z17" s="17" t="n">
+        <v>60593.4</v>
+      </c>
+      <c r="AA17" s="17" t="n">
+        <v>14221.98</v>
+      </c>
+      <c r="AB17" s="17" t="n">
+        <v>14221.98</v>
+      </c>
+      <c r="AC17" s="17" t="n">
+        <v>14223.6</v>
+      </c>
+      <c r="AD17" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE17" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF17" s="17" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="AG17" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH17" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI17" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ17" s="17" t="n">
+        <v>54.66</v>
+      </c>
+      <c r="AK17" s="17" t="n">
+        <v>14168.94</v>
+      </c>
+      <c r="AL17" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM17" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN17" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -7078,7 +7481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN30"/>
+  <dimension ref="A1:AN32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11497,6 +11900,310 @@
         <v>50000</v>
       </c>
       <c r="AN30" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G31" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H31" s="16" t="n">
+        <v>57506.76</v>
+      </c>
+      <c r="I31" s="16" t="n">
+        <v>56326.72</v>
+      </c>
+      <c r="J31" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K31" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L31" s="16" t="n">
+        <v>31</v>
+      </c>
+      <c r="M31" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N31" s="16" t="inlineStr">
+        <is>
+          <t>14:44 IST</t>
+        </is>
+      </c>
+      <c r="O31" s="16" t="n">
+        <v>57727.35</v>
+      </c>
+      <c r="P31" s="16" t="n">
+        <v>58177.05</v>
+      </c>
+      <c r="Q31" s="16" t="inlineStr">
+        <is>
+          <t>57600 CE</t>
+        </is>
+      </c>
+      <c r="R31" s="16" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="S31" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="T31" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U31" s="16" t="n">
+        <v>510</v>
+      </c>
+      <c r="V31" s="16" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="W31" s="16" t="n">
+        <v>93.16</v>
+      </c>
+      <c r="X31" s="16" t="n">
+        <v>48858</v>
+      </c>
+      <c r="Y31" s="16" t="n">
+        <v>48912.89</v>
+      </c>
+      <c r="Z31" s="16" t="n">
+        <v>53142</v>
+      </c>
+      <c r="AA31" s="16" t="n">
+        <v>14657.4</v>
+      </c>
+      <c r="AB31" s="16" t="n">
+        <v>14657.4</v>
+      </c>
+      <c r="AC31" s="16" t="n">
+        <v>-1346.4</v>
+      </c>
+      <c r="AD31" s="16" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="AE31" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF31" s="16" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="AG31" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH31" s="16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI31" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ31" s="16" t="n">
+        <v>54.89</v>
+      </c>
+      <c r="AK31" s="16" t="n">
+        <v>-1401.29</v>
+      </c>
+      <c r="AL31" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM31" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN31" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>57506.76</v>
+      </c>
+      <c r="I32" s="15" t="n">
+        <v>56326.72</v>
+      </c>
+      <c r="J32" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K32" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L32" s="15" t="n">
+        <v>31</v>
+      </c>
+      <c r="M32" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N32" s="15" t="inlineStr">
+        <is>
+          <t>10:56 IST</t>
+        </is>
+      </c>
+      <c r="O32" s="15" t="n">
+        <v>57727.35</v>
+      </c>
+      <c r="P32" s="15" t="n">
+        <v>58177.05</v>
+      </c>
+      <c r="Q32" s="15" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="R32" s="15" t="inlineStr">
+        <is>
+          <t>57600 PE</t>
+        </is>
+      </c>
+      <c r="S32" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="T32" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U32" s="15" t="n">
+        <v>510</v>
+      </c>
+      <c r="V32" s="15" t="n">
+        <v>92.15000000000001</v>
+      </c>
+      <c r="W32" s="15" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="X32" s="15" t="n">
+        <v>46996.5</v>
+      </c>
+      <c r="Y32" s="15" t="n">
+        <v>47051.1</v>
+      </c>
+      <c r="Z32" s="15" t="n">
+        <v>55003.5</v>
+      </c>
+      <c r="AA32" s="15" t="n">
+        <v>14098.95</v>
+      </c>
+      <c r="AB32" s="15" t="n">
+        <v>14098.95</v>
+      </c>
+      <c r="AC32" s="15" t="n">
+        <v>-14101.5</v>
+      </c>
+      <c r="AD32" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE32" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF32" s="15" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="AG32" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH32" s="15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI32" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ32" s="15" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="AK32" s="15" t="n">
+        <v>-14156.1</v>
+      </c>
+      <c r="AL32" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM32" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN32" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -13126,7 +13833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13540,6 +14247,72 @@
         <v>55931.18</v>
       </c>
       <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>23934.65</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>23794.94</v>
+      </c>
+      <c r="G14" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>57506.76</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>56326.72</v>
+      </c>
+      <c r="G15" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -13559,7 +14332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA18"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15314,6 +16087,105 @@
         <v>1000</v>
       </c>
       <c r="AA18" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>11:04 ET</t>
+        </is>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>29856</v>
+      </c>
+      <c r="I19" s="17" t="n">
+        <v>29850</v>
+      </c>
+      <c r="J19" s="17" t="n">
+        <v>29875</v>
+      </c>
+      <c r="K19" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="L19" s="17" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="M19" s="17" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="N19" s="17" t="n">
+        <v>991.23</v>
+      </c>
+      <c r="O19" s="17" t="n">
+        <v>919.45</v>
+      </c>
+      <c r="P19" s="17" t="n">
+        <v>279.16</v>
+      </c>
+      <c r="Q19" s="17" t="n">
+        <v>279.16</v>
+      </c>
+      <c r="R19" s="17" t="n">
+        <v>279.35</v>
+      </c>
+      <c r="S19" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T19" s="17" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="U19" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="V19" s="17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W19" s="17" t="n">
+        <v>60.68</v>
+      </c>
+      <c r="X19" s="17" t="n">
+        <v>218.67</v>
+      </c>
+      <c r="Y19" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z19" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA19" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -15433,7 +16305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16618,6 +17490,76 @@
       <c r="I34" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" s="19" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="E35" s="19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F35" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G35" s="19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H35" s="19" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="I35" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — STOP LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C36" s="19" t="n">
+        <v>37</v>
+      </c>
+      <c r="D36" s="19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" s="19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F36" s="19" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G36" s="19" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="H36" s="19" t="n">
+        <v>60.68</v>
+      </c>
+      <c r="I36" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — PROFIT</t>
         </is>
       </c>
     </row>
@@ -17084,7 +18026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN16"/>
+  <dimension ref="A1:AN17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -19420,6 +20362,158 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>23934.65</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>23794.94</v>
+      </c>
+      <c r="J17" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K17" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L17" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N17" s="15" t="inlineStr">
+        <is>
+          <t>10:07 IST</t>
+        </is>
+      </c>
+      <c r="O17" s="15" t="n">
+        <v>23946.25</v>
+      </c>
+      <c r="P17" s="15" t="n">
+        <v>24056</v>
+      </c>
+      <c r="Q17" s="15" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="R17" s="15" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="S17" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="T17" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U17" s="15" t="n">
+        <v>1430</v>
+      </c>
+      <c r="V17" s="15" t="n">
+        <v>34.33</v>
+      </c>
+      <c r="W17" s="15" t="n">
+        <v>24.03</v>
+      </c>
+      <c r="X17" s="15" t="n">
+        <v>49091.9</v>
+      </c>
+      <c r="Y17" s="15" t="n">
+        <v>49146.83</v>
+      </c>
+      <c r="Z17" s="15" t="n">
+        <v>93908.10000000001</v>
+      </c>
+      <c r="AA17" s="15" t="n">
+        <v>14727.57</v>
+      </c>
+      <c r="AB17" s="15" t="n">
+        <v>14727.57</v>
+      </c>
+      <c r="AC17" s="15" t="n">
+        <v>-14729</v>
+      </c>
+      <c r="AD17" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE17" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF17" s="15" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="AG17" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH17" s="15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI17" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ17" s="15" t="n">
+        <v>54.93</v>
+      </c>
+      <c r="AK17" s="15" t="n">
+        <v>-14783.93</v>
+      </c>
+      <c r="AL17" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM17" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN17" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -19434,7 +20528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN16"/>
+  <dimension ref="A1:AN17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21770,6 +22864,158 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>23934.65</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>23794.94</v>
+      </c>
+      <c r="J17" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K17" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L17" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N17" s="15" t="inlineStr">
+        <is>
+          <t>10:17 IST</t>
+        </is>
+      </c>
+      <c r="O17" s="15" t="n">
+        <v>23946.25</v>
+      </c>
+      <c r="P17" s="15" t="n">
+        <v>24056</v>
+      </c>
+      <c r="Q17" s="15" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="R17" s="15" t="inlineStr">
+        <is>
+          <t>23900 PE</t>
+        </is>
+      </c>
+      <c r="S17" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U17" s="15" t="n">
+        <v>1625</v>
+      </c>
+      <c r="V17" s="15" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="W17" s="15" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="X17" s="15" t="n">
+        <v>47368.75</v>
+      </c>
+      <c r="Y17" s="15" t="n">
+        <v>47423.4</v>
+      </c>
+      <c r="Z17" s="15" t="n">
+        <v>115131.25</v>
+      </c>
+      <c r="AA17" s="15" t="n">
+        <v>14210.62</v>
+      </c>
+      <c r="AB17" s="15" t="n">
+        <v>14210.62</v>
+      </c>
+      <c r="AC17" s="15" t="n">
+        <v>-14218.75</v>
+      </c>
+      <c r="AD17" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE17" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF17" s="15" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="AG17" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH17" s="15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI17" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ17" s="15" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="AK17" s="15" t="n">
+        <v>-14273.4</v>
+      </c>
+      <c r="AL17" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM17" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN17" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -21784,7 +23030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN30"/>
+  <dimension ref="A1:AN32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -26203,6 +27449,310 @@
         <v>50000</v>
       </c>
       <c r="AN30" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G31" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H31" s="16" t="n">
+        <v>23934.65</v>
+      </c>
+      <c r="I31" s="16" t="n">
+        <v>23794.94</v>
+      </c>
+      <c r="J31" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K31" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L31" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M31" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N31" s="16" t="inlineStr">
+        <is>
+          <t>14:07 IST</t>
+        </is>
+      </c>
+      <c r="O31" s="16" t="n">
+        <v>23946.25</v>
+      </c>
+      <c r="P31" s="16" t="n">
+        <v>24056</v>
+      </c>
+      <c r="Q31" s="16" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="R31" s="16" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="S31" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="T31" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U31" s="16" t="n">
+        <v>1495</v>
+      </c>
+      <c r="V31" s="16" t="n">
+        <v>31.78</v>
+      </c>
+      <c r="W31" s="16" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="X31" s="16" t="n">
+        <v>47511.1</v>
+      </c>
+      <c r="Y31" s="16" t="n">
+        <v>47565.78</v>
+      </c>
+      <c r="Z31" s="16" t="n">
+        <v>101988.9</v>
+      </c>
+      <c r="AA31" s="16" t="n">
+        <v>14253.33</v>
+      </c>
+      <c r="AB31" s="16" t="n">
+        <v>14253.33</v>
+      </c>
+      <c r="AC31" s="16" t="n">
+        <v>179.4</v>
+      </c>
+      <c r="AD31" s="16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AE31" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF31" s="16" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AG31" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH31" s="16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI31" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ31" s="16" t="n">
+        <v>54.68</v>
+      </c>
+      <c r="AK31" s="16" t="n">
+        <v>124.72</v>
+      </c>
+      <c r="AL31" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM31" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN31" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>23934.65</v>
+      </c>
+      <c r="I32" s="15" t="n">
+        <v>23794.94</v>
+      </c>
+      <c r="J32" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K32" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L32" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M32" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N32" s="15" t="inlineStr">
+        <is>
+          <t>10:02 IST</t>
+        </is>
+      </c>
+      <c r="O32" s="15" t="n">
+        <v>23946.25</v>
+      </c>
+      <c r="P32" s="15" t="n">
+        <v>24056</v>
+      </c>
+      <c r="Q32" s="15" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="R32" s="15" t="inlineStr">
+        <is>
+          <t>23900 PE</t>
+        </is>
+      </c>
+      <c r="S32" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="T32" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U32" s="15" t="n">
+        <v>1495</v>
+      </c>
+      <c r="V32" s="15" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="W32" s="15" t="n">
+        <v>22.57</v>
+      </c>
+      <c r="X32" s="15" t="n">
+        <v>48213.75</v>
+      </c>
+      <c r="Y32" s="15" t="n">
+        <v>48268.54</v>
+      </c>
+      <c r="Z32" s="15" t="n">
+        <v>101286.25</v>
+      </c>
+      <c r="AA32" s="15" t="n">
+        <v>14464.12</v>
+      </c>
+      <c r="AB32" s="15" t="n">
+        <v>14464.12</v>
+      </c>
+      <c r="AC32" s="15" t="n">
+        <v>-14471.6</v>
+      </c>
+      <c r="AD32" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE32" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF32" s="15" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AG32" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH32" s="15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI32" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ32" s="15" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="AK32" s="15" t="n">
+        <v>-14526.39</v>
+      </c>
+      <c r="AL32" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM32" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN32" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA20"/>
+  <dimension ref="A1:AA21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2562,6 +2562,105 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>13:44 ET</t>
+        </is>
+      </c>
+      <c r="H21" s="17" t="n">
+        <v>30154.75</v>
+      </c>
+      <c r="I21" s="17" t="n">
+        <v>30150</v>
+      </c>
+      <c r="J21" s="17" t="n">
+        <v>30175</v>
+      </c>
+      <c r="K21" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L21" s="17" t="n">
+        <v>229.86</v>
+      </c>
+      <c r="M21" s="17" t="n">
+        <v>298.82</v>
+      </c>
+      <c r="N21" s="17" t="n">
+        <v>949.04</v>
+      </c>
+      <c r="O21" s="17" t="n">
+        <v>1080.56</v>
+      </c>
+      <c r="P21" s="17" t="n">
+        <v>275.83</v>
+      </c>
+      <c r="Q21" s="17" t="n">
+        <v>275.83</v>
+      </c>
+      <c r="R21" s="17" t="n">
+        <v>275.84</v>
+      </c>
+      <c r="S21" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T21" s="17" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="U21" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="V21" s="17" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W21" s="17" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="X21" s="17" t="n">
+        <v>246.24</v>
+      </c>
+      <c r="Y21" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z21" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -2576,7 +2675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN18"/>
+  <dimension ref="A1:AN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5216,6 +5315,158 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>57515.81</v>
+      </c>
+      <c r="I19" s="17" t="n">
+        <v>56405.26</v>
+      </c>
+      <c r="J19" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K19" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L19" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="M19" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N19" s="17" t="inlineStr">
+        <is>
+          <t>12:19 IST</t>
+        </is>
+      </c>
+      <c r="O19" s="17" t="n">
+        <v>57542.9</v>
+      </c>
+      <c r="P19" s="17" t="n">
+        <v>57727.35</v>
+      </c>
+      <c r="Q19" s="17" t="inlineStr">
+        <is>
+          <t>57400 CE</t>
+        </is>
+      </c>
+      <c r="R19" s="17" t="inlineStr">
+        <is>
+          <t>57600 CE</t>
+        </is>
+      </c>
+      <c r="S19" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="T19" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U19" s="17" t="n">
+        <v>570</v>
+      </c>
+      <c r="V19" s="17" t="n">
+        <v>82.67</v>
+      </c>
+      <c r="W19" s="17" t="n">
+        <v>107.47</v>
+      </c>
+      <c r="X19" s="17" t="n">
+        <v>47121.9</v>
+      </c>
+      <c r="Y19" s="17" t="n">
+        <v>47176.52</v>
+      </c>
+      <c r="Z19" s="17" t="n">
+        <v>66878.10000000001</v>
+      </c>
+      <c r="AA19" s="17" t="n">
+        <v>14136.57</v>
+      </c>
+      <c r="AB19" s="17" t="n">
+        <v>14136.57</v>
+      </c>
+      <c r="AC19" s="17" t="n">
+        <v>14136</v>
+      </c>
+      <c r="AD19" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE19" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF19" s="17" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AG19" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH19" s="17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI19" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ19" s="17" t="n">
+        <v>54.62</v>
+      </c>
+      <c r="AK19" s="17" t="n">
+        <v>14081.38</v>
+      </c>
+      <c r="AL19" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM19" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN19" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -5230,7 +5481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN18"/>
+  <dimension ref="A1:AN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7870,6 +8121,158 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>57515.81</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>56405.26</v>
+      </c>
+      <c r="J19" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K19" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L19" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="M19" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N19" s="15" t="inlineStr">
+        <is>
+          <t>09:36 IST</t>
+        </is>
+      </c>
+      <c r="O19" s="15" t="n">
+        <v>57542.9</v>
+      </c>
+      <c r="P19" s="15" t="n">
+        <v>57727.35</v>
+      </c>
+      <c r="Q19" s="15" t="inlineStr">
+        <is>
+          <t>57600 PE</t>
+        </is>
+      </c>
+      <c r="R19" s="15" t="inlineStr">
+        <is>
+          <t>57400 PE</t>
+        </is>
+      </c>
+      <c r="S19" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="T19" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U19" s="15" t="n">
+        <v>480</v>
+      </c>
+      <c r="V19" s="15" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="W19" s="15" t="n">
+        <v>69.51000000000001</v>
+      </c>
+      <c r="X19" s="15" t="n">
+        <v>47664</v>
+      </c>
+      <c r="Y19" s="15" t="n">
+        <v>47718.7</v>
+      </c>
+      <c r="Z19" s="15" t="n">
+        <v>48336</v>
+      </c>
+      <c r="AA19" s="15" t="n">
+        <v>14299.2</v>
+      </c>
+      <c r="AB19" s="15" t="n">
+        <v>14299.2</v>
+      </c>
+      <c r="AC19" s="15" t="n">
+        <v>-14299.2</v>
+      </c>
+      <c r="AD19" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE19" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF19" s="15" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="AG19" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH19" s="15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI19" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ19" s="15" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="AK19" s="15" t="n">
+        <v>-14353.9</v>
+      </c>
+      <c r="AL19" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM19" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN19" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -7884,7 +8287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN34"/>
+  <dimension ref="A1:AN36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12911,6 +13314,310 @@
         <v>50000</v>
       </c>
       <c r="AN34" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G35" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H35" s="16" t="n">
+        <v>57515.81</v>
+      </c>
+      <c r="I35" s="16" t="n">
+        <v>56405.26</v>
+      </c>
+      <c r="J35" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K35" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L35" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="M35" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N35" s="16" t="inlineStr">
+        <is>
+          <t>13:33 IST</t>
+        </is>
+      </c>
+      <c r="O35" s="16" t="n">
+        <v>57542.9</v>
+      </c>
+      <c r="P35" s="16" t="n">
+        <v>57727.35</v>
+      </c>
+      <c r="Q35" s="16" t="inlineStr">
+        <is>
+          <t>57400 CE</t>
+        </is>
+      </c>
+      <c r="R35" s="16" t="inlineStr">
+        <is>
+          <t>57600 CE</t>
+        </is>
+      </c>
+      <c r="S35" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U35" s="16" t="n">
+        <v>450</v>
+      </c>
+      <c r="V35" s="16" t="n">
+        <v>106.82</v>
+      </c>
+      <c r="W35" s="16" t="n">
+        <v>101.83</v>
+      </c>
+      <c r="X35" s="16" t="n">
+        <v>48069</v>
+      </c>
+      <c r="Y35" s="16" t="n">
+        <v>48123.76</v>
+      </c>
+      <c r="Z35" s="16" t="n">
+        <v>41931</v>
+      </c>
+      <c r="AA35" s="16" t="n">
+        <v>14420.7</v>
+      </c>
+      <c r="AB35" s="16" t="n">
+        <v>14420.7</v>
+      </c>
+      <c r="AC35" s="16" t="n">
+        <v>-2245.5</v>
+      </c>
+      <c r="AD35" s="16" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="AE35" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF35" s="16" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="AG35" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH35" s="16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI35" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ35" s="16" t="n">
+        <v>54.76</v>
+      </c>
+      <c r="AK35" s="16" t="n">
+        <v>-2300.26</v>
+      </c>
+      <c r="AL35" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM35" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN35" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H36" s="17" t="n">
+        <v>57515.81</v>
+      </c>
+      <c r="I36" s="17" t="n">
+        <v>56405.26</v>
+      </c>
+      <c r="J36" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K36" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L36" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="M36" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N36" s="17" t="inlineStr">
+        <is>
+          <t>09:47 IST</t>
+        </is>
+      </c>
+      <c r="O36" s="17" t="n">
+        <v>57542.9</v>
+      </c>
+      <c r="P36" s="17" t="n">
+        <v>57727.35</v>
+      </c>
+      <c r="Q36" s="17" t="inlineStr">
+        <is>
+          <t>57600 PE</t>
+        </is>
+      </c>
+      <c r="R36" s="17" t="inlineStr">
+        <is>
+          <t>57400 PE</t>
+        </is>
+      </c>
+      <c r="S36" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="T36" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U36" s="17" t="n">
+        <v>570</v>
+      </c>
+      <c r="V36" s="17" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="W36" s="17" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="X36" s="17" t="n">
+        <v>47025</v>
+      </c>
+      <c r="Y36" s="17" t="n">
+        <v>47079.6</v>
+      </c>
+      <c r="Z36" s="17" t="n">
+        <v>66975</v>
+      </c>
+      <c r="AA36" s="17" t="n">
+        <v>14107.5</v>
+      </c>
+      <c r="AB36" s="17" t="n">
+        <v>14107.5</v>
+      </c>
+      <c r="AC36" s="17" t="n">
+        <v>14107.5</v>
+      </c>
+      <c r="AD36" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE36" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF36" s="17" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="AG36" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH36" s="17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI36" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ36" s="17" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="AK36" s="17" t="n">
+        <v>14052.9</v>
+      </c>
+      <c r="AL36" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM36" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN36" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -14692,7 +15399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15172,6 +15879,72 @@
         <v>56326.72</v>
       </c>
       <c r="G15" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>23921.32</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>23787.88</v>
+      </c>
+      <c r="G16" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>57515.81</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>56405.26</v>
+      </c>
+      <c r="G17" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -15191,7 +15964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA20"/>
+  <dimension ref="A1:AA21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17144,6 +17917,105 @@
         <v>1000</v>
       </c>
       <c r="AA20" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>12:22 ET</t>
+        </is>
+      </c>
+      <c r="H21" s="17" t="n">
+        <v>30154</v>
+      </c>
+      <c r="I21" s="17" t="n">
+        <v>30150</v>
+      </c>
+      <c r="J21" s="17" t="n">
+        <v>30175</v>
+      </c>
+      <c r="K21" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="L21" s="17" t="n">
+        <v>24.48</v>
+      </c>
+      <c r="M21" s="17" t="n">
+        <v>31.82</v>
+      </c>
+      <c r="N21" s="17" t="n">
+        <v>992.5599999999999</v>
+      </c>
+      <c r="O21" s="17" t="n">
+        <v>969.76</v>
+      </c>
+      <c r="P21" s="17" t="n">
+        <v>279.07</v>
+      </c>
+      <c r="Q21" s="17" t="n">
+        <v>279.07</v>
+      </c>
+      <c r="R21" s="17" t="n">
+        <v>278.92</v>
+      </c>
+      <c r="S21" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T21" s="17" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="U21" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="V21" s="17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W21" s="17" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="X21" s="17" t="n">
+        <v>216.6</v>
+      </c>
+      <c r="Y21" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z21" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -17263,7 +18135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18586,6 +19458,76 @@
         <v>67.23999999999999</v>
       </c>
       <c r="I38" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" s="19" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="E39" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F39" s="19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G39" s="19" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H39" s="19" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I39" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C40" s="19" t="n">
+        <v>38</v>
+      </c>
+      <c r="D40" s="19" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="E40" s="19" t="n">
+        <v>19</v>
+      </c>
+      <c r="F40" s="19" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G40" s="19" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="H40" s="19" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="I40" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — PROFIT</t>
         </is>
@@ -19054,7 +19996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN18"/>
+  <dimension ref="A1:AN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21694,6 +22636,158 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>23921.32</v>
+      </c>
+      <c r="I19" s="17" t="n">
+        <v>23787.88</v>
+      </c>
+      <c r="J19" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K19" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L19" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N19" s="17" t="inlineStr">
+        <is>
+          <t>12:08 IST</t>
+        </is>
+      </c>
+      <c r="O19" s="17" t="n">
+        <v>23865.75</v>
+      </c>
+      <c r="P19" s="17" t="n">
+        <v>23946.25</v>
+      </c>
+      <c r="Q19" s="17" t="inlineStr">
+        <is>
+          <t>23800 CE</t>
+        </is>
+      </c>
+      <c r="R19" s="17" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="S19" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="T19" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U19" s="17" t="n">
+        <v>2405</v>
+      </c>
+      <c r="V19" s="17" t="n">
+        <v>20.13</v>
+      </c>
+      <c r="W19" s="17" t="n">
+        <v>26.17</v>
+      </c>
+      <c r="X19" s="17" t="n">
+        <v>48412.65</v>
+      </c>
+      <c r="Y19" s="17" t="n">
+        <v>48467.47</v>
+      </c>
+      <c r="Z19" s="17" t="n">
+        <v>192087.35</v>
+      </c>
+      <c r="AA19" s="17" t="n">
+        <v>14523.8</v>
+      </c>
+      <c r="AB19" s="17" t="n">
+        <v>14523.8</v>
+      </c>
+      <c r="AC19" s="17" t="n">
+        <v>14526.2</v>
+      </c>
+      <c r="AD19" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE19" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF19" s="17" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AG19" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH19" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI19" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ19" s="17" t="n">
+        <v>54.82</v>
+      </c>
+      <c r="AK19" s="17" t="n">
+        <v>14471.38</v>
+      </c>
+      <c r="AL19" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM19" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN19" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -21708,7 +22802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN18"/>
+  <dimension ref="A1:AN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -24348,6 +25442,158 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>23921.32</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>23787.88</v>
+      </c>
+      <c r="J19" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K19" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L19" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N19" s="15" t="inlineStr">
+        <is>
+          <t>11:18 IST</t>
+        </is>
+      </c>
+      <c r="O19" s="15" t="n">
+        <v>23865.75</v>
+      </c>
+      <c r="P19" s="15" t="n">
+        <v>23946.25</v>
+      </c>
+      <c r="Q19" s="15" t="inlineStr">
+        <is>
+          <t>23900 PE</t>
+        </is>
+      </c>
+      <c r="R19" s="15" t="inlineStr">
+        <is>
+          <t>23800 PE</t>
+        </is>
+      </c>
+      <c r="S19" s="15" t="n">
+        <v>33</v>
+      </c>
+      <c r="T19" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U19" s="15" t="n">
+        <v>2145</v>
+      </c>
+      <c r="V19" s="15" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="W19" s="15" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="X19" s="15" t="n">
+        <v>48391.2</v>
+      </c>
+      <c r="Y19" s="15" t="n">
+        <v>48446.01</v>
+      </c>
+      <c r="Z19" s="15" t="n">
+        <v>166108.8</v>
+      </c>
+      <c r="AA19" s="15" t="n">
+        <v>14517.36</v>
+      </c>
+      <c r="AB19" s="15" t="n">
+        <v>14517.36</v>
+      </c>
+      <c r="AC19" s="15" t="n">
+        <v>-14521.65</v>
+      </c>
+      <c r="AD19" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE19" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF19" s="15" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AG19" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH19" s="15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI19" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ19" s="15" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="AK19" s="15" t="n">
+        <v>-14576.46</v>
+      </c>
+      <c r="AL19" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM19" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN19" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -24362,7 +25608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN34"/>
+  <dimension ref="A1:AN36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -29389,6 +30635,310 @@
         <v>50000</v>
       </c>
       <c r="AN34" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G35" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H35" s="16" t="n">
+        <v>23921.32</v>
+      </c>
+      <c r="I35" s="16" t="n">
+        <v>23787.88</v>
+      </c>
+      <c r="J35" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K35" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L35" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M35" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N35" s="16" t="inlineStr">
+        <is>
+          <t>15:12 IST</t>
+        </is>
+      </c>
+      <c r="O35" s="16" t="n">
+        <v>23865.75</v>
+      </c>
+      <c r="P35" s="16" t="n">
+        <v>23946.25</v>
+      </c>
+      <c r="Q35" s="16" t="inlineStr">
+        <is>
+          <t>23800 CE</t>
+        </is>
+      </c>
+      <c r="R35" s="16" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="S35" s="16" t="n">
+        <v>44</v>
+      </c>
+      <c r="T35" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U35" s="16" t="n">
+        <v>2860</v>
+      </c>
+      <c r="V35" s="16" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="W35" s="16" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="X35" s="16" t="n">
+        <v>47218.6</v>
+      </c>
+      <c r="Y35" s="16" t="n">
+        <v>47273.23</v>
+      </c>
+      <c r="Z35" s="16" t="n">
+        <v>238781.4</v>
+      </c>
+      <c r="AA35" s="16" t="n">
+        <v>14165.58</v>
+      </c>
+      <c r="AB35" s="16" t="n">
+        <v>14165.58</v>
+      </c>
+      <c r="AC35" s="16" t="n">
+        <v>1029.6</v>
+      </c>
+      <c r="AD35" s="16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE35" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF35" s="16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AG35" s="16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH35" s="16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI35" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ35" s="16" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="AK35" s="16" t="n">
+        <v>974.97</v>
+      </c>
+      <c r="AL35" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM35" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN35" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E36" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G36" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H36" s="16" t="n">
+        <v>23921.32</v>
+      </c>
+      <c r="I36" s="16" t="n">
+        <v>23787.88</v>
+      </c>
+      <c r="J36" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K36" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L36" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M36" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N36" s="16" t="inlineStr">
+        <is>
+          <t>14:57 IST</t>
+        </is>
+      </c>
+      <c r="O36" s="16" t="n">
+        <v>23865.75</v>
+      </c>
+      <c r="P36" s="16" t="n">
+        <v>23946.25</v>
+      </c>
+      <c r="Q36" s="16" t="inlineStr">
+        <is>
+          <t>23900 PE</t>
+        </is>
+      </c>
+      <c r="R36" s="16" t="inlineStr">
+        <is>
+          <t>23800 PE</t>
+        </is>
+      </c>
+      <c r="S36" s="16" t="n">
+        <v>48</v>
+      </c>
+      <c r="T36" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U36" s="16" t="n">
+        <v>3120</v>
+      </c>
+      <c r="V36" s="16" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="W36" s="16" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="X36" s="16" t="n">
+        <v>48016.8</v>
+      </c>
+      <c r="Y36" s="16" t="n">
+        <v>48071.56</v>
+      </c>
+      <c r="Z36" s="16" t="n">
+        <v>263983.2</v>
+      </c>
+      <c r="AA36" s="16" t="n">
+        <v>14405.04</v>
+      </c>
+      <c r="AB36" s="16" t="n">
+        <v>14405.04</v>
+      </c>
+      <c r="AC36" s="16" t="n">
+        <v>-312</v>
+      </c>
+      <c r="AD36" s="16" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="AE36" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF36" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG36" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH36" s="16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI36" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ36" s="16" t="n">
+        <v>54.76</v>
+      </c>
+      <c r="AK36" s="16" t="n">
+        <v>-366.76</v>
+      </c>
+      <c r="AL36" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM36" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN36" s="16" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA21"/>
+  <dimension ref="A1:AA22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2661,6 +2661,105 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>11:09 ET</t>
+        </is>
+      </c>
+      <c r="H22" s="17" t="n">
+        <v>30503.25</v>
+      </c>
+      <c r="I22" s="17" t="n">
+        <v>30500</v>
+      </c>
+      <c r="J22" s="17" t="n">
+        <v>30525</v>
+      </c>
+      <c r="K22" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L22" s="17" t="n">
+        <v>215.87</v>
+      </c>
+      <c r="M22" s="17" t="n">
+        <v>280.63</v>
+      </c>
+      <c r="N22" s="17" t="n">
+        <v>893.08</v>
+      </c>
+      <c r="O22" s="17" t="n">
+        <v>1136.52</v>
+      </c>
+      <c r="P22" s="17" t="n">
+        <v>259.04</v>
+      </c>
+      <c r="Q22" s="17" t="n">
+        <v>259.04</v>
+      </c>
+      <c r="R22" s="17" t="n">
+        <v>259.04</v>
+      </c>
+      <c r="S22" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T22" s="17" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="U22" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="V22" s="17" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W22" s="17" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="X22" s="17" t="n">
+        <v>229.44</v>
+      </c>
+      <c r="Y22" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z22" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -2675,7 +2774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN19"/>
+  <dimension ref="A1:AN20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5467,6 +5566,158 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H20" s="17" t="n">
+        <v>57509.03</v>
+      </c>
+      <c r="I20" s="17" t="n">
+        <v>56291.5</v>
+      </c>
+      <c r="J20" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L20" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="M20" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N20" s="17" t="inlineStr">
+        <is>
+          <t>10:58 IST</t>
+        </is>
+      </c>
+      <c r="O20" s="17" t="n">
+        <v>57727.35</v>
+      </c>
+      <c r="P20" s="17" t="n">
+        <v>58177.05</v>
+      </c>
+      <c r="Q20" s="17" t="inlineStr">
+        <is>
+          <t>57600 CE</t>
+        </is>
+      </c>
+      <c r="R20" s="17" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="S20" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U20" s="17" t="n">
+        <v>450</v>
+      </c>
+      <c r="V20" s="17" t="n">
+        <v>105.37</v>
+      </c>
+      <c r="W20" s="17" t="n">
+        <v>136.98</v>
+      </c>
+      <c r="X20" s="17" t="n">
+        <v>47416.5</v>
+      </c>
+      <c r="Y20" s="17" t="n">
+        <v>47471.16</v>
+      </c>
+      <c r="Z20" s="17" t="n">
+        <v>42583.5</v>
+      </c>
+      <c r="AA20" s="17" t="n">
+        <v>14224.95</v>
+      </c>
+      <c r="AB20" s="17" t="n">
+        <v>14224.95</v>
+      </c>
+      <c r="AC20" s="17" t="n">
+        <v>14224.5</v>
+      </c>
+      <c r="AD20" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE20" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF20" s="17" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="AG20" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH20" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI20" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ20" s="17" t="n">
+        <v>54.66</v>
+      </c>
+      <c r="AK20" s="17" t="n">
+        <v>14169.84</v>
+      </c>
+      <c r="AL20" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM20" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN20" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -5481,7 +5732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN19"/>
+  <dimension ref="A1:AN20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8273,6 +8524,158 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H20" s="17" t="n">
+        <v>57509.03</v>
+      </c>
+      <c r="I20" s="17" t="n">
+        <v>56291.5</v>
+      </c>
+      <c r="J20" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L20" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="M20" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N20" s="17" t="inlineStr">
+        <is>
+          <t>11:36 IST</t>
+        </is>
+      </c>
+      <c r="O20" s="17" t="n">
+        <v>57727.35</v>
+      </c>
+      <c r="P20" s="17" t="n">
+        <v>58177.05</v>
+      </c>
+      <c r="Q20" s="17" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="R20" s="17" t="inlineStr">
+        <is>
+          <t>57600 PE</t>
+        </is>
+      </c>
+      <c r="S20" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="T20" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U20" s="17" t="n">
+        <v>510</v>
+      </c>
+      <c r="V20" s="17" t="n">
+        <v>95.34</v>
+      </c>
+      <c r="W20" s="17" t="n">
+        <v>123.94</v>
+      </c>
+      <c r="X20" s="17" t="n">
+        <v>48623.4</v>
+      </c>
+      <c r="Y20" s="17" t="n">
+        <v>48678.25</v>
+      </c>
+      <c r="Z20" s="17" t="n">
+        <v>53376.6</v>
+      </c>
+      <c r="AA20" s="17" t="n">
+        <v>14587.02</v>
+      </c>
+      <c r="AB20" s="17" t="n">
+        <v>14587.02</v>
+      </c>
+      <c r="AC20" s="17" t="n">
+        <v>14586</v>
+      </c>
+      <c r="AD20" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE20" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF20" s="17" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="AG20" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH20" s="17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI20" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ20" s="17" t="n">
+        <v>54.85</v>
+      </c>
+      <c r="AK20" s="17" t="n">
+        <v>14531.15</v>
+      </c>
+      <c r="AL20" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM20" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN20" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -8287,7 +8690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN36"/>
+  <dimension ref="A1:AN38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13618,6 +14021,310 @@
         <v>50000</v>
       </c>
       <c r="AN36" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D37" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E37" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H37" s="17" t="n">
+        <v>57509.03</v>
+      </c>
+      <c r="I37" s="17" t="n">
+        <v>56291.5</v>
+      </c>
+      <c r="J37" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K37" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L37" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="M37" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N37" s="17" t="inlineStr">
+        <is>
+          <t>09:58 IST</t>
+        </is>
+      </c>
+      <c r="O37" s="17" t="n">
+        <v>57727.35</v>
+      </c>
+      <c r="P37" s="17" t="n">
+        <v>58177.05</v>
+      </c>
+      <c r="Q37" s="17" t="inlineStr">
+        <is>
+          <t>57600 CE</t>
+        </is>
+      </c>
+      <c r="R37" s="17" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="S37" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="T37" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U37" s="17" t="n">
+        <v>540</v>
+      </c>
+      <c r="V37" s="17" t="n">
+        <v>88.36</v>
+      </c>
+      <c r="W37" s="17" t="n">
+        <v>114.87</v>
+      </c>
+      <c r="X37" s="17" t="n">
+        <v>47714.4</v>
+      </c>
+      <c r="Y37" s="17" t="n">
+        <v>47769.11</v>
+      </c>
+      <c r="Z37" s="17" t="n">
+        <v>60285.6</v>
+      </c>
+      <c r="AA37" s="17" t="n">
+        <v>14314.32</v>
+      </c>
+      <c r="AB37" s="17" t="n">
+        <v>14314.32</v>
+      </c>
+      <c r="AC37" s="17" t="n">
+        <v>14315.4</v>
+      </c>
+      <c r="AD37" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE37" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF37" s="17" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="AG37" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH37" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI37" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ37" s="17" t="n">
+        <v>54.71</v>
+      </c>
+      <c r="AK37" s="17" t="n">
+        <v>14260.69</v>
+      </c>
+      <c r="AL37" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM37" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN37" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G38" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H38" s="16" t="n">
+        <v>57509.03</v>
+      </c>
+      <c r="I38" s="16" t="n">
+        <v>56291.5</v>
+      </c>
+      <c r="J38" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K38" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L38" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="M38" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N38" s="16" t="inlineStr">
+        <is>
+          <t>13:58 IST</t>
+        </is>
+      </c>
+      <c r="O38" s="16" t="n">
+        <v>57727.35</v>
+      </c>
+      <c r="P38" s="16" t="n">
+        <v>58177.05</v>
+      </c>
+      <c r="Q38" s="16" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="R38" s="16" t="inlineStr">
+        <is>
+          <t>57600 PE</t>
+        </is>
+      </c>
+      <c r="S38" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="T38" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U38" s="16" t="n">
+        <v>480</v>
+      </c>
+      <c r="V38" s="16" t="n">
+        <v>99.93000000000001</v>
+      </c>
+      <c r="W38" s="16" t="n">
+        <v>104.91</v>
+      </c>
+      <c r="X38" s="16" t="n">
+        <v>47966.4</v>
+      </c>
+      <c r="Y38" s="16" t="n">
+        <v>48021.15</v>
+      </c>
+      <c r="Z38" s="16" t="n">
+        <v>48033.6</v>
+      </c>
+      <c r="AA38" s="16" t="n">
+        <v>14389.92</v>
+      </c>
+      <c r="AB38" s="16" t="n">
+        <v>14389.92</v>
+      </c>
+      <c r="AC38" s="16" t="n">
+        <v>2390.4</v>
+      </c>
+      <c r="AD38" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE38" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF38" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG38" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH38" s="16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI38" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ38" s="16" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="AK38" s="16" t="n">
+        <v>2335.65</v>
+      </c>
+      <c r="AL38" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM38" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN38" s="16" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -15399,7 +16106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15945,6 +16652,72 @@
         <v>56405.26</v>
       </c>
       <c r="G17" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>23935.21</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>23780.09</v>
+      </c>
+      <c r="G18" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>57509.03</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>56291.5</v>
+      </c>
+      <c r="G19" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -15964,7 +16737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA21"/>
+  <dimension ref="A1:AA22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18016,6 +18789,105 @@
         <v>1000</v>
       </c>
       <c r="AA21" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>12:12 ET</t>
+        </is>
+      </c>
+      <c r="H22" s="17" t="n">
+        <v>30503.5</v>
+      </c>
+      <c r="I22" s="17" t="n">
+        <v>30500</v>
+      </c>
+      <c r="J22" s="17" t="n">
+        <v>30525</v>
+      </c>
+      <c r="K22" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="L22" s="17" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="M22" s="17" t="n">
+        <v>26.99</v>
+      </c>
+      <c r="N22" s="17" t="n">
+        <v>985.6</v>
+      </c>
+      <c r="O22" s="17" t="n">
+        <v>1286.56</v>
+      </c>
+      <c r="P22" s="17" t="n">
+        <v>274.03</v>
+      </c>
+      <c r="Q22" s="17" t="n">
+        <v>274.03</v>
+      </c>
+      <c r="R22" s="17" t="n">
+        <v>274.12</v>
+      </c>
+      <c r="S22" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T22" s="17" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="U22" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="V22" s="17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="W22" s="17" t="n">
+        <v>72.16</v>
+      </c>
+      <c r="X22" s="17" t="n">
+        <v>201.96</v>
+      </c>
+      <c r="Y22" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z22" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -18135,7 +19007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19528,6 +20400,76 @@
         <v>62.32</v>
       </c>
       <c r="I40" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C41" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" s="19" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="E41" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F41" s="19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G41" s="19" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H41" s="19" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I41" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="n">
+        <v>44</v>
+      </c>
+      <c r="D42" s="19" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E42" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="F42" s="19" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G42" s="19" t="n">
+        <v>36.08</v>
+      </c>
+      <c r="H42" s="19" t="n">
+        <v>72.16</v>
+      </c>
+      <c r="I42" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — PROFIT</t>
         </is>
@@ -19996,7 +20938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN19"/>
+  <dimension ref="A1:AN20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22788,6 +23730,158 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H20" s="17" t="n">
+        <v>23935.21</v>
+      </c>
+      <c r="I20" s="17" t="n">
+        <v>23780.09</v>
+      </c>
+      <c r="J20" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L20" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N20" s="17" t="inlineStr">
+        <is>
+          <t>09:56 IST</t>
+        </is>
+      </c>
+      <c r="O20" s="17" t="n">
+        <v>23946.25</v>
+      </c>
+      <c r="P20" s="17" t="n">
+        <v>24056</v>
+      </c>
+      <c r="Q20" s="17" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="R20" s="17" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="S20" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="T20" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U20" s="17" t="n">
+        <v>3120</v>
+      </c>
+      <c r="V20" s="17" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="W20" s="17" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="X20" s="17" t="n">
+        <v>47330.4</v>
+      </c>
+      <c r="Y20" s="17" t="n">
+        <v>47385.05</v>
+      </c>
+      <c r="Z20" s="17" t="n">
+        <v>264669.6</v>
+      </c>
+      <c r="AA20" s="17" t="n">
+        <v>14199.12</v>
+      </c>
+      <c r="AB20" s="17" t="n">
+        <v>14199.12</v>
+      </c>
+      <c r="AC20" s="17" t="n">
+        <v>14196</v>
+      </c>
+      <c r="AD20" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE20" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF20" s="17" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="AG20" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH20" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI20" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ20" s="17" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="AK20" s="17" t="n">
+        <v>14141.35</v>
+      </c>
+      <c r="AL20" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM20" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN20" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -22802,7 +23896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN19"/>
+  <dimension ref="A1:AN20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -25594,6 +26688,158 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H20" s="17" t="n">
+        <v>23935.21</v>
+      </c>
+      <c r="I20" s="17" t="n">
+        <v>23780.09</v>
+      </c>
+      <c r="J20" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L20" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N20" s="17" t="inlineStr">
+        <is>
+          <t>12:16 IST</t>
+        </is>
+      </c>
+      <c r="O20" s="17" t="n">
+        <v>23946.25</v>
+      </c>
+      <c r="P20" s="17" t="n">
+        <v>24056</v>
+      </c>
+      <c r="Q20" s="17" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="R20" s="17" t="inlineStr">
+        <is>
+          <t>23900 PE</t>
+        </is>
+      </c>
+      <c r="S20" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="T20" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U20" s="17" t="n">
+        <v>2015</v>
+      </c>
+      <c r="V20" s="17" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="W20" s="17" t="n">
+        <v>31.07</v>
+      </c>
+      <c r="X20" s="17" t="n">
+        <v>48158.5</v>
+      </c>
+      <c r="Y20" s="17" t="n">
+        <v>48213.28</v>
+      </c>
+      <c r="Z20" s="17" t="n">
+        <v>153341.5</v>
+      </c>
+      <c r="AA20" s="17" t="n">
+        <v>14447.55</v>
+      </c>
+      <c r="AB20" s="17" t="n">
+        <v>14447.55</v>
+      </c>
+      <c r="AC20" s="17" t="n">
+        <v>14447.55</v>
+      </c>
+      <c r="AD20" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE20" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF20" s="17" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="AG20" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH20" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI20" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ20" s="17" t="n">
+        <v>54.78</v>
+      </c>
+      <c r="AK20" s="17" t="n">
+        <v>14392.77</v>
+      </c>
+      <c r="AL20" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM20" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN20" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -25608,7 +26854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN36"/>
+  <dimension ref="A1:AN38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -30939,6 +32185,310 @@
         <v>50000</v>
       </c>
       <c r="AN36" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G37" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H37" s="15" t="n">
+        <v>23935.21</v>
+      </c>
+      <c r="I37" s="15" t="n">
+        <v>23780.09</v>
+      </c>
+      <c r="J37" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K37" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L37" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M37" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N37" s="15" t="inlineStr">
+        <is>
+          <t>09:57 IST</t>
+        </is>
+      </c>
+      <c r="O37" s="15" t="n">
+        <v>23946.25</v>
+      </c>
+      <c r="P37" s="15" t="n">
+        <v>24056</v>
+      </c>
+      <c r="Q37" s="15" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="R37" s="15" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="S37" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="T37" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U37" s="15" t="n">
+        <v>2600</v>
+      </c>
+      <c r="V37" s="15" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="W37" s="15" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="X37" s="15" t="n">
+        <v>48178</v>
+      </c>
+      <c r="Y37" s="15" t="n">
+        <v>48232.78</v>
+      </c>
+      <c r="Z37" s="15" t="n">
+        <v>211822</v>
+      </c>
+      <c r="AA37" s="15" t="n">
+        <v>14453.4</v>
+      </c>
+      <c r="AB37" s="15" t="n">
+        <v>14453.4</v>
+      </c>
+      <c r="AC37" s="15" t="n">
+        <v>-14456</v>
+      </c>
+      <c r="AD37" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE37" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF37" s="15" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="AG37" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH37" s="15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI37" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ37" s="15" t="n">
+        <v>54.78</v>
+      </c>
+      <c r="AK37" s="15" t="n">
+        <v>-14510.78</v>
+      </c>
+      <c r="AL37" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM37" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN37" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G38" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H38" s="17" t="n">
+        <v>23935.21</v>
+      </c>
+      <c r="I38" s="17" t="n">
+        <v>23780.09</v>
+      </c>
+      <c r="J38" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K38" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L38" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M38" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N38" s="17" t="inlineStr">
+        <is>
+          <t>09:57 IST</t>
+        </is>
+      </c>
+      <c r="O38" s="17" t="n">
+        <v>23946.25</v>
+      </c>
+      <c r="P38" s="17" t="n">
+        <v>24056</v>
+      </c>
+      <c r="Q38" s="17" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="R38" s="17" t="inlineStr">
+        <is>
+          <t>23900 PE</t>
+        </is>
+      </c>
+      <c r="S38" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="T38" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U38" s="17" t="n">
+        <v>3120</v>
+      </c>
+      <c r="V38" s="17" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="W38" s="17" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="X38" s="17" t="n">
+        <v>48016.8</v>
+      </c>
+      <c r="Y38" s="17" t="n">
+        <v>48071.56</v>
+      </c>
+      <c r="Z38" s="17" t="n">
+        <v>263983.2</v>
+      </c>
+      <c r="AA38" s="17" t="n">
+        <v>14405.04</v>
+      </c>
+      <c r="AB38" s="17" t="n">
+        <v>14405.04</v>
+      </c>
+      <c r="AC38" s="17" t="n">
+        <v>14414.4</v>
+      </c>
+      <c r="AD38" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE38" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF38" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG38" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH38" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI38" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ38" s="17" t="n">
+        <v>54.76</v>
+      </c>
+      <c r="AK38" s="17" t="n">
+        <v>14359.64</v>
+      </c>
+      <c r="AL38" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM38" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN38" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA23"/>
+  <dimension ref="A1:AA24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2859,6 +2859,105 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="inlineStr">
+        <is>
+          <t>12:12 ET</t>
+        </is>
+      </c>
+      <c r="H24" s="17" t="n">
+        <v>30035.25</v>
+      </c>
+      <c r="I24" s="17" t="n">
+        <v>30025</v>
+      </c>
+      <c r="J24" s="17" t="n">
+        <v>30050</v>
+      </c>
+      <c r="K24" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L24" s="17" t="n">
+        <v>270.94</v>
+      </c>
+      <c r="M24" s="17" t="n">
+        <v>352.22</v>
+      </c>
+      <c r="N24" s="17" t="n">
+        <v>835.02</v>
+      </c>
+      <c r="O24" s="17" t="n">
+        <v>687.1799999999999</v>
+      </c>
+      <c r="P24" s="17" t="n">
+        <v>243.85</v>
+      </c>
+      <c r="Q24" s="17" t="n">
+        <v>243.85</v>
+      </c>
+      <c r="R24" s="17" t="n">
+        <v>243.84</v>
+      </c>
+      <c r="S24" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T24" s="17" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="U24" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="V24" s="17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W24" s="17" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="X24" s="17" t="n">
+        <v>221.64</v>
+      </c>
+      <c r="Y24" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z24" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -2873,7 +2972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN21"/>
+  <dimension ref="A1:AN22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5969,6 +6068,158 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H22" s="17" t="n">
+        <v>57517.14</v>
+      </c>
+      <c r="I22" s="17" t="n">
+        <v>56383.85</v>
+      </c>
+      <c r="J22" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K22" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L22" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="M22" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N22" s="17" t="inlineStr">
+        <is>
+          <t>11:17 IST</t>
+        </is>
+      </c>
+      <c r="O22" s="17" t="n">
+        <v>57542.9</v>
+      </c>
+      <c r="P22" s="17" t="n">
+        <v>57727.35</v>
+      </c>
+      <c r="Q22" s="17" t="inlineStr">
+        <is>
+          <t>57400 CE</t>
+        </is>
+      </c>
+      <c r="R22" s="17" t="inlineStr">
+        <is>
+          <t>57600 CE</t>
+        </is>
+      </c>
+      <c r="S22" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="T22" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U22" s="17" t="n">
+        <v>480</v>
+      </c>
+      <c r="V22" s="17" t="n">
+        <v>99.29000000000001</v>
+      </c>
+      <c r="W22" s="17" t="n">
+        <v>129.08</v>
+      </c>
+      <c r="X22" s="17" t="n">
+        <v>47659.2</v>
+      </c>
+      <c r="Y22" s="17" t="n">
+        <v>47713.9</v>
+      </c>
+      <c r="Z22" s="17" t="n">
+        <v>48340.8</v>
+      </c>
+      <c r="AA22" s="17" t="n">
+        <v>14297.76</v>
+      </c>
+      <c r="AB22" s="17" t="n">
+        <v>14297.76</v>
+      </c>
+      <c r="AC22" s="17" t="n">
+        <v>14299.2</v>
+      </c>
+      <c r="AD22" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE22" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF22" s="17" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="AG22" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH22" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI22" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ22" s="17" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="AK22" s="17" t="n">
+        <v>14244.5</v>
+      </c>
+      <c r="AL22" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM22" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN22" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -5983,7 +6234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN21"/>
+  <dimension ref="A1:AN22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9079,6 +9330,158 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H22" s="17" t="n">
+        <v>57517.14</v>
+      </c>
+      <c r="I22" s="17" t="n">
+        <v>56383.85</v>
+      </c>
+      <c r="J22" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K22" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L22" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="M22" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N22" s="17" t="inlineStr">
+        <is>
+          <t>11:39 IST</t>
+        </is>
+      </c>
+      <c r="O22" s="17" t="n">
+        <v>57542.9</v>
+      </c>
+      <c r="P22" s="17" t="n">
+        <v>57727.35</v>
+      </c>
+      <c r="Q22" s="17" t="inlineStr">
+        <is>
+          <t>57600 PE</t>
+        </is>
+      </c>
+      <c r="R22" s="17" t="inlineStr">
+        <is>
+          <t>57400 PE</t>
+        </is>
+      </c>
+      <c r="S22" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="T22" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U22" s="17" t="n">
+        <v>540</v>
+      </c>
+      <c r="V22" s="17" t="n">
+        <v>86.94</v>
+      </c>
+      <c r="W22" s="17" t="n">
+        <v>113.02</v>
+      </c>
+      <c r="X22" s="17" t="n">
+        <v>46947.6</v>
+      </c>
+      <c r="Y22" s="17" t="n">
+        <v>47002.19</v>
+      </c>
+      <c r="Z22" s="17" t="n">
+        <v>61052.4</v>
+      </c>
+      <c r="AA22" s="17" t="n">
+        <v>14084.28</v>
+      </c>
+      <c r="AB22" s="17" t="n">
+        <v>14084.28</v>
+      </c>
+      <c r="AC22" s="17" t="n">
+        <v>14083.2</v>
+      </c>
+      <c r="AD22" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE22" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF22" s="17" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="AG22" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH22" s="17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI22" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ22" s="17" t="n">
+        <v>54.59</v>
+      </c>
+      <c r="AK22" s="17" t="n">
+        <v>14028.61</v>
+      </c>
+      <c r="AL22" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM22" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN22" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -9093,7 +9496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN40"/>
+  <dimension ref="A1:AN42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15032,6 +15435,310 @@
         <v>50000</v>
       </c>
       <c r="AN40" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E41" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F41" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G41" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H41" s="17" t="n">
+        <v>57517.14</v>
+      </c>
+      <c r="I41" s="17" t="n">
+        <v>56383.85</v>
+      </c>
+      <c r="J41" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K41" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L41" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="M41" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N41" s="17" t="inlineStr">
+        <is>
+          <t>11:42 IST</t>
+        </is>
+      </c>
+      <c r="O41" s="17" t="n">
+        <v>57542.9</v>
+      </c>
+      <c r="P41" s="17" t="n">
+        <v>57727.35</v>
+      </c>
+      <c r="Q41" s="17" t="inlineStr">
+        <is>
+          <t>57400 CE</t>
+        </is>
+      </c>
+      <c r="R41" s="17" t="inlineStr">
+        <is>
+          <t>57600 CE</t>
+        </is>
+      </c>
+      <c r="S41" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="T41" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U41" s="17" t="n">
+        <v>570</v>
+      </c>
+      <c r="V41" s="17" t="n">
+        <v>83.75</v>
+      </c>
+      <c r="W41" s="17" t="n">
+        <v>108.88</v>
+      </c>
+      <c r="X41" s="17" t="n">
+        <v>47737.5</v>
+      </c>
+      <c r="Y41" s="17" t="n">
+        <v>47792.21</v>
+      </c>
+      <c r="Z41" s="17" t="n">
+        <v>66262.5</v>
+      </c>
+      <c r="AA41" s="17" t="n">
+        <v>14321.25</v>
+      </c>
+      <c r="AB41" s="17" t="n">
+        <v>14321.25</v>
+      </c>
+      <c r="AC41" s="17" t="n">
+        <v>14324.1</v>
+      </c>
+      <c r="AD41" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE41" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF41" s="17" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="AG41" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH41" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI41" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ41" s="17" t="n">
+        <v>54.71</v>
+      </c>
+      <c r="AK41" s="17" t="n">
+        <v>14269.39</v>
+      </c>
+      <c r="AL41" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM41" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN41" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H42" s="17" t="n">
+        <v>57517.14</v>
+      </c>
+      <c r="I42" s="17" t="n">
+        <v>56383.85</v>
+      </c>
+      <c r="J42" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K42" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L42" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="M42" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N42" s="17" t="inlineStr">
+        <is>
+          <t>12:11 IST</t>
+        </is>
+      </c>
+      <c r="O42" s="17" t="n">
+        <v>57542.9</v>
+      </c>
+      <c r="P42" s="17" t="n">
+        <v>57727.35</v>
+      </c>
+      <c r="Q42" s="17" t="inlineStr">
+        <is>
+          <t>57600 PE</t>
+        </is>
+      </c>
+      <c r="R42" s="17" t="inlineStr">
+        <is>
+          <t>57400 PE</t>
+        </is>
+      </c>
+      <c r="S42" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U42" s="17" t="n">
+        <v>450</v>
+      </c>
+      <c r="V42" s="17" t="n">
+        <v>108.57</v>
+      </c>
+      <c r="W42" s="17" t="n">
+        <v>141.14</v>
+      </c>
+      <c r="X42" s="17" t="n">
+        <v>48856.5</v>
+      </c>
+      <c r="Y42" s="17" t="n">
+        <v>48911.39</v>
+      </c>
+      <c r="Z42" s="17" t="n">
+        <v>41143.5</v>
+      </c>
+      <c r="AA42" s="17" t="n">
+        <v>14656.95</v>
+      </c>
+      <c r="AB42" s="17" t="n">
+        <v>14656.95</v>
+      </c>
+      <c r="AC42" s="17" t="n">
+        <v>14656.5</v>
+      </c>
+      <c r="AD42" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE42" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF42" s="17" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="AG42" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH42" s="17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI42" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ42" s="17" t="n">
+        <v>54.89</v>
+      </c>
+      <c r="AK42" s="17" t="n">
+        <v>14601.61</v>
+      </c>
+      <c r="AL42" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM42" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN42" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -16965,7 +17672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17577,6 +18284,72 @@
         <v>56291.5</v>
       </c>
       <c r="G19" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>23921.87</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>23777.05</v>
+      </c>
+      <c r="G20" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>57517.14</v>
+      </c>
+      <c r="F21" s="18" t="n">
+        <v>56383.85</v>
+      </c>
+      <c r="G21" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -17596,7 +18369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA23"/>
+  <dimension ref="A1:AA24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19846,6 +20619,105 @@
         <v>1000</v>
       </c>
       <c r="AA23" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G24" s="16" t="inlineStr">
+        <is>
+          <t>15:33 ET</t>
+        </is>
+      </c>
+      <c r="H24" s="16" t="n">
+        <v>30037</v>
+      </c>
+      <c r="I24" s="16" t="n">
+        <v>30025</v>
+      </c>
+      <c r="J24" s="16" t="n">
+        <v>30050</v>
+      </c>
+      <c r="K24" s="16" t="n">
+        <v>36</v>
+      </c>
+      <c r="L24" s="16" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="M24" s="16" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="N24" s="16" t="n">
+        <v>985.3200000000001</v>
+      </c>
+      <c r="O24" s="16" t="n">
+        <v>873.72</v>
+      </c>
+      <c r="P24" s="16" t="n">
+        <v>277.88</v>
+      </c>
+      <c r="Q24" s="16" t="n">
+        <v>277.88</v>
+      </c>
+      <c r="R24" s="16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S24" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T24" s="16" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="U24" s="16" t="n">
+        <v>36</v>
+      </c>
+      <c r="V24" s="16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W24" s="16" t="n">
+        <v>59.04</v>
+      </c>
+      <c r="X24" s="16" t="n">
+        <v>-57.24</v>
+      </c>
+      <c r="Y24" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="Z24" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" s="16" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -19965,7 +20837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21500,6 +22372,76 @@
       <c r="I44" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" s="19" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="E45" s="19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F45" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G45" s="19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H45" s="19" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="I45" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B46" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C46" s="19" t="n">
+        <v>36</v>
+      </c>
+      <c r="D46" s="19" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="E46" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="F46" s="19" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G46" s="19" t="n">
+        <v>29.52</v>
+      </c>
+      <c r="H46" s="19" t="n">
+        <v>59.04</v>
+      </c>
+      <c r="I46" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — FLAT</t>
         </is>
       </c>
     </row>
@@ -21966,7 +22908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN21"/>
+  <dimension ref="A1:AN22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -25062,6 +26004,158 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H22" s="17" t="n">
+        <v>23921.87</v>
+      </c>
+      <c r="I22" s="17" t="n">
+        <v>23777.05</v>
+      </c>
+      <c r="J22" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K22" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L22" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N22" s="17" t="inlineStr">
+        <is>
+          <t>12:06 IST</t>
+        </is>
+      </c>
+      <c r="O22" s="17" t="n">
+        <v>23865.75</v>
+      </c>
+      <c r="P22" s="17" t="n">
+        <v>23946.25</v>
+      </c>
+      <c r="Q22" s="17" t="inlineStr">
+        <is>
+          <t>23800 CE</t>
+        </is>
+      </c>
+      <c r="R22" s="17" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="S22" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="T22" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U22" s="17" t="n">
+        <v>2990</v>
+      </c>
+      <c r="V22" s="17" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="W22" s="17" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="X22" s="17" t="n">
+        <v>47212.1</v>
+      </c>
+      <c r="Y22" s="17" t="n">
+        <v>47266.73</v>
+      </c>
+      <c r="Z22" s="17" t="n">
+        <v>251787.9</v>
+      </c>
+      <c r="AA22" s="17" t="n">
+        <v>14163.63</v>
+      </c>
+      <c r="AB22" s="17" t="n">
+        <v>14163.63</v>
+      </c>
+      <c r="AC22" s="17" t="n">
+        <v>14172.6</v>
+      </c>
+      <c r="AD22" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE22" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF22" s="17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AG22" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH22" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI22" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ22" s="17" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="AK22" s="17" t="n">
+        <v>14117.97</v>
+      </c>
+      <c r="AL22" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM22" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN22" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -25076,7 +26170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN21"/>
+  <dimension ref="A1:AN22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -28172,6 +29266,158 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H22" s="17" t="n">
+        <v>23921.87</v>
+      </c>
+      <c r="I22" s="17" t="n">
+        <v>23777.05</v>
+      </c>
+      <c r="J22" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K22" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L22" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N22" s="17" t="inlineStr">
+        <is>
+          <t>10:53 IST</t>
+        </is>
+      </c>
+      <c r="O22" s="17" t="n">
+        <v>23865.75</v>
+      </c>
+      <c r="P22" s="17" t="n">
+        <v>23946.25</v>
+      </c>
+      <c r="Q22" s="17" t="inlineStr">
+        <is>
+          <t>23900 PE</t>
+        </is>
+      </c>
+      <c r="R22" s="17" t="inlineStr">
+        <is>
+          <t>23800 PE</t>
+        </is>
+      </c>
+      <c r="S22" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="T22" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U22" s="17" t="n">
+        <v>2080</v>
+      </c>
+      <c r="V22" s="17" t="n">
+        <v>23.18</v>
+      </c>
+      <c r="W22" s="17" t="n">
+        <v>30.13</v>
+      </c>
+      <c r="X22" s="17" t="n">
+        <v>48214.4</v>
+      </c>
+      <c r="Y22" s="17" t="n">
+        <v>48269.19</v>
+      </c>
+      <c r="Z22" s="17" t="n">
+        <v>159785.6</v>
+      </c>
+      <c r="AA22" s="17" t="n">
+        <v>14464.32</v>
+      </c>
+      <c r="AB22" s="17" t="n">
+        <v>14464.32</v>
+      </c>
+      <c r="AC22" s="17" t="n">
+        <v>14456</v>
+      </c>
+      <c r="AD22" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE22" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF22" s="17" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AG22" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH22" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI22" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ22" s="17" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="AK22" s="17" t="n">
+        <v>14401.21</v>
+      </c>
+      <c r="AL22" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM22" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN22" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -28186,7 +29432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN40"/>
+  <dimension ref="A1:AN42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -34125,6 +35371,310 @@
         <v>50000</v>
       </c>
       <c r="AN40" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F41" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G41" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="n">
+        <v>23921.87</v>
+      </c>
+      <c r="I41" s="15" t="n">
+        <v>23777.05</v>
+      </c>
+      <c r="J41" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K41" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L41" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N41" s="15" t="inlineStr">
+        <is>
+          <t>09:52 IST</t>
+        </is>
+      </c>
+      <c r="O41" s="15" t="n">
+        <v>23865.75</v>
+      </c>
+      <c r="P41" s="15" t="n">
+        <v>23946.25</v>
+      </c>
+      <c r="Q41" s="15" t="inlineStr">
+        <is>
+          <t>23800 CE</t>
+        </is>
+      </c>
+      <c r="R41" s="15" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="S41" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="T41" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U41" s="15" t="n">
+        <v>1950</v>
+      </c>
+      <c r="V41" s="15" t="n">
+        <v>24.74</v>
+      </c>
+      <c r="W41" s="15" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="X41" s="15" t="n">
+        <v>48243</v>
+      </c>
+      <c r="Y41" s="15" t="n">
+        <v>48297.79</v>
+      </c>
+      <c r="Z41" s="15" t="n">
+        <v>146757</v>
+      </c>
+      <c r="AA41" s="15" t="n">
+        <v>14472.9</v>
+      </c>
+      <c r="AB41" s="15" t="n">
+        <v>14472.9</v>
+      </c>
+      <c r="AC41" s="15" t="n">
+        <v>-14469</v>
+      </c>
+      <c r="AD41" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE41" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF41" s="15" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AG41" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH41" s="15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI41" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ41" s="15" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="AK41" s="15" t="n">
+        <v>-14523.79</v>
+      </c>
+      <c r="AL41" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM41" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN41" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G42" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H42" s="15" t="n">
+        <v>23921.87</v>
+      </c>
+      <c r="I42" s="15" t="n">
+        <v>23777.05</v>
+      </c>
+      <c r="J42" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K42" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L42" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N42" s="15" t="inlineStr">
+        <is>
+          <t>09:56 IST</t>
+        </is>
+      </c>
+      <c r="O42" s="15" t="n">
+        <v>23865.75</v>
+      </c>
+      <c r="P42" s="15" t="n">
+        <v>23946.25</v>
+      </c>
+      <c r="Q42" s="15" t="inlineStr">
+        <is>
+          <t>23900 PE</t>
+        </is>
+      </c>
+      <c r="R42" s="15" t="inlineStr">
+        <is>
+          <t>23800 PE</t>
+        </is>
+      </c>
+      <c r="S42" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="T42" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U42" s="15" t="n">
+        <v>2405</v>
+      </c>
+      <c r="V42" s="15" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="W42" s="15" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="X42" s="15" t="n">
+        <v>47907.6</v>
+      </c>
+      <c r="Y42" s="15" t="n">
+        <v>47962.34</v>
+      </c>
+      <c r="Z42" s="15" t="n">
+        <v>192592.4</v>
+      </c>
+      <c r="AA42" s="15" t="n">
+        <v>14372.28</v>
+      </c>
+      <c r="AB42" s="15" t="n">
+        <v>14372.28</v>
+      </c>
+      <c r="AC42" s="15" t="n">
+        <v>-14381.9</v>
+      </c>
+      <c r="AD42" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE42" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF42" s="15" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="AG42" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH42" s="15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI42" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ42" s="15" t="n">
+        <v>54.74</v>
+      </c>
+      <c r="AK42" s="15" t="n">
+        <v>-14436.64</v>
+      </c>
+      <c r="AL42" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM42" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN42" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA24"/>
+  <dimension ref="A1:AA25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2958,6 +2958,105 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>11:06 ET</t>
+        </is>
+      </c>
+      <c r="H25" s="17" t="n">
+        <v>30066</v>
+      </c>
+      <c r="I25" s="17" t="n">
+        <v>30050</v>
+      </c>
+      <c r="J25" s="17" t="n">
+        <v>30075</v>
+      </c>
+      <c r="K25" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L25" s="17" t="n">
+        <v>224.56</v>
+      </c>
+      <c r="M25" s="17" t="n">
+        <v>291.93</v>
+      </c>
+      <c r="N25" s="17" t="n">
+        <v>927.84</v>
+      </c>
+      <c r="O25" s="17" t="n">
+        <v>1101.76</v>
+      </c>
+      <c r="P25" s="17" t="n">
+        <v>269.47</v>
+      </c>
+      <c r="Q25" s="17" t="n">
+        <v>269.47</v>
+      </c>
+      <c r="R25" s="17" t="n">
+        <v>269.48</v>
+      </c>
+      <c r="S25" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T25" s="17" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="U25" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="V25" s="17" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W25" s="17" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="X25" s="17" t="n">
+        <v>239.88</v>
+      </c>
+      <c r="Y25" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z25" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -2972,7 +3071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN22"/>
+  <dimension ref="A1:AN23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6220,6 +6319,158 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H23" s="17" t="n">
+        <v>57703.9</v>
+      </c>
+      <c r="I23" s="17" t="n">
+        <v>56657.09</v>
+      </c>
+      <c r="J23" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K23" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L23" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="M23" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N23" s="17" t="inlineStr">
+        <is>
+          <t>11:55 IST</t>
+        </is>
+      </c>
+      <c r="O23" s="17" t="n">
+        <v>58031.65</v>
+      </c>
+      <c r="P23" s="17" t="n">
+        <v>58033.05</v>
+      </c>
+      <c r="Q23" s="17" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="R23" s="17" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="S23" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="T23" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U23" s="17" t="n">
+        <v>480</v>
+      </c>
+      <c r="V23" s="17" t="n">
+        <v>98.04000000000001</v>
+      </c>
+      <c r="W23" s="17" t="n">
+        <v>127.45</v>
+      </c>
+      <c r="X23" s="17" t="n">
+        <v>47059.2</v>
+      </c>
+      <c r="Y23" s="17" t="n">
+        <v>47113.81</v>
+      </c>
+      <c r="Z23" s="17" t="n">
+        <v>48940.8</v>
+      </c>
+      <c r="AA23" s="17" t="n">
+        <v>14117.76</v>
+      </c>
+      <c r="AB23" s="17" t="n">
+        <v>14117.76</v>
+      </c>
+      <c r="AC23" s="17" t="n">
+        <v>14116.8</v>
+      </c>
+      <c r="AD23" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE23" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF23" s="17" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="AG23" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH23" s="17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI23" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ23" s="17" t="n">
+        <v>54.61</v>
+      </c>
+      <c r="AK23" s="17" t="n">
+        <v>14062.19</v>
+      </c>
+      <c r="AL23" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM23" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN23" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -6234,7 +6485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN22"/>
+  <dimension ref="A1:AN23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9482,6 +9733,158 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G23" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H23" s="16" t="n">
+        <v>57703.9</v>
+      </c>
+      <c r="I23" s="16" t="n">
+        <v>56657.09</v>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K23" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L23" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="M23" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N23" s="16" t="inlineStr">
+        <is>
+          <t>14:14 IST</t>
+        </is>
+      </c>
+      <c r="O23" s="16" t="n">
+        <v>58031.65</v>
+      </c>
+      <c r="P23" s="16" t="n">
+        <v>58033.05</v>
+      </c>
+      <c r="Q23" s="16" t="inlineStr">
+        <is>
+          <t>58200 PE</t>
+        </is>
+      </c>
+      <c r="R23" s="16" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="S23" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="T23" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U23" s="16" t="n">
+        <v>540</v>
+      </c>
+      <c r="V23" s="16" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="W23" s="16" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="X23" s="16" t="n">
+        <v>48222</v>
+      </c>
+      <c r="Y23" s="16" t="n">
+        <v>48276.79</v>
+      </c>
+      <c r="Z23" s="16" t="n">
+        <v>59778</v>
+      </c>
+      <c r="AA23" s="16" t="n">
+        <v>14466.6</v>
+      </c>
+      <c r="AB23" s="16" t="n">
+        <v>14466.6</v>
+      </c>
+      <c r="AC23" s="16" t="n">
+        <v>-864</v>
+      </c>
+      <c r="AD23" s="16" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="AE23" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF23" s="16" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AG23" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH23" s="16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI23" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ23" s="16" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="AK23" s="16" t="n">
+        <v>-918.79</v>
+      </c>
+      <c r="AL23" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM23" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN23" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -9496,7 +9899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN42"/>
+  <dimension ref="A1:AN44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15739,6 +16142,310 @@
         <v>50000</v>
       </c>
       <c r="AN42" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E43" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F43" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G43" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H43" s="17" t="n">
+        <v>57703.9</v>
+      </c>
+      <c r="I43" s="17" t="n">
+        <v>56657.09</v>
+      </c>
+      <c r="J43" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K43" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L43" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="M43" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N43" s="17" t="inlineStr">
+        <is>
+          <t>11:17 IST</t>
+        </is>
+      </c>
+      <c r="O43" s="17" t="n">
+        <v>58031.65</v>
+      </c>
+      <c r="P43" s="17" t="n">
+        <v>58033.05</v>
+      </c>
+      <c r="Q43" s="17" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="R43" s="17" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="S43" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="T43" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U43" s="17" t="n">
+        <v>510</v>
+      </c>
+      <c r="V43" s="17" t="n">
+        <v>96.17</v>
+      </c>
+      <c r="W43" s="17" t="n">
+        <v>125.02</v>
+      </c>
+      <c r="X43" s="17" t="n">
+        <v>49046.7</v>
+      </c>
+      <c r="Y43" s="17" t="n">
+        <v>49101.62</v>
+      </c>
+      <c r="Z43" s="17" t="n">
+        <v>52953.3</v>
+      </c>
+      <c r="AA43" s="17" t="n">
+        <v>14714.01</v>
+      </c>
+      <c r="AB43" s="17" t="n">
+        <v>14714.01</v>
+      </c>
+      <c r="AC43" s="17" t="n">
+        <v>14713.5</v>
+      </c>
+      <c r="AD43" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE43" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF43" s="17" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="AG43" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH43" s="17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI43" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ43" s="17" t="n">
+        <v>54.92</v>
+      </c>
+      <c r="AK43" s="17" t="n">
+        <v>14658.58</v>
+      </c>
+      <c r="AL43" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM43" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN43" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E44" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F44" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G44" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H44" s="16" t="n">
+        <v>57703.9</v>
+      </c>
+      <c r="I44" s="16" t="n">
+        <v>56657.09</v>
+      </c>
+      <c r="J44" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K44" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L44" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="M44" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N44" s="16" t="inlineStr">
+        <is>
+          <t>14:30 IST</t>
+        </is>
+      </c>
+      <c r="O44" s="16" t="n">
+        <v>58031.65</v>
+      </c>
+      <c r="P44" s="16" t="n">
+        <v>58033.05</v>
+      </c>
+      <c r="Q44" s="16" t="inlineStr">
+        <is>
+          <t>58200 PE</t>
+        </is>
+      </c>
+      <c r="R44" s="16" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="S44" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U44" s="16" t="n">
+        <v>450</v>
+      </c>
+      <c r="V44" s="16" t="n">
+        <v>109.32</v>
+      </c>
+      <c r="W44" s="16" t="n">
+        <v>114.17</v>
+      </c>
+      <c r="X44" s="16" t="n">
+        <v>49194</v>
+      </c>
+      <c r="Y44" s="16" t="n">
+        <v>49248.94</v>
+      </c>
+      <c r="Z44" s="16" t="n">
+        <v>40806</v>
+      </c>
+      <c r="AA44" s="16" t="n">
+        <v>14758.2</v>
+      </c>
+      <c r="AB44" s="16" t="n">
+        <v>14758.2</v>
+      </c>
+      <c r="AC44" s="16" t="n">
+        <v>2182.5</v>
+      </c>
+      <c r="AD44" s="16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE44" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF44" s="16" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AG44" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH44" s="16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI44" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ44" s="16" t="n">
+        <v>54.94</v>
+      </c>
+      <c r="AK44" s="16" t="n">
+        <v>2127.56</v>
+      </c>
+      <c r="AL44" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM44" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN44" s="16" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -17672,7 +18379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18350,6 +19057,39 @@
         <v>56383.85</v>
       </c>
       <c r="G21" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="n">
+        <v>57703.9</v>
+      </c>
+      <c r="F22" s="18" t="n">
+        <v>56657.09</v>
+      </c>
+      <c r="G22" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -18369,7 +19109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA24"/>
+  <dimension ref="A1:AA25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -20718,6 +21458,105 @@
         <v>1000</v>
       </c>
       <c r="AA24" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>12:30 ET</t>
+        </is>
+      </c>
+      <c r="H25" s="17" t="n">
+        <v>30066.5</v>
+      </c>
+      <c r="I25" s="17" t="n">
+        <v>30050</v>
+      </c>
+      <c r="J25" s="17" t="n">
+        <v>30075</v>
+      </c>
+      <c r="K25" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="L25" s="17" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="M25" s="17" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="N25" s="17" t="n">
+        <v>985.3099999999999</v>
+      </c>
+      <c r="O25" s="17" t="n">
+        <v>925.37</v>
+      </c>
+      <c r="P25" s="17" t="n">
+        <v>277.39</v>
+      </c>
+      <c r="Q25" s="17" t="n">
+        <v>277.39</v>
+      </c>
+      <c r="R25" s="17" t="n">
+        <v>277.5</v>
+      </c>
+      <c r="S25" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T25" s="17" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="U25" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="V25" s="17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W25" s="17" t="n">
+        <v>60.68</v>
+      </c>
+      <c r="X25" s="17" t="n">
+        <v>216.82</v>
+      </c>
+      <c r="Y25" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z25" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -20837,7 +21676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22442,6 +23281,76 @@
       <c r="I46" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C47" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" s="19" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="E47" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F47" s="19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G47" s="19" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H47" s="19" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I47" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C48" s="19" t="n">
+        <v>37</v>
+      </c>
+      <c r="D48" s="19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" s="19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F48" s="19" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G48" s="19" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="H48" s="19" t="n">
+        <v>60.68</v>
+      </c>
+      <c r="I48" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — PROFIT</t>
         </is>
       </c>
     </row>
@@ -22908,7 +23817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN22"/>
+  <dimension ref="A1:AN23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -26156,6 +27065,158 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24175.7&gt;24005.85) &amp; EMA9↑(23986.43&gt;23821.26)</t>
+        </is>
+      </c>
+      <c r="H23" s="17" t="n">
+        <v>23986.43</v>
+      </c>
+      <c r="I23" s="17" t="n">
+        <v>23821.26</v>
+      </c>
+      <c r="J23" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K23" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L23" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N23" s="17" t="inlineStr">
+        <is>
+          <t>11:28 IST</t>
+        </is>
+      </c>
+      <c r="O23" s="17" t="n">
+        <v>24175.7</v>
+      </c>
+      <c r="P23" s="17" t="n">
+        <v>24005.85</v>
+      </c>
+      <c r="Q23" s="17" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="R23" s="17" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="S23" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="T23" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U23" s="17" t="n">
+        <v>2080</v>
+      </c>
+      <c r="V23" s="17" t="n">
+        <v>23.24</v>
+      </c>
+      <c r="W23" s="17" t="n">
+        <v>30.21</v>
+      </c>
+      <c r="X23" s="17" t="n">
+        <v>48339.2</v>
+      </c>
+      <c r="Y23" s="17" t="n">
+        <v>48394.01</v>
+      </c>
+      <c r="Z23" s="17" t="n">
+        <v>159660.8</v>
+      </c>
+      <c r="AA23" s="17" t="n">
+        <v>14501.76</v>
+      </c>
+      <c r="AB23" s="17" t="n">
+        <v>14501.76</v>
+      </c>
+      <c r="AC23" s="17" t="n">
+        <v>14497.6</v>
+      </c>
+      <c r="AD23" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE23" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF23" s="17" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="AG23" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH23" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI23" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ23" s="17" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="AK23" s="17" t="n">
+        <v>14442.79</v>
+      </c>
+      <c r="AL23" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM23" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN23" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -26170,7 +27231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN22"/>
+  <dimension ref="A1:AN23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -29418,6 +30479,158 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(24175.7&gt;24005.85) &amp; EMA9↑(23986.43&gt;23821.26)</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>23986.43</v>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v>23821.26</v>
+      </c>
+      <c r="J23" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K23" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N23" s="15" t="inlineStr">
+        <is>
+          <t>09:30 IST</t>
+        </is>
+      </c>
+      <c r="O23" s="15" t="n">
+        <v>24175.7</v>
+      </c>
+      <c r="P23" s="15" t="n">
+        <v>24005.85</v>
+      </c>
+      <c r="Q23" s="15" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="R23" s="15" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="S23" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="T23" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U23" s="15" t="n">
+        <v>2405</v>
+      </c>
+      <c r="V23" s="15" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="W23" s="15" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="X23" s="15" t="n">
+        <v>48484.8</v>
+      </c>
+      <c r="Y23" s="15" t="n">
+        <v>48539.63</v>
+      </c>
+      <c r="Z23" s="15" t="n">
+        <v>192015.2</v>
+      </c>
+      <c r="AA23" s="15" t="n">
+        <v>14545.44</v>
+      </c>
+      <c r="AB23" s="15" t="n">
+        <v>14545.44</v>
+      </c>
+      <c r="AC23" s="15" t="n">
+        <v>-14550.25</v>
+      </c>
+      <c r="AD23" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE23" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF23" s="15" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="AG23" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH23" s="15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI23" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ23" s="15" t="n">
+        <v>54.83</v>
+      </c>
+      <c r="AK23" s="15" t="n">
+        <v>-14605.08</v>
+      </c>
+      <c r="AL23" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM23" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN23" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -29432,7 +30645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN42"/>
+  <dimension ref="A1:AN44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -35680,6 +36893,310 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E43" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F43" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G43" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24175.7&gt;24005.85) &amp; EMA9↑(23986.43&gt;23821.26)</t>
+        </is>
+      </c>
+      <c r="H43" s="17" t="n">
+        <v>23986.43</v>
+      </c>
+      <c r="I43" s="17" t="n">
+        <v>23821.26</v>
+      </c>
+      <c r="J43" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K43" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L43" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N43" s="17" t="inlineStr">
+        <is>
+          <t>12:09 IST</t>
+        </is>
+      </c>
+      <c r="O43" s="17" t="n">
+        <v>24175.7</v>
+      </c>
+      <c r="P43" s="17" t="n">
+        <v>24005.85</v>
+      </c>
+      <c r="Q43" s="17" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="R43" s="17" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="S43" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="T43" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U43" s="17" t="n">
+        <v>2080</v>
+      </c>
+      <c r="V43" s="17" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="W43" s="17" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="X43" s="17" t="n">
+        <v>47361.6</v>
+      </c>
+      <c r="Y43" s="17" t="n">
+        <v>47416.25</v>
+      </c>
+      <c r="Z43" s="17" t="n">
+        <v>160638.4</v>
+      </c>
+      <c r="AA43" s="17" t="n">
+        <v>14208.48</v>
+      </c>
+      <c r="AB43" s="17" t="n">
+        <v>14208.48</v>
+      </c>
+      <c r="AC43" s="17" t="n">
+        <v>14206.4</v>
+      </c>
+      <c r="AD43" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE43" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF43" s="17" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="AG43" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH43" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI43" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ43" s="17" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="AK43" s="17" t="n">
+        <v>14151.75</v>
+      </c>
+      <c r="AL43" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM43" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN43" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E44" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F44" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G44" s="16" t="inlineStr">
+        <is>
+          <t>Price↑(24175.7&gt;24005.85) &amp; EMA9↑(23986.43&gt;23821.26)</t>
+        </is>
+      </c>
+      <c r="H44" s="16" t="n">
+        <v>23986.43</v>
+      </c>
+      <c r="I44" s="16" t="n">
+        <v>23821.26</v>
+      </c>
+      <c r="J44" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K44" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L44" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N44" s="16" t="inlineStr">
+        <is>
+          <t>13:56 IST</t>
+        </is>
+      </c>
+      <c r="O44" s="16" t="n">
+        <v>24175.7</v>
+      </c>
+      <c r="P44" s="16" t="n">
+        <v>24005.85</v>
+      </c>
+      <c r="Q44" s="16" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="R44" s="16" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="S44" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="T44" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U44" s="16" t="n">
+        <v>3185</v>
+      </c>
+      <c r="V44" s="16" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="W44" s="16" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="X44" s="16" t="n">
+        <v>47838.7</v>
+      </c>
+      <c r="Y44" s="16" t="n">
+        <v>47893.43</v>
+      </c>
+      <c r="Z44" s="16" t="n">
+        <v>270661.3</v>
+      </c>
+      <c r="AA44" s="16" t="n">
+        <v>14351.61</v>
+      </c>
+      <c r="AB44" s="16" t="n">
+        <v>14351.61</v>
+      </c>
+      <c r="AC44" s="16" t="n">
+        <v>-1337.7</v>
+      </c>
+      <c r="AD44" s="16" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="AE44" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF44" s="16" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AG44" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH44" s="16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI44" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ44" s="16" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="AK44" s="16" t="n">
+        <v>-1392.43</v>
+      </c>
+      <c r="AL44" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM44" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN44" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -35694,7 +37211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN12"/>
+  <dimension ref="A1:AN13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -37447,6 +38964,158 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24175.7&gt;24005.85) &amp; EMA9↑(23986.43&gt;23821.26)</t>
+        </is>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>23986.43</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>23821.26</v>
+      </c>
+      <c r="J13" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K13" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L13" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N13" s="17" t="inlineStr">
+        <is>
+          <t>11:21 IST</t>
+        </is>
+      </c>
+      <c r="O13" s="17" t="n">
+        <v>24175.7</v>
+      </c>
+      <c r="P13" s="17" t="n">
+        <v>24005.85</v>
+      </c>
+      <c r="Q13" s="17" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="R13" s="17" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="S13" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="T13" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U13" s="17" t="n">
+        <v>2340</v>
+      </c>
+      <c r="V13" s="17" t="n">
+        <v>20.39</v>
+      </c>
+      <c r="W13" s="17" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="X13" s="17" t="n">
+        <v>47712.6</v>
+      </c>
+      <c r="Y13" s="17" t="n">
+        <v>47767.31</v>
+      </c>
+      <c r="Z13" s="17" t="n">
+        <v>186287.4</v>
+      </c>
+      <c r="AA13" s="17" t="n">
+        <v>14313.78</v>
+      </c>
+      <c r="AB13" s="17" t="n">
+        <v>14313.78</v>
+      </c>
+      <c r="AC13" s="17" t="n">
+        <v>14320.8</v>
+      </c>
+      <c r="AD13" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE13" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF13" s="17" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="AG13" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH13" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI13" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ13" s="17" t="n">
+        <v>54.71</v>
+      </c>
+      <c r="AK13" s="17" t="n">
+        <v>14266.09</v>
+      </c>
+      <c r="AL13" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM13" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN13" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA25"/>
+  <dimension ref="A1:AA26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3057,6 +3057,105 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>10:30 ET</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>29504.25</v>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v>29500</v>
+      </c>
+      <c r="J26" s="15" t="n">
+        <v>29525</v>
+      </c>
+      <c r="K26" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="L26" s="15" t="n">
+        <v>220.37</v>
+      </c>
+      <c r="M26" s="15" t="n">
+        <v>154.26</v>
+      </c>
+      <c r="N26" s="15" t="n">
+        <v>911.08</v>
+      </c>
+      <c r="O26" s="15" t="n">
+        <v>1118.52</v>
+      </c>
+      <c r="P26" s="15" t="n">
+        <v>264.44</v>
+      </c>
+      <c r="Q26" s="15" t="n">
+        <v>264.44</v>
+      </c>
+      <c r="R26" s="15" t="n">
+        <v>-264.44</v>
+      </c>
+      <c r="S26" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="T26" s="15" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="U26" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="V26" s="15" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W26" s="15" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="X26" s="15" t="n">
+        <v>-294.04</v>
+      </c>
+      <c r="Y26" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="Z26" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA26" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -3071,7 +3170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN23"/>
+  <dimension ref="A1:AN24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6471,6 +6570,158 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(58033.05&gt;57542.9) &amp; EMA9↑(57621.96&gt;56519.64)</t>
+        </is>
+      </c>
+      <c r="H24" s="17" t="n">
+        <v>57621.96</v>
+      </c>
+      <c r="I24" s="17" t="n">
+        <v>56519.64</v>
+      </c>
+      <c r="J24" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K24" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L24" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="M24" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N24" s="17" t="inlineStr">
+        <is>
+          <t>11:02 IST</t>
+        </is>
+      </c>
+      <c r="O24" s="17" t="n">
+        <v>58033.05</v>
+      </c>
+      <c r="P24" s="17" t="n">
+        <v>57542.9</v>
+      </c>
+      <c r="Q24" s="17" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="R24" s="17" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="S24" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="T24" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U24" s="17" t="n">
+        <v>540</v>
+      </c>
+      <c r="V24" s="17" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="W24" s="17" t="n">
+        <v>116.35</v>
+      </c>
+      <c r="X24" s="17" t="n">
+        <v>48330</v>
+      </c>
+      <c r="Y24" s="17" t="n">
+        <v>48384.81</v>
+      </c>
+      <c r="Z24" s="17" t="n">
+        <v>59670</v>
+      </c>
+      <c r="AA24" s="17" t="n">
+        <v>14499</v>
+      </c>
+      <c r="AB24" s="17" t="n">
+        <v>14499</v>
+      </c>
+      <c r="AC24" s="17" t="n">
+        <v>14499</v>
+      </c>
+      <c r="AD24" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE24" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF24" s="17" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="AG24" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH24" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI24" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ24" s="17" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="AK24" s="17" t="n">
+        <v>14444.19</v>
+      </c>
+      <c r="AL24" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM24" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN24" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -6485,7 +6736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN23"/>
+  <dimension ref="A1:AN24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9885,6 +10136,158 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G24" s="16" t="inlineStr">
+        <is>
+          <t>Price↑(58033.05&gt;57542.9) &amp; EMA9↑(57621.96&gt;56519.64)</t>
+        </is>
+      </c>
+      <c r="H24" s="16" t="n">
+        <v>57621.96</v>
+      </c>
+      <c r="I24" s="16" t="n">
+        <v>56519.64</v>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K24" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L24" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="M24" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N24" s="16" t="inlineStr">
+        <is>
+          <t>14:25 IST</t>
+        </is>
+      </c>
+      <c r="O24" s="16" t="n">
+        <v>58033.05</v>
+      </c>
+      <c r="P24" s="16" t="n">
+        <v>57542.9</v>
+      </c>
+      <c r="Q24" s="16" t="inlineStr">
+        <is>
+          <t>58200 PE</t>
+        </is>
+      </c>
+      <c r="R24" s="16" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="S24" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="T24" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U24" s="16" t="n">
+        <v>480</v>
+      </c>
+      <c r="V24" s="16" t="n">
+        <v>101.14</v>
+      </c>
+      <c r="W24" s="16" t="n">
+        <v>103.77</v>
+      </c>
+      <c r="X24" s="16" t="n">
+        <v>48547.2</v>
+      </c>
+      <c r="Y24" s="16" t="n">
+        <v>48602.04</v>
+      </c>
+      <c r="Z24" s="16" t="n">
+        <v>47452.8</v>
+      </c>
+      <c r="AA24" s="16" t="n">
+        <v>14564.16</v>
+      </c>
+      <c r="AB24" s="16" t="n">
+        <v>14564.16</v>
+      </c>
+      <c r="AC24" s="16" t="n">
+        <v>1262.4</v>
+      </c>
+      <c r="AD24" s="16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE24" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF24" s="16" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="AG24" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH24" s="16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI24" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ24" s="16" t="n">
+        <v>54.84</v>
+      </c>
+      <c r="AK24" s="16" t="n">
+        <v>1207.56</v>
+      </c>
+      <c r="AL24" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM24" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN24" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -9899,7 +10302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN44"/>
+  <dimension ref="A1:AN46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16451,6 +16854,310 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C45" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D45" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E45" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F45" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(58033.05&gt;57542.9) &amp; EMA9↑(57621.96&gt;56519.64)</t>
+        </is>
+      </c>
+      <c r="H45" s="17" t="n">
+        <v>57621.96</v>
+      </c>
+      <c r="I45" s="17" t="n">
+        <v>56519.64</v>
+      </c>
+      <c r="J45" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K45" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L45" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="M45" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N45" s="17" t="inlineStr">
+        <is>
+          <t>11:24 IST</t>
+        </is>
+      </c>
+      <c r="O45" s="17" t="n">
+        <v>58033.05</v>
+      </c>
+      <c r="P45" s="17" t="n">
+        <v>57542.9</v>
+      </c>
+      <c r="Q45" s="17" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="R45" s="17" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="S45" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="T45" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U45" s="17" t="n">
+        <v>510</v>
+      </c>
+      <c r="V45" s="17" t="n">
+        <v>91.59</v>
+      </c>
+      <c r="W45" s="17" t="n">
+        <v>119.07</v>
+      </c>
+      <c r="X45" s="17" t="n">
+        <v>46710.9</v>
+      </c>
+      <c r="Y45" s="17" t="n">
+        <v>46765.45</v>
+      </c>
+      <c r="Z45" s="17" t="n">
+        <v>55289.1</v>
+      </c>
+      <c r="AA45" s="17" t="n">
+        <v>14013.27</v>
+      </c>
+      <c r="AB45" s="17" t="n">
+        <v>14013.27</v>
+      </c>
+      <c r="AC45" s="17" t="n">
+        <v>14014.8</v>
+      </c>
+      <c r="AD45" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE45" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF45" s="17" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="AG45" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH45" s="17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI45" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ45" s="17" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="AK45" s="17" t="n">
+        <v>13960.25</v>
+      </c>
+      <c r="AL45" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM45" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN45" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D46" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E46" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G46" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(58033.05&gt;57542.9) &amp; EMA9↑(57621.96&gt;56519.64)</t>
+        </is>
+      </c>
+      <c r="H46" s="17" t="n">
+        <v>57621.96</v>
+      </c>
+      <c r="I46" s="17" t="n">
+        <v>56519.64</v>
+      </c>
+      <c r="J46" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K46" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L46" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="M46" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N46" s="17" t="inlineStr">
+        <is>
+          <t>12:16 IST</t>
+        </is>
+      </c>
+      <c r="O46" s="17" t="n">
+        <v>58033.05</v>
+      </c>
+      <c r="P46" s="17" t="n">
+        <v>57542.9</v>
+      </c>
+      <c r="Q46" s="17" t="inlineStr">
+        <is>
+          <t>58200 PE</t>
+        </is>
+      </c>
+      <c r="R46" s="17" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="S46" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U46" s="17" t="n">
+        <v>450</v>
+      </c>
+      <c r="V46" s="17" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="W46" s="17" t="n">
+        <v>137.41</v>
+      </c>
+      <c r="X46" s="17" t="n">
+        <v>47565</v>
+      </c>
+      <c r="Y46" s="17" t="n">
+        <v>47619.68</v>
+      </c>
+      <c r="Z46" s="17" t="n">
+        <v>42435</v>
+      </c>
+      <c r="AA46" s="17" t="n">
+        <v>14269.5</v>
+      </c>
+      <c r="AB46" s="17" t="n">
+        <v>14269.5</v>
+      </c>
+      <c r="AC46" s="17" t="n">
+        <v>14269.5</v>
+      </c>
+      <c r="AD46" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE46" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF46" s="17" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AG46" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH46" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI46" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ46" s="17" t="n">
+        <v>54.68</v>
+      </c>
+      <c r="AK46" s="17" t="n">
+        <v>14214.82</v>
+      </c>
+      <c r="AL46" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM46" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN46" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -16465,7 +17172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN13"/>
+  <dimension ref="A1:AN14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18365,6 +19072,158 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(58033.05&gt;57542.9) &amp; EMA9↑(57621.96&gt;56519.64)</t>
+        </is>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>57621.96</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>56519.64</v>
+      </c>
+      <c r="J14" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K14" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L14" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="M14" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N14" s="17" t="inlineStr">
+        <is>
+          <t>10:02 IST</t>
+        </is>
+      </c>
+      <c r="O14" s="17" t="n">
+        <v>58033.05</v>
+      </c>
+      <c r="P14" s="17" t="n">
+        <v>57542.9</v>
+      </c>
+      <c r="Q14" s="17" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="R14" s="17" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="S14" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U14" s="17" t="n">
+        <v>450</v>
+      </c>
+      <c r="V14" s="17" t="n">
+        <v>108.44</v>
+      </c>
+      <c r="W14" s="17" t="n">
+        <v>140.97</v>
+      </c>
+      <c r="X14" s="17" t="n">
+        <v>48798</v>
+      </c>
+      <c r="Y14" s="17" t="n">
+        <v>48852.88</v>
+      </c>
+      <c r="Z14" s="17" t="n">
+        <v>41202</v>
+      </c>
+      <c r="AA14" s="17" t="n">
+        <v>14639.4</v>
+      </c>
+      <c r="AB14" s="17" t="n">
+        <v>14639.4</v>
+      </c>
+      <c r="AC14" s="17" t="n">
+        <v>14638.5</v>
+      </c>
+      <c r="AD14" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE14" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF14" s="17" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AG14" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH14" s="17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI14" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ14" s="17" t="n">
+        <v>54.88</v>
+      </c>
+      <c r="AK14" s="17" t="n">
+        <v>14583.62</v>
+      </c>
+      <c r="AL14" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM14" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN14" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -19109,7 +19968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA25"/>
+  <dimension ref="A1:AA26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -21557,6 +22416,105 @@
         <v>1000</v>
       </c>
       <c r="AA25" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>11:00 ET</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>29504</v>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v>29500</v>
+      </c>
+      <c r="J26" s="15" t="n">
+        <v>29525</v>
+      </c>
+      <c r="K26" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="L26" s="15" t="n">
+        <v>27.07</v>
+      </c>
+      <c r="M26" s="15" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="N26" s="15" t="n">
+        <v>976.14</v>
+      </c>
+      <c r="O26" s="15" t="n">
+        <v>779.62</v>
+      </c>
+      <c r="P26" s="15" t="n">
+        <v>276.11</v>
+      </c>
+      <c r="Q26" s="15" t="n">
+        <v>276.11</v>
+      </c>
+      <c r="R26" s="15" t="n">
+        <v>-276.08</v>
+      </c>
+      <c r="S26" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="T26" s="15" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="U26" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="V26" s="15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W26" s="15" t="n">
+        <v>55.76</v>
+      </c>
+      <c r="X26" s="15" t="n">
+        <v>-331.84</v>
+      </c>
+      <c r="Y26" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="Z26" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA26" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -21676,7 +22634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23351,6 +24309,76 @@
       <c r="I48" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C49" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D49" s="19" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="E49" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F49" s="19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G49" s="19" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H49" s="19" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I49" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — STOP LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B50" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C50" s="19" t="n">
+        <v>34</v>
+      </c>
+      <c r="D50" s="19" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="E50" s="19" t="n">
+        <v>17</v>
+      </c>
+      <c r="F50" s="19" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G50" s="19" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="H50" s="19" t="n">
+        <v>55.76</v>
+      </c>
+      <c r="I50" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — STOP LOSS</t>
         </is>
       </c>
     </row>
@@ -23817,7 +24845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN23"/>
+  <dimension ref="A1:AN24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -27217,6 +28245,158 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24005.85&gt;23865.75) &amp; EMA9↑(23939.11&gt;23785.81)</t>
+        </is>
+      </c>
+      <c r="H24" s="17" t="n">
+        <v>23939.11</v>
+      </c>
+      <c r="I24" s="17" t="n">
+        <v>23785.81</v>
+      </c>
+      <c r="J24" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K24" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N24" s="17" t="inlineStr">
+        <is>
+          <t>12:19 IST</t>
+        </is>
+      </c>
+      <c r="O24" s="17" t="n">
+        <v>24005.85</v>
+      </c>
+      <c r="P24" s="17" t="n">
+        <v>23865.75</v>
+      </c>
+      <c r="Q24" s="17" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="R24" s="17" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="S24" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="T24" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U24" s="17" t="n">
+        <v>3120</v>
+      </c>
+      <c r="V24" s="17" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="W24" s="17" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="X24" s="17" t="n">
+        <v>47611.2</v>
+      </c>
+      <c r="Y24" s="17" t="n">
+        <v>47665.89</v>
+      </c>
+      <c r="Z24" s="17" t="n">
+        <v>264388.8</v>
+      </c>
+      <c r="AA24" s="17" t="n">
+        <v>14283.36</v>
+      </c>
+      <c r="AB24" s="17" t="n">
+        <v>14283.36</v>
+      </c>
+      <c r="AC24" s="17" t="n">
+        <v>14289.6</v>
+      </c>
+      <c r="AD24" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE24" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF24" s="17" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AG24" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH24" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI24" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ24" s="17" t="n">
+        <v>54.69</v>
+      </c>
+      <c r="AK24" s="17" t="n">
+        <v>14234.91</v>
+      </c>
+      <c r="AL24" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM24" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN24" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -27231,7 +28411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN23"/>
+  <dimension ref="A1:AN24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -30631,6 +31811,158 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24005.85&gt;23865.75) &amp; EMA9↑(23939.11&gt;23785.81)</t>
+        </is>
+      </c>
+      <c r="H24" s="17" t="n">
+        <v>23939.11</v>
+      </c>
+      <c r="I24" s="17" t="n">
+        <v>23785.81</v>
+      </c>
+      <c r="J24" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K24" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N24" s="17" t="inlineStr">
+        <is>
+          <t>09:49 IST</t>
+        </is>
+      </c>
+      <c r="O24" s="17" t="n">
+        <v>24005.85</v>
+      </c>
+      <c r="P24" s="17" t="n">
+        <v>23865.75</v>
+      </c>
+      <c r="Q24" s="17" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="R24" s="17" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="S24" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="T24" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U24" s="17" t="n">
+        <v>2405</v>
+      </c>
+      <c r="V24" s="17" t="n">
+        <v>19.76</v>
+      </c>
+      <c r="W24" s="17" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="X24" s="17" t="n">
+        <v>47522.8</v>
+      </c>
+      <c r="Y24" s="17" t="n">
+        <v>47577.48</v>
+      </c>
+      <c r="Z24" s="17" t="n">
+        <v>192977.2</v>
+      </c>
+      <c r="AA24" s="17" t="n">
+        <v>14256.84</v>
+      </c>
+      <c r="AB24" s="17" t="n">
+        <v>14256.84</v>
+      </c>
+      <c r="AC24" s="17" t="n">
+        <v>14261.65</v>
+      </c>
+      <c r="AD24" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE24" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF24" s="17" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AG24" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH24" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI24" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ24" s="17" t="n">
+        <v>54.68</v>
+      </c>
+      <c r="AK24" s="17" t="n">
+        <v>14206.97</v>
+      </c>
+      <c r="AL24" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM24" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN24" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -30645,7 +31977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN44"/>
+  <dimension ref="A1:AN46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -37197,6 +38529,310 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C45" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D45" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E45" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F45" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24005.85&gt;23865.75) &amp; EMA9↑(23939.11&gt;23785.81)</t>
+        </is>
+      </c>
+      <c r="H45" s="17" t="n">
+        <v>23939.11</v>
+      </c>
+      <c r="I45" s="17" t="n">
+        <v>23785.81</v>
+      </c>
+      <c r="J45" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K45" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L45" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N45" s="17" t="inlineStr">
+        <is>
+          <t>10:54 IST</t>
+        </is>
+      </c>
+      <c r="O45" s="17" t="n">
+        <v>24005.85</v>
+      </c>
+      <c r="P45" s="17" t="n">
+        <v>23865.75</v>
+      </c>
+      <c r="Q45" s="17" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="R45" s="17" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="S45" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="T45" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U45" s="17" t="n">
+        <v>2600</v>
+      </c>
+      <c r="V45" s="17" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="W45" s="17" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="X45" s="17" t="n">
+        <v>47788</v>
+      </c>
+      <c r="Y45" s="17" t="n">
+        <v>47842.72</v>
+      </c>
+      <c r="Z45" s="17" t="n">
+        <v>212212</v>
+      </c>
+      <c r="AA45" s="17" t="n">
+        <v>14336.4</v>
+      </c>
+      <c r="AB45" s="17" t="n">
+        <v>14336.4</v>
+      </c>
+      <c r="AC45" s="17" t="n">
+        <v>14326</v>
+      </c>
+      <c r="AD45" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE45" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF45" s="17" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="AG45" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH45" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI45" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ45" s="17" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="AK45" s="17" t="n">
+        <v>14271.28</v>
+      </c>
+      <c r="AL45" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM45" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN45" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D46" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E46" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F46" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G46" s="16" t="inlineStr">
+        <is>
+          <t>Price↑(24005.85&gt;23865.75) &amp; EMA9↑(23939.11&gt;23785.81)</t>
+        </is>
+      </c>
+      <c r="H46" s="16" t="n">
+        <v>23939.11</v>
+      </c>
+      <c r="I46" s="16" t="n">
+        <v>23785.81</v>
+      </c>
+      <c r="J46" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K46" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L46" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N46" s="16" t="inlineStr">
+        <is>
+          <t>14:41 IST</t>
+        </is>
+      </c>
+      <c r="O46" s="16" t="n">
+        <v>24005.85</v>
+      </c>
+      <c r="P46" s="16" t="n">
+        <v>23865.75</v>
+      </c>
+      <c r="Q46" s="16" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="R46" s="16" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="S46" s="16" t="n">
+        <v>48</v>
+      </c>
+      <c r="T46" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U46" s="16" t="n">
+        <v>3120</v>
+      </c>
+      <c r="V46" s="16" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="W46" s="16" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="X46" s="16" t="n">
+        <v>47299.2</v>
+      </c>
+      <c r="Y46" s="16" t="n">
+        <v>47353.84</v>
+      </c>
+      <c r="Z46" s="16" t="n">
+        <v>264700.8</v>
+      </c>
+      <c r="AA46" s="16" t="n">
+        <v>14189.76</v>
+      </c>
+      <c r="AB46" s="16" t="n">
+        <v>14189.76</v>
+      </c>
+      <c r="AC46" s="16" t="n">
+        <v>-1216.8</v>
+      </c>
+      <c r="AD46" s="16" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="AE46" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF46" s="16" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AG46" s="16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH46" s="16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI46" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ46" s="16" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="AK46" s="16" t="n">
+        <v>-1271.44</v>
+      </c>
+      <c r="AL46" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM46" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN46" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -37211,7 +38847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN13"/>
+  <dimension ref="A1:AN14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -39116,6 +40752,158 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24005.85&gt;23865.75) &amp; EMA9↑(23939.11&gt;23785.81)</t>
+        </is>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>23939.11</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>23785.81</v>
+      </c>
+      <c r="J14" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K14" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N14" s="17" t="inlineStr">
+        <is>
+          <t>10:03 IST</t>
+        </is>
+      </c>
+      <c r="O14" s="17" t="n">
+        <v>24005.85</v>
+      </c>
+      <c r="P14" s="17" t="n">
+        <v>23865.75</v>
+      </c>
+      <c r="Q14" s="17" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="R14" s="17" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="S14" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="T14" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U14" s="17" t="n">
+        <v>3055</v>
+      </c>
+      <c r="V14" s="17" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="W14" s="17" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="X14" s="17" t="n">
+        <v>47994.05</v>
+      </c>
+      <c r="Y14" s="17" t="n">
+        <v>48048.8</v>
+      </c>
+      <c r="Z14" s="17" t="n">
+        <v>257505.95</v>
+      </c>
+      <c r="AA14" s="17" t="n">
+        <v>14398.22</v>
+      </c>
+      <c r="AB14" s="17" t="n">
+        <v>14398.22</v>
+      </c>
+      <c r="AC14" s="17" t="n">
+        <v>14389.05</v>
+      </c>
+      <c r="AD14" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE14" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF14" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG14" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH14" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI14" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ14" s="17" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="AK14" s="17" t="n">
+        <v>14334.3</v>
+      </c>
+      <c r="AL14" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM14" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN14" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -3170,7 +3170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN24"/>
+  <dimension ref="A1:AN25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6722,6 +6722,158 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H25" s="17" t="n">
+        <v>57751.18</v>
+      </c>
+      <c r="I25" s="17" t="n">
+        <v>56772.37</v>
+      </c>
+      <c r="J25" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L25" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="M25" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N25" s="17" t="inlineStr">
+        <is>
+          <t>11:20 IST</t>
+        </is>
+      </c>
+      <c r="O25" s="17" t="n">
+        <v>57938.5</v>
+      </c>
+      <c r="P25" s="17" t="n">
+        <v>58031.65</v>
+      </c>
+      <c r="Q25" s="17" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="R25" s="17" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="S25" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="T25" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U25" s="17" t="n">
+        <v>570</v>
+      </c>
+      <c r="V25" s="17" t="n">
+        <v>84.70999999999999</v>
+      </c>
+      <c r="W25" s="17" t="n">
+        <v>110.12</v>
+      </c>
+      <c r="X25" s="17" t="n">
+        <v>48284.7</v>
+      </c>
+      <c r="Y25" s="17" t="n">
+        <v>48339.5</v>
+      </c>
+      <c r="Z25" s="17" t="n">
+        <v>65715.3</v>
+      </c>
+      <c r="AA25" s="17" t="n">
+        <v>14485.41</v>
+      </c>
+      <c r="AB25" s="17" t="n">
+        <v>14485.41</v>
+      </c>
+      <c r="AC25" s="17" t="n">
+        <v>14483.7</v>
+      </c>
+      <c r="AD25" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE25" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF25" s="17" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="AG25" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH25" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI25" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ25" s="17" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="AK25" s="17" t="n">
+        <v>14428.9</v>
+      </c>
+      <c r="AL25" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM25" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN25" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -6736,7 +6888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN24"/>
+  <dimension ref="A1:AN25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10288,6 +10440,158 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H25" s="17" t="n">
+        <v>57751.18</v>
+      </c>
+      <c r="I25" s="17" t="n">
+        <v>56772.37</v>
+      </c>
+      <c r="J25" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L25" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="M25" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N25" s="17" t="inlineStr">
+        <is>
+          <t>09:43 IST</t>
+        </is>
+      </c>
+      <c r="O25" s="17" t="n">
+        <v>57938.5</v>
+      </c>
+      <c r="P25" s="17" t="n">
+        <v>58031.65</v>
+      </c>
+      <c r="Q25" s="17" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="R25" s="17" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="S25" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U25" s="17" t="n">
+        <v>450</v>
+      </c>
+      <c r="V25" s="17" t="n">
+        <v>104.64</v>
+      </c>
+      <c r="W25" s="17" t="n">
+        <v>136.03</v>
+      </c>
+      <c r="X25" s="17" t="n">
+        <v>47088</v>
+      </c>
+      <c r="Y25" s="17" t="n">
+        <v>47142.61</v>
+      </c>
+      <c r="Z25" s="17" t="n">
+        <v>42912</v>
+      </c>
+      <c r="AA25" s="17" t="n">
+        <v>14126.4</v>
+      </c>
+      <c r="AB25" s="17" t="n">
+        <v>14126.4</v>
+      </c>
+      <c r="AC25" s="17" t="n">
+        <v>14125.5</v>
+      </c>
+      <c r="AD25" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE25" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF25" s="17" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AG25" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH25" s="17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI25" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ25" s="17" t="n">
+        <v>54.61</v>
+      </c>
+      <c r="AK25" s="17" t="n">
+        <v>14070.89</v>
+      </c>
+      <c r="AL25" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM25" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN25" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -10302,7 +10606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN46"/>
+  <dimension ref="A1:AN48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17153,6 +17457,310 @@
         <v>50000</v>
       </c>
       <c r="AN46" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E47" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F47" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G47" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H47" s="16" t="n">
+        <v>57751.18</v>
+      </c>
+      <c r="I47" s="16" t="n">
+        <v>56772.37</v>
+      </c>
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K47" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L47" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="M47" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N47" s="16" t="inlineStr">
+        <is>
+          <t>13:44 IST</t>
+        </is>
+      </c>
+      <c r="O47" s="16" t="n">
+        <v>57938.5</v>
+      </c>
+      <c r="P47" s="16" t="n">
+        <v>58031.65</v>
+      </c>
+      <c r="Q47" s="16" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="R47" s="16" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="S47" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U47" s="16" t="n">
+        <v>450</v>
+      </c>
+      <c r="V47" s="16" t="n">
+        <v>106.78</v>
+      </c>
+      <c r="W47" s="16" t="n">
+        <v>105.54</v>
+      </c>
+      <c r="X47" s="16" t="n">
+        <v>48051</v>
+      </c>
+      <c r="Y47" s="16" t="n">
+        <v>48105.76</v>
+      </c>
+      <c r="Z47" s="16" t="n">
+        <v>41949</v>
+      </c>
+      <c r="AA47" s="16" t="n">
+        <v>14415.3</v>
+      </c>
+      <c r="AB47" s="16" t="n">
+        <v>14415.3</v>
+      </c>
+      <c r="AC47" s="16" t="n">
+        <v>-558</v>
+      </c>
+      <c r="AD47" s="16" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AE47" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF47" s="16" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="AG47" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH47" s="16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI47" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ47" s="16" t="n">
+        <v>54.76</v>
+      </c>
+      <c r="AK47" s="16" t="n">
+        <v>-612.76</v>
+      </c>
+      <c r="AL47" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM47" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN47" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F48" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G48" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>57751.18</v>
+      </c>
+      <c r="I48" s="15" t="n">
+        <v>56772.37</v>
+      </c>
+      <c r="J48" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K48" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L48" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="M48" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N48" s="15" t="inlineStr">
+        <is>
+          <t>09:30 IST</t>
+        </is>
+      </c>
+      <c r="O48" s="15" t="n">
+        <v>57938.5</v>
+      </c>
+      <c r="P48" s="15" t="n">
+        <v>58031.65</v>
+      </c>
+      <c r="Q48" s="15" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="R48" s="15" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="S48" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U48" s="15" t="n">
+        <v>450</v>
+      </c>
+      <c r="V48" s="15" t="n">
+        <v>106.22</v>
+      </c>
+      <c r="W48" s="15" t="n">
+        <v>74.34999999999999</v>
+      </c>
+      <c r="X48" s="15" t="n">
+        <v>47799</v>
+      </c>
+      <c r="Y48" s="15" t="n">
+        <v>47853.72</v>
+      </c>
+      <c r="Z48" s="15" t="n">
+        <v>42201</v>
+      </c>
+      <c r="AA48" s="15" t="n">
+        <v>14339.7</v>
+      </c>
+      <c r="AB48" s="15" t="n">
+        <v>14339.7</v>
+      </c>
+      <c r="AC48" s="15" t="n">
+        <v>-14341.5</v>
+      </c>
+      <c r="AD48" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE48" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF48" s="15" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="AG48" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH48" s="15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI48" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ48" s="15" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="AK48" s="15" t="n">
+        <v>-14396.22</v>
+      </c>
+      <c r="AL48" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM48" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN48" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -19238,7 +19846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19949,6 +20557,39 @@
         <v>56657.09</v>
       </c>
       <c r="G22" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>57751.18</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>56772.37</v>
+      </c>
+      <c r="G23" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -24845,7 +25486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN24"/>
+  <dimension ref="A1:AN25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -28397,6 +29038,158 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24270.85&gt;24175.7) &amp; EMA9↑(24043.55&gt;23856.79)</t>
+        </is>
+      </c>
+      <c r="H25" s="17" t="n">
+        <v>24043.55</v>
+      </c>
+      <c r="I25" s="17" t="n">
+        <v>23856.79</v>
+      </c>
+      <c r="J25" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L25" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M25" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N25" s="17" t="inlineStr">
+        <is>
+          <t>10:39 IST</t>
+        </is>
+      </c>
+      <c r="O25" s="17" t="n">
+        <v>24270.85</v>
+      </c>
+      <c r="P25" s="17" t="n">
+        <v>24175.7</v>
+      </c>
+      <c r="Q25" s="17" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="R25" s="17" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="S25" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="T25" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U25" s="17" t="n">
+        <v>1235</v>
+      </c>
+      <c r="V25" s="17" t="n">
+        <v>38.93</v>
+      </c>
+      <c r="W25" s="17" t="n">
+        <v>50.61</v>
+      </c>
+      <c r="X25" s="17" t="n">
+        <v>48078.55</v>
+      </c>
+      <c r="Y25" s="17" t="n">
+        <v>48133.32</v>
+      </c>
+      <c r="Z25" s="17" t="n">
+        <v>75421.45</v>
+      </c>
+      <c r="AA25" s="17" t="n">
+        <v>14423.57</v>
+      </c>
+      <c r="AB25" s="17" t="n">
+        <v>14423.57</v>
+      </c>
+      <c r="AC25" s="17" t="n">
+        <v>14424.8</v>
+      </c>
+      <c r="AD25" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE25" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF25" s="17" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="AG25" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH25" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI25" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ25" s="17" t="n">
+        <v>54.77</v>
+      </c>
+      <c r="AK25" s="17" t="n">
+        <v>14370.03</v>
+      </c>
+      <c r="AL25" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM25" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN25" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -28411,7 +29204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN24"/>
+  <dimension ref="A1:AN25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -31963,6 +32756,158 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24270.85&gt;24175.7) &amp; EMA9↑(24043.55&gt;23856.79)</t>
+        </is>
+      </c>
+      <c r="H25" s="17" t="n">
+        <v>24043.55</v>
+      </c>
+      <c r="I25" s="17" t="n">
+        <v>23856.79</v>
+      </c>
+      <c r="J25" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L25" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M25" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N25" s="17" t="inlineStr">
+        <is>
+          <t>11:49 IST</t>
+        </is>
+      </c>
+      <c r="O25" s="17" t="n">
+        <v>24270.85</v>
+      </c>
+      <c r="P25" s="17" t="n">
+        <v>24175.7</v>
+      </c>
+      <c r="Q25" s="17" t="inlineStr">
+        <is>
+          <t>24300 PE</t>
+        </is>
+      </c>
+      <c r="R25" s="17" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="S25" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U25" s="17" t="n">
+        <v>1625</v>
+      </c>
+      <c r="V25" s="17" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="W25" s="17" t="n">
+        <v>38.35</v>
+      </c>
+      <c r="X25" s="17" t="n">
+        <v>47937.5</v>
+      </c>
+      <c r="Y25" s="17" t="n">
+        <v>47992.24</v>
+      </c>
+      <c r="Z25" s="17" t="n">
+        <v>114562.5</v>
+      </c>
+      <c r="AA25" s="17" t="n">
+        <v>14381.25</v>
+      </c>
+      <c r="AB25" s="17" t="n">
+        <v>14381.25</v>
+      </c>
+      <c r="AC25" s="17" t="n">
+        <v>14381.25</v>
+      </c>
+      <c r="AD25" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE25" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF25" s="17" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="AG25" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH25" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI25" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ25" s="17" t="n">
+        <v>54.74</v>
+      </c>
+      <c r="AK25" s="17" t="n">
+        <v>14326.51</v>
+      </c>
+      <c r="AL25" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM25" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN25" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -31977,7 +32922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN46"/>
+  <dimension ref="A1:AN48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -38833,6 +39778,310 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D47" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E47" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F47" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G47" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24270.85&gt;24175.7) &amp; EMA9↑(24043.55&gt;23856.79)</t>
+        </is>
+      </c>
+      <c r="H47" s="17" t="n">
+        <v>24043.55</v>
+      </c>
+      <c r="I47" s="17" t="n">
+        <v>23856.79</v>
+      </c>
+      <c r="J47" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K47" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L47" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M47" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N47" s="17" t="inlineStr">
+        <is>
+          <t>10:45 IST</t>
+        </is>
+      </c>
+      <c r="O47" s="17" t="n">
+        <v>24270.85</v>
+      </c>
+      <c r="P47" s="17" t="n">
+        <v>24175.7</v>
+      </c>
+      <c r="Q47" s="17" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="R47" s="17" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="S47" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="T47" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U47" s="17" t="n">
+        <v>1495</v>
+      </c>
+      <c r="V47" s="17" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="W47" s="17" t="n">
+        <v>40.99</v>
+      </c>
+      <c r="X47" s="17" t="n">
+        <v>47137.35</v>
+      </c>
+      <c r="Y47" s="17" t="n">
+        <v>47191.97</v>
+      </c>
+      <c r="Z47" s="17" t="n">
+        <v>102362.65</v>
+      </c>
+      <c r="AA47" s="17" t="n">
+        <v>14141.2</v>
+      </c>
+      <c r="AB47" s="17" t="n">
+        <v>14141.2</v>
+      </c>
+      <c r="AC47" s="17" t="n">
+        <v>14142.7</v>
+      </c>
+      <c r="AD47" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE47" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF47" s="17" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AG47" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH47" s="17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI47" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ47" s="17" t="n">
+        <v>54.62</v>
+      </c>
+      <c r="AK47" s="17" t="n">
+        <v>14088.08</v>
+      </c>
+      <c r="AL47" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM47" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN47" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F48" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G48" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(24270.85&gt;24175.7) &amp; EMA9↑(24043.55&gt;23856.79)</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>24043.55</v>
+      </c>
+      <c r="I48" s="15" t="n">
+        <v>23856.79</v>
+      </c>
+      <c r="J48" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K48" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L48" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="M48" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N48" s="15" t="inlineStr">
+        <is>
+          <t>10:57 IST</t>
+        </is>
+      </c>
+      <c r="O48" s="15" t="n">
+        <v>24270.85</v>
+      </c>
+      <c r="P48" s="15" t="n">
+        <v>24175.7</v>
+      </c>
+      <c r="Q48" s="15" t="inlineStr">
+        <is>
+          <t>24300 PE</t>
+        </is>
+      </c>
+      <c r="R48" s="15" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="S48" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="T48" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U48" s="15" t="n">
+        <v>1365</v>
+      </c>
+      <c r="V48" s="15" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="W48" s="15" t="n">
+        <v>24.51</v>
+      </c>
+      <c r="X48" s="15" t="n">
+        <v>47788.65</v>
+      </c>
+      <c r="Y48" s="15" t="n">
+        <v>47843.37</v>
+      </c>
+      <c r="Z48" s="15" t="n">
+        <v>88711.35000000001</v>
+      </c>
+      <c r="AA48" s="15" t="n">
+        <v>14336.59</v>
+      </c>
+      <c r="AB48" s="15" t="n">
+        <v>14336.59</v>
+      </c>
+      <c r="AC48" s="15" t="n">
+        <v>-14332.5</v>
+      </c>
+      <c r="AD48" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE48" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF48" s="15" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="AG48" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH48" s="15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI48" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ48" s="15" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="AK48" s="15" t="n">
+        <v>-14387.22</v>
+      </c>
+      <c r="AL48" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM48" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN48" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -38847,7 +40096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN14"/>
+  <dimension ref="A1:AN15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -40904,6 +42153,158 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G15" s="16" t="inlineStr">
+        <is>
+          <t>Price↑(24270.85&gt;24175.7) &amp; EMA9↑(24043.55&gt;23856.79)</t>
+        </is>
+      </c>
+      <c r="H15" s="16" t="n">
+        <v>24043.55</v>
+      </c>
+      <c r="I15" s="16" t="n">
+        <v>23856.79</v>
+      </c>
+      <c r="J15" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K15" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L15" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="M15" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N15" s="16" t="inlineStr">
+        <is>
+          <t>15:01 IST</t>
+        </is>
+      </c>
+      <c r="O15" s="16" t="n">
+        <v>24270.85</v>
+      </c>
+      <c r="P15" s="16" t="n">
+        <v>24175.7</v>
+      </c>
+      <c r="Q15" s="16" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="R15" s="16" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="S15" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="T15" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U15" s="16" t="n">
+        <v>1690</v>
+      </c>
+      <c r="V15" s="16" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="W15" s="16" t="n">
+        <v>27.86</v>
+      </c>
+      <c r="X15" s="16" t="n">
+        <v>48587.5</v>
+      </c>
+      <c r="Y15" s="16" t="n">
+        <v>48642.35</v>
+      </c>
+      <c r="Z15" s="16" t="n">
+        <v>120412.5</v>
+      </c>
+      <c r="AA15" s="16" t="n">
+        <v>14576.25</v>
+      </c>
+      <c r="AB15" s="16" t="n">
+        <v>14576.25</v>
+      </c>
+      <c r="AC15" s="16" t="n">
+        <v>-1504.1</v>
+      </c>
+      <c r="AD15" s="16" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="AE15" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF15" s="16" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="AG15" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH15" s="16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI15" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ15" s="16" t="n">
+        <v>54.85</v>
+      </c>
+      <c r="AK15" s="16" t="n">
+        <v>-1558.95</v>
+      </c>
+      <c r="AL15" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM15" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN15" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -3170,7 +3170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN25"/>
+  <dimension ref="A1:AN26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6874,6 +6874,158 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G26" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H26" s="16" t="n">
+        <v>57704.35</v>
+      </c>
+      <c r="I26" s="16" t="n">
+        <v>56655.75</v>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K26" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L26" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="M26" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N26" s="16" t="inlineStr">
+        <is>
+          <t>14:36 IST</t>
+        </is>
+      </c>
+      <c r="O26" s="16" t="n">
+        <v>58031.65</v>
+      </c>
+      <c r="P26" s="16" t="n">
+        <v>58033.05</v>
+      </c>
+      <c r="Q26" s="16" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="R26" s="16" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="S26" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U26" s="16" t="n">
+        <v>450</v>
+      </c>
+      <c r="V26" s="16" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="W26" s="16" t="n">
+        <v>107</v>
+      </c>
+      <c r="X26" s="16" t="n">
+        <v>46530</v>
+      </c>
+      <c r="Y26" s="16" t="n">
+        <v>46584.52</v>
+      </c>
+      <c r="Z26" s="16" t="n">
+        <v>43470</v>
+      </c>
+      <c r="AA26" s="16" t="n">
+        <v>13959</v>
+      </c>
+      <c r="AB26" s="16" t="n">
+        <v>13959</v>
+      </c>
+      <c r="AC26" s="16" t="n">
+        <v>1620</v>
+      </c>
+      <c r="AD26" s="16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE26" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF26" s="16" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="AG26" s="16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH26" s="16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI26" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ26" s="16" t="n">
+        <v>54.52</v>
+      </c>
+      <c r="AK26" s="16" t="n">
+        <v>1565.48</v>
+      </c>
+      <c r="AL26" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM26" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN26" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -6888,7 +7040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN25"/>
+  <dimension ref="A1:AN26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10592,6 +10744,158 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>57704.35</v>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v>56655.75</v>
+      </c>
+      <c r="J26" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K26" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L26" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="M26" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N26" s="15" t="inlineStr">
+        <is>
+          <t>10:03 IST</t>
+        </is>
+      </c>
+      <c r="O26" s="15" t="n">
+        <v>58031.65</v>
+      </c>
+      <c r="P26" s="15" t="n">
+        <v>58033.05</v>
+      </c>
+      <c r="Q26" s="15" t="inlineStr">
+        <is>
+          <t>58200 PE</t>
+        </is>
+      </c>
+      <c r="R26" s="15" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="S26" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U26" s="15" t="n">
+        <v>450</v>
+      </c>
+      <c r="V26" s="15" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="W26" s="15" t="n">
+        <v>73.04000000000001</v>
+      </c>
+      <c r="X26" s="15" t="n">
+        <v>46957.5</v>
+      </c>
+      <c r="Y26" s="15" t="n">
+        <v>47012.09</v>
+      </c>
+      <c r="Z26" s="15" t="n">
+        <v>43042.5</v>
+      </c>
+      <c r="AA26" s="15" t="n">
+        <v>14087.25</v>
+      </c>
+      <c r="AB26" s="15" t="n">
+        <v>14087.25</v>
+      </c>
+      <c r="AC26" s="15" t="n">
+        <v>-14089.5</v>
+      </c>
+      <c r="AD26" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE26" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF26" s="15" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="AG26" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH26" s="15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI26" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ26" s="15" t="n">
+        <v>54.59</v>
+      </c>
+      <c r="AK26" s="15" t="n">
+        <v>-14144.09</v>
+      </c>
+      <c r="AL26" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM26" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN26" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -10606,7 +10910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN48"/>
+  <dimension ref="A1:AN50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17761,6 +18065,310 @@
         <v>50000</v>
       </c>
       <c r="AN48" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B49" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D49" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E49" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F49" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G49" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H49" s="16" t="n">
+        <v>57704.35</v>
+      </c>
+      <c r="I49" s="16" t="n">
+        <v>56655.75</v>
+      </c>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K49" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L49" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="M49" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N49" s="16" t="inlineStr">
+        <is>
+          <t>13:50 IST</t>
+        </is>
+      </c>
+      <c r="O49" s="16" t="n">
+        <v>58031.65</v>
+      </c>
+      <c r="P49" s="16" t="n">
+        <v>58033.05</v>
+      </c>
+      <c r="Q49" s="16" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="R49" s="16" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="S49" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T49" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U49" s="16" t="n">
+        <v>600</v>
+      </c>
+      <c r="V49" s="16" t="n">
+        <v>80.47</v>
+      </c>
+      <c r="W49" s="16" t="n">
+        <v>81.64</v>
+      </c>
+      <c r="X49" s="16" t="n">
+        <v>48282</v>
+      </c>
+      <c r="Y49" s="16" t="n">
+        <v>48336.8</v>
+      </c>
+      <c r="Z49" s="16" t="n">
+        <v>71718</v>
+      </c>
+      <c r="AA49" s="16" t="n">
+        <v>14484.6</v>
+      </c>
+      <c r="AB49" s="16" t="n">
+        <v>14484.6</v>
+      </c>
+      <c r="AC49" s="16" t="n">
+        <v>702</v>
+      </c>
+      <c r="AD49" s="16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE49" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF49" s="16" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="AG49" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH49" s="16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI49" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ49" s="16" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="AK49" s="16" t="n">
+        <v>647.2</v>
+      </c>
+      <c r="AL49" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM49" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN49" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E50" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F50" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G50" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H50" s="17" t="n">
+        <v>57704.35</v>
+      </c>
+      <c r="I50" s="17" t="n">
+        <v>56655.75</v>
+      </c>
+      <c r="J50" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K50" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L50" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="M50" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N50" s="17" t="inlineStr">
+        <is>
+          <t>11:07 IST</t>
+        </is>
+      </c>
+      <c r="O50" s="17" t="n">
+        <v>58031.65</v>
+      </c>
+      <c r="P50" s="17" t="n">
+        <v>58033.05</v>
+      </c>
+      <c r="Q50" s="17" t="inlineStr">
+        <is>
+          <t>58200 PE</t>
+        </is>
+      </c>
+      <c r="R50" s="17" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="S50" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="T50" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U50" s="17" t="n">
+        <v>480</v>
+      </c>
+      <c r="V50" s="17" t="n">
+        <v>97.69</v>
+      </c>
+      <c r="W50" s="17" t="n">
+        <v>127</v>
+      </c>
+      <c r="X50" s="17" t="n">
+        <v>46891.2</v>
+      </c>
+      <c r="Y50" s="17" t="n">
+        <v>46945.78</v>
+      </c>
+      <c r="Z50" s="17" t="n">
+        <v>49108.8</v>
+      </c>
+      <c r="AA50" s="17" t="n">
+        <v>14067.36</v>
+      </c>
+      <c r="AB50" s="17" t="n">
+        <v>14067.36</v>
+      </c>
+      <c r="AC50" s="17" t="n">
+        <v>14068.8</v>
+      </c>
+      <c r="AD50" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE50" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF50" s="17" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="AG50" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH50" s="17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI50" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ50" s="17" t="n">
+        <v>54.58</v>
+      </c>
+      <c r="AK50" s="17" t="n">
+        <v>14014.22</v>
+      </c>
+      <c r="AL50" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM50" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN50" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -19846,7 +20454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20590,6 +21198,39 @@
         <v>56772.37</v>
       </c>
       <c r="G23" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>57704.35</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>56655.75</v>
+      </c>
+      <c r="G24" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -25486,7 +26127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN25"/>
+  <dimension ref="A1:AN26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -29190,6 +29831,158 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24175.7&gt;24005.85) &amp; EMA9↑(23986.73&gt;23815.39)</t>
+        </is>
+      </c>
+      <c r="H26" s="17" t="n">
+        <v>23986.73</v>
+      </c>
+      <c r="I26" s="17" t="n">
+        <v>23815.39</v>
+      </c>
+      <c r="J26" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K26" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L26" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M26" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N26" s="17" t="inlineStr">
+        <is>
+          <t>11:14 IST</t>
+        </is>
+      </c>
+      <c r="O26" s="17" t="n">
+        <v>24175.7</v>
+      </c>
+      <c r="P26" s="17" t="n">
+        <v>24005.85</v>
+      </c>
+      <c r="Q26" s="17" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="R26" s="17" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="S26" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="T26" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U26" s="17" t="n">
+        <v>1690</v>
+      </c>
+      <c r="V26" s="17" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="W26" s="17" t="n">
+        <v>36.31</v>
+      </c>
+      <c r="X26" s="17" t="n">
+        <v>47201.7</v>
+      </c>
+      <c r="Y26" s="17" t="n">
+        <v>47256.33</v>
+      </c>
+      <c r="Z26" s="17" t="n">
+        <v>121798.3</v>
+      </c>
+      <c r="AA26" s="17" t="n">
+        <v>14160.51</v>
+      </c>
+      <c r="AB26" s="17" t="n">
+        <v>14160.51</v>
+      </c>
+      <c r="AC26" s="17" t="n">
+        <v>14162.2</v>
+      </c>
+      <c r="AD26" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE26" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF26" s="17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AG26" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH26" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI26" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ26" s="17" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="AK26" s="17" t="n">
+        <v>14107.57</v>
+      </c>
+      <c r="AL26" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM26" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN26" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -29204,7 +29997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN25"/>
+  <dimension ref="A1:AN26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -32908,6 +33701,158 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24175.7&gt;24005.85) &amp; EMA9↑(23986.73&gt;23815.39)</t>
+        </is>
+      </c>
+      <c r="H26" s="17" t="n">
+        <v>23986.73</v>
+      </c>
+      <c r="I26" s="17" t="n">
+        <v>23815.39</v>
+      </c>
+      <c r="J26" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K26" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L26" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M26" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N26" s="17" t="inlineStr">
+        <is>
+          <t>11:52 IST</t>
+        </is>
+      </c>
+      <c r="O26" s="17" t="n">
+        <v>24175.7</v>
+      </c>
+      <c r="P26" s="17" t="n">
+        <v>24005.85</v>
+      </c>
+      <c r="Q26" s="17" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="R26" s="17" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="S26" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="T26" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U26" s="17" t="n">
+        <v>1235</v>
+      </c>
+      <c r="V26" s="17" t="n">
+        <v>39.83</v>
+      </c>
+      <c r="W26" s="17" t="n">
+        <v>51.78</v>
+      </c>
+      <c r="X26" s="17" t="n">
+        <v>49190.05</v>
+      </c>
+      <c r="Y26" s="17" t="n">
+        <v>49244.99</v>
+      </c>
+      <c r="Z26" s="17" t="n">
+        <v>74309.95</v>
+      </c>
+      <c r="AA26" s="17" t="n">
+        <v>14757.01</v>
+      </c>
+      <c r="AB26" s="17" t="n">
+        <v>14757.01</v>
+      </c>
+      <c r="AC26" s="17" t="n">
+        <v>14758.25</v>
+      </c>
+      <c r="AD26" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE26" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF26" s="17" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AG26" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH26" s="17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI26" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ26" s="17" t="n">
+        <v>54.94</v>
+      </c>
+      <c r="AK26" s="17" t="n">
+        <v>14703.31</v>
+      </c>
+      <c r="AL26" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM26" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN26" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -32922,7 +33867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN48"/>
+  <dimension ref="A1:AN50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -40082,6 +41027,310 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D49" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E49" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F49" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G49" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24175.7&gt;24005.85) &amp; EMA9↑(23986.73&gt;23815.39)</t>
+        </is>
+      </c>
+      <c r="H49" s="17" t="n">
+        <v>23986.73</v>
+      </c>
+      <c r="I49" s="17" t="n">
+        <v>23815.39</v>
+      </c>
+      <c r="J49" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K49" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L49" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M49" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N49" s="17" t="inlineStr">
+        <is>
+          <t>12:02 IST</t>
+        </is>
+      </c>
+      <c r="O49" s="17" t="n">
+        <v>24175.7</v>
+      </c>
+      <c r="P49" s="17" t="n">
+        <v>24005.85</v>
+      </c>
+      <c r="Q49" s="17" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="R49" s="17" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="S49" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="T49" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U49" s="17" t="n">
+        <v>1365</v>
+      </c>
+      <c r="V49" s="17" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="W49" s="17" t="n">
+        <v>46.09</v>
+      </c>
+      <c r="X49" s="17" t="n">
+        <v>48389.25</v>
+      </c>
+      <c r="Y49" s="17" t="n">
+        <v>48444.06</v>
+      </c>
+      <c r="Z49" s="17" t="n">
+        <v>88110.75</v>
+      </c>
+      <c r="AA49" s="17" t="n">
+        <v>14516.77</v>
+      </c>
+      <c r="AB49" s="17" t="n">
+        <v>14516.77</v>
+      </c>
+      <c r="AC49" s="17" t="n">
+        <v>14523.6</v>
+      </c>
+      <c r="AD49" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE49" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF49" s="17" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AG49" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH49" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI49" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ49" s="17" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="AK49" s="17" t="n">
+        <v>14468.79</v>
+      </c>
+      <c r="AL49" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM49" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN49" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B50" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D50" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E50" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F50" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G50" s="16" t="inlineStr">
+        <is>
+          <t>Price↑(24175.7&gt;24005.85) &amp; EMA9↑(23986.73&gt;23815.39)</t>
+        </is>
+      </c>
+      <c r="H50" s="16" t="n">
+        <v>23986.73</v>
+      </c>
+      <c r="I50" s="16" t="n">
+        <v>23815.39</v>
+      </c>
+      <c r="J50" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K50" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L50" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="M50" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N50" s="16" t="inlineStr">
+        <is>
+          <t>13:27 IST</t>
+        </is>
+      </c>
+      <c r="O50" s="16" t="n">
+        <v>24175.7</v>
+      </c>
+      <c r="P50" s="16" t="n">
+        <v>24005.85</v>
+      </c>
+      <c r="Q50" s="16" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="R50" s="16" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="S50" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="T50" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U50" s="16" t="n">
+        <v>1495</v>
+      </c>
+      <c r="V50" s="16" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="W50" s="16" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="X50" s="16" t="n">
+        <v>47481.2</v>
+      </c>
+      <c r="Y50" s="16" t="n">
+        <v>47535.87</v>
+      </c>
+      <c r="Z50" s="16" t="n">
+        <v>102018.8</v>
+      </c>
+      <c r="AA50" s="16" t="n">
+        <v>14244.36</v>
+      </c>
+      <c r="AB50" s="16" t="n">
+        <v>14244.36</v>
+      </c>
+      <c r="AC50" s="16" t="n">
+        <v>1405.3</v>
+      </c>
+      <c r="AD50" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE50" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF50" s="16" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AG50" s="16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH50" s="16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI50" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ50" s="16" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="AK50" s="16" t="n">
+        <v>1350.63</v>
+      </c>
+      <c r="AL50" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM50" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN50" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -40096,7 +41345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN15"/>
+  <dimension ref="A1:AN16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42305,6 +43554,158 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24175.7&gt;24005.85) &amp; EMA9↑(23986.73&gt;23815.39)</t>
+        </is>
+      </c>
+      <c r="H16" s="17" t="n">
+        <v>23986.73</v>
+      </c>
+      <c r="I16" s="17" t="n">
+        <v>23815.39</v>
+      </c>
+      <c r="J16" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K16" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L16" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M16" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N16" s="17" t="inlineStr">
+        <is>
+          <t>12:16 IST</t>
+        </is>
+      </c>
+      <c r="O16" s="17" t="n">
+        <v>24175.7</v>
+      </c>
+      <c r="P16" s="17" t="n">
+        <v>24005.85</v>
+      </c>
+      <c r="Q16" s="17" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="R16" s="17" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="S16" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="T16" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U16" s="17" t="n">
+        <v>1365</v>
+      </c>
+      <c r="V16" s="17" t="n">
+        <v>35.04</v>
+      </c>
+      <c r="W16" s="17" t="n">
+        <v>45.55</v>
+      </c>
+      <c r="X16" s="17" t="n">
+        <v>47829.6</v>
+      </c>
+      <c r="Y16" s="17" t="n">
+        <v>47884.33</v>
+      </c>
+      <c r="Z16" s="17" t="n">
+        <v>88670.39999999999</v>
+      </c>
+      <c r="AA16" s="17" t="n">
+        <v>14348.88</v>
+      </c>
+      <c r="AB16" s="17" t="n">
+        <v>14348.88</v>
+      </c>
+      <c r="AC16" s="17" t="n">
+        <v>14346.15</v>
+      </c>
+      <c r="AD16" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE16" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF16" s="17" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AG16" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH16" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI16" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ16" s="17" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="AK16" s="17" t="n">
+        <v>14291.42</v>
+      </c>
+      <c r="AL16" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM16" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN16" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA26"/>
+  <dimension ref="A1:AA27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3156,6 +3156,105 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>10:37 ET</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>30060.5</v>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v>30050</v>
+      </c>
+      <c r="J27" s="15" t="n">
+        <v>30075</v>
+      </c>
+      <c r="K27" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="L27" s="15" t="n">
+        <v>157.92</v>
+      </c>
+      <c r="M27" s="15" t="n">
+        <v>110.54</v>
+      </c>
+      <c r="N27" s="15" t="n">
+        <v>991.92</v>
+      </c>
+      <c r="O27" s="15" t="n">
+        <v>2052.48</v>
+      </c>
+      <c r="P27" s="15" t="n">
+        <v>284.26</v>
+      </c>
+      <c r="Q27" s="15" t="n">
+        <v>284.26</v>
+      </c>
+      <c r="R27" s="15" t="n">
+        <v>-284.28</v>
+      </c>
+      <c r="S27" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="T27" s="15" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="U27" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="V27" s="15" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="W27" s="15" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="X27" s="15" t="n">
+        <v>-328.68</v>
+      </c>
+      <c r="Y27" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="Z27" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA27" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -3170,7 +3269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN26"/>
+  <dimension ref="A1:AN27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7026,6 +7125,158 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(58291.5&gt;57938.5) &amp; EMA9↑(57858.32&gt;56864.47)</t>
+        </is>
+      </c>
+      <c r="H27" s="17" t="n">
+        <v>57858.32</v>
+      </c>
+      <c r="I27" s="17" t="n">
+        <v>56864.47</v>
+      </c>
+      <c r="J27" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K27" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L27" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="M27" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N27" s="17" t="inlineStr">
+        <is>
+          <t>11:07 IST</t>
+        </is>
+      </c>
+      <c r="O27" s="17" t="n">
+        <v>58291.5</v>
+      </c>
+      <c r="P27" s="17" t="n">
+        <v>57938.5</v>
+      </c>
+      <c r="Q27" s="17" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="R27" s="17" t="inlineStr">
+        <is>
+          <t>58400 CE</t>
+        </is>
+      </c>
+      <c r="S27" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U27" s="17" t="n">
+        <v>450</v>
+      </c>
+      <c r="V27" s="17" t="n">
+        <v>106.82</v>
+      </c>
+      <c r="W27" s="17" t="n">
+        <v>138.87</v>
+      </c>
+      <c r="X27" s="17" t="n">
+        <v>48069</v>
+      </c>
+      <c r="Y27" s="17" t="n">
+        <v>48123.76</v>
+      </c>
+      <c r="Z27" s="17" t="n">
+        <v>41931</v>
+      </c>
+      <c r="AA27" s="17" t="n">
+        <v>14420.7</v>
+      </c>
+      <c r="AB27" s="17" t="n">
+        <v>14420.7</v>
+      </c>
+      <c r="AC27" s="17" t="n">
+        <v>14422.5</v>
+      </c>
+      <c r="AD27" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE27" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF27" s="17" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="AG27" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH27" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI27" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ27" s="17" t="n">
+        <v>54.76</v>
+      </c>
+      <c r="AK27" s="17" t="n">
+        <v>14367.74</v>
+      </c>
+      <c r="AL27" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM27" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN27" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -7040,7 +7291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN26"/>
+  <dimension ref="A1:AN27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10896,6 +11147,158 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(58291.5&gt;57938.5) &amp; EMA9↑(57858.32&gt;56864.47)</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>57858.32</v>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v>56864.47</v>
+      </c>
+      <c r="J27" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K27" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L27" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="M27" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N27" s="15" t="inlineStr">
+        <is>
+          <t>11:16 IST</t>
+        </is>
+      </c>
+      <c r="O27" s="15" t="n">
+        <v>58291.5</v>
+      </c>
+      <c r="P27" s="15" t="n">
+        <v>57938.5</v>
+      </c>
+      <c r="Q27" s="15" t="inlineStr">
+        <is>
+          <t>58400 PE</t>
+        </is>
+      </c>
+      <c r="R27" s="15" t="inlineStr">
+        <is>
+          <t>58200 PE</t>
+        </is>
+      </c>
+      <c r="S27" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="T27" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U27" s="15" t="n">
+        <v>570</v>
+      </c>
+      <c r="V27" s="15" t="n">
+        <v>83.86</v>
+      </c>
+      <c r="W27" s="15" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="X27" s="15" t="n">
+        <v>47800.2</v>
+      </c>
+      <c r="Y27" s="15" t="n">
+        <v>47854.92</v>
+      </c>
+      <c r="Z27" s="15" t="n">
+        <v>66199.8</v>
+      </c>
+      <c r="AA27" s="15" t="n">
+        <v>14340.06</v>
+      </c>
+      <c r="AB27" s="15" t="n">
+        <v>14340.06</v>
+      </c>
+      <c r="AC27" s="15" t="n">
+        <v>-14341.2</v>
+      </c>
+      <c r="AD27" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE27" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF27" s="15" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AG27" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH27" s="15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI27" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ27" s="15" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="AK27" s="15" t="n">
+        <v>-14395.92</v>
+      </c>
+      <c r="AL27" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM27" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN27" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -10910,7 +11313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN50"/>
+  <dimension ref="A1:AN52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18374,6 +18777,310 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C51" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D51" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E51" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F51" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G51" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(58291.5&gt;57938.5) &amp; EMA9↑(57858.32&gt;56864.47)</t>
+        </is>
+      </c>
+      <c r="H51" s="17" t="n">
+        <v>57858.32</v>
+      </c>
+      <c r="I51" s="17" t="n">
+        <v>56864.47</v>
+      </c>
+      <c r="J51" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K51" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L51" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="M51" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N51" s="17" t="inlineStr">
+        <is>
+          <t>09:52 IST</t>
+        </is>
+      </c>
+      <c r="O51" s="17" t="n">
+        <v>58291.5</v>
+      </c>
+      <c r="P51" s="17" t="n">
+        <v>57938.5</v>
+      </c>
+      <c r="Q51" s="17" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="R51" s="17" t="inlineStr">
+        <is>
+          <t>58400 CE</t>
+        </is>
+      </c>
+      <c r="S51" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="T51" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U51" s="17" t="n">
+        <v>510</v>
+      </c>
+      <c r="V51" s="17" t="n">
+        <v>94.73</v>
+      </c>
+      <c r="W51" s="17" t="n">
+        <v>123.15</v>
+      </c>
+      <c r="X51" s="17" t="n">
+        <v>48312.3</v>
+      </c>
+      <c r="Y51" s="17" t="n">
+        <v>48367.1</v>
+      </c>
+      <c r="Z51" s="17" t="n">
+        <v>53687.7</v>
+      </c>
+      <c r="AA51" s="17" t="n">
+        <v>14493.69</v>
+      </c>
+      <c r="AB51" s="17" t="n">
+        <v>14493.69</v>
+      </c>
+      <c r="AC51" s="17" t="n">
+        <v>14494.2</v>
+      </c>
+      <c r="AD51" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE51" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF51" s="17" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="AG51" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH51" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI51" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ51" s="17" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="AK51" s="17" t="n">
+        <v>14439.4</v>
+      </c>
+      <c r="AL51" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM51" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN51" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B52" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D52" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E52" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F52" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G52" s="16" t="inlineStr">
+        <is>
+          <t>Price↑(58291.5&gt;57938.5) &amp; EMA9↑(57858.32&gt;56864.47)</t>
+        </is>
+      </c>
+      <c r="H52" s="16" t="n">
+        <v>57858.32</v>
+      </c>
+      <c r="I52" s="16" t="n">
+        <v>56864.47</v>
+      </c>
+      <c r="J52" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K52" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L52" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="M52" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N52" s="16" t="inlineStr">
+        <is>
+          <t>14:13 IST</t>
+        </is>
+      </c>
+      <c r="O52" s="16" t="n">
+        <v>58291.5</v>
+      </c>
+      <c r="P52" s="16" t="n">
+        <v>57938.5</v>
+      </c>
+      <c r="Q52" s="16" t="inlineStr">
+        <is>
+          <t>58400 PE</t>
+        </is>
+      </c>
+      <c r="R52" s="16" t="inlineStr">
+        <is>
+          <t>58200 PE</t>
+        </is>
+      </c>
+      <c r="S52" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="T52" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U52" s="16" t="n">
+        <v>540</v>
+      </c>
+      <c r="V52" s="16" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="W52" s="16" t="n">
+        <v>91.98</v>
+      </c>
+      <c r="X52" s="16" t="n">
+        <v>47844</v>
+      </c>
+      <c r="Y52" s="16" t="n">
+        <v>47898.73</v>
+      </c>
+      <c r="Z52" s="16" t="n">
+        <v>60156</v>
+      </c>
+      <c r="AA52" s="16" t="n">
+        <v>14353.2</v>
+      </c>
+      <c r="AB52" s="16" t="n">
+        <v>14353.2</v>
+      </c>
+      <c r="AC52" s="16" t="n">
+        <v>1825.2</v>
+      </c>
+      <c r="AD52" s="16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE52" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF52" s="16" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AG52" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH52" s="16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI52" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ52" s="16" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="AK52" s="16" t="n">
+        <v>1770.47</v>
+      </c>
+      <c r="AL52" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM52" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN52" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -18388,7 +19095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN14"/>
+  <dimension ref="A1:AN15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -20440,6 +21147,158 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G15" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(58291.5&gt;57938.5) &amp; EMA9↑(57858.32&gt;56864.47)</t>
+        </is>
+      </c>
+      <c r="H15" s="17" t="n">
+        <v>57858.32</v>
+      </c>
+      <c r="I15" s="17" t="n">
+        <v>56864.47</v>
+      </c>
+      <c r="J15" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K15" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L15" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="M15" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N15" s="17" t="inlineStr">
+        <is>
+          <t>10:58 IST</t>
+        </is>
+      </c>
+      <c r="O15" s="17" t="n">
+        <v>58291.5</v>
+      </c>
+      <c r="P15" s="17" t="n">
+        <v>57938.5</v>
+      </c>
+      <c r="Q15" s="17" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="R15" s="17" t="inlineStr">
+        <is>
+          <t>58400 CE</t>
+        </is>
+      </c>
+      <c r="S15" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="T15" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U15" s="17" t="n">
+        <v>480</v>
+      </c>
+      <c r="V15" s="17" t="n">
+        <v>97.63</v>
+      </c>
+      <c r="W15" s="17" t="n">
+        <v>126.92</v>
+      </c>
+      <c r="X15" s="17" t="n">
+        <v>46862.4</v>
+      </c>
+      <c r="Y15" s="17" t="n">
+        <v>46916.97</v>
+      </c>
+      <c r="Z15" s="17" t="n">
+        <v>49137.6</v>
+      </c>
+      <c r="AA15" s="17" t="n">
+        <v>14058.72</v>
+      </c>
+      <c r="AB15" s="17" t="n">
+        <v>14058.72</v>
+      </c>
+      <c r="AC15" s="17" t="n">
+        <v>14059.2</v>
+      </c>
+      <c r="AD15" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE15" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF15" s="17" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="AG15" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH15" s="17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI15" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ15" s="17" t="n">
+        <v>54.57</v>
+      </c>
+      <c r="AK15" s="17" t="n">
+        <v>14004.63</v>
+      </c>
+      <c r="AL15" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM15" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN15" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -21250,7 +22109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA26"/>
+  <dimension ref="A1:AA27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -23797,6 +24656,105 @@
         <v>1000</v>
       </c>
       <c r="AA26" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>10:20 ET</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>30060.5</v>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v>30050</v>
+      </c>
+      <c r="J27" s="15" t="n">
+        <v>30075</v>
+      </c>
+      <c r="K27" s="15" t="n">
+        <v>57</v>
+      </c>
+      <c r="L27" s="15" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="M27" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="N27" s="15" t="n">
+        <v>988.95</v>
+      </c>
+      <c r="O27" s="15" t="n">
+        <v>1954.53</v>
+      </c>
+      <c r="P27" s="15" t="n">
+        <v>268.64</v>
+      </c>
+      <c r="Q27" s="15" t="n">
+        <v>268.64</v>
+      </c>
+      <c r="R27" s="15" t="n">
+        <v>-268.47</v>
+      </c>
+      <c r="S27" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="T27" s="15" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="U27" s="15" t="n">
+        <v>57</v>
+      </c>
+      <c r="V27" s="15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="W27" s="15" t="n">
+        <v>93.48</v>
+      </c>
+      <c r="X27" s="15" t="n">
+        <v>-361.95</v>
+      </c>
+      <c r="Y27" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="Z27" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA27" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -23916,7 +24874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25659,6 +26617,76 @@
         <v>55.76</v>
       </c>
       <c r="I50" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — STOP LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B51" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D51" s="19" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="E51" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="F51" s="19" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G51" s="19" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="H51" s="19" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="I51" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — STOP LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B52" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C52" s="19" t="n">
+        <v>57</v>
+      </c>
+      <c r="D52" s="19" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="E52" s="19" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F52" s="19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G52" s="19" t="n">
+        <v>46.74</v>
+      </c>
+      <c r="H52" s="19" t="n">
+        <v>93.48</v>
+      </c>
+      <c r="I52" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — STOP LOSS</t>
         </is>
@@ -26127,7 +27155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN26"/>
+  <dimension ref="A1:AN27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -29983,6 +31011,158 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24430.35&gt;24270.85) &amp; EMA9↑(24120.85&gt;23891.81)</t>
+        </is>
+      </c>
+      <c r="H27" s="17" t="n">
+        <v>24120.85</v>
+      </c>
+      <c r="I27" s="17" t="n">
+        <v>23891.81</v>
+      </c>
+      <c r="J27" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K27" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L27" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M27" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N27" s="17" t="inlineStr">
+        <is>
+          <t>11:46 IST</t>
+        </is>
+      </c>
+      <c r="O27" s="17" t="n">
+        <v>24430.35</v>
+      </c>
+      <c r="P27" s="17" t="n">
+        <v>24270.85</v>
+      </c>
+      <c r="Q27" s="17" t="inlineStr">
+        <is>
+          <t>24400 CE</t>
+        </is>
+      </c>
+      <c r="R27" s="17" t="inlineStr">
+        <is>
+          <t>24500 CE</t>
+        </is>
+      </c>
+      <c r="S27" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="T27" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U27" s="17" t="n">
+        <v>1560</v>
+      </c>
+      <c r="V27" s="17" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="W27" s="17" t="n">
+        <v>40.43</v>
+      </c>
+      <c r="X27" s="17" t="n">
+        <v>48516</v>
+      </c>
+      <c r="Y27" s="17" t="n">
+        <v>48570.83</v>
+      </c>
+      <c r="Z27" s="17" t="n">
+        <v>107484</v>
+      </c>
+      <c r="AA27" s="17" t="n">
+        <v>14554.8</v>
+      </c>
+      <c r="AB27" s="17" t="n">
+        <v>14554.8</v>
+      </c>
+      <c r="AC27" s="17" t="n">
+        <v>14554.8</v>
+      </c>
+      <c r="AD27" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE27" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF27" s="17" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="AG27" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH27" s="17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI27" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ27" s="17" t="n">
+        <v>54.83</v>
+      </c>
+      <c r="AK27" s="17" t="n">
+        <v>14499.97</v>
+      </c>
+      <c r="AL27" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM27" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN27" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -29997,7 +31177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN26"/>
+  <dimension ref="A1:AN27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -33853,6 +35033,158 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24430.35&gt;24270.85) &amp; EMA9↑(24120.85&gt;23891.81)</t>
+        </is>
+      </c>
+      <c r="H27" s="17" t="n">
+        <v>24120.85</v>
+      </c>
+      <c r="I27" s="17" t="n">
+        <v>23891.81</v>
+      </c>
+      <c r="J27" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K27" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L27" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M27" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N27" s="17" t="inlineStr">
+        <is>
+          <t>11:22 IST</t>
+        </is>
+      </c>
+      <c r="O27" s="17" t="n">
+        <v>24430.35</v>
+      </c>
+      <c r="P27" s="17" t="n">
+        <v>24270.85</v>
+      </c>
+      <c r="Q27" s="17" t="inlineStr">
+        <is>
+          <t>24500 PE</t>
+        </is>
+      </c>
+      <c r="R27" s="17" t="inlineStr">
+        <is>
+          <t>24400 PE</t>
+        </is>
+      </c>
+      <c r="S27" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="T27" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U27" s="17" t="n">
+        <v>1885</v>
+      </c>
+      <c r="V27" s="17" t="n">
+        <v>25.41</v>
+      </c>
+      <c r="W27" s="17" t="n">
+        <v>33.03</v>
+      </c>
+      <c r="X27" s="17" t="n">
+        <v>47897.85</v>
+      </c>
+      <c r="Y27" s="17" t="n">
+        <v>47952.59</v>
+      </c>
+      <c r="Z27" s="17" t="n">
+        <v>140602.15</v>
+      </c>
+      <c r="AA27" s="17" t="n">
+        <v>14369.35</v>
+      </c>
+      <c r="AB27" s="17" t="n">
+        <v>14369.35</v>
+      </c>
+      <c r="AC27" s="17" t="n">
+        <v>14363.7</v>
+      </c>
+      <c r="AD27" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE27" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF27" s="17" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="AG27" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH27" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI27" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ27" s="17" t="n">
+        <v>54.74</v>
+      </c>
+      <c r="AK27" s="17" t="n">
+        <v>14308.96</v>
+      </c>
+      <c r="AL27" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM27" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN27" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -33867,7 +35199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN50"/>
+  <dimension ref="A1:AN52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -41331,6 +42663,310 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D51" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E51" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F51" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G51" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(24430.35&gt;24270.85) &amp; EMA9↑(24120.85&gt;23891.81)</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>24120.85</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>23891.81</v>
+      </c>
+      <c r="J51" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K51" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L51" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M51" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N51" s="15" t="inlineStr">
+        <is>
+          <t>10:38 IST</t>
+        </is>
+      </c>
+      <c r="O51" s="15" t="n">
+        <v>24430.35</v>
+      </c>
+      <c r="P51" s="15" t="n">
+        <v>24270.85</v>
+      </c>
+      <c r="Q51" s="15" t="inlineStr">
+        <is>
+          <t>24400 CE</t>
+        </is>
+      </c>
+      <c r="R51" s="15" t="inlineStr">
+        <is>
+          <t>24500 CE</t>
+        </is>
+      </c>
+      <c r="S51" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="T51" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U51" s="15" t="n">
+        <v>1495</v>
+      </c>
+      <c r="V51" s="15" t="n">
+        <v>32.67</v>
+      </c>
+      <c r="W51" s="15" t="n">
+        <v>22.87</v>
+      </c>
+      <c r="X51" s="15" t="n">
+        <v>48841.65</v>
+      </c>
+      <c r="Y51" s="15" t="n">
+        <v>48896.54</v>
+      </c>
+      <c r="Z51" s="15" t="n">
+        <v>100658.35</v>
+      </c>
+      <c r="AA51" s="15" t="n">
+        <v>14652.5</v>
+      </c>
+      <c r="AB51" s="15" t="n">
+        <v>14652.5</v>
+      </c>
+      <c r="AC51" s="15" t="n">
+        <v>-14651</v>
+      </c>
+      <c r="AD51" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE51" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF51" s="15" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="AG51" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH51" s="15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI51" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ51" s="15" t="n">
+        <v>54.89</v>
+      </c>
+      <c r="AK51" s="15" t="n">
+        <v>-14705.89</v>
+      </c>
+      <c r="AL51" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM51" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN51" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B52" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D52" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E52" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F52" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G52" s="16" t="inlineStr">
+        <is>
+          <t>Price↑(24430.35&gt;24270.85) &amp; EMA9↑(24120.85&gt;23891.81)</t>
+        </is>
+      </c>
+      <c r="H52" s="16" t="n">
+        <v>24120.85</v>
+      </c>
+      <c r="I52" s="16" t="n">
+        <v>23891.81</v>
+      </c>
+      <c r="J52" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K52" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L52" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M52" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N52" s="16" t="inlineStr">
+        <is>
+          <t>14:25 IST</t>
+        </is>
+      </c>
+      <c r="O52" s="16" t="n">
+        <v>24430.35</v>
+      </c>
+      <c r="P52" s="16" t="n">
+        <v>24270.85</v>
+      </c>
+      <c r="Q52" s="16" t="inlineStr">
+        <is>
+          <t>24500 PE</t>
+        </is>
+      </c>
+      <c r="R52" s="16" t="inlineStr">
+        <is>
+          <t>24400 PE</t>
+        </is>
+      </c>
+      <c r="S52" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="T52" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U52" s="16" t="n">
+        <v>1235</v>
+      </c>
+      <c r="V52" s="16" t="n">
+        <v>38.51</v>
+      </c>
+      <c r="W52" s="16" t="n">
+        <v>39.57</v>
+      </c>
+      <c r="X52" s="16" t="n">
+        <v>47559.85</v>
+      </c>
+      <c r="Y52" s="16" t="n">
+        <v>47614.53</v>
+      </c>
+      <c r="Z52" s="16" t="n">
+        <v>75940.14999999999</v>
+      </c>
+      <c r="AA52" s="16" t="n">
+        <v>14267.95</v>
+      </c>
+      <c r="AB52" s="16" t="n">
+        <v>14267.95</v>
+      </c>
+      <c r="AC52" s="16" t="n">
+        <v>1309.1</v>
+      </c>
+      <c r="AD52" s="16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE52" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF52" s="16" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AG52" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH52" s="16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI52" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ52" s="16" t="n">
+        <v>54.68</v>
+      </c>
+      <c r="AK52" s="16" t="n">
+        <v>1254.42</v>
+      </c>
+      <c r="AL52" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM52" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN52" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -41345,7 +42981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN16"/>
+  <dimension ref="A1:AN17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -43706,6 +45342,158 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G17" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24430.35&gt;24270.85) &amp; EMA9↑(24120.85&gt;23891.81)</t>
+        </is>
+      </c>
+      <c r="H17" s="17" t="n">
+        <v>24120.85</v>
+      </c>
+      <c r="I17" s="17" t="n">
+        <v>23891.81</v>
+      </c>
+      <c r="J17" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K17" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L17" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N17" s="17" t="inlineStr">
+        <is>
+          <t>10:01 IST</t>
+        </is>
+      </c>
+      <c r="O17" s="17" t="n">
+        <v>24430.35</v>
+      </c>
+      <c r="P17" s="17" t="n">
+        <v>24270.85</v>
+      </c>
+      <c r="Q17" s="17" t="inlineStr">
+        <is>
+          <t>24400 CE</t>
+        </is>
+      </c>
+      <c r="R17" s="17" t="inlineStr">
+        <is>
+          <t>24500 CE</t>
+        </is>
+      </c>
+      <c r="S17" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="T17" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U17" s="17" t="n">
+        <v>1365</v>
+      </c>
+      <c r="V17" s="17" t="n">
+        <v>34.79</v>
+      </c>
+      <c r="W17" s="17" t="n">
+        <v>45.23</v>
+      </c>
+      <c r="X17" s="17" t="n">
+        <v>47488.35</v>
+      </c>
+      <c r="Y17" s="17" t="n">
+        <v>47543.02</v>
+      </c>
+      <c r="Z17" s="17" t="n">
+        <v>89011.64999999999</v>
+      </c>
+      <c r="AA17" s="17" t="n">
+        <v>14246.5</v>
+      </c>
+      <c r="AB17" s="17" t="n">
+        <v>14246.5</v>
+      </c>
+      <c r="AC17" s="17" t="n">
+        <v>14250.6</v>
+      </c>
+      <c r="AD17" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE17" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF17" s="17" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AG17" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH17" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI17" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ17" s="17" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="AK17" s="17" t="n">
+        <v>14195.93</v>
+      </c>
+      <c r="AL17" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM17" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN17" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA27"/>
+  <dimension ref="A1:AA28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3255,6 +3255,105 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>11:52 ET</t>
+        </is>
+      </c>
+      <c r="H28" s="17" t="n">
+        <v>29953</v>
+      </c>
+      <c r="I28" s="17" t="n">
+        <v>29950</v>
+      </c>
+      <c r="J28" s="17" t="n">
+        <v>29975</v>
+      </c>
+      <c r="K28" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L28" s="17" t="n">
+        <v>159.88</v>
+      </c>
+      <c r="M28" s="17" t="n">
+        <v>207.84</v>
+      </c>
+      <c r="N28" s="17" t="n">
+        <v>836.4</v>
+      </c>
+      <c r="O28" s="17" t="n">
+        <v>1700.6</v>
+      </c>
+      <c r="P28" s="17" t="n">
+        <v>239.82</v>
+      </c>
+      <c r="Q28" s="17" t="n">
+        <v>239.82</v>
+      </c>
+      <c r="R28" s="17" t="n">
+        <v>239.8</v>
+      </c>
+      <c r="S28" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T28" s="17" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="U28" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="V28" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W28" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="X28" s="17" t="n">
+        <v>202.8</v>
+      </c>
+      <c r="Y28" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z28" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA28" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -3269,7 +3368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN27"/>
+  <dimension ref="A1:AN28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7277,6 +7376,158 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E28" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G28" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H28" s="16" t="n">
+        <v>57750.02</v>
+      </c>
+      <c r="I28" s="16" t="n">
+        <v>56721.77</v>
+      </c>
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K28" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L28" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="M28" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N28" s="16" t="inlineStr">
+        <is>
+          <t>13:57 IST</t>
+        </is>
+      </c>
+      <c r="O28" s="16" t="n">
+        <v>57938.5</v>
+      </c>
+      <c r="P28" s="16" t="n">
+        <v>58031.65</v>
+      </c>
+      <c r="Q28" s="16" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="R28" s="16" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="S28" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U28" s="16" t="n">
+        <v>450</v>
+      </c>
+      <c r="V28" s="16" t="n">
+        <v>109.62</v>
+      </c>
+      <c r="W28" s="16" t="n">
+        <v>111.18</v>
+      </c>
+      <c r="X28" s="16" t="n">
+        <v>49329</v>
+      </c>
+      <c r="Y28" s="16" t="n">
+        <v>49383.96</v>
+      </c>
+      <c r="Z28" s="16" t="n">
+        <v>40671</v>
+      </c>
+      <c r="AA28" s="16" t="n">
+        <v>14798.7</v>
+      </c>
+      <c r="AB28" s="16" t="n">
+        <v>14798.7</v>
+      </c>
+      <c r="AC28" s="16" t="n">
+        <v>702</v>
+      </c>
+      <c r="AD28" s="16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE28" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF28" s="16" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="AG28" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH28" s="16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI28" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ28" s="16" t="n">
+        <v>54.96</v>
+      </c>
+      <c r="AK28" s="16" t="n">
+        <v>647.04</v>
+      </c>
+      <c r="AL28" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM28" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN28" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -7291,7 +7542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN27"/>
+  <dimension ref="A1:AN28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11299,6 +11550,158 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H28" s="17" t="n">
+        <v>57750.02</v>
+      </c>
+      <c r="I28" s="17" t="n">
+        <v>56721.77</v>
+      </c>
+      <c r="J28" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K28" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L28" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="M28" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N28" s="17" t="inlineStr">
+        <is>
+          <t>10:54 IST</t>
+        </is>
+      </c>
+      <c r="O28" s="17" t="n">
+        <v>57938.5</v>
+      </c>
+      <c r="P28" s="17" t="n">
+        <v>58031.65</v>
+      </c>
+      <c r="Q28" s="17" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="R28" s="17" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="S28" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U28" s="17" t="n">
+        <v>600</v>
+      </c>
+      <c r="V28" s="17" t="n">
+        <v>80.52</v>
+      </c>
+      <c r="W28" s="17" t="n">
+        <v>104.68</v>
+      </c>
+      <c r="X28" s="17" t="n">
+        <v>48312</v>
+      </c>
+      <c r="Y28" s="17" t="n">
+        <v>48366.8</v>
+      </c>
+      <c r="Z28" s="17" t="n">
+        <v>71688</v>
+      </c>
+      <c r="AA28" s="17" t="n">
+        <v>14493.6</v>
+      </c>
+      <c r="AB28" s="17" t="n">
+        <v>14493.6</v>
+      </c>
+      <c r="AC28" s="17" t="n">
+        <v>14496</v>
+      </c>
+      <c r="AD28" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE28" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF28" s="17" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="AG28" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH28" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI28" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ28" s="17" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="AK28" s="17" t="n">
+        <v>14441.2</v>
+      </c>
+      <c r="AL28" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM28" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN28" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -11313,7 +11716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN52"/>
+  <dimension ref="A1:AN54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -19076,6 +19479,310 @@
         <v>50000</v>
       </c>
       <c r="AN52" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C53" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D53" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E53" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F53" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G53" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H53" s="17" t="n">
+        <v>57750.02</v>
+      </c>
+      <c r="I53" s="17" t="n">
+        <v>56721.77</v>
+      </c>
+      <c r="J53" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K53" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L53" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="M53" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N53" s="17" t="inlineStr">
+        <is>
+          <t>10:30 IST</t>
+        </is>
+      </c>
+      <c r="O53" s="17" t="n">
+        <v>57938.5</v>
+      </c>
+      <c r="P53" s="17" t="n">
+        <v>58031.65</v>
+      </c>
+      <c r="Q53" s="17" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="R53" s="17" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="S53" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="T53" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U53" s="17" t="n">
+        <v>480</v>
+      </c>
+      <c r="V53" s="17" t="n">
+        <v>98.91</v>
+      </c>
+      <c r="W53" s="17" t="n">
+        <v>128.58</v>
+      </c>
+      <c r="X53" s="17" t="n">
+        <v>47476.8</v>
+      </c>
+      <c r="Y53" s="17" t="n">
+        <v>47531.47</v>
+      </c>
+      <c r="Z53" s="17" t="n">
+        <v>48523.2</v>
+      </c>
+      <c r="AA53" s="17" t="n">
+        <v>14243.04</v>
+      </c>
+      <c r="AB53" s="17" t="n">
+        <v>14243.04</v>
+      </c>
+      <c r="AC53" s="17" t="n">
+        <v>14241.6</v>
+      </c>
+      <c r="AD53" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE53" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF53" s="17" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="AG53" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH53" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI53" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ53" s="17" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="AK53" s="17" t="n">
+        <v>14186.93</v>
+      </c>
+      <c r="AL53" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM53" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN53" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E54" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F54" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G54" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>57750.02</v>
+      </c>
+      <c r="I54" s="15" t="n">
+        <v>56721.77</v>
+      </c>
+      <c r="J54" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K54" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L54" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="M54" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N54" s="15" t="inlineStr">
+        <is>
+          <t>10:37 IST</t>
+        </is>
+      </c>
+      <c r="O54" s="15" t="n">
+        <v>57938.5</v>
+      </c>
+      <c r="P54" s="15" t="n">
+        <v>58031.65</v>
+      </c>
+      <c r="Q54" s="15" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="R54" s="15" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="S54" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="T54" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U54" s="15" t="n">
+        <v>540</v>
+      </c>
+      <c r="V54" s="15" t="n">
+        <v>90.54000000000001</v>
+      </c>
+      <c r="W54" s="15" t="n">
+        <v>63.38</v>
+      </c>
+      <c r="X54" s="15" t="n">
+        <v>48891.6</v>
+      </c>
+      <c r="Y54" s="15" t="n">
+        <v>48946.49</v>
+      </c>
+      <c r="Z54" s="15" t="n">
+        <v>59108.4</v>
+      </c>
+      <c r="AA54" s="15" t="n">
+        <v>14667.48</v>
+      </c>
+      <c r="AB54" s="15" t="n">
+        <v>14667.48</v>
+      </c>
+      <c r="AC54" s="15" t="n">
+        <v>-14666.4</v>
+      </c>
+      <c r="AD54" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE54" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF54" s="15" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="AG54" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH54" s="15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI54" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ54" s="15" t="n">
+        <v>54.89</v>
+      </c>
+      <c r="AK54" s="15" t="n">
+        <v>-14721.29</v>
+      </c>
+      <c r="AL54" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM54" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN54" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -21313,7 +22020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22090,6 +22797,39 @@
         <v>56655.75</v>
       </c>
       <c r="G24" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>57750.02</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <v>56721.77</v>
+      </c>
+      <c r="G25" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -22109,7 +22849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA27"/>
+  <dimension ref="A1:AA28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -24755,6 +25495,105 @@
         <v>1000</v>
       </c>
       <c r="AA27" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>11:22 ET</t>
+        </is>
+      </c>
+      <c r="H28" s="17" t="n">
+        <v>29953.5</v>
+      </c>
+      <c r="I28" s="17" t="n">
+        <v>29950</v>
+      </c>
+      <c r="J28" s="17" t="n">
+        <v>29975</v>
+      </c>
+      <c r="K28" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="L28" s="17" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="M28" s="17" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="N28" s="17" t="n">
+        <v>988.3200000000001</v>
+      </c>
+      <c r="O28" s="17" t="n">
+        <v>1490.4</v>
+      </c>
+      <c r="P28" s="17" t="n">
+        <v>272.88</v>
+      </c>
+      <c r="Q28" s="17" t="n">
+        <v>272.88</v>
+      </c>
+      <c r="R28" s="17" t="n">
+        <v>273.12</v>
+      </c>
+      <c r="S28" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T28" s="17" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="U28" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="V28" s="17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="W28" s="17" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="X28" s="17" t="n">
+        <v>194.4</v>
+      </c>
+      <c r="Y28" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z28" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA28" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -24874,7 +25713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -26689,6 +27528,76 @@
       <c r="I52" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — STOP LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B53" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C53" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D53" s="19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E53" s="19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F53" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G53" s="19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H53" s="19" t="n">
+        <v>37</v>
+      </c>
+      <c r="I53" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B54" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C54" s="19" t="n">
+        <v>48</v>
+      </c>
+      <c r="D54" s="19" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E54" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="F54" s="19" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G54" s="19" t="n">
+        <v>39.36</v>
+      </c>
+      <c r="H54" s="19" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="I54" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — PROFIT</t>
         </is>
       </c>
     </row>
@@ -27155,7 +28064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN27"/>
+  <dimension ref="A1:AN28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -31163,6 +32072,158 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(24270.85&gt;24175.7) &amp; EMA9↑(24043.47&gt;23837.96)</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="n">
+        <v>24043.47</v>
+      </c>
+      <c r="I28" s="15" t="n">
+        <v>23837.96</v>
+      </c>
+      <c r="J28" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K28" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L28" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M28" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N28" s="15" t="inlineStr">
+        <is>
+          <t>10:18 IST</t>
+        </is>
+      </c>
+      <c r="O28" s="15" t="n">
+        <v>24270.85</v>
+      </c>
+      <c r="P28" s="15" t="n">
+        <v>24175.7</v>
+      </c>
+      <c r="Q28" s="15" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="R28" s="15" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="S28" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="T28" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U28" s="15" t="n">
+        <v>1430</v>
+      </c>
+      <c r="V28" s="15" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="W28" s="15" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="X28" s="15" t="n">
+        <v>48262.5</v>
+      </c>
+      <c r="Y28" s="15" t="n">
+        <v>48317.29</v>
+      </c>
+      <c r="Z28" s="15" t="n">
+        <v>94737.5</v>
+      </c>
+      <c r="AA28" s="15" t="n">
+        <v>14478.75</v>
+      </c>
+      <c r="AB28" s="15" t="n">
+        <v>14478.75</v>
+      </c>
+      <c r="AC28" s="15" t="n">
+        <v>-14485.9</v>
+      </c>
+      <c r="AD28" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE28" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF28" s="15" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AG28" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH28" s="15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI28" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ28" s="15" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="AK28" s="15" t="n">
+        <v>-14540.69</v>
+      </c>
+      <c r="AL28" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM28" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN28" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -31177,7 +32238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN27"/>
+  <dimension ref="A1:AN28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -35185,6 +36246,158 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24270.85&gt;24175.7) &amp; EMA9↑(24043.47&gt;23837.96)</t>
+        </is>
+      </c>
+      <c r="H28" s="17" t="n">
+        <v>24043.47</v>
+      </c>
+      <c r="I28" s="17" t="n">
+        <v>23837.96</v>
+      </c>
+      <c r="J28" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K28" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L28" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M28" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N28" s="17" t="inlineStr">
+        <is>
+          <t>10:18 IST</t>
+        </is>
+      </c>
+      <c r="O28" s="17" t="n">
+        <v>24270.85</v>
+      </c>
+      <c r="P28" s="17" t="n">
+        <v>24175.7</v>
+      </c>
+      <c r="Q28" s="17" t="inlineStr">
+        <is>
+          <t>24300 PE</t>
+        </is>
+      </c>
+      <c r="R28" s="17" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="S28" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="T28" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U28" s="17" t="n">
+        <v>1235</v>
+      </c>
+      <c r="V28" s="17" t="n">
+        <v>38.72</v>
+      </c>
+      <c r="W28" s="17" t="n">
+        <v>50.34</v>
+      </c>
+      <c r="X28" s="17" t="n">
+        <v>47819.2</v>
+      </c>
+      <c r="Y28" s="17" t="n">
+        <v>47873.92</v>
+      </c>
+      <c r="Z28" s="17" t="n">
+        <v>75680.8</v>
+      </c>
+      <c r="AA28" s="17" t="n">
+        <v>14345.76</v>
+      </c>
+      <c r="AB28" s="17" t="n">
+        <v>14345.76</v>
+      </c>
+      <c r="AC28" s="17" t="n">
+        <v>14350.7</v>
+      </c>
+      <c r="AD28" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE28" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF28" s="17" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AG28" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH28" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI28" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ28" s="17" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="AK28" s="17" t="n">
+        <v>14295.98</v>
+      </c>
+      <c r="AL28" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM28" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN28" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -35199,7 +36412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN52"/>
+  <dimension ref="A1:AN54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42967,6 +44180,310 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B53" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D53" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E53" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F53" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G53" s="16" t="inlineStr">
+        <is>
+          <t>Price↑(24270.85&gt;24175.7) &amp; EMA9↑(24043.47&gt;23837.96)</t>
+        </is>
+      </c>
+      <c r="H53" s="16" t="n">
+        <v>24043.47</v>
+      </c>
+      <c r="I53" s="16" t="n">
+        <v>23837.96</v>
+      </c>
+      <c r="J53" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K53" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L53" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M53" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N53" s="16" t="inlineStr">
+        <is>
+          <t>13:39 IST</t>
+        </is>
+      </c>
+      <c r="O53" s="16" t="n">
+        <v>24270.85</v>
+      </c>
+      <c r="P53" s="16" t="n">
+        <v>24175.7</v>
+      </c>
+      <c r="Q53" s="16" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="R53" s="16" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="S53" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="T53" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U53" s="16" t="n">
+        <v>1560</v>
+      </c>
+      <c r="V53" s="16" t="n">
+        <v>30.42</v>
+      </c>
+      <c r="W53" s="16" t="n">
+        <v>30.65</v>
+      </c>
+      <c r="X53" s="16" t="n">
+        <v>47455.2</v>
+      </c>
+      <c r="Y53" s="16" t="n">
+        <v>47509.87</v>
+      </c>
+      <c r="Z53" s="16" t="n">
+        <v>108544.8</v>
+      </c>
+      <c r="AA53" s="16" t="n">
+        <v>14236.56</v>
+      </c>
+      <c r="AB53" s="16" t="n">
+        <v>14236.56</v>
+      </c>
+      <c r="AC53" s="16" t="n">
+        <v>358.8</v>
+      </c>
+      <c r="AD53" s="16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AE53" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF53" s="16" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="AG53" s="16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH53" s="16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI53" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ53" s="16" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="AK53" s="16" t="n">
+        <v>304.13</v>
+      </c>
+      <c r="AL53" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM53" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN53" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E54" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G54" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24270.85&gt;24175.7) &amp; EMA9↑(24043.47&gt;23837.96)</t>
+        </is>
+      </c>
+      <c r="H54" s="17" t="n">
+        <v>24043.47</v>
+      </c>
+      <c r="I54" s="17" t="n">
+        <v>23837.96</v>
+      </c>
+      <c r="J54" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K54" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L54" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M54" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N54" s="17" t="inlineStr">
+        <is>
+          <t>11:20 IST</t>
+        </is>
+      </c>
+      <c r="O54" s="17" t="n">
+        <v>24270.85</v>
+      </c>
+      <c r="P54" s="17" t="n">
+        <v>24175.7</v>
+      </c>
+      <c r="Q54" s="17" t="inlineStr">
+        <is>
+          <t>24300 PE</t>
+        </is>
+      </c>
+      <c r="R54" s="17" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="S54" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="T54" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U54" s="17" t="n">
+        <v>1885</v>
+      </c>
+      <c r="V54" s="17" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="W54" s="17" t="n">
+        <v>33.49</v>
+      </c>
+      <c r="X54" s="17" t="n">
+        <v>48557.6</v>
+      </c>
+      <c r="Y54" s="17" t="n">
+        <v>48612.44</v>
+      </c>
+      <c r="Z54" s="17" t="n">
+        <v>139942.4</v>
+      </c>
+      <c r="AA54" s="17" t="n">
+        <v>14567.28</v>
+      </c>
+      <c r="AB54" s="17" t="n">
+        <v>14567.28</v>
+      </c>
+      <c r="AC54" s="17" t="n">
+        <v>14571.05</v>
+      </c>
+      <c r="AD54" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE54" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF54" s="17" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="AG54" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH54" s="17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI54" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ54" s="17" t="n">
+        <v>54.84</v>
+      </c>
+      <c r="AK54" s="17" t="n">
+        <v>14516.21</v>
+      </c>
+      <c r="AL54" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM54" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN54" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -42981,7 +44498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN17"/>
+  <dimension ref="A1:AN18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -45494,6 +47011,158 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G18" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24270.85&gt;24175.7) &amp; EMA9↑(24043.47&gt;23837.96)</t>
+        </is>
+      </c>
+      <c r="H18" s="17" t="n">
+        <v>24043.47</v>
+      </c>
+      <c r="I18" s="17" t="n">
+        <v>23837.96</v>
+      </c>
+      <c r="J18" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K18" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L18" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N18" s="17" t="inlineStr">
+        <is>
+          <t>11:22 IST</t>
+        </is>
+      </c>
+      <c r="O18" s="17" t="n">
+        <v>24270.85</v>
+      </c>
+      <c r="P18" s="17" t="n">
+        <v>24175.7</v>
+      </c>
+      <c r="Q18" s="17" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="R18" s="17" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="S18" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="T18" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U18" s="17" t="n">
+        <v>1690</v>
+      </c>
+      <c r="V18" s="17" t="n">
+        <v>28.39</v>
+      </c>
+      <c r="W18" s="17" t="n">
+        <v>36.91</v>
+      </c>
+      <c r="X18" s="17" t="n">
+        <v>47979.1</v>
+      </c>
+      <c r="Y18" s="17" t="n">
+        <v>48033.85</v>
+      </c>
+      <c r="Z18" s="17" t="n">
+        <v>121020.9</v>
+      </c>
+      <c r="AA18" s="17" t="n">
+        <v>14393.73</v>
+      </c>
+      <c r="AB18" s="17" t="n">
+        <v>14393.73</v>
+      </c>
+      <c r="AC18" s="17" t="n">
+        <v>14398.8</v>
+      </c>
+      <c r="AD18" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE18" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF18" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG18" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH18" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI18" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ18" s="17" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="AK18" s="17" t="n">
+        <v>14344.05</v>
+      </c>
+      <c r="AL18" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM18" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN18" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA28"/>
+  <dimension ref="A1:AA29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3354,6 +3354,105 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>10:35 ET</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>29685.5</v>
+      </c>
+      <c r="I29" s="15" t="n">
+        <v>29675</v>
+      </c>
+      <c r="J29" s="15" t="n">
+        <v>29700</v>
+      </c>
+      <c r="K29" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="L29" s="15" t="n">
+        <v>192.6</v>
+      </c>
+      <c r="M29" s="15" t="n">
+        <v>134.82</v>
+      </c>
+      <c r="N29" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O29" s="15" t="n">
+        <v>1537</v>
+      </c>
+      <c r="P29" s="15" t="n">
+        <v>288.9</v>
+      </c>
+      <c r="Q29" s="15" t="n">
+        <v>288.9</v>
+      </c>
+      <c r="R29" s="15" t="n">
+        <v>-288.9</v>
+      </c>
+      <c r="S29" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="T29" s="15" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="U29" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="V29" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W29" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="X29" s="15" t="n">
+        <v>-325.9</v>
+      </c>
+      <c r="Y29" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="Z29" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA29" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -3368,7 +3467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN28"/>
+  <dimension ref="A1:AN29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7528,6 +7627,158 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H29" s="17" t="n">
+        <v>57924.34</v>
+      </c>
+      <c r="I29" s="17" t="n">
+        <v>56950.61</v>
+      </c>
+      <c r="J29" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K29" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L29" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="M29" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N29" s="17" t="inlineStr">
+        <is>
+          <t>10:00 IST</t>
+        </is>
+      </c>
+      <c r="O29" s="17" t="n">
+        <v>58200.7</v>
+      </c>
+      <c r="P29" s="17" t="n">
+        <v>58291.5</v>
+      </c>
+      <c r="Q29" s="17" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="R29" s="17" t="inlineStr">
+        <is>
+          <t>58400 CE</t>
+        </is>
+      </c>
+      <c r="S29" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="T29" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U29" s="17" t="n">
+        <v>480</v>
+      </c>
+      <c r="V29" s="17" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="W29" s="17" t="n">
+        <v>130.78</v>
+      </c>
+      <c r="X29" s="17" t="n">
+        <v>48288</v>
+      </c>
+      <c r="Y29" s="17" t="n">
+        <v>48342.8</v>
+      </c>
+      <c r="Z29" s="17" t="n">
+        <v>47712</v>
+      </c>
+      <c r="AA29" s="17" t="n">
+        <v>14486.4</v>
+      </c>
+      <c r="AB29" s="17" t="n">
+        <v>14486.4</v>
+      </c>
+      <c r="AC29" s="17" t="n">
+        <v>14486.4</v>
+      </c>
+      <c r="AD29" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE29" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF29" s="17" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="AG29" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH29" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI29" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ29" s="17" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="AK29" s="17" t="n">
+        <v>14431.6</v>
+      </c>
+      <c r="AL29" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM29" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN29" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -7542,7 +7793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN28"/>
+  <dimension ref="A1:AN29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11702,6 +11953,158 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G29" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H29" s="16" t="n">
+        <v>57924.34</v>
+      </c>
+      <c r="I29" s="16" t="n">
+        <v>56950.61</v>
+      </c>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K29" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L29" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="M29" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N29" s="16" t="inlineStr">
+        <is>
+          <t>14:24 IST</t>
+        </is>
+      </c>
+      <c r="O29" s="16" t="n">
+        <v>58200.7</v>
+      </c>
+      <c r="P29" s="16" t="n">
+        <v>58291.5</v>
+      </c>
+      <c r="Q29" s="16" t="inlineStr">
+        <is>
+          <t>58400 PE</t>
+        </is>
+      </c>
+      <c r="R29" s="16" t="inlineStr">
+        <is>
+          <t>58200 PE</t>
+        </is>
+      </c>
+      <c r="S29" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="T29" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U29" s="16" t="n">
+        <v>570</v>
+      </c>
+      <c r="V29" s="16" t="n">
+        <v>83.84999999999999</v>
+      </c>
+      <c r="W29" s="16" t="n">
+        <v>83.58</v>
+      </c>
+      <c r="X29" s="16" t="n">
+        <v>47794.5</v>
+      </c>
+      <c r="Y29" s="16" t="n">
+        <v>47849.22</v>
+      </c>
+      <c r="Z29" s="16" t="n">
+        <v>66205.5</v>
+      </c>
+      <c r="AA29" s="16" t="n">
+        <v>14338.35</v>
+      </c>
+      <c r="AB29" s="16" t="n">
+        <v>14338.35</v>
+      </c>
+      <c r="AC29" s="16" t="n">
+        <v>-153.9</v>
+      </c>
+      <c r="AD29" s="16" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AE29" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF29" s="16" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="AG29" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH29" s="16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI29" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ29" s="16" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="AK29" s="16" t="n">
+        <v>-208.62</v>
+      </c>
+      <c r="AL29" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM29" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN29" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -11716,7 +12119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN54"/>
+  <dimension ref="A1:AN56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -19783,6 +20186,310 @@
         <v>50000</v>
       </c>
       <c r="AN54" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C55" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D55" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E55" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F55" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G55" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H55" s="17" t="n">
+        <v>57924.34</v>
+      </c>
+      <c r="I55" s="17" t="n">
+        <v>56950.61</v>
+      </c>
+      <c r="J55" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K55" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L55" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="M55" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N55" s="17" t="inlineStr">
+        <is>
+          <t>10:42 IST</t>
+        </is>
+      </c>
+      <c r="O55" s="17" t="n">
+        <v>58200.7</v>
+      </c>
+      <c r="P55" s="17" t="n">
+        <v>58291.5</v>
+      </c>
+      <c r="Q55" s="17" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="R55" s="17" t="inlineStr">
+        <is>
+          <t>58400 CE</t>
+        </is>
+      </c>
+      <c r="S55" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U55" s="17" t="n">
+        <v>450</v>
+      </c>
+      <c r="V55" s="17" t="n">
+        <v>107.31</v>
+      </c>
+      <c r="W55" s="17" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="X55" s="17" t="n">
+        <v>48289.5</v>
+      </c>
+      <c r="Y55" s="17" t="n">
+        <v>48344.3</v>
+      </c>
+      <c r="Z55" s="17" t="n">
+        <v>41710.5</v>
+      </c>
+      <c r="AA55" s="17" t="n">
+        <v>14486.85</v>
+      </c>
+      <c r="AB55" s="17" t="n">
+        <v>14486.85</v>
+      </c>
+      <c r="AC55" s="17" t="n">
+        <v>14485.5</v>
+      </c>
+      <c r="AD55" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE55" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF55" s="17" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="AG55" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH55" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI55" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ55" s="17" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="AK55" s="17" t="n">
+        <v>14430.7</v>
+      </c>
+      <c r="AL55" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM55" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN55" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B56" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D56" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E56" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F56" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G56" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H56" s="16" t="n">
+        <v>57924.34</v>
+      </c>
+      <c r="I56" s="16" t="n">
+        <v>56950.61</v>
+      </c>
+      <c r="J56" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K56" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L56" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="M56" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N56" s="16" t="inlineStr">
+        <is>
+          <t>14:30 IST</t>
+        </is>
+      </c>
+      <c r="O56" s="16" t="n">
+        <v>58200.7</v>
+      </c>
+      <c r="P56" s="16" t="n">
+        <v>58291.5</v>
+      </c>
+      <c r="Q56" s="16" t="inlineStr">
+        <is>
+          <t>58400 PE</t>
+        </is>
+      </c>
+      <c r="R56" s="16" t="inlineStr">
+        <is>
+          <t>58200 PE</t>
+        </is>
+      </c>
+      <c r="S56" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U56" s="16" t="n">
+        <v>450</v>
+      </c>
+      <c r="V56" s="16" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="W56" s="16" t="n">
+        <v>100.86</v>
+      </c>
+      <c r="X56" s="16" t="n">
+        <v>46305</v>
+      </c>
+      <c r="Y56" s="16" t="n">
+        <v>46359.49</v>
+      </c>
+      <c r="Z56" s="16" t="n">
+        <v>43695</v>
+      </c>
+      <c r="AA56" s="16" t="n">
+        <v>13891.5</v>
+      </c>
+      <c r="AB56" s="16" t="n">
+        <v>13891.5</v>
+      </c>
+      <c r="AC56" s="16" t="n">
+        <v>-918</v>
+      </c>
+      <c r="AD56" s="16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE56" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF56" s="16" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="AG56" s="16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH56" s="16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI56" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ56" s="16" t="n">
+        <v>54.49</v>
+      </c>
+      <c r="AK56" s="16" t="n">
+        <v>-972.49</v>
+      </c>
+      <c r="AL56" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM56" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN56" s="16" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -22020,7 +22727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22830,6 +23537,72 @@
         <v>56721.77</v>
       </c>
       <c r="G25" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>24176.1</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <v>23922.87</v>
+      </c>
+      <c r="G26" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>57924.34</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>56950.61</v>
+      </c>
+      <c r="G27" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -22849,7 +23622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA28"/>
+  <dimension ref="A1:AA29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -25594,6 +26367,105 @@
         <v>1000</v>
       </c>
       <c r="AA28" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G29" s="16" t="inlineStr">
+        <is>
+          <t>15:52 ET</t>
+        </is>
+      </c>
+      <c r="H29" s="16" t="n">
+        <v>29685</v>
+      </c>
+      <c r="I29" s="16" t="n">
+        <v>29675</v>
+      </c>
+      <c r="J29" s="16" t="n">
+        <v>29700</v>
+      </c>
+      <c r="K29" s="16" t="n">
+        <v>51</v>
+      </c>
+      <c r="L29" s="16" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="M29" s="16" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="N29" s="16" t="n">
+        <v>997.05</v>
+      </c>
+      <c r="O29" s="16" t="n">
+        <v>1636.59</v>
+      </c>
+      <c r="P29" s="16" t="n">
+        <v>274.02</v>
+      </c>
+      <c r="Q29" s="16" t="n">
+        <v>274.02</v>
+      </c>
+      <c r="R29" s="16" t="n">
+        <v>13.26</v>
+      </c>
+      <c r="S29" s="16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T29" s="16" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="U29" s="16" t="n">
+        <v>51</v>
+      </c>
+      <c r="V29" s="16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="W29" s="16" t="n">
+        <v>83.64</v>
+      </c>
+      <c r="X29" s="16" t="n">
+        <v>-70.38</v>
+      </c>
+      <c r="Y29" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="Z29" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA29" s="16" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -25713,7 +26585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27598,6 +28470,76 @@
       <c r="I54" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B55" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C55" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D55" s="19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E55" s="19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F55" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G55" s="19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H55" s="19" t="n">
+        <v>37</v>
+      </c>
+      <c r="I55" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — STOP LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B56" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C56" s="19" t="n">
+        <v>51</v>
+      </c>
+      <c r="D56" s="19" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E56" s="19" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F56" s="19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G56" s="19" t="n">
+        <v>41.82</v>
+      </c>
+      <c r="H56" s="19" t="n">
+        <v>83.64</v>
+      </c>
+      <c r="I56" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — FLAT</t>
         </is>
       </c>
     </row>
@@ -28064,7 +29006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN28"/>
+  <dimension ref="A1:AN29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -32224,6 +33166,158 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H29" s="17" t="n">
+        <v>24176.1</v>
+      </c>
+      <c r="I29" s="17" t="n">
+        <v>23922.87</v>
+      </c>
+      <c r="J29" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K29" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L29" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N29" s="17" t="inlineStr">
+        <is>
+          <t>09:56 IST</t>
+        </is>
+      </c>
+      <c r="O29" s="17" t="n">
+        <v>24398.7</v>
+      </c>
+      <c r="P29" s="17" t="n">
+        <v>24430.35</v>
+      </c>
+      <c r="Q29" s="17" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="R29" s="17" t="inlineStr">
+        <is>
+          <t>24400 CE</t>
+        </is>
+      </c>
+      <c r="S29" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="T29" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U29" s="17" t="n">
+        <v>2275</v>
+      </c>
+      <c r="V29" s="17" t="n">
+        <v>21.27</v>
+      </c>
+      <c r="W29" s="17" t="n">
+        <v>27.65</v>
+      </c>
+      <c r="X29" s="17" t="n">
+        <v>48389.25</v>
+      </c>
+      <c r="Y29" s="17" t="n">
+        <v>48444.06</v>
+      </c>
+      <c r="Z29" s="17" t="n">
+        <v>179110.75</v>
+      </c>
+      <c r="AA29" s="17" t="n">
+        <v>14516.77</v>
+      </c>
+      <c r="AB29" s="17" t="n">
+        <v>14516.77</v>
+      </c>
+      <c r="AC29" s="17" t="n">
+        <v>14514.5</v>
+      </c>
+      <c r="AD29" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE29" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF29" s="17" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AG29" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH29" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI29" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ29" s="17" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="AK29" s="17" t="n">
+        <v>14459.69</v>
+      </c>
+      <c r="AL29" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM29" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN29" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -32238,7 +33332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN28"/>
+  <dimension ref="A1:AN29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -36398,6 +37492,158 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H29" s="17" t="n">
+        <v>24176.1</v>
+      </c>
+      <c r="I29" s="17" t="n">
+        <v>23922.87</v>
+      </c>
+      <c r="J29" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K29" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L29" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N29" s="17" t="inlineStr">
+        <is>
+          <t>10:29 IST</t>
+        </is>
+      </c>
+      <c r="O29" s="17" t="n">
+        <v>24398.7</v>
+      </c>
+      <c r="P29" s="17" t="n">
+        <v>24430.35</v>
+      </c>
+      <c r="Q29" s="17" t="inlineStr">
+        <is>
+          <t>24400 PE</t>
+        </is>
+      </c>
+      <c r="R29" s="17" t="inlineStr">
+        <is>
+          <t>24300 PE</t>
+        </is>
+      </c>
+      <c r="S29" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="T29" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U29" s="17" t="n">
+        <v>2340</v>
+      </c>
+      <c r="V29" s="17" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="W29" s="17" t="n">
+        <v>26.69</v>
+      </c>
+      <c r="X29" s="17" t="n">
+        <v>48040.2</v>
+      </c>
+      <c r="Y29" s="17" t="n">
+        <v>48094.96</v>
+      </c>
+      <c r="Z29" s="17" t="n">
+        <v>185959.8</v>
+      </c>
+      <c r="AA29" s="17" t="n">
+        <v>14412.06</v>
+      </c>
+      <c r="AB29" s="17" t="n">
+        <v>14412.06</v>
+      </c>
+      <c r="AC29" s="17" t="n">
+        <v>14414.4</v>
+      </c>
+      <c r="AD29" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE29" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF29" s="17" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="AG29" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH29" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI29" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ29" s="17" t="n">
+        <v>54.76</v>
+      </c>
+      <c r="AK29" s="17" t="n">
+        <v>14359.64</v>
+      </c>
+      <c r="AL29" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM29" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN29" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -36412,7 +37658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN54"/>
+  <dimension ref="A1:AN56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -44479,6 +45725,310 @@
         <v>50000</v>
       </c>
       <c r="AN54" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D55" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E55" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F55" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G55" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>24176.1</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>23922.87</v>
+      </c>
+      <c r="J55" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K55" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L55" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M55" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N55" s="15" t="inlineStr">
+        <is>
+          <t>10:22 IST</t>
+        </is>
+      </c>
+      <c r="O55" s="15" t="n">
+        <v>24398.7</v>
+      </c>
+      <c r="P55" s="15" t="n">
+        <v>24430.35</v>
+      </c>
+      <c r="Q55" s="15" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="R55" s="15" t="inlineStr">
+        <is>
+          <t>24400 CE</t>
+        </is>
+      </c>
+      <c r="S55" s="15" t="n">
+        <v>31</v>
+      </c>
+      <c r="T55" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U55" s="15" t="n">
+        <v>2015</v>
+      </c>
+      <c r="V55" s="15" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="W55" s="15" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="X55" s="15" t="n">
+        <v>48158.5</v>
+      </c>
+      <c r="Y55" s="15" t="n">
+        <v>48213.28</v>
+      </c>
+      <c r="Z55" s="15" t="n">
+        <v>153341.5</v>
+      </c>
+      <c r="AA55" s="15" t="n">
+        <v>14447.55</v>
+      </c>
+      <c r="AB55" s="15" t="n">
+        <v>14447.55</v>
+      </c>
+      <c r="AC55" s="15" t="n">
+        <v>-14447.55</v>
+      </c>
+      <c r="AD55" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE55" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF55" s="15" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="AG55" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH55" s="15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI55" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ55" s="15" t="n">
+        <v>54.78</v>
+      </c>
+      <c r="AK55" s="15" t="n">
+        <v>-14502.33</v>
+      </c>
+      <c r="AL55" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM55" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN55" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D56" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E56" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F56" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G56" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="n">
+        <v>24176.1</v>
+      </c>
+      <c r="I56" s="15" t="n">
+        <v>23922.87</v>
+      </c>
+      <c r="J56" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K56" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L56" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M56" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N56" s="15" t="inlineStr">
+        <is>
+          <t>11:10 IST</t>
+        </is>
+      </c>
+      <c r="O56" s="15" t="n">
+        <v>24398.7</v>
+      </c>
+      <c r="P56" s="15" t="n">
+        <v>24430.35</v>
+      </c>
+      <c r="Q56" s="15" t="inlineStr">
+        <is>
+          <t>24400 PE</t>
+        </is>
+      </c>
+      <c r="R56" s="15" t="inlineStr">
+        <is>
+          <t>24300 PE</t>
+        </is>
+      </c>
+      <c r="S56" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="T56" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U56" s="15" t="n">
+        <v>2340</v>
+      </c>
+      <c r="V56" s="15" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="W56" s="15" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="X56" s="15" t="n">
+        <v>47619</v>
+      </c>
+      <c r="Y56" s="15" t="n">
+        <v>47673.69</v>
+      </c>
+      <c r="Z56" s="15" t="n">
+        <v>186381</v>
+      </c>
+      <c r="AA56" s="15" t="n">
+        <v>14285.7</v>
+      </c>
+      <c r="AB56" s="15" t="n">
+        <v>14285.7</v>
+      </c>
+      <c r="AC56" s="15" t="n">
+        <v>-14297.4</v>
+      </c>
+      <c r="AD56" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE56" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF56" s="15" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AG56" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH56" s="15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI56" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ56" s="15" t="n">
+        <v>54.69</v>
+      </c>
+      <c r="AK56" s="15" t="n">
+        <v>-14352.09</v>
+      </c>
+      <c r="AL56" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM56" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN56" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA29"/>
+  <dimension ref="A1:AA30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3453,6 +3453,105 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="inlineStr">
+        <is>
+          <t>12:04 ET</t>
+        </is>
+      </c>
+      <c r="H30" s="17" t="n">
+        <v>29407.25</v>
+      </c>
+      <c r="I30" s="17" t="n">
+        <v>29400</v>
+      </c>
+      <c r="J30" s="17" t="n">
+        <v>29425</v>
+      </c>
+      <c r="K30" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L30" s="17" t="n">
+        <v>196.4</v>
+      </c>
+      <c r="M30" s="17" t="n">
+        <v>255.32</v>
+      </c>
+      <c r="N30" s="17" t="n">
+        <v>815.2</v>
+      </c>
+      <c r="O30" s="17" t="n">
+        <v>1214.4</v>
+      </c>
+      <c r="P30" s="17" t="n">
+        <v>235.68</v>
+      </c>
+      <c r="Q30" s="17" t="n">
+        <v>235.68</v>
+      </c>
+      <c r="R30" s="17" t="n">
+        <v>235.68</v>
+      </c>
+      <c r="S30" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T30" s="17" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="U30" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="V30" s="17" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W30" s="17" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="X30" s="17" t="n">
+        <v>206.08</v>
+      </c>
+      <c r="Y30" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z30" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA30" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -3467,7 +3566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN29"/>
+  <dimension ref="A1:AN30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7779,6 +7878,158 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(58291.5&gt;57938.5) &amp; EMA9↑(57855.26&gt;56825.6)</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v>57855.26</v>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v>56825.6</v>
+      </c>
+      <c r="J30" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K30" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L30" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="M30" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N30" s="15" t="inlineStr">
+        <is>
+          <t>10:13 IST</t>
+        </is>
+      </c>
+      <c r="O30" s="15" t="n">
+        <v>58291.5</v>
+      </c>
+      <c r="P30" s="15" t="n">
+        <v>57938.5</v>
+      </c>
+      <c r="Q30" s="15" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="R30" s="15" t="inlineStr">
+        <is>
+          <t>58400 CE</t>
+        </is>
+      </c>
+      <c r="S30" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="T30" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U30" s="15" t="n">
+        <v>540</v>
+      </c>
+      <c r="V30" s="15" t="n">
+        <v>89.55</v>
+      </c>
+      <c r="W30" s="15" t="n">
+        <v>62.68</v>
+      </c>
+      <c r="X30" s="15" t="n">
+        <v>48357</v>
+      </c>
+      <c r="Y30" s="15" t="n">
+        <v>48411.81</v>
+      </c>
+      <c r="Z30" s="15" t="n">
+        <v>59643</v>
+      </c>
+      <c r="AA30" s="15" t="n">
+        <v>14507.1</v>
+      </c>
+      <c r="AB30" s="15" t="n">
+        <v>14507.1</v>
+      </c>
+      <c r="AC30" s="15" t="n">
+        <v>-14509.8</v>
+      </c>
+      <c r="AD30" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE30" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF30" s="15" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="AG30" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH30" s="15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI30" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ30" s="15" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="AK30" s="15" t="n">
+        <v>-14564.61</v>
+      </c>
+      <c r="AL30" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM30" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN30" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -7793,7 +8044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN29"/>
+  <dimension ref="A1:AN30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12105,6 +12356,158 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G30" s="16" t="inlineStr">
+        <is>
+          <t>Price↑(58291.5&gt;57938.5) &amp; EMA9↑(57855.26&gt;56825.6)</t>
+        </is>
+      </c>
+      <c r="H30" s="16" t="n">
+        <v>57855.26</v>
+      </c>
+      <c r="I30" s="16" t="n">
+        <v>56825.6</v>
+      </c>
+      <c r="J30" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K30" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L30" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="M30" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N30" s="16" t="inlineStr">
+        <is>
+          <t>13:51 IST</t>
+        </is>
+      </c>
+      <c r="O30" s="16" t="n">
+        <v>58291.5</v>
+      </c>
+      <c r="P30" s="16" t="n">
+        <v>57938.5</v>
+      </c>
+      <c r="Q30" s="16" t="inlineStr">
+        <is>
+          <t>58400 PE</t>
+        </is>
+      </c>
+      <c r="R30" s="16" t="inlineStr">
+        <is>
+          <t>58200 PE</t>
+        </is>
+      </c>
+      <c r="S30" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="T30" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U30" s="16" t="n">
+        <v>570</v>
+      </c>
+      <c r="V30" s="16" t="n">
+        <v>83.34999999999999</v>
+      </c>
+      <c r="W30" s="16" t="n">
+        <v>79.18000000000001</v>
+      </c>
+      <c r="X30" s="16" t="n">
+        <v>47509.5</v>
+      </c>
+      <c r="Y30" s="16" t="n">
+        <v>47564.18</v>
+      </c>
+      <c r="Z30" s="16" t="n">
+        <v>66490.5</v>
+      </c>
+      <c r="AA30" s="16" t="n">
+        <v>14252.85</v>
+      </c>
+      <c r="AB30" s="16" t="n">
+        <v>14252.85</v>
+      </c>
+      <c r="AC30" s="16" t="n">
+        <v>-2376.9</v>
+      </c>
+      <c r="AD30" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AE30" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF30" s="16" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AG30" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH30" s="16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI30" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ30" s="16" t="n">
+        <v>54.68</v>
+      </c>
+      <c r="AK30" s="16" t="n">
+        <v>-2431.58</v>
+      </c>
+      <c r="AL30" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM30" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN30" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -12119,7 +12522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN56"/>
+  <dimension ref="A1:AN58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -20495,6 +20898,310 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D57" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E57" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F57" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G57" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(58291.5&gt;57938.5) &amp; EMA9↑(57855.26&gt;56825.6)</t>
+        </is>
+      </c>
+      <c r="H57" s="17" t="n">
+        <v>57855.26</v>
+      </c>
+      <c r="I57" s="17" t="n">
+        <v>56825.6</v>
+      </c>
+      <c r="J57" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K57" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L57" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="M57" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N57" s="17" t="inlineStr">
+        <is>
+          <t>11:52 IST</t>
+        </is>
+      </c>
+      <c r="O57" s="17" t="n">
+        <v>58291.5</v>
+      </c>
+      <c r="P57" s="17" t="n">
+        <v>57938.5</v>
+      </c>
+      <c r="Q57" s="17" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="R57" s="17" t="inlineStr">
+        <is>
+          <t>58400 CE</t>
+        </is>
+      </c>
+      <c r="S57" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="T57" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U57" s="17" t="n">
+        <v>570</v>
+      </c>
+      <c r="V57" s="17" t="n">
+        <v>82.26000000000001</v>
+      </c>
+      <c r="W57" s="17" t="n">
+        <v>106.94</v>
+      </c>
+      <c r="X57" s="17" t="n">
+        <v>46888.2</v>
+      </c>
+      <c r="Y57" s="17" t="n">
+        <v>46942.78</v>
+      </c>
+      <c r="Z57" s="17" t="n">
+        <v>67111.8</v>
+      </c>
+      <c r="AA57" s="17" t="n">
+        <v>14066.46</v>
+      </c>
+      <c r="AB57" s="17" t="n">
+        <v>14066.46</v>
+      </c>
+      <c r="AC57" s="17" t="n">
+        <v>14067.6</v>
+      </c>
+      <c r="AD57" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE57" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF57" s="17" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="AG57" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH57" s="17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI57" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ57" s="17" t="n">
+        <v>54.58</v>
+      </c>
+      <c r="AK57" s="17" t="n">
+        <v>14013.02</v>
+      </c>
+      <c r="AL57" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM57" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN57" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D58" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E58" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F58" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G58" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(58291.5&gt;57938.5) &amp; EMA9↑(57855.26&gt;56825.6)</t>
+        </is>
+      </c>
+      <c r="H58" s="17" t="n">
+        <v>57855.26</v>
+      </c>
+      <c r="I58" s="17" t="n">
+        <v>56825.6</v>
+      </c>
+      <c r="J58" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K58" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L58" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="M58" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N58" s="17" t="inlineStr">
+        <is>
+          <t>11:23 IST</t>
+        </is>
+      </c>
+      <c r="O58" s="17" t="n">
+        <v>58291.5</v>
+      </c>
+      <c r="P58" s="17" t="n">
+        <v>57938.5</v>
+      </c>
+      <c r="Q58" s="17" t="inlineStr">
+        <is>
+          <t>58400 PE</t>
+        </is>
+      </c>
+      <c r="R58" s="17" t="inlineStr">
+        <is>
+          <t>58200 PE</t>
+        </is>
+      </c>
+      <c r="S58" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="T58" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U58" s="17" t="n">
+        <v>540</v>
+      </c>
+      <c r="V58" s="17" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="W58" s="17" t="n">
+        <v>112.84</v>
+      </c>
+      <c r="X58" s="17" t="n">
+        <v>46872</v>
+      </c>
+      <c r="Y58" s="17" t="n">
+        <v>46926.58</v>
+      </c>
+      <c r="Z58" s="17" t="n">
+        <v>61128</v>
+      </c>
+      <c r="AA58" s="17" t="n">
+        <v>14061.6</v>
+      </c>
+      <c r="AB58" s="17" t="n">
+        <v>14061.6</v>
+      </c>
+      <c r="AC58" s="17" t="n">
+        <v>14061.6</v>
+      </c>
+      <c r="AD58" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE58" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF58" s="17" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="AG58" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH58" s="17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI58" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ58" s="17" t="n">
+        <v>54.58</v>
+      </c>
+      <c r="AK58" s="17" t="n">
+        <v>14007.02</v>
+      </c>
+      <c r="AL58" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM58" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN58" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -20509,7 +21216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN15"/>
+  <dimension ref="A1:AN16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22713,6 +23420,158 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(58291.5&gt;57938.5) &amp; EMA9↑(57855.26&gt;56825.6)</t>
+        </is>
+      </c>
+      <c r="H16" s="17" t="n">
+        <v>57855.26</v>
+      </c>
+      <c r="I16" s="17" t="n">
+        <v>56825.6</v>
+      </c>
+      <c r="J16" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K16" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L16" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="M16" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N16" s="17" t="inlineStr">
+        <is>
+          <t>11:26 IST</t>
+        </is>
+      </c>
+      <c r="O16" s="17" t="n">
+        <v>58291.5</v>
+      </c>
+      <c r="P16" s="17" t="n">
+        <v>57938.5</v>
+      </c>
+      <c r="Q16" s="17" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="R16" s="17" t="inlineStr">
+        <is>
+          <t>58400 CE</t>
+        </is>
+      </c>
+      <c r="S16" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U16" s="17" t="n">
+        <v>450</v>
+      </c>
+      <c r="V16" s="17" t="n">
+        <v>109.26</v>
+      </c>
+      <c r="W16" s="17" t="n">
+        <v>142.04</v>
+      </c>
+      <c r="X16" s="17" t="n">
+        <v>49167</v>
+      </c>
+      <c r="Y16" s="17" t="n">
+        <v>49221.94</v>
+      </c>
+      <c r="Z16" s="17" t="n">
+        <v>40833</v>
+      </c>
+      <c r="AA16" s="17" t="n">
+        <v>14750.1</v>
+      </c>
+      <c r="AB16" s="17" t="n">
+        <v>14750.1</v>
+      </c>
+      <c r="AC16" s="17" t="n">
+        <v>14751</v>
+      </c>
+      <c r="AD16" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE16" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF16" s="17" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AG16" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH16" s="17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI16" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ16" s="17" t="n">
+        <v>54.94</v>
+      </c>
+      <c r="AK16" s="17" t="n">
+        <v>14696.06</v>
+      </c>
+      <c r="AL16" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM16" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN16" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -23622,7 +24481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA29"/>
+  <dimension ref="A1:AA30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -26466,6 +27325,105 @@
         <v>1000</v>
       </c>
       <c r="AA29" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>11:02 ET</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v>29407</v>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v>29400</v>
+      </c>
+      <c r="J30" s="15" t="n">
+        <v>29425</v>
+      </c>
+      <c r="K30" s="15" t="n">
+        <v>54</v>
+      </c>
+      <c r="L30" s="15" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="M30" s="15" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="N30" s="15" t="n">
+        <v>985.5</v>
+      </c>
+      <c r="O30" s="15" t="n">
+        <v>1803.06</v>
+      </c>
+      <c r="P30" s="15" t="n">
+        <v>269.08</v>
+      </c>
+      <c r="Q30" s="15" t="n">
+        <v>269.08</v>
+      </c>
+      <c r="R30" s="15" t="n">
+        <v>-268.92</v>
+      </c>
+      <c r="S30" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="T30" s="15" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="U30" s="15" t="n">
+        <v>54</v>
+      </c>
+      <c r="V30" s="15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="W30" s="15" t="n">
+        <v>88.56</v>
+      </c>
+      <c r="X30" s="15" t="n">
+        <v>-357.48</v>
+      </c>
+      <c r="Y30" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="Z30" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA30" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -26585,7 +27543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28540,6 +29498,76 @@
       <c r="I56" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B57" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C57" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D57" s="19" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="E57" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F57" s="19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G57" s="19" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H57" s="19" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I57" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B58" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C58" s="19" t="n">
+        <v>54</v>
+      </c>
+      <c r="D58" s="19" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="E58" s="19" t="n">
+        <v>27</v>
+      </c>
+      <c r="F58" s="19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G58" s="19" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="H58" s="19" t="n">
+        <v>88.56</v>
+      </c>
+      <c r="I58" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — STOP LOSS</t>
         </is>
       </c>
     </row>
@@ -29006,7 +30034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN29"/>
+  <dimension ref="A1:AN30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -33318,6 +34346,158 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(24430.35&gt;24270.85) &amp; EMA9↑(24120.45&gt;23875.28)</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v>24120.45</v>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v>23875.28</v>
+      </c>
+      <c r="J30" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K30" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L30" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M30" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N30" s="15" t="inlineStr">
+        <is>
+          <t>09:34 IST</t>
+        </is>
+      </c>
+      <c r="O30" s="15" t="n">
+        <v>24430.35</v>
+      </c>
+      <c r="P30" s="15" t="n">
+        <v>24270.85</v>
+      </c>
+      <c r="Q30" s="15" t="inlineStr">
+        <is>
+          <t>24400 CE</t>
+        </is>
+      </c>
+      <c r="R30" s="15" t="inlineStr">
+        <is>
+          <t>24500 CE</t>
+        </is>
+      </c>
+      <c r="S30" s="15" t="n">
+        <v>41</v>
+      </c>
+      <c r="T30" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U30" s="15" t="n">
+        <v>2665</v>
+      </c>
+      <c r="V30" s="15" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="W30" s="15" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="X30" s="15" t="n">
+        <v>48049.95</v>
+      </c>
+      <c r="Y30" s="15" t="n">
+        <v>48104.71</v>
+      </c>
+      <c r="Z30" s="15" t="n">
+        <v>218450.05</v>
+      </c>
+      <c r="AA30" s="15" t="n">
+        <v>14414.98</v>
+      </c>
+      <c r="AB30" s="15" t="n">
+        <v>14414.98</v>
+      </c>
+      <c r="AC30" s="15" t="n">
+        <v>-14417.65</v>
+      </c>
+      <c r="AD30" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE30" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF30" s="15" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="AG30" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH30" s="15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI30" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ30" s="15" t="n">
+        <v>54.76</v>
+      </c>
+      <c r="AK30" s="15" t="n">
+        <v>-14472.41</v>
+      </c>
+      <c r="AL30" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM30" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN30" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -33332,7 +34512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN29"/>
+  <dimension ref="A1:AN30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -37644,6 +38824,158 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24430.35&gt;24270.85) &amp; EMA9↑(24120.45&gt;23875.28)</t>
+        </is>
+      </c>
+      <c r="H30" s="17" t="n">
+        <v>24120.45</v>
+      </c>
+      <c r="I30" s="17" t="n">
+        <v>23875.28</v>
+      </c>
+      <c r="J30" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K30" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L30" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M30" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N30" s="17" t="inlineStr">
+        <is>
+          <t>12:09 IST</t>
+        </is>
+      </c>
+      <c r="O30" s="17" t="n">
+        <v>24430.35</v>
+      </c>
+      <c r="P30" s="17" t="n">
+        <v>24270.85</v>
+      </c>
+      <c r="Q30" s="17" t="inlineStr">
+        <is>
+          <t>24500 PE</t>
+        </is>
+      </c>
+      <c r="R30" s="17" t="inlineStr">
+        <is>
+          <t>24400 PE</t>
+        </is>
+      </c>
+      <c r="S30" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="T30" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U30" s="17" t="n">
+        <v>2535</v>
+      </c>
+      <c r="V30" s="17" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="W30" s="17" t="n">
+        <v>24.31</v>
+      </c>
+      <c r="X30" s="17" t="n">
+        <v>47404.5</v>
+      </c>
+      <c r="Y30" s="17" t="n">
+        <v>47459.16</v>
+      </c>
+      <c r="Z30" s="17" t="n">
+        <v>206095.5</v>
+      </c>
+      <c r="AA30" s="17" t="n">
+        <v>14221.35</v>
+      </c>
+      <c r="AB30" s="17" t="n">
+        <v>14221.35</v>
+      </c>
+      <c r="AC30" s="17" t="n">
+        <v>14221.35</v>
+      </c>
+      <c r="AD30" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE30" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF30" s="17" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="AG30" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH30" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI30" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ30" s="17" t="n">
+        <v>54.66</v>
+      </c>
+      <c r="AK30" s="17" t="n">
+        <v>14166.69</v>
+      </c>
+      <c r="AL30" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM30" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN30" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -37658,7 +38990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN56"/>
+  <dimension ref="A1:AN58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -46034,6 +47366,310 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D57" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E57" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F57" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G57" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24430.35&gt;24270.85) &amp; EMA9↑(24120.45&gt;23875.28)</t>
+        </is>
+      </c>
+      <c r="H57" s="17" t="n">
+        <v>24120.45</v>
+      </c>
+      <c r="I57" s="17" t="n">
+        <v>23875.28</v>
+      </c>
+      <c r="J57" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K57" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L57" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M57" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N57" s="17" t="inlineStr">
+        <is>
+          <t>12:10 IST</t>
+        </is>
+      </c>
+      <c r="O57" s="17" t="n">
+        <v>24430.35</v>
+      </c>
+      <c r="P57" s="17" t="n">
+        <v>24270.85</v>
+      </c>
+      <c r="Q57" s="17" t="inlineStr">
+        <is>
+          <t>24400 CE</t>
+        </is>
+      </c>
+      <c r="R57" s="17" t="inlineStr">
+        <is>
+          <t>24500 CE</t>
+        </is>
+      </c>
+      <c r="S57" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="T57" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U57" s="17" t="n">
+        <v>2275</v>
+      </c>
+      <c r="V57" s="17" t="n">
+        <v>21.19</v>
+      </c>
+      <c r="W57" s="17" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="X57" s="17" t="n">
+        <v>48207.25</v>
+      </c>
+      <c r="Y57" s="17" t="n">
+        <v>48262.04</v>
+      </c>
+      <c r="Z57" s="17" t="n">
+        <v>179292.75</v>
+      </c>
+      <c r="AA57" s="17" t="n">
+        <v>14462.17</v>
+      </c>
+      <c r="AB57" s="17" t="n">
+        <v>14462.17</v>
+      </c>
+      <c r="AC57" s="17" t="n">
+        <v>14469</v>
+      </c>
+      <c r="AD57" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE57" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF57" s="17" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AG57" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH57" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI57" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ57" s="17" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="AK57" s="17" t="n">
+        <v>14414.21</v>
+      </c>
+      <c r="AL57" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM57" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN57" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C58" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E58" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F58" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G58" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(24430.35&gt;24270.85) &amp; EMA9↑(24120.45&gt;23875.28)</t>
+        </is>
+      </c>
+      <c r="H58" s="15" t="n">
+        <v>24120.45</v>
+      </c>
+      <c r="I58" s="15" t="n">
+        <v>23875.28</v>
+      </c>
+      <c r="J58" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K58" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L58" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M58" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N58" s="15" t="inlineStr">
+        <is>
+          <t>09:48 IST</t>
+        </is>
+      </c>
+      <c r="O58" s="15" t="n">
+        <v>24430.35</v>
+      </c>
+      <c r="P58" s="15" t="n">
+        <v>24270.85</v>
+      </c>
+      <c r="Q58" s="15" t="inlineStr">
+        <is>
+          <t>24500 PE</t>
+        </is>
+      </c>
+      <c r="R58" s="15" t="inlineStr">
+        <is>
+          <t>24400 PE</t>
+        </is>
+      </c>
+      <c r="S58" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="T58" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U58" s="15" t="n">
+        <v>2470</v>
+      </c>
+      <c r="V58" s="15" t="n">
+        <v>19.39</v>
+      </c>
+      <c r="W58" s="15" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="X58" s="15" t="n">
+        <v>47893.3</v>
+      </c>
+      <c r="Y58" s="15" t="n">
+        <v>47948.04</v>
+      </c>
+      <c r="Z58" s="15" t="n">
+        <v>199106.7</v>
+      </c>
+      <c r="AA58" s="15" t="n">
+        <v>14367.99</v>
+      </c>
+      <c r="AB58" s="15" t="n">
+        <v>14367.99</v>
+      </c>
+      <c r="AC58" s="15" t="n">
+        <v>-14375.4</v>
+      </c>
+      <c r="AD58" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE58" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF58" s="15" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="AG58" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH58" s="15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI58" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ58" s="15" t="n">
+        <v>54.74</v>
+      </c>
+      <c r="AK58" s="15" t="n">
+        <v>-14430.14</v>
+      </c>
+      <c r="AL58" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM58" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN58" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -46048,7 +47684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN18"/>
+  <dimension ref="A1:AN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -48713,6 +50349,158 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G19" s="16" t="inlineStr">
+        <is>
+          <t>Price↑(24430.35&gt;24270.85) &amp; EMA9↑(24120.45&gt;23875.28)</t>
+        </is>
+      </c>
+      <c r="H19" s="16" t="n">
+        <v>24120.45</v>
+      </c>
+      <c r="I19" s="16" t="n">
+        <v>23875.28</v>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K19" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L19" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N19" s="16" t="inlineStr">
+        <is>
+          <t>14:34 IST</t>
+        </is>
+      </c>
+      <c r="O19" s="16" t="n">
+        <v>24430.35</v>
+      </c>
+      <c r="P19" s="16" t="n">
+        <v>24270.85</v>
+      </c>
+      <c r="Q19" s="16" t="inlineStr">
+        <is>
+          <t>24400 CE</t>
+        </is>
+      </c>
+      <c r="R19" s="16" t="inlineStr">
+        <is>
+          <t>24500 CE</t>
+        </is>
+      </c>
+      <c r="S19" s="16" t="n">
+        <v>31</v>
+      </c>
+      <c r="T19" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U19" s="16" t="n">
+        <v>2015</v>
+      </c>
+      <c r="V19" s="16" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="W19" s="16" t="n">
+        <v>24.03</v>
+      </c>
+      <c r="X19" s="16" t="n">
+        <v>47453.25</v>
+      </c>
+      <c r="Y19" s="16" t="n">
+        <v>47507.92</v>
+      </c>
+      <c r="Z19" s="16" t="n">
+        <v>154046.75</v>
+      </c>
+      <c r="AA19" s="16" t="n">
+        <v>14235.98</v>
+      </c>
+      <c r="AB19" s="16" t="n">
+        <v>14235.98</v>
+      </c>
+      <c r="AC19" s="16" t="n">
+        <v>967.2</v>
+      </c>
+      <c r="AD19" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE19" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF19" s="16" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="AG19" s="16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH19" s="16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI19" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ19" s="16" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="AK19" s="16" t="n">
+        <v>912.53</v>
+      </c>
+      <c r="AL19" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM19" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN19" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA30"/>
+  <dimension ref="A1:AA31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3552,6 +3552,105 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>10:15 ET</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="n">
+        <v>29001.75</v>
+      </c>
+      <c r="I31" s="15" t="n">
+        <v>29000</v>
+      </c>
+      <c r="J31" s="15" t="n">
+        <v>29025</v>
+      </c>
+      <c r="K31" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="L31" s="15" t="n">
+        <v>164.82</v>
+      </c>
+      <c r="M31" s="15" t="n">
+        <v>115.37</v>
+      </c>
+      <c r="N31" s="15" t="n">
+        <v>861.1</v>
+      </c>
+      <c r="O31" s="15" t="n">
+        <v>1675.9</v>
+      </c>
+      <c r="P31" s="15" t="n">
+        <v>247.23</v>
+      </c>
+      <c r="Q31" s="15" t="n">
+        <v>247.23</v>
+      </c>
+      <c r="R31" s="15" t="n">
+        <v>-247.25</v>
+      </c>
+      <c r="S31" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="T31" s="15" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="U31" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="V31" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W31" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="X31" s="15" t="n">
+        <v>-284.25</v>
+      </c>
+      <c r="Y31" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="Z31" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA31" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -3566,7 +3665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN30"/>
+  <dimension ref="A1:AN31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8030,6 +8129,158 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G31" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H31" s="16" t="n">
+        <v>57686.08</v>
+      </c>
+      <c r="I31" s="16" t="n">
+        <v>56919.04</v>
+      </c>
+      <c r="J31" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K31" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L31" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="M31" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N31" s="16" t="inlineStr">
+        <is>
+          <t>13:54 IST</t>
+        </is>
+      </c>
+      <c r="O31" s="16" t="n">
+        <v>56742.6</v>
+      </c>
+      <c r="P31" s="16" t="n">
+        <v>58200.7</v>
+      </c>
+      <c r="Q31" s="16" t="inlineStr">
+        <is>
+          <t>56600 CE</t>
+        </is>
+      </c>
+      <c r="R31" s="16" t="inlineStr">
+        <is>
+          <t>56800 CE</t>
+        </is>
+      </c>
+      <c r="S31" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="T31" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U31" s="16" t="n">
+        <v>570</v>
+      </c>
+      <c r="V31" s="16" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="W31" s="16" t="n">
+        <v>83.98</v>
+      </c>
+      <c r="X31" s="16" t="n">
+        <v>48393</v>
+      </c>
+      <c r="Y31" s="16" t="n">
+        <v>48447.82</v>
+      </c>
+      <c r="Z31" s="16" t="n">
+        <v>65607</v>
+      </c>
+      <c r="AA31" s="16" t="n">
+        <v>14517.9</v>
+      </c>
+      <c r="AB31" s="16" t="n">
+        <v>14517.9</v>
+      </c>
+      <c r="AC31" s="16" t="n">
+        <v>-524.4</v>
+      </c>
+      <c r="AD31" s="16" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AE31" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF31" s="16" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AG31" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH31" s="16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI31" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ31" s="16" t="n">
+        <v>54.82</v>
+      </c>
+      <c r="AK31" s="16" t="n">
+        <v>-579.22</v>
+      </c>
+      <c r="AL31" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM31" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN31" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -8044,7 +8295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN30"/>
+  <dimension ref="A1:AN31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12508,6 +12759,158 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G31" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H31" s="16" t="n">
+        <v>57686.08</v>
+      </c>
+      <c r="I31" s="16" t="n">
+        <v>56919.04</v>
+      </c>
+      <c r="J31" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K31" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L31" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="M31" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N31" s="16" t="inlineStr">
+        <is>
+          <t>14:17 IST</t>
+        </is>
+      </c>
+      <c r="O31" s="16" t="n">
+        <v>56742.6</v>
+      </c>
+      <c r="P31" s="16" t="n">
+        <v>58200.7</v>
+      </c>
+      <c r="Q31" s="16" t="inlineStr">
+        <is>
+          <t>56800 PE</t>
+        </is>
+      </c>
+      <c r="R31" s="16" t="inlineStr">
+        <is>
+          <t>56600 PE</t>
+        </is>
+      </c>
+      <c r="S31" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="T31" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U31" s="16" t="n">
+        <v>510</v>
+      </c>
+      <c r="V31" s="16" t="n">
+        <v>91.42</v>
+      </c>
+      <c r="W31" s="16" t="n">
+        <v>91.70999999999999</v>
+      </c>
+      <c r="X31" s="16" t="n">
+        <v>46624.2</v>
+      </c>
+      <c r="Y31" s="16" t="n">
+        <v>46678.74</v>
+      </c>
+      <c r="Z31" s="16" t="n">
+        <v>55375.8</v>
+      </c>
+      <c r="AA31" s="16" t="n">
+        <v>13987.26</v>
+      </c>
+      <c r="AB31" s="16" t="n">
+        <v>13987.26</v>
+      </c>
+      <c r="AC31" s="16" t="n">
+        <v>147.9</v>
+      </c>
+      <c r="AD31" s="16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AE31" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF31" s="16" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="AG31" s="16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH31" s="16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI31" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ31" s="16" t="n">
+        <v>54.54</v>
+      </c>
+      <c r="AK31" s="16" t="n">
+        <v>93.36</v>
+      </c>
+      <c r="AL31" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM31" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN31" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -12522,7 +12925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN58"/>
+  <dimension ref="A1:AN60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21197,6 +21600,310 @@
         <v>50000</v>
       </c>
       <c r="AN58" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C59" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D59" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E59" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F59" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G59" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="n">
+        <v>57686.08</v>
+      </c>
+      <c r="I59" s="15" t="n">
+        <v>56919.04</v>
+      </c>
+      <c r="J59" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K59" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L59" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="M59" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N59" s="15" t="inlineStr">
+        <is>
+          <t>11:19 IST</t>
+        </is>
+      </c>
+      <c r="O59" s="15" t="n">
+        <v>56742.6</v>
+      </c>
+      <c r="P59" s="15" t="n">
+        <v>58200.7</v>
+      </c>
+      <c r="Q59" s="15" t="inlineStr">
+        <is>
+          <t>56600 CE</t>
+        </is>
+      </c>
+      <c r="R59" s="15" t="inlineStr">
+        <is>
+          <t>56800 CE</t>
+        </is>
+      </c>
+      <c r="S59" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U59" s="15" t="n">
+        <v>450</v>
+      </c>
+      <c r="V59" s="15" t="n">
+        <v>106.16</v>
+      </c>
+      <c r="W59" s="15" t="n">
+        <v>74.31</v>
+      </c>
+      <c r="X59" s="15" t="n">
+        <v>47772</v>
+      </c>
+      <c r="Y59" s="15" t="n">
+        <v>47826.72</v>
+      </c>
+      <c r="Z59" s="15" t="n">
+        <v>42228</v>
+      </c>
+      <c r="AA59" s="15" t="n">
+        <v>14331.6</v>
+      </c>
+      <c r="AB59" s="15" t="n">
+        <v>14331.6</v>
+      </c>
+      <c r="AC59" s="15" t="n">
+        <v>-14332.5</v>
+      </c>
+      <c r="AD59" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE59" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF59" s="15" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="AG59" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH59" s="15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI59" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ59" s="15" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="AK59" s="15" t="n">
+        <v>-14387.22</v>
+      </c>
+      <c r="AL59" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM59" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN59" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C60" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D60" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E60" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G60" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H60" s="17" t="n">
+        <v>57686.08</v>
+      </c>
+      <c r="I60" s="17" t="n">
+        <v>56919.04</v>
+      </c>
+      <c r="J60" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K60" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L60" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="M60" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N60" s="17" t="inlineStr">
+        <is>
+          <t>12:11 IST</t>
+        </is>
+      </c>
+      <c r="O60" s="17" t="n">
+        <v>56742.6</v>
+      </c>
+      <c r="P60" s="17" t="n">
+        <v>58200.7</v>
+      </c>
+      <c r="Q60" s="17" t="inlineStr">
+        <is>
+          <t>56800 PE</t>
+        </is>
+      </c>
+      <c r="R60" s="17" t="inlineStr">
+        <is>
+          <t>56600 PE</t>
+        </is>
+      </c>
+      <c r="S60" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="T60" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U60" s="17" t="n">
+        <v>510</v>
+      </c>
+      <c r="V60" s="17" t="n">
+        <v>91.54000000000001</v>
+      </c>
+      <c r="W60" s="17" t="n">
+        <v>119</v>
+      </c>
+      <c r="X60" s="17" t="n">
+        <v>46685.4</v>
+      </c>
+      <c r="Y60" s="17" t="n">
+        <v>46739.95</v>
+      </c>
+      <c r="Z60" s="17" t="n">
+        <v>55314.6</v>
+      </c>
+      <c r="AA60" s="17" t="n">
+        <v>14005.62</v>
+      </c>
+      <c r="AB60" s="17" t="n">
+        <v>14005.62</v>
+      </c>
+      <c r="AC60" s="17" t="n">
+        <v>14004.6</v>
+      </c>
+      <c r="AD60" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE60" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF60" s="17" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="AG60" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH60" s="17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI60" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ60" s="17" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="AK60" s="17" t="n">
+        <v>13950.05</v>
+      </c>
+      <c r="AL60" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM60" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN60" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -23586,7 +24293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24462,6 +25169,72 @@
         <v>56950.61</v>
       </c>
       <c r="G27" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>24116.8</v>
+      </c>
+      <c r="F28" s="18" t="n">
+        <v>23907.04</v>
+      </c>
+      <c r="G28" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>57686.08</v>
+      </c>
+      <c r="F29" s="18" t="n">
+        <v>56919.04</v>
+      </c>
+      <c r="G29" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -24481,7 +25254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA30"/>
+  <dimension ref="A1:AA31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27424,6 +28197,105 @@
         <v>1000</v>
       </c>
       <c r="AA30" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="inlineStr">
+        <is>
+          <t>11:03 ET</t>
+        </is>
+      </c>
+      <c r="H31" s="17" t="n">
+        <v>29002</v>
+      </c>
+      <c r="I31" s="17" t="n">
+        <v>29000</v>
+      </c>
+      <c r="J31" s="17" t="n">
+        <v>29025</v>
+      </c>
+      <c r="K31" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="L31" s="17" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="M31" s="17" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="N31" s="17" t="n">
+        <v>983.3200000000001</v>
+      </c>
+      <c r="O31" s="17" t="n">
+        <v>1701.96</v>
+      </c>
+      <c r="P31" s="17" t="n">
+        <v>269.41</v>
+      </c>
+      <c r="Q31" s="17" t="n">
+        <v>269.41</v>
+      </c>
+      <c r="R31" s="17" t="n">
+        <v>269.36</v>
+      </c>
+      <c r="S31" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T31" s="17" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="U31" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="V31" s="17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W31" s="17" t="n">
+        <v>85.28</v>
+      </c>
+      <c r="X31" s="17" t="n">
+        <v>184.08</v>
+      </c>
+      <c r="Y31" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z31" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA31" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -27543,7 +28415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -29568,6 +30440,76 @@
       <c r="I58" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — STOP LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B59" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C59" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D59" s="19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E59" s="19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F59" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G59" s="19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H59" s="19" t="n">
+        <v>37</v>
+      </c>
+      <c r="I59" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — STOP LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B60" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C60" s="19" t="n">
+        <v>52</v>
+      </c>
+      <c r="D60" s="19" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E60" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="F60" s="19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G60" s="19" t="n">
+        <v>42.64</v>
+      </c>
+      <c r="H60" s="19" t="n">
+        <v>85.28</v>
+      </c>
+      <c r="I60" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — PROFIT</t>
         </is>
       </c>
     </row>
@@ -30034,7 +30976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN30"/>
+  <dimension ref="A1:AN31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -34498,6 +35440,158 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H31" s="17" t="n">
+        <v>24116.8</v>
+      </c>
+      <c r="I31" s="17" t="n">
+        <v>23907.04</v>
+      </c>
+      <c r="J31" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K31" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L31" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N31" s="17" t="inlineStr">
+        <is>
+          <t>10:29 IST</t>
+        </is>
+      </c>
+      <c r="O31" s="17" t="n">
+        <v>23882.05</v>
+      </c>
+      <c r="P31" s="17" t="n">
+        <v>24398.7</v>
+      </c>
+      <c r="Q31" s="17" t="inlineStr">
+        <is>
+          <t>23800 CE</t>
+        </is>
+      </c>
+      <c r="R31" s="17" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="S31" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="T31" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U31" s="17" t="n">
+        <v>2795</v>
+      </c>
+      <c r="V31" s="17" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="W31" s="17" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="X31" s="17" t="n">
+        <v>47347.3</v>
+      </c>
+      <c r="Y31" s="17" t="n">
+        <v>47401.95</v>
+      </c>
+      <c r="Z31" s="17" t="n">
+        <v>232152.7</v>
+      </c>
+      <c r="AA31" s="17" t="n">
+        <v>14204.19</v>
+      </c>
+      <c r="AB31" s="17" t="n">
+        <v>14204.19</v>
+      </c>
+      <c r="AC31" s="17" t="n">
+        <v>14198.6</v>
+      </c>
+      <c r="AD31" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE31" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF31" s="17" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="AG31" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH31" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI31" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ31" s="17" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="AK31" s="17" t="n">
+        <v>14143.95</v>
+      </c>
+      <c r="AL31" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM31" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN31" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -34512,7 +35606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN30"/>
+  <dimension ref="A1:AN31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -38976,6 +40070,158 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H31" s="17" t="n">
+        <v>24116.8</v>
+      </c>
+      <c r="I31" s="17" t="n">
+        <v>23907.04</v>
+      </c>
+      <c r="J31" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K31" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L31" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N31" s="17" t="inlineStr">
+        <is>
+          <t>11:36 IST</t>
+        </is>
+      </c>
+      <c r="O31" s="17" t="n">
+        <v>23882.05</v>
+      </c>
+      <c r="P31" s="17" t="n">
+        <v>24398.7</v>
+      </c>
+      <c r="Q31" s="17" t="inlineStr">
+        <is>
+          <t>23900 PE</t>
+        </is>
+      </c>
+      <c r="R31" s="17" t="inlineStr">
+        <is>
+          <t>23800 PE</t>
+        </is>
+      </c>
+      <c r="S31" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="T31" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U31" s="17" t="n">
+        <v>2340</v>
+      </c>
+      <c r="V31" s="17" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="W31" s="17" t="n">
+        <v>26.96</v>
+      </c>
+      <c r="X31" s="17" t="n">
+        <v>48531.6</v>
+      </c>
+      <c r="Y31" s="17" t="n">
+        <v>48586.44</v>
+      </c>
+      <c r="Z31" s="17" t="n">
+        <v>185468.4</v>
+      </c>
+      <c r="AA31" s="17" t="n">
+        <v>14559.48</v>
+      </c>
+      <c r="AB31" s="17" t="n">
+        <v>14559.48</v>
+      </c>
+      <c r="AC31" s="17" t="n">
+        <v>14554.8</v>
+      </c>
+      <c r="AD31" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE31" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF31" s="17" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="AG31" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH31" s="17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI31" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ31" s="17" t="n">
+        <v>54.84</v>
+      </c>
+      <c r="AK31" s="17" t="n">
+        <v>14499.96</v>
+      </c>
+      <c r="AL31" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM31" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN31" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -38990,7 +40236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN58"/>
+  <dimension ref="A1:AN60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -47665,6 +48911,310 @@
         <v>50000</v>
       </c>
       <c r="AN58" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C59" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D59" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E59" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F59" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G59" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H59" s="17" t="n">
+        <v>24116.8</v>
+      </c>
+      <c r="I59" s="17" t="n">
+        <v>23907.04</v>
+      </c>
+      <c r="J59" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K59" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L59" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N59" s="17" t="inlineStr">
+        <is>
+          <t>10:04 IST</t>
+        </is>
+      </c>
+      <c r="O59" s="17" t="n">
+        <v>23882.05</v>
+      </c>
+      <c r="P59" s="17" t="n">
+        <v>24398.7</v>
+      </c>
+      <c r="Q59" s="17" t="inlineStr">
+        <is>
+          <t>23800 CE</t>
+        </is>
+      </c>
+      <c r="R59" s="17" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="S59" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="T59" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U59" s="17" t="n">
+        <v>2080</v>
+      </c>
+      <c r="V59" s="17" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="W59" s="17" t="n">
+        <v>29.56</v>
+      </c>
+      <c r="X59" s="17" t="n">
+        <v>47299.2</v>
+      </c>
+      <c r="Y59" s="17" t="n">
+        <v>47353.84</v>
+      </c>
+      <c r="Z59" s="17" t="n">
+        <v>160700.8</v>
+      </c>
+      <c r="AA59" s="17" t="n">
+        <v>14189.76</v>
+      </c>
+      <c r="AB59" s="17" t="n">
+        <v>14189.76</v>
+      </c>
+      <c r="AC59" s="17" t="n">
+        <v>14185.6</v>
+      </c>
+      <c r="AD59" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE59" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF59" s="17" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AG59" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH59" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI59" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ59" s="17" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="AK59" s="17" t="n">
+        <v>14130.96</v>
+      </c>
+      <c r="AL59" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM59" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN59" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C60" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D60" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E60" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G60" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H60" s="17" t="n">
+        <v>24116.8</v>
+      </c>
+      <c r="I60" s="17" t="n">
+        <v>23907.04</v>
+      </c>
+      <c r="J60" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K60" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L60" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M60" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N60" s="17" t="inlineStr">
+        <is>
+          <t>11:21 IST</t>
+        </is>
+      </c>
+      <c r="O60" s="17" t="n">
+        <v>23882.05</v>
+      </c>
+      <c r="P60" s="17" t="n">
+        <v>24398.7</v>
+      </c>
+      <c r="Q60" s="17" t="inlineStr">
+        <is>
+          <t>23900 PE</t>
+        </is>
+      </c>
+      <c r="R60" s="17" t="inlineStr">
+        <is>
+          <t>23800 PE</t>
+        </is>
+      </c>
+      <c r="S60" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="T60" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U60" s="17" t="n">
+        <v>2665</v>
+      </c>
+      <c r="V60" s="17" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="W60" s="17" t="n">
+        <v>23.49</v>
+      </c>
+      <c r="X60" s="17" t="n">
+        <v>48156.55</v>
+      </c>
+      <c r="Y60" s="17" t="n">
+        <v>48211.33</v>
+      </c>
+      <c r="Z60" s="17" t="n">
+        <v>218343.45</v>
+      </c>
+      <c r="AA60" s="17" t="n">
+        <v>14446.97</v>
+      </c>
+      <c r="AB60" s="17" t="n">
+        <v>14446.97</v>
+      </c>
+      <c r="AC60" s="17" t="n">
+        <v>14444.3</v>
+      </c>
+      <c r="AD60" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE60" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF60" s="17" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="AG60" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH60" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI60" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ60" s="17" t="n">
+        <v>54.78</v>
+      </c>
+      <c r="AK60" s="17" t="n">
+        <v>14389.52</v>
+      </c>
+      <c r="AL60" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM60" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN60" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA31"/>
+  <dimension ref="A1:AA32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3651,6 +3651,105 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E32" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G32" s="16" t="inlineStr">
+        <is>
+          <t>15:10 ET</t>
+        </is>
+      </c>
+      <c r="H32" s="16" t="n">
+        <v>29393.5</v>
+      </c>
+      <c r="I32" s="16" t="n">
+        <v>29375</v>
+      </c>
+      <c r="J32" s="16" t="n">
+        <v>29400</v>
+      </c>
+      <c r="K32" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L32" s="16" t="n">
+        <v>201.96</v>
+      </c>
+      <c r="M32" s="16" t="n">
+        <v>194.73</v>
+      </c>
+      <c r="N32" s="16" t="n">
+        <v>837.4400000000001</v>
+      </c>
+      <c r="O32" s="16" t="n">
+        <v>1192.16</v>
+      </c>
+      <c r="P32" s="16" t="n">
+        <v>242.35</v>
+      </c>
+      <c r="Q32" s="16" t="n">
+        <v>242.35</v>
+      </c>
+      <c r="R32" s="16" t="n">
+        <v>-28.92</v>
+      </c>
+      <c r="S32" s="16" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="T32" s="16" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="U32" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="V32" s="16" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W32" s="16" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="X32" s="16" t="n">
+        <v>-58.52</v>
+      </c>
+      <c r="Y32" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="Z32" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA32" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -3665,7 +3764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN31"/>
+  <dimension ref="A1:AN32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8281,6 +8380,158 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H32" s="17" t="n">
+        <v>57921.95</v>
+      </c>
+      <c r="I32" s="17" t="n">
+        <v>56936.69</v>
+      </c>
+      <c r="J32" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K32" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L32" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="M32" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N32" s="17" t="inlineStr">
+        <is>
+          <t>11:05 IST</t>
+        </is>
+      </c>
+      <c r="O32" s="17" t="n">
+        <v>58200.7</v>
+      </c>
+      <c r="P32" s="17" t="n">
+        <v>58291.5</v>
+      </c>
+      <c r="Q32" s="17" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="R32" s="17" t="inlineStr">
+        <is>
+          <t>58400 CE</t>
+        </is>
+      </c>
+      <c r="S32" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="T32" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U32" s="17" t="n">
+        <v>480</v>
+      </c>
+      <c r="V32" s="17" t="n">
+        <v>97.42</v>
+      </c>
+      <c r="W32" s="17" t="n">
+        <v>126.65</v>
+      </c>
+      <c r="X32" s="17" t="n">
+        <v>46761.6</v>
+      </c>
+      <c r="Y32" s="17" t="n">
+        <v>46816.16</v>
+      </c>
+      <c r="Z32" s="17" t="n">
+        <v>49238.4</v>
+      </c>
+      <c r="AA32" s="17" t="n">
+        <v>14028.48</v>
+      </c>
+      <c r="AB32" s="17" t="n">
+        <v>14028.48</v>
+      </c>
+      <c r="AC32" s="17" t="n">
+        <v>14030.4</v>
+      </c>
+      <c r="AD32" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE32" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF32" s="17" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AG32" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH32" s="17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI32" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ32" s="17" t="n">
+        <v>54.56</v>
+      </c>
+      <c r="AK32" s="17" t="n">
+        <v>13975.84</v>
+      </c>
+      <c r="AL32" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM32" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN32" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -8295,7 +8546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN31"/>
+  <dimension ref="A1:AN32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12911,6 +13162,158 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H32" s="17" t="n">
+        <v>57921.95</v>
+      </c>
+      <c r="I32" s="17" t="n">
+        <v>56936.69</v>
+      </c>
+      <c r="J32" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K32" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L32" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="M32" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N32" s="17" t="inlineStr">
+        <is>
+          <t>12:13 IST</t>
+        </is>
+      </c>
+      <c r="O32" s="17" t="n">
+        <v>58200.7</v>
+      </c>
+      <c r="P32" s="17" t="n">
+        <v>58291.5</v>
+      </c>
+      <c r="Q32" s="17" t="inlineStr">
+        <is>
+          <t>58400 PE</t>
+        </is>
+      </c>
+      <c r="R32" s="17" t="inlineStr">
+        <is>
+          <t>58200 PE</t>
+        </is>
+      </c>
+      <c r="S32" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="T32" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U32" s="17" t="n">
+        <v>570</v>
+      </c>
+      <c r="V32" s="17" t="n">
+        <v>82.47</v>
+      </c>
+      <c r="W32" s="17" t="n">
+        <v>107.21</v>
+      </c>
+      <c r="X32" s="17" t="n">
+        <v>47007.9</v>
+      </c>
+      <c r="Y32" s="17" t="n">
+        <v>47062.5</v>
+      </c>
+      <c r="Z32" s="17" t="n">
+        <v>66992.10000000001</v>
+      </c>
+      <c r="AA32" s="17" t="n">
+        <v>14102.37</v>
+      </c>
+      <c r="AB32" s="17" t="n">
+        <v>14102.37</v>
+      </c>
+      <c r="AC32" s="17" t="n">
+        <v>14101.8</v>
+      </c>
+      <c r="AD32" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE32" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF32" s="17" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="AG32" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH32" s="17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI32" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ32" s="17" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="AK32" s="17" t="n">
+        <v>14047.2</v>
+      </c>
+      <c r="AL32" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM32" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN32" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -12925,7 +13328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN60"/>
+  <dimension ref="A1:AN62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21904,6 +22307,310 @@
         <v>50000</v>
       </c>
       <c r="AN60" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C61" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D61" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E61" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F61" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G61" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H61" s="15" t="n">
+        <v>57921.95</v>
+      </c>
+      <c r="I61" s="15" t="n">
+        <v>56936.69</v>
+      </c>
+      <c r="J61" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K61" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L61" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="M61" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N61" s="15" t="inlineStr">
+        <is>
+          <t>10:31 IST</t>
+        </is>
+      </c>
+      <c r="O61" s="15" t="n">
+        <v>58200.7</v>
+      </c>
+      <c r="P61" s="15" t="n">
+        <v>58291.5</v>
+      </c>
+      <c r="Q61" s="15" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="R61" s="15" t="inlineStr">
+        <is>
+          <t>58400 CE</t>
+        </is>
+      </c>
+      <c r="S61" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T61" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U61" s="15" t="n">
+        <v>450</v>
+      </c>
+      <c r="V61" s="15" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="W61" s="15" t="n">
+        <v>75.95</v>
+      </c>
+      <c r="X61" s="15" t="n">
+        <v>48825</v>
+      </c>
+      <c r="Y61" s="15" t="n">
+        <v>48879.88</v>
+      </c>
+      <c r="Z61" s="15" t="n">
+        <v>41175</v>
+      </c>
+      <c r="AA61" s="15" t="n">
+        <v>14647.5</v>
+      </c>
+      <c r="AB61" s="15" t="n">
+        <v>14647.5</v>
+      </c>
+      <c r="AC61" s="15" t="n">
+        <v>-14647.5</v>
+      </c>
+      <c r="AD61" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE61" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF61" s="15" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AG61" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH61" s="15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI61" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ61" s="15" t="n">
+        <v>54.88</v>
+      </c>
+      <c r="AK61" s="15" t="n">
+        <v>-14702.38</v>
+      </c>
+      <c r="AL61" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM61" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN61" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B62" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C62" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D62" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E62" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F62" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G62" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H62" s="16" t="n">
+        <v>57921.95</v>
+      </c>
+      <c r="I62" s="16" t="n">
+        <v>56936.69</v>
+      </c>
+      <c r="J62" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K62" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L62" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="M62" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N62" s="16" t="inlineStr">
+        <is>
+          <t>13:31 IST</t>
+        </is>
+      </c>
+      <c r="O62" s="16" t="n">
+        <v>58200.7</v>
+      </c>
+      <c r="P62" s="16" t="n">
+        <v>58291.5</v>
+      </c>
+      <c r="Q62" s="16" t="inlineStr">
+        <is>
+          <t>58400 PE</t>
+        </is>
+      </c>
+      <c r="R62" s="16" t="inlineStr">
+        <is>
+          <t>58200 PE</t>
+        </is>
+      </c>
+      <c r="S62" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="T62" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U62" s="16" t="n">
+        <v>570</v>
+      </c>
+      <c r="V62" s="16" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="W62" s="16" t="n">
+        <v>84.61</v>
+      </c>
+      <c r="X62" s="16" t="n">
+        <v>47196</v>
+      </c>
+      <c r="Y62" s="16" t="n">
+        <v>47250.63</v>
+      </c>
+      <c r="Z62" s="16" t="n">
+        <v>66804</v>
+      </c>
+      <c r="AA62" s="16" t="n">
+        <v>14158.8</v>
+      </c>
+      <c r="AB62" s="16" t="n">
+        <v>14158.8</v>
+      </c>
+      <c r="AC62" s="16" t="n">
+        <v>1031.7</v>
+      </c>
+      <c r="AD62" s="16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE62" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF62" s="16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AG62" s="16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH62" s="16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI62" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ62" s="16" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="AK62" s="16" t="n">
+        <v>977.0700000000001</v>
+      </c>
+      <c r="AL62" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM62" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN62" s="16" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -24293,7 +25000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25235,6 +25942,72 @@
         <v>56919.04</v>
       </c>
       <c r="G29" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>24175.49</v>
+      </c>
+      <c r="F30" s="18" t="n">
+        <v>23909.54</v>
+      </c>
+      <c r="G30" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>57921.95</v>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>56936.69</v>
+      </c>
+      <c r="G31" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -25254,7 +26027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA31"/>
+  <dimension ref="A1:AA32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -28296,6 +29069,105 @@
         <v>1000</v>
       </c>
       <c r="AA31" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>12:45 ET</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>29393</v>
+      </c>
+      <c r="I32" s="15" t="n">
+        <v>29375</v>
+      </c>
+      <c r="J32" s="15" t="n">
+        <v>29400</v>
+      </c>
+      <c r="K32" s="15" t="n">
+        <v>47</v>
+      </c>
+      <c r="L32" s="15" t="n">
+        <v>19.26</v>
+      </c>
+      <c r="M32" s="15" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="N32" s="15" t="n">
+        <v>982.3</v>
+      </c>
+      <c r="O32" s="15" t="n">
+        <v>1444.78</v>
+      </c>
+      <c r="P32" s="15" t="n">
+        <v>271.57</v>
+      </c>
+      <c r="Q32" s="15" t="n">
+        <v>271.57</v>
+      </c>
+      <c r="R32" s="15" t="n">
+        <v>-271.66</v>
+      </c>
+      <c r="S32" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="T32" s="15" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="U32" s="15" t="n">
+        <v>47</v>
+      </c>
+      <c r="V32" s="15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="W32" s="15" t="n">
+        <v>77.08</v>
+      </c>
+      <c r="X32" s="15" t="n">
+        <v>-348.74</v>
+      </c>
+      <c r="Y32" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="Z32" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA32" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -28415,7 +29287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -30510,6 +31382,76 @@
       <c r="I60" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B61" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C61" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D61" s="19" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="E61" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F61" s="19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G61" s="19" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H61" s="19" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I61" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B62" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C62" s="19" t="n">
+        <v>47</v>
+      </c>
+      <c r="D62" s="19" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="E62" s="19" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F62" s="19" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G62" s="19" t="n">
+        <v>38.54</v>
+      </c>
+      <c r="H62" s="19" t="n">
+        <v>77.08</v>
+      </c>
+      <c r="I62" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — STOP LOSS</t>
         </is>
       </c>
     </row>
@@ -30976,7 +31918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN31"/>
+  <dimension ref="A1:AN32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -35592,6 +36534,158 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E32" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G32" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H32" s="16" t="n">
+        <v>24175.49</v>
+      </c>
+      <c r="I32" s="16" t="n">
+        <v>23909.54</v>
+      </c>
+      <c r="J32" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K32" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L32" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N32" s="16" t="inlineStr">
+        <is>
+          <t>15:20 IST</t>
+        </is>
+      </c>
+      <c r="O32" s="16" t="n">
+        <v>24398.7</v>
+      </c>
+      <c r="P32" s="16" t="n">
+        <v>24430.35</v>
+      </c>
+      <c r="Q32" s="16" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="R32" s="16" t="inlineStr">
+        <is>
+          <t>24400 CE</t>
+        </is>
+      </c>
+      <c r="S32" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="T32" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U32" s="16" t="n">
+        <v>2275</v>
+      </c>
+      <c r="V32" s="16" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="W32" s="16" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="X32" s="16" t="n">
+        <v>48412</v>
+      </c>
+      <c r="Y32" s="16" t="n">
+        <v>48466.82</v>
+      </c>
+      <c r="Z32" s="16" t="n">
+        <v>179088</v>
+      </c>
+      <c r="AA32" s="16" t="n">
+        <v>14523.6</v>
+      </c>
+      <c r="AB32" s="16" t="n">
+        <v>14523.6</v>
+      </c>
+      <c r="AC32" s="16" t="n">
+        <v>-1114.75</v>
+      </c>
+      <c r="AD32" s="16" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="AE32" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF32" s="16" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AG32" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH32" s="16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI32" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ32" s="16" t="n">
+        <v>54.82</v>
+      </c>
+      <c r="AK32" s="16" t="n">
+        <v>-1169.57</v>
+      </c>
+      <c r="AL32" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM32" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN32" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -35606,7 +36700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN31"/>
+  <dimension ref="A1:AN32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -40222,6 +41316,158 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E32" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G32" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H32" s="16" t="n">
+        <v>24175.49</v>
+      </c>
+      <c r="I32" s="16" t="n">
+        <v>23909.54</v>
+      </c>
+      <c r="J32" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K32" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L32" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N32" s="16" t="inlineStr">
+        <is>
+          <t>13:25 IST</t>
+        </is>
+      </c>
+      <c r="O32" s="16" t="n">
+        <v>24398.7</v>
+      </c>
+      <c r="P32" s="16" t="n">
+        <v>24430.35</v>
+      </c>
+      <c r="Q32" s="16" t="inlineStr">
+        <is>
+          <t>24400 PE</t>
+        </is>
+      </c>
+      <c r="R32" s="16" t="inlineStr">
+        <is>
+          <t>24300 PE</t>
+        </is>
+      </c>
+      <c r="S32" s="16" t="n">
+        <v>33</v>
+      </c>
+      <c r="T32" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U32" s="16" t="n">
+        <v>2145</v>
+      </c>
+      <c r="V32" s="16" t="n">
+        <v>22.31</v>
+      </c>
+      <c r="W32" s="16" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="X32" s="16" t="n">
+        <v>47854.95</v>
+      </c>
+      <c r="Y32" s="16" t="n">
+        <v>47909.68</v>
+      </c>
+      <c r="Z32" s="16" t="n">
+        <v>166645.05</v>
+      </c>
+      <c r="AA32" s="16" t="n">
+        <v>14356.48</v>
+      </c>
+      <c r="AB32" s="16" t="n">
+        <v>14356.48</v>
+      </c>
+      <c r="AC32" s="16" t="n">
+        <v>-965.25</v>
+      </c>
+      <c r="AD32" s="16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE32" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF32" s="16" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AG32" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH32" s="16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI32" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ32" s="16" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="AK32" s="16" t="n">
+        <v>-1019.98</v>
+      </c>
+      <c r="AL32" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM32" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN32" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -40236,7 +41482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN60"/>
+  <dimension ref="A1:AN62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -49215,6 +50461,310 @@
         <v>50000</v>
       </c>
       <c r="AN60" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C61" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D61" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E61" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F61" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G61" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H61" s="15" t="n">
+        <v>24175.49</v>
+      </c>
+      <c r="I61" s="15" t="n">
+        <v>23909.54</v>
+      </c>
+      <c r="J61" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K61" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L61" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M61" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N61" s="15" t="inlineStr">
+        <is>
+          <t>11:11 IST</t>
+        </is>
+      </c>
+      <c r="O61" s="15" t="n">
+        <v>24398.7</v>
+      </c>
+      <c r="P61" s="15" t="n">
+        <v>24430.35</v>
+      </c>
+      <c r="Q61" s="15" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="R61" s="15" t="inlineStr">
+        <is>
+          <t>24400 CE</t>
+        </is>
+      </c>
+      <c r="S61" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="T61" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U61" s="15" t="n">
+        <v>2405</v>
+      </c>
+      <c r="V61" s="15" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="W61" s="15" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="X61" s="15" t="n">
+        <v>47402.55</v>
+      </c>
+      <c r="Y61" s="15" t="n">
+        <v>47457.21</v>
+      </c>
+      <c r="Z61" s="15" t="n">
+        <v>193097.45</v>
+      </c>
+      <c r="AA61" s="15" t="n">
+        <v>14220.77</v>
+      </c>
+      <c r="AB61" s="15" t="n">
+        <v>14220.77</v>
+      </c>
+      <c r="AC61" s="15" t="n">
+        <v>-14213.55</v>
+      </c>
+      <c r="AD61" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE61" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF61" s="15" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="AG61" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH61" s="15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI61" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ61" s="15" t="n">
+        <v>54.66</v>
+      </c>
+      <c r="AK61" s="15" t="n">
+        <v>-14268.21</v>
+      </c>
+      <c r="AL61" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM61" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN61" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D62" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E62" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F62" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G62" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H62" s="17" t="n">
+        <v>24175.49</v>
+      </c>
+      <c r="I62" s="17" t="n">
+        <v>23909.54</v>
+      </c>
+      <c r="J62" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K62" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L62" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M62" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N62" s="17" t="inlineStr">
+        <is>
+          <t>12:04 IST</t>
+        </is>
+      </c>
+      <c r="O62" s="17" t="n">
+        <v>24398.7</v>
+      </c>
+      <c r="P62" s="17" t="n">
+        <v>24430.35</v>
+      </c>
+      <c r="Q62" s="17" t="inlineStr">
+        <is>
+          <t>24400 PE</t>
+        </is>
+      </c>
+      <c r="R62" s="17" t="inlineStr">
+        <is>
+          <t>24300 PE</t>
+        </is>
+      </c>
+      <c r="S62" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="T62" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U62" s="17" t="n">
+        <v>2860</v>
+      </c>
+      <c r="V62" s="17" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="W62" s="17" t="n">
+        <v>21.67</v>
+      </c>
+      <c r="X62" s="17" t="n">
+        <v>47676.2</v>
+      </c>
+      <c r="Y62" s="17" t="n">
+        <v>47730.9</v>
+      </c>
+      <c r="Z62" s="17" t="n">
+        <v>238323.8</v>
+      </c>
+      <c r="AA62" s="17" t="n">
+        <v>14302.86</v>
+      </c>
+      <c r="AB62" s="17" t="n">
+        <v>14302.86</v>
+      </c>
+      <c r="AC62" s="17" t="n">
+        <v>14300</v>
+      </c>
+      <c r="AD62" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE62" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF62" s="17" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="AG62" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH62" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI62" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ62" s="17" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="AK62" s="17" t="n">
+        <v>14245.3</v>
+      </c>
+      <c r="AL62" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM62" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN62" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA32"/>
+  <dimension ref="A1:AA33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3750,6 +3750,105 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="inlineStr">
+        <is>
+          <t>10:30 ET</t>
+        </is>
+      </c>
+      <c r="H33" s="17" t="n">
+        <v>29837.5</v>
+      </c>
+      <c r="I33" s="17" t="n">
+        <v>29825</v>
+      </c>
+      <c r="J33" s="17" t="n">
+        <v>29850</v>
+      </c>
+      <c r="K33" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L33" s="17" t="n">
+        <v>208.74</v>
+      </c>
+      <c r="M33" s="17" t="n">
+        <v>271.36</v>
+      </c>
+      <c r="N33" s="17" t="n">
+        <v>864.5599999999999</v>
+      </c>
+      <c r="O33" s="17" t="n">
+        <v>1165.04</v>
+      </c>
+      <c r="P33" s="17" t="n">
+        <v>250.49</v>
+      </c>
+      <c r="Q33" s="17" t="n">
+        <v>250.49</v>
+      </c>
+      <c r="R33" s="17" t="n">
+        <v>250.48</v>
+      </c>
+      <c r="S33" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T33" s="17" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="U33" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="V33" s="17" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W33" s="17" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="X33" s="17" t="n">
+        <v>220.88</v>
+      </c>
+      <c r="Y33" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z33" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA33" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -3764,7 +3863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN32"/>
+  <dimension ref="A1:AN33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8532,6 +8631,158 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G33" s="16" t="inlineStr">
+        <is>
+          <t>Price↑(57252.45&gt;56742.6) &amp; EMA9↑(57599.36&gt;56949.35)</t>
+        </is>
+      </c>
+      <c r="H33" s="16" t="n">
+        <v>57599.36</v>
+      </c>
+      <c r="I33" s="16" t="n">
+        <v>56949.35</v>
+      </c>
+      <c r="J33" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K33" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L33" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="M33" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N33" s="16" t="inlineStr">
+        <is>
+          <t>14:12 IST</t>
+        </is>
+      </c>
+      <c r="O33" s="16" t="n">
+        <v>57252.45</v>
+      </c>
+      <c r="P33" s="16" t="n">
+        <v>56742.6</v>
+      </c>
+      <c r="Q33" s="16" t="inlineStr">
+        <is>
+          <t>57200 CE</t>
+        </is>
+      </c>
+      <c r="R33" s="16" t="inlineStr">
+        <is>
+          <t>57400 CE</t>
+        </is>
+      </c>
+      <c r="S33" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="T33" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U33" s="16" t="n">
+        <v>540</v>
+      </c>
+      <c r="V33" s="16" t="n">
+        <v>89.91</v>
+      </c>
+      <c r="W33" s="16" t="n">
+        <v>86.37</v>
+      </c>
+      <c r="X33" s="16" t="n">
+        <v>48551.4</v>
+      </c>
+      <c r="Y33" s="16" t="n">
+        <v>48606.24</v>
+      </c>
+      <c r="Z33" s="16" t="n">
+        <v>59448.6</v>
+      </c>
+      <c r="AA33" s="16" t="n">
+        <v>14565.42</v>
+      </c>
+      <c r="AB33" s="16" t="n">
+        <v>14565.42</v>
+      </c>
+      <c r="AC33" s="16" t="n">
+        <v>-1911.6</v>
+      </c>
+      <c r="AD33" s="16" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="AE33" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF33" s="16" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="AG33" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH33" s="16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI33" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ33" s="16" t="n">
+        <v>54.84</v>
+      </c>
+      <c r="AK33" s="16" t="n">
+        <v>-1966.44</v>
+      </c>
+      <c r="AL33" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM33" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN33" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -8546,7 +8797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN32"/>
+  <dimension ref="A1:AN33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13314,6 +13565,158 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(57252.45&gt;56742.6) &amp; EMA9↑(57599.36&gt;56949.35)</t>
+        </is>
+      </c>
+      <c r="H33" s="17" t="n">
+        <v>57599.36</v>
+      </c>
+      <c r="I33" s="17" t="n">
+        <v>56949.35</v>
+      </c>
+      <c r="J33" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K33" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L33" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="M33" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N33" s="17" t="inlineStr">
+        <is>
+          <t>09:58 IST</t>
+        </is>
+      </c>
+      <c r="O33" s="17" t="n">
+        <v>57252.45</v>
+      </c>
+      <c r="P33" s="17" t="n">
+        <v>56742.6</v>
+      </c>
+      <c r="Q33" s="17" t="inlineStr">
+        <is>
+          <t>57400 PE</t>
+        </is>
+      </c>
+      <c r="R33" s="17" t="inlineStr">
+        <is>
+          <t>57200 PE</t>
+        </is>
+      </c>
+      <c r="S33" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="T33" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U33" s="17" t="n">
+        <v>570</v>
+      </c>
+      <c r="V33" s="17" t="n">
+        <v>83.93000000000001</v>
+      </c>
+      <c r="W33" s="17" t="n">
+        <v>109.11</v>
+      </c>
+      <c r="X33" s="17" t="n">
+        <v>47840.1</v>
+      </c>
+      <c r="Y33" s="17" t="n">
+        <v>47894.83</v>
+      </c>
+      <c r="Z33" s="17" t="n">
+        <v>66159.89999999999</v>
+      </c>
+      <c r="AA33" s="17" t="n">
+        <v>14352.03</v>
+      </c>
+      <c r="AB33" s="17" t="n">
+        <v>14352.03</v>
+      </c>
+      <c r="AC33" s="17" t="n">
+        <v>14352.6</v>
+      </c>
+      <c r="AD33" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE33" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF33" s="17" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AG33" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH33" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI33" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ33" s="17" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="AK33" s="17" t="n">
+        <v>14297.87</v>
+      </c>
+      <c r="AL33" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM33" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN33" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -13328,7 +13731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN62"/>
+  <dimension ref="A1:AN64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22616,6 +23019,310 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C63" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D63" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E63" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F63" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G63" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(57252.45&gt;56742.6) &amp; EMA9↑(57599.36&gt;56949.35)</t>
+        </is>
+      </c>
+      <c r="H63" s="17" t="n">
+        <v>57599.36</v>
+      </c>
+      <c r="I63" s="17" t="n">
+        <v>56949.35</v>
+      </c>
+      <c r="J63" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K63" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L63" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="M63" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N63" s="17" t="inlineStr">
+        <is>
+          <t>10:54 IST</t>
+        </is>
+      </c>
+      <c r="O63" s="17" t="n">
+        <v>57252.45</v>
+      </c>
+      <c r="P63" s="17" t="n">
+        <v>56742.6</v>
+      </c>
+      <c r="Q63" s="17" t="inlineStr">
+        <is>
+          <t>57200 CE</t>
+        </is>
+      </c>
+      <c r="R63" s="17" t="inlineStr">
+        <is>
+          <t>57400 CE</t>
+        </is>
+      </c>
+      <c r="S63" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="T63" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U63" s="17" t="n">
+        <v>480</v>
+      </c>
+      <c r="V63" s="17" t="n">
+        <v>100.98</v>
+      </c>
+      <c r="W63" s="17" t="n">
+        <v>131.27</v>
+      </c>
+      <c r="X63" s="17" t="n">
+        <v>48470.4</v>
+      </c>
+      <c r="Y63" s="17" t="n">
+        <v>48525.23</v>
+      </c>
+      <c r="Z63" s="17" t="n">
+        <v>47529.6</v>
+      </c>
+      <c r="AA63" s="17" t="n">
+        <v>14541.12</v>
+      </c>
+      <c r="AB63" s="17" t="n">
+        <v>14541.12</v>
+      </c>
+      <c r="AC63" s="17" t="n">
+        <v>14539.2</v>
+      </c>
+      <c r="AD63" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE63" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF63" s="17" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="AG63" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH63" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI63" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ63" s="17" t="n">
+        <v>54.83</v>
+      </c>
+      <c r="AK63" s="17" t="n">
+        <v>14484.37</v>
+      </c>
+      <c r="AL63" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM63" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN63" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C64" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D64" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E64" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F64" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G64" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(57252.45&gt;56742.6) &amp; EMA9↑(57599.36&gt;56949.35)</t>
+        </is>
+      </c>
+      <c r="H64" s="17" t="n">
+        <v>57599.36</v>
+      </c>
+      <c r="I64" s="17" t="n">
+        <v>56949.35</v>
+      </c>
+      <c r="J64" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K64" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L64" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="M64" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N64" s="17" t="inlineStr">
+        <is>
+          <t>10:54 IST</t>
+        </is>
+      </c>
+      <c r="O64" s="17" t="n">
+        <v>57252.45</v>
+      </c>
+      <c r="P64" s="17" t="n">
+        <v>56742.6</v>
+      </c>
+      <c r="Q64" s="17" t="inlineStr">
+        <is>
+          <t>57400 PE</t>
+        </is>
+      </c>
+      <c r="R64" s="17" t="inlineStr">
+        <is>
+          <t>57200 PE</t>
+        </is>
+      </c>
+      <c r="S64" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T64" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U64" s="17" t="n">
+        <v>450</v>
+      </c>
+      <c r="V64" s="17" t="n">
+        <v>105.76</v>
+      </c>
+      <c r="W64" s="17" t="n">
+        <v>137.49</v>
+      </c>
+      <c r="X64" s="17" t="n">
+        <v>47592</v>
+      </c>
+      <c r="Y64" s="17" t="n">
+        <v>47646.69</v>
+      </c>
+      <c r="Z64" s="17" t="n">
+        <v>42408</v>
+      </c>
+      <c r="AA64" s="17" t="n">
+        <v>14277.6</v>
+      </c>
+      <c r="AB64" s="17" t="n">
+        <v>14277.6</v>
+      </c>
+      <c r="AC64" s="17" t="n">
+        <v>14278.5</v>
+      </c>
+      <c r="AD64" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE64" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF64" s="17" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AG64" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH64" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI64" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ64" s="17" t="n">
+        <v>54.69</v>
+      </c>
+      <c r="AK64" s="17" t="n">
+        <v>14223.81</v>
+      </c>
+      <c r="AL64" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM64" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN64" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -22630,7 +23337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN16"/>
+  <dimension ref="A1:AN17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -24986,6 +25693,158 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(57252.45&gt;56742.6) &amp; EMA9↑(57599.36&gt;56949.35)</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>57599.36</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>56949.35</v>
+      </c>
+      <c r="J17" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K17" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L17" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="M17" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N17" s="15" t="inlineStr">
+        <is>
+          <t>09:34 IST</t>
+        </is>
+      </c>
+      <c r="O17" s="15" t="n">
+        <v>57252.45</v>
+      </c>
+      <c r="P17" s="15" t="n">
+        <v>56742.6</v>
+      </c>
+      <c r="Q17" s="15" t="inlineStr">
+        <is>
+          <t>57200 CE</t>
+        </is>
+      </c>
+      <c r="R17" s="15" t="inlineStr">
+        <is>
+          <t>57400 CE</t>
+        </is>
+      </c>
+      <c r="S17" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="T17" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U17" s="15" t="n">
+        <v>570</v>
+      </c>
+      <c r="V17" s="15" t="n">
+        <v>84.43000000000001</v>
+      </c>
+      <c r="W17" s="15" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="X17" s="15" t="n">
+        <v>48125.1</v>
+      </c>
+      <c r="Y17" s="15" t="n">
+        <v>48179.87</v>
+      </c>
+      <c r="Z17" s="15" t="n">
+        <v>65874.89999999999</v>
+      </c>
+      <c r="AA17" s="15" t="n">
+        <v>14437.53</v>
+      </c>
+      <c r="AB17" s="15" t="n">
+        <v>14437.53</v>
+      </c>
+      <c r="AC17" s="15" t="n">
+        <v>-14438.1</v>
+      </c>
+      <c r="AD17" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE17" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF17" s="15" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="AG17" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH17" s="15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI17" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ17" s="15" t="n">
+        <v>54.77</v>
+      </c>
+      <c r="AK17" s="15" t="n">
+        <v>-14492.87</v>
+      </c>
+      <c r="AL17" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM17" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN17" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -26027,7 +26886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA32"/>
+  <dimension ref="A1:AA33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -29168,6 +30027,105 @@
         <v>1000</v>
       </c>
       <c r="AA32" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="inlineStr">
+        <is>
+          <t>11:09 ET</t>
+        </is>
+      </c>
+      <c r="H33" s="17" t="n">
+        <v>29837.25</v>
+      </c>
+      <c r="I33" s="17" t="n">
+        <v>29825</v>
+      </c>
+      <c r="J33" s="17" t="n">
+        <v>29850</v>
+      </c>
+      <c r="K33" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="L33" s="17" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M33" s="17" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="N33" s="17" t="n">
+        <v>981.12</v>
+      </c>
+      <c r="O33" s="17" t="n">
+        <v>1497.6</v>
+      </c>
+      <c r="P33" s="17" t="n">
+        <v>270.72</v>
+      </c>
+      <c r="Q33" s="17" t="n">
+        <v>270.72</v>
+      </c>
+      <c r="R33" s="17" t="n">
+        <v>270.72</v>
+      </c>
+      <c r="S33" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T33" s="17" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="U33" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="V33" s="17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="W33" s="17" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="X33" s="17" t="n">
+        <v>192</v>
+      </c>
+      <c r="Y33" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z33" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA33" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -29287,7 +30245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -31452,6 +32410,76 @@
       <c r="I62" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — STOP LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B63" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C63" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D63" s="19" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="E63" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F63" s="19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G63" s="19" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H63" s="19" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I63" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B64" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C64" s="19" t="n">
+        <v>48</v>
+      </c>
+      <c r="D64" s="19" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E64" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="F64" s="19" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G64" s="19" t="n">
+        <v>39.36</v>
+      </c>
+      <c r="H64" s="19" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="I64" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — PROFIT</t>
         </is>
       </c>
     </row>
@@ -31918,7 +32946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN32"/>
+  <dimension ref="A1:AN33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -36686,6 +37714,158 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(23962.8&gt;23882.05) &amp; EMA9↑(24086.0&gt;23912.11)</t>
+        </is>
+      </c>
+      <c r="H33" s="17" t="n">
+        <v>24086</v>
+      </c>
+      <c r="I33" s="17" t="n">
+        <v>23912.11</v>
+      </c>
+      <c r="J33" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K33" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L33" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N33" s="17" t="inlineStr">
+        <is>
+          <t>12:02 IST</t>
+        </is>
+      </c>
+      <c r="O33" s="17" t="n">
+        <v>23962.8</v>
+      </c>
+      <c r="P33" s="17" t="n">
+        <v>23882.05</v>
+      </c>
+      <c r="Q33" s="17" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="R33" s="17" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="S33" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="T33" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U33" s="17" t="n">
+        <v>2665</v>
+      </c>
+      <c r="V33" s="17" t="n">
+        <v>17.81</v>
+      </c>
+      <c r="W33" s="17" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="X33" s="17" t="n">
+        <v>47463.65</v>
+      </c>
+      <c r="Y33" s="17" t="n">
+        <v>47518.32</v>
+      </c>
+      <c r="Z33" s="17" t="n">
+        <v>219036.35</v>
+      </c>
+      <c r="AA33" s="17" t="n">
+        <v>14239.09</v>
+      </c>
+      <c r="AB33" s="17" t="n">
+        <v>14239.09</v>
+      </c>
+      <c r="AC33" s="17" t="n">
+        <v>14231.1</v>
+      </c>
+      <c r="AD33" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE33" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF33" s="17" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="AG33" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH33" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI33" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ33" s="17" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="AK33" s="17" t="n">
+        <v>14176.43</v>
+      </c>
+      <c r="AL33" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM33" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN33" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -36700,7 +37880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN32"/>
+  <dimension ref="A1:AN33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -41468,6 +42648,158 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(23962.8&gt;23882.05) &amp; EMA9↑(24086.0&gt;23912.11)</t>
+        </is>
+      </c>
+      <c r="H33" s="17" t="n">
+        <v>24086</v>
+      </c>
+      <c r="I33" s="17" t="n">
+        <v>23912.11</v>
+      </c>
+      <c r="J33" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K33" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L33" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N33" s="17" t="inlineStr">
+        <is>
+          <t>12:11 IST</t>
+        </is>
+      </c>
+      <c r="O33" s="17" t="n">
+        <v>23962.8</v>
+      </c>
+      <c r="P33" s="17" t="n">
+        <v>23882.05</v>
+      </c>
+      <c r="Q33" s="17" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="R33" s="17" t="inlineStr">
+        <is>
+          <t>23900 PE</t>
+        </is>
+      </c>
+      <c r="S33" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="T33" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U33" s="17" t="n">
+        <v>2990</v>
+      </c>
+      <c r="V33" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="W33" s="17" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="X33" s="17" t="n">
+        <v>47840</v>
+      </c>
+      <c r="Y33" s="17" t="n">
+        <v>47894.73</v>
+      </c>
+      <c r="Z33" s="17" t="n">
+        <v>251160</v>
+      </c>
+      <c r="AA33" s="17" t="n">
+        <v>14352</v>
+      </c>
+      <c r="AB33" s="17" t="n">
+        <v>14352</v>
+      </c>
+      <c r="AC33" s="17" t="n">
+        <v>14352</v>
+      </c>
+      <c r="AD33" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE33" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF33" s="17" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AG33" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH33" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI33" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ33" s="17" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="AK33" s="17" t="n">
+        <v>14297.27</v>
+      </c>
+      <c r="AL33" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM33" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN33" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -41482,7 +42814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN62"/>
+  <dimension ref="A1:AN64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -50770,6 +52102,310 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C63" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D63" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E63" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F63" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G63" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(23962.8&gt;23882.05) &amp; EMA9↑(24086.0&gt;23912.11)</t>
+        </is>
+      </c>
+      <c r="H63" s="15" t="n">
+        <v>24086</v>
+      </c>
+      <c r="I63" s="15" t="n">
+        <v>23912.11</v>
+      </c>
+      <c r="J63" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K63" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L63" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N63" s="15" t="inlineStr">
+        <is>
+          <t>10:01 IST</t>
+        </is>
+      </c>
+      <c r="O63" s="15" t="n">
+        <v>23962.8</v>
+      </c>
+      <c r="P63" s="15" t="n">
+        <v>23882.05</v>
+      </c>
+      <c r="Q63" s="15" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="R63" s="15" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="S63" s="15" t="n">
+        <v>33</v>
+      </c>
+      <c r="T63" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U63" s="15" t="n">
+        <v>2145</v>
+      </c>
+      <c r="V63" s="15" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="W63" s="15" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X63" s="15" t="n">
+        <v>47790.6</v>
+      </c>
+      <c r="Y63" s="15" t="n">
+        <v>47845.32</v>
+      </c>
+      <c r="Z63" s="15" t="n">
+        <v>166709.4</v>
+      </c>
+      <c r="AA63" s="15" t="n">
+        <v>14337.18</v>
+      </c>
+      <c r="AB63" s="15" t="n">
+        <v>14337.18</v>
+      </c>
+      <c r="AC63" s="15" t="n">
+        <v>-14328.6</v>
+      </c>
+      <c r="AD63" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE63" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF63" s="15" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="AG63" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH63" s="15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI63" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ63" s="15" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="AK63" s="15" t="n">
+        <v>-14383.32</v>
+      </c>
+      <c r="AL63" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM63" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN63" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C64" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D64" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E64" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F64" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G64" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(23962.8&gt;23882.05) &amp; EMA9↑(24086.0&gt;23912.11)</t>
+        </is>
+      </c>
+      <c r="H64" s="17" t="n">
+        <v>24086</v>
+      </c>
+      <c r="I64" s="17" t="n">
+        <v>23912.11</v>
+      </c>
+      <c r="J64" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K64" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L64" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N64" s="17" t="inlineStr">
+        <is>
+          <t>11:02 IST</t>
+        </is>
+      </c>
+      <c r="O64" s="17" t="n">
+        <v>23962.8</v>
+      </c>
+      <c r="P64" s="17" t="n">
+        <v>23882.05</v>
+      </c>
+      <c r="Q64" s="17" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="R64" s="17" t="inlineStr">
+        <is>
+          <t>23900 PE</t>
+        </is>
+      </c>
+      <c r="S64" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="T64" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U64" s="17" t="n">
+        <v>2015</v>
+      </c>
+      <c r="V64" s="17" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="W64" s="17" t="n">
+        <v>30.62</v>
+      </c>
+      <c r="X64" s="17" t="n">
+        <v>47453.25</v>
+      </c>
+      <c r="Y64" s="17" t="n">
+        <v>47507.92</v>
+      </c>
+      <c r="Z64" s="17" t="n">
+        <v>154046.75</v>
+      </c>
+      <c r="AA64" s="17" t="n">
+        <v>14235.98</v>
+      </c>
+      <c r="AB64" s="17" t="n">
+        <v>14235.98</v>
+      </c>
+      <c r="AC64" s="17" t="n">
+        <v>14246.05</v>
+      </c>
+      <c r="AD64" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE64" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF64" s="17" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="AG64" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH64" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI64" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ64" s="17" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="AK64" s="17" t="n">
+        <v>14191.38</v>
+      </c>
+      <c r="AL64" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM64" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN64" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -50784,7 +52420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN19"/>
+  <dimension ref="A1:AN20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -53601,6 +55237,158 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(23962.8&gt;23882.05) &amp; EMA9↑(24086.0&gt;23912.11)</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>24086</v>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>23912.11</v>
+      </c>
+      <c r="J20" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K20" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N20" s="15" t="inlineStr">
+        <is>
+          <t>10:32 IST</t>
+        </is>
+      </c>
+      <c r="O20" s="15" t="n">
+        <v>23962.8</v>
+      </c>
+      <c r="P20" s="15" t="n">
+        <v>23882.05</v>
+      </c>
+      <c r="Q20" s="15" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="R20" s="15" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="S20" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="T20" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U20" s="15" t="n">
+        <v>1950</v>
+      </c>
+      <c r="V20" s="15" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="W20" s="15" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="X20" s="15" t="n">
+        <v>47775</v>
+      </c>
+      <c r="Y20" s="15" t="n">
+        <v>47829.72</v>
+      </c>
+      <c r="Z20" s="15" t="n">
+        <v>147225</v>
+      </c>
+      <c r="AA20" s="15" t="n">
+        <v>14332.5</v>
+      </c>
+      <c r="AB20" s="15" t="n">
+        <v>14332.5</v>
+      </c>
+      <c r="AC20" s="15" t="n">
+        <v>-14332.5</v>
+      </c>
+      <c r="AD20" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE20" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF20" s="15" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="AG20" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH20" s="15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI20" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ20" s="15" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="AK20" s="15" t="n">
+        <v>-14387.22</v>
+      </c>
+      <c r="AL20" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM20" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN20" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA33"/>
+  <dimension ref="A1:AA34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3849,6 +3849,105 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="inlineStr">
+        <is>
+          <t>12:20 ET</t>
+        </is>
+      </c>
+      <c r="H34" s="17" t="n">
+        <v>29922</v>
+      </c>
+      <c r="I34" s="17" t="n">
+        <v>29900</v>
+      </c>
+      <c r="J34" s="17" t="n">
+        <v>29925</v>
+      </c>
+      <c r="K34" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L34" s="17" t="n">
+        <v>186.17</v>
+      </c>
+      <c r="M34" s="17" t="n">
+        <v>242.02</v>
+      </c>
+      <c r="N34" s="17" t="n">
+        <v>967.85</v>
+      </c>
+      <c r="O34" s="17" t="n">
+        <v>1569.15</v>
+      </c>
+      <c r="P34" s="17" t="n">
+        <v>279.25</v>
+      </c>
+      <c r="Q34" s="17" t="n">
+        <v>279.25</v>
+      </c>
+      <c r="R34" s="17" t="n">
+        <v>279.25</v>
+      </c>
+      <c r="S34" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T34" s="17" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="U34" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="V34" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W34" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="X34" s="17" t="n">
+        <v>242.25</v>
+      </c>
+      <c r="Y34" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z34" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA34" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -3863,7 +3962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN33"/>
+  <dimension ref="A1:AN34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8783,6 +8882,158 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H34" s="17" t="n">
+        <v>57686.08</v>
+      </c>
+      <c r="I34" s="17" t="n">
+        <v>56919.04</v>
+      </c>
+      <c r="J34" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K34" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L34" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="M34" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N34" s="17" t="inlineStr">
+        <is>
+          <t>09:56 IST</t>
+        </is>
+      </c>
+      <c r="O34" s="17" t="n">
+        <v>56742.6</v>
+      </c>
+      <c r="P34" s="17" t="n">
+        <v>58200.7</v>
+      </c>
+      <c r="Q34" s="17" t="inlineStr">
+        <is>
+          <t>56600 CE</t>
+        </is>
+      </c>
+      <c r="R34" s="17" t="inlineStr">
+        <is>
+          <t>56800 CE</t>
+        </is>
+      </c>
+      <c r="S34" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="T34" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U34" s="17" t="n">
+        <v>510</v>
+      </c>
+      <c r="V34" s="17" t="n">
+        <v>96.23</v>
+      </c>
+      <c r="W34" s="17" t="n">
+        <v>125.1</v>
+      </c>
+      <c r="X34" s="17" t="n">
+        <v>49077.3</v>
+      </c>
+      <c r="Y34" s="17" t="n">
+        <v>49132.22</v>
+      </c>
+      <c r="Z34" s="17" t="n">
+        <v>52922.7</v>
+      </c>
+      <c r="AA34" s="17" t="n">
+        <v>14723.19</v>
+      </c>
+      <c r="AB34" s="17" t="n">
+        <v>14723.19</v>
+      </c>
+      <c r="AC34" s="17" t="n">
+        <v>14723.7</v>
+      </c>
+      <c r="AD34" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE34" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF34" s="17" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="AG34" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH34" s="17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI34" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ34" s="17" t="n">
+        <v>54.92</v>
+      </c>
+      <c r="AK34" s="17" t="n">
+        <v>14668.78</v>
+      </c>
+      <c r="AL34" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM34" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN34" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -8797,7 +9048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN33"/>
+  <dimension ref="A1:AN34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13717,6 +13968,158 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F34" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G34" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H34" s="16" t="n">
+        <v>57686.08</v>
+      </c>
+      <c r="I34" s="16" t="n">
+        <v>56919.04</v>
+      </c>
+      <c r="J34" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K34" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L34" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="M34" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N34" s="16" t="inlineStr">
+        <is>
+          <t>15:14 IST</t>
+        </is>
+      </c>
+      <c r="O34" s="16" t="n">
+        <v>56742.6</v>
+      </c>
+      <c r="P34" s="16" t="n">
+        <v>58200.7</v>
+      </c>
+      <c r="Q34" s="16" t="inlineStr">
+        <is>
+          <t>56800 PE</t>
+        </is>
+      </c>
+      <c r="R34" s="16" t="inlineStr">
+        <is>
+          <t>56600 PE</t>
+        </is>
+      </c>
+      <c r="S34" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="T34" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U34" s="16" t="n">
+        <v>540</v>
+      </c>
+      <c r="V34" s="16" t="n">
+        <v>88.81999999999999</v>
+      </c>
+      <c r="W34" s="16" t="n">
+        <v>85.92</v>
+      </c>
+      <c r="X34" s="16" t="n">
+        <v>47962.8</v>
+      </c>
+      <c r="Y34" s="16" t="n">
+        <v>48017.55</v>
+      </c>
+      <c r="Z34" s="16" t="n">
+        <v>60037.2</v>
+      </c>
+      <c r="AA34" s="16" t="n">
+        <v>14388.84</v>
+      </c>
+      <c r="AB34" s="16" t="n">
+        <v>14388.84</v>
+      </c>
+      <c r="AC34" s="16" t="n">
+        <v>-1566</v>
+      </c>
+      <c r="AD34" s="16" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="AE34" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF34" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG34" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH34" s="16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI34" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ34" s="16" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="AK34" s="16" t="n">
+        <v>-1620.75</v>
+      </c>
+      <c r="AL34" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM34" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN34" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -13731,7 +14134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN64"/>
+  <dimension ref="A1:AN66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -23318,6 +23721,310 @@
         <v>50000</v>
       </c>
       <c r="AN64" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B65" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C65" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D65" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E65" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F65" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G65" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H65" s="15" t="n">
+        <v>57686.08</v>
+      </c>
+      <c r="I65" s="15" t="n">
+        <v>56919.04</v>
+      </c>
+      <c r="J65" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K65" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L65" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="M65" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N65" s="15" t="inlineStr">
+        <is>
+          <t>10:52 IST</t>
+        </is>
+      </c>
+      <c r="O65" s="15" t="n">
+        <v>56742.6</v>
+      </c>
+      <c r="P65" s="15" t="n">
+        <v>58200.7</v>
+      </c>
+      <c r="Q65" s="15" t="inlineStr">
+        <is>
+          <t>56600 CE</t>
+        </is>
+      </c>
+      <c r="R65" s="15" t="inlineStr">
+        <is>
+          <t>56800 CE</t>
+        </is>
+      </c>
+      <c r="S65" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T65" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U65" s="15" t="n">
+        <v>450</v>
+      </c>
+      <c r="V65" s="15" t="n">
+        <v>103.58</v>
+      </c>
+      <c r="W65" s="15" t="n">
+        <v>72.51000000000001</v>
+      </c>
+      <c r="X65" s="15" t="n">
+        <v>46611</v>
+      </c>
+      <c r="Y65" s="15" t="n">
+        <v>46665.53</v>
+      </c>
+      <c r="Z65" s="15" t="n">
+        <v>43389</v>
+      </c>
+      <c r="AA65" s="15" t="n">
+        <v>13983.3</v>
+      </c>
+      <c r="AB65" s="15" t="n">
+        <v>13983.3</v>
+      </c>
+      <c r="AC65" s="15" t="n">
+        <v>-13981.5</v>
+      </c>
+      <c r="AD65" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE65" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF65" s="15" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="AG65" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH65" s="15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI65" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ65" s="15" t="n">
+        <v>54.53</v>
+      </c>
+      <c r="AK65" s="15" t="n">
+        <v>-14036.03</v>
+      </c>
+      <c r="AL65" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM65" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN65" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B66" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C66" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D66" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E66" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F66" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G66" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H66" s="16" t="n">
+        <v>57686.08</v>
+      </c>
+      <c r="I66" s="16" t="n">
+        <v>56919.04</v>
+      </c>
+      <c r="J66" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K66" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L66" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="M66" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N66" s="16" t="inlineStr">
+        <is>
+          <t>14:16 IST</t>
+        </is>
+      </c>
+      <c r="O66" s="16" t="n">
+        <v>56742.6</v>
+      </c>
+      <c r="P66" s="16" t="n">
+        <v>58200.7</v>
+      </c>
+      <c r="Q66" s="16" t="inlineStr">
+        <is>
+          <t>56800 PE</t>
+        </is>
+      </c>
+      <c r="R66" s="16" t="inlineStr">
+        <is>
+          <t>56600 PE</t>
+        </is>
+      </c>
+      <c r="S66" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="T66" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U66" s="16" t="n">
+        <v>480</v>
+      </c>
+      <c r="V66" s="16" t="n">
+        <v>98.56</v>
+      </c>
+      <c r="W66" s="16" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="X66" s="16" t="n">
+        <v>47308.8</v>
+      </c>
+      <c r="Y66" s="16" t="n">
+        <v>47363.44</v>
+      </c>
+      <c r="Z66" s="16" t="n">
+        <v>48691.2</v>
+      </c>
+      <c r="AA66" s="16" t="n">
+        <v>14192.64</v>
+      </c>
+      <c r="AB66" s="16" t="n">
+        <v>14192.64</v>
+      </c>
+      <c r="AC66" s="16" t="n">
+        <v>1411.2</v>
+      </c>
+      <c r="AD66" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE66" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF66" s="16" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AG66" s="16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH66" s="16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI66" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ66" s="16" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="AK66" s="16" t="n">
+        <v>1356.56</v>
+      </c>
+      <c r="AL66" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM66" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN66" s="16" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -25859,7 +26566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -26867,6 +27574,72 @@
         <v>56936.69</v>
       </c>
       <c r="G31" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>24116.8</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>23907.04</v>
+      </c>
+      <c r="G32" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D33" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>57686.08</v>
+      </c>
+      <c r="F33" s="18" t="n">
+        <v>56919.04</v>
+      </c>
+      <c r="G33" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -26886,7 +27659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA33"/>
+  <dimension ref="A1:AA34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -30126,6 +30899,105 @@
         <v>1000</v>
       </c>
       <c r="AA33" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="inlineStr">
+        <is>
+          <t>10:51 ET</t>
+        </is>
+      </c>
+      <c r="H34" s="17" t="n">
+        <v>29922.25</v>
+      </c>
+      <c r="I34" s="17" t="n">
+        <v>29900</v>
+      </c>
+      <c r="J34" s="17" t="n">
+        <v>29925</v>
+      </c>
+      <c r="K34" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="L34" s="17" t="n">
+        <v>20.68</v>
+      </c>
+      <c r="M34" s="17" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="N34" s="17" t="n">
+        <v>982.08</v>
+      </c>
+      <c r="O34" s="17" t="n">
+        <v>1290.08</v>
+      </c>
+      <c r="P34" s="17" t="n">
+        <v>272.98</v>
+      </c>
+      <c r="Q34" s="17" t="n">
+        <v>272.98</v>
+      </c>
+      <c r="R34" s="17" t="n">
+        <v>272.8</v>
+      </c>
+      <c r="S34" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T34" s="17" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="U34" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="V34" s="17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="W34" s="17" t="n">
+        <v>72.16</v>
+      </c>
+      <c r="X34" s="17" t="n">
+        <v>200.64</v>
+      </c>
+      <c r="Y34" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z34" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA34" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -30245,7 +31117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32478,6 +33350,76 @@
         <v>78.72</v>
       </c>
       <c r="I64" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B65" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C65" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D65" s="19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E65" s="19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F65" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G65" s="19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H65" s="19" t="n">
+        <v>37</v>
+      </c>
+      <c r="I65" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B66" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C66" s="19" t="n">
+        <v>44</v>
+      </c>
+      <c r="D66" s="19" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E66" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="F66" s="19" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G66" s="19" t="n">
+        <v>36.08</v>
+      </c>
+      <c r="H66" s="19" t="n">
+        <v>72.16</v>
+      </c>
+      <c r="I66" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — PROFIT</t>
         </is>
@@ -32946,7 +33888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN33"/>
+  <dimension ref="A1:AN34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -37866,6 +38808,158 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F34" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G34" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H34" s="16" t="n">
+        <v>24116.8</v>
+      </c>
+      <c r="I34" s="16" t="n">
+        <v>23907.04</v>
+      </c>
+      <c r="J34" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K34" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L34" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N34" s="16" t="inlineStr">
+        <is>
+          <t>13:36 IST</t>
+        </is>
+      </c>
+      <c r="O34" s="16" t="n">
+        <v>23882.05</v>
+      </c>
+      <c r="P34" s="16" t="n">
+        <v>24398.7</v>
+      </c>
+      <c r="Q34" s="16" t="inlineStr">
+        <is>
+          <t>23800 CE</t>
+        </is>
+      </c>
+      <c r="R34" s="16" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="S34" s="16" t="n">
+        <v>39</v>
+      </c>
+      <c r="T34" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U34" s="16" t="n">
+        <v>2535</v>
+      </c>
+      <c r="V34" s="16" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="W34" s="16" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="X34" s="16" t="n">
+        <v>48088.95</v>
+      </c>
+      <c r="Y34" s="16" t="n">
+        <v>48143.72</v>
+      </c>
+      <c r="Z34" s="16" t="n">
+        <v>205411.05</v>
+      </c>
+      <c r="AA34" s="16" t="n">
+        <v>14426.68</v>
+      </c>
+      <c r="AB34" s="16" t="n">
+        <v>14426.68</v>
+      </c>
+      <c r="AC34" s="16" t="n">
+        <v>-304.2</v>
+      </c>
+      <c r="AD34" s="16" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="AE34" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF34" s="16" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="AG34" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH34" s="16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI34" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ34" s="16" t="n">
+        <v>54.77</v>
+      </c>
+      <c r="AK34" s="16" t="n">
+        <v>-358.97</v>
+      </c>
+      <c r="AL34" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM34" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN34" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -37880,7 +38974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN33"/>
+  <dimension ref="A1:AN34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42800,6 +43894,158 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H34" s="17" t="n">
+        <v>24116.8</v>
+      </c>
+      <c r="I34" s="17" t="n">
+        <v>23907.04</v>
+      </c>
+      <c r="J34" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K34" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N34" s="17" t="inlineStr">
+        <is>
+          <t>10:18 IST</t>
+        </is>
+      </c>
+      <c r="O34" s="17" t="n">
+        <v>23882.05</v>
+      </c>
+      <c r="P34" s="17" t="n">
+        <v>24398.7</v>
+      </c>
+      <c r="Q34" s="17" t="inlineStr">
+        <is>
+          <t>23900 PE</t>
+        </is>
+      </c>
+      <c r="R34" s="17" t="inlineStr">
+        <is>
+          <t>23800 PE</t>
+        </is>
+      </c>
+      <c r="S34" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="T34" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U34" s="17" t="n">
+        <v>2080</v>
+      </c>
+      <c r="V34" s="17" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="W34" s="17" t="n">
+        <v>29.89</v>
+      </c>
+      <c r="X34" s="17" t="n">
+        <v>47819.2</v>
+      </c>
+      <c r="Y34" s="17" t="n">
+        <v>47873.92</v>
+      </c>
+      <c r="Z34" s="17" t="n">
+        <v>160180.8</v>
+      </c>
+      <c r="AA34" s="17" t="n">
+        <v>14345.76</v>
+      </c>
+      <c r="AB34" s="17" t="n">
+        <v>14345.76</v>
+      </c>
+      <c r="AC34" s="17" t="n">
+        <v>14352</v>
+      </c>
+      <c r="AD34" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE34" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF34" s="17" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AG34" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH34" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI34" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ34" s="17" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="AK34" s="17" t="n">
+        <v>14297.28</v>
+      </c>
+      <c r="AL34" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM34" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN34" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -42814,7 +44060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN64"/>
+  <dimension ref="A1:AN66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -52401,6 +53647,310 @@
         <v>50000</v>
       </c>
       <c r="AN64" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B65" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C65" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D65" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E65" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F65" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G65" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H65" s="15" t="n">
+        <v>24116.8</v>
+      </c>
+      <c r="I65" s="15" t="n">
+        <v>23907.04</v>
+      </c>
+      <c r="J65" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K65" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L65" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N65" s="15" t="inlineStr">
+        <is>
+          <t>09:53 IST</t>
+        </is>
+      </c>
+      <c r="O65" s="15" t="n">
+        <v>23882.05</v>
+      </c>
+      <c r="P65" s="15" t="n">
+        <v>24398.7</v>
+      </c>
+      <c r="Q65" s="15" t="inlineStr">
+        <is>
+          <t>23800 CE</t>
+        </is>
+      </c>
+      <c r="R65" s="15" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="S65" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="T65" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U65" s="15" t="n">
+        <v>2600</v>
+      </c>
+      <c r="V65" s="15" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="W65" s="15" t="n">
+        <v>13.01</v>
+      </c>
+      <c r="X65" s="15" t="n">
+        <v>48334</v>
+      </c>
+      <c r="Y65" s="15" t="n">
+        <v>48388.81</v>
+      </c>
+      <c r="Z65" s="15" t="n">
+        <v>211666</v>
+      </c>
+      <c r="AA65" s="15" t="n">
+        <v>14500.2</v>
+      </c>
+      <c r="AB65" s="15" t="n">
+        <v>14500.2</v>
+      </c>
+      <c r="AC65" s="15" t="n">
+        <v>-14508</v>
+      </c>
+      <c r="AD65" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE65" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF65" s="15" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="AG65" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH65" s="15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI65" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ65" s="15" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="AK65" s="15" t="n">
+        <v>-14562.81</v>
+      </c>
+      <c r="AL65" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM65" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN65" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B66" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C66" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D66" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E66" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F66" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G66" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H66" s="16" t="n">
+        <v>24116.8</v>
+      </c>
+      <c r="I66" s="16" t="n">
+        <v>23907.04</v>
+      </c>
+      <c r="J66" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="K66" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L66" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N66" s="16" t="inlineStr">
+        <is>
+          <t>14:16 IST</t>
+        </is>
+      </c>
+      <c r="O66" s="16" t="n">
+        <v>23882.05</v>
+      </c>
+      <c r="P66" s="16" t="n">
+        <v>24398.7</v>
+      </c>
+      <c r="Q66" s="16" t="inlineStr">
+        <is>
+          <t>23900 PE</t>
+        </is>
+      </c>
+      <c r="R66" s="16" t="inlineStr">
+        <is>
+          <t>23800 PE</t>
+        </is>
+      </c>
+      <c r="S66" s="16" t="n">
+        <v>41</v>
+      </c>
+      <c r="T66" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U66" s="16" t="n">
+        <v>2665</v>
+      </c>
+      <c r="V66" s="16" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="W66" s="16" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="X66" s="16" t="n">
+        <v>48289.8</v>
+      </c>
+      <c r="Y66" s="16" t="n">
+        <v>48344.6</v>
+      </c>
+      <c r="Z66" s="16" t="n">
+        <v>218210.2</v>
+      </c>
+      <c r="AA66" s="16" t="n">
+        <v>14486.94</v>
+      </c>
+      <c r="AB66" s="16" t="n">
+        <v>14486.94</v>
+      </c>
+      <c r="AC66" s="16" t="n">
+        <v>1252.55</v>
+      </c>
+      <c r="AD66" s="16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE66" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF66" s="16" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="AG66" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH66" s="16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI66" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ66" s="16" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="AK66" s="16" t="n">
+        <v>1197.75</v>
+      </c>
+      <c r="AL66" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM66" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN66" s="16" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA34"/>
+  <dimension ref="A1:AA35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3948,6 +3948,105 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="inlineStr">
+        <is>
+          <t>11:08 ET</t>
+        </is>
+      </c>
+      <c r="H35" s="17" t="n">
+        <v>29855.25</v>
+      </c>
+      <c r="I35" s="17" t="n">
+        <v>29850</v>
+      </c>
+      <c r="J35" s="17" t="n">
+        <v>29875</v>
+      </c>
+      <c r="K35" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L35" s="17" t="n">
+        <v>188.12</v>
+      </c>
+      <c r="M35" s="17" t="n">
+        <v>244.56</v>
+      </c>
+      <c r="N35" s="17" t="n">
+        <v>977.6</v>
+      </c>
+      <c r="O35" s="17" t="n">
+        <v>1559.4</v>
+      </c>
+      <c r="P35" s="17" t="n">
+        <v>282.18</v>
+      </c>
+      <c r="Q35" s="17" t="n">
+        <v>282.18</v>
+      </c>
+      <c r="R35" s="17" t="n">
+        <v>282.2</v>
+      </c>
+      <c r="S35" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T35" s="17" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="U35" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="V35" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W35" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="X35" s="17" t="n">
+        <v>245.2</v>
+      </c>
+      <c r="Y35" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z35" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA35" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -3962,7 +4061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN34"/>
+  <dimension ref="A1:AN35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9034,6 +9133,158 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G35" s="16" t="inlineStr">
+        <is>
+          <t>Price↑(58045.9&gt;57252.45) &amp; EMA9↑(57687.91&gt;57060.71)</t>
+        </is>
+      </c>
+      <c r="H35" s="16" t="n">
+        <v>57687.91</v>
+      </c>
+      <c r="I35" s="16" t="n">
+        <v>57060.71</v>
+      </c>
+      <c r="J35" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K35" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L35" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="M35" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N35" s="16" t="inlineStr">
+        <is>
+          <t>13:53 IST</t>
+        </is>
+      </c>
+      <c r="O35" s="16" t="n">
+        <v>58045.9</v>
+      </c>
+      <c r="P35" s="16" t="n">
+        <v>57252.45</v>
+      </c>
+      <c r="Q35" s="16" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="R35" s="16" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="S35" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="T35" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U35" s="16" t="n">
+        <v>510</v>
+      </c>
+      <c r="V35" s="16" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="W35" s="16" t="n">
+        <v>94.56999999999999</v>
+      </c>
+      <c r="X35" s="16" t="n">
+        <v>47251.5</v>
+      </c>
+      <c r="Y35" s="16" t="n">
+        <v>47306.14</v>
+      </c>
+      <c r="Z35" s="16" t="n">
+        <v>54748.5</v>
+      </c>
+      <c r="AA35" s="16" t="n">
+        <v>14175.45</v>
+      </c>
+      <c r="AB35" s="16" t="n">
+        <v>14175.45</v>
+      </c>
+      <c r="AC35" s="16" t="n">
+        <v>979.2</v>
+      </c>
+      <c r="AD35" s="16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE35" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF35" s="16" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AG35" s="16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH35" s="16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI35" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ35" s="16" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="AK35" s="16" t="n">
+        <v>924.5599999999999</v>
+      </c>
+      <c r="AL35" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM35" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN35" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -9048,7 +9299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN34"/>
+  <dimension ref="A1:AN35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14120,6 +14371,158 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(58045.9&gt;57252.45) &amp; EMA9↑(57687.91&gt;57060.71)</t>
+        </is>
+      </c>
+      <c r="H35" s="17" t="n">
+        <v>57687.91</v>
+      </c>
+      <c r="I35" s="17" t="n">
+        <v>57060.71</v>
+      </c>
+      <c r="J35" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K35" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L35" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="M35" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N35" s="17" t="inlineStr">
+        <is>
+          <t>12:08 IST</t>
+        </is>
+      </c>
+      <c r="O35" s="17" t="n">
+        <v>58045.9</v>
+      </c>
+      <c r="P35" s="17" t="n">
+        <v>57252.45</v>
+      </c>
+      <c r="Q35" s="17" t="inlineStr">
+        <is>
+          <t>58200 PE</t>
+        </is>
+      </c>
+      <c r="R35" s="17" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="S35" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U35" s="17" t="n">
+        <v>600</v>
+      </c>
+      <c r="V35" s="17" t="n">
+        <v>80.16</v>
+      </c>
+      <c r="W35" s="17" t="n">
+        <v>104.21</v>
+      </c>
+      <c r="X35" s="17" t="n">
+        <v>48096</v>
+      </c>
+      <c r="Y35" s="17" t="n">
+        <v>48150.77</v>
+      </c>
+      <c r="Z35" s="17" t="n">
+        <v>71904</v>
+      </c>
+      <c r="AA35" s="17" t="n">
+        <v>14428.8</v>
+      </c>
+      <c r="AB35" s="17" t="n">
+        <v>14428.8</v>
+      </c>
+      <c r="AC35" s="17" t="n">
+        <v>14430</v>
+      </c>
+      <c r="AD35" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE35" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF35" s="17" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="AG35" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH35" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI35" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ35" s="17" t="n">
+        <v>54.77</v>
+      </c>
+      <c r="AK35" s="17" t="n">
+        <v>14375.23</v>
+      </c>
+      <c r="AL35" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM35" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN35" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -14134,7 +14537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN66"/>
+  <dimension ref="A1:AN68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -24030,6 +24433,310 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B67" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C67" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D67" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E67" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F67" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G67" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(58045.9&gt;57252.45) &amp; EMA9↑(57687.91&gt;57060.71)</t>
+        </is>
+      </c>
+      <c r="H67" s="17" t="n">
+        <v>57687.91</v>
+      </c>
+      <c r="I67" s="17" t="n">
+        <v>57060.71</v>
+      </c>
+      <c r="J67" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K67" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L67" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="M67" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N67" s="17" t="inlineStr">
+        <is>
+          <t>10:01 IST</t>
+        </is>
+      </c>
+      <c r="O67" s="17" t="n">
+        <v>58045.9</v>
+      </c>
+      <c r="P67" s="17" t="n">
+        <v>57252.45</v>
+      </c>
+      <c r="Q67" s="17" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="R67" s="17" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="S67" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T67" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U67" s="17" t="n">
+        <v>450</v>
+      </c>
+      <c r="V67" s="17" t="n">
+        <v>104.98</v>
+      </c>
+      <c r="W67" s="17" t="n">
+        <v>136.47</v>
+      </c>
+      <c r="X67" s="17" t="n">
+        <v>47241</v>
+      </c>
+      <c r="Y67" s="17" t="n">
+        <v>47295.63</v>
+      </c>
+      <c r="Z67" s="17" t="n">
+        <v>42759</v>
+      </c>
+      <c r="AA67" s="17" t="n">
+        <v>14172.3</v>
+      </c>
+      <c r="AB67" s="17" t="n">
+        <v>14172.3</v>
+      </c>
+      <c r="AC67" s="17" t="n">
+        <v>14170.5</v>
+      </c>
+      <c r="AD67" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE67" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF67" s="17" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AG67" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH67" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI67" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ67" s="17" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="AK67" s="17" t="n">
+        <v>14115.87</v>
+      </c>
+      <c r="AL67" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM67" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN67" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B68" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C68" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D68" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E68" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F68" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G68" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(58045.9&gt;57252.45) &amp; EMA9↑(57687.91&gt;57060.71)</t>
+        </is>
+      </c>
+      <c r="H68" s="17" t="n">
+        <v>57687.91</v>
+      </c>
+      <c r="I68" s="17" t="n">
+        <v>57060.71</v>
+      </c>
+      <c r="J68" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K68" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L68" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="M68" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N68" s="17" t="inlineStr">
+        <is>
+          <t>10:43 IST</t>
+        </is>
+      </c>
+      <c r="O68" s="17" t="n">
+        <v>58045.9</v>
+      </c>
+      <c r="P68" s="17" t="n">
+        <v>57252.45</v>
+      </c>
+      <c r="Q68" s="17" t="inlineStr">
+        <is>
+          <t>58200 PE</t>
+        </is>
+      </c>
+      <c r="R68" s="17" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="S68" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="T68" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U68" s="17" t="n">
+        <v>570</v>
+      </c>
+      <c r="V68" s="17" t="n">
+        <v>85.16</v>
+      </c>
+      <c r="W68" s="17" t="n">
+        <v>110.71</v>
+      </c>
+      <c r="X68" s="17" t="n">
+        <v>48541.2</v>
+      </c>
+      <c r="Y68" s="17" t="n">
+        <v>48596.04</v>
+      </c>
+      <c r="Z68" s="17" t="n">
+        <v>65458.8</v>
+      </c>
+      <c r="AA68" s="17" t="n">
+        <v>14562.36</v>
+      </c>
+      <c r="AB68" s="17" t="n">
+        <v>14562.36</v>
+      </c>
+      <c r="AC68" s="17" t="n">
+        <v>14563.5</v>
+      </c>
+      <c r="AD68" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE68" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF68" s="17" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="AG68" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH68" s="17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI68" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ68" s="17" t="n">
+        <v>54.84</v>
+      </c>
+      <c r="AK68" s="17" t="n">
+        <v>14508.66</v>
+      </c>
+      <c r="AL68" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM68" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN68" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -24044,7 +24751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN17"/>
+  <dimension ref="A1:AN18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -26552,6 +27259,158 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G18" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(58045.9&gt;57252.45) &amp; EMA9↑(57687.91&gt;57060.71)</t>
+        </is>
+      </c>
+      <c r="H18" s="17" t="n">
+        <v>57687.91</v>
+      </c>
+      <c r="I18" s="17" t="n">
+        <v>57060.71</v>
+      </c>
+      <c r="J18" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K18" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L18" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="M18" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N18" s="17" t="inlineStr">
+        <is>
+          <t>11:04 IST</t>
+        </is>
+      </c>
+      <c r="O18" s="17" t="n">
+        <v>58045.9</v>
+      </c>
+      <c r="P18" s="17" t="n">
+        <v>57252.45</v>
+      </c>
+      <c r="Q18" s="17" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="R18" s="17" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="S18" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="T18" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U18" s="17" t="n">
+        <v>480</v>
+      </c>
+      <c r="V18" s="17" t="n">
+        <v>96.97</v>
+      </c>
+      <c r="W18" s="17" t="n">
+        <v>126.06</v>
+      </c>
+      <c r="X18" s="17" t="n">
+        <v>46545.6</v>
+      </c>
+      <c r="Y18" s="17" t="n">
+        <v>46600.12</v>
+      </c>
+      <c r="Z18" s="17" t="n">
+        <v>49454.4</v>
+      </c>
+      <c r="AA18" s="17" t="n">
+        <v>13963.68</v>
+      </c>
+      <c r="AB18" s="17" t="n">
+        <v>13963.68</v>
+      </c>
+      <c r="AC18" s="17" t="n">
+        <v>13963.2</v>
+      </c>
+      <c r="AD18" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE18" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF18" s="17" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="AG18" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH18" s="17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI18" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ18" s="17" t="n">
+        <v>54.52</v>
+      </c>
+      <c r="AK18" s="17" t="n">
+        <v>13908.68</v>
+      </c>
+      <c r="AL18" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM18" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN18" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -27659,7 +28518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA34"/>
+  <dimension ref="A1:AA35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -30998,6 +31857,105 @@
         <v>1000</v>
       </c>
       <c r="AA34" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="inlineStr">
+        <is>
+          <t>11:41 ET</t>
+        </is>
+      </c>
+      <c r="H35" s="17" t="n">
+        <v>29854</v>
+      </c>
+      <c r="I35" s="17" t="n">
+        <v>29850</v>
+      </c>
+      <c r="J35" s="17" t="n">
+        <v>29875</v>
+      </c>
+      <c r="K35" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="L35" s="17" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="M35" s="17" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="N35" s="17" t="n">
+        <v>978.67</v>
+      </c>
+      <c r="O35" s="17" t="n">
+        <v>1138.57</v>
+      </c>
+      <c r="P35" s="17" t="n">
+        <v>273.43</v>
+      </c>
+      <c r="Q35" s="17" t="n">
+        <v>273.43</v>
+      </c>
+      <c r="R35" s="17" t="n">
+        <v>273.47</v>
+      </c>
+      <c r="S35" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T35" s="17" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="U35" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="V35" s="17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W35" s="17" t="n">
+        <v>67.23999999999999</v>
+      </c>
+      <c r="X35" s="17" t="n">
+        <v>206.23</v>
+      </c>
+      <c r="Y35" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z35" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA35" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -31117,7 +32075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -33420,6 +34378,76 @@
         <v>72.16</v>
       </c>
       <c r="I66" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B67" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C67" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D67" s="19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E67" s="19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F67" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G67" s="19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H67" s="19" t="n">
+        <v>37</v>
+      </c>
+      <c r="I67" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B68" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C68" s="19" t="n">
+        <v>41</v>
+      </c>
+      <c r="D68" s="19" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="E68" s="19" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F68" s="19" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G68" s="19" t="n">
+        <v>33.62</v>
+      </c>
+      <c r="H68" s="19" t="n">
+        <v>67.23999999999999</v>
+      </c>
+      <c r="I68" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — PROFIT</t>
         </is>
@@ -33888,7 +34916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN34"/>
+  <dimension ref="A1:AN35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -38960,6 +39988,158 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G35" s="16" t="inlineStr">
+        <is>
+          <t>Price↑(24206.9&gt;23962.8) &amp; EMA9↑(24110.13&gt;23937.59)</t>
+        </is>
+      </c>
+      <c r="H35" s="16" t="n">
+        <v>24110.13</v>
+      </c>
+      <c r="I35" s="16" t="n">
+        <v>23937.59</v>
+      </c>
+      <c r="J35" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K35" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L35" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="M35" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N35" s="16" t="inlineStr">
+        <is>
+          <t>13:56 IST</t>
+        </is>
+      </c>
+      <c r="O35" s="16" t="n">
+        <v>24206.9</v>
+      </c>
+      <c r="P35" s="16" t="n">
+        <v>23962.8</v>
+      </c>
+      <c r="Q35" s="16" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="R35" s="16" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="S35" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U35" s="16" t="n">
+        <v>1300</v>
+      </c>
+      <c r="V35" s="16" t="n">
+        <v>37.17</v>
+      </c>
+      <c r="W35" s="16" t="n">
+        <v>38.21</v>
+      </c>
+      <c r="X35" s="16" t="n">
+        <v>48321</v>
+      </c>
+      <c r="Y35" s="16" t="n">
+        <v>48375.8</v>
+      </c>
+      <c r="Z35" s="16" t="n">
+        <v>81679</v>
+      </c>
+      <c r="AA35" s="16" t="n">
+        <v>14496.3</v>
+      </c>
+      <c r="AB35" s="16" t="n">
+        <v>14496.3</v>
+      </c>
+      <c r="AC35" s="16" t="n">
+        <v>1352</v>
+      </c>
+      <c r="AD35" s="16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE35" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF35" s="16" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="AG35" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH35" s="16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI35" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ35" s="16" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="AK35" s="16" t="n">
+        <v>1297.2</v>
+      </c>
+      <c r="AL35" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM35" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN35" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -38974,7 +40154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN34"/>
+  <dimension ref="A1:AN35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -44046,6 +45226,158 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24206.9&gt;23962.8) &amp; EMA9↑(24110.13&gt;23937.59)</t>
+        </is>
+      </c>
+      <c r="H35" s="17" t="n">
+        <v>24110.13</v>
+      </c>
+      <c r="I35" s="17" t="n">
+        <v>23937.59</v>
+      </c>
+      <c r="J35" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K35" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L35" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M35" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N35" s="17" t="inlineStr">
+        <is>
+          <t>10:23 IST</t>
+        </is>
+      </c>
+      <c r="O35" s="17" t="n">
+        <v>24206.9</v>
+      </c>
+      <c r="P35" s="17" t="n">
+        <v>23962.8</v>
+      </c>
+      <c r="Q35" s="17" t="inlineStr">
+        <is>
+          <t>24300 PE</t>
+        </is>
+      </c>
+      <c r="R35" s="17" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="S35" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U35" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="V35" s="17" t="n">
+        <v>37.68</v>
+      </c>
+      <c r="W35" s="17" t="n">
+        <v>48.98</v>
+      </c>
+      <c r="X35" s="17" t="n">
+        <v>48984</v>
+      </c>
+      <c r="Y35" s="17" t="n">
+        <v>49038.91</v>
+      </c>
+      <c r="Z35" s="17" t="n">
+        <v>81016</v>
+      </c>
+      <c r="AA35" s="17" t="n">
+        <v>14695.2</v>
+      </c>
+      <c r="AB35" s="17" t="n">
+        <v>14695.2</v>
+      </c>
+      <c r="AC35" s="17" t="n">
+        <v>14690</v>
+      </c>
+      <c r="AD35" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE35" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF35" s="17" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="AG35" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH35" s="17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI35" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ35" s="17" t="n">
+        <v>54.91</v>
+      </c>
+      <c r="AK35" s="17" t="n">
+        <v>14635.09</v>
+      </c>
+      <c r="AL35" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM35" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN35" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -44060,7 +45392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN66"/>
+  <dimension ref="A1:AN68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -53956,6 +55288,310 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B67" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C67" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D67" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E67" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F67" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G67" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24206.9&gt;23962.8) &amp; EMA9↑(24110.13&gt;23937.59)</t>
+        </is>
+      </c>
+      <c r="H67" s="17" t="n">
+        <v>24110.13</v>
+      </c>
+      <c r="I67" s="17" t="n">
+        <v>23937.59</v>
+      </c>
+      <c r="J67" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K67" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L67" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M67" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N67" s="17" t="inlineStr">
+        <is>
+          <t>11:44 IST</t>
+        </is>
+      </c>
+      <c r="O67" s="17" t="n">
+        <v>24206.9</v>
+      </c>
+      <c r="P67" s="17" t="n">
+        <v>23962.8</v>
+      </c>
+      <c r="Q67" s="17" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="R67" s="17" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="S67" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="T67" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U67" s="17" t="n">
+        <v>1170</v>
+      </c>
+      <c r="V67" s="17" t="n">
+        <v>39.97</v>
+      </c>
+      <c r="W67" s="17" t="n">
+        <v>51.96</v>
+      </c>
+      <c r="X67" s="17" t="n">
+        <v>46764.9</v>
+      </c>
+      <c r="Y67" s="17" t="n">
+        <v>46819.46</v>
+      </c>
+      <c r="Z67" s="17" t="n">
+        <v>70235.10000000001</v>
+      </c>
+      <c r="AA67" s="17" t="n">
+        <v>14029.47</v>
+      </c>
+      <c r="AB67" s="17" t="n">
+        <v>14029.47</v>
+      </c>
+      <c r="AC67" s="17" t="n">
+        <v>14028.3</v>
+      </c>
+      <c r="AD67" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE67" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF67" s="17" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AG67" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH67" s="17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI67" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ67" s="17" t="n">
+        <v>54.56</v>
+      </c>
+      <c r="AK67" s="17" t="n">
+        <v>13973.74</v>
+      </c>
+      <c r="AL67" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM67" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN67" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C68" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D68" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E68" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F68" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G68" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(24206.9&gt;23962.8) &amp; EMA9↑(24110.13&gt;23937.59)</t>
+        </is>
+      </c>
+      <c r="H68" s="15" t="n">
+        <v>24110.13</v>
+      </c>
+      <c r="I68" s="15" t="n">
+        <v>23937.59</v>
+      </c>
+      <c r="J68" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K68" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L68" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="M68" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N68" s="15" t="inlineStr">
+        <is>
+          <t>11:11 IST</t>
+        </is>
+      </c>
+      <c r="O68" s="15" t="n">
+        <v>24206.9</v>
+      </c>
+      <c r="P68" s="15" t="n">
+        <v>23962.8</v>
+      </c>
+      <c r="Q68" s="15" t="inlineStr">
+        <is>
+          <t>24300 PE</t>
+        </is>
+      </c>
+      <c r="R68" s="15" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="S68" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="T68" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U68" s="15" t="n">
+        <v>1885</v>
+      </c>
+      <c r="V68" s="15" t="n">
+        <v>25.48</v>
+      </c>
+      <c r="W68" s="15" t="n">
+        <v>17.84</v>
+      </c>
+      <c r="X68" s="15" t="n">
+        <v>48029.8</v>
+      </c>
+      <c r="Y68" s="15" t="n">
+        <v>48084.56</v>
+      </c>
+      <c r="Z68" s="15" t="n">
+        <v>140470.2</v>
+      </c>
+      <c r="AA68" s="15" t="n">
+        <v>14408.94</v>
+      </c>
+      <c r="AB68" s="15" t="n">
+        <v>14408.94</v>
+      </c>
+      <c r="AC68" s="15" t="n">
+        <v>-14401.4</v>
+      </c>
+      <c r="AD68" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE68" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF68" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG68" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH68" s="15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI68" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ68" s="15" t="n">
+        <v>54.76</v>
+      </c>
+      <c r="AK68" s="15" t="n">
+        <v>-14456.16</v>
+      </c>
+      <c r="AL68" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM68" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN68" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -53970,7 +55606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN20"/>
+  <dimension ref="A1:AN21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -56939,6 +58575,158 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(24206.9&gt;23962.8) &amp; EMA9↑(24110.13&gt;23937.59)</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>24110.13</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>23937.59</v>
+      </c>
+      <c r="J21" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K21" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L21" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="M21" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N21" s="15" t="inlineStr">
+        <is>
+          <t>10:24 IST</t>
+        </is>
+      </c>
+      <c r="O21" s="15" t="n">
+        <v>24206.9</v>
+      </c>
+      <c r="P21" s="15" t="n">
+        <v>23962.8</v>
+      </c>
+      <c r="Q21" s="15" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="R21" s="15" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="S21" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="T21" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U21" s="15" t="n">
+        <v>1235</v>
+      </c>
+      <c r="V21" s="15" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="W21" s="15" t="n">
+        <v>27.31</v>
+      </c>
+      <c r="X21" s="15" t="n">
+        <v>48189.7</v>
+      </c>
+      <c r="Y21" s="15" t="n">
+        <v>48244.48</v>
+      </c>
+      <c r="Z21" s="15" t="n">
+        <v>75310.3</v>
+      </c>
+      <c r="AA21" s="15" t="n">
+        <v>14456.91</v>
+      </c>
+      <c r="AB21" s="15" t="n">
+        <v>14456.91</v>
+      </c>
+      <c r="AC21" s="15" t="n">
+        <v>-14461.85</v>
+      </c>
+      <c r="AD21" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE21" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF21" s="15" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="AG21" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH21" s="15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI21" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ21" s="15" t="n">
+        <v>54.78</v>
+      </c>
+      <c r="AK21" s="15" t="n">
+        <v>-14516.63</v>
+      </c>
+      <c r="AL21" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM21" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN21" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA35"/>
+  <dimension ref="A1:AA36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4047,6 +4047,105 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="inlineStr">
+        <is>
+          <t>12:53 ET</t>
+        </is>
+      </c>
+      <c r="H36" s="17" t="n">
+        <v>30043.75</v>
+      </c>
+      <c r="I36" s="17" t="n">
+        <v>30025</v>
+      </c>
+      <c r="J36" s="17" t="n">
+        <v>30050</v>
+      </c>
+      <c r="K36" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L36" s="17" t="n">
+        <v>186.13</v>
+      </c>
+      <c r="M36" s="17" t="n">
+        <v>241.97</v>
+      </c>
+      <c r="N36" s="17" t="n">
+        <v>967.65</v>
+      </c>
+      <c r="O36" s="17" t="n">
+        <v>1569.35</v>
+      </c>
+      <c r="P36" s="17" t="n">
+        <v>279.19</v>
+      </c>
+      <c r="Q36" s="17" t="n">
+        <v>279.19</v>
+      </c>
+      <c r="R36" s="17" t="n">
+        <v>279.2</v>
+      </c>
+      <c r="S36" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T36" s="17" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="U36" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="V36" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W36" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="X36" s="17" t="n">
+        <v>242.2</v>
+      </c>
+      <c r="Y36" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z36" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA36" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -4061,7 +4160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN35"/>
+  <dimension ref="A1:AN36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9285,6 +9384,158 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(57252.45&gt;56742.6) &amp; EMA9↑(57598.41&gt;56962.19)</t>
+        </is>
+      </c>
+      <c r="H36" s="17" t="n">
+        <v>57598.41</v>
+      </c>
+      <c r="I36" s="17" t="n">
+        <v>56962.19</v>
+      </c>
+      <c r="J36" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K36" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L36" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="M36" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N36" s="17" t="inlineStr">
+        <is>
+          <t>10:35 IST</t>
+        </is>
+      </c>
+      <c r="O36" s="17" t="n">
+        <v>57252.45</v>
+      </c>
+      <c r="P36" s="17" t="n">
+        <v>56742.6</v>
+      </c>
+      <c r="Q36" s="17" t="inlineStr">
+        <is>
+          <t>57200 CE</t>
+        </is>
+      </c>
+      <c r="R36" s="17" t="inlineStr">
+        <is>
+          <t>57400 CE</t>
+        </is>
+      </c>
+      <c r="S36" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U36" s="17" t="n">
+        <v>450</v>
+      </c>
+      <c r="V36" s="17" t="n">
+        <v>109.69</v>
+      </c>
+      <c r="W36" s="17" t="n">
+        <v>142.6</v>
+      </c>
+      <c r="X36" s="17" t="n">
+        <v>49360.5</v>
+      </c>
+      <c r="Y36" s="17" t="n">
+        <v>49415.47</v>
+      </c>
+      <c r="Z36" s="17" t="n">
+        <v>40639.5</v>
+      </c>
+      <c r="AA36" s="17" t="n">
+        <v>14808.15</v>
+      </c>
+      <c r="AB36" s="17" t="n">
+        <v>14808.15</v>
+      </c>
+      <c r="AC36" s="17" t="n">
+        <v>14809.5</v>
+      </c>
+      <c r="AD36" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE36" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF36" s="17" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="AG36" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH36" s="17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI36" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ36" s="17" t="n">
+        <v>54.97</v>
+      </c>
+      <c r="AK36" s="17" t="n">
+        <v>14754.53</v>
+      </c>
+      <c r="AL36" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM36" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN36" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -9299,7 +9550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN35"/>
+  <dimension ref="A1:AN36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14523,6 +14774,158 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F36" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G36" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(57252.45&gt;56742.6) &amp; EMA9↑(57598.41&gt;56962.19)</t>
+        </is>
+      </c>
+      <c r="H36" s="15" t="n">
+        <v>57598.41</v>
+      </c>
+      <c r="I36" s="15" t="n">
+        <v>56962.19</v>
+      </c>
+      <c r="J36" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K36" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L36" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="M36" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N36" s="15" t="inlineStr">
+        <is>
+          <t>10:03 IST</t>
+        </is>
+      </c>
+      <c r="O36" s="15" t="n">
+        <v>57252.45</v>
+      </c>
+      <c r="P36" s="15" t="n">
+        <v>56742.6</v>
+      </c>
+      <c r="Q36" s="15" t="inlineStr">
+        <is>
+          <t>57400 PE</t>
+        </is>
+      </c>
+      <c r="R36" s="15" t="inlineStr">
+        <is>
+          <t>57200 PE</t>
+        </is>
+      </c>
+      <c r="S36" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="T36" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U36" s="15" t="n">
+        <v>480</v>
+      </c>
+      <c r="V36" s="15" t="n">
+        <v>96.81</v>
+      </c>
+      <c r="W36" s="15" t="n">
+        <v>67.77</v>
+      </c>
+      <c r="X36" s="15" t="n">
+        <v>46468.8</v>
+      </c>
+      <c r="Y36" s="15" t="n">
+        <v>46523.31</v>
+      </c>
+      <c r="Z36" s="15" t="n">
+        <v>49531.2</v>
+      </c>
+      <c r="AA36" s="15" t="n">
+        <v>13940.64</v>
+      </c>
+      <c r="AB36" s="15" t="n">
+        <v>13940.64</v>
+      </c>
+      <c r="AC36" s="15" t="n">
+        <v>-13939.2</v>
+      </c>
+      <c r="AD36" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE36" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF36" s="15" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="AG36" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH36" s="15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI36" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ36" s="15" t="n">
+        <v>54.51</v>
+      </c>
+      <c r="AK36" s="15" t="n">
+        <v>-13993.71</v>
+      </c>
+      <c r="AL36" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM36" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN36" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -14537,7 +14940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN68"/>
+  <dimension ref="A1:AN70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -24737,6 +25140,310 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B69" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C69" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D69" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E69" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F69" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G69" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(57252.45&gt;56742.6) &amp; EMA9↑(57598.41&gt;56962.19)</t>
+        </is>
+      </c>
+      <c r="H69" s="17" t="n">
+        <v>57598.41</v>
+      </c>
+      <c r="I69" s="17" t="n">
+        <v>56962.19</v>
+      </c>
+      <c r="J69" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K69" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L69" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="M69" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N69" s="17" t="inlineStr">
+        <is>
+          <t>10:32 IST</t>
+        </is>
+      </c>
+      <c r="O69" s="17" t="n">
+        <v>57252.45</v>
+      </c>
+      <c r="P69" s="17" t="n">
+        <v>56742.6</v>
+      </c>
+      <c r="Q69" s="17" t="inlineStr">
+        <is>
+          <t>57200 CE</t>
+        </is>
+      </c>
+      <c r="R69" s="17" t="inlineStr">
+        <is>
+          <t>57400 CE</t>
+        </is>
+      </c>
+      <c r="S69" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="T69" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U69" s="17" t="n">
+        <v>480</v>
+      </c>
+      <c r="V69" s="17" t="n">
+        <v>100.29</v>
+      </c>
+      <c r="W69" s="17" t="n">
+        <v>130.38</v>
+      </c>
+      <c r="X69" s="17" t="n">
+        <v>48139.2</v>
+      </c>
+      <c r="Y69" s="17" t="n">
+        <v>48193.98</v>
+      </c>
+      <c r="Z69" s="17" t="n">
+        <v>47860.8</v>
+      </c>
+      <c r="AA69" s="17" t="n">
+        <v>14441.76</v>
+      </c>
+      <c r="AB69" s="17" t="n">
+        <v>14441.76</v>
+      </c>
+      <c r="AC69" s="17" t="n">
+        <v>14443.2</v>
+      </c>
+      <c r="AD69" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE69" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF69" s="17" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="AG69" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH69" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI69" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ69" s="17" t="n">
+        <v>54.78</v>
+      </c>
+      <c r="AK69" s="17" t="n">
+        <v>14388.42</v>
+      </c>
+      <c r="AL69" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM69" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN69" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B70" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C70" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D70" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E70" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F70" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G70" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(57252.45&gt;56742.6) &amp; EMA9↑(57598.41&gt;56962.19)</t>
+        </is>
+      </c>
+      <c r="H70" s="17" t="n">
+        <v>57598.41</v>
+      </c>
+      <c r="I70" s="17" t="n">
+        <v>56962.19</v>
+      </c>
+      <c r="J70" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K70" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L70" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="M70" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N70" s="17" t="inlineStr">
+        <is>
+          <t>10:56 IST</t>
+        </is>
+      </c>
+      <c r="O70" s="17" t="n">
+        <v>57252.45</v>
+      </c>
+      <c r="P70" s="17" t="n">
+        <v>56742.6</v>
+      </c>
+      <c r="Q70" s="17" t="inlineStr">
+        <is>
+          <t>57400 PE</t>
+        </is>
+      </c>
+      <c r="R70" s="17" t="inlineStr">
+        <is>
+          <t>57200 PE</t>
+        </is>
+      </c>
+      <c r="S70" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="T70" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U70" s="17" t="n">
+        <v>510</v>
+      </c>
+      <c r="V70" s="17" t="n">
+        <v>94.73</v>
+      </c>
+      <c r="W70" s="17" t="n">
+        <v>123.15</v>
+      </c>
+      <c r="X70" s="17" t="n">
+        <v>48312.3</v>
+      </c>
+      <c r="Y70" s="17" t="n">
+        <v>48367.1</v>
+      </c>
+      <c r="Z70" s="17" t="n">
+        <v>53687.7</v>
+      </c>
+      <c r="AA70" s="17" t="n">
+        <v>14493.69</v>
+      </c>
+      <c r="AB70" s="17" t="n">
+        <v>14493.69</v>
+      </c>
+      <c r="AC70" s="17" t="n">
+        <v>14494.2</v>
+      </c>
+      <c r="AD70" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE70" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF70" s="17" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="AG70" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH70" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI70" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ70" s="17" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="AK70" s="17" t="n">
+        <v>14439.4</v>
+      </c>
+      <c r="AL70" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM70" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN70" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -24751,7 +25458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN18"/>
+  <dimension ref="A1:AN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -27411,6 +28118,158 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(57252.45&gt;56742.6) &amp; EMA9↑(57598.41&gt;56962.19)</t>
+        </is>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>57598.41</v>
+      </c>
+      <c r="I19" s="17" t="n">
+        <v>56962.19</v>
+      </c>
+      <c r="J19" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K19" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L19" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="M19" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N19" s="17" t="inlineStr">
+        <is>
+          <t>11:13 IST</t>
+        </is>
+      </c>
+      <c r="O19" s="17" t="n">
+        <v>57252.45</v>
+      </c>
+      <c r="P19" s="17" t="n">
+        <v>56742.6</v>
+      </c>
+      <c r="Q19" s="17" t="inlineStr">
+        <is>
+          <t>57200 CE</t>
+        </is>
+      </c>
+      <c r="R19" s="17" t="inlineStr">
+        <is>
+          <t>57400 CE</t>
+        </is>
+      </c>
+      <c r="S19" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U19" s="17" t="n">
+        <v>450</v>
+      </c>
+      <c r="V19" s="17" t="n">
+        <v>102.94</v>
+      </c>
+      <c r="W19" s="17" t="n">
+        <v>133.82</v>
+      </c>
+      <c r="X19" s="17" t="n">
+        <v>46323</v>
+      </c>
+      <c r="Y19" s="17" t="n">
+        <v>46377.49</v>
+      </c>
+      <c r="Z19" s="17" t="n">
+        <v>43677</v>
+      </c>
+      <c r="AA19" s="17" t="n">
+        <v>13896.9</v>
+      </c>
+      <c r="AB19" s="17" t="n">
+        <v>13896.9</v>
+      </c>
+      <c r="AC19" s="17" t="n">
+        <v>13896</v>
+      </c>
+      <c r="AD19" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE19" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF19" s="17" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="AG19" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH19" s="17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI19" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ19" s="17" t="n">
+        <v>54.49</v>
+      </c>
+      <c r="AK19" s="17" t="n">
+        <v>13841.51</v>
+      </c>
+      <c r="AL19" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM19" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN19" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -28518,7 +29377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA35"/>
+  <dimension ref="A1:AA36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -31956,6 +32815,105 @@
         <v>1000</v>
       </c>
       <c r="AA35" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F36" s="15" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G36" s="15" t="inlineStr">
+        <is>
+          <t>12:55 ET</t>
+        </is>
+      </c>
+      <c r="H36" s="15" t="n">
+        <v>30043.25</v>
+      </c>
+      <c r="I36" s="15" t="n">
+        <v>30025</v>
+      </c>
+      <c r="J36" s="15" t="n">
+        <v>30050</v>
+      </c>
+      <c r="K36" s="15" t="n">
+        <v>42</v>
+      </c>
+      <c r="L36" s="15" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="M36" s="15" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="N36" s="15" t="n">
+        <v>979.86</v>
+      </c>
+      <c r="O36" s="15" t="n">
+        <v>1189.02</v>
+      </c>
+      <c r="P36" s="15" t="n">
+        <v>273.29</v>
+      </c>
+      <c r="Q36" s="15" t="n">
+        <v>273.29</v>
+      </c>
+      <c r="R36" s="15" t="n">
+        <v>-273.42</v>
+      </c>
+      <c r="S36" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="T36" s="15" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="U36" s="15" t="n">
+        <v>42</v>
+      </c>
+      <c r="V36" s="15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W36" s="15" t="n">
+        <v>68.88</v>
+      </c>
+      <c r="X36" s="15" t="n">
+        <v>-342.3</v>
+      </c>
+      <c r="Y36" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="Z36" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA36" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -32075,7 +33033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -34450,6 +35408,76 @@
       <c r="I68" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B69" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C69" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D69" s="19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E69" s="19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F69" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G69" s="19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H69" s="19" t="n">
+        <v>37</v>
+      </c>
+      <c r="I69" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B70" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C70" s="19" t="n">
+        <v>42</v>
+      </c>
+      <c r="D70" s="19" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="E70" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="F70" s="19" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G70" s="19" t="n">
+        <v>34.44</v>
+      </c>
+      <c r="H70" s="19" t="n">
+        <v>68.88</v>
+      </c>
+      <c r="I70" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — STOP LOSS</t>
         </is>
       </c>
     </row>
@@ -34916,7 +35944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN35"/>
+  <dimension ref="A1:AN36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -40140,6 +41168,158 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E36" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G36" s="16" t="inlineStr">
+        <is>
+          <t>Price↑(23962.8&gt;23882.05) &amp; EMA9↑(24085.94&gt;23910.66)</t>
+        </is>
+      </c>
+      <c r="H36" s="16" t="n">
+        <v>24085.94</v>
+      </c>
+      <c r="I36" s="16" t="n">
+        <v>23910.66</v>
+      </c>
+      <c r="J36" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K36" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L36" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="M36" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N36" s="16" t="inlineStr">
+        <is>
+          <t>13:48 IST</t>
+        </is>
+      </c>
+      <c r="O36" s="16" t="n">
+        <v>23962.8</v>
+      </c>
+      <c r="P36" s="16" t="n">
+        <v>23882.05</v>
+      </c>
+      <c r="Q36" s="16" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="R36" s="16" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="S36" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="T36" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U36" s="16" t="n">
+        <v>1820</v>
+      </c>
+      <c r="V36" s="16" t="n">
+        <v>26.12</v>
+      </c>
+      <c r="W36" s="16" t="n">
+        <v>25.48</v>
+      </c>
+      <c r="X36" s="16" t="n">
+        <v>47538.4</v>
+      </c>
+      <c r="Y36" s="16" t="n">
+        <v>47593.08</v>
+      </c>
+      <c r="Z36" s="16" t="n">
+        <v>134461.6</v>
+      </c>
+      <c r="AA36" s="16" t="n">
+        <v>14261.52</v>
+      </c>
+      <c r="AB36" s="16" t="n">
+        <v>14261.52</v>
+      </c>
+      <c r="AC36" s="16" t="n">
+        <v>-1164.8</v>
+      </c>
+      <c r="AD36" s="16" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AE36" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF36" s="16" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AG36" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH36" s="16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI36" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ36" s="16" t="n">
+        <v>54.68</v>
+      </c>
+      <c r="AK36" s="16" t="n">
+        <v>-1219.48</v>
+      </c>
+      <c r="AL36" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM36" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN36" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -40154,7 +41334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN35"/>
+  <dimension ref="A1:AN36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -45378,6 +46558,158 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(23962.8&gt;23882.05) &amp; EMA9↑(24085.94&gt;23910.66)</t>
+        </is>
+      </c>
+      <c r="H36" s="17" t="n">
+        <v>24085.94</v>
+      </c>
+      <c r="I36" s="17" t="n">
+        <v>23910.66</v>
+      </c>
+      <c r="J36" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K36" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L36" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M36" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N36" s="17" t="inlineStr">
+        <is>
+          <t>10:44 IST</t>
+        </is>
+      </c>
+      <c r="O36" s="17" t="n">
+        <v>23962.8</v>
+      </c>
+      <c r="P36" s="17" t="n">
+        <v>23882.05</v>
+      </c>
+      <c r="Q36" s="17" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="R36" s="17" t="inlineStr">
+        <is>
+          <t>23900 PE</t>
+        </is>
+      </c>
+      <c r="S36" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="T36" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U36" s="17" t="n">
+        <v>1170</v>
+      </c>
+      <c r="V36" s="17" t="n">
+        <v>39.96</v>
+      </c>
+      <c r="W36" s="17" t="n">
+        <v>51.95</v>
+      </c>
+      <c r="X36" s="17" t="n">
+        <v>46753.2</v>
+      </c>
+      <c r="Y36" s="17" t="n">
+        <v>46807.76</v>
+      </c>
+      <c r="Z36" s="17" t="n">
+        <v>70246.8</v>
+      </c>
+      <c r="AA36" s="17" t="n">
+        <v>14025.96</v>
+      </c>
+      <c r="AB36" s="17" t="n">
+        <v>14025.96</v>
+      </c>
+      <c r="AC36" s="17" t="n">
+        <v>14028.3</v>
+      </c>
+      <c r="AD36" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE36" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF36" s="17" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="AG36" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH36" s="17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI36" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ36" s="17" t="n">
+        <v>54.56</v>
+      </c>
+      <c r="AK36" s="17" t="n">
+        <v>13973.74</v>
+      </c>
+      <c r="AL36" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM36" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN36" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -45392,7 +46724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN68"/>
+  <dimension ref="A1:AN70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -55592,6 +56924,310 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B69" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C69" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D69" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E69" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F69" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G69" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(23962.8&gt;23882.05) &amp; EMA9↑(24085.94&gt;23910.66)</t>
+        </is>
+      </c>
+      <c r="H69" s="17" t="n">
+        <v>24085.94</v>
+      </c>
+      <c r="I69" s="17" t="n">
+        <v>23910.66</v>
+      </c>
+      <c r="J69" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K69" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L69" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M69" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N69" s="17" t="inlineStr">
+        <is>
+          <t>09:44 IST</t>
+        </is>
+      </c>
+      <c r="O69" s="17" t="n">
+        <v>23962.8</v>
+      </c>
+      <c r="P69" s="17" t="n">
+        <v>23882.05</v>
+      </c>
+      <c r="Q69" s="17" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="R69" s="17" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="S69" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T69" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U69" s="17" t="n">
+        <v>1625</v>
+      </c>
+      <c r="V69" s="17" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="W69" s="17" t="n">
+        <v>37.89</v>
+      </c>
+      <c r="X69" s="17" t="n">
+        <v>47368.75</v>
+      </c>
+      <c r="Y69" s="17" t="n">
+        <v>47423.4</v>
+      </c>
+      <c r="Z69" s="17" t="n">
+        <v>115131.25</v>
+      </c>
+      <c r="AA69" s="17" t="n">
+        <v>14210.62</v>
+      </c>
+      <c r="AB69" s="17" t="n">
+        <v>14210.62</v>
+      </c>
+      <c r="AC69" s="17" t="n">
+        <v>14202.5</v>
+      </c>
+      <c r="AD69" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE69" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF69" s="17" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="AG69" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH69" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI69" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ69" s="17" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="AK69" s="17" t="n">
+        <v>14147.85</v>
+      </c>
+      <c r="AL69" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM69" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN69" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B70" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C70" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D70" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E70" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F70" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G70" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(23962.8&gt;23882.05) &amp; EMA9↑(24085.94&gt;23910.66)</t>
+        </is>
+      </c>
+      <c r="H70" s="17" t="n">
+        <v>24085.94</v>
+      </c>
+      <c r="I70" s="17" t="n">
+        <v>23910.66</v>
+      </c>
+      <c r="J70" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K70" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L70" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M70" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N70" s="17" t="inlineStr">
+        <is>
+          <t>10:32 IST</t>
+        </is>
+      </c>
+      <c r="O70" s="17" t="n">
+        <v>23962.8</v>
+      </c>
+      <c r="P70" s="17" t="n">
+        <v>23882.05</v>
+      </c>
+      <c r="Q70" s="17" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="R70" s="17" t="inlineStr">
+        <is>
+          <t>23900 PE</t>
+        </is>
+      </c>
+      <c r="S70" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="T70" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U70" s="17" t="n">
+        <v>1690</v>
+      </c>
+      <c r="V70" s="17" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="W70" s="17" t="n">
+        <v>36.83</v>
+      </c>
+      <c r="X70" s="17" t="n">
+        <v>47877.7</v>
+      </c>
+      <c r="Y70" s="17" t="n">
+        <v>47932.43</v>
+      </c>
+      <c r="Z70" s="17" t="n">
+        <v>121122.3</v>
+      </c>
+      <c r="AA70" s="17" t="n">
+        <v>14363.31</v>
+      </c>
+      <c r="AB70" s="17" t="n">
+        <v>14363.31</v>
+      </c>
+      <c r="AC70" s="17" t="n">
+        <v>14365</v>
+      </c>
+      <c r="AD70" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE70" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF70" s="17" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AG70" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH70" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI70" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ70" s="17" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="AK70" s="17" t="n">
+        <v>14310.27</v>
+      </c>
+      <c r="AL70" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM70" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN70" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -55606,7 +57242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN21"/>
+  <dimension ref="A1:AN22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -58727,6 +60363,158 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(23962.8&gt;23882.05) &amp; EMA9↑(24085.94&gt;23910.66)</t>
+        </is>
+      </c>
+      <c r="H22" s="17" t="n">
+        <v>24085.94</v>
+      </c>
+      <c r="I22" s="17" t="n">
+        <v>23910.66</v>
+      </c>
+      <c r="J22" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K22" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L22" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M22" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N22" s="17" t="inlineStr">
+        <is>
+          <t>12:10 IST</t>
+        </is>
+      </c>
+      <c r="O22" s="17" t="n">
+        <v>23962.8</v>
+      </c>
+      <c r="P22" s="17" t="n">
+        <v>23882.05</v>
+      </c>
+      <c r="Q22" s="17" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="R22" s="17" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="S22" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="T22" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U22" s="17" t="n">
+        <v>1495</v>
+      </c>
+      <c r="V22" s="17" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="W22" s="17" t="n">
+        <v>41.38</v>
+      </c>
+      <c r="X22" s="17" t="n">
+        <v>47585.85</v>
+      </c>
+      <c r="Y22" s="17" t="n">
+        <v>47640.54</v>
+      </c>
+      <c r="Z22" s="17" t="n">
+        <v>101914.15</v>
+      </c>
+      <c r="AA22" s="17" t="n">
+        <v>14275.75</v>
+      </c>
+      <c r="AB22" s="17" t="n">
+        <v>14275.75</v>
+      </c>
+      <c r="AC22" s="17" t="n">
+        <v>14277.25</v>
+      </c>
+      <c r="AD22" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE22" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF22" s="17" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AG22" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH22" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI22" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ22" s="17" t="n">
+        <v>54.69</v>
+      </c>
+      <c r="AK22" s="17" t="n">
+        <v>14222.56</v>
+      </c>
+      <c r="AL22" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM22" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN22" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA36"/>
+  <dimension ref="A1:AA37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4146,6 +4146,105 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D37" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F37" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="inlineStr">
+        <is>
+          <t>11:47 ET</t>
+        </is>
+      </c>
+      <c r="H37" s="17" t="n">
+        <v>29671.75</v>
+      </c>
+      <c r="I37" s="17" t="n">
+        <v>29650</v>
+      </c>
+      <c r="J37" s="17" t="n">
+        <v>29675</v>
+      </c>
+      <c r="K37" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="L37" s="17" t="n">
+        <v>139.54</v>
+      </c>
+      <c r="M37" s="17" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="N37" s="17" t="n">
+        <v>881.64</v>
+      </c>
+      <c r="O37" s="17" t="n">
+        <v>2162.76</v>
+      </c>
+      <c r="P37" s="17" t="n">
+        <v>251.17</v>
+      </c>
+      <c r="Q37" s="17" t="n">
+        <v>251.17</v>
+      </c>
+      <c r="R37" s="17" t="n">
+        <v>251.16</v>
+      </c>
+      <c r="S37" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T37" s="17" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="U37" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="V37" s="17" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="W37" s="17" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="X37" s="17" t="n">
+        <v>206.76</v>
+      </c>
+      <c r="Y37" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z37" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA37" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -4160,7 +4259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN36"/>
+  <dimension ref="A1:AN37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9536,6 +9635,158 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G37" s="16" t="inlineStr">
+        <is>
+          <t>Price↑(58131.45&gt;58045.9) &amp; EMA9↑(57775.18&gt;57179.74)</t>
+        </is>
+      </c>
+      <c r="H37" s="16" t="n">
+        <v>57775.18</v>
+      </c>
+      <c r="I37" s="16" t="n">
+        <v>57179.74</v>
+      </c>
+      <c r="J37" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K37" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L37" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="M37" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N37" s="16" t="inlineStr">
+        <is>
+          <t>14:04 IST</t>
+        </is>
+      </c>
+      <c r="O37" s="16" t="n">
+        <v>58131.45</v>
+      </c>
+      <c r="P37" s="16" t="n">
+        <v>58045.9</v>
+      </c>
+      <c r="Q37" s="16" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="R37" s="16" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="S37" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U37" s="16" t="n">
+        <v>450</v>
+      </c>
+      <c r="V37" s="16" t="n">
+        <v>105.93</v>
+      </c>
+      <c r="W37" s="16" t="n">
+        <v>110.52</v>
+      </c>
+      <c r="X37" s="16" t="n">
+        <v>47668.5</v>
+      </c>
+      <c r="Y37" s="16" t="n">
+        <v>47723.2</v>
+      </c>
+      <c r="Z37" s="16" t="n">
+        <v>42331.5</v>
+      </c>
+      <c r="AA37" s="16" t="n">
+        <v>14300.55</v>
+      </c>
+      <c r="AB37" s="16" t="n">
+        <v>14300.55</v>
+      </c>
+      <c r="AC37" s="16" t="n">
+        <v>2065.5</v>
+      </c>
+      <c r="AD37" s="16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE37" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF37" s="16" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="AG37" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH37" s="16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI37" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ37" s="16" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="AK37" s="16" t="n">
+        <v>2010.8</v>
+      </c>
+      <c r="AL37" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM37" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN37" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -9550,7 +9801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN36"/>
+  <dimension ref="A1:AN37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14926,6 +15177,158 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D37" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E37" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(58131.45&gt;58045.9) &amp; EMA9↑(57775.18&gt;57179.74)</t>
+        </is>
+      </c>
+      <c r="H37" s="17" t="n">
+        <v>57775.18</v>
+      </c>
+      <c r="I37" s="17" t="n">
+        <v>57179.74</v>
+      </c>
+      <c r="J37" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K37" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L37" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="M37" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N37" s="17" t="inlineStr">
+        <is>
+          <t>11:09 IST</t>
+        </is>
+      </c>
+      <c r="O37" s="17" t="n">
+        <v>58131.45</v>
+      </c>
+      <c r="P37" s="17" t="n">
+        <v>58045.9</v>
+      </c>
+      <c r="Q37" s="17" t="inlineStr">
+        <is>
+          <t>58200 PE</t>
+        </is>
+      </c>
+      <c r="R37" s="17" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="S37" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T37" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U37" s="17" t="n">
+        <v>600</v>
+      </c>
+      <c r="V37" s="17" t="n">
+        <v>81.65000000000001</v>
+      </c>
+      <c r="W37" s="17" t="n">
+        <v>106.15</v>
+      </c>
+      <c r="X37" s="17" t="n">
+        <v>48990</v>
+      </c>
+      <c r="Y37" s="17" t="n">
+        <v>49044.91</v>
+      </c>
+      <c r="Z37" s="17" t="n">
+        <v>71010</v>
+      </c>
+      <c r="AA37" s="17" t="n">
+        <v>14697</v>
+      </c>
+      <c r="AB37" s="17" t="n">
+        <v>14697</v>
+      </c>
+      <c r="AC37" s="17" t="n">
+        <v>14700</v>
+      </c>
+      <c r="AD37" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE37" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF37" s="17" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="AG37" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH37" s="17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI37" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ37" s="17" t="n">
+        <v>54.91</v>
+      </c>
+      <c r="AK37" s="17" t="n">
+        <v>14645.09</v>
+      </c>
+      <c r="AL37" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM37" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN37" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -14940,7 +15343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN70"/>
+  <dimension ref="A1:AN72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -25444,6 +25847,310 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C71" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D71" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E71" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F71" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G71" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(58131.45&gt;58045.9) &amp; EMA9↑(57775.18&gt;57179.74)</t>
+        </is>
+      </c>
+      <c r="H71" s="15" t="n">
+        <v>57775.18</v>
+      </c>
+      <c r="I71" s="15" t="n">
+        <v>57179.74</v>
+      </c>
+      <c r="J71" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K71" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L71" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="M71" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N71" s="15" t="inlineStr">
+        <is>
+          <t>10:11 IST</t>
+        </is>
+      </c>
+      <c r="O71" s="15" t="n">
+        <v>58131.45</v>
+      </c>
+      <c r="P71" s="15" t="n">
+        <v>58045.9</v>
+      </c>
+      <c r="Q71" s="15" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="R71" s="15" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="S71" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T71" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U71" s="15" t="n">
+        <v>450</v>
+      </c>
+      <c r="V71" s="15" t="n">
+        <v>108.77</v>
+      </c>
+      <c r="W71" s="15" t="n">
+        <v>76.14</v>
+      </c>
+      <c r="X71" s="15" t="n">
+        <v>48946.5</v>
+      </c>
+      <c r="Y71" s="15" t="n">
+        <v>49001.4</v>
+      </c>
+      <c r="Z71" s="15" t="n">
+        <v>41053.5</v>
+      </c>
+      <c r="AA71" s="15" t="n">
+        <v>14683.95</v>
+      </c>
+      <c r="AB71" s="15" t="n">
+        <v>14683.95</v>
+      </c>
+      <c r="AC71" s="15" t="n">
+        <v>-14683.5</v>
+      </c>
+      <c r="AD71" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE71" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF71" s="15" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="AG71" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH71" s="15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI71" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ71" s="15" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="AK71" s="15" t="n">
+        <v>-14738.4</v>
+      </c>
+      <c r="AL71" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM71" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN71" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B72" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C72" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D72" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E72" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F72" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G72" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(58131.45&gt;58045.9) &amp; EMA9↑(57775.18&gt;57179.74)</t>
+        </is>
+      </c>
+      <c r="H72" s="15" t="n">
+        <v>57775.18</v>
+      </c>
+      <c r="I72" s="15" t="n">
+        <v>57179.74</v>
+      </c>
+      <c r="J72" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K72" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L72" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="M72" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N72" s="15" t="inlineStr">
+        <is>
+          <t>10:10 IST</t>
+        </is>
+      </c>
+      <c r="O72" s="15" t="n">
+        <v>58131.45</v>
+      </c>
+      <c r="P72" s="15" t="n">
+        <v>58045.9</v>
+      </c>
+      <c r="Q72" s="15" t="inlineStr">
+        <is>
+          <t>58200 PE</t>
+        </is>
+      </c>
+      <c r="R72" s="15" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="S72" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="T72" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U72" s="15" t="n">
+        <v>540</v>
+      </c>
+      <c r="V72" s="15" t="n">
+        <v>87.41</v>
+      </c>
+      <c r="W72" s="15" t="n">
+        <v>61.19</v>
+      </c>
+      <c r="X72" s="15" t="n">
+        <v>47201.4</v>
+      </c>
+      <c r="Y72" s="15" t="n">
+        <v>47256.03</v>
+      </c>
+      <c r="Z72" s="15" t="n">
+        <v>60798.6</v>
+      </c>
+      <c r="AA72" s="15" t="n">
+        <v>14160.42</v>
+      </c>
+      <c r="AB72" s="15" t="n">
+        <v>14160.42</v>
+      </c>
+      <c r="AC72" s="15" t="n">
+        <v>-14158.8</v>
+      </c>
+      <c r="AD72" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE72" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF72" s="15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AG72" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH72" s="15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI72" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ72" s="15" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="AK72" s="15" t="n">
+        <v>-14213.43</v>
+      </c>
+      <c r="AL72" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM72" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN72" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -25458,7 +26165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN19"/>
+  <dimension ref="A1:AN20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -28270,6 +28977,158 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G20" s="16" t="inlineStr">
+        <is>
+          <t>Price↑(58131.45&gt;58045.9) &amp; EMA9↑(57775.18&gt;57179.74)</t>
+        </is>
+      </c>
+      <c r="H20" s="16" t="n">
+        <v>57775.18</v>
+      </c>
+      <c r="I20" s="16" t="n">
+        <v>57179.74</v>
+      </c>
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K20" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L20" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="M20" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N20" s="16" t="inlineStr">
+        <is>
+          <t>13:39 IST</t>
+        </is>
+      </c>
+      <c r="O20" s="16" t="n">
+        <v>58131.45</v>
+      </c>
+      <c r="P20" s="16" t="n">
+        <v>58045.9</v>
+      </c>
+      <c r="Q20" s="16" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="R20" s="16" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="S20" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="T20" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U20" s="16" t="n">
+        <v>510</v>
+      </c>
+      <c r="V20" s="16" t="n">
+        <v>93.56999999999999</v>
+      </c>
+      <c r="W20" s="16" t="n">
+        <v>89</v>
+      </c>
+      <c r="X20" s="16" t="n">
+        <v>47720.7</v>
+      </c>
+      <c r="Y20" s="16" t="n">
+        <v>47775.41</v>
+      </c>
+      <c r="Z20" s="16" t="n">
+        <v>54279.3</v>
+      </c>
+      <c r="AA20" s="16" t="n">
+        <v>14316.21</v>
+      </c>
+      <c r="AB20" s="16" t="n">
+        <v>14316.21</v>
+      </c>
+      <c r="AC20" s="16" t="n">
+        <v>-2330.7</v>
+      </c>
+      <c r="AD20" s="16" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="AE20" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF20" s="16" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="AG20" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH20" s="16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI20" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ20" s="16" t="n">
+        <v>54.71</v>
+      </c>
+      <c r="AK20" s="16" t="n">
+        <v>-2385.41</v>
+      </c>
+      <c r="AL20" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM20" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN20" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -29377,7 +30236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA36"/>
+  <dimension ref="A1:AA37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -32914,6 +33773,105 @@
         <v>1000</v>
       </c>
       <c r="AA36" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D37" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F37" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="inlineStr">
+        <is>
+          <t>11:40 ET</t>
+        </is>
+      </c>
+      <c r="H37" s="17" t="n">
+        <v>29671.75</v>
+      </c>
+      <c r="I37" s="17" t="n">
+        <v>29650</v>
+      </c>
+      <c r="J37" s="17" t="n">
+        <v>29675</v>
+      </c>
+      <c r="K37" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="L37" s="17" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="M37" s="17" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="N37" s="17" t="n">
+        <v>991.8</v>
+      </c>
+      <c r="O37" s="17" t="n">
+        <v>2106.6</v>
+      </c>
+      <c r="P37" s="17" t="n">
+        <v>268.02</v>
+      </c>
+      <c r="Q37" s="17" t="n">
+        <v>268.02</v>
+      </c>
+      <c r="R37" s="17" t="n">
+        <v>268.2</v>
+      </c>
+      <c r="S37" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T37" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="U37" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="V37" s="17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W37" s="17" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="X37" s="17" t="n">
+        <v>169.8</v>
+      </c>
+      <c r="Y37" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z37" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA37" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -33033,7 +33991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -35478,6 +36436,76 @@
       <c r="I70" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — STOP LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B71" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C71" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D71" s="19" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="E71" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="F71" s="19" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G71" s="19" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="H71" s="19" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="I71" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B72" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C72" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="D72" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="E72" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F72" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G72" s="19" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="H72" s="19" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="I72" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — PROFIT</t>
         </is>
       </c>
     </row>
@@ -35944,7 +36972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN36"/>
+  <dimension ref="A1:AN37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -41320,6 +42348,158 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D37" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E37" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24211.0&gt;24206.9) &amp; EMA9↑(24129.89&gt;23962.6)</t>
+        </is>
+      </c>
+      <c r="H37" s="17" t="n">
+        <v>24129.89</v>
+      </c>
+      <c r="I37" s="17" t="n">
+        <v>23962.6</v>
+      </c>
+      <c r="J37" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K37" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L37" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M37" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N37" s="17" t="inlineStr">
+        <is>
+          <t>11:37 IST</t>
+        </is>
+      </c>
+      <c r="O37" s="17" t="n">
+        <v>24211</v>
+      </c>
+      <c r="P37" s="17" t="n">
+        <v>24206.9</v>
+      </c>
+      <c r="Q37" s="17" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="R37" s="17" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="S37" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U37" s="17" t="n">
+        <v>1625</v>
+      </c>
+      <c r="V37" s="17" t="n">
+        <v>29.24</v>
+      </c>
+      <c r="W37" s="17" t="n">
+        <v>38.01</v>
+      </c>
+      <c r="X37" s="17" t="n">
+        <v>47515</v>
+      </c>
+      <c r="Y37" s="17" t="n">
+        <v>47569.68</v>
+      </c>
+      <c r="Z37" s="17" t="n">
+        <v>114985</v>
+      </c>
+      <c r="AA37" s="17" t="n">
+        <v>14254.5</v>
+      </c>
+      <c r="AB37" s="17" t="n">
+        <v>14254.5</v>
+      </c>
+      <c r="AC37" s="17" t="n">
+        <v>14251.25</v>
+      </c>
+      <c r="AD37" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE37" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF37" s="17" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AG37" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH37" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI37" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ37" s="17" t="n">
+        <v>54.68</v>
+      </c>
+      <c r="AK37" s="17" t="n">
+        <v>14196.57</v>
+      </c>
+      <c r="AL37" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM37" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN37" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -41334,7 +42514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN36"/>
+  <dimension ref="A1:AN37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -46710,6 +47890,158 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G37" s="16" t="inlineStr">
+        <is>
+          <t>Price↑(24211.0&gt;24206.9) &amp; EMA9↑(24129.89&gt;23962.6)</t>
+        </is>
+      </c>
+      <c r="H37" s="16" t="n">
+        <v>24129.89</v>
+      </c>
+      <c r="I37" s="16" t="n">
+        <v>23962.6</v>
+      </c>
+      <c r="J37" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K37" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L37" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M37" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N37" s="16" t="inlineStr">
+        <is>
+          <t>14:44 IST</t>
+        </is>
+      </c>
+      <c r="O37" s="16" t="n">
+        <v>24211</v>
+      </c>
+      <c r="P37" s="16" t="n">
+        <v>24206.9</v>
+      </c>
+      <c r="Q37" s="16" t="inlineStr">
+        <is>
+          <t>24300 PE</t>
+        </is>
+      </c>
+      <c r="R37" s="16" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="S37" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="T37" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U37" s="16" t="n">
+        <v>1690</v>
+      </c>
+      <c r="V37" s="16" t="n">
+        <v>28.01</v>
+      </c>
+      <c r="W37" s="16" t="n">
+        <v>27.36</v>
+      </c>
+      <c r="X37" s="16" t="n">
+        <v>47336.9</v>
+      </c>
+      <c r="Y37" s="16" t="n">
+        <v>47391.55</v>
+      </c>
+      <c r="Z37" s="16" t="n">
+        <v>121663.1</v>
+      </c>
+      <c r="AA37" s="16" t="n">
+        <v>14201.07</v>
+      </c>
+      <c r="AB37" s="16" t="n">
+        <v>14201.07</v>
+      </c>
+      <c r="AC37" s="16" t="n">
+        <v>-1098.5</v>
+      </c>
+      <c r="AD37" s="16" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="AE37" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF37" s="16" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="AG37" s="16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH37" s="16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI37" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ37" s="16" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="AK37" s="16" t="n">
+        <v>-1153.15</v>
+      </c>
+      <c r="AL37" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM37" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN37" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -46724,7 +48056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN70"/>
+  <dimension ref="A1:AN72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -57228,6 +58560,310 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B71" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C71" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D71" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E71" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F71" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G71" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24211.0&gt;24206.9) &amp; EMA9↑(24129.89&gt;23962.6)</t>
+        </is>
+      </c>
+      <c r="H71" s="17" t="n">
+        <v>24129.89</v>
+      </c>
+      <c r="I71" s="17" t="n">
+        <v>23962.6</v>
+      </c>
+      <c r="J71" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K71" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L71" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M71" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N71" s="17" t="inlineStr">
+        <is>
+          <t>09:49 IST</t>
+        </is>
+      </c>
+      <c r="O71" s="17" t="n">
+        <v>24211</v>
+      </c>
+      <c r="P71" s="17" t="n">
+        <v>24206.9</v>
+      </c>
+      <c r="Q71" s="17" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="R71" s="17" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="S71" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="T71" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U71" s="17" t="n">
+        <v>1365</v>
+      </c>
+      <c r="V71" s="17" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="W71" s="17" t="n">
+        <v>45.47</v>
+      </c>
+      <c r="X71" s="17" t="n">
+        <v>47747.7</v>
+      </c>
+      <c r="Y71" s="17" t="n">
+        <v>47802.41</v>
+      </c>
+      <c r="Z71" s="17" t="n">
+        <v>88752.3</v>
+      </c>
+      <c r="AA71" s="17" t="n">
+        <v>14324.31</v>
+      </c>
+      <c r="AB71" s="17" t="n">
+        <v>14324.31</v>
+      </c>
+      <c r="AC71" s="17" t="n">
+        <v>14318.85</v>
+      </c>
+      <c r="AD71" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE71" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF71" s="17" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="AG71" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH71" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI71" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ71" s="17" t="n">
+        <v>54.71</v>
+      </c>
+      <c r="AK71" s="17" t="n">
+        <v>14264.14</v>
+      </c>
+      <c r="AL71" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM71" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN71" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B72" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C72" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D72" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E72" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F72" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G72" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24211.0&gt;24206.9) &amp; EMA9↑(24129.89&gt;23962.6)</t>
+        </is>
+      </c>
+      <c r="H72" s="17" t="n">
+        <v>24129.89</v>
+      </c>
+      <c r="I72" s="17" t="n">
+        <v>23962.6</v>
+      </c>
+      <c r="J72" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K72" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L72" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M72" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N72" s="17" t="inlineStr">
+        <is>
+          <t>11:54 IST</t>
+        </is>
+      </c>
+      <c r="O72" s="17" t="n">
+        <v>24211</v>
+      </c>
+      <c r="P72" s="17" t="n">
+        <v>24206.9</v>
+      </c>
+      <c r="Q72" s="17" t="inlineStr">
+        <is>
+          <t>24300 PE</t>
+        </is>
+      </c>
+      <c r="R72" s="17" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="S72" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="T72" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U72" s="17" t="n">
+        <v>1755</v>
+      </c>
+      <c r="V72" s="17" t="n">
+        <v>27.36</v>
+      </c>
+      <c r="W72" s="17" t="n">
+        <v>35.57</v>
+      </c>
+      <c r="X72" s="17" t="n">
+        <v>48016.8</v>
+      </c>
+      <c r="Y72" s="17" t="n">
+        <v>48071.56</v>
+      </c>
+      <c r="Z72" s="17" t="n">
+        <v>127483.2</v>
+      </c>
+      <c r="AA72" s="17" t="n">
+        <v>14405.04</v>
+      </c>
+      <c r="AB72" s="17" t="n">
+        <v>14405.04</v>
+      </c>
+      <c r="AC72" s="17" t="n">
+        <v>14408.55</v>
+      </c>
+      <c r="AD72" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE72" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF72" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG72" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH72" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI72" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ72" s="17" t="n">
+        <v>54.76</v>
+      </c>
+      <c r="AK72" s="17" t="n">
+        <v>14353.79</v>
+      </c>
+      <c r="AL72" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM72" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN72" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -57242,7 +58878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN22"/>
+  <dimension ref="A1:AN23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -60515,6 +62151,158 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(24211.0&gt;24206.9) &amp; EMA9↑(24129.89&gt;23962.6)</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>24129.89</v>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v>23962.6</v>
+      </c>
+      <c r="J23" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K23" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L23" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M23" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N23" s="15" t="inlineStr">
+        <is>
+          <t>11:01 IST</t>
+        </is>
+      </c>
+      <c r="O23" s="15" t="n">
+        <v>24211</v>
+      </c>
+      <c r="P23" s="15" t="n">
+        <v>24206.9</v>
+      </c>
+      <c r="Q23" s="15" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="R23" s="15" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="S23" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U23" s="15" t="n">
+        <v>1625</v>
+      </c>
+      <c r="V23" s="15" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="W23" s="15" t="n">
+        <v>20.97</v>
+      </c>
+      <c r="X23" s="15" t="n">
+        <v>48685</v>
+      </c>
+      <c r="Y23" s="15" t="n">
+        <v>48739.86</v>
+      </c>
+      <c r="Z23" s="15" t="n">
+        <v>113815</v>
+      </c>
+      <c r="AA23" s="15" t="n">
+        <v>14605.5</v>
+      </c>
+      <c r="AB23" s="15" t="n">
+        <v>14605.5</v>
+      </c>
+      <c r="AC23" s="15" t="n">
+        <v>-14608.75</v>
+      </c>
+      <c r="AD23" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE23" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF23" s="15" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="AG23" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH23" s="15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI23" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ23" s="15" t="n">
+        <v>54.86</v>
+      </c>
+      <c r="AK23" s="15" t="n">
+        <v>-14663.61</v>
+      </c>
+      <c r="AL23" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM23" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN23" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA37"/>
+  <dimension ref="A1:AA38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4245,6 +4245,105 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G38" s="17" t="inlineStr">
+        <is>
+          <t>13:27 ET</t>
+        </is>
+      </c>
+      <c r="H38" s="17" t="n">
+        <v>29515</v>
+      </c>
+      <c r="I38" s="17" t="n">
+        <v>29500</v>
+      </c>
+      <c r="J38" s="17" t="n">
+        <v>29525</v>
+      </c>
+      <c r="K38" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L38" s="17" t="n">
+        <v>106.01</v>
+      </c>
+      <c r="M38" s="17" t="n">
+        <v>137.81</v>
+      </c>
+      <c r="N38" s="17" t="n">
+        <v>907.28</v>
+      </c>
+      <c r="O38" s="17" t="n">
+        <v>3151.92</v>
+      </c>
+      <c r="P38" s="17" t="n">
+        <v>254.42</v>
+      </c>
+      <c r="Q38" s="17" t="n">
+        <v>254.42</v>
+      </c>
+      <c r="R38" s="17" t="n">
+        <v>254.4</v>
+      </c>
+      <c r="S38" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T38" s="17" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="U38" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="V38" s="17" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="W38" s="17" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="X38" s="17" t="n">
+        <v>195.2</v>
+      </c>
+      <c r="Y38" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z38" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA38" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -4259,7 +4358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN37"/>
+  <dimension ref="A1:AN38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9787,6 +9886,158 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G38" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(58045.9&gt;57252.45) &amp; EMA9↑(57686.12&gt;57084.57)</t>
+        </is>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>57686.12</v>
+      </c>
+      <c r="I38" s="15" t="n">
+        <v>57084.57</v>
+      </c>
+      <c r="J38" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K38" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L38" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="M38" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N38" s="15" t="inlineStr">
+        <is>
+          <t>09:53 IST</t>
+        </is>
+      </c>
+      <c r="O38" s="15" t="n">
+        <v>58045.9</v>
+      </c>
+      <c r="P38" s="15" t="n">
+        <v>57252.45</v>
+      </c>
+      <c r="Q38" s="15" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="R38" s="15" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="S38" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U38" s="15" t="n">
+        <v>450</v>
+      </c>
+      <c r="V38" s="15" t="n">
+        <v>103.03</v>
+      </c>
+      <c r="W38" s="15" t="n">
+        <v>72.12</v>
+      </c>
+      <c r="X38" s="15" t="n">
+        <v>46363.5</v>
+      </c>
+      <c r="Y38" s="15" t="n">
+        <v>46418</v>
+      </c>
+      <c r="Z38" s="15" t="n">
+        <v>43636.5</v>
+      </c>
+      <c r="AA38" s="15" t="n">
+        <v>13909.05</v>
+      </c>
+      <c r="AB38" s="15" t="n">
+        <v>13909.05</v>
+      </c>
+      <c r="AC38" s="15" t="n">
+        <v>-13909.5</v>
+      </c>
+      <c r="AD38" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE38" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF38" s="15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AG38" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH38" s="15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI38" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ38" s="15" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="AK38" s="15" t="n">
+        <v>-13964</v>
+      </c>
+      <c r="AL38" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM38" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN38" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -9801,7 +10052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN37"/>
+  <dimension ref="A1:AN38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15329,6 +15580,158 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G38" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(58045.9&gt;57252.45) &amp; EMA9↑(57686.12&gt;57084.57)</t>
+        </is>
+      </c>
+      <c r="H38" s="17" t="n">
+        <v>57686.12</v>
+      </c>
+      <c r="I38" s="17" t="n">
+        <v>57084.57</v>
+      </c>
+      <c r="J38" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K38" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L38" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="M38" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N38" s="17" t="inlineStr">
+        <is>
+          <t>09:49 IST</t>
+        </is>
+      </c>
+      <c r="O38" s="17" t="n">
+        <v>58045.9</v>
+      </c>
+      <c r="P38" s="17" t="n">
+        <v>57252.45</v>
+      </c>
+      <c r="Q38" s="17" t="inlineStr">
+        <is>
+          <t>58200 PE</t>
+        </is>
+      </c>
+      <c r="R38" s="17" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="S38" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="T38" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U38" s="17" t="n">
+        <v>510</v>
+      </c>
+      <c r="V38" s="17" t="n">
+        <v>95.52</v>
+      </c>
+      <c r="W38" s="17" t="n">
+        <v>124.18</v>
+      </c>
+      <c r="X38" s="17" t="n">
+        <v>48715.2</v>
+      </c>
+      <c r="Y38" s="17" t="n">
+        <v>48770.07</v>
+      </c>
+      <c r="Z38" s="17" t="n">
+        <v>53284.8</v>
+      </c>
+      <c r="AA38" s="17" t="n">
+        <v>14614.56</v>
+      </c>
+      <c r="AB38" s="17" t="n">
+        <v>14614.56</v>
+      </c>
+      <c r="AC38" s="17" t="n">
+        <v>14616.6</v>
+      </c>
+      <c r="AD38" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE38" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF38" s="17" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="AG38" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH38" s="17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI38" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ38" s="17" t="n">
+        <v>54.87</v>
+      </c>
+      <c r="AK38" s="17" t="n">
+        <v>14561.73</v>
+      </c>
+      <c r="AL38" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM38" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN38" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -15343,7 +15746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN72"/>
+  <dimension ref="A1:AN74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -26151,6 +26554,310 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B73" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C73" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D73" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E73" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F73" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G73" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(58045.9&gt;57252.45) &amp; EMA9↑(57686.12&gt;57084.57)</t>
+        </is>
+      </c>
+      <c r="H73" s="15" t="n">
+        <v>57686.12</v>
+      </c>
+      <c r="I73" s="15" t="n">
+        <v>57084.57</v>
+      </c>
+      <c r="J73" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K73" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L73" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="M73" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N73" s="15" t="inlineStr">
+        <is>
+          <t>10:36 IST</t>
+        </is>
+      </c>
+      <c r="O73" s="15" t="n">
+        <v>58045.9</v>
+      </c>
+      <c r="P73" s="15" t="n">
+        <v>57252.45</v>
+      </c>
+      <c r="Q73" s="15" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="R73" s="15" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="S73" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T73" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U73" s="15" t="n">
+        <v>600</v>
+      </c>
+      <c r="V73" s="15" t="n">
+        <v>81.53</v>
+      </c>
+      <c r="W73" s="15" t="n">
+        <v>57.07</v>
+      </c>
+      <c r="X73" s="15" t="n">
+        <v>48918</v>
+      </c>
+      <c r="Y73" s="15" t="n">
+        <v>48972.9</v>
+      </c>
+      <c r="Z73" s="15" t="n">
+        <v>71082</v>
+      </c>
+      <c r="AA73" s="15" t="n">
+        <v>14675.4</v>
+      </c>
+      <c r="AB73" s="15" t="n">
+        <v>14675.4</v>
+      </c>
+      <c r="AC73" s="15" t="n">
+        <v>-14676</v>
+      </c>
+      <c r="AD73" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE73" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF73" s="15" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="AG73" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH73" s="15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI73" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ73" s="15" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="AK73" s="15" t="n">
+        <v>-14730.9</v>
+      </c>
+      <c r="AL73" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM73" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN73" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B74" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C74" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E74" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F74" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G74" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(58045.9&gt;57252.45) &amp; EMA9↑(57686.12&gt;57084.57)</t>
+        </is>
+      </c>
+      <c r="H74" s="15" t="n">
+        <v>57686.12</v>
+      </c>
+      <c r="I74" s="15" t="n">
+        <v>57084.57</v>
+      </c>
+      <c r="J74" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K74" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L74" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="M74" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N74" s="15" t="inlineStr">
+        <is>
+          <t>10:29 IST</t>
+        </is>
+      </c>
+      <c r="O74" s="15" t="n">
+        <v>58045.9</v>
+      </c>
+      <c r="P74" s="15" t="n">
+        <v>57252.45</v>
+      </c>
+      <c r="Q74" s="15" t="inlineStr">
+        <is>
+          <t>58200 PE</t>
+        </is>
+      </c>
+      <c r="R74" s="15" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="S74" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="T74" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U74" s="15" t="n">
+        <v>540</v>
+      </c>
+      <c r="V74" s="15" t="n">
+        <v>86.81</v>
+      </c>
+      <c r="W74" s="15" t="n">
+        <v>60.77</v>
+      </c>
+      <c r="X74" s="15" t="n">
+        <v>46877.4</v>
+      </c>
+      <c r="Y74" s="15" t="n">
+        <v>46931.98</v>
+      </c>
+      <c r="Z74" s="15" t="n">
+        <v>61122.6</v>
+      </c>
+      <c r="AA74" s="15" t="n">
+        <v>14063.22</v>
+      </c>
+      <c r="AB74" s="15" t="n">
+        <v>14063.22</v>
+      </c>
+      <c r="AC74" s="15" t="n">
+        <v>-14061.6</v>
+      </c>
+      <c r="AD74" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE74" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF74" s="15" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="AG74" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH74" s="15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI74" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ74" s="15" t="n">
+        <v>54.58</v>
+      </c>
+      <c r="AK74" s="15" t="n">
+        <v>-14116.18</v>
+      </c>
+      <c r="AL74" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM74" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN74" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -26165,7 +26872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN20"/>
+  <dimension ref="A1:AN21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -29129,6 +29836,158 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(58045.9&gt;57252.45) &amp; EMA9↑(57686.12&gt;57084.57)</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>57686.12</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>57084.57</v>
+      </c>
+      <c r="J21" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K21" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L21" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="M21" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N21" s="15" t="inlineStr">
+        <is>
+          <t>10:08 IST</t>
+        </is>
+      </c>
+      <c r="O21" s="15" t="n">
+        <v>58045.9</v>
+      </c>
+      <c r="P21" s="15" t="n">
+        <v>57252.45</v>
+      </c>
+      <c r="Q21" s="15" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="R21" s="15" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="S21" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="T21" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U21" s="15" t="n">
+        <v>510</v>
+      </c>
+      <c r="V21" s="15" t="n">
+        <v>95.81999999999999</v>
+      </c>
+      <c r="W21" s="15" t="n">
+        <v>67.06999999999999</v>
+      </c>
+      <c r="X21" s="15" t="n">
+        <v>48868.2</v>
+      </c>
+      <c r="Y21" s="15" t="n">
+        <v>48923.09</v>
+      </c>
+      <c r="Z21" s="15" t="n">
+        <v>53131.8</v>
+      </c>
+      <c r="AA21" s="15" t="n">
+        <v>14660.46</v>
+      </c>
+      <c r="AB21" s="15" t="n">
+        <v>14660.46</v>
+      </c>
+      <c r="AC21" s="15" t="n">
+        <v>-14662.5</v>
+      </c>
+      <c r="AD21" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE21" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF21" s="15" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="AG21" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH21" s="15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI21" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ21" s="15" t="n">
+        <v>54.89</v>
+      </c>
+      <c r="AK21" s="15" t="n">
+        <v>-14717.39</v>
+      </c>
+      <c r="AL21" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM21" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN21" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -30236,7 +31095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA37"/>
+  <dimension ref="A1:AA38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -33872,6 +34731,105 @@
         <v>1000</v>
       </c>
       <c r="AA37" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G38" s="16" t="inlineStr">
+        <is>
+          <t>15:40 ET</t>
+        </is>
+      </c>
+      <c r="H38" s="16" t="n">
+        <v>29509.25</v>
+      </c>
+      <c r="I38" s="16" t="n">
+        <v>29500</v>
+      </c>
+      <c r="J38" s="16" t="n">
+        <v>29525</v>
+      </c>
+      <c r="K38" s="16" t="n">
+        <v>75</v>
+      </c>
+      <c r="L38" s="16" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="M38" s="16" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="N38" s="16" t="n">
+        <v>999</v>
+      </c>
+      <c r="O38" s="16" t="n">
+        <v>2874</v>
+      </c>
+      <c r="P38" s="16" t="n">
+        <v>262.8</v>
+      </c>
+      <c r="Q38" s="16" t="n">
+        <v>262.8</v>
+      </c>
+      <c r="R38" s="16" t="n">
+        <v>-32.25</v>
+      </c>
+      <c r="S38" s="16" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="T38" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="U38" s="16" t="n">
+        <v>75</v>
+      </c>
+      <c r="V38" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="W38" s="16" t="n">
+        <v>123</v>
+      </c>
+      <c r="X38" s="16" t="n">
+        <v>-155.25</v>
+      </c>
+      <c r="Y38" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="Z38" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA38" s="16" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -33991,7 +34949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -36506,6 +37464,76 @@
       <c r="I72" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B73" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C73" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="D73" s="19" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="E73" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="F73" s="19" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G73" s="19" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="H73" s="19" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="I73" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B74" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C74" s="19" t="n">
+        <v>75</v>
+      </c>
+      <c r="D74" s="19" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E74" s="19" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="F74" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G74" s="19" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="H74" s="19" t="n">
+        <v>123</v>
+      </c>
+      <c r="I74" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — FLAT</t>
         </is>
       </c>
     </row>
@@ -36972,7 +38000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN37"/>
+  <dimension ref="A1:AN38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -42500,6 +43528,158 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G38" s="16" t="inlineStr">
+        <is>
+          <t>Price↑(24206.9&gt;23962.8) &amp; EMA9↑(24109.62&gt;23937.76)</t>
+        </is>
+      </c>
+      <c r="H38" s="16" t="n">
+        <v>24109.62</v>
+      </c>
+      <c r="I38" s="16" t="n">
+        <v>23937.76</v>
+      </c>
+      <c r="J38" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K38" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L38" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M38" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N38" s="16" t="inlineStr">
+        <is>
+          <t>15:03 IST</t>
+        </is>
+      </c>
+      <c r="O38" s="16" t="n">
+        <v>24206.9</v>
+      </c>
+      <c r="P38" s="16" t="n">
+        <v>23962.8</v>
+      </c>
+      <c r="Q38" s="16" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="R38" s="16" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="S38" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="T38" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U38" s="16" t="n">
+        <v>1430</v>
+      </c>
+      <c r="V38" s="16" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="W38" s="16" t="n">
+        <v>33.87</v>
+      </c>
+      <c r="X38" s="16" t="n">
+        <v>48691.5</v>
+      </c>
+      <c r="Y38" s="16" t="n">
+        <v>48746.36</v>
+      </c>
+      <c r="Z38" s="16" t="n">
+        <v>94308.5</v>
+      </c>
+      <c r="AA38" s="16" t="n">
+        <v>14607.45</v>
+      </c>
+      <c r="AB38" s="16" t="n">
+        <v>14607.45</v>
+      </c>
+      <c r="AC38" s="16" t="n">
+        <v>-257.4</v>
+      </c>
+      <c r="AD38" s="16" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AE38" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF38" s="16" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="AG38" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH38" s="16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI38" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ38" s="16" t="n">
+        <v>54.86</v>
+      </c>
+      <c r="AK38" s="16" t="n">
+        <v>-312.26</v>
+      </c>
+      <c r="AL38" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM38" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN38" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -42514,7 +43694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN37"/>
+  <dimension ref="A1:AN38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -48042,6 +49222,158 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G38" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24206.9&gt;23962.8) &amp; EMA9↑(24109.62&gt;23937.76)</t>
+        </is>
+      </c>
+      <c r="H38" s="17" t="n">
+        <v>24109.62</v>
+      </c>
+      <c r="I38" s="17" t="n">
+        <v>23937.76</v>
+      </c>
+      <c r="J38" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K38" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L38" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M38" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N38" s="17" t="inlineStr">
+        <is>
+          <t>11:50 IST</t>
+        </is>
+      </c>
+      <c r="O38" s="17" t="n">
+        <v>24206.9</v>
+      </c>
+      <c r="P38" s="17" t="n">
+        <v>23962.8</v>
+      </c>
+      <c r="Q38" s="17" t="inlineStr">
+        <is>
+          <t>24300 PE</t>
+        </is>
+      </c>
+      <c r="R38" s="17" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="S38" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="T38" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U38" s="17" t="n">
+        <v>1365</v>
+      </c>
+      <c r="V38" s="17" t="n">
+        <v>35.58</v>
+      </c>
+      <c r="W38" s="17" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="X38" s="17" t="n">
+        <v>48566.7</v>
+      </c>
+      <c r="Y38" s="17" t="n">
+        <v>48621.54</v>
+      </c>
+      <c r="Z38" s="17" t="n">
+        <v>87933.3</v>
+      </c>
+      <c r="AA38" s="17" t="n">
+        <v>14570.01</v>
+      </c>
+      <c r="AB38" s="17" t="n">
+        <v>14570.01</v>
+      </c>
+      <c r="AC38" s="17" t="n">
+        <v>14564.55</v>
+      </c>
+      <c r="AD38" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE38" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF38" s="17" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="AG38" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH38" s="17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI38" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ38" s="17" t="n">
+        <v>54.84</v>
+      </c>
+      <c r="AK38" s="17" t="n">
+        <v>14509.71</v>
+      </c>
+      <c r="AL38" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM38" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN38" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -48056,7 +49388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN72"/>
+  <dimension ref="A1:AN74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -58864,6 +60196,310 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B73" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C73" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D73" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E73" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F73" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G73" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(24206.9&gt;23962.8) &amp; EMA9↑(24109.62&gt;23937.76)</t>
+        </is>
+      </c>
+      <c r="H73" s="15" t="n">
+        <v>24109.62</v>
+      </c>
+      <c r="I73" s="15" t="n">
+        <v>23937.76</v>
+      </c>
+      <c r="J73" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K73" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L73" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M73" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N73" s="15" t="inlineStr">
+        <is>
+          <t>09:34 IST</t>
+        </is>
+      </c>
+      <c r="O73" s="15" t="n">
+        <v>24206.9</v>
+      </c>
+      <c r="P73" s="15" t="n">
+        <v>23962.8</v>
+      </c>
+      <c r="Q73" s="15" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="R73" s="15" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="S73" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="T73" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U73" s="15" t="n">
+        <v>1495</v>
+      </c>
+      <c r="V73" s="15" t="n">
+        <v>32.78</v>
+      </c>
+      <c r="W73" s="15" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="X73" s="15" t="n">
+        <v>49006.1</v>
+      </c>
+      <c r="Y73" s="15" t="n">
+        <v>49061.01</v>
+      </c>
+      <c r="Z73" s="15" t="n">
+        <v>100493.9</v>
+      </c>
+      <c r="AA73" s="15" t="n">
+        <v>14701.83</v>
+      </c>
+      <c r="AB73" s="15" t="n">
+        <v>14701.83</v>
+      </c>
+      <c r="AC73" s="15" t="n">
+        <v>-14695.85</v>
+      </c>
+      <c r="AD73" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE73" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF73" s="15" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="AG73" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH73" s="15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI73" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ73" s="15" t="n">
+        <v>54.91</v>
+      </c>
+      <c r="AK73" s="15" t="n">
+        <v>-14750.76</v>
+      </c>
+      <c r="AL73" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM73" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN73" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B74" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C74" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D74" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E74" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F74" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G74" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24206.9&gt;23962.8) &amp; EMA9↑(24109.62&gt;23937.76)</t>
+        </is>
+      </c>
+      <c r="H74" s="17" t="n">
+        <v>24109.62</v>
+      </c>
+      <c r="I74" s="17" t="n">
+        <v>23937.76</v>
+      </c>
+      <c r="J74" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K74" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L74" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M74" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N74" s="17" t="inlineStr">
+        <is>
+          <t>10:22 IST</t>
+        </is>
+      </c>
+      <c r="O74" s="17" t="n">
+        <v>24206.9</v>
+      </c>
+      <c r="P74" s="17" t="n">
+        <v>23962.8</v>
+      </c>
+      <c r="Q74" s="17" t="inlineStr">
+        <is>
+          <t>24300 PE</t>
+        </is>
+      </c>
+      <c r="R74" s="17" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="S74" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="T74" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U74" s="17" t="n">
+        <v>1235</v>
+      </c>
+      <c r="V74" s="17" t="n">
+        <v>38.15</v>
+      </c>
+      <c r="W74" s="17" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="X74" s="17" t="n">
+        <v>47115.25</v>
+      </c>
+      <c r="Y74" s="17" t="n">
+        <v>47169.86</v>
+      </c>
+      <c r="Z74" s="17" t="n">
+        <v>76384.75</v>
+      </c>
+      <c r="AA74" s="17" t="n">
+        <v>14134.57</v>
+      </c>
+      <c r="AB74" s="17" t="n">
+        <v>14134.57</v>
+      </c>
+      <c r="AC74" s="17" t="n">
+        <v>14128.4</v>
+      </c>
+      <c r="AD74" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE74" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF74" s="17" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AG74" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH74" s="17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI74" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ74" s="17" t="n">
+        <v>54.61</v>
+      </c>
+      <c r="AK74" s="17" t="n">
+        <v>14073.79</v>
+      </c>
+      <c r="AL74" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM74" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN74" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -58878,7 +60514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN23"/>
+  <dimension ref="A1:AN24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -62303,6 +63939,158 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24206.9&gt;23962.8) &amp; EMA9↑(24109.62&gt;23937.76)</t>
+        </is>
+      </c>
+      <c r="H24" s="17" t="n">
+        <v>24109.62</v>
+      </c>
+      <c r="I24" s="17" t="n">
+        <v>23937.76</v>
+      </c>
+      <c r="J24" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K24" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L24" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M24" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N24" s="17" t="inlineStr">
+        <is>
+          <t>10:57 IST</t>
+        </is>
+      </c>
+      <c r="O24" s="17" t="n">
+        <v>24206.9</v>
+      </c>
+      <c r="P24" s="17" t="n">
+        <v>23962.8</v>
+      </c>
+      <c r="Q24" s="17" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="R24" s="17" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="S24" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U24" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="V24" s="17" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="W24" s="17" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="X24" s="17" t="n">
+        <v>48022</v>
+      </c>
+      <c r="Y24" s="17" t="n">
+        <v>48076.76</v>
+      </c>
+      <c r="Z24" s="17" t="n">
+        <v>81978</v>
+      </c>
+      <c r="AA24" s="17" t="n">
+        <v>14406.6</v>
+      </c>
+      <c r="AB24" s="17" t="n">
+        <v>14406.6</v>
+      </c>
+      <c r="AC24" s="17" t="n">
+        <v>14404</v>
+      </c>
+      <c r="AD24" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE24" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF24" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG24" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH24" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI24" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ24" s="17" t="n">
+        <v>54.76</v>
+      </c>
+      <c r="AK24" s="17" t="n">
+        <v>14349.24</v>
+      </c>
+      <c r="AL24" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM24" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN24" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA38"/>
+  <dimension ref="A1:AA39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4344,6 +4344,105 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" s="15" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G39" s="15" t="inlineStr">
+        <is>
+          <t>10:29 ET</t>
+        </is>
+      </c>
+      <c r="H39" s="15" t="n">
+        <v>29594.75</v>
+      </c>
+      <c r="I39" s="15" t="n">
+        <v>29575</v>
+      </c>
+      <c r="J39" s="15" t="n">
+        <v>29600</v>
+      </c>
+      <c r="K39" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L39" s="15" t="n">
+        <v>116.32</v>
+      </c>
+      <c r="M39" s="15" t="n">
+        <v>81.42</v>
+      </c>
+      <c r="N39" s="15" t="n">
+        <v>989.76</v>
+      </c>
+      <c r="O39" s="15" t="n">
+        <v>3069.44</v>
+      </c>
+      <c r="P39" s="15" t="n">
+        <v>279.17</v>
+      </c>
+      <c r="Q39" s="15" t="n">
+        <v>279.17</v>
+      </c>
+      <c r="R39" s="15" t="n">
+        <v>-279.2</v>
+      </c>
+      <c r="S39" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="T39" s="15" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="U39" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="V39" s="15" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="W39" s="15" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="X39" s="15" t="n">
+        <v>-338.4</v>
+      </c>
+      <c r="Y39" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="Z39" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA39" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -4358,7 +4457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN38"/>
+  <dimension ref="A1:AN39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10038,6 +10137,158 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G39" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H39" s="16" t="n">
+        <v>57746.15</v>
+      </c>
+      <c r="I39" s="16" t="n">
+        <v>57250.18</v>
+      </c>
+      <c r="J39" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K39" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L39" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="M39" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N39" s="16" t="inlineStr">
+        <is>
+          <t>14:53 IST</t>
+        </is>
+      </c>
+      <c r="O39" s="16" t="n">
+        <v>57635.55</v>
+      </c>
+      <c r="P39" s="16" t="n">
+        <v>58131.45</v>
+      </c>
+      <c r="Q39" s="16" t="inlineStr">
+        <is>
+          <t>57600 CE</t>
+        </is>
+      </c>
+      <c r="R39" s="16" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="S39" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="T39" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U39" s="16" t="n">
+        <v>540</v>
+      </c>
+      <c r="V39" s="16" t="n">
+        <v>91.08</v>
+      </c>
+      <c r="W39" s="16" t="n">
+        <v>88.29000000000001</v>
+      </c>
+      <c r="X39" s="16" t="n">
+        <v>49183.2</v>
+      </c>
+      <c r="Y39" s="16" t="n">
+        <v>49238.14</v>
+      </c>
+      <c r="Z39" s="16" t="n">
+        <v>58816.8</v>
+      </c>
+      <c r="AA39" s="16" t="n">
+        <v>14754.96</v>
+      </c>
+      <c r="AB39" s="16" t="n">
+        <v>14754.96</v>
+      </c>
+      <c r="AC39" s="16" t="n">
+        <v>-1506.6</v>
+      </c>
+      <c r="AD39" s="16" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="AE39" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF39" s="16" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AG39" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH39" s="16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI39" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ39" s="16" t="n">
+        <v>54.94</v>
+      </c>
+      <c r="AK39" s="16" t="n">
+        <v>-1561.54</v>
+      </c>
+      <c r="AL39" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM39" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN39" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -10052,7 +10303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN38"/>
+  <dimension ref="A1:AN39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15732,6 +15983,158 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D39" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E39" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F39" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G39" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H39" s="17" t="n">
+        <v>57746.15</v>
+      </c>
+      <c r="I39" s="17" t="n">
+        <v>57250.18</v>
+      </c>
+      <c r="J39" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K39" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L39" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="M39" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N39" s="17" t="inlineStr">
+        <is>
+          <t>11:25 IST</t>
+        </is>
+      </c>
+      <c r="O39" s="17" t="n">
+        <v>57635.55</v>
+      </c>
+      <c r="P39" s="17" t="n">
+        <v>58131.45</v>
+      </c>
+      <c r="Q39" s="17" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="R39" s="17" t="inlineStr">
+        <is>
+          <t>57600 PE</t>
+        </is>
+      </c>
+      <c r="S39" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="T39" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U39" s="17" t="n">
+        <v>510</v>
+      </c>
+      <c r="V39" s="17" t="n">
+        <v>92.27</v>
+      </c>
+      <c r="W39" s="17" t="n">
+        <v>119.95</v>
+      </c>
+      <c r="X39" s="17" t="n">
+        <v>47057.7</v>
+      </c>
+      <c r="Y39" s="17" t="n">
+        <v>47112.3</v>
+      </c>
+      <c r="Z39" s="17" t="n">
+        <v>54942.3</v>
+      </c>
+      <c r="AA39" s="17" t="n">
+        <v>14117.31</v>
+      </c>
+      <c r="AB39" s="17" t="n">
+        <v>14117.31</v>
+      </c>
+      <c r="AC39" s="17" t="n">
+        <v>14116.8</v>
+      </c>
+      <c r="AD39" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE39" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF39" s="17" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="AG39" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH39" s="17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI39" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ39" s="17" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="AK39" s="17" t="n">
+        <v>14062.2</v>
+      </c>
+      <c r="AL39" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM39" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN39" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -15746,7 +16149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN74"/>
+  <dimension ref="A1:AN76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -26853,6 +27256,310 @@
         <v>50000</v>
       </c>
       <c r="AN74" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B75" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C75" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D75" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E75" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F75" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G75" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H75" s="16" t="n">
+        <v>57746.15</v>
+      </c>
+      <c r="I75" s="16" t="n">
+        <v>57250.18</v>
+      </c>
+      <c r="J75" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K75" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L75" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="M75" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N75" s="16" t="inlineStr">
+        <is>
+          <t>13:59 IST</t>
+        </is>
+      </c>
+      <c r="O75" s="16" t="n">
+        <v>57635.55</v>
+      </c>
+      <c r="P75" s="16" t="n">
+        <v>58131.45</v>
+      </c>
+      <c r="Q75" s="16" t="inlineStr">
+        <is>
+          <t>57600 CE</t>
+        </is>
+      </c>
+      <c r="R75" s="16" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="S75" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="T75" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U75" s="16" t="n">
+        <v>540</v>
+      </c>
+      <c r="V75" s="16" t="n">
+        <v>86.98</v>
+      </c>
+      <c r="W75" s="16" t="n">
+        <v>84.08</v>
+      </c>
+      <c r="X75" s="16" t="n">
+        <v>46969.2</v>
+      </c>
+      <c r="Y75" s="16" t="n">
+        <v>47023.79</v>
+      </c>
+      <c r="Z75" s="16" t="n">
+        <v>61030.8</v>
+      </c>
+      <c r="AA75" s="16" t="n">
+        <v>14090.76</v>
+      </c>
+      <c r="AB75" s="16" t="n">
+        <v>14090.76</v>
+      </c>
+      <c r="AC75" s="16" t="n">
+        <v>-1566</v>
+      </c>
+      <c r="AD75" s="16" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="AE75" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF75" s="16" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="AG75" s="16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH75" s="16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI75" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ75" s="16" t="n">
+        <v>54.59</v>
+      </c>
+      <c r="AK75" s="16" t="n">
+        <v>-1620.59</v>
+      </c>
+      <c r="AL75" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM75" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN75" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B76" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C76" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D76" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E76" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F76" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G76" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H76" s="16" t="n">
+        <v>57746.15</v>
+      </c>
+      <c r="I76" s="16" t="n">
+        <v>57250.18</v>
+      </c>
+      <c r="J76" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K76" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L76" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="M76" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N76" s="16" t="inlineStr">
+        <is>
+          <t>14:56 IST</t>
+        </is>
+      </c>
+      <c r="O76" s="16" t="n">
+        <v>57635.55</v>
+      </c>
+      <c r="P76" s="16" t="n">
+        <v>58131.45</v>
+      </c>
+      <c r="Q76" s="16" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="R76" s="16" t="inlineStr">
+        <is>
+          <t>57600 PE</t>
+        </is>
+      </c>
+      <c r="S76" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="T76" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U76" s="16" t="n">
+        <v>510</v>
+      </c>
+      <c r="V76" s="16" t="n">
+        <v>95.67</v>
+      </c>
+      <c r="W76" s="16" t="n">
+        <v>91.31999999999999</v>
+      </c>
+      <c r="X76" s="16" t="n">
+        <v>48791.7</v>
+      </c>
+      <c r="Y76" s="16" t="n">
+        <v>48846.58</v>
+      </c>
+      <c r="Z76" s="16" t="n">
+        <v>53208.3</v>
+      </c>
+      <c r="AA76" s="16" t="n">
+        <v>14637.51</v>
+      </c>
+      <c r="AB76" s="16" t="n">
+        <v>14637.51</v>
+      </c>
+      <c r="AC76" s="16" t="n">
+        <v>-2218.5</v>
+      </c>
+      <c r="AD76" s="16" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AE76" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF76" s="16" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AG76" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH76" s="16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI76" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ76" s="16" t="n">
+        <v>54.88</v>
+      </c>
+      <c r="AK76" s="16" t="n">
+        <v>-2273.38</v>
+      </c>
+      <c r="AL76" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM76" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN76" s="16" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -30002,7 +30709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -31076,6 +31783,72 @@
         <v>56919.04</v>
       </c>
       <c r="G33" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E34" s="18" t="n">
+        <v>24131.43</v>
+      </c>
+      <c r="F34" s="18" t="n">
+        <v>23974.58</v>
+      </c>
+      <c r="G34" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B35" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D35" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>57746.15</v>
+      </c>
+      <c r="F35" s="18" t="n">
+        <v>57250.18</v>
+      </c>
+      <c r="G35" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -31095,7 +31868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA38"/>
+  <dimension ref="A1:AA39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -34830,6 +35603,105 @@
         <v>1000</v>
       </c>
       <c r="AA38" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" s="15" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G39" s="15" t="inlineStr">
+        <is>
+          <t>10:38 ET</t>
+        </is>
+      </c>
+      <c r="H39" s="15" t="n">
+        <v>29592.75</v>
+      </c>
+      <c r="I39" s="15" t="n">
+        <v>29575</v>
+      </c>
+      <c r="J39" s="15" t="n">
+        <v>29600</v>
+      </c>
+      <c r="K39" s="15" t="n">
+        <v>73</v>
+      </c>
+      <c r="L39" s="15" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="M39" s="15" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="N39" s="15" t="n">
+        <v>989.15</v>
+      </c>
+      <c r="O39" s="15" t="n">
+        <v>2780.57</v>
+      </c>
+      <c r="P39" s="15" t="n">
+        <v>260.83</v>
+      </c>
+      <c r="Q39" s="15" t="n">
+        <v>260.83</v>
+      </c>
+      <c r="R39" s="15" t="n">
+        <v>-260.61</v>
+      </c>
+      <c r="S39" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="T39" s="15" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="U39" s="15" t="n">
+        <v>73</v>
+      </c>
+      <c r="V39" s="15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="W39" s="15" t="n">
+        <v>119.72</v>
+      </c>
+      <c r="X39" s="15" t="n">
+        <v>-380.33</v>
+      </c>
+      <c r="Y39" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="Z39" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA39" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -34949,7 +35821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -37534,6 +38406,76 @@
       <c r="I74" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B75" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C75" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="D75" s="19" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="E75" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="F75" s="19" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G75" s="19" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="H75" s="19" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="I75" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — STOP LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B76" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C76" s="19" t="n">
+        <v>73</v>
+      </c>
+      <c r="D76" s="19" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E76" s="19" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="F76" s="19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="G76" s="19" t="n">
+        <v>59.86</v>
+      </c>
+      <c r="H76" s="19" t="n">
+        <v>119.72</v>
+      </c>
+      <c r="I76" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — STOP LOSS</t>
         </is>
       </c>
     </row>
@@ -38000,7 +38942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN38"/>
+  <dimension ref="A1:AN39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -43680,6 +44622,158 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E39" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F39" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G39" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H39" s="15" t="n">
+        <v>24131.43</v>
+      </c>
+      <c r="I39" s="15" t="n">
+        <v>23974.58</v>
+      </c>
+      <c r="J39" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K39" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L39" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M39" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N39" s="15" t="inlineStr">
+        <is>
+          <t>09:54 IST</t>
+        </is>
+      </c>
+      <c r="O39" s="15" t="n">
+        <v>24141.15</v>
+      </c>
+      <c r="P39" s="15" t="n">
+        <v>24211</v>
+      </c>
+      <c r="Q39" s="15" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="R39" s="15" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="S39" s="15" t="n">
+        <v>33</v>
+      </c>
+      <c r="T39" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U39" s="15" t="n">
+        <v>2145</v>
+      </c>
+      <c r="V39" s="15" t="n">
+        <v>22.12</v>
+      </c>
+      <c r="W39" s="15" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="X39" s="15" t="n">
+        <v>47447.4</v>
+      </c>
+      <c r="Y39" s="15" t="n">
+        <v>47502.07</v>
+      </c>
+      <c r="Z39" s="15" t="n">
+        <v>167052.6</v>
+      </c>
+      <c r="AA39" s="15" t="n">
+        <v>14234.22</v>
+      </c>
+      <c r="AB39" s="15" t="n">
+        <v>14234.22</v>
+      </c>
+      <c r="AC39" s="15" t="n">
+        <v>-14242.8</v>
+      </c>
+      <c r="AD39" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE39" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF39" s="15" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="AG39" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH39" s="15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI39" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ39" s="15" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="AK39" s="15" t="n">
+        <v>-14297.47</v>
+      </c>
+      <c r="AL39" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM39" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN39" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -43694,7 +44788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN38"/>
+  <dimension ref="A1:AN39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -49374,6 +50468,158 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D39" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E39" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F39" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G39" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H39" s="17" t="n">
+        <v>24131.43</v>
+      </c>
+      <c r="I39" s="17" t="n">
+        <v>23974.58</v>
+      </c>
+      <c r="J39" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K39" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L39" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M39" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N39" s="17" t="inlineStr">
+        <is>
+          <t>10:20 IST</t>
+        </is>
+      </c>
+      <c r="O39" s="17" t="n">
+        <v>24141.15</v>
+      </c>
+      <c r="P39" s="17" t="n">
+        <v>24211</v>
+      </c>
+      <c r="Q39" s="17" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="R39" s="17" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="S39" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="T39" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U39" s="17" t="n">
+        <v>2925</v>
+      </c>
+      <c r="V39" s="17" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="W39" s="17" t="n">
+        <v>20.98</v>
+      </c>
+      <c r="X39" s="17" t="n">
+        <v>47209.5</v>
+      </c>
+      <c r="Y39" s="17" t="n">
+        <v>47264.13</v>
+      </c>
+      <c r="Z39" s="17" t="n">
+        <v>245290.5</v>
+      </c>
+      <c r="AA39" s="17" t="n">
+        <v>14162.85</v>
+      </c>
+      <c r="AB39" s="17" t="n">
+        <v>14162.85</v>
+      </c>
+      <c r="AC39" s="17" t="n">
+        <v>14157</v>
+      </c>
+      <c r="AD39" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE39" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF39" s="17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AG39" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH39" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI39" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ39" s="17" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="AK39" s="17" t="n">
+        <v>14102.37</v>
+      </c>
+      <c r="AL39" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM39" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN39" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -49388,7 +50634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN74"/>
+  <dimension ref="A1:AN76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -60495,6 +61741,310 @@
         <v>50000</v>
       </c>
       <c r="AN74" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B75" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C75" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D75" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E75" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F75" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G75" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H75" s="17" t="n">
+        <v>24131.43</v>
+      </c>
+      <c r="I75" s="17" t="n">
+        <v>23974.58</v>
+      </c>
+      <c r="J75" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K75" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L75" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M75" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N75" s="17" t="inlineStr">
+        <is>
+          <t>11:22 IST</t>
+        </is>
+      </c>
+      <c r="O75" s="17" t="n">
+        <v>24141.15</v>
+      </c>
+      <c r="P75" s="17" t="n">
+        <v>24211</v>
+      </c>
+      <c r="Q75" s="17" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="R75" s="17" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="S75" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="T75" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U75" s="17" t="n">
+        <v>3055</v>
+      </c>
+      <c r="V75" s="17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W75" s="17" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="X75" s="17" t="n">
+        <v>47352.5</v>
+      </c>
+      <c r="Y75" s="17" t="n">
+        <v>47407.15</v>
+      </c>
+      <c r="Z75" s="17" t="n">
+        <v>258147.5</v>
+      </c>
+      <c r="AA75" s="17" t="n">
+        <v>14205.75</v>
+      </c>
+      <c r="AB75" s="17" t="n">
+        <v>14205.75</v>
+      </c>
+      <c r="AC75" s="17" t="n">
+        <v>14205.75</v>
+      </c>
+      <c r="AD75" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE75" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF75" s="17" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="AG75" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH75" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI75" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ75" s="17" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="AK75" s="17" t="n">
+        <v>14151.1</v>
+      </c>
+      <c r="AL75" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM75" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN75" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B76" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C76" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D76" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E76" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F76" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G76" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H76" s="17" t="n">
+        <v>24131.43</v>
+      </c>
+      <c r="I76" s="17" t="n">
+        <v>23974.58</v>
+      </c>
+      <c r="J76" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K76" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L76" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M76" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N76" s="17" t="inlineStr">
+        <is>
+          <t>12:12 IST</t>
+        </is>
+      </c>
+      <c r="O76" s="17" t="n">
+        <v>24141.15</v>
+      </c>
+      <c r="P76" s="17" t="n">
+        <v>24211</v>
+      </c>
+      <c r="Q76" s="17" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="R76" s="17" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="S76" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="T76" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U76" s="17" t="n">
+        <v>2795</v>
+      </c>
+      <c r="V76" s="17" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="W76" s="17" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="X76" s="17" t="n">
+        <v>48269.65</v>
+      </c>
+      <c r="Y76" s="17" t="n">
+        <v>48324.45</v>
+      </c>
+      <c r="Z76" s="17" t="n">
+        <v>231230.35</v>
+      </c>
+      <c r="AA76" s="17" t="n">
+        <v>14480.9</v>
+      </c>
+      <c r="AB76" s="17" t="n">
+        <v>14480.9</v>
+      </c>
+      <c r="AC76" s="17" t="n">
+        <v>14478.1</v>
+      </c>
+      <c r="AD76" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE76" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF76" s="17" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AG76" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH76" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI76" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ76" s="17" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="AK76" s="17" t="n">
+        <v>14423.3</v>
+      </c>
+      <c r="AL76" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM76" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN76" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA39"/>
+  <dimension ref="A1:AA40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4443,6 +4443,105 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="inlineStr">
+        <is>
+          <t>12:12 ET</t>
+        </is>
+      </c>
+      <c r="H40" s="17" t="n">
+        <v>29856.75</v>
+      </c>
+      <c r="I40" s="17" t="n">
+        <v>29850</v>
+      </c>
+      <c r="J40" s="17" t="n">
+        <v>29875</v>
+      </c>
+      <c r="K40" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L40" s="17" t="n">
+        <v>115.62</v>
+      </c>
+      <c r="M40" s="17" t="n">
+        <v>150.31</v>
+      </c>
+      <c r="N40" s="17" t="n">
+        <v>984.16</v>
+      </c>
+      <c r="O40" s="17" t="n">
+        <v>3075.04</v>
+      </c>
+      <c r="P40" s="17" t="n">
+        <v>277.49</v>
+      </c>
+      <c r="Q40" s="17" t="n">
+        <v>277.49</v>
+      </c>
+      <c r="R40" s="17" t="n">
+        <v>277.52</v>
+      </c>
+      <c r="S40" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T40" s="17" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="U40" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="V40" s="17" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="W40" s="17" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="X40" s="17" t="n">
+        <v>218.32</v>
+      </c>
+      <c r="Y40" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z40" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA40" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -4457,7 +4556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN39"/>
+  <dimension ref="A1:AN40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10289,6 +10388,158 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E40" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G40" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H40" s="16" t="n">
+        <v>57711.5</v>
+      </c>
+      <c r="I40" s="16" t="n">
+        <v>57234.43</v>
+      </c>
+      <c r="J40" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K40" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L40" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="M40" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N40" s="16" t="inlineStr">
+        <is>
+          <t>15:07 IST</t>
+        </is>
+      </c>
+      <c r="O40" s="16" t="n">
+        <v>57462.3</v>
+      </c>
+      <c r="P40" s="16" t="n">
+        <v>58131.45</v>
+      </c>
+      <c r="Q40" s="16" t="inlineStr">
+        <is>
+          <t>57400 CE</t>
+        </is>
+      </c>
+      <c r="R40" s="16" t="inlineStr">
+        <is>
+          <t>57600 CE</t>
+        </is>
+      </c>
+      <c r="S40" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="T40" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U40" s="16" t="n">
+        <v>570</v>
+      </c>
+      <c r="V40" s="16" t="n">
+        <v>83.43000000000001</v>
+      </c>
+      <c r="W40" s="16" t="n">
+        <v>81.78</v>
+      </c>
+      <c r="X40" s="16" t="n">
+        <v>47555.1</v>
+      </c>
+      <c r="Y40" s="16" t="n">
+        <v>47609.78</v>
+      </c>
+      <c r="Z40" s="16" t="n">
+        <v>66444.89999999999</v>
+      </c>
+      <c r="AA40" s="16" t="n">
+        <v>14266.53</v>
+      </c>
+      <c r="AB40" s="16" t="n">
+        <v>14266.53</v>
+      </c>
+      <c r="AC40" s="16" t="n">
+        <v>-940.5</v>
+      </c>
+      <c r="AD40" s="16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE40" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF40" s="16" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AG40" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH40" s="16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI40" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ40" s="16" t="n">
+        <v>54.68</v>
+      </c>
+      <c r="AK40" s="16" t="n">
+        <v>-995.1799999999999</v>
+      </c>
+      <c r="AL40" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM40" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN40" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -10303,7 +10554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN39"/>
+  <dimension ref="A1:AN40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16135,6 +16386,158 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F40" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G40" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H40" s="15" t="n">
+        <v>57711.5</v>
+      </c>
+      <c r="I40" s="15" t="n">
+        <v>57234.43</v>
+      </c>
+      <c r="J40" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K40" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L40" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="M40" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N40" s="15" t="inlineStr">
+        <is>
+          <t>09:47 IST</t>
+        </is>
+      </c>
+      <c r="O40" s="15" t="n">
+        <v>57462.3</v>
+      </c>
+      <c r="P40" s="15" t="n">
+        <v>58131.45</v>
+      </c>
+      <c r="Q40" s="15" t="inlineStr">
+        <is>
+          <t>57600 PE</t>
+        </is>
+      </c>
+      <c r="R40" s="15" t="inlineStr">
+        <is>
+          <t>57400 PE</t>
+        </is>
+      </c>
+      <c r="S40" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="T40" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U40" s="15" t="n">
+        <v>480</v>
+      </c>
+      <c r="V40" s="15" t="n">
+        <v>98.69</v>
+      </c>
+      <c r="W40" s="15" t="n">
+        <v>69.08</v>
+      </c>
+      <c r="X40" s="15" t="n">
+        <v>47371.2</v>
+      </c>
+      <c r="Y40" s="15" t="n">
+        <v>47425.85</v>
+      </c>
+      <c r="Z40" s="15" t="n">
+        <v>48628.8</v>
+      </c>
+      <c r="AA40" s="15" t="n">
+        <v>14211.36</v>
+      </c>
+      <c r="AB40" s="15" t="n">
+        <v>14211.36</v>
+      </c>
+      <c r="AC40" s="15" t="n">
+        <v>-14212.8</v>
+      </c>
+      <c r="AD40" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE40" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF40" s="15" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="AG40" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH40" s="15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI40" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ40" s="15" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="AK40" s="15" t="n">
+        <v>-14267.45</v>
+      </c>
+      <c r="AL40" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM40" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN40" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -16149,7 +16552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN76"/>
+  <dimension ref="A1:AN78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -27560,6 +27963,310 @@
         <v>50000</v>
       </c>
       <c r="AN76" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B77" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C77" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E77" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F77" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G77" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H77" s="15" t="n">
+        <v>57711.5</v>
+      </c>
+      <c r="I77" s="15" t="n">
+        <v>57234.43</v>
+      </c>
+      <c r="J77" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K77" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L77" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="M77" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N77" s="15" t="inlineStr">
+        <is>
+          <t>10:25 IST</t>
+        </is>
+      </c>
+      <c r="O77" s="15" t="n">
+        <v>57462.3</v>
+      </c>
+      <c r="P77" s="15" t="n">
+        <v>58131.45</v>
+      </c>
+      <c r="Q77" s="15" t="inlineStr">
+        <is>
+          <t>57400 CE</t>
+        </is>
+      </c>
+      <c r="R77" s="15" t="inlineStr">
+        <is>
+          <t>57600 CE</t>
+        </is>
+      </c>
+      <c r="S77" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="T77" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U77" s="15" t="n">
+        <v>510</v>
+      </c>
+      <c r="V77" s="15" t="n">
+        <v>95.36</v>
+      </c>
+      <c r="W77" s="15" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="X77" s="15" t="n">
+        <v>48633.6</v>
+      </c>
+      <c r="Y77" s="15" t="n">
+        <v>48688.45</v>
+      </c>
+      <c r="Z77" s="15" t="n">
+        <v>53366.4</v>
+      </c>
+      <c r="AA77" s="15" t="n">
+        <v>14590.08</v>
+      </c>
+      <c r="AB77" s="15" t="n">
+        <v>14590.08</v>
+      </c>
+      <c r="AC77" s="15" t="n">
+        <v>-14591.1</v>
+      </c>
+      <c r="AD77" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE77" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF77" s="15" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="AG77" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH77" s="15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI77" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ77" s="15" t="n">
+        <v>54.85</v>
+      </c>
+      <c r="AK77" s="15" t="n">
+        <v>-14645.95</v>
+      </c>
+      <c r="AL77" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM77" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN77" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B78" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C78" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D78" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E78" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F78" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G78" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H78" s="17" t="n">
+        <v>57711.5</v>
+      </c>
+      <c r="I78" s="17" t="n">
+        <v>57234.43</v>
+      </c>
+      <c r="J78" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K78" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L78" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="M78" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N78" s="17" t="inlineStr">
+        <is>
+          <t>10:13 IST</t>
+        </is>
+      </c>
+      <c r="O78" s="17" t="n">
+        <v>57462.3</v>
+      </c>
+      <c r="P78" s="17" t="n">
+        <v>58131.45</v>
+      </c>
+      <c r="Q78" s="17" t="inlineStr">
+        <is>
+          <t>57600 PE</t>
+        </is>
+      </c>
+      <c r="R78" s="17" t="inlineStr">
+        <is>
+          <t>57400 PE</t>
+        </is>
+      </c>
+      <c r="S78" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T78" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U78" s="17" t="n">
+        <v>450</v>
+      </c>
+      <c r="V78" s="17" t="n">
+        <v>105.02</v>
+      </c>
+      <c r="W78" s="17" t="n">
+        <v>136.53</v>
+      </c>
+      <c r="X78" s="17" t="n">
+        <v>47259</v>
+      </c>
+      <c r="Y78" s="17" t="n">
+        <v>47313.64</v>
+      </c>
+      <c r="Z78" s="17" t="n">
+        <v>42741</v>
+      </c>
+      <c r="AA78" s="17" t="n">
+        <v>14177.7</v>
+      </c>
+      <c r="AB78" s="17" t="n">
+        <v>14177.7</v>
+      </c>
+      <c r="AC78" s="17" t="n">
+        <v>14179.5</v>
+      </c>
+      <c r="AD78" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE78" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF78" s="17" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AG78" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH78" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI78" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ78" s="17" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="AK78" s="17" t="n">
+        <v>14124.86</v>
+      </c>
+      <c r="AL78" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM78" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN78" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -30709,7 +31416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -31849,6 +32556,72 @@
         <v>57250.18</v>
       </c>
       <c r="G35" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D36" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>24113.61</v>
+      </c>
+      <c r="F36" s="18" t="n">
+        <v>23966.48</v>
+      </c>
+      <c r="G36" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B37" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D37" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E37" s="18" t="n">
+        <v>57711.5</v>
+      </c>
+      <c r="F37" s="18" t="n">
+        <v>57234.43</v>
+      </c>
+      <c r="G37" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -31868,7 +32641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA39"/>
+  <dimension ref="A1:AA40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -35702,6 +36475,105 @@
         <v>1000</v>
       </c>
       <c r="AA39" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="inlineStr">
+        <is>
+          <t>10:44 ET</t>
+        </is>
+      </c>
+      <c r="H40" s="17" t="n">
+        <v>29856.75</v>
+      </c>
+      <c r="I40" s="17" t="n">
+        <v>29850</v>
+      </c>
+      <c r="J40" s="17" t="n">
+        <v>29875</v>
+      </c>
+      <c r="K40" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="L40" s="17" t="n">
+        <v>14.28</v>
+      </c>
+      <c r="M40" s="17" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="N40" s="17" t="n">
+        <v>987.04</v>
+      </c>
+      <c r="O40" s="17" t="n">
+        <v>2214.64</v>
+      </c>
+      <c r="P40" s="17" t="n">
+        <v>265.61</v>
+      </c>
+      <c r="Q40" s="17" t="n">
+        <v>265.61</v>
+      </c>
+      <c r="R40" s="17" t="n">
+        <v>265.36</v>
+      </c>
+      <c r="S40" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T40" s="17" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="U40" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="V40" s="17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="W40" s="17" t="n">
+        <v>101.68</v>
+      </c>
+      <c r="X40" s="17" t="n">
+        <v>163.68</v>
+      </c>
+      <c r="Y40" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z40" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA40" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -35821,7 +36693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -38476,6 +39348,76 @@
       <c r="I76" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — STOP LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B77" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C77" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="D77" s="19" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="E77" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="F77" s="19" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G77" s="19" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="H77" s="19" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="I77" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B78" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C78" s="19" t="n">
+        <v>62</v>
+      </c>
+      <c r="D78" s="19" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="E78" s="19" t="n">
+        <v>31</v>
+      </c>
+      <c r="F78" s="19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="G78" s="19" t="n">
+        <v>50.84</v>
+      </c>
+      <c r="H78" s="19" t="n">
+        <v>101.68</v>
+      </c>
+      <c r="I78" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — PROFIT</t>
         </is>
       </c>
     </row>
@@ -38942,7 +39884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN39"/>
+  <dimension ref="A1:AN40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -44774,6 +45716,158 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F40" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H40" s="17" t="n">
+        <v>24113.61</v>
+      </c>
+      <c r="I40" s="17" t="n">
+        <v>23966.48</v>
+      </c>
+      <c r="J40" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K40" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L40" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M40" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N40" s="17" t="inlineStr">
+        <is>
+          <t>11:48 IST</t>
+        </is>
+      </c>
+      <c r="O40" s="17" t="n">
+        <v>24052.05</v>
+      </c>
+      <c r="P40" s="17" t="n">
+        <v>24211</v>
+      </c>
+      <c r="Q40" s="17" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="R40" s="17" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="S40" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="T40" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U40" s="17" t="n">
+        <v>2145</v>
+      </c>
+      <c r="V40" s="17" t="n">
+        <v>22.01</v>
+      </c>
+      <c r="W40" s="17" t="n">
+        <v>28.61</v>
+      </c>
+      <c r="X40" s="17" t="n">
+        <v>47211.45</v>
+      </c>
+      <c r="Y40" s="17" t="n">
+        <v>47266.08</v>
+      </c>
+      <c r="Z40" s="17" t="n">
+        <v>167288.55</v>
+      </c>
+      <c r="AA40" s="17" t="n">
+        <v>14163.43</v>
+      </c>
+      <c r="AB40" s="17" t="n">
+        <v>14163.43</v>
+      </c>
+      <c r="AC40" s="17" t="n">
+        <v>14157</v>
+      </c>
+      <c r="AD40" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE40" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF40" s="17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AG40" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH40" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI40" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ40" s="17" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="AK40" s="17" t="n">
+        <v>14102.37</v>
+      </c>
+      <c r="AL40" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM40" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN40" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -44788,7 +45882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN39"/>
+  <dimension ref="A1:AN40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -50620,6 +51714,158 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F40" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H40" s="17" t="n">
+        <v>24113.61</v>
+      </c>
+      <c r="I40" s="17" t="n">
+        <v>23966.48</v>
+      </c>
+      <c r="J40" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K40" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L40" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M40" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N40" s="17" t="inlineStr">
+        <is>
+          <t>12:14 IST</t>
+        </is>
+      </c>
+      <c r="O40" s="17" t="n">
+        <v>24052.05</v>
+      </c>
+      <c r="P40" s="17" t="n">
+        <v>24211</v>
+      </c>
+      <c r="Q40" s="17" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="R40" s="17" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="S40" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="T40" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U40" s="17" t="n">
+        <v>2470</v>
+      </c>
+      <c r="V40" s="17" t="n">
+        <v>19.41</v>
+      </c>
+      <c r="W40" s="17" t="n">
+        <v>25.23</v>
+      </c>
+      <c r="X40" s="17" t="n">
+        <v>47942.7</v>
+      </c>
+      <c r="Y40" s="17" t="n">
+        <v>47997.44</v>
+      </c>
+      <c r="Z40" s="17" t="n">
+        <v>199057.3</v>
+      </c>
+      <c r="AA40" s="17" t="n">
+        <v>14382.81</v>
+      </c>
+      <c r="AB40" s="17" t="n">
+        <v>14382.81</v>
+      </c>
+      <c r="AC40" s="17" t="n">
+        <v>14375.4</v>
+      </c>
+      <c r="AD40" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE40" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF40" s="17" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="AG40" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH40" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI40" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ40" s="17" t="n">
+        <v>54.74</v>
+      </c>
+      <c r="AK40" s="17" t="n">
+        <v>14320.66</v>
+      </c>
+      <c r="AL40" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM40" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN40" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -50634,7 +51880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN76"/>
+  <dimension ref="A1:AN78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -62045,6 +63291,310 @@
         <v>50000</v>
       </c>
       <c r="AN76" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B77" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C77" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D77" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E77" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F77" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G77" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H77" s="17" t="n">
+        <v>24113.61</v>
+      </c>
+      <c r="I77" s="17" t="n">
+        <v>23966.48</v>
+      </c>
+      <c r="J77" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K77" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L77" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M77" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N77" s="17" t="inlineStr">
+        <is>
+          <t>12:15 IST</t>
+        </is>
+      </c>
+      <c r="O77" s="17" t="n">
+        <v>24052.05</v>
+      </c>
+      <c r="P77" s="17" t="n">
+        <v>24211</v>
+      </c>
+      <c r="Q77" s="17" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="R77" s="17" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="S77" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="T77" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U77" s="17" t="n">
+        <v>2990</v>
+      </c>
+      <c r="V77" s="17" t="n">
+        <v>15.97</v>
+      </c>
+      <c r="W77" s="17" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="X77" s="17" t="n">
+        <v>47750.3</v>
+      </c>
+      <c r="Y77" s="17" t="n">
+        <v>47805.01</v>
+      </c>
+      <c r="Z77" s="17" t="n">
+        <v>251249.7</v>
+      </c>
+      <c r="AA77" s="17" t="n">
+        <v>14325.09</v>
+      </c>
+      <c r="AB77" s="17" t="n">
+        <v>14325.09</v>
+      </c>
+      <c r="AC77" s="17" t="n">
+        <v>14322.1</v>
+      </c>
+      <c r="AD77" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE77" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF77" s="17" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="AG77" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH77" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI77" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ77" s="17" t="n">
+        <v>54.71</v>
+      </c>
+      <c r="AK77" s="17" t="n">
+        <v>14267.39</v>
+      </c>
+      <c r="AL77" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM77" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN77" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B78" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C78" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D78" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E78" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F78" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G78" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H78" s="17" t="n">
+        <v>24113.61</v>
+      </c>
+      <c r="I78" s="17" t="n">
+        <v>23966.48</v>
+      </c>
+      <c r="J78" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K78" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L78" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M78" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N78" s="17" t="inlineStr">
+        <is>
+          <t>10:07 IST</t>
+        </is>
+      </c>
+      <c r="O78" s="17" t="n">
+        <v>24052.05</v>
+      </c>
+      <c r="P78" s="17" t="n">
+        <v>24211</v>
+      </c>
+      <c r="Q78" s="17" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="R78" s="17" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="S78" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="T78" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U78" s="17" t="n">
+        <v>2080</v>
+      </c>
+      <c r="V78" s="17" t="n">
+        <v>22.72</v>
+      </c>
+      <c r="W78" s="17" t="n">
+        <v>29.54</v>
+      </c>
+      <c r="X78" s="17" t="n">
+        <v>47257.6</v>
+      </c>
+      <c r="Y78" s="17" t="n">
+        <v>47312.24</v>
+      </c>
+      <c r="Z78" s="17" t="n">
+        <v>160742.4</v>
+      </c>
+      <c r="AA78" s="17" t="n">
+        <v>14177.28</v>
+      </c>
+      <c r="AB78" s="17" t="n">
+        <v>14177.28</v>
+      </c>
+      <c r="AC78" s="17" t="n">
+        <v>14185.6</v>
+      </c>
+      <c r="AD78" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE78" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF78" s="17" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AG78" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH78" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI78" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ78" s="17" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="AK78" s="17" t="n">
+        <v>14130.96</v>
+      </c>
+      <c r="AL78" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM78" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN78" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA40"/>
+  <dimension ref="A1:AA41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4542,6 +4542,105 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G41" s="17" t="inlineStr">
+        <is>
+          <t>12:11 ET</t>
+        </is>
+      </c>
+      <c r="H41" s="17" t="n">
+        <v>29997</v>
+      </c>
+      <c r="I41" s="17" t="n">
+        <v>29975</v>
+      </c>
+      <c r="J41" s="17" t="n">
+        <v>30000</v>
+      </c>
+      <c r="K41" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="L41" s="17" t="n">
+        <v>149.96</v>
+      </c>
+      <c r="M41" s="17" t="n">
+        <v>194.95</v>
+      </c>
+      <c r="N41" s="17" t="n">
+        <v>944.16</v>
+      </c>
+      <c r="O41" s="17" t="n">
+        <v>2100.24</v>
+      </c>
+      <c r="P41" s="17" t="n">
+        <v>269.93</v>
+      </c>
+      <c r="Q41" s="17" t="n">
+        <v>269.93</v>
+      </c>
+      <c r="R41" s="17" t="n">
+        <v>269.94</v>
+      </c>
+      <c r="S41" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T41" s="17" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="U41" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="V41" s="17" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="W41" s="17" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="X41" s="17" t="n">
+        <v>225.54</v>
+      </c>
+      <c r="Y41" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z41" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA41" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -4556,7 +4655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN40"/>
+  <dimension ref="A1:AN41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10540,6 +10639,158 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E41" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F41" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G41" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H41" s="17" t="n">
+        <v>57832.62</v>
+      </c>
+      <c r="I41" s="17" t="n">
+        <v>57322.04</v>
+      </c>
+      <c r="J41" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K41" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L41" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="M41" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N41" s="17" t="inlineStr">
+        <is>
+          <t>12:15 IST</t>
+        </is>
+      </c>
+      <c r="O41" s="17" t="n">
+        <v>58073.65</v>
+      </c>
+      <c r="P41" s="17" t="n">
+        <v>58131.45</v>
+      </c>
+      <c r="Q41" s="17" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="R41" s="17" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="S41" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="T41" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U41" s="17" t="n">
+        <v>540</v>
+      </c>
+      <c r="V41" s="17" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="W41" s="17" t="n">
+        <v>117.39</v>
+      </c>
+      <c r="X41" s="17" t="n">
+        <v>48762</v>
+      </c>
+      <c r="Y41" s="17" t="n">
+        <v>48816.87</v>
+      </c>
+      <c r="Z41" s="17" t="n">
+        <v>59238</v>
+      </c>
+      <c r="AA41" s="17" t="n">
+        <v>14628.6</v>
+      </c>
+      <c r="AB41" s="17" t="n">
+        <v>14628.6</v>
+      </c>
+      <c r="AC41" s="17" t="n">
+        <v>14628.6</v>
+      </c>
+      <c r="AD41" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE41" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF41" s="17" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AG41" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH41" s="17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI41" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ41" s="17" t="n">
+        <v>54.87</v>
+      </c>
+      <c r="AK41" s="17" t="n">
+        <v>14573.73</v>
+      </c>
+      <c r="AL41" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM41" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN41" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -10554,7 +10805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN40"/>
+  <dimension ref="A1:AN41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16538,6 +16789,158 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E41" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F41" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G41" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H41" s="17" t="n">
+        <v>57832.62</v>
+      </c>
+      <c r="I41" s="17" t="n">
+        <v>57322.04</v>
+      </c>
+      <c r="J41" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K41" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L41" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="M41" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N41" s="17" t="inlineStr">
+        <is>
+          <t>11:37 IST</t>
+        </is>
+      </c>
+      <c r="O41" s="17" t="n">
+        <v>58073.65</v>
+      </c>
+      <c r="P41" s="17" t="n">
+        <v>58131.45</v>
+      </c>
+      <c r="Q41" s="17" t="inlineStr">
+        <is>
+          <t>58200 PE</t>
+        </is>
+      </c>
+      <c r="R41" s="17" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="S41" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="T41" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U41" s="17" t="n">
+        <v>540</v>
+      </c>
+      <c r="V41" s="17" t="n">
+        <v>87.56</v>
+      </c>
+      <c r="W41" s="17" t="n">
+        <v>113.83</v>
+      </c>
+      <c r="X41" s="17" t="n">
+        <v>47282.4</v>
+      </c>
+      <c r="Y41" s="17" t="n">
+        <v>47337.04</v>
+      </c>
+      <c r="Z41" s="17" t="n">
+        <v>60717.6</v>
+      </c>
+      <c r="AA41" s="17" t="n">
+        <v>14184.72</v>
+      </c>
+      <c r="AB41" s="17" t="n">
+        <v>14184.72</v>
+      </c>
+      <c r="AC41" s="17" t="n">
+        <v>14185.8</v>
+      </c>
+      <c r="AD41" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE41" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF41" s="17" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AG41" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH41" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI41" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ41" s="17" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="AK41" s="17" t="n">
+        <v>14131.16</v>
+      </c>
+      <c r="AL41" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM41" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN41" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -16552,7 +16955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN78"/>
+  <dimension ref="A1:AN80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -28267,6 +28670,310 @@
         <v>50000</v>
       </c>
       <c r="AN78" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B79" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C79" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D79" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E79" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F79" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G79" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H79" s="15" t="n">
+        <v>57832.62</v>
+      </c>
+      <c r="I79" s="15" t="n">
+        <v>57322.04</v>
+      </c>
+      <c r="J79" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K79" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L79" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="M79" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N79" s="15" t="inlineStr">
+        <is>
+          <t>10:34 IST</t>
+        </is>
+      </c>
+      <c r="O79" s="15" t="n">
+        <v>58073.65</v>
+      </c>
+      <c r="P79" s="15" t="n">
+        <v>58131.45</v>
+      </c>
+      <c r="Q79" s="15" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="R79" s="15" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="S79" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="T79" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U79" s="15" t="n">
+        <v>570</v>
+      </c>
+      <c r="V79" s="15" t="n">
+        <v>85.14</v>
+      </c>
+      <c r="W79" s="15" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="X79" s="15" t="n">
+        <v>48529.8</v>
+      </c>
+      <c r="Y79" s="15" t="n">
+        <v>48584.64</v>
+      </c>
+      <c r="Z79" s="15" t="n">
+        <v>65470.2</v>
+      </c>
+      <c r="AA79" s="15" t="n">
+        <v>14558.94</v>
+      </c>
+      <c r="AB79" s="15" t="n">
+        <v>14558.94</v>
+      </c>
+      <c r="AC79" s="15" t="n">
+        <v>-14557.8</v>
+      </c>
+      <c r="AD79" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE79" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF79" s="15" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="AG79" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH79" s="15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI79" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ79" s="15" t="n">
+        <v>54.84</v>
+      </c>
+      <c r="AK79" s="15" t="n">
+        <v>-14612.64</v>
+      </c>
+      <c r="AL79" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM79" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN79" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B80" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C80" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D80" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E80" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F80" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G80" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H80" s="16" t="n">
+        <v>57832.62</v>
+      </c>
+      <c r="I80" s="16" t="n">
+        <v>57322.04</v>
+      </c>
+      <c r="J80" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K80" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L80" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="M80" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N80" s="16" t="inlineStr">
+        <is>
+          <t>14:15 IST</t>
+        </is>
+      </c>
+      <c r="O80" s="16" t="n">
+        <v>58073.65</v>
+      </c>
+      <c r="P80" s="16" t="n">
+        <v>58131.45</v>
+      </c>
+      <c r="Q80" s="16" t="inlineStr">
+        <is>
+          <t>58200 PE</t>
+        </is>
+      </c>
+      <c r="R80" s="16" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="S80" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="T80" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U80" s="16" t="n">
+        <v>510</v>
+      </c>
+      <c r="V80" s="16" t="n">
+        <v>93.81</v>
+      </c>
+      <c r="W80" s="16" t="n">
+        <v>97.03</v>
+      </c>
+      <c r="X80" s="16" t="n">
+        <v>47843.1</v>
+      </c>
+      <c r="Y80" s="16" t="n">
+        <v>47897.83</v>
+      </c>
+      <c r="Z80" s="16" t="n">
+        <v>54156.9</v>
+      </c>
+      <c r="AA80" s="16" t="n">
+        <v>14352.93</v>
+      </c>
+      <c r="AB80" s="16" t="n">
+        <v>14352.93</v>
+      </c>
+      <c r="AC80" s="16" t="n">
+        <v>1642.2</v>
+      </c>
+      <c r="AD80" s="16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE80" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF80" s="16" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AG80" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH80" s="16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI80" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ80" s="16" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="AK80" s="16" t="n">
+        <v>1587.47</v>
+      </c>
+      <c r="AL80" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM80" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN80" s="16" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -31416,7 +32123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32622,6 +33329,72 @@
         <v>57234.43</v>
       </c>
       <c r="G37" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D38" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E38" s="18" t="n">
+        <v>24143.29</v>
+      </c>
+      <c r="F38" s="18" t="n">
+        <v>23977</v>
+      </c>
+      <c r="G38" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B39" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D39" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>57832.62</v>
+      </c>
+      <c r="F39" s="18" t="n">
+        <v>57322.04</v>
+      </c>
+      <c r="G39" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -32641,7 +33414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA40"/>
+  <dimension ref="A1:AA41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -36574,6 +37347,105 @@
         <v>1000</v>
       </c>
       <c r="AA40" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G41" s="16" t="inlineStr">
+        <is>
+          <t>16:19 ET</t>
+        </is>
+      </c>
+      <c r="H41" s="16" t="n">
+        <v>29995.75</v>
+      </c>
+      <c r="I41" s="16" t="n">
+        <v>29975</v>
+      </c>
+      <c r="J41" s="16" t="n">
+        <v>30000</v>
+      </c>
+      <c r="K41" s="16" t="n">
+        <v>66</v>
+      </c>
+      <c r="L41" s="16" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="M41" s="16" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="N41" s="16" t="n">
+        <v>993.96</v>
+      </c>
+      <c r="O41" s="16" t="n">
+        <v>2414.28</v>
+      </c>
+      <c r="P41" s="16" t="n">
+        <v>265.72</v>
+      </c>
+      <c r="Q41" s="16" t="n">
+        <v>265.72</v>
+      </c>
+      <c r="R41" s="16" t="n">
+        <v>-31.02</v>
+      </c>
+      <c r="S41" s="16" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="T41" s="16" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="U41" s="16" t="n">
+        <v>66</v>
+      </c>
+      <c r="V41" s="16" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="W41" s="16" t="n">
+        <v>108.24</v>
+      </c>
+      <c r="X41" s="16" t="n">
+        <v>-139.26</v>
+      </c>
+      <c r="Y41" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="Z41" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA41" s="16" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -36693,7 +37565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -39418,6 +40290,76 @@
       <c r="I78" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B79" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C79" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D79" s="19" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="E79" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="F79" s="19" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G79" s="19" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="H79" s="19" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="I79" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B80" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C80" s="19" t="n">
+        <v>66</v>
+      </c>
+      <c r="D80" s="19" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="E80" s="19" t="n">
+        <v>33</v>
+      </c>
+      <c r="F80" s="19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G80" s="19" t="n">
+        <v>54.12</v>
+      </c>
+      <c r="H80" s="19" t="n">
+        <v>108.24</v>
+      </c>
+      <c r="I80" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — FLAT</t>
         </is>
       </c>
     </row>
@@ -39884,7 +40826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN40"/>
+  <dimension ref="A1:AN41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -45868,6 +46810,158 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F41" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G41" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="n">
+        <v>24143.29</v>
+      </c>
+      <c r="I41" s="15" t="n">
+        <v>23977</v>
+      </c>
+      <c r="J41" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K41" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L41" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N41" s="15" t="inlineStr">
+        <is>
+          <t>11:11 IST</t>
+        </is>
+      </c>
+      <c r="O41" s="15" t="n">
+        <v>24204.6</v>
+      </c>
+      <c r="P41" s="15" t="n">
+        <v>24211</v>
+      </c>
+      <c r="Q41" s="15" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="R41" s="15" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="S41" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="T41" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U41" s="15" t="n">
+        <v>1950</v>
+      </c>
+      <c r="V41" s="15" t="n">
+        <v>24.73</v>
+      </c>
+      <c r="W41" s="15" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="X41" s="15" t="n">
+        <v>48223.5</v>
+      </c>
+      <c r="Y41" s="15" t="n">
+        <v>48278.29</v>
+      </c>
+      <c r="Z41" s="15" t="n">
+        <v>146776.5</v>
+      </c>
+      <c r="AA41" s="15" t="n">
+        <v>14467.05</v>
+      </c>
+      <c r="AB41" s="15" t="n">
+        <v>14467.05</v>
+      </c>
+      <c r="AC41" s="15" t="n">
+        <v>-14469</v>
+      </c>
+      <c r="AD41" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE41" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF41" s="15" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AG41" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH41" s="15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI41" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ41" s="15" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="AK41" s="15" t="n">
+        <v>-14523.79</v>
+      </c>
+      <c r="AL41" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM41" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN41" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -45882,7 +46976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN40"/>
+  <dimension ref="A1:AN41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -51866,6 +52960,158 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G41" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H41" s="16" t="n">
+        <v>24143.29</v>
+      </c>
+      <c r="I41" s="16" t="n">
+        <v>23977</v>
+      </c>
+      <c r="J41" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K41" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L41" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N41" s="16" t="inlineStr">
+        <is>
+          <t>14:07 IST</t>
+        </is>
+      </c>
+      <c r="O41" s="16" t="n">
+        <v>24204.6</v>
+      </c>
+      <c r="P41" s="16" t="n">
+        <v>24211</v>
+      </c>
+      <c r="Q41" s="16" t="inlineStr">
+        <is>
+          <t>24300 PE</t>
+        </is>
+      </c>
+      <c r="R41" s="16" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="S41" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="T41" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U41" s="16" t="n">
+        <v>1950</v>
+      </c>
+      <c r="V41" s="16" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="W41" s="16" t="n">
+        <v>24.56</v>
+      </c>
+      <c r="X41" s="16" t="n">
+        <v>47541</v>
+      </c>
+      <c r="Y41" s="16" t="n">
+        <v>47595.68</v>
+      </c>
+      <c r="Z41" s="16" t="n">
+        <v>147459</v>
+      </c>
+      <c r="AA41" s="16" t="n">
+        <v>14262.3</v>
+      </c>
+      <c r="AB41" s="16" t="n">
+        <v>14262.3</v>
+      </c>
+      <c r="AC41" s="16" t="n">
+        <v>351</v>
+      </c>
+      <c r="AD41" s="16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AE41" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF41" s="16" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AG41" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH41" s="16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI41" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ41" s="16" t="n">
+        <v>54.68</v>
+      </c>
+      <c r="AK41" s="16" t="n">
+        <v>296.32</v>
+      </c>
+      <c r="AL41" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM41" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN41" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -51880,7 +53126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN78"/>
+  <dimension ref="A1:AN80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -63595,6 +64841,310 @@
         <v>50000</v>
       </c>
       <c r="AN78" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B79" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C79" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D79" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E79" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F79" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G79" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H79" s="17" t="n">
+        <v>24143.29</v>
+      </c>
+      <c r="I79" s="17" t="n">
+        <v>23977</v>
+      </c>
+      <c r="J79" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K79" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L79" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N79" s="17" t="inlineStr">
+        <is>
+          <t>11:48 IST</t>
+        </is>
+      </c>
+      <c r="O79" s="17" t="n">
+        <v>24204.6</v>
+      </c>
+      <c r="P79" s="17" t="n">
+        <v>24211</v>
+      </c>
+      <c r="Q79" s="17" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="R79" s="17" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="S79" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="T79" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U79" s="17" t="n">
+        <v>2015</v>
+      </c>
+      <c r="V79" s="17" t="n">
+        <v>23.51</v>
+      </c>
+      <c r="W79" s="17" t="n">
+        <v>30.56</v>
+      </c>
+      <c r="X79" s="17" t="n">
+        <v>47372.65</v>
+      </c>
+      <c r="Y79" s="17" t="n">
+        <v>47427.3</v>
+      </c>
+      <c r="Z79" s="17" t="n">
+        <v>154127.35</v>
+      </c>
+      <c r="AA79" s="17" t="n">
+        <v>14211.8</v>
+      </c>
+      <c r="AB79" s="17" t="n">
+        <v>14211.8</v>
+      </c>
+      <c r="AC79" s="17" t="n">
+        <v>14205.75</v>
+      </c>
+      <c r="AD79" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE79" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF79" s="17" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="AG79" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH79" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI79" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ79" s="17" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="AK79" s="17" t="n">
+        <v>14151.1</v>
+      </c>
+      <c r="AL79" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM79" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN79" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B80" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C80" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D80" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E80" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F80" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G80" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H80" s="17" t="n">
+        <v>24143.29</v>
+      </c>
+      <c r="I80" s="17" t="n">
+        <v>23977</v>
+      </c>
+      <c r="J80" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K80" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L80" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M80" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N80" s="17" t="inlineStr">
+        <is>
+          <t>11:36 IST</t>
+        </is>
+      </c>
+      <c r="O80" s="17" t="n">
+        <v>24204.6</v>
+      </c>
+      <c r="P80" s="17" t="n">
+        <v>24211</v>
+      </c>
+      <c r="Q80" s="17" t="inlineStr">
+        <is>
+          <t>24300 PE</t>
+        </is>
+      </c>
+      <c r="R80" s="17" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="S80" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="T80" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U80" s="17" t="n">
+        <v>3055</v>
+      </c>
+      <c r="V80" s="17" t="n">
+        <v>15.64</v>
+      </c>
+      <c r="W80" s="17" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="X80" s="17" t="n">
+        <v>47780.2</v>
+      </c>
+      <c r="Y80" s="17" t="n">
+        <v>47834.92</v>
+      </c>
+      <c r="Z80" s="17" t="n">
+        <v>257719.8</v>
+      </c>
+      <c r="AA80" s="17" t="n">
+        <v>14334.06</v>
+      </c>
+      <c r="AB80" s="17" t="n">
+        <v>14334.06</v>
+      </c>
+      <c r="AC80" s="17" t="n">
+        <v>14327.95</v>
+      </c>
+      <c r="AD80" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE80" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF80" s="17" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="AG80" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH80" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI80" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ80" s="17" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="AK80" s="17" t="n">
+        <v>14273.23</v>
+      </c>
+      <c r="AL80" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM80" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN80" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA41"/>
+  <dimension ref="A1:AA42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4641,6 +4641,105 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="inlineStr">
+        <is>
+          <t>12:35 ET</t>
+        </is>
+      </c>
+      <c r="H42" s="17" t="n">
+        <v>29575.25</v>
+      </c>
+      <c r="I42" s="17" t="n">
+        <v>29575</v>
+      </c>
+      <c r="J42" s="17" t="n">
+        <v>29600</v>
+      </c>
+      <c r="K42" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L42" s="17" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="M42" s="17" t="n">
+        <v>151.84</v>
+      </c>
+      <c r="N42" s="17" t="n">
+        <v>993.6</v>
+      </c>
+      <c r="O42" s="17" t="n">
+        <v>3065.6</v>
+      </c>
+      <c r="P42" s="17" t="n">
+        <v>280.32</v>
+      </c>
+      <c r="Q42" s="17" t="n">
+        <v>280.32</v>
+      </c>
+      <c r="R42" s="17" t="n">
+        <v>280.32</v>
+      </c>
+      <c r="S42" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T42" s="17" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="U42" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="V42" s="17" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="W42" s="17" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="X42" s="17" t="n">
+        <v>221.12</v>
+      </c>
+      <c r="Y42" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z42" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA42" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -4655,7 +4754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN41"/>
+  <dimension ref="A1:AN42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10791,6 +10890,158 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E42" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G42" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H42" s="16" t="n">
+        <v>57769.47</v>
+      </c>
+      <c r="I42" s="16" t="n">
+        <v>57293.33</v>
+      </c>
+      <c r="J42" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K42" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L42" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="M42" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N42" s="16" t="inlineStr">
+        <is>
+          <t>15:02 IST</t>
+        </is>
+      </c>
+      <c r="O42" s="16" t="n">
+        <v>57757.85</v>
+      </c>
+      <c r="P42" s="16" t="n">
+        <v>58131.45</v>
+      </c>
+      <c r="Q42" s="16" t="inlineStr">
+        <is>
+          <t>57600 CE</t>
+        </is>
+      </c>
+      <c r="R42" s="16" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="S42" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="T42" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U42" s="16" t="n">
+        <v>510</v>
+      </c>
+      <c r="V42" s="16" t="n">
+        <v>92.91</v>
+      </c>
+      <c r="W42" s="16" t="n">
+        <v>94.84</v>
+      </c>
+      <c r="X42" s="16" t="n">
+        <v>47384.1</v>
+      </c>
+      <c r="Y42" s="16" t="n">
+        <v>47438.76</v>
+      </c>
+      <c r="Z42" s="16" t="n">
+        <v>54615.9</v>
+      </c>
+      <c r="AA42" s="16" t="n">
+        <v>14215.23</v>
+      </c>
+      <c r="AB42" s="16" t="n">
+        <v>14215.23</v>
+      </c>
+      <c r="AC42" s="16" t="n">
+        <v>984.3</v>
+      </c>
+      <c r="AD42" s="16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE42" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF42" s="16" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="AG42" s="16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH42" s="16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI42" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ42" s="16" t="n">
+        <v>54.66</v>
+      </c>
+      <c r="AK42" s="16" t="n">
+        <v>929.64</v>
+      </c>
+      <c r="AL42" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM42" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN42" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -10805,7 +11056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN41"/>
+  <dimension ref="A1:AN42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16941,6 +17192,158 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E42" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G42" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H42" s="16" t="n">
+        <v>57769.47</v>
+      </c>
+      <c r="I42" s="16" t="n">
+        <v>57293.33</v>
+      </c>
+      <c r="J42" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K42" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L42" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="M42" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N42" s="16" t="inlineStr">
+        <is>
+          <t>13:38 IST</t>
+        </is>
+      </c>
+      <c r="O42" s="16" t="n">
+        <v>57757.85</v>
+      </c>
+      <c r="P42" s="16" t="n">
+        <v>58131.45</v>
+      </c>
+      <c r="Q42" s="16" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="R42" s="16" t="inlineStr">
+        <is>
+          <t>57600 PE</t>
+        </is>
+      </c>
+      <c r="S42" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="T42" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U42" s="16" t="n">
+        <v>570</v>
+      </c>
+      <c r="V42" s="16" t="n">
+        <v>85.86</v>
+      </c>
+      <c r="W42" s="16" t="n">
+        <v>82.08</v>
+      </c>
+      <c r="X42" s="16" t="n">
+        <v>48940.2</v>
+      </c>
+      <c r="Y42" s="16" t="n">
+        <v>48995.1</v>
+      </c>
+      <c r="Z42" s="16" t="n">
+        <v>65059.8</v>
+      </c>
+      <c r="AA42" s="16" t="n">
+        <v>14682.06</v>
+      </c>
+      <c r="AB42" s="16" t="n">
+        <v>14682.06</v>
+      </c>
+      <c r="AC42" s="16" t="n">
+        <v>-2154.6</v>
+      </c>
+      <c r="AD42" s="16" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="AE42" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF42" s="16" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="AG42" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH42" s="16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI42" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ42" s="16" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="AK42" s="16" t="n">
+        <v>-2209.5</v>
+      </c>
+      <c r="AL42" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM42" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN42" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -16955,7 +17358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN80"/>
+  <dimension ref="A1:AN82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -28974,6 +29377,310 @@
         <v>50000</v>
       </c>
       <c r="AN80" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C81" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D81" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E81" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F81" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G81" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H81" s="15" t="n">
+        <v>57769.47</v>
+      </c>
+      <c r="I81" s="15" t="n">
+        <v>57293.33</v>
+      </c>
+      <c r="J81" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K81" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L81" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="M81" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N81" s="15" t="inlineStr">
+        <is>
+          <t>10:01 IST</t>
+        </is>
+      </c>
+      <c r="O81" s="15" t="n">
+        <v>57757.85</v>
+      </c>
+      <c r="P81" s="15" t="n">
+        <v>58131.45</v>
+      </c>
+      <c r="Q81" s="15" t="inlineStr">
+        <is>
+          <t>57600 CE</t>
+        </is>
+      </c>
+      <c r="R81" s="15" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="S81" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="T81" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U81" s="15" t="n">
+        <v>570</v>
+      </c>
+      <c r="V81" s="15" t="n">
+        <v>85.01000000000001</v>
+      </c>
+      <c r="W81" s="15" t="n">
+        <v>59.51</v>
+      </c>
+      <c r="X81" s="15" t="n">
+        <v>48455.7</v>
+      </c>
+      <c r="Y81" s="15" t="n">
+        <v>48510.52</v>
+      </c>
+      <c r="Z81" s="15" t="n">
+        <v>65544.3</v>
+      </c>
+      <c r="AA81" s="15" t="n">
+        <v>14536.71</v>
+      </c>
+      <c r="AB81" s="15" t="n">
+        <v>14536.71</v>
+      </c>
+      <c r="AC81" s="15" t="n">
+        <v>-14535</v>
+      </c>
+      <c r="AD81" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE81" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF81" s="15" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="AG81" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH81" s="15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI81" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ81" s="15" t="n">
+        <v>54.82</v>
+      </c>
+      <c r="AK81" s="15" t="n">
+        <v>-14589.82</v>
+      </c>
+      <c r="AL81" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM81" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN81" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B82" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C82" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D82" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E82" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F82" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G82" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H82" s="17" t="n">
+        <v>57769.47</v>
+      </c>
+      <c r="I82" s="17" t="n">
+        <v>57293.33</v>
+      </c>
+      <c r="J82" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K82" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L82" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="M82" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N82" s="17" t="inlineStr">
+        <is>
+          <t>12:12 IST</t>
+        </is>
+      </c>
+      <c r="O82" s="17" t="n">
+        <v>57757.85</v>
+      </c>
+      <c r="P82" s="17" t="n">
+        <v>58131.45</v>
+      </c>
+      <c r="Q82" s="17" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="R82" s="17" t="inlineStr">
+        <is>
+          <t>57600 PE</t>
+        </is>
+      </c>
+      <c r="S82" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="T82" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U82" s="17" t="n">
+        <v>660</v>
+      </c>
+      <c r="V82" s="17" t="n">
+        <v>73.37</v>
+      </c>
+      <c r="W82" s="17" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="X82" s="17" t="n">
+        <v>48424.2</v>
+      </c>
+      <c r="Y82" s="17" t="n">
+        <v>48479.02</v>
+      </c>
+      <c r="Z82" s="17" t="n">
+        <v>83575.8</v>
+      </c>
+      <c r="AA82" s="17" t="n">
+        <v>14527.26</v>
+      </c>
+      <c r="AB82" s="17" t="n">
+        <v>14527.26</v>
+      </c>
+      <c r="AC82" s="17" t="n">
+        <v>14526.6</v>
+      </c>
+      <c r="AD82" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE82" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF82" s="17" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AG82" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH82" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI82" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ82" s="17" t="n">
+        <v>54.82</v>
+      </c>
+      <c r="AK82" s="17" t="n">
+        <v>14471.78</v>
+      </c>
+      <c r="AL82" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM82" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN82" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -32123,7 +32830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -33395,6 +34102,72 @@
         <v>57322.04</v>
       </c>
       <c r="G39" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="n">
+        <v>24118.07</v>
+      </c>
+      <c r="F40" s="18" t="n">
+        <v>23965.53</v>
+      </c>
+      <c r="G40" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B41" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D41" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>57769.47</v>
+      </c>
+      <c r="F41" s="18" t="n">
+        <v>57293.33</v>
+      </c>
+      <c r="G41" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -33414,7 +34187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA41"/>
+  <dimension ref="A1:AA42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -37446,6 +38219,105 @@
         <v>1000</v>
       </c>
       <c r="AA41" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="inlineStr">
+        <is>
+          <t>12:24 ET</t>
+        </is>
+      </c>
+      <c r="H42" s="17" t="n">
+        <v>29575.25</v>
+      </c>
+      <c r="I42" s="17" t="n">
+        <v>29575</v>
+      </c>
+      <c r="J42" s="17" t="n">
+        <v>29600</v>
+      </c>
+      <c r="K42" s="17" t="n">
+        <v>72</v>
+      </c>
+      <c r="L42" s="17" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="M42" s="17" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="N42" s="17" t="n">
+        <v>998.64</v>
+      </c>
+      <c r="O42" s="17" t="n">
+        <v>2719.44</v>
+      </c>
+      <c r="P42" s="17" t="n">
+        <v>264.17</v>
+      </c>
+      <c r="Q42" s="17" t="n">
+        <v>264.17</v>
+      </c>
+      <c r="R42" s="17" t="n">
+        <v>264.24</v>
+      </c>
+      <c r="S42" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T42" s="17" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="U42" s="17" t="n">
+        <v>72</v>
+      </c>
+      <c r="V42" s="17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="W42" s="17" t="n">
+        <v>118.08</v>
+      </c>
+      <c r="X42" s="17" t="n">
+        <v>146.16</v>
+      </c>
+      <c r="Y42" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z42" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA42" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -37565,7 +38437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -40360,6 +41232,76 @@
       <c r="I80" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B81" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C81" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="D81" s="19" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="E81" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="F81" s="19" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G81" s="19" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="H81" s="19" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="I81" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B82" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C82" s="19" t="n">
+        <v>72</v>
+      </c>
+      <c r="D82" s="19" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="E82" s="19" t="n">
+        <v>36</v>
+      </c>
+      <c r="F82" s="19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G82" s="19" t="n">
+        <v>59.04</v>
+      </c>
+      <c r="H82" s="19" t="n">
+        <v>118.08</v>
+      </c>
+      <c r="I82" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — PROFIT</t>
         </is>
       </c>
     </row>
@@ -40826,7 +41768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN41"/>
+  <dimension ref="A1:AN42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -46962,6 +47904,158 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E42" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G42" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H42" s="16" t="n">
+        <v>24118.07</v>
+      </c>
+      <c r="I42" s="16" t="n">
+        <v>23965.53</v>
+      </c>
+      <c r="J42" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K42" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L42" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N42" s="16" t="inlineStr">
+        <is>
+          <t>14:03 IST</t>
+        </is>
+      </c>
+      <c r="O42" s="16" t="n">
+        <v>24078.5</v>
+      </c>
+      <c r="P42" s="16" t="n">
+        <v>24211</v>
+      </c>
+      <c r="Q42" s="16" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="R42" s="16" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="S42" s="16" t="n">
+        <v>38</v>
+      </c>
+      <c r="T42" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U42" s="16" t="n">
+        <v>2470</v>
+      </c>
+      <c r="V42" s="16" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="W42" s="16" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="X42" s="16" t="n">
+        <v>47473.4</v>
+      </c>
+      <c r="Y42" s="16" t="n">
+        <v>47528.07</v>
+      </c>
+      <c r="Z42" s="16" t="n">
+        <v>199526.6</v>
+      </c>
+      <c r="AA42" s="16" t="n">
+        <v>14242.02</v>
+      </c>
+      <c r="AB42" s="16" t="n">
+        <v>14242.02</v>
+      </c>
+      <c r="AC42" s="16" t="n">
+        <v>-617.5</v>
+      </c>
+      <c r="AD42" s="16" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="AE42" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF42" s="16" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="AG42" s="16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH42" s="16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI42" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ42" s="16" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="AK42" s="16" t="n">
+        <v>-672.17</v>
+      </c>
+      <c r="AL42" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM42" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN42" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -46976,7 +48070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN41"/>
+  <dimension ref="A1:AN42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -53112,6 +54206,158 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H42" s="17" t="n">
+        <v>24118.07</v>
+      </c>
+      <c r="I42" s="17" t="n">
+        <v>23965.53</v>
+      </c>
+      <c r="J42" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K42" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L42" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N42" s="17" t="inlineStr">
+        <is>
+          <t>11:04 IST</t>
+        </is>
+      </c>
+      <c r="O42" s="17" t="n">
+        <v>24078.5</v>
+      </c>
+      <c r="P42" s="17" t="n">
+        <v>24211</v>
+      </c>
+      <c r="Q42" s="17" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="R42" s="17" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="S42" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="T42" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U42" s="17" t="n">
+        <v>2470</v>
+      </c>
+      <c r="V42" s="17" t="n">
+        <v>19.37</v>
+      </c>
+      <c r="W42" s="17" t="n">
+        <v>25.18</v>
+      </c>
+      <c r="X42" s="17" t="n">
+        <v>47843.9</v>
+      </c>
+      <c r="Y42" s="17" t="n">
+        <v>47898.63</v>
+      </c>
+      <c r="Z42" s="17" t="n">
+        <v>199156.1</v>
+      </c>
+      <c r="AA42" s="17" t="n">
+        <v>14353.17</v>
+      </c>
+      <c r="AB42" s="17" t="n">
+        <v>14353.17</v>
+      </c>
+      <c r="AC42" s="17" t="n">
+        <v>14350.7</v>
+      </c>
+      <c r="AD42" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE42" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF42" s="17" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AG42" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH42" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI42" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ42" s="17" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="AK42" s="17" t="n">
+        <v>14295.97</v>
+      </c>
+      <c r="AL42" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM42" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN42" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -53126,7 +54372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN80"/>
+  <dimension ref="A1:AN82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -65145,6 +66391,310 @@
         <v>50000</v>
       </c>
       <c r="AN80" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C81" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D81" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E81" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F81" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G81" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H81" s="15" t="n">
+        <v>24118.07</v>
+      </c>
+      <c r="I81" s="15" t="n">
+        <v>23965.53</v>
+      </c>
+      <c r="J81" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K81" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L81" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M81" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N81" s="15" t="inlineStr">
+        <is>
+          <t>09:33 IST</t>
+        </is>
+      </c>
+      <c r="O81" s="15" t="n">
+        <v>24078.5</v>
+      </c>
+      <c r="P81" s="15" t="n">
+        <v>24211</v>
+      </c>
+      <c r="Q81" s="15" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="R81" s="15" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="S81" s="15" t="n">
+        <v>41</v>
+      </c>
+      <c r="T81" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U81" s="15" t="n">
+        <v>2665</v>
+      </c>
+      <c r="V81" s="15" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="W81" s="15" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="X81" s="15" t="n">
+        <v>48129.9</v>
+      </c>
+      <c r="Y81" s="15" t="n">
+        <v>48184.67</v>
+      </c>
+      <c r="Z81" s="15" t="n">
+        <v>218370.1</v>
+      </c>
+      <c r="AA81" s="15" t="n">
+        <v>14438.97</v>
+      </c>
+      <c r="AB81" s="15" t="n">
+        <v>14438.97</v>
+      </c>
+      <c r="AC81" s="15" t="n">
+        <v>-14444.3</v>
+      </c>
+      <c r="AD81" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE81" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF81" s="15" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="AG81" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH81" s="15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI81" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ81" s="15" t="n">
+        <v>54.77</v>
+      </c>
+      <c r="AK81" s="15" t="n">
+        <v>-14499.07</v>
+      </c>
+      <c r="AL81" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM81" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN81" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B82" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C82" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D82" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E82" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F82" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G82" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H82" s="17" t="n">
+        <v>24118.07</v>
+      </c>
+      <c r="I82" s="17" t="n">
+        <v>23965.53</v>
+      </c>
+      <c r="J82" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K82" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L82" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N82" s="17" t="inlineStr">
+        <is>
+          <t>10:25 IST</t>
+        </is>
+      </c>
+      <c r="O82" s="17" t="n">
+        <v>24078.5</v>
+      </c>
+      <c r="P82" s="17" t="n">
+        <v>24211</v>
+      </c>
+      <c r="Q82" s="17" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="R82" s="17" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="S82" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="T82" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U82" s="17" t="n">
+        <v>2145</v>
+      </c>
+      <c r="V82" s="17" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="W82" s="17" t="n">
+        <v>28.63</v>
+      </c>
+      <c r="X82" s="17" t="n">
+        <v>47232.9</v>
+      </c>
+      <c r="Y82" s="17" t="n">
+        <v>47287.53</v>
+      </c>
+      <c r="Z82" s="17" t="n">
+        <v>167267.1</v>
+      </c>
+      <c r="AA82" s="17" t="n">
+        <v>14169.87</v>
+      </c>
+      <c r="AB82" s="17" t="n">
+        <v>14169.87</v>
+      </c>
+      <c r="AC82" s="17" t="n">
+        <v>14178.45</v>
+      </c>
+      <c r="AD82" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE82" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF82" s="17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AG82" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH82" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI82" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ82" s="17" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="AK82" s="17" t="n">
+        <v>14123.82</v>
+      </c>
+      <c r="AL82" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM82" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN82" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA42"/>
+  <dimension ref="A1:AA43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4740,6 +4740,105 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="15" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G43" s="15" t="inlineStr">
+        <is>
+          <t>11:56 ET</t>
+        </is>
+      </c>
+      <c r="H43" s="15" t="n">
+        <v>29698.5</v>
+      </c>
+      <c r="I43" s="15" t="n">
+        <v>29675</v>
+      </c>
+      <c r="J43" s="15" t="n">
+        <v>29700</v>
+      </c>
+      <c r="K43" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="L43" s="15" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="M43" s="15" t="n">
+        <v>83.93000000000001</v>
+      </c>
+      <c r="N43" s="15" t="n">
+        <v>891.1</v>
+      </c>
+      <c r="O43" s="15" t="n">
+        <v>2660.7</v>
+      </c>
+      <c r="P43" s="15" t="n">
+        <v>251.79</v>
+      </c>
+      <c r="Q43" s="15" t="n">
+        <v>251.79</v>
+      </c>
+      <c r="R43" s="15" t="n">
+        <v>-251.79</v>
+      </c>
+      <c r="S43" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="T43" s="15" t="n">
+        <v>16.52</v>
+      </c>
+      <c r="U43" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="V43" s="15" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="W43" s="15" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="X43" s="15" t="n">
+        <v>-303.59</v>
+      </c>
+      <c r="Y43" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="Z43" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA43" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -4754,7 +4853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN42"/>
+  <dimension ref="A1:AN43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11042,6 +11141,158 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E43" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F43" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G43" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H43" s="17" t="n">
+        <v>57711.42</v>
+      </c>
+      <c r="I43" s="17" t="n">
+        <v>57371.59</v>
+      </c>
+      <c r="J43" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K43" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L43" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="M43" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N43" s="17" t="inlineStr">
+        <is>
+          <t>09:56 IST</t>
+        </is>
+      </c>
+      <c r="O43" s="17" t="n">
+        <v>57680.55</v>
+      </c>
+      <c r="P43" s="17" t="n">
+        <v>57757.85</v>
+      </c>
+      <c r="Q43" s="17" t="inlineStr">
+        <is>
+          <t>57600 CE</t>
+        </is>
+      </c>
+      <c r="R43" s="17" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="S43" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="T43" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U43" s="17" t="n">
+        <v>510</v>
+      </c>
+      <c r="V43" s="17" t="n">
+        <v>94.01000000000001</v>
+      </c>
+      <c r="W43" s="17" t="n">
+        <v>122.21</v>
+      </c>
+      <c r="X43" s="17" t="n">
+        <v>47945.1</v>
+      </c>
+      <c r="Y43" s="17" t="n">
+        <v>47999.84</v>
+      </c>
+      <c r="Z43" s="17" t="n">
+        <v>54054.9</v>
+      </c>
+      <c r="AA43" s="17" t="n">
+        <v>14383.53</v>
+      </c>
+      <c r="AB43" s="17" t="n">
+        <v>14383.53</v>
+      </c>
+      <c r="AC43" s="17" t="n">
+        <v>14382</v>
+      </c>
+      <c r="AD43" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE43" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF43" s="17" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="AG43" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH43" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI43" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ43" s="17" t="n">
+        <v>54.74</v>
+      </c>
+      <c r="AK43" s="17" t="n">
+        <v>14327.26</v>
+      </c>
+      <c r="AL43" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM43" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN43" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -11056,7 +11307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN42"/>
+  <dimension ref="A1:AN43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17344,6 +17595,158 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E43" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G43" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H43" s="16" t="n">
+        <v>57711.42</v>
+      </c>
+      <c r="I43" s="16" t="n">
+        <v>57371.59</v>
+      </c>
+      <c r="J43" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K43" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L43" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="M43" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N43" s="16" t="inlineStr">
+        <is>
+          <t>14:13 IST</t>
+        </is>
+      </c>
+      <c r="O43" s="16" t="n">
+        <v>57680.55</v>
+      </c>
+      <c r="P43" s="16" t="n">
+        <v>57757.85</v>
+      </c>
+      <c r="Q43" s="16" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="R43" s="16" t="inlineStr">
+        <is>
+          <t>57600 PE</t>
+        </is>
+      </c>
+      <c r="S43" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T43" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U43" s="16" t="n">
+        <v>600</v>
+      </c>
+      <c r="V43" s="16" t="n">
+        <v>79.91</v>
+      </c>
+      <c r="W43" s="16" t="n">
+        <v>82.59</v>
+      </c>
+      <c r="X43" s="16" t="n">
+        <v>47946</v>
+      </c>
+      <c r="Y43" s="16" t="n">
+        <v>48000.74</v>
+      </c>
+      <c r="Z43" s="16" t="n">
+        <v>72054</v>
+      </c>
+      <c r="AA43" s="16" t="n">
+        <v>14383.8</v>
+      </c>
+      <c r="AB43" s="16" t="n">
+        <v>14383.8</v>
+      </c>
+      <c r="AC43" s="16" t="n">
+        <v>1608</v>
+      </c>
+      <c r="AD43" s="16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE43" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF43" s="16" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="AG43" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH43" s="16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI43" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ43" s="16" t="n">
+        <v>54.74</v>
+      </c>
+      <c r="AK43" s="16" t="n">
+        <v>1553.26</v>
+      </c>
+      <c r="AL43" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM43" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN43" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -17358,7 +17761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN82"/>
+  <dimension ref="A1:AN84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -29681,6 +30084,310 @@
         <v>50000</v>
       </c>
       <c r="AN82" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B83" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C83" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D83" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E83" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F83" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G83" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H83" s="17" t="n">
+        <v>57711.42</v>
+      </c>
+      <c r="I83" s="17" t="n">
+        <v>57371.59</v>
+      </c>
+      <c r="J83" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K83" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L83" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="M83" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N83" s="17" t="inlineStr">
+        <is>
+          <t>10:29 IST</t>
+        </is>
+      </c>
+      <c r="O83" s="17" t="n">
+        <v>57680.55</v>
+      </c>
+      <c r="P83" s="17" t="n">
+        <v>57757.85</v>
+      </c>
+      <c r="Q83" s="17" t="inlineStr">
+        <is>
+          <t>57600 CE</t>
+        </is>
+      </c>
+      <c r="R83" s="17" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="S83" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="T83" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U83" s="17" t="n">
+        <v>540</v>
+      </c>
+      <c r="V83" s="17" t="n">
+        <v>89.76000000000001</v>
+      </c>
+      <c r="W83" s="17" t="n">
+        <v>116.69</v>
+      </c>
+      <c r="X83" s="17" t="n">
+        <v>48470.4</v>
+      </c>
+      <c r="Y83" s="17" t="n">
+        <v>48525.23</v>
+      </c>
+      <c r="Z83" s="17" t="n">
+        <v>59529.6</v>
+      </c>
+      <c r="AA83" s="17" t="n">
+        <v>14541.12</v>
+      </c>
+      <c r="AB83" s="17" t="n">
+        <v>14541.12</v>
+      </c>
+      <c r="AC83" s="17" t="n">
+        <v>14542.2</v>
+      </c>
+      <c r="AD83" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE83" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF83" s="17" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="AG83" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH83" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI83" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ83" s="17" t="n">
+        <v>54.83</v>
+      </c>
+      <c r="AK83" s="17" t="n">
+        <v>14487.37</v>
+      </c>
+      <c r="AL83" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM83" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN83" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B84" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C84" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D84" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E84" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F84" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G84" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H84" s="17" t="n">
+        <v>57711.42</v>
+      </c>
+      <c r="I84" s="17" t="n">
+        <v>57371.59</v>
+      </c>
+      <c r="J84" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K84" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L84" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="M84" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N84" s="17" t="inlineStr">
+        <is>
+          <t>09:51 IST</t>
+        </is>
+      </c>
+      <c r="O84" s="17" t="n">
+        <v>57680.55</v>
+      </c>
+      <c r="P84" s="17" t="n">
+        <v>57757.85</v>
+      </c>
+      <c r="Q84" s="17" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="R84" s="17" t="inlineStr">
+        <is>
+          <t>57600 PE</t>
+        </is>
+      </c>
+      <c r="S84" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="T84" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U84" s="17" t="n">
+        <v>540</v>
+      </c>
+      <c r="V84" s="17" t="n">
+        <v>87.98999999999999</v>
+      </c>
+      <c r="W84" s="17" t="n">
+        <v>114.39</v>
+      </c>
+      <c r="X84" s="17" t="n">
+        <v>47514.6</v>
+      </c>
+      <c r="Y84" s="17" t="n">
+        <v>47569.28</v>
+      </c>
+      <c r="Z84" s="17" t="n">
+        <v>60485.4</v>
+      </c>
+      <c r="AA84" s="17" t="n">
+        <v>14254.38</v>
+      </c>
+      <c r="AB84" s="17" t="n">
+        <v>14254.38</v>
+      </c>
+      <c r="AC84" s="17" t="n">
+        <v>14256</v>
+      </c>
+      <c r="AD84" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE84" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF84" s="17" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AG84" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH84" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI84" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ84" s="17" t="n">
+        <v>54.68</v>
+      </c>
+      <c r="AK84" s="17" t="n">
+        <v>14201.32</v>
+      </c>
+      <c r="AL84" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM84" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN84" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -32830,7 +33537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -34168,6 +34875,39 @@
         <v>57293.33</v>
       </c>
       <c r="G41" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E42" s="18" t="n">
+        <v>57711.42</v>
+      </c>
+      <c r="F42" s="18" t="n">
+        <v>57371.59</v>
+      </c>
+      <c r="G42" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -34187,7 +34927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA42"/>
+  <dimension ref="A1:AA43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -38318,6 +39058,105 @@
         <v>1000</v>
       </c>
       <c r="AA42" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G43" s="17" t="inlineStr">
+        <is>
+          <t>11:52 ET</t>
+        </is>
+      </c>
+      <c r="H43" s="17" t="n">
+        <v>29698.5</v>
+      </c>
+      <c r="I43" s="17" t="n">
+        <v>29675</v>
+      </c>
+      <c r="J43" s="17" t="n">
+        <v>29700</v>
+      </c>
+      <c r="K43" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="L43" s="17" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="M43" s="17" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="N43" s="17" t="n">
+        <v>999.05</v>
+      </c>
+      <c r="O43" s="17" t="n">
+        <v>2357.55</v>
+      </c>
+      <c r="P43" s="17" t="n">
+        <v>267.74</v>
+      </c>
+      <c r="Q43" s="17" t="n">
+        <v>267.74</v>
+      </c>
+      <c r="R43" s="17" t="n">
+        <v>267.8</v>
+      </c>
+      <c r="S43" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T43" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="U43" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="V43" s="17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W43" s="17" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="X43" s="17" t="n">
+        <v>161.2</v>
+      </c>
+      <c r="Y43" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z43" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA43" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -38437,7 +39276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -41300,6 +42139,76 @@
         <v>118.08</v>
       </c>
       <c r="I82" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B83" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C83" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="D83" s="19" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="E83" s="19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F83" s="19" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G83" s="19" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="H83" s="19" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="I83" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — STOP LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B84" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C84" s="19" t="n">
+        <v>65</v>
+      </c>
+      <c r="D84" s="19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="E84" s="19" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="F84" s="19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G84" s="19" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="H84" s="19" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="I84" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — PROFIT</t>
         </is>
@@ -41768,7 +42677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN42"/>
+  <dimension ref="A1:AN43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -48056,6 +48965,158 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E43" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F43" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G43" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24152.45&gt;24078.5) &amp; EMA9↑(24114.61&gt;23985.11)</t>
+        </is>
+      </c>
+      <c r="H43" s="17" t="n">
+        <v>24114.61</v>
+      </c>
+      <c r="I43" s="17" t="n">
+        <v>23985.11</v>
+      </c>
+      <c r="J43" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K43" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L43" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N43" s="17" t="inlineStr">
+        <is>
+          <t>11:45 IST</t>
+        </is>
+      </c>
+      <c r="O43" s="17" t="n">
+        <v>24152.45</v>
+      </c>
+      <c r="P43" s="17" t="n">
+        <v>24078.5</v>
+      </c>
+      <c r="Q43" s="17" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="R43" s="17" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="S43" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="T43" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U43" s="17" t="n">
+        <v>2015</v>
+      </c>
+      <c r="V43" s="17" t="n">
+        <v>24.04</v>
+      </c>
+      <c r="W43" s="17" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="X43" s="17" t="n">
+        <v>48440.6</v>
+      </c>
+      <c r="Y43" s="17" t="n">
+        <v>48495.42</v>
+      </c>
+      <c r="Z43" s="17" t="n">
+        <v>153059.4</v>
+      </c>
+      <c r="AA43" s="17" t="n">
+        <v>14532.18</v>
+      </c>
+      <c r="AB43" s="17" t="n">
+        <v>14532.18</v>
+      </c>
+      <c r="AC43" s="17" t="n">
+        <v>14528.15</v>
+      </c>
+      <c r="AD43" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE43" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF43" s="17" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="AG43" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH43" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI43" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ43" s="17" t="n">
+        <v>54.82</v>
+      </c>
+      <c r="AK43" s="17" t="n">
+        <v>14473.33</v>
+      </c>
+      <c r="AL43" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM43" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN43" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -48070,7 +49131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN42"/>
+  <dimension ref="A1:AN43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -54358,6 +55419,158 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E43" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G43" s="16" t="inlineStr">
+        <is>
+          <t>Price↑(24152.45&gt;24078.5) &amp; EMA9↑(24114.61&gt;23985.11)</t>
+        </is>
+      </c>
+      <c r="H43" s="16" t="n">
+        <v>24114.61</v>
+      </c>
+      <c r="I43" s="16" t="n">
+        <v>23985.11</v>
+      </c>
+      <c r="J43" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K43" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L43" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N43" s="16" t="inlineStr">
+        <is>
+          <t>13:41 IST</t>
+        </is>
+      </c>
+      <c r="O43" s="16" t="n">
+        <v>24152.45</v>
+      </c>
+      <c r="P43" s="16" t="n">
+        <v>24078.5</v>
+      </c>
+      <c r="Q43" s="16" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="R43" s="16" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="S43" s="16" t="n">
+        <v>36</v>
+      </c>
+      <c r="T43" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U43" s="16" t="n">
+        <v>2340</v>
+      </c>
+      <c r="V43" s="16" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="W43" s="16" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="X43" s="16" t="n">
+        <v>48297.6</v>
+      </c>
+      <c r="Y43" s="16" t="n">
+        <v>48352.4</v>
+      </c>
+      <c r="Z43" s="16" t="n">
+        <v>185702.4</v>
+      </c>
+      <c r="AA43" s="16" t="n">
+        <v>14489.28</v>
+      </c>
+      <c r="AB43" s="16" t="n">
+        <v>14489.28</v>
+      </c>
+      <c r="AC43" s="16" t="n">
+        <v>374.4</v>
+      </c>
+      <c r="AD43" s="16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AE43" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF43" s="16" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="AG43" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH43" s="16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI43" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ43" s="16" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="AK43" s="16" t="n">
+        <v>319.6</v>
+      </c>
+      <c r="AL43" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM43" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN43" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -54372,7 +55585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN82"/>
+  <dimension ref="A1:AN84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -66700,6 +67913,310 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B83" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C83" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D83" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E83" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F83" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G83" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24152.45&gt;24078.5) &amp; EMA9↑(24114.61&gt;23985.11)</t>
+        </is>
+      </c>
+      <c r="H83" s="17" t="n">
+        <v>24114.61</v>
+      </c>
+      <c r="I83" s="17" t="n">
+        <v>23985.11</v>
+      </c>
+      <c r="J83" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K83" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L83" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N83" s="17" t="inlineStr">
+        <is>
+          <t>11:29 IST</t>
+        </is>
+      </c>
+      <c r="O83" s="17" t="n">
+        <v>24152.45</v>
+      </c>
+      <c r="P83" s="17" t="n">
+        <v>24078.5</v>
+      </c>
+      <c r="Q83" s="17" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="R83" s="17" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="S83" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="T83" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U83" s="17" t="n">
+        <v>2665</v>
+      </c>
+      <c r="V83" s="17" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="W83" s="17" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="X83" s="17" t="n">
+        <v>48236.5</v>
+      </c>
+      <c r="Y83" s="17" t="n">
+        <v>48291.29</v>
+      </c>
+      <c r="Z83" s="17" t="n">
+        <v>218263.5</v>
+      </c>
+      <c r="AA83" s="17" t="n">
+        <v>14470.95</v>
+      </c>
+      <c r="AB83" s="17" t="n">
+        <v>14470.95</v>
+      </c>
+      <c r="AC83" s="17" t="n">
+        <v>14470.95</v>
+      </c>
+      <c r="AD83" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE83" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF83" s="17" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AG83" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH83" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI83" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ83" s="17" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="AK83" s="17" t="n">
+        <v>14416.16</v>
+      </c>
+      <c r="AL83" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM83" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN83" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B84" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C84" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D84" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E84" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F84" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G84" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24152.45&gt;24078.5) &amp; EMA9↑(24114.61&gt;23985.11)</t>
+        </is>
+      </c>
+      <c r="H84" s="17" t="n">
+        <v>24114.61</v>
+      </c>
+      <c r="I84" s="17" t="n">
+        <v>23985.11</v>
+      </c>
+      <c r="J84" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K84" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L84" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N84" s="17" t="inlineStr">
+        <is>
+          <t>11:39 IST</t>
+        </is>
+      </c>
+      <c r="O84" s="17" t="n">
+        <v>24152.45</v>
+      </c>
+      <c r="P84" s="17" t="n">
+        <v>24078.5</v>
+      </c>
+      <c r="Q84" s="17" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="R84" s="17" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="S84" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="T84" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U84" s="17" t="n">
+        <v>2015</v>
+      </c>
+      <c r="V84" s="17" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="W84" s="17" t="n">
+        <v>30.55</v>
+      </c>
+      <c r="X84" s="17" t="n">
+        <v>47352.5</v>
+      </c>
+      <c r="Y84" s="17" t="n">
+        <v>47407.15</v>
+      </c>
+      <c r="Z84" s="17" t="n">
+        <v>154147.5</v>
+      </c>
+      <c r="AA84" s="17" t="n">
+        <v>14205.75</v>
+      </c>
+      <c r="AB84" s="17" t="n">
+        <v>14205.75</v>
+      </c>
+      <c r="AC84" s="17" t="n">
+        <v>14205.75</v>
+      </c>
+      <c r="AD84" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE84" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF84" s="17" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="AG84" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH84" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI84" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ84" s="17" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="AK84" s="17" t="n">
+        <v>14151.1</v>
+      </c>
+      <c r="AL84" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM84" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN84" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -66714,7 +68231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN24"/>
+  <dimension ref="A1:AN25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -70291,6 +71808,158 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G25" s="16" t="inlineStr">
+        <is>
+          <t>Price↑(24152.45&gt;24078.5) &amp; EMA9↑(24114.61&gt;23985.11)</t>
+        </is>
+      </c>
+      <c r="H25" s="16" t="n">
+        <v>24114.61</v>
+      </c>
+      <c r="I25" s="16" t="n">
+        <v>23985.11</v>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K25" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L25" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N25" s="16" t="inlineStr">
+        <is>
+          <t>14:09 IST</t>
+        </is>
+      </c>
+      <c r="O25" s="16" t="n">
+        <v>24152.45</v>
+      </c>
+      <c r="P25" s="16" t="n">
+        <v>24078.5</v>
+      </c>
+      <c r="Q25" s="16" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="R25" s="16" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="S25" s="16" t="n">
+        <v>31</v>
+      </c>
+      <c r="T25" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U25" s="16" t="n">
+        <v>2015</v>
+      </c>
+      <c r="V25" s="16" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="W25" s="16" t="n">
+        <v>23.26</v>
+      </c>
+      <c r="X25" s="16" t="n">
+        <v>48561.5</v>
+      </c>
+      <c r="Y25" s="16" t="n">
+        <v>48616.34</v>
+      </c>
+      <c r="Z25" s="16" t="n">
+        <v>152938.5</v>
+      </c>
+      <c r="AA25" s="16" t="n">
+        <v>14568.45</v>
+      </c>
+      <c r="AB25" s="16" t="n">
+        <v>14568.45</v>
+      </c>
+      <c r="AC25" s="16" t="n">
+        <v>-1692.6</v>
+      </c>
+      <c r="AD25" s="16" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AE25" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF25" s="16" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="AG25" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH25" s="16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI25" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ25" s="16" t="n">
+        <v>54.84</v>
+      </c>
+      <c r="AK25" s="16" t="n">
+        <v>-1747.44</v>
+      </c>
+      <c r="AL25" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM25" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN25" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA43"/>
+  <dimension ref="A1:AA44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4839,6 +4839,105 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G44" s="17" t="inlineStr">
+        <is>
+          <t>13:59 ET</t>
+        </is>
+      </c>
+      <c r="H44" s="17" t="n">
+        <v>29435</v>
+      </c>
+      <c r="I44" s="17" t="n">
+        <v>29425</v>
+      </c>
+      <c r="J44" s="17" t="n">
+        <v>29450</v>
+      </c>
+      <c r="K44" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="L44" s="17" t="n">
+        <v>147.73</v>
+      </c>
+      <c r="M44" s="17" t="n">
+        <v>192.05</v>
+      </c>
+      <c r="N44" s="17" t="n">
+        <v>930.78</v>
+      </c>
+      <c r="O44" s="17" t="n">
+        <v>2113.62</v>
+      </c>
+      <c r="P44" s="17" t="n">
+        <v>265.91</v>
+      </c>
+      <c r="Q44" s="17" t="n">
+        <v>265.91</v>
+      </c>
+      <c r="R44" s="17" t="n">
+        <v>265.92</v>
+      </c>
+      <c r="S44" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T44" s="17" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="U44" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="V44" s="17" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="W44" s="17" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="X44" s="17" t="n">
+        <v>221.52</v>
+      </c>
+      <c r="Y44" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z44" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA44" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -4853,7 +4952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN43"/>
+  <dimension ref="A1:AN44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11293,6 +11392,158 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E44" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F44" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G44" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H44" s="16" t="n">
+        <v>57691.76</v>
+      </c>
+      <c r="I44" s="16" t="n">
+        <v>57362.65</v>
+      </c>
+      <c r="J44" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K44" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L44" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="M44" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N44" s="16" t="inlineStr">
+        <is>
+          <t>15:13 IST</t>
+        </is>
+      </c>
+      <c r="O44" s="16" t="n">
+        <v>57582.25</v>
+      </c>
+      <c r="P44" s="16" t="n">
+        <v>57757.85</v>
+      </c>
+      <c r="Q44" s="16" t="inlineStr">
+        <is>
+          <t>57400 CE</t>
+        </is>
+      </c>
+      <c r="R44" s="16" t="inlineStr">
+        <is>
+          <t>57600 CE</t>
+        </is>
+      </c>
+      <c r="S44" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="T44" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U44" s="16" t="n">
+        <v>630</v>
+      </c>
+      <c r="V44" s="16" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="W44" s="16" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="X44" s="16" t="n">
+        <v>48384</v>
+      </c>
+      <c r="Y44" s="16" t="n">
+        <v>48438.81</v>
+      </c>
+      <c r="Z44" s="16" t="n">
+        <v>77616</v>
+      </c>
+      <c r="AA44" s="16" t="n">
+        <v>14515.2</v>
+      </c>
+      <c r="AB44" s="16" t="n">
+        <v>14515.2</v>
+      </c>
+      <c r="AC44" s="16" t="n">
+        <v>-346.5</v>
+      </c>
+      <c r="AD44" s="16" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AE44" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF44" s="16" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AG44" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH44" s="16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI44" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ44" s="16" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="AK44" s="16" t="n">
+        <v>-401.31</v>
+      </c>
+      <c r="AL44" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM44" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN44" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -11307,7 +11558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN43"/>
+  <dimension ref="A1:AN44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17747,6 +17998,158 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E44" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F44" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G44" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H44" s="16" t="n">
+        <v>57691.76</v>
+      </c>
+      <c r="I44" s="16" t="n">
+        <v>57362.65</v>
+      </c>
+      <c r="J44" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K44" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L44" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="M44" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N44" s="16" t="inlineStr">
+        <is>
+          <t>13:40 IST</t>
+        </is>
+      </c>
+      <c r="O44" s="16" t="n">
+        <v>57582.25</v>
+      </c>
+      <c r="P44" s="16" t="n">
+        <v>57757.85</v>
+      </c>
+      <c r="Q44" s="16" t="inlineStr">
+        <is>
+          <t>57600 PE</t>
+        </is>
+      </c>
+      <c r="R44" s="16" t="inlineStr">
+        <is>
+          <t>57400 PE</t>
+        </is>
+      </c>
+      <c r="S44" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="T44" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U44" s="16" t="n">
+        <v>480</v>
+      </c>
+      <c r="V44" s="16" t="n">
+        <v>99.23999999999999</v>
+      </c>
+      <c r="W44" s="16" t="n">
+        <v>101.13</v>
+      </c>
+      <c r="X44" s="16" t="n">
+        <v>47635.2</v>
+      </c>
+      <c r="Y44" s="16" t="n">
+        <v>47689.9</v>
+      </c>
+      <c r="Z44" s="16" t="n">
+        <v>48364.8</v>
+      </c>
+      <c r="AA44" s="16" t="n">
+        <v>14290.56</v>
+      </c>
+      <c r="AB44" s="16" t="n">
+        <v>14290.56</v>
+      </c>
+      <c r="AC44" s="16" t="n">
+        <v>907.2</v>
+      </c>
+      <c r="AD44" s="16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE44" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF44" s="16" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AG44" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH44" s="16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI44" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ44" s="16" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="AK44" s="16" t="n">
+        <v>852.5</v>
+      </c>
+      <c r="AL44" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM44" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN44" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -17761,7 +18164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN84"/>
+  <dimension ref="A1:AN86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -30388,6 +30791,310 @@
         <v>50000</v>
       </c>
       <c r="AN84" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C85" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D85" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E85" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F85" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G85" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H85" s="15" t="n">
+        <v>57691.76</v>
+      </c>
+      <c r="I85" s="15" t="n">
+        <v>57362.65</v>
+      </c>
+      <c r="J85" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K85" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L85" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="M85" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N85" s="15" t="inlineStr">
+        <is>
+          <t>10:37 IST</t>
+        </is>
+      </c>
+      <c r="O85" s="15" t="n">
+        <v>57582.25</v>
+      </c>
+      <c r="P85" s="15" t="n">
+        <v>57757.85</v>
+      </c>
+      <c r="Q85" s="15" t="inlineStr">
+        <is>
+          <t>57400 CE</t>
+        </is>
+      </c>
+      <c r="R85" s="15" t="inlineStr">
+        <is>
+          <t>57600 CE</t>
+        </is>
+      </c>
+      <c r="S85" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="T85" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U85" s="15" t="n">
+        <v>540</v>
+      </c>
+      <c r="V85" s="15" t="n">
+        <v>88.63</v>
+      </c>
+      <c r="W85" s="15" t="n">
+        <v>62.04</v>
+      </c>
+      <c r="X85" s="15" t="n">
+        <v>47860.2</v>
+      </c>
+      <c r="Y85" s="15" t="n">
+        <v>47914.93</v>
+      </c>
+      <c r="Z85" s="15" t="n">
+        <v>60139.8</v>
+      </c>
+      <c r="AA85" s="15" t="n">
+        <v>14358.06</v>
+      </c>
+      <c r="AB85" s="15" t="n">
+        <v>14358.06</v>
+      </c>
+      <c r="AC85" s="15" t="n">
+        <v>-14358.6</v>
+      </c>
+      <c r="AD85" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE85" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF85" s="15" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AG85" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH85" s="15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI85" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ85" s="15" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="AK85" s="15" t="n">
+        <v>-14413.33</v>
+      </c>
+      <c r="AL85" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM85" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN85" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B86" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C86" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D86" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E86" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F86" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G86" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H86" s="15" t="n">
+        <v>57691.76</v>
+      </c>
+      <c r="I86" s="15" t="n">
+        <v>57362.65</v>
+      </c>
+      <c r="J86" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K86" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L86" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="M86" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N86" s="15" t="inlineStr">
+        <is>
+          <t>10:37 IST</t>
+        </is>
+      </c>
+      <c r="O86" s="15" t="n">
+        <v>57582.25</v>
+      </c>
+      <c r="P86" s="15" t="n">
+        <v>57757.85</v>
+      </c>
+      <c r="Q86" s="15" t="inlineStr">
+        <is>
+          <t>57600 PE</t>
+        </is>
+      </c>
+      <c r="R86" s="15" t="inlineStr">
+        <is>
+          <t>57400 PE</t>
+        </is>
+      </c>
+      <c r="S86" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="T86" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U86" s="15" t="n">
+        <v>660</v>
+      </c>
+      <c r="V86" s="15" t="n">
+        <v>72.03</v>
+      </c>
+      <c r="W86" s="15" t="n">
+        <v>50.42</v>
+      </c>
+      <c r="X86" s="15" t="n">
+        <v>47539.8</v>
+      </c>
+      <c r="Y86" s="15" t="n">
+        <v>47594.48</v>
+      </c>
+      <c r="Z86" s="15" t="n">
+        <v>84460.2</v>
+      </c>
+      <c r="AA86" s="15" t="n">
+        <v>14261.94</v>
+      </c>
+      <c r="AB86" s="15" t="n">
+        <v>14261.94</v>
+      </c>
+      <c r="AC86" s="15" t="n">
+        <v>-14262.6</v>
+      </c>
+      <c r="AD86" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE86" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF86" s="15" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AG86" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH86" s="15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI86" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ86" s="15" t="n">
+        <v>54.68</v>
+      </c>
+      <c r="AK86" s="15" t="n">
+        <v>-14317.28</v>
+      </c>
+      <c r="AL86" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM86" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN86" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -33537,7 +34244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -34908,6 +35615,72 @@
         <v>57371.59</v>
       </c>
       <c r="G42" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E43" s="18" t="n">
+        <v>24098.67</v>
+      </c>
+      <c r="F43" s="18" t="n">
+        <v>23977.87</v>
+      </c>
+      <c r="G43" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D44" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E44" s="18" t="n">
+        <v>57691.76</v>
+      </c>
+      <c r="F44" s="18" t="n">
+        <v>57362.65</v>
+      </c>
+      <c r="G44" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -34927,7 +35700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA43"/>
+  <dimension ref="A1:AA44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -39157,6 +39930,105 @@
         <v>1000</v>
       </c>
       <c r="AA43" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="15" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G44" s="15" t="inlineStr">
+        <is>
+          <t>10:19 ET</t>
+        </is>
+      </c>
+      <c r="H44" s="15" t="n">
+        <v>29429.75</v>
+      </c>
+      <c r="I44" s="15" t="n">
+        <v>29425</v>
+      </c>
+      <c r="J44" s="15" t="n">
+        <v>29450</v>
+      </c>
+      <c r="K44" s="15" t="n">
+        <v>64</v>
+      </c>
+      <c r="L44" s="15" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="M44" s="15" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="N44" s="15" t="n">
+        <v>993.92</v>
+      </c>
+      <c r="O44" s="15" t="n">
+        <v>2311.04</v>
+      </c>
+      <c r="P44" s="15" t="n">
+        <v>266.69</v>
+      </c>
+      <c r="Q44" s="15" t="n">
+        <v>266.69</v>
+      </c>
+      <c r="R44" s="15" t="n">
+        <v>-266.88</v>
+      </c>
+      <c r="S44" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="T44" s="15" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="U44" s="15" t="n">
+        <v>64</v>
+      </c>
+      <c r="V44" s="15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="W44" s="15" t="n">
+        <v>104.96</v>
+      </c>
+      <c r="X44" s="15" t="n">
+        <v>-371.84</v>
+      </c>
+      <c r="Y44" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="Z44" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA44" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -39276,7 +40148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -42211,6 +43083,76 @@
       <c r="I84" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B85" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C85" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D85" s="19" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="E85" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="F85" s="19" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G85" s="19" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="H85" s="19" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="I85" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B86" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C86" s="19" t="n">
+        <v>64</v>
+      </c>
+      <c r="D86" s="19" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="E86" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="F86" s="19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G86" s="19" t="n">
+        <v>52.48</v>
+      </c>
+      <c r="H86" s="19" t="n">
+        <v>104.96</v>
+      </c>
+      <c r="I86" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — STOP LOSS</t>
         </is>
       </c>
     </row>
@@ -42677,7 +43619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN43"/>
+  <dimension ref="A1:AN44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -49117,6 +50059,158 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E44" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F44" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G44" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H44" s="15" t="n">
+        <v>24098.67</v>
+      </c>
+      <c r="I44" s="15" t="n">
+        <v>23977.87</v>
+      </c>
+      <c r="J44" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K44" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L44" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N44" s="15" t="inlineStr">
+        <is>
+          <t>09:47 IST</t>
+        </is>
+      </c>
+      <c r="O44" s="15" t="n">
+        <v>24072.75</v>
+      </c>
+      <c r="P44" s="15" t="n">
+        <v>24078.5</v>
+      </c>
+      <c r="Q44" s="15" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="R44" s="15" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="S44" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="T44" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U44" s="15" t="n">
+        <v>2535</v>
+      </c>
+      <c r="V44" s="15" t="n">
+        <v>18.82</v>
+      </c>
+      <c r="W44" s="15" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="X44" s="15" t="n">
+        <v>47708.7</v>
+      </c>
+      <c r="Y44" s="15" t="n">
+        <v>47763.41</v>
+      </c>
+      <c r="Z44" s="15" t="n">
+        <v>205791.3</v>
+      </c>
+      <c r="AA44" s="15" t="n">
+        <v>14312.61</v>
+      </c>
+      <c r="AB44" s="15" t="n">
+        <v>14312.61</v>
+      </c>
+      <c r="AC44" s="15" t="n">
+        <v>-14322.75</v>
+      </c>
+      <c r="AD44" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE44" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF44" s="15" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="AG44" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH44" s="15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI44" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ44" s="15" t="n">
+        <v>54.71</v>
+      </c>
+      <c r="AK44" s="15" t="n">
+        <v>-14377.46</v>
+      </c>
+      <c r="AL44" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM44" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN44" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -49131,7 +50225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN43"/>
+  <dimension ref="A1:AN44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -55571,6 +56665,158 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E44" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F44" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G44" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H44" s="16" t="n">
+        <v>24098.67</v>
+      </c>
+      <c r="I44" s="16" t="n">
+        <v>23977.87</v>
+      </c>
+      <c r="J44" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K44" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L44" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N44" s="16" t="inlineStr">
+        <is>
+          <t>15:06 IST</t>
+        </is>
+      </c>
+      <c r="O44" s="16" t="n">
+        <v>24072.75</v>
+      </c>
+      <c r="P44" s="16" t="n">
+        <v>24078.5</v>
+      </c>
+      <c r="Q44" s="16" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="R44" s="16" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="S44" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="T44" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U44" s="16" t="n">
+        <v>2600</v>
+      </c>
+      <c r="V44" s="16" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="W44" s="16" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="X44" s="16" t="n">
+        <v>47840</v>
+      </c>
+      <c r="Y44" s="16" t="n">
+        <v>47894.73</v>
+      </c>
+      <c r="Z44" s="16" t="n">
+        <v>212160</v>
+      </c>
+      <c r="AA44" s="16" t="n">
+        <v>14352</v>
+      </c>
+      <c r="AB44" s="16" t="n">
+        <v>14352</v>
+      </c>
+      <c r="AC44" s="16" t="n">
+        <v>-2080</v>
+      </c>
+      <c r="AD44" s="16" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="AE44" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF44" s="16" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AG44" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH44" s="16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI44" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ44" s="16" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="AK44" s="16" t="n">
+        <v>-2134.73</v>
+      </c>
+      <c r="AL44" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM44" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN44" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -55585,7 +56831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN84"/>
+  <dimension ref="A1:AN86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -68212,6 +69458,310 @@
         <v>50000</v>
       </c>
       <c r="AN84" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C85" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D85" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E85" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F85" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G85" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H85" s="15" t="n">
+        <v>24098.67</v>
+      </c>
+      <c r="I85" s="15" t="n">
+        <v>23977.87</v>
+      </c>
+      <c r="J85" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K85" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L85" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N85" s="15" t="inlineStr">
+        <is>
+          <t>10:30 IST</t>
+        </is>
+      </c>
+      <c r="O85" s="15" t="n">
+        <v>24072.75</v>
+      </c>
+      <c r="P85" s="15" t="n">
+        <v>24078.5</v>
+      </c>
+      <c r="Q85" s="15" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="R85" s="15" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="S85" s="15" t="n">
+        <v>44</v>
+      </c>
+      <c r="T85" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U85" s="15" t="n">
+        <v>2860</v>
+      </c>
+      <c r="V85" s="15" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="W85" s="15" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="X85" s="15" t="n">
+        <v>48105.2</v>
+      </c>
+      <c r="Y85" s="15" t="n">
+        <v>48159.97</v>
+      </c>
+      <c r="Z85" s="15" t="n">
+        <v>237894.8</v>
+      </c>
+      <c r="AA85" s="15" t="n">
+        <v>14431.56</v>
+      </c>
+      <c r="AB85" s="15" t="n">
+        <v>14431.56</v>
+      </c>
+      <c r="AC85" s="15" t="n">
+        <v>-14443</v>
+      </c>
+      <c r="AD85" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE85" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF85" s="15" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="AG85" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH85" s="15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI85" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ85" s="15" t="n">
+        <v>54.77</v>
+      </c>
+      <c r="AK85" s="15" t="n">
+        <v>-14497.77</v>
+      </c>
+      <c r="AL85" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM85" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN85" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B86" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C86" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D86" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E86" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F86" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G86" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H86" s="15" t="n">
+        <v>24098.67</v>
+      </c>
+      <c r="I86" s="15" t="n">
+        <v>23977.87</v>
+      </c>
+      <c r="J86" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K86" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L86" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N86" s="15" t="inlineStr">
+        <is>
+          <t>10:19 IST</t>
+        </is>
+      </c>
+      <c r="O86" s="15" t="n">
+        <v>24072.75</v>
+      </c>
+      <c r="P86" s="15" t="n">
+        <v>24078.5</v>
+      </c>
+      <c r="Q86" s="15" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="R86" s="15" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="S86" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="T86" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U86" s="15" t="n">
+        <v>1950</v>
+      </c>
+      <c r="V86" s="15" t="n">
+        <v>24.68</v>
+      </c>
+      <c r="W86" s="15" t="n">
+        <v>17.28</v>
+      </c>
+      <c r="X86" s="15" t="n">
+        <v>48126</v>
+      </c>
+      <c r="Y86" s="15" t="n">
+        <v>48180.77</v>
+      </c>
+      <c r="Z86" s="15" t="n">
+        <v>146874</v>
+      </c>
+      <c r="AA86" s="15" t="n">
+        <v>14437.8</v>
+      </c>
+      <c r="AB86" s="15" t="n">
+        <v>14437.8</v>
+      </c>
+      <c r="AC86" s="15" t="n">
+        <v>-14430</v>
+      </c>
+      <c r="AD86" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE86" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF86" s="15" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="AG86" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH86" s="15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI86" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ86" s="15" t="n">
+        <v>54.77</v>
+      </c>
+      <c r="AK86" s="15" t="n">
+        <v>-14484.77</v>
+      </c>
+      <c r="AL86" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM86" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN86" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA44"/>
+  <dimension ref="A1:AA45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4938,6 +4938,105 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B45" s="16" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="F45" s="16" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G45" s="16" t="inlineStr">
+        <is>
+          <t>15:47 ET</t>
+        </is>
+      </c>
+      <c r="H45" s="16" t="n">
+        <v>28739.75</v>
+      </c>
+      <c r="I45" s="16" t="n">
+        <v>28725</v>
+      </c>
+      <c r="J45" s="16" t="n">
+        <v>28750</v>
+      </c>
+      <c r="K45" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L45" s="16" t="n">
+        <v>222.31</v>
+      </c>
+      <c r="M45" s="16" t="n">
+        <v>232.82</v>
+      </c>
+      <c r="N45" s="16" t="n">
+        <v>918.84</v>
+      </c>
+      <c r="O45" s="16" t="n">
+        <v>1110.76</v>
+      </c>
+      <c r="P45" s="16" t="n">
+        <v>266.77</v>
+      </c>
+      <c r="Q45" s="16" t="n">
+        <v>266.77</v>
+      </c>
+      <c r="R45" s="16" t="n">
+        <v>42.04</v>
+      </c>
+      <c r="S45" s="16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T45" s="16" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="U45" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="V45" s="16" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W45" s="16" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="X45" s="16" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="Y45" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="Z45" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA45" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -4952,7 +5051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN44"/>
+  <dimension ref="A1:AN45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11544,6 +11643,158 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B45" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E45" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F45" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G45" s="16" t="inlineStr">
+        <is>
+          <t>Price↑(58085.9&gt;57582.25) &amp; EMA9↑(57770.23&gt;57460.96)</t>
+        </is>
+      </c>
+      <c r="H45" s="16" t="n">
+        <v>57770.23</v>
+      </c>
+      <c r="I45" s="16" t="n">
+        <v>57460.96</v>
+      </c>
+      <c r="J45" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K45" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L45" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="M45" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N45" s="16" t="inlineStr">
+        <is>
+          <t>14:23 IST</t>
+        </is>
+      </c>
+      <c r="O45" s="16" t="n">
+        <v>58085.9</v>
+      </c>
+      <c r="P45" s="16" t="n">
+        <v>57582.25</v>
+      </c>
+      <c r="Q45" s="16" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="R45" s="16" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="S45" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T45" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U45" s="16" t="n">
+        <v>600</v>
+      </c>
+      <c r="V45" s="16" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="W45" s="16" t="n">
+        <v>83.28</v>
+      </c>
+      <c r="X45" s="16" t="n">
+        <v>49020</v>
+      </c>
+      <c r="Y45" s="16" t="n">
+        <v>49074.91</v>
+      </c>
+      <c r="Z45" s="16" t="n">
+        <v>70980</v>
+      </c>
+      <c r="AA45" s="16" t="n">
+        <v>14706</v>
+      </c>
+      <c r="AB45" s="16" t="n">
+        <v>14706</v>
+      </c>
+      <c r="AC45" s="16" t="n">
+        <v>948</v>
+      </c>
+      <c r="AD45" s="16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE45" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF45" s="16" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="AG45" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH45" s="16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI45" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ45" s="16" t="n">
+        <v>54.91</v>
+      </c>
+      <c r="AK45" s="16" t="n">
+        <v>893.09</v>
+      </c>
+      <c r="AL45" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM45" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN45" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -11558,7 +11809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN44"/>
+  <dimension ref="A1:AN45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18150,6 +18401,158 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C45" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D45" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E45" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F45" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(58085.9&gt;57582.25) &amp; EMA9↑(57770.23&gt;57460.96)</t>
+        </is>
+      </c>
+      <c r="H45" s="17" t="n">
+        <v>57770.23</v>
+      </c>
+      <c r="I45" s="17" t="n">
+        <v>57460.96</v>
+      </c>
+      <c r="J45" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K45" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L45" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="M45" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N45" s="17" t="inlineStr">
+        <is>
+          <t>11:01 IST</t>
+        </is>
+      </c>
+      <c r="O45" s="17" t="n">
+        <v>58085.9</v>
+      </c>
+      <c r="P45" s="17" t="n">
+        <v>57582.25</v>
+      </c>
+      <c r="Q45" s="17" t="inlineStr">
+        <is>
+          <t>58200 PE</t>
+        </is>
+      </c>
+      <c r="R45" s="17" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="S45" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="T45" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U45" s="17" t="n">
+        <v>570</v>
+      </c>
+      <c r="V45" s="17" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="W45" s="17" t="n">
+        <v>109.71</v>
+      </c>
+      <c r="X45" s="17" t="n">
+        <v>48102.3</v>
+      </c>
+      <c r="Y45" s="17" t="n">
+        <v>48157.07</v>
+      </c>
+      <c r="Z45" s="17" t="n">
+        <v>65897.7</v>
+      </c>
+      <c r="AA45" s="17" t="n">
+        <v>14430.69</v>
+      </c>
+      <c r="AB45" s="17" t="n">
+        <v>14430.69</v>
+      </c>
+      <c r="AC45" s="17" t="n">
+        <v>14432.4</v>
+      </c>
+      <c r="AD45" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE45" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF45" s="17" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="AG45" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH45" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI45" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ45" s="17" t="n">
+        <v>54.77</v>
+      </c>
+      <c r="AK45" s="17" t="n">
+        <v>14377.63</v>
+      </c>
+      <c r="AL45" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM45" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN45" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -18164,7 +18567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN86"/>
+  <dimension ref="A1:AN88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -31100,6 +31503,310 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B87" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C87" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D87" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E87" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F87" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G87" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(58085.9&gt;57582.25) &amp; EMA9↑(57770.23&gt;57460.96)</t>
+        </is>
+      </c>
+      <c r="H87" s="17" t="n">
+        <v>57770.23</v>
+      </c>
+      <c r="I87" s="17" t="n">
+        <v>57460.96</v>
+      </c>
+      <c r="J87" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K87" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L87" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="M87" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N87" s="17" t="inlineStr">
+        <is>
+          <t>10:50 IST</t>
+        </is>
+      </c>
+      <c r="O87" s="17" t="n">
+        <v>58085.9</v>
+      </c>
+      <c r="P87" s="17" t="n">
+        <v>57582.25</v>
+      </c>
+      <c r="Q87" s="17" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="R87" s="17" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="S87" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="T87" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U87" s="17" t="n">
+        <v>570</v>
+      </c>
+      <c r="V87" s="17" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="W87" s="17" t="n">
+        <v>107.64</v>
+      </c>
+      <c r="X87" s="17" t="n">
+        <v>47196</v>
+      </c>
+      <c r="Y87" s="17" t="n">
+        <v>47250.63</v>
+      </c>
+      <c r="Z87" s="17" t="n">
+        <v>66804</v>
+      </c>
+      <c r="AA87" s="17" t="n">
+        <v>14158.8</v>
+      </c>
+      <c r="AB87" s="17" t="n">
+        <v>14158.8</v>
+      </c>
+      <c r="AC87" s="17" t="n">
+        <v>14158.8</v>
+      </c>
+      <c r="AD87" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE87" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF87" s="17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AG87" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH87" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI87" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ87" s="17" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="AK87" s="17" t="n">
+        <v>14104.17</v>
+      </c>
+      <c r="AL87" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM87" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN87" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B88" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C88" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D88" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E88" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F88" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G88" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(58085.9&gt;57582.25) &amp; EMA9↑(57770.23&gt;57460.96)</t>
+        </is>
+      </c>
+      <c r="H88" s="15" t="n">
+        <v>57770.23</v>
+      </c>
+      <c r="I88" s="15" t="n">
+        <v>57460.96</v>
+      </c>
+      <c r="J88" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K88" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L88" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="M88" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N88" s="15" t="inlineStr">
+        <is>
+          <t>09:32 IST</t>
+        </is>
+      </c>
+      <c r="O88" s="15" t="n">
+        <v>58085.9</v>
+      </c>
+      <c r="P88" s="15" t="n">
+        <v>57582.25</v>
+      </c>
+      <c r="Q88" s="15" t="inlineStr">
+        <is>
+          <t>58200 PE</t>
+        </is>
+      </c>
+      <c r="R88" s="15" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="S88" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="T88" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U88" s="15" t="n">
+        <v>630</v>
+      </c>
+      <c r="V88" s="15" t="n">
+        <v>76.81999999999999</v>
+      </c>
+      <c r="W88" s="15" t="n">
+        <v>53.77</v>
+      </c>
+      <c r="X88" s="15" t="n">
+        <v>48396.6</v>
+      </c>
+      <c r="Y88" s="15" t="n">
+        <v>48451.42</v>
+      </c>
+      <c r="Z88" s="15" t="n">
+        <v>77603.39999999999</v>
+      </c>
+      <c r="AA88" s="15" t="n">
+        <v>14518.98</v>
+      </c>
+      <c r="AB88" s="15" t="n">
+        <v>14518.98</v>
+      </c>
+      <c r="AC88" s="15" t="n">
+        <v>-14521.5</v>
+      </c>
+      <c r="AD88" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE88" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF88" s="15" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AG88" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH88" s="15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI88" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ88" s="15" t="n">
+        <v>54.82</v>
+      </c>
+      <c r="AK88" s="15" t="n">
+        <v>-14576.32</v>
+      </c>
+      <c r="AL88" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM88" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN88" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -31114,7 +31821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN21"/>
+  <dimension ref="A1:AN22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -34230,6 +34937,158 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G22" s="16" t="inlineStr">
+        <is>
+          <t>Price↑(58085.9&gt;57582.25) &amp; EMA9↑(57770.23&gt;57460.96)</t>
+        </is>
+      </c>
+      <c r="H22" s="16" t="n">
+        <v>57770.23</v>
+      </c>
+      <c r="I22" s="16" t="n">
+        <v>57460.96</v>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K22" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L22" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="M22" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N22" s="16" t="inlineStr">
+        <is>
+          <t>14:52 IST</t>
+        </is>
+      </c>
+      <c r="O22" s="16" t="n">
+        <v>58085.9</v>
+      </c>
+      <c r="P22" s="16" t="n">
+        <v>57582.25</v>
+      </c>
+      <c r="Q22" s="16" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="R22" s="16" t="inlineStr">
+        <is>
+          <t>58200 CE</t>
+        </is>
+      </c>
+      <c r="S22" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="T22" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U22" s="16" t="n">
+        <v>630</v>
+      </c>
+      <c r="V22" s="16" t="n">
+        <v>77.33</v>
+      </c>
+      <c r="W22" s="16" t="n">
+        <v>75.70999999999999</v>
+      </c>
+      <c r="X22" s="16" t="n">
+        <v>48717.9</v>
+      </c>
+      <c r="Y22" s="16" t="n">
+        <v>48772.77</v>
+      </c>
+      <c r="Z22" s="16" t="n">
+        <v>77282.10000000001</v>
+      </c>
+      <c r="AA22" s="16" t="n">
+        <v>14615.37</v>
+      </c>
+      <c r="AB22" s="16" t="n">
+        <v>14615.37</v>
+      </c>
+      <c r="AC22" s="16" t="n">
+        <v>-1020.6</v>
+      </c>
+      <c r="AD22" s="16" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="AE22" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF22" s="16" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="AG22" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH22" s="16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI22" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ22" s="16" t="n">
+        <v>54.87</v>
+      </c>
+      <c r="AK22" s="16" t="n">
+        <v>-1075.47</v>
+      </c>
+      <c r="AL22" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM22" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN22" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -35700,7 +36559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA44"/>
+  <dimension ref="A1:AA45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -40029,6 +40888,105 @@
         <v>1000</v>
       </c>
       <c r="AA44" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C45" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D45" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="F45" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="inlineStr">
+        <is>
+          <t>11:08 ET</t>
+        </is>
+      </c>
+      <c r="H45" s="17" t="n">
+        <v>28740.25</v>
+      </c>
+      <c r="I45" s="17" t="n">
+        <v>28725</v>
+      </c>
+      <c r="J45" s="17" t="n">
+        <v>28750</v>
+      </c>
+      <c r="K45" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="L45" s="17" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="M45" s="17" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="N45" s="17" t="n">
+        <v>982.72</v>
+      </c>
+      <c r="O45" s="17" t="n">
+        <v>927.96</v>
+      </c>
+      <c r="P45" s="17" t="n">
+        <v>276.61</v>
+      </c>
+      <c r="Q45" s="17" t="n">
+        <v>276.61</v>
+      </c>
+      <c r="R45" s="17" t="n">
+        <v>276.76</v>
+      </c>
+      <c r="S45" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T45" s="17" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="U45" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="V45" s="17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W45" s="17" t="n">
+        <v>60.68</v>
+      </c>
+      <c r="X45" s="17" t="n">
+        <v>216.08</v>
+      </c>
+      <c r="Y45" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z45" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA45" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -40148,7 +41106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -43153,6 +44111,76 @@
       <c r="I86" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — STOP LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B87" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C87" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D87" s="19" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="E87" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F87" s="19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G87" s="19" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H87" s="19" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I87" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B88" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C88" s="19" t="n">
+        <v>37</v>
+      </c>
+      <c r="D88" s="19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E88" s="19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F88" s="19" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G88" s="19" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="H88" s="19" t="n">
+        <v>60.68</v>
+      </c>
+      <c r="I88" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — PROFIT</t>
         </is>
       </c>
     </row>
@@ -43619,7 +44647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN44"/>
+  <dimension ref="A1:AN45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -50211,6 +51239,158 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G45" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(24255.3&gt;24072.75) &amp; EMA9↑(24129.52&gt;24002.12)</t>
+        </is>
+      </c>
+      <c r="H45" s="15" t="n">
+        <v>24129.52</v>
+      </c>
+      <c r="I45" s="15" t="n">
+        <v>24002.12</v>
+      </c>
+      <c r="J45" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K45" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L45" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="M45" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N45" s="15" t="inlineStr">
+        <is>
+          <t>11:09 IST</t>
+        </is>
+      </c>
+      <c r="O45" s="15" t="n">
+        <v>24255.3</v>
+      </c>
+      <c r="P45" s="15" t="n">
+        <v>24072.75</v>
+      </c>
+      <c r="Q45" s="15" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="R45" s="15" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="S45" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U45" s="15" t="n">
+        <v>1625</v>
+      </c>
+      <c r="V45" s="15" t="n">
+        <v>29.35</v>
+      </c>
+      <c r="W45" s="15" t="n">
+        <v>20.54</v>
+      </c>
+      <c r="X45" s="15" t="n">
+        <v>47693.75</v>
+      </c>
+      <c r="Y45" s="15" t="n">
+        <v>47748.46</v>
+      </c>
+      <c r="Z45" s="15" t="n">
+        <v>114806.25</v>
+      </c>
+      <c r="AA45" s="15" t="n">
+        <v>14308.12</v>
+      </c>
+      <c r="AB45" s="15" t="n">
+        <v>14308.12</v>
+      </c>
+      <c r="AC45" s="15" t="n">
+        <v>-14316.25</v>
+      </c>
+      <c r="AD45" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE45" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF45" s="15" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="AG45" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH45" s="15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI45" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ45" s="15" t="n">
+        <v>54.71</v>
+      </c>
+      <c r="AK45" s="15" t="n">
+        <v>-14370.96</v>
+      </c>
+      <c r="AL45" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM45" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN45" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -50225,7 +51405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN44"/>
+  <dimension ref="A1:AN45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -56817,6 +57997,158 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C45" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D45" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E45" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F45" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24255.3&gt;24072.75) &amp; EMA9↑(24129.52&gt;24002.12)</t>
+        </is>
+      </c>
+      <c r="H45" s="17" t="n">
+        <v>24129.52</v>
+      </c>
+      <c r="I45" s="17" t="n">
+        <v>24002.12</v>
+      </c>
+      <c r="J45" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K45" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L45" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M45" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N45" s="17" t="inlineStr">
+        <is>
+          <t>10:48 IST</t>
+        </is>
+      </c>
+      <c r="O45" s="17" t="n">
+        <v>24255.3</v>
+      </c>
+      <c r="P45" s="17" t="n">
+        <v>24072.75</v>
+      </c>
+      <c r="Q45" s="17" t="inlineStr">
+        <is>
+          <t>24300 PE</t>
+        </is>
+      </c>
+      <c r="R45" s="17" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="S45" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T45" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U45" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="V45" s="17" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="W45" s="17" t="n">
+        <v>49.05</v>
+      </c>
+      <c r="X45" s="17" t="n">
+        <v>49049</v>
+      </c>
+      <c r="Y45" s="17" t="n">
+        <v>49103.92</v>
+      </c>
+      <c r="Z45" s="17" t="n">
+        <v>80951</v>
+      </c>
+      <c r="AA45" s="17" t="n">
+        <v>14714.7</v>
+      </c>
+      <c r="AB45" s="17" t="n">
+        <v>14714.7</v>
+      </c>
+      <c r="AC45" s="17" t="n">
+        <v>14716</v>
+      </c>
+      <c r="AD45" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE45" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF45" s="17" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="AG45" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH45" s="17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI45" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ45" s="17" t="n">
+        <v>54.92</v>
+      </c>
+      <c r="AK45" s="17" t="n">
+        <v>14661.08</v>
+      </c>
+      <c r="AL45" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM45" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN45" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -56831,7 +58163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN86"/>
+  <dimension ref="A1:AN88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -69767,6 +71099,310 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B87" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C87" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D87" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E87" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F87" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G87" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24255.3&gt;24072.75) &amp; EMA9↑(24129.52&gt;24002.12)</t>
+        </is>
+      </c>
+      <c r="H87" s="17" t="n">
+        <v>24129.52</v>
+      </c>
+      <c r="I87" s="17" t="n">
+        <v>24002.12</v>
+      </c>
+      <c r="J87" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K87" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L87" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M87" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N87" s="17" t="inlineStr">
+        <is>
+          <t>09:45 IST</t>
+        </is>
+      </c>
+      <c r="O87" s="17" t="n">
+        <v>24255.3</v>
+      </c>
+      <c r="P87" s="17" t="n">
+        <v>24072.75</v>
+      </c>
+      <c r="Q87" s="17" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="R87" s="17" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="S87" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T87" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U87" s="17" t="n">
+        <v>1625</v>
+      </c>
+      <c r="V87" s="17" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="W87" s="17" t="n">
+        <v>38.61</v>
+      </c>
+      <c r="X87" s="17" t="n">
+        <v>48262.5</v>
+      </c>
+      <c r="Y87" s="17" t="n">
+        <v>48317.29</v>
+      </c>
+      <c r="Z87" s="17" t="n">
+        <v>114237.5</v>
+      </c>
+      <c r="AA87" s="17" t="n">
+        <v>14478.75</v>
+      </c>
+      <c r="AB87" s="17" t="n">
+        <v>14478.75</v>
+      </c>
+      <c r="AC87" s="17" t="n">
+        <v>14478.75</v>
+      </c>
+      <c r="AD87" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE87" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF87" s="17" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AG87" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH87" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI87" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ87" s="17" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="AK87" s="17" t="n">
+        <v>14423.96</v>
+      </c>
+      <c r="AL87" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM87" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN87" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B88" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C88" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D88" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E88" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F88" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G88" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24255.3&gt;24072.75) &amp; EMA9↑(24129.52&gt;24002.12)</t>
+        </is>
+      </c>
+      <c r="H88" s="17" t="n">
+        <v>24129.52</v>
+      </c>
+      <c r="I88" s="17" t="n">
+        <v>24002.12</v>
+      </c>
+      <c r="J88" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K88" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L88" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M88" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N88" s="17" t="inlineStr">
+        <is>
+          <t>11:12 IST</t>
+        </is>
+      </c>
+      <c r="O88" s="17" t="n">
+        <v>24255.3</v>
+      </c>
+      <c r="P88" s="17" t="n">
+        <v>24072.75</v>
+      </c>
+      <c r="Q88" s="17" t="inlineStr">
+        <is>
+          <t>24300 PE</t>
+        </is>
+      </c>
+      <c r="R88" s="17" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="S88" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="T88" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U88" s="17" t="n">
+        <v>1495</v>
+      </c>
+      <c r="V88" s="17" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="W88" s="17" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="X88" s="17" t="n">
+        <v>47286.85</v>
+      </c>
+      <c r="Y88" s="17" t="n">
+        <v>47341.49</v>
+      </c>
+      <c r="Z88" s="17" t="n">
+        <v>102213.15</v>
+      </c>
+      <c r="AA88" s="17" t="n">
+        <v>14186.05</v>
+      </c>
+      <c r="AB88" s="17" t="n">
+        <v>14186.05</v>
+      </c>
+      <c r="AC88" s="17" t="n">
+        <v>14187.55</v>
+      </c>
+      <c r="AD88" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE88" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF88" s="17" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AG88" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH88" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI88" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ88" s="17" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="AK88" s="17" t="n">
+        <v>14132.91</v>
+      </c>
+      <c r="AL88" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM88" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN88" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -69781,7 +71417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN25"/>
+  <dimension ref="A1:AN26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -73510,6 +75146,158 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G26" s="16" t="inlineStr">
+        <is>
+          <t>Price↑(24255.3&gt;24072.75) &amp; EMA9↑(24129.52&gt;24002.12)</t>
+        </is>
+      </c>
+      <c r="H26" s="16" t="n">
+        <v>24129.52</v>
+      </c>
+      <c r="I26" s="16" t="n">
+        <v>24002.12</v>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K26" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L26" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="M26" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N26" s="16" t="inlineStr">
+        <is>
+          <t>14:01 IST</t>
+        </is>
+      </c>
+      <c r="O26" s="16" t="n">
+        <v>24255.3</v>
+      </c>
+      <c r="P26" s="16" t="n">
+        <v>24072.75</v>
+      </c>
+      <c r="Q26" s="16" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="R26" s="16" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="S26" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="T26" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U26" s="16" t="n">
+        <v>1495</v>
+      </c>
+      <c r="V26" s="16" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="W26" s="16" t="n">
+        <v>32.58</v>
+      </c>
+      <c r="X26" s="16" t="n">
+        <v>47720.4</v>
+      </c>
+      <c r="Y26" s="16" t="n">
+        <v>47775.11</v>
+      </c>
+      <c r="Z26" s="16" t="n">
+        <v>101779.6</v>
+      </c>
+      <c r="AA26" s="16" t="n">
+        <v>14316.12</v>
+      </c>
+      <c r="AB26" s="16" t="n">
+        <v>14316.12</v>
+      </c>
+      <c r="AC26" s="16" t="n">
+        <v>986.7</v>
+      </c>
+      <c r="AD26" s="16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE26" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF26" s="16" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="AG26" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH26" s="16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI26" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ26" s="16" t="n">
+        <v>54.71</v>
+      </c>
+      <c r="AK26" s="16" t="n">
+        <v>931.99</v>
+      </c>
+      <c r="AL26" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM26" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN26" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA45"/>
+  <dimension ref="A1:AA46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5037,6 +5037,105 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D46" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G46" s="17" t="inlineStr">
+        <is>
+          <t>13:47 ET</t>
+        </is>
+      </c>
+      <c r="H46" s="17" t="n">
+        <v>28698.25</v>
+      </c>
+      <c r="I46" s="17" t="n">
+        <v>28675</v>
+      </c>
+      <c r="J46" s="17" t="n">
+        <v>28700</v>
+      </c>
+      <c r="K46" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L46" s="17" t="n">
+        <v>214.06</v>
+      </c>
+      <c r="M46" s="17" t="n">
+        <v>278.28</v>
+      </c>
+      <c r="N46" s="17" t="n">
+        <v>885.84</v>
+      </c>
+      <c r="O46" s="17" t="n">
+        <v>1143.76</v>
+      </c>
+      <c r="P46" s="17" t="n">
+        <v>256.87</v>
+      </c>
+      <c r="Q46" s="17" t="n">
+        <v>256.87</v>
+      </c>
+      <c r="R46" s="17" t="n">
+        <v>256.88</v>
+      </c>
+      <c r="S46" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T46" s="17" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="U46" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="V46" s="17" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W46" s="17" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="X46" s="17" t="n">
+        <v>227.28</v>
+      </c>
+      <c r="Y46" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z46" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA46" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -5051,7 +5150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN45"/>
+  <dimension ref="A1:AN46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11795,6 +11894,158 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D46" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E46" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G46" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(58521.4&gt;57582.25) &amp; EMA9↑(57857.33&gt;57500.55)</t>
+        </is>
+      </c>
+      <c r="H46" s="17" t="n">
+        <v>57857.33</v>
+      </c>
+      <c r="I46" s="17" t="n">
+        <v>57500.55</v>
+      </c>
+      <c r="J46" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K46" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L46" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="M46" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N46" s="17" t="inlineStr">
+        <is>
+          <t>12:05 IST</t>
+        </is>
+      </c>
+      <c r="O46" s="17" t="n">
+        <v>58521.4</v>
+      </c>
+      <c r="P46" s="17" t="n">
+        <v>57582.25</v>
+      </c>
+      <c r="Q46" s="17" t="inlineStr">
+        <is>
+          <t>58400 CE</t>
+        </is>
+      </c>
+      <c r="R46" s="17" t="inlineStr">
+        <is>
+          <t>58600 CE</t>
+        </is>
+      </c>
+      <c r="S46" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="T46" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U46" s="17" t="n">
+        <v>480</v>
+      </c>
+      <c r="V46" s="17" t="n">
+        <v>97.09</v>
+      </c>
+      <c r="W46" s="17" t="n">
+        <v>126.22</v>
+      </c>
+      <c r="X46" s="17" t="n">
+        <v>46603.2</v>
+      </c>
+      <c r="Y46" s="17" t="n">
+        <v>46657.73</v>
+      </c>
+      <c r="Z46" s="17" t="n">
+        <v>49396.8</v>
+      </c>
+      <c r="AA46" s="17" t="n">
+        <v>13980.96</v>
+      </c>
+      <c r="AB46" s="17" t="n">
+        <v>13980.96</v>
+      </c>
+      <c r="AC46" s="17" t="n">
+        <v>13982.4</v>
+      </c>
+      <c r="AD46" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE46" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF46" s="17" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="AG46" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH46" s="17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI46" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ46" s="17" t="n">
+        <v>54.53</v>
+      </c>
+      <c r="AK46" s="17" t="n">
+        <v>13927.87</v>
+      </c>
+      <c r="AL46" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM46" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN46" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -11809,7 +12060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN45"/>
+  <dimension ref="A1:AN46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18553,6 +18804,158 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D46" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E46" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G46" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(58521.4&gt;57582.25) &amp; EMA9↑(57857.33&gt;57500.55)</t>
+        </is>
+      </c>
+      <c r="H46" s="17" t="n">
+        <v>57857.33</v>
+      </c>
+      <c r="I46" s="17" t="n">
+        <v>57500.55</v>
+      </c>
+      <c r="J46" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K46" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L46" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="M46" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N46" s="17" t="inlineStr">
+        <is>
+          <t>09:47 IST</t>
+        </is>
+      </c>
+      <c r="O46" s="17" t="n">
+        <v>58521.4</v>
+      </c>
+      <c r="P46" s="17" t="n">
+        <v>57582.25</v>
+      </c>
+      <c r="Q46" s="17" t="inlineStr">
+        <is>
+          <t>58600 PE</t>
+        </is>
+      </c>
+      <c r="R46" s="17" t="inlineStr">
+        <is>
+          <t>58400 PE</t>
+        </is>
+      </c>
+      <c r="S46" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="T46" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U46" s="17" t="n">
+        <v>510</v>
+      </c>
+      <c r="V46" s="17" t="n">
+        <v>94.04000000000001</v>
+      </c>
+      <c r="W46" s="17" t="n">
+        <v>122.25</v>
+      </c>
+      <c r="X46" s="17" t="n">
+        <v>47960.4</v>
+      </c>
+      <c r="Y46" s="17" t="n">
+        <v>48015.15</v>
+      </c>
+      <c r="Z46" s="17" t="n">
+        <v>54039.6</v>
+      </c>
+      <c r="AA46" s="17" t="n">
+        <v>14388.12</v>
+      </c>
+      <c r="AB46" s="17" t="n">
+        <v>14388.12</v>
+      </c>
+      <c r="AC46" s="17" t="n">
+        <v>14387.1</v>
+      </c>
+      <c r="AD46" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE46" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF46" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG46" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH46" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI46" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ46" s="17" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="AK46" s="17" t="n">
+        <v>14332.35</v>
+      </c>
+      <c r="AL46" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM46" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN46" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -18567,7 +18970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN88"/>
+  <dimension ref="A1:AN90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -31807,6 +32210,310 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B89" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C89" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D89" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E89" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F89" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G89" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(58521.4&gt;57582.25) &amp; EMA9↑(57857.33&gt;57500.55)</t>
+        </is>
+      </c>
+      <c r="H89" s="17" t="n">
+        <v>57857.33</v>
+      </c>
+      <c r="I89" s="17" t="n">
+        <v>57500.55</v>
+      </c>
+      <c r="J89" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K89" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L89" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="M89" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N89" s="17" t="inlineStr">
+        <is>
+          <t>09:49 IST</t>
+        </is>
+      </c>
+      <c r="O89" s="17" t="n">
+        <v>58521.4</v>
+      </c>
+      <c r="P89" s="17" t="n">
+        <v>57582.25</v>
+      </c>
+      <c r="Q89" s="17" t="inlineStr">
+        <is>
+          <t>58400 CE</t>
+        </is>
+      </c>
+      <c r="R89" s="17" t="inlineStr">
+        <is>
+          <t>58600 CE</t>
+        </is>
+      </c>
+      <c r="S89" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="T89" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U89" s="17" t="n">
+        <v>540</v>
+      </c>
+      <c r="V89" s="17" t="n">
+        <v>87.98999999999999</v>
+      </c>
+      <c r="W89" s="17" t="n">
+        <v>114.39</v>
+      </c>
+      <c r="X89" s="17" t="n">
+        <v>47514.6</v>
+      </c>
+      <c r="Y89" s="17" t="n">
+        <v>47569.28</v>
+      </c>
+      <c r="Z89" s="17" t="n">
+        <v>60485.4</v>
+      </c>
+      <c r="AA89" s="17" t="n">
+        <v>14254.38</v>
+      </c>
+      <c r="AB89" s="17" t="n">
+        <v>14254.38</v>
+      </c>
+      <c r="AC89" s="17" t="n">
+        <v>14256</v>
+      </c>
+      <c r="AD89" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE89" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF89" s="17" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AG89" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH89" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI89" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ89" s="17" t="n">
+        <v>54.68</v>
+      </c>
+      <c r="AK89" s="17" t="n">
+        <v>14201.32</v>
+      </c>
+      <c r="AL89" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM89" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN89" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B90" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C90" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D90" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E90" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F90" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G90" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(58521.4&gt;57582.25) &amp; EMA9↑(57857.33&gt;57500.55)</t>
+        </is>
+      </c>
+      <c r="H90" s="17" t="n">
+        <v>57857.33</v>
+      </c>
+      <c r="I90" s="17" t="n">
+        <v>57500.55</v>
+      </c>
+      <c r="J90" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K90" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L90" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="M90" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N90" s="17" t="inlineStr">
+        <is>
+          <t>11:55 IST</t>
+        </is>
+      </c>
+      <c r="O90" s="17" t="n">
+        <v>58521.4</v>
+      </c>
+      <c r="P90" s="17" t="n">
+        <v>57582.25</v>
+      </c>
+      <c r="Q90" s="17" t="inlineStr">
+        <is>
+          <t>58600 PE</t>
+        </is>
+      </c>
+      <c r="R90" s="17" t="inlineStr">
+        <is>
+          <t>58400 PE</t>
+        </is>
+      </c>
+      <c r="S90" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="T90" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U90" s="17" t="n">
+        <v>660</v>
+      </c>
+      <c r="V90" s="17" t="n">
+        <v>72.06999999999999</v>
+      </c>
+      <c r="W90" s="17" t="n">
+        <v>93.69</v>
+      </c>
+      <c r="X90" s="17" t="n">
+        <v>47566.2</v>
+      </c>
+      <c r="Y90" s="17" t="n">
+        <v>47620.89</v>
+      </c>
+      <c r="Z90" s="17" t="n">
+        <v>84433.8</v>
+      </c>
+      <c r="AA90" s="17" t="n">
+        <v>14269.86</v>
+      </c>
+      <c r="AB90" s="17" t="n">
+        <v>14269.86</v>
+      </c>
+      <c r="AC90" s="17" t="n">
+        <v>14269.2</v>
+      </c>
+      <c r="AD90" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE90" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF90" s="17" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AG90" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH90" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI90" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ90" s="17" t="n">
+        <v>54.69</v>
+      </c>
+      <c r="AK90" s="17" t="n">
+        <v>14214.51</v>
+      </c>
+      <c r="AL90" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM90" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN90" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -31821,7 +32528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN22"/>
+  <dimension ref="A1:AN23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -35089,6 +35796,158 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(58521.4&gt;57582.25) &amp; EMA9↑(57857.33&gt;57500.55)</t>
+        </is>
+      </c>
+      <c r="H23" s="17" t="n">
+        <v>57857.33</v>
+      </c>
+      <c r="I23" s="17" t="n">
+        <v>57500.55</v>
+      </c>
+      <c r="J23" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K23" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L23" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="M23" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N23" s="17" t="inlineStr">
+        <is>
+          <t>10:26 IST</t>
+        </is>
+      </c>
+      <c r="O23" s="17" t="n">
+        <v>58521.4</v>
+      </c>
+      <c r="P23" s="17" t="n">
+        <v>57582.25</v>
+      </c>
+      <c r="Q23" s="17" t="inlineStr">
+        <is>
+          <t>58400 CE</t>
+        </is>
+      </c>
+      <c r="R23" s="17" t="inlineStr">
+        <is>
+          <t>58600 CE</t>
+        </is>
+      </c>
+      <c r="S23" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="T23" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U23" s="17" t="n">
+        <v>540</v>
+      </c>
+      <c r="V23" s="17" t="n">
+        <v>88.33</v>
+      </c>
+      <c r="W23" s="17" t="n">
+        <v>114.83</v>
+      </c>
+      <c r="X23" s="17" t="n">
+        <v>47698.2</v>
+      </c>
+      <c r="Y23" s="17" t="n">
+        <v>47752.91</v>
+      </c>
+      <c r="Z23" s="17" t="n">
+        <v>60301.8</v>
+      </c>
+      <c r="AA23" s="17" t="n">
+        <v>14309.46</v>
+      </c>
+      <c r="AB23" s="17" t="n">
+        <v>14309.46</v>
+      </c>
+      <c r="AC23" s="17" t="n">
+        <v>14310</v>
+      </c>
+      <c r="AD23" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE23" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF23" s="17" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="AG23" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH23" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI23" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ23" s="17" t="n">
+        <v>54.71</v>
+      </c>
+      <c r="AK23" s="17" t="n">
+        <v>14255.29</v>
+      </c>
+      <c r="AL23" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM23" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN23" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -36559,7 +37418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA45"/>
+  <dimension ref="A1:AA46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -40987,6 +41846,105 @@
         <v>1000</v>
       </c>
       <c r="AA45" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D46" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E46" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="F46" s="16" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G46" s="16" t="inlineStr">
+        <is>
+          <t>15:23 ET</t>
+        </is>
+      </c>
+      <c r="H46" s="16" t="n">
+        <v>28699</v>
+      </c>
+      <c r="I46" s="16" t="n">
+        <v>28675</v>
+      </c>
+      <c r="J46" s="16" t="n">
+        <v>28700</v>
+      </c>
+      <c r="K46" s="16" t="n">
+        <v>39</v>
+      </c>
+      <c r="L46" s="16" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="M46" s="16" t="n">
+        <v>24.11</v>
+      </c>
+      <c r="N46" s="16" t="n">
+        <v>975.78</v>
+      </c>
+      <c r="O46" s="16" t="n">
+        <v>1038.18</v>
+      </c>
+      <c r="P46" s="16" t="n">
+        <v>273.55</v>
+      </c>
+      <c r="Q46" s="16" t="n">
+        <v>273.55</v>
+      </c>
+      <c r="R46" s="16" t="n">
+        <v>28.47</v>
+      </c>
+      <c r="S46" s="16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T46" s="16" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="U46" s="16" t="n">
+        <v>39</v>
+      </c>
+      <c r="V46" s="16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W46" s="16" t="n">
+        <v>63.96</v>
+      </c>
+      <c r="X46" s="16" t="n">
+        <v>-35.49</v>
+      </c>
+      <c r="Y46" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="Z46" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA46" s="16" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -41106,7 +42064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -44181,6 +45139,76 @@
       <c r="I88" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B89" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C89" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D89" s="19" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="E89" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F89" s="19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G89" s="19" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H89" s="19" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I89" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B90" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C90" s="19" t="n">
+        <v>39</v>
+      </c>
+      <c r="D90" s="19" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="E90" s="19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F90" s="19" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G90" s="19" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="H90" s="19" t="n">
+        <v>63.96</v>
+      </c>
+      <c r="I90" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — FLAT</t>
         </is>
       </c>
     </row>
@@ -44647,7 +45675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN45"/>
+  <dimension ref="A1:AN46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -51391,6 +52419,158 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D46" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E46" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G46" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24334.3&gt;24072.75) &amp; EMA9↑(24145.32&gt;24009.3)</t>
+        </is>
+      </c>
+      <c r="H46" s="17" t="n">
+        <v>24145.32</v>
+      </c>
+      <c r="I46" s="17" t="n">
+        <v>24009.3</v>
+      </c>
+      <c r="J46" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K46" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L46" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M46" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N46" s="17" t="inlineStr">
+        <is>
+          <t>10:51 IST</t>
+        </is>
+      </c>
+      <c r="O46" s="17" t="n">
+        <v>24334.3</v>
+      </c>
+      <c r="P46" s="17" t="n">
+        <v>24072.75</v>
+      </c>
+      <c r="Q46" s="17" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="R46" s="17" t="inlineStr">
+        <is>
+          <t>24400 CE</t>
+        </is>
+      </c>
+      <c r="S46" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="T46" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U46" s="17" t="n">
+        <v>1690</v>
+      </c>
+      <c r="V46" s="17" t="n">
+        <v>28.42</v>
+      </c>
+      <c r="W46" s="17" t="n">
+        <v>36.95</v>
+      </c>
+      <c r="X46" s="17" t="n">
+        <v>48029.8</v>
+      </c>
+      <c r="Y46" s="17" t="n">
+        <v>48084.56</v>
+      </c>
+      <c r="Z46" s="17" t="n">
+        <v>120970.2</v>
+      </c>
+      <c r="AA46" s="17" t="n">
+        <v>14408.94</v>
+      </c>
+      <c r="AB46" s="17" t="n">
+        <v>14408.94</v>
+      </c>
+      <c r="AC46" s="17" t="n">
+        <v>14415.7</v>
+      </c>
+      <c r="AD46" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE46" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF46" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG46" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH46" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI46" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ46" s="17" t="n">
+        <v>54.76</v>
+      </c>
+      <c r="AK46" s="17" t="n">
+        <v>14360.94</v>
+      </c>
+      <c r="AL46" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM46" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN46" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -51405,7 +52585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN45"/>
+  <dimension ref="A1:AN46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -58149,6 +59329,158 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D46" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E46" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G46" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24334.3&gt;24072.75) &amp; EMA9↑(24145.32&gt;24009.3)</t>
+        </is>
+      </c>
+      <c r="H46" s="17" t="n">
+        <v>24145.32</v>
+      </c>
+      <c r="I46" s="17" t="n">
+        <v>24009.3</v>
+      </c>
+      <c r="J46" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K46" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L46" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M46" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N46" s="17" t="inlineStr">
+        <is>
+          <t>11:10 IST</t>
+        </is>
+      </c>
+      <c r="O46" s="17" t="n">
+        <v>24334.3</v>
+      </c>
+      <c r="P46" s="17" t="n">
+        <v>24072.75</v>
+      </c>
+      <c r="Q46" s="17" t="inlineStr">
+        <is>
+          <t>24400 PE</t>
+        </is>
+      </c>
+      <c r="R46" s="17" t="inlineStr">
+        <is>
+          <t>24300 PE</t>
+        </is>
+      </c>
+      <c r="S46" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="T46" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U46" s="17" t="n">
+        <v>1430</v>
+      </c>
+      <c r="V46" s="17" t="n">
+        <v>33.56</v>
+      </c>
+      <c r="W46" s="17" t="n">
+        <v>43.63</v>
+      </c>
+      <c r="X46" s="17" t="n">
+        <v>47990.8</v>
+      </c>
+      <c r="Y46" s="17" t="n">
+        <v>48045.55</v>
+      </c>
+      <c r="Z46" s="17" t="n">
+        <v>95009.2</v>
+      </c>
+      <c r="AA46" s="17" t="n">
+        <v>14397.24</v>
+      </c>
+      <c r="AB46" s="17" t="n">
+        <v>14397.24</v>
+      </c>
+      <c r="AC46" s="17" t="n">
+        <v>14400.1</v>
+      </c>
+      <c r="AD46" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE46" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF46" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG46" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH46" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI46" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ46" s="17" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="AK46" s="17" t="n">
+        <v>14345.35</v>
+      </c>
+      <c r="AL46" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM46" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN46" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -58163,7 +59495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN88"/>
+  <dimension ref="A1:AN90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -71403,6 +72735,310 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B89" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C89" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D89" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E89" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F89" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G89" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(24334.3&gt;24072.75) &amp; EMA9↑(24145.32&gt;24009.3)</t>
+        </is>
+      </c>
+      <c r="H89" s="15" t="n">
+        <v>24145.32</v>
+      </c>
+      <c r="I89" s="15" t="n">
+        <v>24009.3</v>
+      </c>
+      <c r="J89" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K89" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L89" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="M89" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N89" s="15" t="inlineStr">
+        <is>
+          <t>09:44 IST</t>
+        </is>
+      </c>
+      <c r="O89" s="15" t="n">
+        <v>24334.3</v>
+      </c>
+      <c r="P89" s="15" t="n">
+        <v>24072.75</v>
+      </c>
+      <c r="Q89" s="15" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="R89" s="15" t="inlineStr">
+        <is>
+          <t>24400 CE</t>
+        </is>
+      </c>
+      <c r="S89" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="T89" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U89" s="15" t="n">
+        <v>1560</v>
+      </c>
+      <c r="V89" s="15" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="W89" s="15" t="n">
+        <v>21.97</v>
+      </c>
+      <c r="X89" s="15" t="n">
+        <v>48968.4</v>
+      </c>
+      <c r="Y89" s="15" t="n">
+        <v>49023.31</v>
+      </c>
+      <c r="Z89" s="15" t="n">
+        <v>107031.6</v>
+      </c>
+      <c r="AA89" s="15" t="n">
+        <v>14690.52</v>
+      </c>
+      <c r="AB89" s="15" t="n">
+        <v>14690.52</v>
+      </c>
+      <c r="AC89" s="15" t="n">
+        <v>-14695.2</v>
+      </c>
+      <c r="AD89" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE89" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF89" s="15" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="AG89" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH89" s="15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI89" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ89" s="15" t="n">
+        <v>54.91</v>
+      </c>
+      <c r="AK89" s="15" t="n">
+        <v>-14750.11</v>
+      </c>
+      <c r="AL89" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM89" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN89" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B90" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C90" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D90" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E90" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F90" s="15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G90" s="15" t="inlineStr">
+        <is>
+          <t>Price↑(24334.3&gt;24072.75) &amp; EMA9↑(24145.32&gt;24009.3)</t>
+        </is>
+      </c>
+      <c r="H90" s="15" t="n">
+        <v>24145.32</v>
+      </c>
+      <c r="I90" s="15" t="n">
+        <v>24009.3</v>
+      </c>
+      <c r="J90" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K90" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L90" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="M90" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N90" s="15" t="inlineStr">
+        <is>
+          <t>10:17 IST</t>
+        </is>
+      </c>
+      <c r="O90" s="15" t="n">
+        <v>24334.3</v>
+      </c>
+      <c r="P90" s="15" t="n">
+        <v>24072.75</v>
+      </c>
+      <c r="Q90" s="15" t="inlineStr">
+        <is>
+          <t>24400 PE</t>
+        </is>
+      </c>
+      <c r="R90" s="15" t="inlineStr">
+        <is>
+          <t>24300 PE</t>
+        </is>
+      </c>
+      <c r="S90" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="T90" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U90" s="15" t="n">
+        <v>1885</v>
+      </c>
+      <c r="V90" s="15" t="n">
+        <v>25.17</v>
+      </c>
+      <c r="W90" s="15" t="n">
+        <v>17.62</v>
+      </c>
+      <c r="X90" s="15" t="n">
+        <v>47445.45</v>
+      </c>
+      <c r="Y90" s="15" t="n">
+        <v>47500.12</v>
+      </c>
+      <c r="Z90" s="15" t="n">
+        <v>141054.55</v>
+      </c>
+      <c r="AA90" s="15" t="n">
+        <v>14233.63</v>
+      </c>
+      <c r="AB90" s="15" t="n">
+        <v>14233.63</v>
+      </c>
+      <c r="AC90" s="15" t="n">
+        <v>-14231.75</v>
+      </c>
+      <c r="AD90" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE90" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF90" s="15" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="AG90" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH90" s="15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI90" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ90" s="15" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="AK90" s="15" t="n">
+        <v>-14286.42</v>
+      </c>
+      <c r="AL90" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM90" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN90" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -71417,7 +73053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN26"/>
+  <dimension ref="A1:AN27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -75298,6 +76934,158 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>Price↑(24334.3&gt;24072.75) &amp; EMA9↑(24145.32&gt;24009.3)</t>
+        </is>
+      </c>
+      <c r="H27" s="17" t="n">
+        <v>24145.32</v>
+      </c>
+      <c r="I27" s="17" t="n">
+        <v>24009.3</v>
+      </c>
+      <c r="J27" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K27" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L27" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M27" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N27" s="17" t="inlineStr">
+        <is>
+          <t>11:07 IST</t>
+        </is>
+      </c>
+      <c r="O27" s="17" t="n">
+        <v>24334.3</v>
+      </c>
+      <c r="P27" s="17" t="n">
+        <v>24072.75</v>
+      </c>
+      <c r="Q27" s="17" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="R27" s="17" t="inlineStr">
+        <is>
+          <t>24400 CE</t>
+        </is>
+      </c>
+      <c r="S27" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="T27" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U27" s="17" t="n">
+        <v>1885</v>
+      </c>
+      <c r="V27" s="17" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="W27" s="17" t="n">
+        <v>33.45</v>
+      </c>
+      <c r="X27" s="17" t="n">
+        <v>48501.05</v>
+      </c>
+      <c r="Y27" s="17" t="n">
+        <v>48555.88</v>
+      </c>
+      <c r="Z27" s="17" t="n">
+        <v>139998.95</v>
+      </c>
+      <c r="AA27" s="17" t="n">
+        <v>14550.32</v>
+      </c>
+      <c r="AB27" s="17" t="n">
+        <v>14550.32</v>
+      </c>
+      <c r="AC27" s="17" t="n">
+        <v>14552.2</v>
+      </c>
+      <c r="AD27" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE27" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF27" s="17" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="AG27" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH27" s="17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI27" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ27" s="17" t="n">
+        <v>54.83</v>
+      </c>
+      <c r="AK27" s="17" t="n">
+        <v>14497.37</v>
+      </c>
+      <c r="AL27" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM27" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN27" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA46"/>
+  <dimension ref="A1:AA47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5136,6 +5136,105 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E47" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="F47" s="16" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G47" s="16" t="inlineStr">
+        <is>
+          <t>16:26 ET</t>
+        </is>
+      </c>
+      <c r="H47" s="16" t="n">
+        <v>28777.25</v>
+      </c>
+      <c r="I47" s="16" t="n">
+        <v>28775</v>
+      </c>
+      <c r="J47" s="16" t="n">
+        <v>28800</v>
+      </c>
+      <c r="K47" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L47" s="16" t="n">
+        <v>215.09</v>
+      </c>
+      <c r="M47" s="16" t="n">
+        <v>217.14</v>
+      </c>
+      <c r="N47" s="16" t="n">
+        <v>889.96</v>
+      </c>
+      <c r="O47" s="16" t="n">
+        <v>1139.64</v>
+      </c>
+      <c r="P47" s="16" t="n">
+        <v>258.11</v>
+      </c>
+      <c r="Q47" s="16" t="n">
+        <v>258.11</v>
+      </c>
+      <c r="R47" s="16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="S47" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" s="16" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="U47" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="V47" s="16" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W47" s="16" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="X47" s="16" t="n">
+        <v>-21.4</v>
+      </c>
+      <c r="Y47" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="Z47" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA47" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -5150,7 +5249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN46"/>
+  <dimension ref="A1:AN47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12046,6 +12145,158 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E47" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F47" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G47" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H47" s="16" t="n">
+        <v>57821.95</v>
+      </c>
+      <c r="I47" s="16" t="n">
+        <v>57595.38</v>
+      </c>
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K47" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L47" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="M47" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N47" s="16" t="inlineStr">
+        <is>
+          <t>14:05 IST</t>
+        </is>
+      </c>
+      <c r="O47" s="16" t="n">
+        <v>57673.6</v>
+      </c>
+      <c r="P47" s="16" t="n">
+        <v>58521.4</v>
+      </c>
+      <c r="Q47" s="16" t="inlineStr">
+        <is>
+          <t>57600 CE</t>
+        </is>
+      </c>
+      <c r="R47" s="16" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="S47" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="T47" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U47" s="16" t="n">
+        <v>510</v>
+      </c>
+      <c r="V47" s="16" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="W47" s="16" t="n">
+        <v>94.08</v>
+      </c>
+      <c r="X47" s="16" t="n">
+        <v>48552</v>
+      </c>
+      <c r="Y47" s="16" t="n">
+        <v>48606.84</v>
+      </c>
+      <c r="Z47" s="16" t="n">
+        <v>53448</v>
+      </c>
+      <c r="AA47" s="16" t="n">
+        <v>14565.6</v>
+      </c>
+      <c r="AB47" s="16" t="n">
+        <v>14565.6</v>
+      </c>
+      <c r="AC47" s="16" t="n">
+        <v>-571.2</v>
+      </c>
+      <c r="AD47" s="16" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AE47" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF47" s="16" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="AG47" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH47" s="16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI47" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ47" s="16" t="n">
+        <v>54.84</v>
+      </c>
+      <c r="AK47" s="16" t="n">
+        <v>-626.04</v>
+      </c>
+      <c r="AL47" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM47" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN47" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -12060,7 +12311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN46"/>
+  <dimension ref="A1:AN47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18956,6 +19207,158 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D47" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E47" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F47" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G47" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H47" s="17" t="n">
+        <v>57821.95</v>
+      </c>
+      <c r="I47" s="17" t="n">
+        <v>57595.38</v>
+      </c>
+      <c r="J47" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K47" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L47" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="M47" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N47" s="17" t="inlineStr">
+        <is>
+          <t>10:47 IST</t>
+        </is>
+      </c>
+      <c r="O47" s="17" t="n">
+        <v>57673.6</v>
+      </c>
+      <c r="P47" s="17" t="n">
+        <v>58521.4</v>
+      </c>
+      <c r="Q47" s="17" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="R47" s="17" t="inlineStr">
+        <is>
+          <t>57600 PE</t>
+        </is>
+      </c>
+      <c r="S47" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="T47" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U47" s="17" t="n">
+        <v>510</v>
+      </c>
+      <c r="V47" s="17" t="n">
+        <v>92.17</v>
+      </c>
+      <c r="W47" s="17" t="n">
+        <v>119.82</v>
+      </c>
+      <c r="X47" s="17" t="n">
+        <v>47006.7</v>
+      </c>
+      <c r="Y47" s="17" t="n">
+        <v>47061.3</v>
+      </c>
+      <c r="Z47" s="17" t="n">
+        <v>54993.3</v>
+      </c>
+      <c r="AA47" s="17" t="n">
+        <v>14102.01</v>
+      </c>
+      <c r="AB47" s="17" t="n">
+        <v>14102.01</v>
+      </c>
+      <c r="AC47" s="17" t="n">
+        <v>14101.5</v>
+      </c>
+      <c r="AD47" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE47" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF47" s="17" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="AG47" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH47" s="17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI47" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ47" s="17" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="AK47" s="17" t="n">
+        <v>14046.9</v>
+      </c>
+      <c r="AL47" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM47" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN47" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -18970,7 +19373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN90"/>
+  <dimension ref="A1:AN92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -32509,6 +32912,310 @@
         <v>50000</v>
       </c>
       <c r="AN90" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B91" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C91" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D91" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E91" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F91" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G91" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H91" s="16" t="n">
+        <v>57821.95</v>
+      </c>
+      <c r="I91" s="16" t="n">
+        <v>57595.38</v>
+      </c>
+      <c r="J91" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K91" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L91" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="M91" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N91" s="16" t="inlineStr">
+        <is>
+          <t>13:27 IST</t>
+        </is>
+      </c>
+      <c r="O91" s="16" t="n">
+        <v>57673.6</v>
+      </c>
+      <c r="P91" s="16" t="n">
+        <v>58521.4</v>
+      </c>
+      <c r="Q91" s="16" t="inlineStr">
+        <is>
+          <t>57600 CE</t>
+        </is>
+      </c>
+      <c r="R91" s="16" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="S91" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="T91" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U91" s="16" t="n">
+        <v>480</v>
+      </c>
+      <c r="V91" s="16" t="n">
+        <v>99.31999999999999</v>
+      </c>
+      <c r="W91" s="16" t="n">
+        <v>100.67</v>
+      </c>
+      <c r="X91" s="16" t="n">
+        <v>47673.6</v>
+      </c>
+      <c r="Y91" s="16" t="n">
+        <v>47728.3</v>
+      </c>
+      <c r="Z91" s="16" t="n">
+        <v>48326.4</v>
+      </c>
+      <c r="AA91" s="16" t="n">
+        <v>14302.08</v>
+      </c>
+      <c r="AB91" s="16" t="n">
+        <v>14302.08</v>
+      </c>
+      <c r="AC91" s="16" t="n">
+        <v>648</v>
+      </c>
+      <c r="AD91" s="16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE91" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF91" s="16" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="AG91" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH91" s="16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI91" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ91" s="16" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="AK91" s="16" t="n">
+        <v>593.3</v>
+      </c>
+      <c r="AL91" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM91" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN91" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B92" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C92" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D92" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E92" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F92" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G92" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H92" s="15" t="n">
+        <v>57821.95</v>
+      </c>
+      <c r="I92" s="15" t="n">
+        <v>57595.38</v>
+      </c>
+      <c r="J92" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K92" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L92" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="M92" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N92" s="15" t="inlineStr">
+        <is>
+          <t>10:45 IST</t>
+        </is>
+      </c>
+      <c r="O92" s="15" t="n">
+        <v>57673.6</v>
+      </c>
+      <c r="P92" s="15" t="n">
+        <v>58521.4</v>
+      </c>
+      <c r="Q92" s="15" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="R92" s="15" t="inlineStr">
+        <is>
+          <t>57600 PE</t>
+        </is>
+      </c>
+      <c r="S92" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="T92" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U92" s="15" t="n">
+        <v>510</v>
+      </c>
+      <c r="V92" s="15" t="n">
+        <v>92.64</v>
+      </c>
+      <c r="W92" s="15" t="n">
+        <v>64.84999999999999</v>
+      </c>
+      <c r="X92" s="15" t="n">
+        <v>47246.4</v>
+      </c>
+      <c r="Y92" s="15" t="n">
+        <v>47301.03</v>
+      </c>
+      <c r="Z92" s="15" t="n">
+        <v>54753.6</v>
+      </c>
+      <c r="AA92" s="15" t="n">
+        <v>14173.92</v>
+      </c>
+      <c r="AB92" s="15" t="n">
+        <v>14173.92</v>
+      </c>
+      <c r="AC92" s="15" t="n">
+        <v>-14172.9</v>
+      </c>
+      <c r="AD92" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE92" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF92" s="15" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AG92" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH92" s="15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI92" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ92" s="15" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="AK92" s="15" t="n">
+        <v>-14227.53</v>
+      </c>
+      <c r="AL92" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM92" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN92" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -35962,7 +36669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -37399,6 +38106,72 @@
         <v>57362.65</v>
       </c>
       <c r="G44" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D45" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E45" s="18" t="n">
+        <v>24152.5</v>
+      </c>
+      <c r="F45" s="18" t="n">
+        <v>24041.8</v>
+      </c>
+      <c r="G45" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E46" s="18" t="n">
+        <v>57821.95</v>
+      </c>
+      <c r="F46" s="18" t="n">
+        <v>57595.38</v>
+      </c>
+      <c r="G46" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -37418,7 +38191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA46"/>
+  <dimension ref="A1:AA47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -41945,6 +42718,105 @@
         <v>1000</v>
       </c>
       <c r="AA46" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E47" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="F47" s="16" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G47" s="16" t="inlineStr">
+        <is>
+          <t>15:20 ET</t>
+        </is>
+      </c>
+      <c r="H47" s="16" t="n">
+        <v>28777.75</v>
+      </c>
+      <c r="I47" s="16" t="n">
+        <v>28775</v>
+      </c>
+      <c r="J47" s="16" t="n">
+        <v>28800</v>
+      </c>
+      <c r="K47" s="16" t="n">
+        <v>36</v>
+      </c>
+      <c r="L47" s="16" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="M47" s="16" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="N47" s="16" t="n">
+        <v>982.8</v>
+      </c>
+      <c r="O47" s="16" t="n">
+        <v>876.24</v>
+      </c>
+      <c r="P47" s="16" t="n">
+        <v>277.13</v>
+      </c>
+      <c r="Q47" s="16" t="n">
+        <v>277.13</v>
+      </c>
+      <c r="R47" s="16" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="S47" s="16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T47" s="16" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="U47" s="16" t="n">
+        <v>36</v>
+      </c>
+      <c r="V47" s="16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W47" s="16" t="n">
+        <v>59.04</v>
+      </c>
+      <c r="X47" s="16" t="n">
+        <v>-26.28</v>
+      </c>
+      <c r="Y47" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="Z47" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA47" s="16" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -42064,7 +42936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I90"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -45207,6 +46079,76 @@
         <v>63.96</v>
       </c>
       <c r="I90" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B91" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C91" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D91" s="19" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="E91" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F91" s="19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G91" s="19" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H91" s="19" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I91" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B92" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C92" s="19" t="n">
+        <v>36</v>
+      </c>
+      <c r="D92" s="19" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="E92" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="F92" s="19" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G92" s="19" t="n">
+        <v>29.52</v>
+      </c>
+      <c r="H92" s="19" t="n">
+        <v>59.04</v>
+      </c>
+      <c r="I92" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — FLAT</t>
         </is>
@@ -45675,7 +46617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN46"/>
+  <dimension ref="A1:AN47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -52571,6 +53513,158 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E47" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F47" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G47" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H47" s="16" t="n">
+        <v>24152.5</v>
+      </c>
+      <c r="I47" s="16" t="n">
+        <v>24041.8</v>
+      </c>
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K47" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L47" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M47" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N47" s="16" t="inlineStr">
+        <is>
+          <t>13:25 IST</t>
+        </is>
+      </c>
+      <c r="O47" s="16" t="n">
+        <v>24180.2</v>
+      </c>
+      <c r="P47" s="16" t="n">
+        <v>24334.3</v>
+      </c>
+      <c r="Q47" s="16" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="R47" s="16" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="S47" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="T47" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U47" s="16" t="n">
+        <v>1885</v>
+      </c>
+      <c r="V47" s="16" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="W47" s="16" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="X47" s="16" t="n">
+        <v>48783.8</v>
+      </c>
+      <c r="Y47" s="16" t="n">
+        <v>48838.68</v>
+      </c>
+      <c r="Z47" s="16" t="n">
+        <v>139716.2</v>
+      </c>
+      <c r="AA47" s="16" t="n">
+        <v>14635.14</v>
+      </c>
+      <c r="AB47" s="16" t="n">
+        <v>14635.14</v>
+      </c>
+      <c r="AC47" s="16" t="n">
+        <v>-2375.1</v>
+      </c>
+      <c r="AD47" s="16" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="AE47" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF47" s="16" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AG47" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH47" s="16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI47" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ47" s="16" t="n">
+        <v>54.88</v>
+      </c>
+      <c r="AK47" s="16" t="n">
+        <v>-2429.98</v>
+      </c>
+      <c r="AL47" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM47" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN47" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -52585,7 +53679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN46"/>
+  <dimension ref="A1:AN47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -59481,6 +60575,158 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D47" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E47" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F47" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G47" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H47" s="17" t="n">
+        <v>24152.5</v>
+      </c>
+      <c r="I47" s="17" t="n">
+        <v>24041.8</v>
+      </c>
+      <c r="J47" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K47" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L47" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M47" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N47" s="17" t="inlineStr">
+        <is>
+          <t>10:32 IST</t>
+        </is>
+      </c>
+      <c r="O47" s="17" t="n">
+        <v>24180.2</v>
+      </c>
+      <c r="P47" s="17" t="n">
+        <v>24334.3</v>
+      </c>
+      <c r="Q47" s="17" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="R47" s="17" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="S47" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="T47" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U47" s="17" t="n">
+        <v>1690</v>
+      </c>
+      <c r="V47" s="17" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="W47" s="17" t="n">
+        <v>36.28</v>
+      </c>
+      <c r="X47" s="17" t="n">
+        <v>47167.9</v>
+      </c>
+      <c r="Y47" s="17" t="n">
+        <v>47222.52</v>
+      </c>
+      <c r="Z47" s="17" t="n">
+        <v>121832.1</v>
+      </c>
+      <c r="AA47" s="17" t="n">
+        <v>14150.37</v>
+      </c>
+      <c r="AB47" s="17" t="n">
+        <v>14150.37</v>
+      </c>
+      <c r="AC47" s="17" t="n">
+        <v>14145.3</v>
+      </c>
+      <c r="AD47" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE47" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF47" s="17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AG47" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH47" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI47" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ47" s="17" t="n">
+        <v>54.62</v>
+      </c>
+      <c r="AK47" s="17" t="n">
+        <v>14090.68</v>
+      </c>
+      <c r="AL47" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM47" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN47" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -59495,7 +60741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN90"/>
+  <dimension ref="A1:AN92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -73034,6 +74280,310 @@
         <v>50000</v>
       </c>
       <c r="AN90" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B91" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C91" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D91" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E91" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F91" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G91" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H91" s="17" t="n">
+        <v>24152.5</v>
+      </c>
+      <c r="I91" s="17" t="n">
+        <v>24041.8</v>
+      </c>
+      <c r="J91" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K91" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L91" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M91" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N91" s="17" t="inlineStr">
+        <is>
+          <t>11:47 IST</t>
+        </is>
+      </c>
+      <c r="O91" s="17" t="n">
+        <v>24180.2</v>
+      </c>
+      <c r="P91" s="17" t="n">
+        <v>24334.3</v>
+      </c>
+      <c r="Q91" s="17" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="R91" s="17" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="S91" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="T91" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U91" s="17" t="n">
+        <v>1820</v>
+      </c>
+      <c r="V91" s="17" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="W91" s="17" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="X91" s="17" t="n">
+        <v>47465.6</v>
+      </c>
+      <c r="Y91" s="17" t="n">
+        <v>47520.27</v>
+      </c>
+      <c r="Z91" s="17" t="n">
+        <v>134534.4</v>
+      </c>
+      <c r="AA91" s="17" t="n">
+        <v>14239.68</v>
+      </c>
+      <c r="AB91" s="17" t="n">
+        <v>14239.68</v>
+      </c>
+      <c r="AC91" s="17" t="n">
+        <v>14232.4</v>
+      </c>
+      <c r="AD91" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE91" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF91" s="17" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="AG91" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH91" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI91" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ91" s="17" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="AK91" s="17" t="n">
+        <v>14177.73</v>
+      </c>
+      <c r="AL91" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM91" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN91" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B92" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C92" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D92" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E92" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F92" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G92" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H92" s="16" t="n">
+        <v>24152.5</v>
+      </c>
+      <c r="I92" s="16" t="n">
+        <v>24041.8</v>
+      </c>
+      <c r="J92" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K92" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L92" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M92" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N92" s="16" t="inlineStr">
+        <is>
+          <t>14:10 IST</t>
+        </is>
+      </c>
+      <c r="O92" s="16" t="n">
+        <v>24180.2</v>
+      </c>
+      <c r="P92" s="16" t="n">
+        <v>24334.3</v>
+      </c>
+      <c r="Q92" s="16" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="R92" s="16" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="S92" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="T92" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U92" s="16" t="n">
+        <v>1495</v>
+      </c>
+      <c r="V92" s="16" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="W92" s="16" t="n">
+        <v>31.51</v>
+      </c>
+      <c r="X92" s="16" t="n">
+        <v>47705.45</v>
+      </c>
+      <c r="Y92" s="16" t="n">
+        <v>47760.16</v>
+      </c>
+      <c r="Z92" s="16" t="n">
+        <v>101794.55</v>
+      </c>
+      <c r="AA92" s="16" t="n">
+        <v>14311.63</v>
+      </c>
+      <c r="AB92" s="16" t="n">
+        <v>14311.63</v>
+      </c>
+      <c r="AC92" s="16" t="n">
+        <v>-598</v>
+      </c>
+      <c r="AD92" s="16" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="AE92" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF92" s="16" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="AG92" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH92" s="16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI92" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ92" s="16" t="n">
+        <v>54.71</v>
+      </c>
+      <c r="AK92" s="16" t="n">
+        <v>-652.71</v>
+      </c>
+      <c r="AL92" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM92" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN92" s="16" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA47"/>
+  <dimension ref="A1:AA48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5235,6 +5235,105 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B48" s="16" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E48" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="F48" s="16" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G48" s="16" t="inlineStr">
+        <is>
+          <t>16:02 ET</t>
+        </is>
+      </c>
+      <c r="H48" s="16" t="n">
+        <v>29008.5</v>
+      </c>
+      <c r="I48" s="16" t="n">
+        <v>29000</v>
+      </c>
+      <c r="J48" s="16" t="n">
+        <v>29025</v>
+      </c>
+      <c r="K48" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L48" s="16" t="n">
+        <v>236.33</v>
+      </c>
+      <c r="M48" s="16" t="n">
+        <v>245.03</v>
+      </c>
+      <c r="N48" s="16" t="n">
+        <v>974.92</v>
+      </c>
+      <c r="O48" s="16" t="n">
+        <v>1054.68</v>
+      </c>
+      <c r="P48" s="16" t="n">
+        <v>283.6</v>
+      </c>
+      <c r="Q48" s="16" t="n">
+        <v>283.6</v>
+      </c>
+      <c r="R48" s="16" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="S48" s="16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T48" s="16" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="U48" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="V48" s="16" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W48" s="16" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="X48" s="16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y48" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="Z48" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA48" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -5249,7 +5348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN47"/>
+  <dimension ref="A1:AN48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12297,6 +12396,158 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F48" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G48" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>57876.23</v>
+      </c>
+      <c r="I48" s="15" t="n">
+        <v>57620.05</v>
+      </c>
+      <c r="J48" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K48" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L48" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="M48" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N48" s="15" t="inlineStr">
+        <is>
+          <t>10:29 IST</t>
+        </is>
+      </c>
+      <c r="O48" s="15" t="n">
+        <v>57945</v>
+      </c>
+      <c r="P48" s="15" t="n">
+        <v>58521.4</v>
+      </c>
+      <c r="Q48" s="15" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="R48" s="15" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="S48" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="T48" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U48" s="15" t="n">
+        <v>540</v>
+      </c>
+      <c r="V48" s="15" t="n">
+        <v>87.87</v>
+      </c>
+      <c r="W48" s="15" t="n">
+        <v>61.51</v>
+      </c>
+      <c r="X48" s="15" t="n">
+        <v>47449.8</v>
+      </c>
+      <c r="Y48" s="15" t="n">
+        <v>47504.47</v>
+      </c>
+      <c r="Z48" s="15" t="n">
+        <v>60550.2</v>
+      </c>
+      <c r="AA48" s="15" t="n">
+        <v>14234.94</v>
+      </c>
+      <c r="AB48" s="15" t="n">
+        <v>14234.94</v>
+      </c>
+      <c r="AC48" s="15" t="n">
+        <v>-14234.4</v>
+      </c>
+      <c r="AD48" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE48" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF48" s="15" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="AG48" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH48" s="15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI48" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ48" s="15" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="AK48" s="15" t="n">
+        <v>-14289.07</v>
+      </c>
+      <c r="AL48" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM48" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN48" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -12311,7 +12562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN47"/>
+  <dimension ref="A1:AN48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -19359,6 +19610,158 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D48" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E48" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F48" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G48" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H48" s="17" t="n">
+        <v>57876.23</v>
+      </c>
+      <c r="I48" s="17" t="n">
+        <v>57620.05</v>
+      </c>
+      <c r="J48" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K48" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L48" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="M48" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N48" s="17" t="inlineStr">
+        <is>
+          <t>10:25 IST</t>
+        </is>
+      </c>
+      <c r="O48" s="17" t="n">
+        <v>57945</v>
+      </c>
+      <c r="P48" s="17" t="n">
+        <v>58521.4</v>
+      </c>
+      <c r="Q48" s="17" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="R48" s="17" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="S48" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="T48" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U48" s="17" t="n">
+        <v>630</v>
+      </c>
+      <c r="V48" s="17" t="n">
+        <v>76.36</v>
+      </c>
+      <c r="W48" s="17" t="n">
+        <v>99.27</v>
+      </c>
+      <c r="X48" s="17" t="n">
+        <v>48106.8</v>
+      </c>
+      <c r="Y48" s="17" t="n">
+        <v>48161.57</v>
+      </c>
+      <c r="Z48" s="17" t="n">
+        <v>77893.2</v>
+      </c>
+      <c r="AA48" s="17" t="n">
+        <v>14432.04</v>
+      </c>
+      <c r="AB48" s="17" t="n">
+        <v>14432.04</v>
+      </c>
+      <c r="AC48" s="17" t="n">
+        <v>14433.3</v>
+      </c>
+      <c r="AD48" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE48" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF48" s="17" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="AG48" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH48" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI48" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ48" s="17" t="n">
+        <v>54.77</v>
+      </c>
+      <c r="AK48" s="17" t="n">
+        <v>14378.53</v>
+      </c>
+      <c r="AL48" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM48" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN48" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -19373,7 +19776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN92"/>
+  <dimension ref="A1:AN94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -33216,6 +33619,310 @@
         <v>50000</v>
       </c>
       <c r="AN92" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B93" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C93" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D93" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E93" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F93" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G93" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H93" s="16" t="n">
+        <v>57876.23</v>
+      </c>
+      <c r="I93" s="16" t="n">
+        <v>57620.05</v>
+      </c>
+      <c r="J93" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K93" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L93" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="M93" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N93" s="16" t="inlineStr">
+        <is>
+          <t>13:48 IST</t>
+        </is>
+      </c>
+      <c r="O93" s="16" t="n">
+        <v>57945</v>
+      </c>
+      <c r="P93" s="16" t="n">
+        <v>58521.4</v>
+      </c>
+      <c r="Q93" s="16" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="R93" s="16" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="S93" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="T93" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U93" s="16" t="n">
+        <v>540</v>
+      </c>
+      <c r="V93" s="16" t="n">
+        <v>90.98</v>
+      </c>
+      <c r="W93" s="16" t="n">
+        <v>94.59</v>
+      </c>
+      <c r="X93" s="16" t="n">
+        <v>49129.2</v>
+      </c>
+      <c r="Y93" s="16" t="n">
+        <v>49184.13</v>
+      </c>
+      <c r="Z93" s="16" t="n">
+        <v>58870.8</v>
+      </c>
+      <c r="AA93" s="16" t="n">
+        <v>14738.76</v>
+      </c>
+      <c r="AB93" s="16" t="n">
+        <v>14738.76</v>
+      </c>
+      <c r="AC93" s="16" t="n">
+        <v>1949.4</v>
+      </c>
+      <c r="AD93" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE93" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF93" s="16" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="AG93" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH93" s="16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI93" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ93" s="16" t="n">
+        <v>54.93</v>
+      </c>
+      <c r="AK93" s="16" t="n">
+        <v>1894.47</v>
+      </c>
+      <c r="AL93" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM93" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN93" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B94" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C94" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D94" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E94" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F94" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G94" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H94" s="15" t="n">
+        <v>57876.23</v>
+      </c>
+      <c r="I94" s="15" t="n">
+        <v>57620.05</v>
+      </c>
+      <c r="J94" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K94" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L94" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="M94" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N94" s="15" t="inlineStr">
+        <is>
+          <t>10:46 IST</t>
+        </is>
+      </c>
+      <c r="O94" s="15" t="n">
+        <v>57945</v>
+      </c>
+      <c r="P94" s="15" t="n">
+        <v>58521.4</v>
+      </c>
+      <c r="Q94" s="15" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="R94" s="15" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="S94" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="T94" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U94" s="15" t="n">
+        <v>570</v>
+      </c>
+      <c r="V94" s="15" t="n">
+        <v>82.88</v>
+      </c>
+      <c r="W94" s="15" t="n">
+        <v>58.02</v>
+      </c>
+      <c r="X94" s="15" t="n">
+        <v>47241.6</v>
+      </c>
+      <c r="Y94" s="15" t="n">
+        <v>47296.23</v>
+      </c>
+      <c r="Z94" s="15" t="n">
+        <v>66758.39999999999</v>
+      </c>
+      <c r="AA94" s="15" t="n">
+        <v>14172.48</v>
+      </c>
+      <c r="AB94" s="15" t="n">
+        <v>14172.48</v>
+      </c>
+      <c r="AC94" s="15" t="n">
+        <v>-14170.2</v>
+      </c>
+      <c r="AD94" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE94" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF94" s="15" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AG94" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH94" s="15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI94" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ94" s="15" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="AK94" s="15" t="n">
+        <v>-14224.83</v>
+      </c>
+      <c r="AL94" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM94" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN94" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -36669,7 +37376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -38172,6 +38879,72 @@
         <v>57595.38</v>
       </c>
       <c r="G46" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D47" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E47" s="18" t="n">
+        <v>24164.16</v>
+      </c>
+      <c r="F47" s="18" t="n">
+        <v>24047.1</v>
+      </c>
+      <c r="G47" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B48" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D48" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E48" s="18" t="n">
+        <v>57876.23</v>
+      </c>
+      <c r="F48" s="18" t="n">
+        <v>57620.05</v>
+      </c>
+      <c r="G48" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -38191,7 +38964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA47"/>
+  <dimension ref="A1:AA48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -42817,6 +43590,105 @@
         <v>1000</v>
       </c>
       <c r="AA47" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="n">
+        <v>32</v>
+      </c>
+      <c r="F48" s="15" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G48" s="15" t="inlineStr">
+        <is>
+          <t>12:05 ET</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>29007.25</v>
+      </c>
+      <c r="I48" s="15" t="n">
+        <v>29000</v>
+      </c>
+      <c r="J48" s="15" t="n">
+        <v>29025</v>
+      </c>
+      <c r="K48" s="15" t="n">
+        <v>43</v>
+      </c>
+      <c r="L48" s="15" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="M48" s="15" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="N48" s="15" t="n">
+        <v>985.5599999999999</v>
+      </c>
+      <c r="O48" s="15" t="n">
+        <v>1234.96</v>
+      </c>
+      <c r="P48" s="15" t="n">
+        <v>274.51</v>
+      </c>
+      <c r="Q48" s="15" t="n">
+        <v>274.51</v>
+      </c>
+      <c r="R48" s="15" t="n">
+        <v>-274.34</v>
+      </c>
+      <c r="S48" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="T48" s="15" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="U48" s="15" t="n">
+        <v>43</v>
+      </c>
+      <c r="V48" s="15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W48" s="15" t="n">
+        <v>70.52</v>
+      </c>
+      <c r="X48" s="15" t="n">
+        <v>-344.86</v>
+      </c>
+      <c r="Y48" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="Z48" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA48" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -42936,7 +43808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -46151,6 +47023,76 @@
       <c r="I92" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B93" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C93" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D93" s="19" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="E93" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F93" s="19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G93" s="19" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H93" s="19" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I93" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B94" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C94" s="19" t="n">
+        <v>43</v>
+      </c>
+      <c r="D94" s="19" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="E94" s="19" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F94" s="19" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G94" s="19" t="n">
+        <v>35.26</v>
+      </c>
+      <c r="H94" s="19" t="n">
+        <v>70.52</v>
+      </c>
+      <c r="I94" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — STOP LOSS</t>
         </is>
       </c>
     </row>
@@ -46617,7 +47559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN47"/>
+  <dimension ref="A1:AN48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -53665,6 +54607,158 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B48" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E48" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F48" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G48" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H48" s="16" t="n">
+        <v>24164.16</v>
+      </c>
+      <c r="I48" s="16" t="n">
+        <v>24047.1</v>
+      </c>
+      <c r="J48" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K48" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L48" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M48" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N48" s="16" t="inlineStr">
+        <is>
+          <t>13:40 IST</t>
+        </is>
+      </c>
+      <c r="O48" s="16" t="n">
+        <v>24238.5</v>
+      </c>
+      <c r="P48" s="16" t="n">
+        <v>24334.3</v>
+      </c>
+      <c r="Q48" s="16" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="R48" s="16" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="S48" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="T48" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U48" s="16" t="n">
+        <v>1235</v>
+      </c>
+      <c r="V48" s="16" t="n">
+        <v>38.85</v>
+      </c>
+      <c r="W48" s="16" t="n">
+        <v>40.27</v>
+      </c>
+      <c r="X48" s="16" t="n">
+        <v>47979.75</v>
+      </c>
+      <c r="Y48" s="16" t="n">
+        <v>48034.5</v>
+      </c>
+      <c r="Z48" s="16" t="n">
+        <v>75520.25</v>
+      </c>
+      <c r="AA48" s="16" t="n">
+        <v>14393.92</v>
+      </c>
+      <c r="AB48" s="16" t="n">
+        <v>14393.92</v>
+      </c>
+      <c r="AC48" s="16" t="n">
+        <v>1753.7</v>
+      </c>
+      <c r="AD48" s="16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE48" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF48" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG48" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH48" s="16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI48" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ48" s="16" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="AK48" s="16" t="n">
+        <v>1698.95</v>
+      </c>
+      <c r="AL48" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM48" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN48" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -53679,7 +54773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN47"/>
+  <dimension ref="A1:AN48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -60727,6 +61821,158 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F48" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G48" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>24164.16</v>
+      </c>
+      <c r="I48" s="15" t="n">
+        <v>24047.1</v>
+      </c>
+      <c r="J48" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K48" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L48" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M48" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N48" s="15" t="inlineStr">
+        <is>
+          <t>09:45 IST</t>
+        </is>
+      </c>
+      <c r="O48" s="15" t="n">
+        <v>24238.5</v>
+      </c>
+      <c r="P48" s="15" t="n">
+        <v>24334.3</v>
+      </c>
+      <c r="Q48" s="15" t="inlineStr">
+        <is>
+          <t>24300 PE</t>
+        </is>
+      </c>
+      <c r="R48" s="15" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="S48" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="T48" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U48" s="15" t="n">
+        <v>1885</v>
+      </c>
+      <c r="V48" s="15" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="W48" s="15" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="X48" s="15" t="n">
+        <v>48633</v>
+      </c>
+      <c r="Y48" s="15" t="n">
+        <v>48687.85</v>
+      </c>
+      <c r="Z48" s="15" t="n">
+        <v>139867</v>
+      </c>
+      <c r="AA48" s="15" t="n">
+        <v>14589.9</v>
+      </c>
+      <c r="AB48" s="15" t="n">
+        <v>14589.9</v>
+      </c>
+      <c r="AC48" s="15" t="n">
+        <v>-14589.9</v>
+      </c>
+      <c r="AD48" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE48" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF48" s="15" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="AG48" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH48" s="15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI48" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ48" s="15" t="n">
+        <v>54.85</v>
+      </c>
+      <c r="AK48" s="15" t="n">
+        <v>-14644.75</v>
+      </c>
+      <c r="AL48" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM48" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN48" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -60741,7 +61987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN92"/>
+  <dimension ref="A1:AN94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -74584,6 +75830,310 @@
         <v>50000</v>
       </c>
       <c r="AN92" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B93" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C93" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D93" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E93" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F93" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G93" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H93" s="16" t="n">
+        <v>24164.16</v>
+      </c>
+      <c r="I93" s="16" t="n">
+        <v>24047.1</v>
+      </c>
+      <c r="J93" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K93" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L93" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M93" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N93" s="16" t="inlineStr">
+        <is>
+          <t>14:42 IST</t>
+        </is>
+      </c>
+      <c r="O93" s="16" t="n">
+        <v>24238.5</v>
+      </c>
+      <c r="P93" s="16" t="n">
+        <v>24334.3</v>
+      </c>
+      <c r="Q93" s="16" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="R93" s="16" t="inlineStr">
+        <is>
+          <t>24300 CE</t>
+        </is>
+      </c>
+      <c r="S93" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T93" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U93" s="16" t="n">
+        <v>1300</v>
+      </c>
+      <c r="V93" s="16" t="n">
+        <v>37.17</v>
+      </c>
+      <c r="W93" s="16" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="X93" s="16" t="n">
+        <v>48321</v>
+      </c>
+      <c r="Y93" s="16" t="n">
+        <v>48375.8</v>
+      </c>
+      <c r="Z93" s="16" t="n">
+        <v>81679</v>
+      </c>
+      <c r="AA93" s="16" t="n">
+        <v>14496.3</v>
+      </c>
+      <c r="AB93" s="16" t="n">
+        <v>14496.3</v>
+      </c>
+      <c r="AC93" s="16" t="n">
+        <v>-39</v>
+      </c>
+      <c r="AD93" s="16" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AE93" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF93" s="16" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="AG93" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH93" s="16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI93" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ93" s="16" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="AK93" s="16" t="n">
+        <v>-93.8</v>
+      </c>
+      <c r="AL93" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM93" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN93" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B94" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C94" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D94" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E94" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F94" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G94" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H94" s="15" t="n">
+        <v>24164.16</v>
+      </c>
+      <c r="I94" s="15" t="n">
+        <v>24047.1</v>
+      </c>
+      <c r="J94" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K94" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L94" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M94" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N94" s="15" t="inlineStr">
+        <is>
+          <t>10:16 IST</t>
+        </is>
+      </c>
+      <c r="O94" s="15" t="n">
+        <v>24238.5</v>
+      </c>
+      <c r="P94" s="15" t="n">
+        <v>24334.3</v>
+      </c>
+      <c r="Q94" s="15" t="inlineStr">
+        <is>
+          <t>24300 PE</t>
+        </is>
+      </c>
+      <c r="R94" s="15" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="S94" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="T94" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U94" s="15" t="n">
+        <v>1430</v>
+      </c>
+      <c r="V94" s="15" t="n">
+        <v>34.08</v>
+      </c>
+      <c r="W94" s="15" t="n">
+        <v>23.86</v>
+      </c>
+      <c r="X94" s="15" t="n">
+        <v>48734.4</v>
+      </c>
+      <c r="Y94" s="15" t="n">
+        <v>48789.27</v>
+      </c>
+      <c r="Z94" s="15" t="n">
+        <v>94265.60000000001</v>
+      </c>
+      <c r="AA94" s="15" t="n">
+        <v>14620.32</v>
+      </c>
+      <c r="AB94" s="15" t="n">
+        <v>14620.32</v>
+      </c>
+      <c r="AC94" s="15" t="n">
+        <v>-14614.6</v>
+      </c>
+      <c r="AD94" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE94" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF94" s="15" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="AG94" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH94" s="15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI94" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ94" s="15" t="n">
+        <v>54.87</v>
+      </c>
+      <c r="AK94" s="15" t="n">
+        <v>-14669.47</v>
+      </c>
+      <c r="AL94" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM94" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN94" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA48"/>
+  <dimension ref="A1:AA49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5334,6 +5334,105 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D49" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="F49" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G49" s="17" t="inlineStr">
+        <is>
+          <t>10:49 ET</t>
+        </is>
+      </c>
+      <c r="H49" s="17" t="n">
+        <v>29112.25</v>
+      </c>
+      <c r="I49" s="17" t="n">
+        <v>29100</v>
+      </c>
+      <c r="J49" s="17" t="n">
+        <v>29125</v>
+      </c>
+      <c r="K49" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L49" s="17" t="n">
+        <v>207.18</v>
+      </c>
+      <c r="M49" s="17" t="n">
+        <v>269.33</v>
+      </c>
+      <c r="N49" s="17" t="n">
+        <v>858.3200000000001</v>
+      </c>
+      <c r="O49" s="17" t="n">
+        <v>1171.28</v>
+      </c>
+      <c r="P49" s="17" t="n">
+        <v>248.62</v>
+      </c>
+      <c r="Q49" s="17" t="n">
+        <v>248.62</v>
+      </c>
+      <c r="R49" s="17" t="n">
+        <v>248.6</v>
+      </c>
+      <c r="S49" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T49" s="17" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="U49" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="V49" s="17" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W49" s="17" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="X49" s="17" t="n">
+        <v>219</v>
+      </c>
+      <c r="Y49" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z49" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA49" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -5348,7 +5447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN48"/>
+  <dimension ref="A1:AN49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12548,6 +12647,158 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D49" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E49" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F49" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G49" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H49" s="17" t="n">
+        <v>57869.66</v>
+      </c>
+      <c r="I49" s="17" t="n">
+        <v>57689.18</v>
+      </c>
+      <c r="J49" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K49" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L49" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="M49" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N49" s="17" t="inlineStr">
+        <is>
+          <t>12:02 IST</t>
+        </is>
+      </c>
+      <c r="O49" s="17" t="n">
+        <v>57840.45</v>
+      </c>
+      <c r="P49" s="17" t="n">
+        <v>57945</v>
+      </c>
+      <c r="Q49" s="17" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="R49" s="17" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="S49" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="T49" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U49" s="17" t="n">
+        <v>540</v>
+      </c>
+      <c r="V49" s="17" t="n">
+        <v>90.56999999999999</v>
+      </c>
+      <c r="W49" s="17" t="n">
+        <v>117.74</v>
+      </c>
+      <c r="X49" s="17" t="n">
+        <v>48907.8</v>
+      </c>
+      <c r="Y49" s="17" t="n">
+        <v>48962.7</v>
+      </c>
+      <c r="Z49" s="17" t="n">
+        <v>59092.2</v>
+      </c>
+      <c r="AA49" s="17" t="n">
+        <v>14672.34</v>
+      </c>
+      <c r="AB49" s="17" t="n">
+        <v>14672.34</v>
+      </c>
+      <c r="AC49" s="17" t="n">
+        <v>14671.8</v>
+      </c>
+      <c r="AD49" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE49" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF49" s="17" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="AG49" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH49" s="17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI49" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ49" s="17" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="AK49" s="17" t="n">
+        <v>14616.9</v>
+      </c>
+      <c r="AL49" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM49" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN49" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -12562,7 +12813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN48"/>
+  <dimension ref="A1:AN49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -19762,6 +20013,158 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E49" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F49" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G49" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>57869.66</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>57689.18</v>
+      </c>
+      <c r="J49" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K49" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L49" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="M49" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N49" s="15" t="inlineStr">
+        <is>
+          <t>10:22 IST</t>
+        </is>
+      </c>
+      <c r="O49" s="15" t="n">
+        <v>57840.45</v>
+      </c>
+      <c r="P49" s="15" t="n">
+        <v>57945</v>
+      </c>
+      <c r="Q49" s="15" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="R49" s="15" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="S49" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="T49" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U49" s="15" t="n">
+        <v>540</v>
+      </c>
+      <c r="V49" s="15" t="n">
+        <v>86.95999999999999</v>
+      </c>
+      <c r="W49" s="15" t="n">
+        <v>60.87</v>
+      </c>
+      <c r="X49" s="15" t="n">
+        <v>46958.4</v>
+      </c>
+      <c r="Y49" s="15" t="n">
+        <v>47012.99</v>
+      </c>
+      <c r="Z49" s="15" t="n">
+        <v>61041.6</v>
+      </c>
+      <c r="AA49" s="15" t="n">
+        <v>14087.52</v>
+      </c>
+      <c r="AB49" s="15" t="n">
+        <v>14087.52</v>
+      </c>
+      <c r="AC49" s="15" t="n">
+        <v>-14088.6</v>
+      </c>
+      <c r="AD49" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE49" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF49" s="15" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="AG49" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH49" s="15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI49" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ49" s="15" t="n">
+        <v>54.59</v>
+      </c>
+      <c r="AK49" s="15" t="n">
+        <v>-14143.19</v>
+      </c>
+      <c r="AL49" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM49" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN49" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -19776,7 +20179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN94"/>
+  <dimension ref="A1:AN96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -33923,6 +34326,310 @@
         <v>50000</v>
       </c>
       <c r="AN94" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B95" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C95" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D95" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E95" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F95" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G95" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H95" s="17" t="n">
+        <v>57869.66</v>
+      </c>
+      <c r="I95" s="17" t="n">
+        <v>57689.18</v>
+      </c>
+      <c r="J95" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K95" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L95" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="M95" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N95" s="17" t="inlineStr">
+        <is>
+          <t>11:57 IST</t>
+        </is>
+      </c>
+      <c r="O95" s="17" t="n">
+        <v>57840.45</v>
+      </c>
+      <c r="P95" s="17" t="n">
+        <v>57945</v>
+      </c>
+      <c r="Q95" s="17" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="R95" s="17" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="S95" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="T95" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U95" s="17" t="n">
+        <v>660</v>
+      </c>
+      <c r="V95" s="17" t="n">
+        <v>72.34</v>
+      </c>
+      <c r="W95" s="17" t="n">
+        <v>94.04000000000001</v>
+      </c>
+      <c r="X95" s="17" t="n">
+        <v>47744.4</v>
+      </c>
+      <c r="Y95" s="17" t="n">
+        <v>47799.11</v>
+      </c>
+      <c r="Z95" s="17" t="n">
+        <v>84255.60000000001</v>
+      </c>
+      <c r="AA95" s="17" t="n">
+        <v>14323.32</v>
+      </c>
+      <c r="AB95" s="17" t="n">
+        <v>14323.32</v>
+      </c>
+      <c r="AC95" s="17" t="n">
+        <v>14322</v>
+      </c>
+      <c r="AD95" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE95" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF95" s="17" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="AG95" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH95" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI95" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ95" s="17" t="n">
+        <v>54.71</v>
+      </c>
+      <c r="AK95" s="17" t="n">
+        <v>14267.29</v>
+      </c>
+      <c r="AL95" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM95" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN95" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B96" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C96" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D96" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E96" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F96" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G96" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H96" s="16" t="n">
+        <v>57869.66</v>
+      </c>
+      <c r="I96" s="16" t="n">
+        <v>57689.18</v>
+      </c>
+      <c r="J96" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K96" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L96" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="M96" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N96" s="16" t="inlineStr">
+        <is>
+          <t>14:02 IST</t>
+        </is>
+      </c>
+      <c r="O96" s="16" t="n">
+        <v>57840.45</v>
+      </c>
+      <c r="P96" s="16" t="n">
+        <v>57945</v>
+      </c>
+      <c r="Q96" s="16" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="R96" s="16" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="S96" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T96" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U96" s="16" t="n">
+        <v>600</v>
+      </c>
+      <c r="V96" s="16" t="n">
+        <v>81.62</v>
+      </c>
+      <c r="W96" s="16" t="n">
+        <v>78.28</v>
+      </c>
+      <c r="X96" s="16" t="n">
+        <v>48972</v>
+      </c>
+      <c r="Y96" s="16" t="n">
+        <v>49026.91</v>
+      </c>
+      <c r="Z96" s="16" t="n">
+        <v>71028</v>
+      </c>
+      <c r="AA96" s="16" t="n">
+        <v>14691.6</v>
+      </c>
+      <c r="AB96" s="16" t="n">
+        <v>14691.6</v>
+      </c>
+      <c r="AC96" s="16" t="n">
+        <v>-2004</v>
+      </c>
+      <c r="AD96" s="16" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="AE96" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF96" s="16" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="AG96" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH96" s="16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI96" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ96" s="16" t="n">
+        <v>54.91</v>
+      </c>
+      <c r="AK96" s="16" t="n">
+        <v>-2058.91</v>
+      </c>
+      <c r="AL96" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM96" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN96" s="16" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -37376,7 +38083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -38945,6 +39652,72 @@
         <v>57620.05</v>
       </c>
       <c r="G48" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B49" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D49" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E49" s="18" t="n">
+        <v>24164.13</v>
+      </c>
+      <c r="F49" s="18" t="n">
+        <v>24071.86</v>
+      </c>
+      <c r="G49" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E50" s="18" t="n">
+        <v>57869.66</v>
+      </c>
+      <c r="F50" s="18" t="n">
+        <v>57689.18</v>
+      </c>
+      <c r="G50" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -38964,7 +39737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA48"/>
+  <dimension ref="A1:AA49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -43689,6 +44462,105 @@
         <v>1000</v>
       </c>
       <c r="AA48" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>31</v>
+      </c>
+      <c r="F49" s="15" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G49" s="15" t="inlineStr">
+        <is>
+          <t>12:13 ET</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>29113.25</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>29100</v>
+      </c>
+      <c r="J49" s="15" t="n">
+        <v>29125</v>
+      </c>
+      <c r="K49" s="15" t="n">
+        <v>41</v>
+      </c>
+      <c r="L49" s="15" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="M49" s="15" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="N49" s="15" t="n">
+        <v>987.6900000000001</v>
+      </c>
+      <c r="O49" s="15" t="n">
+        <v>1129.55</v>
+      </c>
+      <c r="P49" s="15" t="n">
+        <v>276.13</v>
+      </c>
+      <c r="Q49" s="15" t="n">
+        <v>276.13</v>
+      </c>
+      <c r="R49" s="15" t="n">
+        <v>-276.34</v>
+      </c>
+      <c r="S49" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="T49" s="15" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="U49" s="15" t="n">
+        <v>41</v>
+      </c>
+      <c r="V49" s="15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W49" s="15" t="n">
+        <v>67.23999999999999</v>
+      </c>
+      <c r="X49" s="15" t="n">
+        <v>-343.58</v>
+      </c>
+      <c r="Y49" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="Z49" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA49" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -43808,7 +44680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:I96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -47091,6 +47963,76 @@
         <v>70.52</v>
       </c>
       <c r="I94" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — STOP LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B95" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C95" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D95" s="19" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="E95" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F95" s="19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G95" s="19" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H95" s="19" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I95" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B96" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C96" s="19" t="n">
+        <v>41</v>
+      </c>
+      <c r="D96" s="19" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="E96" s="19" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F96" s="19" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G96" s="19" t="n">
+        <v>33.62</v>
+      </c>
+      <c r="H96" s="19" t="n">
+        <v>67.23999999999999</v>
+      </c>
+      <c r="I96" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — STOP LOSS</t>
         </is>
@@ -47559,7 +48501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN48"/>
+  <dimension ref="A1:AN49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -54759,6 +55701,158 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D49" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E49" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F49" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G49" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H49" s="17" t="n">
+        <v>24164.13</v>
+      </c>
+      <c r="I49" s="17" t="n">
+        <v>24071.86</v>
+      </c>
+      <c r="J49" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K49" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L49" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M49" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N49" s="17" t="inlineStr">
+        <is>
+          <t>09:42 IST</t>
+        </is>
+      </c>
+      <c r="O49" s="17" t="n">
+        <v>24163.1</v>
+      </c>
+      <c r="P49" s="17" t="n">
+        <v>24238.5</v>
+      </c>
+      <c r="Q49" s="17" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="R49" s="17" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="S49" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="T49" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U49" s="17" t="n">
+        <v>2080</v>
+      </c>
+      <c r="V49" s="17" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="W49" s="17" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="X49" s="17" t="n">
+        <v>47361.6</v>
+      </c>
+      <c r="Y49" s="17" t="n">
+        <v>47416.25</v>
+      </c>
+      <c r="Z49" s="17" t="n">
+        <v>160638.4</v>
+      </c>
+      <c r="AA49" s="17" t="n">
+        <v>14208.48</v>
+      </c>
+      <c r="AB49" s="17" t="n">
+        <v>14208.48</v>
+      </c>
+      <c r="AC49" s="17" t="n">
+        <v>14206.4</v>
+      </c>
+      <c r="AD49" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE49" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF49" s="17" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="AG49" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH49" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI49" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ49" s="17" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="AK49" s="17" t="n">
+        <v>14151.75</v>
+      </c>
+      <c r="AL49" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM49" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN49" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -54773,7 +55867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN48"/>
+  <dimension ref="A1:AN49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -61973,6 +63067,158 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E49" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F49" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G49" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>24164.13</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>24071.86</v>
+      </c>
+      <c r="J49" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K49" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L49" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M49" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N49" s="15" t="inlineStr">
+        <is>
+          <t>09:33 IST</t>
+        </is>
+      </c>
+      <c r="O49" s="15" t="n">
+        <v>24163.1</v>
+      </c>
+      <c r="P49" s="15" t="n">
+        <v>24238.5</v>
+      </c>
+      <c r="Q49" s="15" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="R49" s="15" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="S49" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="T49" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U49" s="15" t="n">
+        <v>2405</v>
+      </c>
+      <c r="V49" s="15" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="W49" s="15" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="X49" s="15" t="n">
+        <v>48196.2</v>
+      </c>
+      <c r="Y49" s="15" t="n">
+        <v>48250.98</v>
+      </c>
+      <c r="Z49" s="15" t="n">
+        <v>192303.8</v>
+      </c>
+      <c r="AA49" s="15" t="n">
+        <v>14458.86</v>
+      </c>
+      <c r="AB49" s="15" t="n">
+        <v>14458.86</v>
+      </c>
+      <c r="AC49" s="15" t="n">
+        <v>-14454.05</v>
+      </c>
+      <c r="AD49" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE49" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF49" s="15" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="AG49" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH49" s="15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI49" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ49" s="15" t="n">
+        <v>54.78</v>
+      </c>
+      <c r="AK49" s="15" t="n">
+        <v>-14508.83</v>
+      </c>
+      <c r="AL49" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM49" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN49" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -61987,7 +63233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN94"/>
+  <dimension ref="A1:AN96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -76134,6 +77380,310 @@
         <v>50000</v>
       </c>
       <c r="AN94" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B95" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C95" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D95" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E95" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F95" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G95" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H95" s="17" t="n">
+        <v>24164.13</v>
+      </c>
+      <c r="I95" s="17" t="n">
+        <v>24071.86</v>
+      </c>
+      <c r="J95" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K95" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L95" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M95" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N95" s="17" t="inlineStr">
+        <is>
+          <t>10:36 IST</t>
+        </is>
+      </c>
+      <c r="O95" s="17" t="n">
+        <v>24163.1</v>
+      </c>
+      <c r="P95" s="17" t="n">
+        <v>24238.5</v>
+      </c>
+      <c r="Q95" s="17" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="R95" s="17" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="S95" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="T95" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U95" s="17" t="n">
+        <v>2990</v>
+      </c>
+      <c r="V95" s="17" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="W95" s="17" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="X95" s="17" t="n">
+        <v>48079.2</v>
+      </c>
+      <c r="Y95" s="17" t="n">
+        <v>48133.97</v>
+      </c>
+      <c r="Z95" s="17" t="n">
+        <v>250920.8</v>
+      </c>
+      <c r="AA95" s="17" t="n">
+        <v>14423.76</v>
+      </c>
+      <c r="AB95" s="17" t="n">
+        <v>14423.76</v>
+      </c>
+      <c r="AC95" s="17" t="n">
+        <v>14411.8</v>
+      </c>
+      <c r="AD95" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE95" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF95" s="17" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="AG95" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH95" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI95" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ95" s="17" t="n">
+        <v>54.77</v>
+      </c>
+      <c r="AK95" s="17" t="n">
+        <v>14357.03</v>
+      </c>
+      <c r="AL95" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM95" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN95" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B96" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C96" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D96" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E96" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F96" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G96" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H96" s="15" t="n">
+        <v>24164.13</v>
+      </c>
+      <c r="I96" s="15" t="n">
+        <v>24071.86</v>
+      </c>
+      <c r="J96" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K96" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L96" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M96" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N96" s="15" t="inlineStr">
+        <is>
+          <t>11:03 IST</t>
+        </is>
+      </c>
+      <c r="O96" s="15" t="n">
+        <v>24163.1</v>
+      </c>
+      <c r="P96" s="15" t="n">
+        <v>24238.5</v>
+      </c>
+      <c r="Q96" s="15" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="R96" s="15" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="S96" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="T96" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U96" s="15" t="n">
+        <v>1950</v>
+      </c>
+      <c r="V96" s="15" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="W96" s="15" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="X96" s="15" t="n">
+        <v>47853</v>
+      </c>
+      <c r="Y96" s="15" t="n">
+        <v>47907.73</v>
+      </c>
+      <c r="Z96" s="15" t="n">
+        <v>147147</v>
+      </c>
+      <c r="AA96" s="15" t="n">
+        <v>14355.9</v>
+      </c>
+      <c r="AB96" s="15" t="n">
+        <v>14355.9</v>
+      </c>
+      <c r="AC96" s="15" t="n">
+        <v>-14352</v>
+      </c>
+      <c r="AD96" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE96" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF96" s="15" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AG96" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH96" s="15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI96" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ96" s="15" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="AK96" s="15" t="n">
+        <v>-14406.73</v>
+      </c>
+      <c r="AL96" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM96" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN96" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA49"/>
+  <dimension ref="A1:AA50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5433,6 +5433,105 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="F50" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G50" s="17" t="inlineStr">
+        <is>
+          <t>12:25 ET</t>
+        </is>
+      </c>
+      <c r="H50" s="17" t="n">
+        <v>29292.25</v>
+      </c>
+      <c r="I50" s="17" t="n">
+        <v>29275</v>
+      </c>
+      <c r="J50" s="17" t="n">
+        <v>29300</v>
+      </c>
+      <c r="K50" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L50" s="17" t="n">
+        <v>250.08</v>
+      </c>
+      <c r="M50" s="17" t="n">
+        <v>325.1</v>
+      </c>
+      <c r="N50" s="17" t="n">
+        <v>772.4400000000001</v>
+      </c>
+      <c r="O50" s="17" t="n">
+        <v>749.76</v>
+      </c>
+      <c r="P50" s="17" t="n">
+        <v>225.07</v>
+      </c>
+      <c r="Q50" s="17" t="n">
+        <v>225.07</v>
+      </c>
+      <c r="R50" s="17" t="n">
+        <v>225.06</v>
+      </c>
+      <c r="S50" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T50" s="17" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="U50" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="V50" s="17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W50" s="17" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="X50" s="17" t="n">
+        <v>202.86</v>
+      </c>
+      <c r="Y50" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z50" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA50" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -5447,7 +5546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN49"/>
+  <dimension ref="A1:AN50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12799,6 +12898,158 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F50" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G50" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>57868.64</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>57688.71</v>
+      </c>
+      <c r="J50" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K50" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L50" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="M50" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N50" s="15" t="inlineStr">
+        <is>
+          <t>09:37 IST</t>
+        </is>
+      </c>
+      <c r="O50" s="15" t="n">
+        <v>57835.35</v>
+      </c>
+      <c r="P50" s="15" t="n">
+        <v>57945</v>
+      </c>
+      <c r="Q50" s="15" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="R50" s="15" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="S50" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="T50" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U50" s="15" t="n">
+        <v>510</v>
+      </c>
+      <c r="V50" s="15" t="n">
+        <v>94.04000000000001</v>
+      </c>
+      <c r="W50" s="15" t="n">
+        <v>65.83</v>
+      </c>
+      <c r="X50" s="15" t="n">
+        <v>47960.4</v>
+      </c>
+      <c r="Y50" s="15" t="n">
+        <v>48015.15</v>
+      </c>
+      <c r="Z50" s="15" t="n">
+        <v>54039.6</v>
+      </c>
+      <c r="AA50" s="15" t="n">
+        <v>14388.12</v>
+      </c>
+      <c r="AB50" s="15" t="n">
+        <v>14388.12</v>
+      </c>
+      <c r="AC50" s="15" t="n">
+        <v>-14387.1</v>
+      </c>
+      <c r="AD50" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE50" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF50" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG50" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH50" s="15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI50" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ50" s="15" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="AK50" s="15" t="n">
+        <v>-14441.85</v>
+      </c>
+      <c r="AL50" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM50" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN50" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -12813,7 +13064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN49"/>
+  <dimension ref="A1:AN50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -20165,6 +20416,158 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F50" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G50" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>57868.64</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>57688.71</v>
+      </c>
+      <c r="J50" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K50" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L50" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="M50" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N50" s="15" t="inlineStr">
+        <is>
+          <t>09:44 IST</t>
+        </is>
+      </c>
+      <c r="O50" s="15" t="n">
+        <v>57835.35</v>
+      </c>
+      <c r="P50" s="15" t="n">
+        <v>57945</v>
+      </c>
+      <c r="Q50" s="15" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="R50" s="15" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="S50" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="T50" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U50" s="15" t="n">
+        <v>660</v>
+      </c>
+      <c r="V50" s="15" t="n">
+        <v>73.28</v>
+      </c>
+      <c r="W50" s="15" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="X50" s="15" t="n">
+        <v>48364.8</v>
+      </c>
+      <c r="Y50" s="15" t="n">
+        <v>48419.61</v>
+      </c>
+      <c r="Z50" s="15" t="n">
+        <v>83635.2</v>
+      </c>
+      <c r="AA50" s="15" t="n">
+        <v>14509.44</v>
+      </c>
+      <c r="AB50" s="15" t="n">
+        <v>14509.44</v>
+      </c>
+      <c r="AC50" s="15" t="n">
+        <v>-14506.8</v>
+      </c>
+      <c r="AD50" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE50" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF50" s="15" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AG50" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH50" s="15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI50" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ50" s="15" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="AK50" s="15" t="n">
+        <v>-14561.61</v>
+      </c>
+      <c r="AL50" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM50" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN50" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -20179,7 +20582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN96"/>
+  <dimension ref="A1:AN98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -34630,6 +35033,310 @@
         <v>50000</v>
       </c>
       <c r="AN96" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B97" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C97" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D97" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E97" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F97" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G97" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H97" s="16" t="n">
+        <v>57868.64</v>
+      </c>
+      <c r="I97" s="16" t="n">
+        <v>57688.71</v>
+      </c>
+      <c r="J97" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K97" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L97" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="M97" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N97" s="16" t="inlineStr">
+        <is>
+          <t>13:25 IST</t>
+        </is>
+      </c>
+      <c r="O97" s="16" t="n">
+        <v>57835.35</v>
+      </c>
+      <c r="P97" s="16" t="n">
+        <v>57945</v>
+      </c>
+      <c r="Q97" s="16" t="inlineStr">
+        <is>
+          <t>57800 CE</t>
+        </is>
+      </c>
+      <c r="R97" s="16" t="inlineStr">
+        <is>
+          <t>58000 CE</t>
+        </is>
+      </c>
+      <c r="S97" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="T97" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U97" s="16" t="n">
+        <v>630</v>
+      </c>
+      <c r="V97" s="16" t="n">
+        <v>77.39</v>
+      </c>
+      <c r="W97" s="16" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="X97" s="16" t="n">
+        <v>48755.7</v>
+      </c>
+      <c r="Y97" s="16" t="n">
+        <v>48810.57</v>
+      </c>
+      <c r="Z97" s="16" t="n">
+        <v>77244.3</v>
+      </c>
+      <c r="AA97" s="16" t="n">
+        <v>14626.71</v>
+      </c>
+      <c r="AB97" s="16" t="n">
+        <v>14626.71</v>
+      </c>
+      <c r="AC97" s="16" t="n">
+        <v>1203.3</v>
+      </c>
+      <c r="AD97" s="16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE97" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF97" s="16" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="AG97" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH97" s="16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI97" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ97" s="16" t="n">
+        <v>54.87</v>
+      </c>
+      <c r="AK97" s="16" t="n">
+        <v>1148.43</v>
+      </c>
+      <c r="AL97" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM97" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN97" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B98" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C98" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D98" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E98" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F98" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G98" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H98" s="16" t="n">
+        <v>57868.64</v>
+      </c>
+      <c r="I98" s="16" t="n">
+        <v>57688.71</v>
+      </c>
+      <c r="J98" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K98" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L98" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="M98" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N98" s="16" t="inlineStr">
+        <is>
+          <t>15:17 IST</t>
+        </is>
+      </c>
+      <c r="O98" s="16" t="n">
+        <v>57835.35</v>
+      </c>
+      <c r="P98" s="16" t="n">
+        <v>57945</v>
+      </c>
+      <c r="Q98" s="16" t="inlineStr">
+        <is>
+          <t>58000 PE</t>
+        </is>
+      </c>
+      <c r="R98" s="16" t="inlineStr">
+        <is>
+          <t>57800 PE</t>
+        </is>
+      </c>
+      <c r="S98" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="T98" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U98" s="16" t="n">
+        <v>540</v>
+      </c>
+      <c r="V98" s="16" t="n">
+        <v>90.23</v>
+      </c>
+      <c r="W98" s="16" t="n">
+        <v>92.95</v>
+      </c>
+      <c r="X98" s="16" t="n">
+        <v>48724.2</v>
+      </c>
+      <c r="Y98" s="16" t="n">
+        <v>48779.07</v>
+      </c>
+      <c r="Z98" s="16" t="n">
+        <v>59275.8</v>
+      </c>
+      <c r="AA98" s="16" t="n">
+        <v>14617.26</v>
+      </c>
+      <c r="AB98" s="16" t="n">
+        <v>14617.26</v>
+      </c>
+      <c r="AC98" s="16" t="n">
+        <v>1468.8</v>
+      </c>
+      <c r="AD98" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE98" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF98" s="16" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="AG98" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH98" s="16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI98" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ98" s="16" t="n">
+        <v>54.87</v>
+      </c>
+      <c r="AK98" s="16" t="n">
+        <v>1413.93</v>
+      </c>
+      <c r="AL98" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM98" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN98" s="16" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -38083,7 +38790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -39718,6 +40425,72 @@
         <v>57689.18</v>
       </c>
       <c r="G50" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B51" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D51" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E51" s="18" t="n">
+        <v>24169.05</v>
+      </c>
+      <c r="F51" s="18" t="n">
+        <v>24074.1</v>
+      </c>
+      <c r="G51" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D52" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E52" s="18" t="n">
+        <v>57868.64</v>
+      </c>
+      <c r="F52" s="18" t="n">
+        <v>57688.71</v>
+      </c>
+      <c r="G52" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -39737,7 +40510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA49"/>
+  <dimension ref="A1:AA50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -44561,6 +45334,105 @@
         <v>1000</v>
       </c>
       <c r="AA49" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="F50" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G50" s="17" t="inlineStr">
+        <is>
+          <t>12:39 ET</t>
+        </is>
+      </c>
+      <c r="H50" s="17" t="n">
+        <v>29292.25</v>
+      </c>
+      <c r="I50" s="17" t="n">
+        <v>29275</v>
+      </c>
+      <c r="J50" s="17" t="n">
+        <v>29300</v>
+      </c>
+      <c r="K50" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="L50" s="17" t="n">
+        <v>26.73</v>
+      </c>
+      <c r="M50" s="17" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="N50" s="17" t="n">
+        <v>992.95</v>
+      </c>
+      <c r="O50" s="17" t="n">
+        <v>814.45</v>
+      </c>
+      <c r="P50" s="17" t="n">
+        <v>280.66</v>
+      </c>
+      <c r="Q50" s="17" t="n">
+        <v>280.66</v>
+      </c>
+      <c r="R50" s="17" t="n">
+        <v>280.7</v>
+      </c>
+      <c r="S50" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T50" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="U50" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="V50" s="17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W50" s="17" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="X50" s="17" t="n">
+        <v>223.3</v>
+      </c>
+      <c r="Y50" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z50" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA50" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -44680,7 +45552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I96"/>
+  <dimension ref="A1:I98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48035,6 +48907,76 @@
       <c r="I96" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — STOP LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B97" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C97" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D97" s="19" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="E97" s="19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F97" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G97" s="19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H97" s="19" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="I97" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B98" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C98" s="19" t="n">
+        <v>35</v>
+      </c>
+      <c r="D98" s="19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E98" s="19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F98" s="19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G98" s="19" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="H98" s="19" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="I98" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — PROFIT</t>
         </is>
       </c>
     </row>
@@ -48501,7 +49443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN49"/>
+  <dimension ref="A1:AN50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -55853,6 +56795,158 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F50" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G50" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>24169.05</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>24074.1</v>
+      </c>
+      <c r="J50" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K50" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L50" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M50" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N50" s="15" t="inlineStr">
+        <is>
+          <t>10:20 IST</t>
+        </is>
+      </c>
+      <c r="O50" s="15" t="n">
+        <v>24187.7</v>
+      </c>
+      <c r="P50" s="15" t="n">
+        <v>24238.5</v>
+      </c>
+      <c r="Q50" s="15" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="R50" s="15" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="S50" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="T50" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U50" s="15" t="n">
+        <v>2275</v>
+      </c>
+      <c r="V50" s="15" t="n">
+        <v>20.98</v>
+      </c>
+      <c r="W50" s="15" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="X50" s="15" t="n">
+        <v>47729.5</v>
+      </c>
+      <c r="Y50" s="15" t="n">
+        <v>47784.21</v>
+      </c>
+      <c r="Z50" s="15" t="n">
+        <v>179770.5</v>
+      </c>
+      <c r="AA50" s="15" t="n">
+        <v>14318.85</v>
+      </c>
+      <c r="AB50" s="15" t="n">
+        <v>14318.85</v>
+      </c>
+      <c r="AC50" s="15" t="n">
+        <v>-14309.75</v>
+      </c>
+      <c r="AD50" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE50" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF50" s="15" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="AG50" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH50" s="15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI50" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ50" s="15" t="n">
+        <v>54.71</v>
+      </c>
+      <c r="AK50" s="15" t="n">
+        <v>-14364.46</v>
+      </c>
+      <c r="AL50" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM50" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN50" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -55867,7 +56961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN49"/>
+  <dimension ref="A1:AN50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -63219,6 +64313,158 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F50" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G50" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>24169.05</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>24074.1</v>
+      </c>
+      <c r="J50" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K50" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L50" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M50" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N50" s="15" t="inlineStr">
+        <is>
+          <t>10:52 IST</t>
+        </is>
+      </c>
+      <c r="O50" s="15" t="n">
+        <v>24187.7</v>
+      </c>
+      <c r="P50" s="15" t="n">
+        <v>24238.5</v>
+      </c>
+      <c r="Q50" s="15" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="R50" s="15" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="S50" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="T50" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U50" s="15" t="n">
+        <v>2405</v>
+      </c>
+      <c r="V50" s="15" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="W50" s="15" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="X50" s="15" t="n">
+        <v>47739.25</v>
+      </c>
+      <c r="Y50" s="15" t="n">
+        <v>47793.96</v>
+      </c>
+      <c r="Z50" s="15" t="n">
+        <v>192760.75</v>
+      </c>
+      <c r="AA50" s="15" t="n">
+        <v>14321.77</v>
+      </c>
+      <c r="AB50" s="15" t="n">
+        <v>14321.77</v>
+      </c>
+      <c r="AC50" s="15" t="n">
+        <v>-14333.8</v>
+      </c>
+      <c r="AD50" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE50" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF50" s="15" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="AG50" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH50" s="15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI50" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ50" s="15" t="n">
+        <v>54.71</v>
+      </c>
+      <c r="AK50" s="15" t="n">
+        <v>-14388.51</v>
+      </c>
+      <c r="AL50" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM50" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN50" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -63233,7 +64479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN96"/>
+  <dimension ref="A1:AN98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -77684,6 +78930,310 @@
         <v>50000</v>
       </c>
       <c r="AN96" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B97" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C97" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D97" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E97" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F97" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G97" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H97" s="17" t="n">
+        <v>24169.05</v>
+      </c>
+      <c r="I97" s="17" t="n">
+        <v>24074.1</v>
+      </c>
+      <c r="J97" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K97" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L97" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M97" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N97" s="17" t="inlineStr">
+        <is>
+          <t>11:20 IST</t>
+        </is>
+      </c>
+      <c r="O97" s="17" t="n">
+        <v>24187.7</v>
+      </c>
+      <c r="P97" s="17" t="n">
+        <v>24238.5</v>
+      </c>
+      <c r="Q97" s="17" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="R97" s="17" t="inlineStr">
+        <is>
+          <t>24200 CE</t>
+        </is>
+      </c>
+      <c r="S97" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="T97" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U97" s="17" t="n">
+        <v>2665</v>
+      </c>
+      <c r="V97" s="17" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="W97" s="17" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="X97" s="17" t="n">
+        <v>48236.5</v>
+      </c>
+      <c r="Y97" s="17" t="n">
+        <v>48291.29</v>
+      </c>
+      <c r="Z97" s="17" t="n">
+        <v>218263.5</v>
+      </c>
+      <c r="AA97" s="17" t="n">
+        <v>14470.95</v>
+      </c>
+      <c r="AB97" s="17" t="n">
+        <v>14470.95</v>
+      </c>
+      <c r="AC97" s="17" t="n">
+        <v>14470.95</v>
+      </c>
+      <c r="AD97" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE97" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF97" s="17" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AG97" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH97" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI97" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ97" s="17" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="AK97" s="17" t="n">
+        <v>14416.16</v>
+      </c>
+      <c r="AL97" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM97" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN97" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B98" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C98" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D98" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E98" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F98" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G98" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H98" s="15" t="n">
+        <v>24169.05</v>
+      </c>
+      <c r="I98" s="15" t="n">
+        <v>24074.1</v>
+      </c>
+      <c r="J98" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K98" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L98" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M98" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N98" s="15" t="inlineStr">
+        <is>
+          <t>10:30 IST</t>
+        </is>
+      </c>
+      <c r="O98" s="15" t="n">
+        <v>24187.7</v>
+      </c>
+      <c r="P98" s="15" t="n">
+        <v>24238.5</v>
+      </c>
+      <c r="Q98" s="15" t="inlineStr">
+        <is>
+          <t>24200 PE</t>
+        </is>
+      </c>
+      <c r="R98" s="15" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="S98" s="15" t="n">
+        <v>48</v>
+      </c>
+      <c r="T98" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U98" s="15" t="n">
+        <v>3120</v>
+      </c>
+      <c r="V98" s="15" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="W98" s="15" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="X98" s="15" t="n">
+        <v>47299.2</v>
+      </c>
+      <c r="Y98" s="15" t="n">
+        <v>47353.84</v>
+      </c>
+      <c r="Z98" s="15" t="n">
+        <v>264700.8</v>
+      </c>
+      <c r="AA98" s="15" t="n">
+        <v>14189.76</v>
+      </c>
+      <c r="AB98" s="15" t="n">
+        <v>14189.76</v>
+      </c>
+      <c r="AC98" s="15" t="n">
+        <v>-14196</v>
+      </c>
+      <c r="AD98" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE98" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF98" s="15" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AG98" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH98" s="15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI98" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ98" s="15" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="AK98" s="15" t="n">
+        <v>-14250.64</v>
+      </c>
+      <c r="AL98" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM98" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN98" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA50"/>
+  <dimension ref="A1:AA51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5532,6 +5532,105 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D51" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="F51" s="15" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G51" s="15" t="inlineStr">
+        <is>
+          <t>12:36 ET</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>29132.75</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>29125</v>
+      </c>
+      <c r="J51" s="15" t="n">
+        <v>29150</v>
+      </c>
+      <c r="K51" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="L51" s="15" t="n">
+        <v>235.62</v>
+      </c>
+      <c r="M51" s="15" t="n">
+        <v>164.93</v>
+      </c>
+      <c r="N51" s="15" t="n">
+        <v>972.08</v>
+      </c>
+      <c r="O51" s="15" t="n">
+        <v>1057.52</v>
+      </c>
+      <c r="P51" s="15" t="n">
+        <v>282.74</v>
+      </c>
+      <c r="Q51" s="15" t="n">
+        <v>282.74</v>
+      </c>
+      <c r="R51" s="15" t="n">
+        <v>-282.76</v>
+      </c>
+      <c r="S51" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="T51" s="15" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="U51" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="V51" s="15" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W51" s="15" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="X51" s="15" t="n">
+        <v>-312.36</v>
+      </c>
+      <c r="Y51" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="Z51" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA51" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -5546,7 +5645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN50"/>
+  <dimension ref="A1:AN51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13050,6 +13149,158 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D51" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E51" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F51" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G51" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>57751.03</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>57689.93</v>
+      </c>
+      <c r="J51" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K51" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L51" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="M51" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N51" s="15" t="inlineStr">
+        <is>
+          <t>10:18 IST</t>
+        </is>
+      </c>
+      <c r="O51" s="15" t="n">
+        <v>57269.65</v>
+      </c>
+      <c r="P51" s="15" t="n">
+        <v>57835.35</v>
+      </c>
+      <c r="Q51" s="15" t="inlineStr">
+        <is>
+          <t>57200 CE</t>
+        </is>
+      </c>
+      <c r="R51" s="15" t="inlineStr">
+        <is>
+          <t>57400 CE</t>
+        </is>
+      </c>
+      <c r="S51" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="T51" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U51" s="15" t="n">
+        <v>510</v>
+      </c>
+      <c r="V51" s="15" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="W51" s="15" t="n">
+        <v>66.43000000000001</v>
+      </c>
+      <c r="X51" s="15" t="n">
+        <v>48399</v>
+      </c>
+      <c r="Y51" s="15" t="n">
+        <v>48453.82</v>
+      </c>
+      <c r="Z51" s="15" t="n">
+        <v>53601</v>
+      </c>
+      <c r="AA51" s="15" t="n">
+        <v>14519.7</v>
+      </c>
+      <c r="AB51" s="15" t="n">
+        <v>14519.7</v>
+      </c>
+      <c r="AC51" s="15" t="n">
+        <v>-14519.7</v>
+      </c>
+      <c r="AD51" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE51" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF51" s="15" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AG51" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH51" s="15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI51" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ51" s="15" t="n">
+        <v>54.82</v>
+      </c>
+      <c r="AK51" s="15" t="n">
+        <v>-14574.52</v>
+      </c>
+      <c r="AL51" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM51" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN51" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -13064,7 +13315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN50"/>
+  <dimension ref="A1:AN51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -20568,6 +20819,158 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C51" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D51" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E51" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F51" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G51" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H51" s="17" t="n">
+        <v>57751.03</v>
+      </c>
+      <c r="I51" s="17" t="n">
+        <v>57689.93</v>
+      </c>
+      <c r="J51" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K51" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L51" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="M51" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N51" s="17" t="inlineStr">
+        <is>
+          <t>11:27 IST</t>
+        </is>
+      </c>
+      <c r="O51" s="17" t="n">
+        <v>57269.65</v>
+      </c>
+      <c r="P51" s="17" t="n">
+        <v>57835.35</v>
+      </c>
+      <c r="Q51" s="17" t="inlineStr">
+        <is>
+          <t>57400 PE</t>
+        </is>
+      </c>
+      <c r="R51" s="17" t="inlineStr">
+        <is>
+          <t>57200 PE</t>
+        </is>
+      </c>
+      <c r="S51" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T51" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U51" s="17" t="n">
+        <v>600</v>
+      </c>
+      <c r="V51" s="17" t="n">
+        <v>78.79000000000001</v>
+      </c>
+      <c r="W51" s="17" t="n">
+        <v>102.43</v>
+      </c>
+      <c r="X51" s="17" t="n">
+        <v>47274</v>
+      </c>
+      <c r="Y51" s="17" t="n">
+        <v>47328.64</v>
+      </c>
+      <c r="Z51" s="17" t="n">
+        <v>72726</v>
+      </c>
+      <c r="AA51" s="17" t="n">
+        <v>14182.2</v>
+      </c>
+      <c r="AB51" s="17" t="n">
+        <v>14182.2</v>
+      </c>
+      <c r="AC51" s="17" t="n">
+        <v>14184</v>
+      </c>
+      <c r="AD51" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE51" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF51" s="17" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AG51" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH51" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI51" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ51" s="17" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="AK51" s="17" t="n">
+        <v>14129.36</v>
+      </c>
+      <c r="AL51" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM51" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN51" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -20582,7 +20985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN98"/>
+  <dimension ref="A1:AN100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -35337,6 +35740,310 @@
         <v>50000</v>
       </c>
       <c r="AN98" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B99" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C99" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D99" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E99" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F99" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G99" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H99" s="17" t="n">
+        <v>57751.03</v>
+      </c>
+      <c r="I99" s="17" t="n">
+        <v>57689.93</v>
+      </c>
+      <c r="J99" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K99" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L99" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="M99" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N99" s="17" t="inlineStr">
+        <is>
+          <t>12:16 IST</t>
+        </is>
+      </c>
+      <c r="O99" s="17" t="n">
+        <v>57269.65</v>
+      </c>
+      <c r="P99" s="17" t="n">
+        <v>57835.35</v>
+      </c>
+      <c r="Q99" s="17" t="inlineStr">
+        <is>
+          <t>57200 CE</t>
+        </is>
+      </c>
+      <c r="R99" s="17" t="inlineStr">
+        <is>
+          <t>57400 CE</t>
+        </is>
+      </c>
+      <c r="S99" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="T99" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U99" s="17" t="n">
+        <v>540</v>
+      </c>
+      <c r="V99" s="17" t="n">
+        <v>87.64</v>
+      </c>
+      <c r="W99" s="17" t="n">
+        <v>113.93</v>
+      </c>
+      <c r="X99" s="17" t="n">
+        <v>47325.6</v>
+      </c>
+      <c r="Y99" s="17" t="n">
+        <v>47380.25</v>
+      </c>
+      <c r="Z99" s="17" t="n">
+        <v>60674.4</v>
+      </c>
+      <c r="AA99" s="17" t="n">
+        <v>14197.68</v>
+      </c>
+      <c r="AB99" s="17" t="n">
+        <v>14197.68</v>
+      </c>
+      <c r="AC99" s="17" t="n">
+        <v>14196.6</v>
+      </c>
+      <c r="AD99" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE99" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF99" s="17" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="AG99" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH99" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI99" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ99" s="17" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="AK99" s="17" t="n">
+        <v>14141.95</v>
+      </c>
+      <c r="AL99" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM99" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN99" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B100" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C100" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D100" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E100" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F100" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G100" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H100" s="17" t="n">
+        <v>57751.03</v>
+      </c>
+      <c r="I100" s="17" t="n">
+        <v>57689.93</v>
+      </c>
+      <c r="J100" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K100" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L100" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="M100" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N100" s="17" t="inlineStr">
+        <is>
+          <t>11:36 IST</t>
+        </is>
+      </c>
+      <c r="O100" s="17" t="n">
+        <v>57269.65</v>
+      </c>
+      <c r="P100" s="17" t="n">
+        <v>57835.35</v>
+      </c>
+      <c r="Q100" s="17" t="inlineStr">
+        <is>
+          <t>57400 PE</t>
+        </is>
+      </c>
+      <c r="R100" s="17" t="inlineStr">
+        <is>
+          <t>57200 PE</t>
+        </is>
+      </c>
+      <c r="S100" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="T100" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U100" s="17" t="n">
+        <v>540</v>
+      </c>
+      <c r="V100" s="17" t="n">
+        <v>88.51000000000001</v>
+      </c>
+      <c r="W100" s="17" t="n">
+        <v>115.06</v>
+      </c>
+      <c r="X100" s="17" t="n">
+        <v>47795.4</v>
+      </c>
+      <c r="Y100" s="17" t="n">
+        <v>47850.12</v>
+      </c>
+      <c r="Z100" s="17" t="n">
+        <v>60204.6</v>
+      </c>
+      <c r="AA100" s="17" t="n">
+        <v>14338.62</v>
+      </c>
+      <c r="AB100" s="17" t="n">
+        <v>14338.62</v>
+      </c>
+      <c r="AC100" s="17" t="n">
+        <v>14337</v>
+      </c>
+      <c r="AD100" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE100" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF100" s="17" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="AG100" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH100" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI100" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ100" s="17" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="AK100" s="17" t="n">
+        <v>14282.28</v>
+      </c>
+      <c r="AL100" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM100" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN100" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -38790,7 +39497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -40491,6 +41198,72 @@
         <v>57688.71</v>
       </c>
       <c r="G52" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B53" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D53" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E53" s="18" t="n">
+        <v>24145.08</v>
+      </c>
+      <c r="F53" s="18" t="n">
+        <v>24082.85</v>
+      </c>
+      <c r="G53" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D54" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E54" s="18" t="n">
+        <v>57751.03</v>
+      </c>
+      <c r="F54" s="18" t="n">
+        <v>57689.93</v>
+      </c>
+      <c r="G54" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -40510,7 +41283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA50"/>
+  <dimension ref="A1:AA51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -45433,6 +46206,105 @@
         <v>1000</v>
       </c>
       <c r="AA50" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D51" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="F51" s="15" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G51" s="15" t="inlineStr">
+        <is>
+          <t>12:47 ET</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>29134</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>29125</v>
+      </c>
+      <c r="J51" s="15" t="n">
+        <v>29150</v>
+      </c>
+      <c r="K51" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="L51" s="15" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="M51" s="15" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="N51" s="15" t="n">
+        <v>979.76</v>
+      </c>
+      <c r="O51" s="15" t="n">
+        <v>930.92</v>
+      </c>
+      <c r="P51" s="15" t="n">
+        <v>275.72</v>
+      </c>
+      <c r="Q51" s="15" t="n">
+        <v>275.72</v>
+      </c>
+      <c r="R51" s="15" t="n">
+        <v>-275.65</v>
+      </c>
+      <c r="S51" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="T51" s="15" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="U51" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="V51" s="15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W51" s="15" t="n">
+        <v>60.68</v>
+      </c>
+      <c r="X51" s="15" t="n">
+        <v>-336.33</v>
+      </c>
+      <c r="Y51" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="Z51" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA51" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -45552,7 +46424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I98"/>
+  <dimension ref="A1:I100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48977,6 +49849,76 @@
       <c r="I98" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B99" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C99" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D99" s="19" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="E99" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F99" s="19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G99" s="19" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H99" s="19" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I99" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — STOP LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B100" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C100" s="19" t="n">
+        <v>37</v>
+      </c>
+      <c r="D100" s="19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E100" s="19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F100" s="19" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G100" s="19" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="H100" s="19" t="n">
+        <v>60.68</v>
+      </c>
+      <c r="I100" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — STOP LOSS</t>
         </is>
       </c>
     </row>
@@ -49443,7 +50385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN50"/>
+  <dimension ref="A1:AN51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -56947,6 +57889,158 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B51" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D51" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E51" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F51" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G51" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H51" s="16" t="n">
+        <v>24145.08</v>
+      </c>
+      <c r="I51" s="16" t="n">
+        <v>24082.85</v>
+      </c>
+      <c r="J51" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K51" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L51" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N51" s="16" t="inlineStr">
+        <is>
+          <t>13:27 IST</t>
+        </is>
+      </c>
+      <c r="O51" s="16" t="n">
+        <v>24045.55</v>
+      </c>
+      <c r="P51" s="16" t="n">
+        <v>24187.7</v>
+      </c>
+      <c r="Q51" s="16" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="R51" s="16" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="S51" s="16" t="n">
+        <v>37</v>
+      </c>
+      <c r="T51" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U51" s="16" t="n">
+        <v>2405</v>
+      </c>
+      <c r="V51" s="16" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="W51" s="16" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="X51" s="16" t="n">
+        <v>47330.4</v>
+      </c>
+      <c r="Y51" s="16" t="n">
+        <v>47385.05</v>
+      </c>
+      <c r="Z51" s="16" t="n">
+        <v>193169.6</v>
+      </c>
+      <c r="AA51" s="16" t="n">
+        <v>14199.12</v>
+      </c>
+      <c r="AB51" s="16" t="n">
+        <v>14199.12</v>
+      </c>
+      <c r="AC51" s="16" t="n">
+        <v>-1130.35</v>
+      </c>
+      <c r="AD51" s="16" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="AE51" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF51" s="16" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="AG51" s="16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH51" s="16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI51" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ51" s="16" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="AK51" s="16" t="n">
+        <v>-1185</v>
+      </c>
+      <c r="AL51" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM51" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN51" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -56961,7 +58055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN50"/>
+  <dimension ref="A1:AN51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -64465,6 +65559,158 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C51" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D51" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E51" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F51" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G51" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H51" s="17" t="n">
+        <v>24145.08</v>
+      </c>
+      <c r="I51" s="17" t="n">
+        <v>24082.85</v>
+      </c>
+      <c r="J51" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K51" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L51" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N51" s="17" t="inlineStr">
+        <is>
+          <t>10:17 IST</t>
+        </is>
+      </c>
+      <c r="O51" s="17" t="n">
+        <v>24045.55</v>
+      </c>
+      <c r="P51" s="17" t="n">
+        <v>24187.7</v>
+      </c>
+      <c r="Q51" s="17" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="R51" s="17" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="S51" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="T51" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U51" s="17" t="n">
+        <v>2340</v>
+      </c>
+      <c r="V51" s="17" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="W51" s="17" t="n">
+        <v>26.72</v>
+      </c>
+      <c r="X51" s="17" t="n">
+        <v>48087</v>
+      </c>
+      <c r="Y51" s="17" t="n">
+        <v>48141.77</v>
+      </c>
+      <c r="Z51" s="17" t="n">
+        <v>185913</v>
+      </c>
+      <c r="AA51" s="17" t="n">
+        <v>14426.1</v>
+      </c>
+      <c r="AB51" s="17" t="n">
+        <v>14426.1</v>
+      </c>
+      <c r="AC51" s="17" t="n">
+        <v>14437.8</v>
+      </c>
+      <c r="AD51" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE51" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF51" s="17" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="AG51" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH51" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI51" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ51" s="17" t="n">
+        <v>54.77</v>
+      </c>
+      <c r="AK51" s="17" t="n">
+        <v>14383.03</v>
+      </c>
+      <c r="AL51" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM51" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN51" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -64479,7 +65725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN98"/>
+  <dimension ref="A1:AN100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -79234,6 +80480,310 @@
         <v>50000</v>
       </c>
       <c r="AN98" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B99" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C99" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D99" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E99" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F99" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G99" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H99" s="17" t="n">
+        <v>24145.08</v>
+      </c>
+      <c r="I99" s="17" t="n">
+        <v>24082.85</v>
+      </c>
+      <c r="J99" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K99" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L99" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M99" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N99" s="17" t="inlineStr">
+        <is>
+          <t>11:08 IST</t>
+        </is>
+      </c>
+      <c r="O99" s="17" t="n">
+        <v>24045.55</v>
+      </c>
+      <c r="P99" s="17" t="n">
+        <v>24187.7</v>
+      </c>
+      <c r="Q99" s="17" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="R99" s="17" t="inlineStr">
+        <is>
+          <t>24100 CE</t>
+        </is>
+      </c>
+      <c r="S99" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="T99" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U99" s="17" t="n">
+        <v>2665</v>
+      </c>
+      <c r="V99" s="17" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="W99" s="17" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="X99" s="17" t="n">
+        <v>47197.15</v>
+      </c>
+      <c r="Y99" s="17" t="n">
+        <v>47251.78</v>
+      </c>
+      <c r="Z99" s="17" t="n">
+        <v>219302.85</v>
+      </c>
+      <c r="AA99" s="17" t="n">
+        <v>14159.15</v>
+      </c>
+      <c r="AB99" s="17" t="n">
+        <v>14159.15</v>
+      </c>
+      <c r="AC99" s="17" t="n">
+        <v>14151.15</v>
+      </c>
+      <c r="AD99" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE99" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF99" s="17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AG99" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH99" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI99" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ99" s="17" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="AK99" s="17" t="n">
+        <v>14096.52</v>
+      </c>
+      <c r="AL99" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM99" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN99" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B100" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C100" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D100" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E100" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F100" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G100" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H100" s="15" t="n">
+        <v>24145.08</v>
+      </c>
+      <c r="I100" s="15" t="n">
+        <v>24082.85</v>
+      </c>
+      <c r="J100" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K100" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L100" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M100" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N100" s="15" t="inlineStr">
+        <is>
+          <t>11:05 IST</t>
+        </is>
+      </c>
+      <c r="O100" s="15" t="n">
+        <v>24045.55</v>
+      </c>
+      <c r="P100" s="15" t="n">
+        <v>24187.7</v>
+      </c>
+      <c r="Q100" s="15" t="inlineStr">
+        <is>
+          <t>24100 PE</t>
+        </is>
+      </c>
+      <c r="R100" s="15" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="S100" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="T100" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U100" s="15" t="n">
+        <v>2340</v>
+      </c>
+      <c r="V100" s="15" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="W100" s="15" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="X100" s="15" t="n">
+        <v>47431.8</v>
+      </c>
+      <c r="Y100" s="15" t="n">
+        <v>47486.46</v>
+      </c>
+      <c r="Z100" s="15" t="n">
+        <v>186568.2</v>
+      </c>
+      <c r="AA100" s="15" t="n">
+        <v>14229.54</v>
+      </c>
+      <c r="AB100" s="15" t="n">
+        <v>14229.54</v>
+      </c>
+      <c r="AC100" s="15" t="n">
+        <v>-14227.2</v>
+      </c>
+      <c r="AD100" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE100" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF100" s="15" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="AG100" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH100" s="15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI100" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ100" s="15" t="n">
+        <v>54.66</v>
+      </c>
+      <c r="AK100" s="15" t="n">
+        <v>-14281.86</v>
+      </c>
+      <c r="AL100" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM100" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN100" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA51"/>
+  <dimension ref="A1:AA52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5631,6 +5631,105 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D52" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="F52" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G52" s="17" t="inlineStr">
+        <is>
+          <t>11:25 ET</t>
+        </is>
+      </c>
+      <c r="H52" s="17" t="n">
+        <v>29323</v>
+      </c>
+      <c r="I52" s="17" t="n">
+        <v>29300</v>
+      </c>
+      <c r="J52" s="17" t="n">
+        <v>29325</v>
+      </c>
+      <c r="K52" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L52" s="17" t="n">
+        <v>213.72</v>
+      </c>
+      <c r="M52" s="17" t="n">
+        <v>277.84</v>
+      </c>
+      <c r="N52" s="17" t="n">
+        <v>884.48</v>
+      </c>
+      <c r="O52" s="17" t="n">
+        <v>1145.12</v>
+      </c>
+      <c r="P52" s="17" t="n">
+        <v>256.46</v>
+      </c>
+      <c r="Q52" s="17" t="n">
+        <v>256.46</v>
+      </c>
+      <c r="R52" s="17" t="n">
+        <v>256.48</v>
+      </c>
+      <c r="S52" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T52" s="17" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="U52" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="V52" s="17" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W52" s="17" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="X52" s="17" t="n">
+        <v>226.88</v>
+      </c>
+      <c r="Y52" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z52" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA52" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -5645,7 +5744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN51"/>
+  <dimension ref="A1:AN52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13301,6 +13400,158 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B52" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D52" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E52" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F52" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G52" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H52" s="16" t="n">
+        <v>57722.46</v>
+      </c>
+      <c r="I52" s="16" t="n">
+        <v>57676.95</v>
+      </c>
+      <c r="J52" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K52" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L52" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="M52" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N52" s="16" t="inlineStr">
+        <is>
+          <t>14:49 IST</t>
+        </is>
+      </c>
+      <c r="O52" s="16" t="n">
+        <v>57126.8</v>
+      </c>
+      <c r="P52" s="16" t="n">
+        <v>57835.35</v>
+      </c>
+      <c r="Q52" s="16" t="inlineStr">
+        <is>
+          <t>57000 CE</t>
+        </is>
+      </c>
+      <c r="R52" s="16" t="inlineStr">
+        <is>
+          <t>57200 CE</t>
+        </is>
+      </c>
+      <c r="S52" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="T52" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U52" s="16" t="n">
+        <v>570</v>
+      </c>
+      <c r="V52" s="16" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="W52" s="16" t="n">
+        <v>84.56</v>
+      </c>
+      <c r="X52" s="16" t="n">
+        <v>46825.5</v>
+      </c>
+      <c r="Y52" s="16" t="n">
+        <v>46880.07</v>
+      </c>
+      <c r="Z52" s="16" t="n">
+        <v>67174.5</v>
+      </c>
+      <c r="AA52" s="16" t="n">
+        <v>14047.65</v>
+      </c>
+      <c r="AB52" s="16" t="n">
+        <v>14047.65</v>
+      </c>
+      <c r="AC52" s="16" t="n">
+        <v>1373.7</v>
+      </c>
+      <c r="AD52" s="16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE52" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF52" s="16" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AG52" s="16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH52" s="16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI52" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ52" s="16" t="n">
+        <v>54.57</v>
+      </c>
+      <c r="AK52" s="16" t="n">
+        <v>1319.13</v>
+      </c>
+      <c r="AL52" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM52" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN52" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -13315,7 +13566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN51"/>
+  <dimension ref="A1:AN52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -20971,6 +21222,158 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E52" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F52" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G52" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="n">
+        <v>57722.46</v>
+      </c>
+      <c r="I52" s="15" t="n">
+        <v>57676.95</v>
+      </c>
+      <c r="J52" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K52" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L52" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="M52" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N52" s="15" t="inlineStr">
+        <is>
+          <t>11:09 IST</t>
+        </is>
+      </c>
+      <c r="O52" s="15" t="n">
+        <v>57126.8</v>
+      </c>
+      <c r="P52" s="15" t="n">
+        <v>57835.35</v>
+      </c>
+      <c r="Q52" s="15" t="inlineStr">
+        <is>
+          <t>57200 PE</t>
+        </is>
+      </c>
+      <c r="R52" s="15" t="inlineStr">
+        <is>
+          <t>57000 PE</t>
+        </is>
+      </c>
+      <c r="S52" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="T52" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U52" s="15" t="n">
+        <v>540</v>
+      </c>
+      <c r="V52" s="15" t="n">
+        <v>87.29000000000001</v>
+      </c>
+      <c r="W52" s="15" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="X52" s="15" t="n">
+        <v>47136.6</v>
+      </c>
+      <c r="Y52" s="15" t="n">
+        <v>47191.22</v>
+      </c>
+      <c r="Z52" s="15" t="n">
+        <v>60863.4</v>
+      </c>
+      <c r="AA52" s="15" t="n">
+        <v>14140.98</v>
+      </c>
+      <c r="AB52" s="15" t="n">
+        <v>14140.98</v>
+      </c>
+      <c r="AC52" s="15" t="n">
+        <v>-14142.6</v>
+      </c>
+      <c r="AD52" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE52" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF52" s="15" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AG52" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH52" s="15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI52" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ52" s="15" t="n">
+        <v>54.62</v>
+      </c>
+      <c r="AK52" s="15" t="n">
+        <v>-14197.22</v>
+      </c>
+      <c r="AL52" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM52" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN52" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -20985,7 +21388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN100"/>
+  <dimension ref="A1:AN102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -36044,6 +36447,310 @@
         <v>50000</v>
       </c>
       <c r="AN100" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B101" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C101" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D101" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E101" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F101" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G101" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H101" s="17" t="n">
+        <v>57722.46</v>
+      </c>
+      <c r="I101" s="17" t="n">
+        <v>57676.95</v>
+      </c>
+      <c r="J101" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K101" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L101" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="M101" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N101" s="17" t="inlineStr">
+        <is>
+          <t>12:10 IST</t>
+        </is>
+      </c>
+      <c r="O101" s="17" t="n">
+        <v>57126.8</v>
+      </c>
+      <c r="P101" s="17" t="n">
+        <v>57835.35</v>
+      </c>
+      <c r="Q101" s="17" t="inlineStr">
+        <is>
+          <t>57000 CE</t>
+        </is>
+      </c>
+      <c r="R101" s="17" t="inlineStr">
+        <is>
+          <t>57200 CE</t>
+        </is>
+      </c>
+      <c r="S101" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="T101" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U101" s="17" t="n">
+        <v>510</v>
+      </c>
+      <c r="V101" s="17" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="W101" s="17" t="n">
+        <v>119.34</v>
+      </c>
+      <c r="X101" s="17" t="n">
+        <v>46818</v>
+      </c>
+      <c r="Y101" s="17" t="n">
+        <v>46872.57</v>
+      </c>
+      <c r="Z101" s="17" t="n">
+        <v>55182</v>
+      </c>
+      <c r="AA101" s="17" t="n">
+        <v>14045.4</v>
+      </c>
+      <c r="AB101" s="17" t="n">
+        <v>14045.4</v>
+      </c>
+      <c r="AC101" s="17" t="n">
+        <v>14045.4</v>
+      </c>
+      <c r="AD101" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE101" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF101" s="17" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AG101" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH101" s="17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI101" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ101" s="17" t="n">
+        <v>54.57</v>
+      </c>
+      <c r="AK101" s="17" t="n">
+        <v>13990.83</v>
+      </c>
+      <c r="AL101" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM101" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN101" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B102" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C102" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D102" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E102" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F102" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G102" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H102" s="17" t="n">
+        <v>57722.46</v>
+      </c>
+      <c r="I102" s="17" t="n">
+        <v>57676.95</v>
+      </c>
+      <c r="J102" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K102" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L102" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="M102" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N102" s="17" t="inlineStr">
+        <is>
+          <t>10:19 IST</t>
+        </is>
+      </c>
+      <c r="O102" s="17" t="n">
+        <v>57126.8</v>
+      </c>
+      <c r="P102" s="17" t="n">
+        <v>57835.35</v>
+      </c>
+      <c r="Q102" s="17" t="inlineStr">
+        <is>
+          <t>57200 PE</t>
+        </is>
+      </c>
+      <c r="R102" s="17" t="inlineStr">
+        <is>
+          <t>57000 PE</t>
+        </is>
+      </c>
+      <c r="S102" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="T102" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U102" s="17" t="n">
+        <v>480</v>
+      </c>
+      <c r="V102" s="17" t="n">
+        <v>97.02</v>
+      </c>
+      <c r="W102" s="17" t="n">
+        <v>126.13</v>
+      </c>
+      <c r="X102" s="17" t="n">
+        <v>46569.6</v>
+      </c>
+      <c r="Y102" s="17" t="n">
+        <v>46624.13</v>
+      </c>
+      <c r="Z102" s="17" t="n">
+        <v>49430.4</v>
+      </c>
+      <c r="AA102" s="17" t="n">
+        <v>13970.88</v>
+      </c>
+      <c r="AB102" s="17" t="n">
+        <v>13970.88</v>
+      </c>
+      <c r="AC102" s="17" t="n">
+        <v>13972.8</v>
+      </c>
+      <c r="AD102" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE102" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF102" s="17" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="AG102" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH102" s="17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI102" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ102" s="17" t="n">
+        <v>54.53</v>
+      </c>
+      <c r="AK102" s="17" t="n">
+        <v>13918.27</v>
+      </c>
+      <c r="AL102" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM102" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN102" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -39497,7 +40204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -41264,6 +41971,72 @@
         <v>57689.93</v>
       </c>
       <c r="G54" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B55" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D55" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E55" s="18" t="n">
+        <v>24135.22</v>
+      </c>
+      <c r="F55" s="18" t="n">
+        <v>24078.37</v>
+      </c>
+      <c r="G55" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B56" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D56" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E56" s="18" t="n">
+        <v>57722.46</v>
+      </c>
+      <c r="F56" s="18" t="n">
+        <v>57676.95</v>
+      </c>
+      <c r="G56" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -41283,7 +42056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA51"/>
+  <dimension ref="A1:AA52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -46305,6 +47078,105 @@
         <v>1000</v>
       </c>
       <c r="AA51" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D52" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="F52" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G52" s="17" t="inlineStr">
+        <is>
+          <t>11:15 ET</t>
+        </is>
+      </c>
+      <c r="H52" s="17" t="n">
+        <v>29323</v>
+      </c>
+      <c r="I52" s="17" t="n">
+        <v>29300</v>
+      </c>
+      <c r="J52" s="17" t="n">
+        <v>29325</v>
+      </c>
+      <c r="K52" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="L52" s="17" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="M52" s="17" t="n">
+        <v>31.85</v>
+      </c>
+      <c r="N52" s="17" t="n">
+        <v>993.3200000000001</v>
+      </c>
+      <c r="O52" s="17" t="n">
+        <v>969</v>
+      </c>
+      <c r="P52" s="17" t="n">
+        <v>279.3</v>
+      </c>
+      <c r="Q52" s="17" t="n">
+        <v>279.3</v>
+      </c>
+      <c r="R52" s="17" t="n">
+        <v>279.3</v>
+      </c>
+      <c r="S52" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T52" s="17" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="U52" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="V52" s="17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W52" s="17" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="X52" s="17" t="n">
+        <v>216.98</v>
+      </c>
+      <c r="Y52" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z52" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA52" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -46424,7 +47296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I100"/>
+  <dimension ref="A1:I102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -49919,6 +50791,76 @@
       <c r="I100" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — STOP LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B101" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C101" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D101" s="19" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="E101" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F101" s="19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G101" s="19" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H101" s="19" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I101" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B102" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C102" s="19" t="n">
+        <v>38</v>
+      </c>
+      <c r="D102" s="19" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="E102" s="19" t="n">
+        <v>19</v>
+      </c>
+      <c r="F102" s="19" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G102" s="19" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="H102" s="19" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="I102" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — PROFIT</t>
         </is>
       </c>
     </row>
@@ -50385,7 +51327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN51"/>
+  <dimension ref="A1:AN52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -58041,6 +58983,158 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D52" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E52" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F52" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G52" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H52" s="17" t="n">
+        <v>24135.22</v>
+      </c>
+      <c r="I52" s="17" t="n">
+        <v>24078.37</v>
+      </c>
+      <c r="J52" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K52" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L52" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N52" s="17" t="inlineStr">
+        <is>
+          <t>11:47 IST</t>
+        </is>
+      </c>
+      <c r="O52" s="17" t="n">
+        <v>23996.25</v>
+      </c>
+      <c r="P52" s="17" t="n">
+        <v>24187.7</v>
+      </c>
+      <c r="Q52" s="17" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="R52" s="17" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="S52" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="T52" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U52" s="17" t="n">
+        <v>2990</v>
+      </c>
+      <c r="V52" s="17" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="W52" s="17" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="X52" s="17" t="n">
+        <v>47720.4</v>
+      </c>
+      <c r="Y52" s="17" t="n">
+        <v>47775.11</v>
+      </c>
+      <c r="Z52" s="17" t="n">
+        <v>251279.6</v>
+      </c>
+      <c r="AA52" s="17" t="n">
+        <v>14316.12</v>
+      </c>
+      <c r="AB52" s="17" t="n">
+        <v>14316.12</v>
+      </c>
+      <c r="AC52" s="17" t="n">
+        <v>14322.1</v>
+      </c>
+      <c r="AD52" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE52" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF52" s="17" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="AG52" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH52" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI52" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ52" s="17" t="n">
+        <v>54.71</v>
+      </c>
+      <c r="AK52" s="17" t="n">
+        <v>14267.39</v>
+      </c>
+      <c r="AL52" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM52" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN52" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -58055,7 +59149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN51"/>
+  <dimension ref="A1:AN52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -65711,6 +66805,158 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D52" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E52" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F52" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G52" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H52" s="17" t="n">
+        <v>24135.22</v>
+      </c>
+      <c r="I52" s="17" t="n">
+        <v>24078.37</v>
+      </c>
+      <c r="J52" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K52" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L52" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N52" s="17" t="inlineStr">
+        <is>
+          <t>10:14 IST</t>
+        </is>
+      </c>
+      <c r="O52" s="17" t="n">
+        <v>23996.25</v>
+      </c>
+      <c r="P52" s="17" t="n">
+        <v>24187.7</v>
+      </c>
+      <c r="Q52" s="17" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="R52" s="17" t="inlineStr">
+        <is>
+          <t>23900 PE</t>
+        </is>
+      </c>
+      <c r="S52" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="T52" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U52" s="17" t="n">
+        <v>3120</v>
+      </c>
+      <c r="V52" s="17" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="W52" s="17" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="X52" s="17" t="n">
+        <v>48016.8</v>
+      </c>
+      <c r="Y52" s="17" t="n">
+        <v>48071.56</v>
+      </c>
+      <c r="Z52" s="17" t="n">
+        <v>263983.2</v>
+      </c>
+      <c r="AA52" s="17" t="n">
+        <v>14405.04</v>
+      </c>
+      <c r="AB52" s="17" t="n">
+        <v>14405.04</v>
+      </c>
+      <c r="AC52" s="17" t="n">
+        <v>14414.4</v>
+      </c>
+      <c r="AD52" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE52" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF52" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG52" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH52" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI52" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ52" s="17" t="n">
+        <v>54.76</v>
+      </c>
+      <c r="AK52" s="17" t="n">
+        <v>14359.64</v>
+      </c>
+      <c r="AL52" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM52" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN52" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -65725,7 +66971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN100"/>
+  <dimension ref="A1:AN102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -80784,6 +82030,310 @@
         <v>50000</v>
       </c>
       <c r="AN100" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B101" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C101" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D101" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E101" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F101" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G101" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H101" s="15" t="n">
+        <v>24135.22</v>
+      </c>
+      <c r="I101" s="15" t="n">
+        <v>24078.37</v>
+      </c>
+      <c r="J101" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K101" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L101" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M101" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N101" s="15" t="inlineStr">
+        <is>
+          <t>10:23 IST</t>
+        </is>
+      </c>
+      <c r="O101" s="15" t="n">
+        <v>23996.25</v>
+      </c>
+      <c r="P101" s="15" t="n">
+        <v>24187.7</v>
+      </c>
+      <c r="Q101" s="15" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="R101" s="15" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="S101" s="15" t="n">
+        <v>47</v>
+      </c>
+      <c r="T101" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U101" s="15" t="n">
+        <v>3055</v>
+      </c>
+      <c r="V101" s="15" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="W101" s="15" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="X101" s="15" t="n">
+        <v>47169.2</v>
+      </c>
+      <c r="Y101" s="15" t="n">
+        <v>47223.82</v>
+      </c>
+      <c r="Z101" s="15" t="n">
+        <v>258330.8</v>
+      </c>
+      <c r="AA101" s="15" t="n">
+        <v>14150.76</v>
+      </c>
+      <c r="AB101" s="15" t="n">
+        <v>14150.76</v>
+      </c>
+      <c r="AC101" s="15" t="n">
+        <v>-14144.65</v>
+      </c>
+      <c r="AD101" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE101" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF101" s="15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AG101" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH101" s="15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI101" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ101" s="15" t="n">
+        <v>54.62</v>
+      </c>
+      <c r="AK101" s="15" t="n">
+        <v>-14199.27</v>
+      </c>
+      <c r="AL101" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM101" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN101" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B102" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C102" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D102" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E102" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F102" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G102" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H102" s="15" t="n">
+        <v>24135.22</v>
+      </c>
+      <c r="I102" s="15" t="n">
+        <v>24078.37</v>
+      </c>
+      <c r="J102" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K102" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L102" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M102" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N102" s="15" t="inlineStr">
+        <is>
+          <t>11:00 IST</t>
+        </is>
+      </c>
+      <c r="O102" s="15" t="n">
+        <v>23996.25</v>
+      </c>
+      <c r="P102" s="15" t="n">
+        <v>24187.7</v>
+      </c>
+      <c r="Q102" s="15" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="R102" s="15" t="inlineStr">
+        <is>
+          <t>23900 PE</t>
+        </is>
+      </c>
+      <c r="S102" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="T102" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U102" s="15" t="n">
+        <v>1950</v>
+      </c>
+      <c r="V102" s="15" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="W102" s="15" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="X102" s="15" t="n">
+        <v>47658</v>
+      </c>
+      <c r="Y102" s="15" t="n">
+        <v>47712.7</v>
+      </c>
+      <c r="Z102" s="15" t="n">
+        <v>147342</v>
+      </c>
+      <c r="AA102" s="15" t="n">
+        <v>14297.4</v>
+      </c>
+      <c r="AB102" s="15" t="n">
+        <v>14297.4</v>
+      </c>
+      <c r="AC102" s="15" t="n">
+        <v>-14293.5</v>
+      </c>
+      <c r="AD102" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE102" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF102" s="15" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="AG102" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH102" s="15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI102" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ102" s="15" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="AK102" s="15" t="n">
+        <v>-14348.2</v>
+      </c>
+      <c r="AL102" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM102" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN102" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA52"/>
+  <dimension ref="A1:AA53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5730,6 +5730,105 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D53" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E53" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="F53" s="15" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G53" s="15" t="inlineStr">
+        <is>
+          <t>11:34 ET</t>
+        </is>
+      </c>
+      <c r="H53" s="15" t="n">
+        <v>29089.25</v>
+      </c>
+      <c r="I53" s="15" t="n">
+        <v>29075</v>
+      </c>
+      <c r="J53" s="15" t="n">
+        <v>29100</v>
+      </c>
+      <c r="K53" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="L53" s="15" t="n">
+        <v>226.52</v>
+      </c>
+      <c r="M53" s="15" t="n">
+        <v>158.56</v>
+      </c>
+      <c r="N53" s="15" t="n">
+        <v>935.6799999999999</v>
+      </c>
+      <c r="O53" s="15" t="n">
+        <v>1093.92</v>
+      </c>
+      <c r="P53" s="15" t="n">
+        <v>271.82</v>
+      </c>
+      <c r="Q53" s="15" t="n">
+        <v>271.82</v>
+      </c>
+      <c r="R53" s="15" t="n">
+        <v>-271.84</v>
+      </c>
+      <c r="S53" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="T53" s="15" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="U53" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="V53" s="15" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W53" s="15" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="X53" s="15" t="n">
+        <v>-301.44</v>
+      </c>
+      <c r="Y53" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="Z53" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA53" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -5744,7 +5843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN52"/>
+  <dimension ref="A1:AN53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13552,6 +13651,158 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B53" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D53" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E53" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F53" s="16" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G53" s="16" t="inlineStr">
+        <is>
+          <t>Price↓(56618.7&lt;57126.8) &amp; EMA9↓(57503.33&lt;57622.58)</t>
+        </is>
+      </c>
+      <c r="H53" s="16" t="n">
+        <v>57503.33</v>
+      </c>
+      <c r="I53" s="16" t="n">
+        <v>57622.58</v>
+      </c>
+      <c r="J53" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K53" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L53" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="M53" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N53" s="16" t="inlineStr">
+        <is>
+          <t>15:20 IST</t>
+        </is>
+      </c>
+      <c r="O53" s="16" t="n">
+        <v>56618.7</v>
+      </c>
+      <c r="P53" s="16" t="n">
+        <v>57126.8</v>
+      </c>
+      <c r="Q53" s="16" t="inlineStr">
+        <is>
+          <t>56600 CE</t>
+        </is>
+      </c>
+      <c r="R53" s="16" t="inlineStr">
+        <is>
+          <t>56800 CE</t>
+        </is>
+      </c>
+      <c r="S53" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="T53" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U53" s="16" t="n">
+        <v>870</v>
+      </c>
+      <c r="V53" s="16" t="n">
+        <v>54.29</v>
+      </c>
+      <c r="W53" s="16" t="n">
+        <v>54.59</v>
+      </c>
+      <c r="X53" s="16" t="n">
+        <v>47232.3</v>
+      </c>
+      <c r="Y53" s="16" t="n">
+        <v>47286.93</v>
+      </c>
+      <c r="Z53" s="16" t="n">
+        <v>126767.7</v>
+      </c>
+      <c r="AA53" s="16" t="n">
+        <v>14169.69</v>
+      </c>
+      <c r="AB53" s="16" t="n">
+        <v>14169.69</v>
+      </c>
+      <c r="AC53" s="16" t="n">
+        <v>261</v>
+      </c>
+      <c r="AD53" s="16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AE53" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF53" s="16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AG53" s="16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH53" s="16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI53" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ53" s="16" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="AK53" s="16" t="n">
+        <v>206.37</v>
+      </c>
+      <c r="AL53" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM53" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN53" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -13566,7 +13817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN52"/>
+  <dimension ref="A1:AN53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21374,6 +21625,158 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B53" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D53" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E53" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F53" s="16" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G53" s="16" t="inlineStr">
+        <is>
+          <t>Price↓(56618.7&lt;57126.8) &amp; EMA9↓(57503.33&lt;57622.58)</t>
+        </is>
+      </c>
+      <c r="H53" s="16" t="n">
+        <v>57503.33</v>
+      </c>
+      <c r="I53" s="16" t="n">
+        <v>57622.58</v>
+      </c>
+      <c r="J53" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K53" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L53" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="M53" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N53" s="16" t="inlineStr">
+        <is>
+          <t>14:11 IST</t>
+        </is>
+      </c>
+      <c r="O53" s="16" t="n">
+        <v>56618.7</v>
+      </c>
+      <c r="P53" s="16" t="n">
+        <v>57126.8</v>
+      </c>
+      <c r="Q53" s="16" t="inlineStr">
+        <is>
+          <t>56800 PE</t>
+        </is>
+      </c>
+      <c r="R53" s="16" t="inlineStr">
+        <is>
+          <t>56600 PE</t>
+        </is>
+      </c>
+      <c r="S53" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="T53" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U53" s="16" t="n">
+        <v>780</v>
+      </c>
+      <c r="V53" s="16" t="n">
+        <v>62.67</v>
+      </c>
+      <c r="W53" s="16" t="n">
+        <v>63.71</v>
+      </c>
+      <c r="X53" s="16" t="n">
+        <v>48882.6</v>
+      </c>
+      <c r="Y53" s="16" t="n">
+        <v>48937.49</v>
+      </c>
+      <c r="Z53" s="16" t="n">
+        <v>107117.4</v>
+      </c>
+      <c r="AA53" s="16" t="n">
+        <v>14664.78</v>
+      </c>
+      <c r="AB53" s="16" t="n">
+        <v>14664.78</v>
+      </c>
+      <c r="AC53" s="16" t="n">
+        <v>811.2</v>
+      </c>
+      <c r="AD53" s="16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE53" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF53" s="16" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="AG53" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH53" s="16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI53" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ53" s="16" t="n">
+        <v>54.89</v>
+      </c>
+      <c r="AK53" s="16" t="n">
+        <v>756.3099999999999</v>
+      </c>
+      <c r="AL53" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM53" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN53" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -21388,7 +21791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN102"/>
+  <dimension ref="A1:AN104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -36756,6 +37159,310 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B103" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C103" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D103" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E103" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F103" s="16" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G103" s="16" t="inlineStr">
+        <is>
+          <t>Price↓(56618.7&lt;57126.8) &amp; EMA9↓(57503.33&lt;57622.58)</t>
+        </is>
+      </c>
+      <c r="H103" s="16" t="n">
+        <v>57503.33</v>
+      </c>
+      <c r="I103" s="16" t="n">
+        <v>57622.58</v>
+      </c>
+      <c r="J103" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K103" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L103" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="M103" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N103" s="16" t="inlineStr">
+        <is>
+          <t>15:05 IST</t>
+        </is>
+      </c>
+      <c r="O103" s="16" t="n">
+        <v>56618.7</v>
+      </c>
+      <c r="P103" s="16" t="n">
+        <v>57126.8</v>
+      </c>
+      <c r="Q103" s="16" t="inlineStr">
+        <is>
+          <t>56600 CE</t>
+        </is>
+      </c>
+      <c r="R103" s="16" t="inlineStr">
+        <is>
+          <t>56800 CE</t>
+        </is>
+      </c>
+      <c r="S103" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="T103" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U103" s="16" t="n">
+        <v>690</v>
+      </c>
+      <c r="V103" s="16" t="n">
+        <v>70.63</v>
+      </c>
+      <c r="W103" s="16" t="n">
+        <v>72.06</v>
+      </c>
+      <c r="X103" s="16" t="n">
+        <v>48734.7</v>
+      </c>
+      <c r="Y103" s="16" t="n">
+        <v>48789.57</v>
+      </c>
+      <c r="Z103" s="16" t="n">
+        <v>89265.3</v>
+      </c>
+      <c r="AA103" s="16" t="n">
+        <v>14620.41</v>
+      </c>
+      <c r="AB103" s="16" t="n">
+        <v>14620.41</v>
+      </c>
+      <c r="AC103" s="16" t="n">
+        <v>986.7</v>
+      </c>
+      <c r="AD103" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE103" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF103" s="16" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="AG103" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH103" s="16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI103" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ103" s="16" t="n">
+        <v>54.87</v>
+      </c>
+      <c r="AK103" s="16" t="n">
+        <v>931.83</v>
+      </c>
+      <c r="AL103" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM103" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN103" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B104" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C104" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D104" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E104" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F104" s="15" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G104" s="15" t="inlineStr">
+        <is>
+          <t>Price↓(56618.7&lt;57126.8) &amp; EMA9↓(57503.33&lt;57622.58)</t>
+        </is>
+      </c>
+      <c r="H104" s="15" t="n">
+        <v>57503.33</v>
+      </c>
+      <c r="I104" s="15" t="n">
+        <v>57622.58</v>
+      </c>
+      <c r="J104" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K104" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L104" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="M104" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N104" s="15" t="inlineStr">
+        <is>
+          <t>11:15 IST</t>
+        </is>
+      </c>
+      <c r="O104" s="15" t="n">
+        <v>56618.7</v>
+      </c>
+      <c r="P104" s="15" t="n">
+        <v>57126.8</v>
+      </c>
+      <c r="Q104" s="15" t="inlineStr">
+        <is>
+          <t>56800 PE</t>
+        </is>
+      </c>
+      <c r="R104" s="15" t="inlineStr">
+        <is>
+          <t>56600 PE</t>
+        </is>
+      </c>
+      <c r="S104" s="15" t="n">
+        <v>32</v>
+      </c>
+      <c r="T104" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U104" s="15" t="n">
+        <v>960</v>
+      </c>
+      <c r="V104" s="15" t="n">
+        <v>50.04</v>
+      </c>
+      <c r="W104" s="15" t="n">
+        <v>35.03</v>
+      </c>
+      <c r="X104" s="15" t="n">
+        <v>48038.4</v>
+      </c>
+      <c r="Y104" s="15" t="n">
+        <v>48093.16</v>
+      </c>
+      <c r="Z104" s="15" t="n">
+        <v>143961.6</v>
+      </c>
+      <c r="AA104" s="15" t="n">
+        <v>14411.52</v>
+      </c>
+      <c r="AB104" s="15" t="n">
+        <v>14411.52</v>
+      </c>
+      <c r="AC104" s="15" t="n">
+        <v>-14409.6</v>
+      </c>
+      <c r="AD104" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE104" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF104" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG104" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH104" s="15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI104" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ104" s="15" t="n">
+        <v>54.76</v>
+      </c>
+      <c r="AK104" s="15" t="n">
+        <v>-14464.36</v>
+      </c>
+      <c r="AL104" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM104" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN104" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -36770,7 +37477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN23"/>
+  <dimension ref="A1:AN24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -40190,6 +40897,158 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G24" s="16" t="inlineStr">
+        <is>
+          <t>Price↓(56618.7&lt;57126.8) &amp; EMA9↓(57503.33&lt;57622.58)</t>
+        </is>
+      </c>
+      <c r="H24" s="16" t="n">
+        <v>57503.33</v>
+      </c>
+      <c r="I24" s="16" t="n">
+        <v>57622.58</v>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K24" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L24" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="M24" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N24" s="16" t="inlineStr">
+        <is>
+          <t>14:23 IST</t>
+        </is>
+      </c>
+      <c r="O24" s="16" t="n">
+        <v>56618.7</v>
+      </c>
+      <c r="P24" s="16" t="n">
+        <v>57126.8</v>
+      </c>
+      <c r="Q24" s="16" t="inlineStr">
+        <is>
+          <t>56800 PE</t>
+        </is>
+      </c>
+      <c r="R24" s="16" t="inlineStr">
+        <is>
+          <t>56600 PE</t>
+        </is>
+      </c>
+      <c r="S24" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U24" s="16" t="n">
+        <v>600</v>
+      </c>
+      <c r="V24" s="16" t="n">
+        <v>79.38</v>
+      </c>
+      <c r="W24" s="16" t="n">
+        <v>80.91</v>
+      </c>
+      <c r="X24" s="16" t="n">
+        <v>47628</v>
+      </c>
+      <c r="Y24" s="16" t="n">
+        <v>47682.69</v>
+      </c>
+      <c r="Z24" s="16" t="n">
+        <v>72372</v>
+      </c>
+      <c r="AA24" s="16" t="n">
+        <v>14288.4</v>
+      </c>
+      <c r="AB24" s="16" t="n">
+        <v>14288.4</v>
+      </c>
+      <c r="AC24" s="16" t="n">
+        <v>918</v>
+      </c>
+      <c r="AD24" s="16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE24" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF24" s="16" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AG24" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH24" s="16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI24" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ24" s="16" t="n">
+        <v>54.69</v>
+      </c>
+      <c r="AK24" s="16" t="n">
+        <v>863.3099999999999</v>
+      </c>
+      <c r="AL24" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM24" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN24" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -40204,7 +41063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -42037,6 +42896,39 @@
         <v>57676.95</v>
       </c>
       <c r="G56" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B57" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D57" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E57" s="18" t="n">
+        <v>24097.47</v>
+      </c>
+      <c r="F57" s="18" t="n">
+        <v>24080.49</v>
+      </c>
+      <c r="G57" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -42056,7 +42948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA52"/>
+  <dimension ref="A1:AA53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -47177,6 +48069,105 @@
         <v>1000</v>
       </c>
       <c r="AA52" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B53" s="16" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D53" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E53" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="F53" s="16" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G53" s="16" t="inlineStr">
+        <is>
+          <t>15:00 ET</t>
+        </is>
+      </c>
+      <c r="H53" s="16" t="n">
+        <v>29086</v>
+      </c>
+      <c r="I53" s="16" t="n">
+        <v>29075</v>
+      </c>
+      <c r="J53" s="16" t="n">
+        <v>29100</v>
+      </c>
+      <c r="K53" s="16" t="n">
+        <v>42</v>
+      </c>
+      <c r="L53" s="16" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="M53" s="16" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="N53" s="16" t="n">
+        <v>987.42</v>
+      </c>
+      <c r="O53" s="16" t="n">
+        <v>1181.46</v>
+      </c>
+      <c r="P53" s="16" t="n">
+        <v>275.56</v>
+      </c>
+      <c r="Q53" s="16" t="n">
+        <v>275.56</v>
+      </c>
+      <c r="R53" s="16" t="n">
+        <v>-27.72</v>
+      </c>
+      <c r="S53" s="16" t="n">
+        <v>-3</v>
+      </c>
+      <c r="T53" s="16" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="U53" s="16" t="n">
+        <v>42</v>
+      </c>
+      <c r="V53" s="16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W53" s="16" t="n">
+        <v>68.88</v>
+      </c>
+      <c r="X53" s="16" t="n">
+        <v>-96.59999999999999</v>
+      </c>
+      <c r="Y53" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="Z53" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA53" s="16" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -47296,7 +48287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I102"/>
+  <dimension ref="A1:I104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -50861,6 +51852,76 @@
       <c r="I102" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B103" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C103" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D103" s="19" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="E103" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F103" s="19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G103" s="19" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H103" s="19" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I103" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — STOP LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B104" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C104" s="19" t="n">
+        <v>42</v>
+      </c>
+      <c r="D104" s="19" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="E104" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="F104" s="19" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G104" s="19" t="n">
+        <v>34.44</v>
+      </c>
+      <c r="H104" s="19" t="n">
+        <v>68.88</v>
+      </c>
+      <c r="I104" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — FLAT</t>
         </is>
       </c>
     </row>
@@ -51327,7 +52388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN52"/>
+  <dimension ref="A1:AN53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -59135,6 +60196,158 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C53" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D53" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E53" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F53" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G53" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H53" s="17" t="n">
+        <v>24097.47</v>
+      </c>
+      <c r="I53" s="17" t="n">
+        <v>24080.49</v>
+      </c>
+      <c r="J53" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K53" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L53" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N53" s="17" t="inlineStr">
+        <is>
+          <t>11:45 IST</t>
+        </is>
+      </c>
+      <c r="O53" s="17" t="n">
+        <v>23942.7</v>
+      </c>
+      <c r="P53" s="17" t="n">
+        <v>23996.25</v>
+      </c>
+      <c r="Q53" s="17" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="R53" s="17" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="S53" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="T53" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U53" s="17" t="n">
+        <v>2470</v>
+      </c>
+      <c r="V53" s="17" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="W53" s="17" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="X53" s="17" t="n">
+        <v>48387.3</v>
+      </c>
+      <c r="Y53" s="17" t="n">
+        <v>48442.11</v>
+      </c>
+      <c r="Z53" s="17" t="n">
+        <v>198612.7</v>
+      </c>
+      <c r="AA53" s="17" t="n">
+        <v>14516.19</v>
+      </c>
+      <c r="AB53" s="17" t="n">
+        <v>14516.19</v>
+      </c>
+      <c r="AC53" s="17" t="n">
+        <v>14523.6</v>
+      </c>
+      <c r="AD53" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE53" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF53" s="17" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AG53" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH53" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI53" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ53" s="17" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="AK53" s="17" t="n">
+        <v>14468.79</v>
+      </c>
+      <c r="AL53" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM53" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN53" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -59149,7 +60362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN52"/>
+  <dimension ref="A1:AN53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -66957,6 +68170,158 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D53" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E53" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F53" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G53" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H53" s="15" t="n">
+        <v>24097.47</v>
+      </c>
+      <c r="I53" s="15" t="n">
+        <v>24080.49</v>
+      </c>
+      <c r="J53" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K53" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L53" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N53" s="15" t="inlineStr">
+        <is>
+          <t>10:50 IST</t>
+        </is>
+      </c>
+      <c r="O53" s="15" t="n">
+        <v>23942.7</v>
+      </c>
+      <c r="P53" s="15" t="n">
+        <v>23996.25</v>
+      </c>
+      <c r="Q53" s="15" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="R53" s="15" t="inlineStr">
+        <is>
+          <t>23900 PE</t>
+        </is>
+      </c>
+      <c r="S53" s="15" t="n">
+        <v>32</v>
+      </c>
+      <c r="T53" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U53" s="15" t="n">
+        <v>2080</v>
+      </c>
+      <c r="V53" s="15" t="n">
+        <v>23.17</v>
+      </c>
+      <c r="W53" s="15" t="n">
+        <v>16.22</v>
+      </c>
+      <c r="X53" s="15" t="n">
+        <v>48193.6</v>
+      </c>
+      <c r="Y53" s="15" t="n">
+        <v>48248.38</v>
+      </c>
+      <c r="Z53" s="15" t="n">
+        <v>159806.4</v>
+      </c>
+      <c r="AA53" s="15" t="n">
+        <v>14458.08</v>
+      </c>
+      <c r="AB53" s="15" t="n">
+        <v>14458.08</v>
+      </c>
+      <c r="AC53" s="15" t="n">
+        <v>-14456</v>
+      </c>
+      <c r="AD53" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE53" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF53" s="15" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="AG53" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH53" s="15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI53" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ53" s="15" t="n">
+        <v>54.78</v>
+      </c>
+      <c r="AK53" s="15" t="n">
+        <v>-14510.78</v>
+      </c>
+      <c r="AL53" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM53" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN53" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -66971,7 +68336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN102"/>
+  <dimension ref="A1:AN104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -82334,6 +83699,310 @@
         <v>50000</v>
       </c>
       <c r="AN102" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B103" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C103" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D103" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E103" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F103" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G103" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H103" s="17" t="n">
+        <v>24097.47</v>
+      </c>
+      <c r="I103" s="17" t="n">
+        <v>24080.49</v>
+      </c>
+      <c r="J103" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K103" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L103" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N103" s="17" t="inlineStr">
+        <is>
+          <t>10:33 IST</t>
+        </is>
+      </c>
+      <c r="O103" s="17" t="n">
+        <v>23942.7</v>
+      </c>
+      <c r="P103" s="17" t="n">
+        <v>23996.25</v>
+      </c>
+      <c r="Q103" s="17" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="R103" s="17" t="inlineStr">
+        <is>
+          <t>24000 CE</t>
+        </is>
+      </c>
+      <c r="S103" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="T103" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U103" s="17" t="n">
+        <v>2470</v>
+      </c>
+      <c r="V103" s="17" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="W103" s="17" t="n">
+        <v>25.31</v>
+      </c>
+      <c r="X103" s="17" t="n">
+        <v>48090.9</v>
+      </c>
+      <c r="Y103" s="17" t="n">
+        <v>48145.67</v>
+      </c>
+      <c r="Z103" s="17" t="n">
+        <v>198909.1</v>
+      </c>
+      <c r="AA103" s="17" t="n">
+        <v>14427.27</v>
+      </c>
+      <c r="AB103" s="17" t="n">
+        <v>14427.27</v>
+      </c>
+      <c r="AC103" s="17" t="n">
+        <v>14424.8</v>
+      </c>
+      <c r="AD103" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE103" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF103" s="17" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="AG103" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH103" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI103" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ103" s="17" t="n">
+        <v>54.77</v>
+      </c>
+      <c r="AK103" s="17" t="n">
+        <v>14370.03</v>
+      </c>
+      <c r="AL103" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM103" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN103" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B104" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C104" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D104" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E104" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F104" s="16" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G104" s="16" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H104" s="16" t="n">
+        <v>24097.47</v>
+      </c>
+      <c r="I104" s="16" t="n">
+        <v>24080.49</v>
+      </c>
+      <c r="J104" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K104" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L104" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N104" s="16" t="inlineStr">
+        <is>
+          <t>14:16 IST</t>
+        </is>
+      </c>
+      <c r="O104" s="16" t="n">
+        <v>23942.7</v>
+      </c>
+      <c r="P104" s="16" t="n">
+        <v>23996.25</v>
+      </c>
+      <c r="Q104" s="16" t="inlineStr">
+        <is>
+          <t>24000 PE</t>
+        </is>
+      </c>
+      <c r="R104" s="16" t="inlineStr">
+        <is>
+          <t>23900 PE</t>
+        </is>
+      </c>
+      <c r="S104" s="16" t="n">
+        <v>43</v>
+      </c>
+      <c r="T104" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U104" s="16" t="n">
+        <v>2795</v>
+      </c>
+      <c r="V104" s="16" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="W104" s="16" t="n">
+        <v>17.19</v>
+      </c>
+      <c r="X104" s="16" t="n">
+        <v>47487.05</v>
+      </c>
+      <c r="Y104" s="16" t="n">
+        <v>47541.72</v>
+      </c>
+      <c r="Z104" s="16" t="n">
+        <v>232012.95</v>
+      </c>
+      <c r="AA104" s="16" t="n">
+        <v>14246.11</v>
+      </c>
+      <c r="AB104" s="16" t="n">
+        <v>14246.11</v>
+      </c>
+      <c r="AC104" s="16" t="n">
+        <v>559</v>
+      </c>
+      <c r="AD104" s="16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE104" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF104" s="16" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AG104" s="16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH104" s="16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI104" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ104" s="16" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="AK104" s="16" t="n">
+        <v>504.33</v>
+      </c>
+      <c r="AL104" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM104" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN104" s="16" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA53"/>
+  <dimension ref="A1:AA54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5829,6 +5829,105 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G54" s="17" t="inlineStr">
+        <is>
+          <t>13:56 ET</t>
+        </is>
+      </c>
+      <c r="H54" s="17" t="n">
+        <v>28512</v>
+      </c>
+      <c r="I54" s="17" t="n">
+        <v>28500</v>
+      </c>
+      <c r="J54" s="17" t="n">
+        <v>28525</v>
+      </c>
+      <c r="K54" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L54" s="17" t="n">
+        <v>210.9</v>
+      </c>
+      <c r="M54" s="17" t="n">
+        <v>274.17</v>
+      </c>
+      <c r="N54" s="17" t="n">
+        <v>873.2</v>
+      </c>
+      <c r="O54" s="17" t="n">
+        <v>1156.4</v>
+      </c>
+      <c r="P54" s="17" t="n">
+        <v>253.08</v>
+      </c>
+      <c r="Q54" s="17" t="n">
+        <v>253.08</v>
+      </c>
+      <c r="R54" s="17" t="n">
+        <v>253.08</v>
+      </c>
+      <c r="S54" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T54" s="17" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="U54" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="V54" s="17" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W54" s="17" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="X54" s="17" t="n">
+        <v>223.48</v>
+      </c>
+      <c r="Y54" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z54" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA54" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -5843,7 +5942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN53"/>
+  <dimension ref="A1:AN54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13803,6 +13902,158 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E54" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G54" s="17" t="inlineStr">
+        <is>
+          <t>Price↓(56592.0&lt;57126.8) &amp; EMA9↓(57498.0&lt;57620.15)</t>
+        </is>
+      </c>
+      <c r="H54" s="17" t="n">
+        <v>57498</v>
+      </c>
+      <c r="I54" s="17" t="n">
+        <v>57620.15</v>
+      </c>
+      <c r="J54" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K54" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L54" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="M54" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N54" s="17" t="inlineStr">
+        <is>
+          <t>10:16 IST</t>
+        </is>
+      </c>
+      <c r="O54" s="17" t="n">
+        <v>56592</v>
+      </c>
+      <c r="P54" s="17" t="n">
+        <v>57126.8</v>
+      </c>
+      <c r="Q54" s="17" t="inlineStr">
+        <is>
+          <t>56400 CE</t>
+        </is>
+      </c>
+      <c r="R54" s="17" t="inlineStr">
+        <is>
+          <t>56600 CE</t>
+        </is>
+      </c>
+      <c r="S54" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="T54" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U54" s="17" t="n">
+        <v>690</v>
+      </c>
+      <c r="V54" s="17" t="n">
+        <v>68.31999999999999</v>
+      </c>
+      <c r="W54" s="17" t="n">
+        <v>88.81999999999999</v>
+      </c>
+      <c r="X54" s="17" t="n">
+        <v>47140.8</v>
+      </c>
+      <c r="Y54" s="17" t="n">
+        <v>47195.42</v>
+      </c>
+      <c r="Z54" s="17" t="n">
+        <v>90859.2</v>
+      </c>
+      <c r="AA54" s="17" t="n">
+        <v>14142.24</v>
+      </c>
+      <c r="AB54" s="17" t="n">
+        <v>14142.24</v>
+      </c>
+      <c r="AC54" s="17" t="n">
+        <v>14145</v>
+      </c>
+      <c r="AD54" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE54" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF54" s="17" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AG54" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH54" s="17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI54" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ54" s="17" t="n">
+        <v>54.62</v>
+      </c>
+      <c r="AK54" s="17" t="n">
+        <v>14090.38</v>
+      </c>
+      <c r="AL54" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM54" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN54" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -13817,7 +14068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN53"/>
+  <dimension ref="A1:AN54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21777,6 +22028,158 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E54" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G54" s="17" t="inlineStr">
+        <is>
+          <t>Price↓(56592.0&lt;57126.8) &amp; EMA9↓(57498.0&lt;57620.15)</t>
+        </is>
+      </c>
+      <c r="H54" s="17" t="n">
+        <v>57498</v>
+      </c>
+      <c r="I54" s="17" t="n">
+        <v>57620.15</v>
+      </c>
+      <c r="J54" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K54" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L54" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="M54" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N54" s="17" t="inlineStr">
+        <is>
+          <t>10:21 IST</t>
+        </is>
+      </c>
+      <c r="O54" s="17" t="n">
+        <v>56592</v>
+      </c>
+      <c r="P54" s="17" t="n">
+        <v>57126.8</v>
+      </c>
+      <c r="Q54" s="17" t="inlineStr">
+        <is>
+          <t>56600 PE</t>
+        </is>
+      </c>
+      <c r="R54" s="17" t="inlineStr">
+        <is>
+          <t>56400 PE</t>
+        </is>
+      </c>
+      <c r="S54" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="T54" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U54" s="17" t="n">
+        <v>660</v>
+      </c>
+      <c r="V54" s="17" t="n">
+        <v>72.01000000000001</v>
+      </c>
+      <c r="W54" s="17" t="n">
+        <v>93.61</v>
+      </c>
+      <c r="X54" s="17" t="n">
+        <v>47526.6</v>
+      </c>
+      <c r="Y54" s="17" t="n">
+        <v>47581.28</v>
+      </c>
+      <c r="Z54" s="17" t="n">
+        <v>84473.39999999999</v>
+      </c>
+      <c r="AA54" s="17" t="n">
+        <v>14257.98</v>
+      </c>
+      <c r="AB54" s="17" t="n">
+        <v>14257.98</v>
+      </c>
+      <c r="AC54" s="17" t="n">
+        <v>14256</v>
+      </c>
+      <c r="AD54" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE54" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF54" s="17" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AG54" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH54" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI54" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ54" s="17" t="n">
+        <v>54.68</v>
+      </c>
+      <c r="AK54" s="17" t="n">
+        <v>14201.32</v>
+      </c>
+      <c r="AL54" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM54" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN54" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -21791,7 +22194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN104"/>
+  <dimension ref="A1:AN106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -37463,6 +37866,310 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B105" s="16" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C105" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D105" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E105" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F105" s="16" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G105" s="16" t="inlineStr">
+        <is>
+          <t>Price↓(56592.0&lt;57126.8) &amp; EMA9↓(57498.0&lt;57620.15)</t>
+        </is>
+      </c>
+      <c r="H105" s="16" t="n">
+        <v>57498</v>
+      </c>
+      <c r="I105" s="16" t="n">
+        <v>57620.15</v>
+      </c>
+      <c r="J105" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K105" s="16" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L105" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="M105" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N105" s="16" t="inlineStr">
+        <is>
+          <t>13:51 IST</t>
+        </is>
+      </c>
+      <c r="O105" s="16" t="n">
+        <v>56592</v>
+      </c>
+      <c r="P105" s="16" t="n">
+        <v>57126.8</v>
+      </c>
+      <c r="Q105" s="16" t="inlineStr">
+        <is>
+          <t>56400 CE</t>
+        </is>
+      </c>
+      <c r="R105" s="16" t="inlineStr">
+        <is>
+          <t>56600 CE</t>
+        </is>
+      </c>
+      <c r="S105" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T105" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="U105" s="16" t="n">
+        <v>600</v>
+      </c>
+      <c r="V105" s="16" t="n">
+        <v>79.44</v>
+      </c>
+      <c r="W105" s="16" t="n">
+        <v>78.06</v>
+      </c>
+      <c r="X105" s="16" t="n">
+        <v>47664</v>
+      </c>
+      <c r="Y105" s="16" t="n">
+        <v>47718.7</v>
+      </c>
+      <c r="Z105" s="16" t="n">
+        <v>72336</v>
+      </c>
+      <c r="AA105" s="16" t="n">
+        <v>14299.2</v>
+      </c>
+      <c r="AB105" s="16" t="n">
+        <v>14299.2</v>
+      </c>
+      <c r="AC105" s="16" t="n">
+        <v>-828</v>
+      </c>
+      <c r="AD105" s="16" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="AE105" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF105" s="16" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="AG105" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH105" s="16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI105" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ105" s="16" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="AK105" s="16" t="n">
+        <v>-882.7</v>
+      </c>
+      <c r="AL105" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM105" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN105" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B106" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C106" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D106" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E106" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F106" s="17" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G106" s="17" t="inlineStr">
+        <is>
+          <t>Price↓(56592.0&lt;57126.8) &amp; EMA9↓(57498.0&lt;57620.15)</t>
+        </is>
+      </c>
+      <c r="H106" s="17" t="n">
+        <v>57498</v>
+      </c>
+      <c r="I106" s="17" t="n">
+        <v>57620.15</v>
+      </c>
+      <c r="J106" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K106" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L106" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="M106" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N106" s="17" t="inlineStr">
+        <is>
+          <t>10:17 IST</t>
+        </is>
+      </c>
+      <c r="O106" s="17" t="n">
+        <v>56592</v>
+      </c>
+      <c r="P106" s="17" t="n">
+        <v>57126.8</v>
+      </c>
+      <c r="Q106" s="17" t="inlineStr">
+        <is>
+          <t>56600 PE</t>
+        </is>
+      </c>
+      <c r="R106" s="17" t="inlineStr">
+        <is>
+          <t>56400 PE</t>
+        </is>
+      </c>
+      <c r="S106" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="T106" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U106" s="17" t="n">
+        <v>690</v>
+      </c>
+      <c r="V106" s="17" t="n">
+        <v>70.36</v>
+      </c>
+      <c r="W106" s="17" t="n">
+        <v>91.47</v>
+      </c>
+      <c r="X106" s="17" t="n">
+        <v>48548.4</v>
+      </c>
+      <c r="Y106" s="17" t="n">
+        <v>48603.24</v>
+      </c>
+      <c r="Z106" s="17" t="n">
+        <v>89451.60000000001</v>
+      </c>
+      <c r="AA106" s="17" t="n">
+        <v>14564.52</v>
+      </c>
+      <c r="AB106" s="17" t="n">
+        <v>14564.52</v>
+      </c>
+      <c r="AC106" s="17" t="n">
+        <v>14565.9</v>
+      </c>
+      <c r="AD106" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE106" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF106" s="17" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="AG106" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH106" s="17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI106" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ106" s="17" t="n">
+        <v>54.84</v>
+      </c>
+      <c r="AK106" s="17" t="n">
+        <v>14511.06</v>
+      </c>
+      <c r="AL106" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM106" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN106" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -37477,7 +38184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN24"/>
+  <dimension ref="A1:AN25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -41049,6 +41756,158 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>Price↓(56592.0&lt;57126.8) &amp; EMA9↓(57498.0&lt;57620.15)</t>
+        </is>
+      </c>
+      <c r="H25" s="17" t="n">
+        <v>57498</v>
+      </c>
+      <c r="I25" s="17" t="n">
+        <v>57620.15</v>
+      </c>
+      <c r="J25" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L25" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="M25" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N25" s="17" t="inlineStr">
+        <is>
+          <t>10:00 IST</t>
+        </is>
+      </c>
+      <c r="O25" s="17" t="n">
+        <v>56592</v>
+      </c>
+      <c r="P25" s="17" t="n">
+        <v>57126.8</v>
+      </c>
+      <c r="Q25" s="17" t="inlineStr">
+        <is>
+          <t>56600 PE</t>
+        </is>
+      </c>
+      <c r="R25" s="17" t="inlineStr">
+        <is>
+          <t>56400 PE</t>
+        </is>
+      </c>
+      <c r="S25" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="T25" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U25" s="17" t="n">
+        <v>840</v>
+      </c>
+      <c r="V25" s="17" t="n">
+        <v>57.53</v>
+      </c>
+      <c r="W25" s="17" t="n">
+        <v>74.79000000000001</v>
+      </c>
+      <c r="X25" s="17" t="n">
+        <v>48325.2</v>
+      </c>
+      <c r="Y25" s="17" t="n">
+        <v>48380</v>
+      </c>
+      <c r="Z25" s="17" t="n">
+        <v>119674.8</v>
+      </c>
+      <c r="AA25" s="17" t="n">
+        <v>14497.56</v>
+      </c>
+      <c r="AB25" s="17" t="n">
+        <v>14497.56</v>
+      </c>
+      <c r="AC25" s="17" t="n">
+        <v>14498.4</v>
+      </c>
+      <c r="AD25" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE25" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF25" s="17" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="AG25" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH25" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI25" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ25" s="17" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="AK25" s="17" t="n">
+        <v>14443.6</v>
+      </c>
+      <c r="AL25" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM25" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN25" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -41063,7 +41922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -42929,6 +43788,39 @@
         <v>24080.49</v>
       </c>
       <c r="G57" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B58" s="18" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D58" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="E58" s="18" t="n">
+        <v>24082.85</v>
+      </c>
+      <c r="F58" s="18" t="n">
+        <v>24073.84</v>
+      </c>
+      <c r="G58" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -42948,7 +43840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA53"/>
+  <dimension ref="A1:AA54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -48168,6 +49060,105 @@
         <v>1000</v>
       </c>
       <c r="AA53" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G54" s="17" t="inlineStr">
+        <is>
+          <t>12:42 ET</t>
+        </is>
+      </c>
+      <c r="H54" s="17" t="n">
+        <v>28512.5</v>
+      </c>
+      <c r="I54" s="17" t="n">
+        <v>28500</v>
+      </c>
+      <c r="J54" s="17" t="n">
+        <v>28525</v>
+      </c>
+      <c r="K54" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="L54" s="17" t="n">
+        <v>25.01</v>
+      </c>
+      <c r="M54" s="17" t="n">
+        <v>32.51</v>
+      </c>
+      <c r="N54" s="17" t="n">
+        <v>986.05</v>
+      </c>
+      <c r="O54" s="17" t="n">
+        <v>924.63</v>
+      </c>
+      <c r="P54" s="17" t="n">
+        <v>277.61</v>
+      </c>
+      <c r="Q54" s="17" t="n">
+        <v>277.61</v>
+      </c>
+      <c r="R54" s="17" t="n">
+        <v>277.5</v>
+      </c>
+      <c r="S54" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T54" s="17" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="U54" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="V54" s="17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W54" s="17" t="n">
+        <v>60.68</v>
+      </c>
+      <c r="X54" s="17" t="n">
+        <v>216.82</v>
+      </c>
+      <c r="Y54" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z54" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA54" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -48287,7 +49278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I104"/>
+  <dimension ref="A1:I106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -51922,6 +52913,76 @@
       <c r="I104" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B105" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C105" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D105" s="19" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="E105" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F105" s="19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G105" s="19" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H105" s="19" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I105" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B106" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C106" s="19" t="n">
+        <v>37</v>
+      </c>
+      <c r="D106" s="19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E106" s="19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F106" s="19" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G106" s="19" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="H106" s="19" t="n">
+        <v>60.68</v>
+      </c>
+      <c r="I106" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — PROFIT</t>
         </is>
       </c>
     </row>
@@ -52388,7 +53449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN53"/>
+  <dimension ref="A1:AN54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -60348,6 +61409,158 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E54" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G54" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H54" s="17" t="n">
+        <v>24082.85</v>
+      </c>
+      <c r="I54" s="17" t="n">
+        <v>24073.84</v>
+      </c>
+      <c r="J54" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K54" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L54" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N54" s="17" t="inlineStr">
+        <is>
+          <t>10:08 IST</t>
+        </is>
+      </c>
+      <c r="O54" s="17" t="n">
+        <v>23869.6</v>
+      </c>
+      <c r="P54" s="17" t="n">
+        <v>23996.25</v>
+      </c>
+      <c r="Q54" s="17" t="inlineStr">
+        <is>
+          <t>23800 CE</t>
+        </is>
+      </c>
+      <c r="R54" s="17" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="S54" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="T54" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U54" s="17" t="n">
+        <v>2860</v>
+      </c>
+      <c r="V54" s="17" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="W54" s="17" t="n">
+        <v>21.72</v>
+      </c>
+      <c r="X54" s="17" t="n">
+        <v>47790.6</v>
+      </c>
+      <c r="Y54" s="17" t="n">
+        <v>47845.32</v>
+      </c>
+      <c r="Z54" s="17" t="n">
+        <v>238209.4</v>
+      </c>
+      <c r="AA54" s="17" t="n">
+        <v>14337.18</v>
+      </c>
+      <c r="AB54" s="17" t="n">
+        <v>14337.18</v>
+      </c>
+      <c r="AC54" s="17" t="n">
+        <v>14328.6</v>
+      </c>
+      <c r="AD54" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE54" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF54" s="17" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="AG54" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH54" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI54" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ54" s="17" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="AK54" s="17" t="n">
+        <v>14273.88</v>
+      </c>
+      <c r="AL54" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM54" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN54" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -60362,7 +61575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN53"/>
+  <dimension ref="A1:AN54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -68322,6 +69535,158 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E54" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F54" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G54" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>24082.85</v>
+      </c>
+      <c r="I54" s="15" t="n">
+        <v>24073.84</v>
+      </c>
+      <c r="J54" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K54" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L54" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N54" s="15" t="inlineStr">
+        <is>
+          <t>10:10 IST</t>
+        </is>
+      </c>
+      <c r="O54" s="15" t="n">
+        <v>23869.6</v>
+      </c>
+      <c r="P54" s="15" t="n">
+        <v>23996.25</v>
+      </c>
+      <c r="Q54" s="15" t="inlineStr">
+        <is>
+          <t>23900 PE</t>
+        </is>
+      </c>
+      <c r="R54" s="15" t="inlineStr">
+        <is>
+          <t>23800 PE</t>
+        </is>
+      </c>
+      <c r="S54" s="15" t="n">
+        <v>31</v>
+      </c>
+      <c r="T54" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U54" s="15" t="n">
+        <v>2015</v>
+      </c>
+      <c r="V54" s="15" t="n">
+        <v>23.87</v>
+      </c>
+      <c r="W54" s="15" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="X54" s="15" t="n">
+        <v>48098.05</v>
+      </c>
+      <c r="Y54" s="15" t="n">
+        <v>48152.82</v>
+      </c>
+      <c r="Z54" s="15" t="n">
+        <v>153401.95</v>
+      </c>
+      <c r="AA54" s="15" t="n">
+        <v>14429.42</v>
+      </c>
+      <c r="AB54" s="15" t="n">
+        <v>14429.42</v>
+      </c>
+      <c r="AC54" s="15" t="n">
+        <v>-14427.4</v>
+      </c>
+      <c r="AD54" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE54" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF54" s="15" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="AG54" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH54" s="15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI54" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ54" s="15" t="n">
+        <v>54.77</v>
+      </c>
+      <c r="AK54" s="15" t="n">
+        <v>-14482.17</v>
+      </c>
+      <c r="AL54" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM54" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN54" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -68336,7 +69701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN104"/>
+  <dimension ref="A1:AN106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -84003,6 +85368,310 @@
         <v>50000</v>
       </c>
       <c r="AN104" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B105" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C105" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D105" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E105" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F105" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G105" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H105" s="17" t="n">
+        <v>24082.85</v>
+      </c>
+      <c r="I105" s="17" t="n">
+        <v>24073.84</v>
+      </c>
+      <c r="J105" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K105" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L105" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N105" s="17" t="inlineStr">
+        <is>
+          <t>11:33 IST</t>
+        </is>
+      </c>
+      <c r="O105" s="17" t="n">
+        <v>23869.6</v>
+      </c>
+      <c r="P105" s="17" t="n">
+        <v>23996.25</v>
+      </c>
+      <c r="Q105" s="17" t="inlineStr">
+        <is>
+          <t>23800 CE</t>
+        </is>
+      </c>
+      <c r="R105" s="17" t="inlineStr">
+        <is>
+          <t>23900 CE</t>
+        </is>
+      </c>
+      <c r="S105" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="T105" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U105" s="17" t="n">
+        <v>2470</v>
+      </c>
+      <c r="V105" s="17" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="W105" s="17" t="n">
+        <v>24.93</v>
+      </c>
+      <c r="X105" s="17" t="n">
+        <v>47374.6</v>
+      </c>
+      <c r="Y105" s="17" t="n">
+        <v>47429.25</v>
+      </c>
+      <c r="Z105" s="17" t="n">
+        <v>199625.4</v>
+      </c>
+      <c r="AA105" s="17" t="n">
+        <v>14212.38</v>
+      </c>
+      <c r="AB105" s="17" t="n">
+        <v>14212.38</v>
+      </c>
+      <c r="AC105" s="17" t="n">
+        <v>14202.5</v>
+      </c>
+      <c r="AD105" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE105" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF105" s="17" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="AG105" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH105" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI105" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ105" s="17" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="AK105" s="17" t="n">
+        <v>14147.85</v>
+      </c>
+      <c r="AL105" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM105" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN105" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B106" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C106" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D106" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E106" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F106" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G106" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BEARISH EMA:BULLISH</t>
+        </is>
+      </c>
+      <c r="H106" s="17" t="n">
+        <v>24082.85</v>
+      </c>
+      <c r="I106" s="17" t="n">
+        <v>24073.84</v>
+      </c>
+      <c r="J106" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="K106" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L106" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N106" s="17" t="inlineStr">
+        <is>
+          <t>10:38 IST</t>
+        </is>
+      </c>
+      <c r="O106" s="17" t="n">
+        <v>23869.6</v>
+      </c>
+      <c r="P106" s="17" t="n">
+        <v>23996.25</v>
+      </c>
+      <c r="Q106" s="17" t="inlineStr">
+        <is>
+          <t>23900 PE</t>
+        </is>
+      </c>
+      <c r="R106" s="17" t="inlineStr">
+        <is>
+          <t>23800 PE</t>
+        </is>
+      </c>
+      <c r="S106" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="T106" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U106" s="17" t="n">
+        <v>2275</v>
+      </c>
+      <c r="V106" s="17" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="W106" s="17" t="n">
+        <v>26.99</v>
+      </c>
+      <c r="X106" s="17" t="n">
+        <v>47229</v>
+      </c>
+      <c r="Y106" s="17" t="n">
+        <v>47283.63</v>
+      </c>
+      <c r="Z106" s="17" t="n">
+        <v>180271</v>
+      </c>
+      <c r="AA106" s="17" t="n">
+        <v>14168.7</v>
+      </c>
+      <c r="AB106" s="17" t="n">
+        <v>14168.7</v>
+      </c>
+      <c r="AC106" s="17" t="n">
+        <v>14173.25</v>
+      </c>
+      <c r="AD106" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE106" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF106" s="17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AG106" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH106" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI106" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ106" s="17" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="AK106" s="17" t="n">
+        <v>14118.62</v>
+      </c>
+      <c r="AL106" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM106" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN106" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA54"/>
+  <dimension ref="A1:AA55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5928,6 +5928,105 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C55" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D55" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E55" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="F55" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G55" s="17" t="inlineStr">
+        <is>
+          <t>11:33 ET</t>
+        </is>
+      </c>
+      <c r="H55" s="17" t="n">
+        <v>28526.25</v>
+      </c>
+      <c r="I55" s="17" t="n">
+        <v>28525</v>
+      </c>
+      <c r="J55" s="17" t="n">
+        <v>28550</v>
+      </c>
+      <c r="K55" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L55" s="17" t="n">
+        <v>234.25</v>
+      </c>
+      <c r="M55" s="17" t="n">
+        <v>304.53</v>
+      </c>
+      <c r="N55" s="17" t="n">
+        <v>966.6</v>
+      </c>
+      <c r="O55" s="17" t="n">
+        <v>1063</v>
+      </c>
+      <c r="P55" s="17" t="n">
+        <v>281.1</v>
+      </c>
+      <c r="Q55" s="17" t="n">
+        <v>281.1</v>
+      </c>
+      <c r="R55" s="17" t="n">
+        <v>281.12</v>
+      </c>
+      <c r="S55" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T55" s="17" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="U55" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="V55" s="17" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W55" s="17" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="X55" s="17" t="n">
+        <v>251.52</v>
+      </c>
+      <c r="Y55" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z55" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA55" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -5942,7 +6041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN54"/>
+  <dimension ref="A1:AN55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14054,6 +14153,158 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C55" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D55" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E55" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F55" s="17" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G55" s="17" t="inlineStr">
+        <is>
+          <t>Price↓(56220.4&lt;56592.0) &amp; EMA9↓(57242.74&lt;57517.83)</t>
+        </is>
+      </c>
+      <c r="H55" s="17" t="n">
+        <v>57242.74</v>
+      </c>
+      <c r="I55" s="17" t="n">
+        <v>57517.83</v>
+      </c>
+      <c r="J55" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K55" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L55" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M55" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N55" s="17" t="inlineStr">
+        <is>
+          <t>11:12 IST</t>
+        </is>
+      </c>
+      <c r="O55" s="17" t="n">
+        <v>56220.4</v>
+      </c>
+      <c r="P55" s="17" t="n">
+        <v>56592</v>
+      </c>
+      <c r="Q55" s="17" t="inlineStr">
+        <is>
+          <t>56200 CE</t>
+        </is>
+      </c>
+      <c r="R55" s="17" t="inlineStr">
+        <is>
+          <t>56400 CE</t>
+        </is>
+      </c>
+      <c r="S55" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U55" s="17" t="n">
+        <v>750</v>
+      </c>
+      <c r="V55" s="17" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="W55" s="17" t="n">
+        <v>84.89</v>
+      </c>
+      <c r="X55" s="17" t="n">
+        <v>48975</v>
+      </c>
+      <c r="Y55" s="17" t="n">
+        <v>49029.91</v>
+      </c>
+      <c r="Z55" s="17" t="n">
+        <v>101025</v>
+      </c>
+      <c r="AA55" s="17" t="n">
+        <v>14692.5</v>
+      </c>
+      <c r="AB55" s="17" t="n">
+        <v>14692.5</v>
+      </c>
+      <c r="AC55" s="17" t="n">
+        <v>14692.5</v>
+      </c>
+      <c r="AD55" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE55" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF55" s="17" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="AG55" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH55" s="17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI55" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ55" s="17" t="n">
+        <v>54.91</v>
+      </c>
+      <c r="AK55" s="17" t="n">
+        <v>14637.59</v>
+      </c>
+      <c r="AL55" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM55" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN55" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -14068,7 +14319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN54"/>
+  <dimension ref="A1:AN55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22180,6 +22431,158 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D55" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E55" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F55" s="15" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G55" s="15" t="inlineStr">
+        <is>
+          <t>Price↓(56220.4&lt;56592.0) &amp; EMA9↓(57242.74&lt;57517.83)</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>57242.74</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>57517.83</v>
+      </c>
+      <c r="J55" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K55" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L55" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="M55" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N55" s="15" t="inlineStr">
+        <is>
+          <t>09:37 IST</t>
+        </is>
+      </c>
+      <c r="O55" s="15" t="n">
+        <v>56220.4</v>
+      </c>
+      <c r="P55" s="15" t="n">
+        <v>56592</v>
+      </c>
+      <c r="Q55" s="15" t="inlineStr">
+        <is>
+          <t>56400 PE</t>
+        </is>
+      </c>
+      <c r="R55" s="15" t="inlineStr">
+        <is>
+          <t>56200 PE</t>
+        </is>
+      </c>
+      <c r="S55" s="15" t="n">
+        <v>32</v>
+      </c>
+      <c r="T55" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U55" s="15" t="n">
+        <v>960</v>
+      </c>
+      <c r="V55" s="15" t="n">
+        <v>50.26</v>
+      </c>
+      <c r="W55" s="15" t="n">
+        <v>35.18</v>
+      </c>
+      <c r="X55" s="15" t="n">
+        <v>48249.6</v>
+      </c>
+      <c r="Y55" s="15" t="n">
+        <v>48304.39</v>
+      </c>
+      <c r="Z55" s="15" t="n">
+        <v>143750.4</v>
+      </c>
+      <c r="AA55" s="15" t="n">
+        <v>14474.88</v>
+      </c>
+      <c r="AB55" s="15" t="n">
+        <v>14474.88</v>
+      </c>
+      <c r="AC55" s="15" t="n">
+        <v>-14476.8</v>
+      </c>
+      <c r="AD55" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE55" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF55" s="15" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AG55" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH55" s="15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI55" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ55" s="15" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="AK55" s="15" t="n">
+        <v>-14531.59</v>
+      </c>
+      <c r="AL55" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM55" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN55" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -22194,7 +22597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN106"/>
+  <dimension ref="A1:AN108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -38170,6 +38573,310 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B107" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C107" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D107" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E107" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F107" s="17" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G107" s="17" t="inlineStr">
+        <is>
+          <t>Price↓(56220.4&lt;56592.0) &amp; EMA9↓(57242.74&lt;57517.83)</t>
+        </is>
+      </c>
+      <c r="H107" s="17" t="n">
+        <v>57242.74</v>
+      </c>
+      <c r="I107" s="17" t="n">
+        <v>57517.83</v>
+      </c>
+      <c r="J107" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K107" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L107" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M107" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N107" s="17" t="inlineStr">
+        <is>
+          <t>10:41 IST</t>
+        </is>
+      </c>
+      <c r="O107" s="17" t="n">
+        <v>56220.4</v>
+      </c>
+      <c r="P107" s="17" t="n">
+        <v>56592</v>
+      </c>
+      <c r="Q107" s="17" t="inlineStr">
+        <is>
+          <t>56200 CE</t>
+        </is>
+      </c>
+      <c r="R107" s="17" t="inlineStr">
+        <is>
+          <t>56400 CE</t>
+        </is>
+      </c>
+      <c r="S107" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T107" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U107" s="17" t="n">
+        <v>750</v>
+      </c>
+      <c r="V107" s="17" t="n">
+        <v>64.73999999999999</v>
+      </c>
+      <c r="W107" s="17" t="n">
+        <v>84.16</v>
+      </c>
+      <c r="X107" s="17" t="n">
+        <v>48555</v>
+      </c>
+      <c r="Y107" s="17" t="n">
+        <v>48609.84</v>
+      </c>
+      <c r="Z107" s="17" t="n">
+        <v>101445</v>
+      </c>
+      <c r="AA107" s="17" t="n">
+        <v>14566.5</v>
+      </c>
+      <c r="AB107" s="17" t="n">
+        <v>14566.5</v>
+      </c>
+      <c r="AC107" s="17" t="n">
+        <v>14565</v>
+      </c>
+      <c r="AD107" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE107" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF107" s="17" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="AG107" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH107" s="17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI107" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ107" s="17" t="n">
+        <v>54.84</v>
+      </c>
+      <c r="AK107" s="17" t="n">
+        <v>14510.16</v>
+      </c>
+      <c r="AL107" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM107" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN107" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B108" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C108" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D108" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E108" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F108" s="15" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G108" s="15" t="inlineStr">
+        <is>
+          <t>Price↓(56220.4&lt;56592.0) &amp; EMA9↓(57242.74&lt;57517.83)</t>
+        </is>
+      </c>
+      <c r="H108" s="15" t="n">
+        <v>57242.74</v>
+      </c>
+      <c r="I108" s="15" t="n">
+        <v>57517.83</v>
+      </c>
+      <c r="J108" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K108" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L108" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="M108" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N108" s="15" t="inlineStr">
+        <is>
+          <t>09:37 IST</t>
+        </is>
+      </c>
+      <c r="O108" s="15" t="n">
+        <v>56220.4</v>
+      </c>
+      <c r="P108" s="15" t="n">
+        <v>56592</v>
+      </c>
+      <c r="Q108" s="15" t="inlineStr">
+        <is>
+          <t>56400 PE</t>
+        </is>
+      </c>
+      <c r="R108" s="15" t="inlineStr">
+        <is>
+          <t>56200 PE</t>
+        </is>
+      </c>
+      <c r="S108" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="T108" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U108" s="15" t="n">
+        <v>840</v>
+      </c>
+      <c r="V108" s="15" t="n">
+        <v>58.18</v>
+      </c>
+      <c r="W108" s="15" t="n">
+        <v>40.73</v>
+      </c>
+      <c r="X108" s="15" t="n">
+        <v>48871.2</v>
+      </c>
+      <c r="Y108" s="15" t="n">
+        <v>48926.09</v>
+      </c>
+      <c r="Z108" s="15" t="n">
+        <v>119128.8</v>
+      </c>
+      <c r="AA108" s="15" t="n">
+        <v>14661.36</v>
+      </c>
+      <c r="AB108" s="15" t="n">
+        <v>14661.36</v>
+      </c>
+      <c r="AC108" s="15" t="n">
+        <v>-14658</v>
+      </c>
+      <c r="AD108" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE108" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF108" s="15" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="AG108" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH108" s="15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI108" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ108" s="15" t="n">
+        <v>54.89</v>
+      </c>
+      <c r="AK108" s="15" t="n">
+        <v>-14712.89</v>
+      </c>
+      <c r="AL108" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM108" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN108" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -38184,7 +38891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN25"/>
+  <dimension ref="A1:AN26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -41908,6 +42615,158 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr">
+        <is>
+          <t>Price↓(56220.4&lt;56592.0) &amp; EMA9↓(57242.74&lt;57517.83)</t>
+        </is>
+      </c>
+      <c r="H26" s="17" t="n">
+        <v>57242.74</v>
+      </c>
+      <c r="I26" s="17" t="n">
+        <v>57517.83</v>
+      </c>
+      <c r="J26" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K26" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L26" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M26" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N26" s="17" t="inlineStr">
+        <is>
+          <t>10:17 IST</t>
+        </is>
+      </c>
+      <c r="O26" s="17" t="n">
+        <v>56220.4</v>
+      </c>
+      <c r="P26" s="17" t="n">
+        <v>56592</v>
+      </c>
+      <c r="Q26" s="17" t="inlineStr">
+        <is>
+          <t>56400 PE</t>
+        </is>
+      </c>
+      <c r="R26" s="17" t="inlineStr">
+        <is>
+          <t>56200 PE</t>
+        </is>
+      </c>
+      <c r="S26" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="T26" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U26" s="17" t="n">
+        <v>840</v>
+      </c>
+      <c r="V26" s="17" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="W26" s="17" t="n">
+        <v>73.31999999999999</v>
+      </c>
+      <c r="X26" s="17" t="n">
+        <v>47376</v>
+      </c>
+      <c r="Y26" s="17" t="n">
+        <v>47430.66</v>
+      </c>
+      <c r="Z26" s="17" t="n">
+        <v>120624</v>
+      </c>
+      <c r="AA26" s="17" t="n">
+        <v>14212.8</v>
+      </c>
+      <c r="AB26" s="17" t="n">
+        <v>14212.8</v>
+      </c>
+      <c r="AC26" s="17" t="n">
+        <v>14212.8</v>
+      </c>
+      <c r="AD26" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE26" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF26" s="17" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="AG26" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH26" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI26" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ26" s="17" t="n">
+        <v>54.66</v>
+      </c>
+      <c r="AK26" s="17" t="n">
+        <v>14158.14</v>
+      </c>
+      <c r="AL26" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM26" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN26" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -43840,7 +44699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA54"/>
+  <dimension ref="A1:AA55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -49159,6 +50018,105 @@
         <v>1000</v>
       </c>
       <c r="AA54" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B55" s="16" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D55" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E55" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="F55" s="16" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G55" s="16" t="inlineStr">
+        <is>
+          <t>15:46 ET</t>
+        </is>
+      </c>
+      <c r="H55" s="16" t="n">
+        <v>28526</v>
+      </c>
+      <c r="I55" s="16" t="n">
+        <v>28525</v>
+      </c>
+      <c r="J55" s="16" t="n">
+        <v>28550</v>
+      </c>
+      <c r="K55" s="16" t="n">
+        <v>39</v>
+      </c>
+      <c r="L55" s="16" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="M55" s="16" t="n">
+        <v>22.91</v>
+      </c>
+      <c r="N55" s="16" t="n">
+        <v>996.84</v>
+      </c>
+      <c r="O55" s="16" t="n">
+        <v>1017.12</v>
+      </c>
+      <c r="P55" s="16" t="n">
+        <v>279.86</v>
+      </c>
+      <c r="Q55" s="16" t="n">
+        <v>279.86</v>
+      </c>
+      <c r="R55" s="16" t="n">
+        <v>-39.39</v>
+      </c>
+      <c r="S55" s="16" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="T55" s="16" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="U55" s="16" t="n">
+        <v>39</v>
+      </c>
+      <c r="V55" s="16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W55" s="16" t="n">
+        <v>63.96</v>
+      </c>
+      <c r="X55" s="16" t="n">
+        <v>-103.35</v>
+      </c>
+      <c r="Y55" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="Z55" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA55" s="16" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -49278,7 +50236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:I108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -52983,6 +53941,76 @@
       <c r="I106" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B107" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C107" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D107" s="19" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="E107" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F107" s="19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G107" s="19" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H107" s="19" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I107" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — PROFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B108" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C108" s="19" t="n">
+        <v>39</v>
+      </c>
+      <c r="D108" s="19" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="E108" s="19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F108" s="19" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G108" s="19" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="H108" s="19" t="n">
+        <v>63.96</v>
+      </c>
+      <c r="I108" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — FLAT</t>
         </is>
       </c>
     </row>
@@ -53449,7 +54477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN54"/>
+  <dimension ref="A1:AN55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -61561,6 +62589,158 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D55" s="15" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E55" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F55" s="15" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G55" s="15" t="inlineStr">
+        <is>
+          <t>Price↓(23682.7&lt;23869.6) &amp; EMA9↓(24003.16&lt;24047.82)</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>24003.16</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>24047.82</v>
+      </c>
+      <c r="J55" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K55" s="15" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L55" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="M55" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N55" s="15" t="inlineStr">
+        <is>
+          <t>10:25 IST</t>
+        </is>
+      </c>
+      <c r="O55" s="15" t="n">
+        <v>23682.7</v>
+      </c>
+      <c r="P55" s="15" t="n">
+        <v>23869.6</v>
+      </c>
+      <c r="Q55" s="15" t="inlineStr">
+        <is>
+          <t>23600 CE</t>
+        </is>
+      </c>
+      <c r="R55" s="15" t="inlineStr">
+        <is>
+          <t>23700 CE</t>
+        </is>
+      </c>
+      <c r="S55" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="T55" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="U55" s="15" t="n">
+        <v>1235</v>
+      </c>
+      <c r="V55" s="15" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="W55" s="15" t="n">
+        <v>26.68</v>
+      </c>
+      <c r="X55" s="15" t="n">
+        <v>47065.85</v>
+      </c>
+      <c r="Y55" s="15" t="n">
+        <v>47120.46</v>
+      </c>
+      <c r="Z55" s="15" t="n">
+        <v>76434.14999999999</v>
+      </c>
+      <c r="AA55" s="15" t="n">
+        <v>14119.75</v>
+      </c>
+      <c r="AB55" s="15" t="n">
+        <v>14119.75</v>
+      </c>
+      <c r="AC55" s="15" t="n">
+        <v>-14116.05</v>
+      </c>
+      <c r="AD55" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE55" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF55" s="15" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="AG55" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH55" s="15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI55" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ55" s="15" t="n">
+        <v>54.61</v>
+      </c>
+      <c r="AK55" s="15" t="n">
+        <v>-14170.66</v>
+      </c>
+      <c r="AL55" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM55" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN55" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -61575,7 +62755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN54"/>
+  <dimension ref="A1:AN55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -69687,6 +70867,158 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C55" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D55" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E55" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F55" s="17" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G55" s="17" t="inlineStr">
+        <is>
+          <t>Price↓(23682.7&lt;23869.6) &amp; EMA9↓(24003.16&lt;24047.82)</t>
+        </is>
+      </c>
+      <c r="H55" s="17" t="n">
+        <v>24003.16</v>
+      </c>
+      <c r="I55" s="17" t="n">
+        <v>24047.82</v>
+      </c>
+      <c r="J55" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K55" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L55" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M55" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N55" s="17" t="inlineStr">
+        <is>
+          <t>12:05 IST</t>
+        </is>
+      </c>
+      <c r="O55" s="17" t="n">
+        <v>23682.7</v>
+      </c>
+      <c r="P55" s="17" t="n">
+        <v>23869.6</v>
+      </c>
+      <c r="Q55" s="17" t="inlineStr">
+        <is>
+          <t>23700 PE</t>
+        </is>
+      </c>
+      <c r="R55" s="17" t="inlineStr">
+        <is>
+          <t>23600 PE</t>
+        </is>
+      </c>
+      <c r="S55" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="T55" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U55" s="17" t="n">
+        <v>1235</v>
+      </c>
+      <c r="V55" s="17" t="n">
+        <v>39.22</v>
+      </c>
+      <c r="W55" s="17" t="n">
+        <v>50.99</v>
+      </c>
+      <c r="X55" s="17" t="n">
+        <v>48436.7</v>
+      </c>
+      <c r="Y55" s="17" t="n">
+        <v>48491.52</v>
+      </c>
+      <c r="Z55" s="17" t="n">
+        <v>75063.3</v>
+      </c>
+      <c r="AA55" s="17" t="n">
+        <v>14531.01</v>
+      </c>
+      <c r="AB55" s="17" t="n">
+        <v>14531.01</v>
+      </c>
+      <c r="AC55" s="17" t="n">
+        <v>14535.95</v>
+      </c>
+      <c r="AD55" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE55" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF55" s="17" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AG55" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH55" s="17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI55" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ55" s="17" t="n">
+        <v>54.82</v>
+      </c>
+      <c r="AK55" s="17" t="n">
+        <v>14481.13</v>
+      </c>
+      <c r="AL55" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM55" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN55" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -69701,7 +71033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN106"/>
+  <dimension ref="A1:AN108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -85677,6 +87009,310 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B107" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C107" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D107" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E107" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F107" s="17" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G107" s="17" t="inlineStr">
+        <is>
+          <t>Price↓(23682.7&lt;23869.6) &amp; EMA9↓(24003.16&lt;24047.82)</t>
+        </is>
+      </c>
+      <c r="H107" s="17" t="n">
+        <v>24003.16</v>
+      </c>
+      <c r="I107" s="17" t="n">
+        <v>24047.82</v>
+      </c>
+      <c r="J107" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K107" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L107" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M107" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N107" s="17" t="inlineStr">
+        <is>
+          <t>11:08 IST</t>
+        </is>
+      </c>
+      <c r="O107" s="17" t="n">
+        <v>23682.7</v>
+      </c>
+      <c r="P107" s="17" t="n">
+        <v>23869.6</v>
+      </c>
+      <c r="Q107" s="17" t="inlineStr">
+        <is>
+          <t>23600 CE</t>
+        </is>
+      </c>
+      <c r="R107" s="17" t="inlineStr">
+        <is>
+          <t>23700 CE</t>
+        </is>
+      </c>
+      <c r="S107" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="T107" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U107" s="17" t="n">
+        <v>1235</v>
+      </c>
+      <c r="V107" s="17" t="n">
+        <v>37.86</v>
+      </c>
+      <c r="W107" s="17" t="n">
+        <v>49.22</v>
+      </c>
+      <c r="X107" s="17" t="n">
+        <v>46757.1</v>
+      </c>
+      <c r="Y107" s="17" t="n">
+        <v>46811.66</v>
+      </c>
+      <c r="Z107" s="17" t="n">
+        <v>76742.89999999999</v>
+      </c>
+      <c r="AA107" s="17" t="n">
+        <v>14027.13</v>
+      </c>
+      <c r="AB107" s="17" t="n">
+        <v>14027.13</v>
+      </c>
+      <c r="AC107" s="17" t="n">
+        <v>14029.6</v>
+      </c>
+      <c r="AD107" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE107" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF107" s="17" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="AG107" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH107" s="17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI107" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ107" s="17" t="n">
+        <v>54.56</v>
+      </c>
+      <c r="AK107" s="17" t="n">
+        <v>13975.04</v>
+      </c>
+      <c r="AL107" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM107" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN107" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B108" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C108" s="16" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D108" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E108" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F108" s="16" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G108" s="16" t="inlineStr">
+        <is>
+          <t>Price↓(23682.7&lt;23869.6) &amp; EMA9↓(24003.16&lt;24047.82)</t>
+        </is>
+      </c>
+      <c r="H108" s="16" t="n">
+        <v>24003.16</v>
+      </c>
+      <c r="I108" s="16" t="n">
+        <v>24047.82</v>
+      </c>
+      <c r="J108" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K108" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L108" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="M108" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N108" s="16" t="inlineStr">
+        <is>
+          <t>13:36 IST</t>
+        </is>
+      </c>
+      <c r="O108" s="16" t="n">
+        <v>23682.7</v>
+      </c>
+      <c r="P108" s="16" t="n">
+        <v>23869.6</v>
+      </c>
+      <c r="Q108" s="16" t="inlineStr">
+        <is>
+          <t>23700 PE</t>
+        </is>
+      </c>
+      <c r="R108" s="16" t="inlineStr">
+        <is>
+          <t>23600 PE</t>
+        </is>
+      </c>
+      <c r="S108" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="T108" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U108" s="16" t="n">
+        <v>1755</v>
+      </c>
+      <c r="V108" s="16" t="n">
+        <v>26.98</v>
+      </c>
+      <c r="W108" s="16" t="n">
+        <v>27.72</v>
+      </c>
+      <c r="X108" s="16" t="n">
+        <v>47349.9</v>
+      </c>
+      <c r="Y108" s="16" t="n">
+        <v>47404.55</v>
+      </c>
+      <c r="Z108" s="16" t="n">
+        <v>128150.1</v>
+      </c>
+      <c r="AA108" s="16" t="n">
+        <v>14204.97</v>
+      </c>
+      <c r="AB108" s="16" t="n">
+        <v>14204.97</v>
+      </c>
+      <c r="AC108" s="16" t="n">
+        <v>1298.7</v>
+      </c>
+      <c r="AD108" s="16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE108" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF108" s="16" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="AG108" s="16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH108" s="16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI108" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ108" s="16" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="AK108" s="16" t="n">
+        <v>1244.05</v>
+      </c>
+      <c r="AL108" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM108" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN108" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -85691,7 +87327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN27"/>
+  <dimension ref="A1:AN28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -89724,6 +91360,158 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E28" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G28" s="16" t="inlineStr">
+        <is>
+          <t>Price↓(23682.7&lt;23869.6) &amp; EMA9↓(24003.16&lt;24047.82)</t>
+        </is>
+      </c>
+      <c r="H28" s="16" t="n">
+        <v>24003.16</v>
+      </c>
+      <c r="I28" s="16" t="n">
+        <v>24047.82</v>
+      </c>
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K28" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L28" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="M28" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N28" s="16" t="inlineStr">
+        <is>
+          <t>13:29 IST</t>
+        </is>
+      </c>
+      <c r="O28" s="16" t="n">
+        <v>23682.7</v>
+      </c>
+      <c r="P28" s="16" t="n">
+        <v>23869.6</v>
+      </c>
+      <c r="Q28" s="16" t="inlineStr">
+        <is>
+          <t>23700 PE</t>
+        </is>
+      </c>
+      <c r="R28" s="16" t="inlineStr">
+        <is>
+          <t>23600 PE</t>
+        </is>
+      </c>
+      <c r="S28" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="T28" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U28" s="16" t="n">
+        <v>1495</v>
+      </c>
+      <c r="V28" s="16" t="n">
+        <v>32.24</v>
+      </c>
+      <c r="W28" s="16" t="n">
+        <v>32.48</v>
+      </c>
+      <c r="X28" s="16" t="n">
+        <v>48198.8</v>
+      </c>
+      <c r="Y28" s="16" t="n">
+        <v>48253.58</v>
+      </c>
+      <c r="Z28" s="16" t="n">
+        <v>101301.2</v>
+      </c>
+      <c r="AA28" s="16" t="n">
+        <v>14459.64</v>
+      </c>
+      <c r="AB28" s="16" t="n">
+        <v>14459.64</v>
+      </c>
+      <c r="AC28" s="16" t="n">
+        <v>358.8</v>
+      </c>
+      <c r="AD28" s="16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AE28" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF28" s="16" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="AG28" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH28" s="16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI28" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ28" s="16" t="n">
+        <v>54.78</v>
+      </c>
+      <c r="AK28" s="16" t="n">
+        <v>304.02</v>
+      </c>
+      <c r="AL28" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM28" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN28" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA55"/>
+  <dimension ref="A1:AA56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6027,6 +6027,105 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B56" s="16" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D56" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E56" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="F56" s="16" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G56" s="16" t="inlineStr">
+        <is>
+          <t>16:04 ET</t>
+        </is>
+      </c>
+      <c r="H56" s="16" t="n">
+        <v>28493</v>
+      </c>
+      <c r="I56" s="16" t="n">
+        <v>28475</v>
+      </c>
+      <c r="J56" s="16" t="n">
+        <v>28500</v>
+      </c>
+      <c r="K56" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L56" s="16" t="n">
+        <v>244.01</v>
+      </c>
+      <c r="M56" s="16" t="n">
+        <v>233.87</v>
+      </c>
+      <c r="N56" s="16" t="n">
+        <v>754.23</v>
+      </c>
+      <c r="O56" s="16" t="n">
+        <v>767.97</v>
+      </c>
+      <c r="P56" s="16" t="n">
+        <v>219.61</v>
+      </c>
+      <c r="Q56" s="16" t="n">
+        <v>219.61</v>
+      </c>
+      <c r="R56" s="16" t="n">
+        <v>-30.42</v>
+      </c>
+      <c r="S56" s="16" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="T56" s="16" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="U56" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="V56" s="16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W56" s="16" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="X56" s="16" t="n">
+        <v>-52.62</v>
+      </c>
+      <c r="Y56" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="Z56" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA56" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AA1"/>
@@ -6041,7 +6140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN55"/>
+  <dimension ref="A1:AN56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14305,6 +14404,158 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D56" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G56" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BULLISH EMA:BEARISH</t>
+        </is>
+      </c>
+      <c r="H56" s="17" t="n">
+        <v>57337.36</v>
+      </c>
+      <c r="I56" s="17" t="n">
+        <v>57560.84</v>
+      </c>
+      <c r="J56" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K56" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L56" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M56" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N56" s="17" t="inlineStr">
+        <is>
+          <t>12:18 IST</t>
+        </is>
+      </c>
+      <c r="O56" s="17" t="n">
+        <v>56693.5</v>
+      </c>
+      <c r="P56" s="17" t="n">
+        <v>56592</v>
+      </c>
+      <c r="Q56" s="17" t="inlineStr">
+        <is>
+          <t>56600 CE</t>
+        </is>
+      </c>
+      <c r="R56" s="17" t="inlineStr">
+        <is>
+          <t>56800 CE</t>
+        </is>
+      </c>
+      <c r="S56" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T56" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U56" s="17" t="n">
+        <v>600</v>
+      </c>
+      <c r="V56" s="17" t="n">
+        <v>79.97</v>
+      </c>
+      <c r="W56" s="17" t="n">
+        <v>103.96</v>
+      </c>
+      <c r="X56" s="17" t="n">
+        <v>47982</v>
+      </c>
+      <c r="Y56" s="17" t="n">
+        <v>48036.75</v>
+      </c>
+      <c r="Z56" s="17" t="n">
+        <v>72018</v>
+      </c>
+      <c r="AA56" s="17" t="n">
+        <v>14394.6</v>
+      </c>
+      <c r="AB56" s="17" t="n">
+        <v>14394.6</v>
+      </c>
+      <c r="AC56" s="17" t="n">
+        <v>14394</v>
+      </c>
+      <c r="AD56" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE56" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF56" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG56" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH56" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI56" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ56" s="17" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="AK56" s="17" t="n">
+        <v>14339.25</v>
+      </c>
+      <c r="AL56" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM56" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN56" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -14319,7 +14570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN55"/>
+  <dimension ref="A1:AN56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22583,6 +22834,158 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D56" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G56" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BULLISH EMA:BEARISH</t>
+        </is>
+      </c>
+      <c r="H56" s="17" t="n">
+        <v>57337.36</v>
+      </c>
+      <c r="I56" s="17" t="n">
+        <v>57560.84</v>
+      </c>
+      <c r="J56" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K56" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L56" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M56" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N56" s="17" t="inlineStr">
+        <is>
+          <t>11:39 IST</t>
+        </is>
+      </c>
+      <c r="O56" s="17" t="n">
+        <v>56693.5</v>
+      </c>
+      <c r="P56" s="17" t="n">
+        <v>56592</v>
+      </c>
+      <c r="Q56" s="17" t="inlineStr">
+        <is>
+          <t>56800 PE</t>
+        </is>
+      </c>
+      <c r="R56" s="17" t="inlineStr">
+        <is>
+          <t>56600 PE</t>
+        </is>
+      </c>
+      <c r="S56" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="T56" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U56" s="17" t="n">
+        <v>690</v>
+      </c>
+      <c r="V56" s="17" t="n">
+        <v>68.34999999999999</v>
+      </c>
+      <c r="W56" s="17" t="n">
+        <v>88.84999999999999</v>
+      </c>
+      <c r="X56" s="17" t="n">
+        <v>47161.5</v>
+      </c>
+      <c r="Y56" s="17" t="n">
+        <v>47216.12</v>
+      </c>
+      <c r="Z56" s="17" t="n">
+        <v>90838.5</v>
+      </c>
+      <c r="AA56" s="17" t="n">
+        <v>14148.45</v>
+      </c>
+      <c r="AB56" s="17" t="n">
+        <v>14148.45</v>
+      </c>
+      <c r="AC56" s="17" t="n">
+        <v>14145</v>
+      </c>
+      <c r="AD56" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE56" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF56" s="17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AG56" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH56" s="17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI56" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ56" s="17" t="n">
+        <v>54.62</v>
+      </c>
+      <c r="AK56" s="17" t="n">
+        <v>14090.38</v>
+      </c>
+      <c r="AL56" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM56" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN56" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -22597,7 +23000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN108"/>
+  <dimension ref="A1:AN110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -38872,6 +39275,310 @@
         <v>50000</v>
       </c>
       <c r="AN108" s="15" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B109" s="17" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C109" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D109" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E109" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F109" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G109" s="17" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BULLISH EMA:BEARISH</t>
+        </is>
+      </c>
+      <c r="H109" s="17" t="n">
+        <v>57337.36</v>
+      </c>
+      <c r="I109" s="17" t="n">
+        <v>57560.84</v>
+      </c>
+      <c r="J109" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K109" s="17" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L109" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M109" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N109" s="17" t="inlineStr">
+        <is>
+          <t>11:08 IST</t>
+        </is>
+      </c>
+      <c r="O109" s="17" t="n">
+        <v>56693.5</v>
+      </c>
+      <c r="P109" s="17" t="n">
+        <v>56592</v>
+      </c>
+      <c r="Q109" s="17" t="inlineStr">
+        <is>
+          <t>56600 CE</t>
+        </is>
+      </c>
+      <c r="R109" s="17" t="inlineStr">
+        <is>
+          <t>56800 CE</t>
+        </is>
+      </c>
+      <c r="S109" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="T109" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="U109" s="17" t="n">
+        <v>630</v>
+      </c>
+      <c r="V109" s="17" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="W109" s="17" t="n">
+        <v>97.37</v>
+      </c>
+      <c r="X109" s="17" t="n">
+        <v>47187</v>
+      </c>
+      <c r="Y109" s="17" t="n">
+        <v>47241.63</v>
+      </c>
+      <c r="Z109" s="17" t="n">
+        <v>78813</v>
+      </c>
+      <c r="AA109" s="17" t="n">
+        <v>14156.1</v>
+      </c>
+      <c r="AB109" s="17" t="n">
+        <v>14156.1</v>
+      </c>
+      <c r="AC109" s="17" t="n">
+        <v>14156.1</v>
+      </c>
+      <c r="AD109" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE109" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF109" s="17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AG109" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH109" s="17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI109" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ109" s="17" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="AK109" s="17" t="n">
+        <v>14101.47</v>
+      </c>
+      <c r="AL109" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM109" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN109" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B110" s="15" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C110" s="15" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D110" s="15" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E110" s="15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F110" s="15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="G110" s="15" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BULLISH EMA:BEARISH</t>
+        </is>
+      </c>
+      <c r="H110" s="15" t="n">
+        <v>57337.36</v>
+      </c>
+      <c r="I110" s="15" t="n">
+        <v>57560.84</v>
+      </c>
+      <c r="J110" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K110" s="15" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="L110" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="M110" s="15" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N110" s="15" t="inlineStr">
+        <is>
+          <t>10:15 IST</t>
+        </is>
+      </c>
+      <c r="O110" s="15" t="n">
+        <v>56693.5</v>
+      </c>
+      <c r="P110" s="15" t="n">
+        <v>56592</v>
+      </c>
+      <c r="Q110" s="15" t="inlineStr">
+        <is>
+          <t>56800 PE</t>
+        </is>
+      </c>
+      <c r="R110" s="15" t="inlineStr">
+        <is>
+          <t>56600 PE</t>
+        </is>
+      </c>
+      <c r="S110" s="15" t="n">
+        <v>26</v>
+      </c>
+      <c r="T110" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="U110" s="15" t="n">
+        <v>780</v>
+      </c>
+      <c r="V110" s="15" t="n">
+        <v>62.17</v>
+      </c>
+      <c r="W110" s="15" t="n">
+        <v>43.52</v>
+      </c>
+      <c r="X110" s="15" t="n">
+        <v>48492.6</v>
+      </c>
+      <c r="Y110" s="15" t="n">
+        <v>48547.43</v>
+      </c>
+      <c r="Z110" s="15" t="n">
+        <v>107507.4</v>
+      </c>
+      <c r="AA110" s="15" t="n">
+        <v>14547.78</v>
+      </c>
+      <c r="AB110" s="15" t="n">
+        <v>14547.78</v>
+      </c>
+      <c r="AC110" s="15" t="n">
+        <v>-14547</v>
+      </c>
+      <c r="AD110" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AE110" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF110" s="15" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="AG110" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH110" s="15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI110" s="15" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ110" s="15" t="n">
+        <v>54.83</v>
+      </c>
+      <c r="AK110" s="15" t="n">
+        <v>-14601.83</v>
+      </c>
+      <c r="AL110" s="15" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="AM110" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN110" s="15" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -42781,7 +43488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -44680,6 +45387,39 @@
         <v>24073.84</v>
       </c>
       <c r="G58" s="18" t="inlineStr">
+        <is>
+          <t>NO TRADE — Conflicting signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B59" s="18" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="D59" s="18" t="inlineStr">
+        <is>
+          <t>Conflicting — Price:BULLISH EMA:BEARISH</t>
+        </is>
+      </c>
+      <c r="E59" s="18" t="n">
+        <v>57337.36</v>
+      </c>
+      <c r="F59" s="18" t="n">
+        <v>57560.84</v>
+      </c>
+      <c r="G59" s="18" t="inlineStr">
         <is>
           <t>NO TRADE — Conflicting signals</t>
         </is>
@@ -44699,7 +45439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA55"/>
+  <dimension ref="A1:AA56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -50117,6 +50857,105 @@
         <v>1000</v>
       </c>
       <c r="AA55" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D56" s="17" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E56" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
+        <is>
+          <t>10:00 ET</t>
+        </is>
+      </c>
+      <c r="G56" s="17" t="inlineStr">
+        <is>
+          <t>11:52 ET</t>
+        </is>
+      </c>
+      <c r="H56" s="17" t="n">
+        <v>28492.5</v>
+      </c>
+      <c r="I56" s="17" t="n">
+        <v>28475</v>
+      </c>
+      <c r="J56" s="17" t="n">
+        <v>28500</v>
+      </c>
+      <c r="K56" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="L56" s="17" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="M56" s="17" t="n">
+        <v>26.68</v>
+      </c>
+      <c r="N56" s="17" t="n">
+        <v>997.2</v>
+      </c>
+      <c r="O56" s="17" t="n">
+        <v>1326.6</v>
+      </c>
+      <c r="P56" s="17" t="n">
+        <v>277.02</v>
+      </c>
+      <c r="Q56" s="17" t="n">
+        <v>277.02</v>
+      </c>
+      <c r="R56" s="17" t="n">
+        <v>277.2</v>
+      </c>
+      <c r="S56" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T56" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="U56" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="V56" s="17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W56" s="17" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="X56" s="17" t="n">
+        <v>203.4</v>
+      </c>
+      <c r="Y56" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="Z56" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA56" s="17" t="inlineStr">
         <is>
           <t>PAPER TRADING</t>
         </is>
@@ -50236,7 +51075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I108"/>
+  <dimension ref="A1:I110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -54011,6 +54850,76 @@
       <c r="I108" s="19" t="inlineStr">
         <is>
           <t>MNQ Bull Call Spread — FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B109" s="19" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="C109" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D109" s="19" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="E109" s="19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F109" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G109" s="19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H109" s="19" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="I109" s="19" t="inlineStr">
+        <is>
+          <t>NQ Bull Call Spread — FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B110" s="19" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="C110" s="19" t="n">
+        <v>45</v>
+      </c>
+      <c r="D110" s="19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E110" s="19" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F110" s="19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G110" s="19" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="H110" s="19" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="I110" s="19" t="inlineStr">
+        <is>
+          <t>MNQ Bull Call Spread — PROFIT</t>
         </is>
       </c>
     </row>
@@ -54477,7 +55386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN55"/>
+  <dimension ref="A1:AN56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -62741,6 +63650,158 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="D56" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G56" s="17" t="inlineStr">
+        <is>
+          <t>Price↓(23767.45&lt;23869.6) &amp; EMA9↓(24020.11&lt;24055.52)</t>
+        </is>
+      </c>
+      <c r="H56" s="17" t="n">
+        <v>24020.11</v>
+      </c>
+      <c r="I56" s="17" t="n">
+        <v>24055.52</v>
+      </c>
+      <c r="J56" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K56" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L56" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M56" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N56" s="17" t="inlineStr">
+        <is>
+          <t>10:21 IST</t>
+        </is>
+      </c>
+      <c r="O56" s="17" t="n">
+        <v>23767.45</v>
+      </c>
+      <c r="P56" s="17" t="n">
+        <v>23869.6</v>
+      </c>
+      <c r="Q56" s="17" t="inlineStr">
+        <is>
+          <t>23700 CE</t>
+        </is>
+      </c>
+      <c r="R56" s="17" t="inlineStr">
+        <is>
+          <t>23800 CE</t>
+        </is>
+      </c>
+      <c r="S56" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T56" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U56" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="V56" s="17" t="n">
+        <v>36.21</v>
+      </c>
+      <c r="W56" s="17" t="n">
+        <v>47.07</v>
+      </c>
+      <c r="X56" s="17" t="n">
+        <v>47073</v>
+      </c>
+      <c r="Y56" s="17" t="n">
+        <v>47127.61</v>
+      </c>
+      <c r="Z56" s="17" t="n">
+        <v>82927</v>
+      </c>
+      <c r="AA56" s="17" t="n">
+        <v>14121.9</v>
+      </c>
+      <c r="AB56" s="17" t="n">
+        <v>14121.9</v>
+      </c>
+      <c r="AC56" s="17" t="n">
+        <v>14118</v>
+      </c>
+      <c r="AD56" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE56" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF56" s="17" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="AG56" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AH56" s="17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI56" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ56" s="17" t="n">
+        <v>54.61</v>
+      </c>
+      <c r="AK56" s="17" t="n">
+        <v>14063.39</v>
+      </c>
+      <c r="AL56" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM56" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN56" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -62755,7 +63816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN55"/>
+  <dimension ref="A1:AN56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -71019,6 +72080,158 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B56" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="D56" s="16" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E56" s="16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F56" s="16" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G56" s="16" t="inlineStr">
+        <is>
+          <t>Price↓(23767.45&lt;23869.6) &amp; EMA9↓(24020.11&lt;24055.52)</t>
+        </is>
+      </c>
+      <c r="H56" s="16" t="n">
+        <v>24020.11</v>
+      </c>
+      <c r="I56" s="16" t="n">
+        <v>24055.52</v>
+      </c>
+      <c r="J56" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K56" s="16" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L56" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="M56" s="16" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N56" s="16" t="inlineStr">
+        <is>
+          <t>14:38 IST</t>
+        </is>
+      </c>
+      <c r="O56" s="16" t="n">
+        <v>23767.45</v>
+      </c>
+      <c r="P56" s="16" t="n">
+        <v>23869.6</v>
+      </c>
+      <c r="Q56" s="16" t="inlineStr">
+        <is>
+          <t>23800 PE</t>
+        </is>
+      </c>
+      <c r="R56" s="16" t="inlineStr">
+        <is>
+          <t>23700 PE</t>
+        </is>
+      </c>
+      <c r="S56" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="T56" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="U56" s="16" t="n">
+        <v>1430</v>
+      </c>
+      <c r="V56" s="16" t="n">
+        <v>33.23</v>
+      </c>
+      <c r="W56" s="16" t="n">
+        <v>32.42</v>
+      </c>
+      <c r="X56" s="16" t="n">
+        <v>47518.9</v>
+      </c>
+      <c r="Y56" s="16" t="n">
+        <v>47573.58</v>
+      </c>
+      <c r="Z56" s="16" t="n">
+        <v>95481.10000000001</v>
+      </c>
+      <c r="AA56" s="16" t="n">
+        <v>14255.67</v>
+      </c>
+      <c r="AB56" s="16" t="n">
+        <v>14255.67</v>
+      </c>
+      <c r="AC56" s="16" t="n">
+        <v>-1158.3</v>
+      </c>
+      <c r="AD56" s="16" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="AE56" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF56" s="16" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AG56" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH56" s="16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI56" s="16" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ56" s="16" t="n">
+        <v>54.68</v>
+      </c>
+      <c r="AK56" s="16" t="n">
+        <v>-1212.98</v>
+      </c>
+      <c r="AL56" s="16" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+      <c r="AM56" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN56" s="16" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -71033,7 +72246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN108"/>
+  <dimension ref="A1:AN110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -87313,6 +88526,310 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B109" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C109" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D109" s="17" t="inlineStr">
+        <is>
+          <t>Bull Call Spread</t>
+        </is>
+      </c>
+      <c r="E109" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F109" s="17" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G109" s="17" t="inlineStr">
+        <is>
+          <t>Price↓(23767.45&lt;23869.6) &amp; EMA9↓(24020.11&lt;24055.52)</t>
+        </is>
+      </c>
+      <c r="H109" s="17" t="n">
+        <v>24020.11</v>
+      </c>
+      <c r="I109" s="17" t="n">
+        <v>24055.52</v>
+      </c>
+      <c r="J109" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K109" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L109" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M109" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N109" s="17" t="inlineStr">
+        <is>
+          <t>11:58 IST</t>
+        </is>
+      </c>
+      <c r="O109" s="17" t="n">
+        <v>23767.45</v>
+      </c>
+      <c r="P109" s="17" t="n">
+        <v>23869.6</v>
+      </c>
+      <c r="Q109" s="17" t="inlineStr">
+        <is>
+          <t>23700 CE</t>
+        </is>
+      </c>
+      <c r="R109" s="17" t="inlineStr">
+        <is>
+          <t>23800 CE</t>
+        </is>
+      </c>
+      <c r="S109" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="T109" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U109" s="17" t="n">
+        <v>1430</v>
+      </c>
+      <c r="V109" s="17" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="W109" s="17" t="n">
+        <v>44.34</v>
+      </c>
+      <c r="X109" s="17" t="n">
+        <v>48777.3</v>
+      </c>
+      <c r="Y109" s="17" t="n">
+        <v>48832.18</v>
+      </c>
+      <c r="Z109" s="17" t="n">
+        <v>94222.7</v>
+      </c>
+      <c r="AA109" s="17" t="n">
+        <v>14633.19</v>
+      </c>
+      <c r="AB109" s="17" t="n">
+        <v>14633.19</v>
+      </c>
+      <c r="AC109" s="17" t="n">
+        <v>14628.9</v>
+      </c>
+      <c r="AD109" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE109" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF109" s="17" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AG109" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH109" s="17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI109" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ109" s="17" t="n">
+        <v>54.88</v>
+      </c>
+      <c r="AK109" s="17" t="n">
+        <v>14574.02</v>
+      </c>
+      <c r="AL109" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM109" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN109" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B110" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C110" s="17" t="inlineStr">
+        <is>
+          <t>Both Spreads</t>
+        </is>
+      </c>
+      <c r="D110" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E110" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F110" s="17" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G110" s="17" t="inlineStr">
+        <is>
+          <t>Price↓(23767.45&lt;23869.6) &amp; EMA9↓(24020.11&lt;24055.52)</t>
+        </is>
+      </c>
+      <c r="H110" s="17" t="n">
+        <v>24020.11</v>
+      </c>
+      <c r="I110" s="17" t="n">
+        <v>24055.52</v>
+      </c>
+      <c r="J110" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K110" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L110" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M110" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N110" s="17" t="inlineStr">
+        <is>
+          <t>10:16 IST</t>
+        </is>
+      </c>
+      <c r="O110" s="17" t="n">
+        <v>23767.45</v>
+      </c>
+      <c r="P110" s="17" t="n">
+        <v>23869.6</v>
+      </c>
+      <c r="Q110" s="17" t="inlineStr">
+        <is>
+          <t>23800 PE</t>
+        </is>
+      </c>
+      <c r="R110" s="17" t="inlineStr">
+        <is>
+          <t>23700 PE</t>
+        </is>
+      </c>
+      <c r="S110" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T110" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U110" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="V110" s="17" t="n">
+        <v>37.78</v>
+      </c>
+      <c r="W110" s="17" t="n">
+        <v>49.11</v>
+      </c>
+      <c r="X110" s="17" t="n">
+        <v>49114</v>
+      </c>
+      <c r="Y110" s="17" t="n">
+        <v>49168.93</v>
+      </c>
+      <c r="Z110" s="17" t="n">
+        <v>80886</v>
+      </c>
+      <c r="AA110" s="17" t="n">
+        <v>14734.2</v>
+      </c>
+      <c r="AB110" s="17" t="n">
+        <v>14734.2</v>
+      </c>
+      <c r="AC110" s="17" t="n">
+        <v>14729</v>
+      </c>
+      <c r="AD110" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE110" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF110" s="17" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="AG110" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH110" s="17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI110" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ110" s="17" t="n">
+        <v>54.93</v>
+      </c>
+      <c r="AK110" s="17" t="n">
+        <v>14674.07</v>
+      </c>
+      <c r="AL110" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM110" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN110" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
@@ -87327,7 +88844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN28"/>
+  <dimension ref="A1:AN29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -91512,6 +93029,158 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>Smart Trend</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>Bear Put Spread</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="inlineStr">
+        <is>
+          <t>Price↓(23767.45&lt;23869.6) &amp; EMA9↓(24020.11&lt;24055.52)</t>
+        </is>
+      </c>
+      <c r="H29" s="17" t="n">
+        <v>24020.11</v>
+      </c>
+      <c r="I29" s="17" t="n">
+        <v>24055.52</v>
+      </c>
+      <c r="J29" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="K29" s="17" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="L29" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M29" s="17" t="inlineStr">
+        <is>
+          <t>09:20 IST</t>
+        </is>
+      </c>
+      <c r="N29" s="17" t="inlineStr">
+        <is>
+          <t>11:46 IST</t>
+        </is>
+      </c>
+      <c r="O29" s="17" t="n">
+        <v>23767.45</v>
+      </c>
+      <c r="P29" s="17" t="n">
+        <v>23869.6</v>
+      </c>
+      <c r="Q29" s="17" t="inlineStr">
+        <is>
+          <t>23800 PE</t>
+        </is>
+      </c>
+      <c r="R29" s="17" t="inlineStr">
+        <is>
+          <t>23700 PE</t>
+        </is>
+      </c>
+      <c r="S29" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="U29" s="17" t="n">
+        <v>1625</v>
+      </c>
+      <c r="V29" s="17" t="n">
+        <v>30.12</v>
+      </c>
+      <c r="W29" s="17" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="X29" s="17" t="n">
+        <v>48945</v>
+      </c>
+      <c r="Y29" s="17" t="n">
+        <v>48999.9</v>
+      </c>
+      <c r="Z29" s="17" t="n">
+        <v>113555</v>
+      </c>
+      <c r="AA29" s="17" t="n">
+        <v>14683.5</v>
+      </c>
+      <c r="AB29" s="17" t="n">
+        <v>14683.5</v>
+      </c>
+      <c r="AC29" s="17" t="n">
+        <v>14690</v>
+      </c>
+      <c r="AD29" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE29" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF29" s="17" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="AG29" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH29" s="17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI29" s="17" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AJ29" s="17" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="AK29" s="17" t="n">
+        <v>14635.1</v>
+      </c>
+      <c r="AL29" s="17" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="AM29" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AN29" s="17" t="inlineStr">
+        <is>
+          <t>PAPER TRADING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AM1"/>
